--- a/Results_metrics.xlsx
+++ b/Results_metrics.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10608"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gaiac\Desktop\polito\machine learning\MaskArchitectureAnomaly_CourseProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ludovicascaffidi/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBBAE0C2-040C-4EF5-9BB8-8D24FF91C5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{97CD21E5-FC13-4B46-BD38-AFD038FE757F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="11480" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="31">
   <si>
     <t>Model</t>
   </si>
@@ -113,6 +124,12 @@
   <si>
     <t>t = 10</t>
   </si>
+  <si>
+    <t>t = 0,75</t>
+  </si>
+  <si>
+    <t>t = 1,1</t>
+  </si>
 </sst>
 </file>
 
@@ -149,7 +166,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -186,6 +203,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="31">
     <border>
@@ -593,7 +616,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
@@ -619,6 +642,17 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -661,16 +695,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -808,9 +832,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$23</c:f>
+              <c:f>Foglio1!$B$17:$B$27</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -818,49 +842,73 @@
                   <c:v>t = 0,5</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>t = 0,75</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>t = 0,8</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>t = 1</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
+                  <c:v>t = 1,1</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>t = 1,2</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>t = 1,5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>t = 2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>t = 5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$D$17:$D$23</c:f>
+              <c:f>Foglio1!$D$17:$D$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>34.270000000000003</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>53.99</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>58.57</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>61.18</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>63.39</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>64.27</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>65.13</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>67.64</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>75.12</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>83.89</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>85.11</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -912,9 +960,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$23</c:f>
+              <c:f>Foglio1!$B$17:$B$27</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -922,49 +970,73 @@
                   <c:v>t = 0,5</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>t = 0,75</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>t = 0,8</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>t = 1</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
+                  <c:v>t = 1,1</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>t = 1,2</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>t = 1,5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>t = 2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>t = 5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$E$17:$E$23</c:f>
+              <c:f>Foglio1!$E$17:$E$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>91.9</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>30.4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>28.7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>28.37</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>27.09</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>26.47</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>25.89</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>24.33</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.82</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.91</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.97</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1247,7 +1319,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1255,6 +1326,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1409,9 +1481,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$23</c:f>
+              <c:f>Foglio1!$B$17:$B$27</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -1419,49 +1491,73 @@
                   <c:v>t = 0,5</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>t = 0,75</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>t = 0,8</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>t = 1</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
+                  <c:v>t = 1,1</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>t = 1,2</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>t = 1,5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>t = 2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>t = 5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$F$17:$F$23</c:f>
+              <c:f>Foglio1!$F$17:$F$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>33.96</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>75.69</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>78.45</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>79.010000000000005</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>81.23</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>82.27</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>82.23</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>85.54</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>88.34</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>91.31</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>91.42</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1513,9 +1609,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$23</c:f>
+              <c:f>Foglio1!$B$17:$B$27</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -1523,49 +1619,73 @@
                   <c:v>t = 0,5</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>t = 0,75</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>t = 0,8</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>t = 1</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
+                  <c:v>t = 1,1</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>t = 1,2</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>t = 1,5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>t = 2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>t = 5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$G$17:$G$23</c:f>
+              <c:f>Foglio1!$G$17:$G$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>91.77</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>25.6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>16.760000000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>16.16</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>13.23</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>10.1</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>9.0399999999999991</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10.210000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>11.92</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>17.89</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>21.24</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1848,7 +1968,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1856,6 +1975,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2010,9 +2130,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$23</c:f>
+              <c:f>Foglio1!$B$17:$B$27</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -2020,49 +2140,73 @@
                   <c:v>t = 0,5</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>t = 0,75</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>t = 0,8</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>t = 1</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
+                  <c:v>t = 1,1</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>t = 1,2</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>t = 1,5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>t = 2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>t = 5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$H$17:$H$23</c:f>
+              <c:f>Foglio1!$H$17:$H$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1.08</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>2.44</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>2.82</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>2.91</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>3.33</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>3.58</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>3.84</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.7699999999999996</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.37</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.97</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7.86</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2114,9 +2258,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$23</c:f>
+              <c:f>Foglio1!$B$17:$B$27</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -2124,49 +2268,73 @@
                   <c:v>t = 0,5</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>t = 0,75</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>t = 0,8</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>t = 1</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
+                  <c:v>t = 1,1</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>t = 1,2</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>t = 1,5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>t = 2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>t = 5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$I$17:$I$23</c:f>
+              <c:f>Foglio1!$I$17:$I$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>92.89</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>53.79</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>30.87</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>30.88</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>31.26</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>31.28</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>31.17</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>31.85</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>32.71</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>34.31</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>34.380000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2449,7 +2617,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2457,6 +2624,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2611,9 +2779,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$23</c:f>
+              <c:f>Foglio1!$B$17:$B$27</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -2621,49 +2789,73 @@
                   <c:v>t = 0,5</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>t = 0,75</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>t = 0,8</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>t = 1</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
+                  <c:v>t = 1,1</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>t = 1,2</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>t = 1,5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>t = 2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>t = 5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$J$17:$J$23</c:f>
+              <c:f>Foglio1!$J$17:$J$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>4.4800000000000004</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>8.73</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>9.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>9.6300000000000008</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>10.29</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>10.68</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>11.13</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>12.55</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14.47</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>15.64</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>15.65</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2715,9 +2907,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$23</c:f>
+              <c:f>Foglio1!$B$17:$B$27</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -2725,49 +2917,73 @@
                   <c:v>t = 0,5</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>t = 0,75</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>t = 0,8</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>t = 1</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
+                  <c:v>t = 1,1</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>t = 1,2</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>t = 1,5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>t = 2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>t = 5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$K$17:$K$23</c:f>
+              <c:f>Foglio1!$K$17:$K$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>93.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>74.12</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>55.77</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>54.26</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>55.32</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>56.7</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>56.71</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>57.72</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>57.57</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>55.85</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>55.84</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3050,7 +3266,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3058,6 +3273,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3212,9 +3428,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$23</c:f>
+              <c:f>Foglio1!$B$17:$B$27</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -3222,29 +3438,41 @@
                   <c:v>t = 0,5</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>t = 0,75</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>t = 0,8</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>t = 1</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
+                  <c:v>t = 1,1</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>t = 1,2</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>t = 1,5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>t = 2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>t = 5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$L$17:$L$23</c:f>
+              <c:f>Foglio1!$L$17:$L$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>27.36</c:v>
                 </c:pt>
@@ -3252,19 +3480,31 @@
                   <c:v>43.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>47.11</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>47.69</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>49.86</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
+                  <c:v>50.72</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>51.47</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>53.18</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>54.85</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>56.42</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>56.43</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3316,9 +3556,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$23</c:f>
+              <c:f>Foglio1!$B$17:$B$27</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -3326,29 +3566,41 @@
                   <c:v>t = 0,5</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>t = 0,75</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>t = 0,8</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>t = 1</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
+                  <c:v>t = 1,1</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>t = 1,2</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>t = 1,5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>t = 2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>t = 5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$M$17:$M$23</c:f>
+              <c:f>Foglio1!$M$17:$M$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>91.26</c:v>
                 </c:pt>
@@ -3356,19 +3608,31 @@
                   <c:v>51.58</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>46.41</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>46.22</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>44.63</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
+                  <c:v>44.22</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>43.53</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>42.7</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>41.58</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>39.4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>40.380000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3651,7 +3915,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3659,6 +3922,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6456,7 +6720,7 @@
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>503787</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>41331</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6488,13 +6752,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>318304</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>173621</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>146903</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>12396</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6526,13 +6790,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>414760</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>163975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>310878</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>2750</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6564,13 +6828,13 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>598026</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>173621</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>494143</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>12396</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6864,55 +7128,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:O27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B1:O28"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="14.54296875" customWidth="1"/>
-    <col min="3" max="3" width="13.08984375" customWidth="1"/>
+    <col min="2" max="2" width="14.5" customWidth="1"/>
+    <col min="3" max="3" width="13.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="25" t="s">
+    <row r="1" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="27"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="38"/>
     </row>
-    <row r="3" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="5"/>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="29"/>
-      <c r="F3" s="28" t="s">
+      <c r="E3" s="40"/>
+      <c r="F3" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="29"/>
-      <c r="H3" s="28" t="s">
+      <c r="G3" s="40"/>
+      <c r="H3" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="29"/>
-      <c r="J3" s="28" t="s">
+      <c r="I3" s="40"/>
+      <c r="J3" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="29"/>
-      <c r="L3" s="28" t="s">
+      <c r="K3" s="40"/>
+      <c r="L3" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="29"/>
+      <c r="M3" s="40"/>
     </row>
-    <row r="4" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
         <v>0</v>
       </c>
@@ -6950,8 +7214,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B5" s="30" t="s">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B5" s="41" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -6988,44 +7252,44 @@
         <v>82.58</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B6" s="31"/>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B6" s="42"/>
       <c r="C6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="46">
+      <c r="D6" s="31">
         <v>38.32</v>
       </c>
-      <c r="E6" s="47">
+      <c r="E6" s="32">
         <v>59.34</v>
       </c>
-      <c r="F6" s="46">
+      <c r="F6" s="31">
         <v>4.63</v>
       </c>
-      <c r="G6" s="47">
+      <c r="G6" s="32">
         <v>48.44</v>
       </c>
-      <c r="H6" s="46">
+      <c r="H6" s="31">
         <v>3.3</v>
       </c>
-      <c r="I6" s="47">
+      <c r="I6" s="32">
         <v>45.49</v>
       </c>
-      <c r="J6" s="46">
+      <c r="J6" s="31">
         <v>9.5</v>
       </c>
-      <c r="K6" s="47">
+      <c r="K6" s="32">
         <v>40.299999999999997</v>
       </c>
-      <c r="L6" s="46">
+      <c r="L6" s="31">
         <v>15.58</v>
       </c>
-      <c r="M6" s="47">
+      <c r="M6" s="32">
         <v>73.25</v>
       </c>
     </row>
-    <row r="7" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="32"/>
+    <row r="7" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="43"/>
       <c r="C7" s="11" t="s">
         <v>12</v>
       </c>
@@ -7060,21 +7324,37 @@
         <v>82.75</v>
       </c>
     </row>
-    <row r="8" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="33" t="s">
+    <row r="8" spans="2:13" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="44" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="20"/>
+      <c r="D8" s="19">
+        <v>63.4</v>
+      </c>
+      <c r="E8" s="20">
+        <v>27.09</v>
+      </c>
+      <c r="F8" s="19">
+        <v>80.95</v>
+      </c>
+      <c r="G8" s="20">
+        <v>14.95</v>
+      </c>
+      <c r="H8" s="19">
+        <v>3.33</v>
+      </c>
+      <c r="I8" s="20">
+        <v>31.26</v>
+      </c>
+      <c r="J8" s="19">
+        <v>10.37</v>
+      </c>
+      <c r="K8" s="20">
+        <v>55.49</v>
+      </c>
       <c r="L8" s="19">
         <v>49.87</v>
       </c>
@@ -7082,19 +7362,35 @@
         <v>44.62</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B9" s="31"/>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B9" s="42"/>
       <c r="C9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="16"/>
+      <c r="D9" s="15">
+        <v>73.989999999999995</v>
+      </c>
+      <c r="E9" s="16">
+        <v>33.9</v>
+      </c>
+      <c r="F9" s="15">
+        <v>90.05</v>
+      </c>
+      <c r="G9" s="16">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="H9" s="15">
+        <v>25.44</v>
+      </c>
+      <c r="I9" s="16">
+        <v>14.65</v>
+      </c>
+      <c r="J9" s="15">
+        <v>54.41</v>
+      </c>
+      <c r="K9" s="16">
+        <v>34.57</v>
+      </c>
       <c r="L9" s="15">
         <v>75.150000000000006</v>
       </c>
@@ -7102,19 +7398,35 @@
         <v>19.09</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B10" s="31"/>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B10" s="42"/>
       <c r="C10" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="16"/>
+      <c r="D10" s="15">
+        <v>66.59</v>
+      </c>
+      <c r="E10" s="16">
+        <v>26.18</v>
+      </c>
+      <c r="F10" s="15">
+        <v>84.36</v>
+      </c>
+      <c r="G10" s="16">
+        <v>11.95</v>
+      </c>
+      <c r="H10" s="15">
+        <v>5.58</v>
+      </c>
+      <c r="I10" s="16">
+        <v>31.27</v>
+      </c>
+      <c r="J10" s="15">
+        <v>13.74</v>
+      </c>
+      <c r="K10" s="16">
+        <v>56.77</v>
+      </c>
       <c r="L10" s="15">
         <v>53.55</v>
       </c>
@@ -7122,19 +7434,35 @@
         <v>44.12</v>
       </c>
     </row>
-    <row r="11" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="34"/>
+    <row r="11" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="45"/>
       <c r="C11" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="21"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="22"/>
+      <c r="D11" s="21">
+        <v>76.45</v>
+      </c>
+      <c r="E11" s="22">
+        <v>33.119999999999997</v>
+      </c>
+      <c r="F11" s="21">
+        <v>89.87</v>
+      </c>
+      <c r="G11" s="22">
+        <v>1.2</v>
+      </c>
+      <c r="H11" s="21">
+        <v>27.97</v>
+      </c>
+      <c r="I11" s="22">
+        <v>13.8</v>
+      </c>
+      <c r="J11" s="21">
+        <v>54.34</v>
+      </c>
+      <c r="K11" s="22">
+        <v>32.880000000000003</v>
+      </c>
       <c r="L11" s="21">
         <v>77.73</v>
       </c>
@@ -7142,435 +7470,504 @@
         <v>17.579999999999998</v>
       </c>
     </row>
-    <row r="13" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="25" t="s">
+    <row r="13" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="35"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="36"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="47"/>
     </row>
-    <row r="15" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="24"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="28" t="s">
+      <c r="D15" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="28" t="s">
+      <c r="E15" s="40"/>
+      <c r="F15" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="29"/>
-      <c r="H15" s="28" t="s">
+      <c r="G15" s="40"/>
+      <c r="H15" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="29"/>
-      <c r="J15" s="28" t="s">
+      <c r="I15" s="40"/>
+      <c r="J15" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="29"/>
-      <c r="L15" s="28" t="s">
+      <c r="K15" s="40"/>
+      <c r="L15" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="M15" s="29"/>
+      <c r="M15" s="40"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B16" s="40" t="s">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B16" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="41" t="s">
+      <c r="C16" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="42" t="s">
+      <c r="D16" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="43" t="s">
+      <c r="E16" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="42" t="s">
+      <c r="F16" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="G16" s="43" t="s">
+      <c r="G16" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="H16" s="42" t="s">
+      <c r="H16" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="I16" s="43" t="s">
+      <c r="I16" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="J16" s="42" t="s">
+      <c r="J16" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="K16" s="43" t="s">
+      <c r="K16" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="L16" s="42" t="s">
+      <c r="L16" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="M16" s="43" t="s">
+      <c r="M16" s="28" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B17" s="44" t="s">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B17" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45">
-        <v>0</v>
-      </c>
-      <c r="E17" s="45">
-        <v>0</v>
-      </c>
-      <c r="F17" s="45">
-        <v>0</v>
-      </c>
-      <c r="G17" s="45">
-        <v>0</v>
-      </c>
-      <c r="H17" s="45">
-        <v>0</v>
-      </c>
-      <c r="I17" s="45">
-        <v>0</v>
-      </c>
-      <c r="J17" s="45">
-        <v>0</v>
-      </c>
-      <c r="K17" s="45">
-        <v>0</v>
-      </c>
-      <c r="L17" s="45">
+      <c r="C17" s="30"/>
+      <c r="D17" s="30">
+        <v>34.270000000000003</v>
+      </c>
+      <c r="E17" s="30">
+        <v>91.9</v>
+      </c>
+      <c r="F17" s="30">
+        <v>33.96</v>
+      </c>
+      <c r="G17" s="30">
+        <v>91.77</v>
+      </c>
+      <c r="H17" s="30">
+        <v>1.08</v>
+      </c>
+      <c r="I17" s="30">
+        <v>92.89</v>
+      </c>
+      <c r="J17" s="30">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="K17" s="30">
+        <v>93.5</v>
+      </c>
+      <c r="L17" s="30">
         <v>27.36</v>
       </c>
-      <c r="M17" s="45">
+      <c r="M17" s="30">
         <v>91.26</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B18" s="44" t="s">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B18" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45">
-        <v>0</v>
-      </c>
-      <c r="E18" s="45">
-        <v>0</v>
-      </c>
-      <c r="F18" s="45">
-        <v>0</v>
-      </c>
-      <c r="G18" s="45">
-        <v>0</v>
-      </c>
-      <c r="H18" s="45">
-        <v>0</v>
-      </c>
-      <c r="I18" s="45">
-        <v>0</v>
-      </c>
-      <c r="J18" s="45">
-        <v>0</v>
-      </c>
-      <c r="K18" s="45">
-        <v>0</v>
-      </c>
-      <c r="L18" s="45">
+      <c r="C18" s="34"/>
+      <c r="D18" s="34">
+        <v>53.99</v>
+      </c>
+      <c r="E18" s="34">
+        <v>30.4</v>
+      </c>
+      <c r="F18" s="34">
+        <v>75.69</v>
+      </c>
+      <c r="G18" s="34">
+        <v>25.6</v>
+      </c>
+      <c r="H18" s="34">
+        <v>2.44</v>
+      </c>
+      <c r="I18" s="34">
+        <v>53.79</v>
+      </c>
+      <c r="J18" s="34">
+        <v>8.73</v>
+      </c>
+      <c r="K18" s="34">
+        <v>74.12</v>
+      </c>
+      <c r="L18" s="34">
         <v>43.75</v>
       </c>
-      <c r="M18" s="45">
+      <c r="M18" s="34">
         <v>51.58</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B19" s="44" t="s">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B19" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34">
+        <v>58.57</v>
+      </c>
+      <c r="E19" s="34">
+        <v>28.7</v>
+      </c>
+      <c r="F19" s="34">
+        <v>78.45</v>
+      </c>
+      <c r="G19" s="34">
+        <v>16.760000000000002</v>
+      </c>
+      <c r="H19" s="34">
+        <v>2.82</v>
+      </c>
+      <c r="I19" s="34">
+        <v>30.87</v>
+      </c>
+      <c r="J19" s="34">
+        <v>9.5</v>
+      </c>
+      <c r="K19" s="34">
+        <v>55.77</v>
+      </c>
+      <c r="L19" s="34">
+        <v>47.11</v>
+      </c>
+      <c r="M19" s="34">
+        <v>46.41</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B20" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45">
-        <v>0</v>
-      </c>
-      <c r="E19" s="45">
-        <v>0</v>
-      </c>
-      <c r="F19" s="45">
-        <v>0</v>
-      </c>
-      <c r="G19" s="45">
-        <v>0</v>
-      </c>
-      <c r="H19" s="45">
-        <v>0</v>
-      </c>
-      <c r="I19" s="45">
-        <v>0</v>
-      </c>
-      <c r="J19" s="45">
-        <v>0</v>
-      </c>
-      <c r="K19" s="45">
-        <v>0</v>
-      </c>
-      <c r="L19" s="45">
+      <c r="C20" s="30"/>
+      <c r="D20" s="30">
+        <v>61.18</v>
+      </c>
+      <c r="E20" s="30">
+        <v>28.37</v>
+      </c>
+      <c r="F20" s="30">
+        <v>79.010000000000005</v>
+      </c>
+      <c r="G20" s="30">
+        <v>16.16</v>
+      </c>
+      <c r="H20" s="30">
+        <v>2.91</v>
+      </c>
+      <c r="I20" s="30">
+        <v>30.88</v>
+      </c>
+      <c r="J20" s="30">
+        <v>9.6300000000000008</v>
+      </c>
+      <c r="K20" s="30">
+        <v>54.26</v>
+      </c>
+      <c r="L20" s="30">
         <v>47.69</v>
       </c>
-      <c r="M19" s="45">
+      <c r="M20" s="30">
         <v>46.22</v>
       </c>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B20" s="44" t="s">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B21" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45">
-        <v>0</v>
-      </c>
-      <c r="E20" s="45">
-        <v>0</v>
-      </c>
-      <c r="F20" s="45">
-        <v>0</v>
-      </c>
-      <c r="G20" s="45">
-        <v>0</v>
-      </c>
-      <c r="H20" s="45">
-        <v>0</v>
-      </c>
-      <c r="I20" s="45">
-        <v>0</v>
-      </c>
-      <c r="J20" s="45">
-        <v>0</v>
-      </c>
-      <c r="K20" s="45">
-        <v>0</v>
-      </c>
-      <c r="L20" s="45">
+      <c r="C21" s="30"/>
+      <c r="D21" s="30">
+        <v>63.39</v>
+      </c>
+      <c r="E21" s="30">
+        <v>27.09</v>
+      </c>
+      <c r="F21" s="35">
+        <v>81.23</v>
+      </c>
+      <c r="G21" s="30">
+        <v>13.23</v>
+      </c>
+      <c r="H21" s="30">
+        <v>3.33</v>
+      </c>
+      <c r="I21" s="30">
+        <v>31.26</v>
+      </c>
+      <c r="J21" s="30">
+        <v>10.29</v>
+      </c>
+      <c r="K21" s="30">
+        <v>55.32</v>
+      </c>
+      <c r="L21" s="30">
         <v>49.86</v>
       </c>
-      <c r="M20" s="45">
+      <c r="M21" s="30">
         <v>44.63</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B21" s="44" t="s">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B22" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34">
+        <v>64.27</v>
+      </c>
+      <c r="E22" s="34">
+        <v>26.47</v>
+      </c>
+      <c r="F22" s="34">
+        <v>82.27</v>
+      </c>
+      <c r="G22" s="34">
+        <v>10.1</v>
+      </c>
+      <c r="H22" s="34">
+        <v>3.58</v>
+      </c>
+      <c r="I22" s="34">
+        <v>31.28</v>
+      </c>
+      <c r="J22" s="34">
+        <v>10.68</v>
+      </c>
+      <c r="K22" s="34">
+        <v>56.7</v>
+      </c>
+      <c r="L22" s="34">
+        <v>50.72</v>
+      </c>
+      <c r="M22" s="34">
+        <v>44.22</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B23" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45">
-        <v>0</v>
-      </c>
-      <c r="E21" s="45">
-        <v>0</v>
-      </c>
-      <c r="F21" s="45">
-        <v>0</v>
-      </c>
-      <c r="G21" s="45">
-        <v>0</v>
-      </c>
-      <c r="H21" s="45">
-        <v>0</v>
-      </c>
-      <c r="I21" s="45">
-        <v>0</v>
-      </c>
-      <c r="J21" s="45">
-        <v>0</v>
-      </c>
-      <c r="K21" s="45">
-        <v>0</v>
-      </c>
-      <c r="L21" s="45">
+      <c r="C23" s="30"/>
+      <c r="D23" s="30">
+        <v>65.13</v>
+      </c>
+      <c r="E23" s="30">
+        <v>25.89</v>
+      </c>
+      <c r="F23" s="30">
+        <v>82.23</v>
+      </c>
+      <c r="G23" s="30">
+        <v>9.0399999999999991</v>
+      </c>
+      <c r="H23" s="30">
+        <v>3.84</v>
+      </c>
+      <c r="I23" s="30">
+        <v>31.17</v>
+      </c>
+      <c r="J23" s="30">
+        <v>11.13</v>
+      </c>
+      <c r="K23" s="30">
+        <v>56.71</v>
+      </c>
+      <c r="L23" s="30">
         <v>51.47</v>
       </c>
-      <c r="M21" s="45">
+      <c r="M23" s="30">
         <v>43.53</v>
       </c>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B22" s="44" t="s">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B24" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45">
-        <v>0</v>
-      </c>
-      <c r="E22" s="45">
-        <v>0</v>
-      </c>
-      <c r="F22" s="45">
-        <v>0</v>
-      </c>
-      <c r="G22" s="45">
-        <v>0</v>
-      </c>
-      <c r="H22" s="45">
-        <v>0</v>
-      </c>
-      <c r="I22" s="45">
-        <v>0</v>
-      </c>
-      <c r="J22" s="45">
-        <v>0</v>
-      </c>
-      <c r="K22" s="45">
-        <v>0</v>
-      </c>
-      <c r="L22" s="45">
+      <c r="C24" s="30"/>
+      <c r="D24" s="30">
+        <v>67.64</v>
+      </c>
+      <c r="E24" s="30">
+        <v>24.33</v>
+      </c>
+      <c r="F24" s="30">
+        <v>85.54</v>
+      </c>
+      <c r="G24" s="30">
+        <v>10.210000000000001</v>
+      </c>
+      <c r="H24" s="30">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="I24" s="30">
+        <v>31.85</v>
+      </c>
+      <c r="J24" s="30">
+        <v>12.55</v>
+      </c>
+      <c r="K24" s="30">
+        <v>57.72</v>
+      </c>
+      <c r="L24" s="30">
         <v>53.18</v>
       </c>
-      <c r="M22" s="45">
+      <c r="M24" s="30">
         <v>42.7</v>
       </c>
-      <c r="O22" s="48"/>
+      <c r="O24" s="33"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B23" s="44" t="s">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B25" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45">
-        <v>0</v>
-      </c>
-      <c r="E23" s="45">
-        <v>0</v>
-      </c>
-      <c r="F23" s="45">
-        <v>0</v>
-      </c>
-      <c r="G23" s="45">
-        <v>0</v>
-      </c>
-      <c r="H23" s="45">
-        <v>0</v>
-      </c>
-      <c r="I23" s="45">
-        <v>0</v>
-      </c>
-      <c r="J23" s="45">
-        <v>0</v>
-      </c>
-      <c r="K23" s="45">
-        <v>0</v>
-      </c>
-      <c r="L23" s="45">
+      <c r="C25" s="30"/>
+      <c r="D25" s="30">
+        <v>75.12</v>
+      </c>
+      <c r="E25" s="30">
+        <v>9.82</v>
+      </c>
+      <c r="F25" s="30">
+        <v>88.34</v>
+      </c>
+      <c r="G25" s="30">
+        <v>11.92</v>
+      </c>
+      <c r="H25" s="30">
+        <v>6.37</v>
+      </c>
+      <c r="I25" s="30">
+        <v>32.71</v>
+      </c>
+      <c r="J25" s="30">
+        <v>14.47</v>
+      </c>
+      <c r="K25" s="30">
+        <v>57.57</v>
+      </c>
+      <c r="L25" s="30">
         <v>54.85</v>
       </c>
-      <c r="M23" s="45">
+      <c r="M25" s="30">
         <v>41.58</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B24" s="44" t="s">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B26" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45">
-        <v>0</v>
-      </c>
-      <c r="E24" s="45">
-        <v>0</v>
-      </c>
-      <c r="F24" s="45">
-        <v>0</v>
-      </c>
-      <c r="G24" s="45">
-        <v>0</v>
-      </c>
-      <c r="H24" s="45">
-        <v>0</v>
-      </c>
-      <c r="I24" s="45">
-        <v>0</v>
-      </c>
-      <c r="J24" s="45">
-        <v>0</v>
-      </c>
-      <c r="K24" s="45">
-        <v>0</v>
-      </c>
-      <c r="L24" s="45">
+      <c r="C26" s="30"/>
+      <c r="D26" s="30">
+        <v>83.89</v>
+      </c>
+      <c r="E26" s="30">
+        <v>3.91</v>
+      </c>
+      <c r="F26" s="30">
+        <v>91.31</v>
+      </c>
+      <c r="G26" s="30">
+        <v>17.89</v>
+      </c>
+      <c r="H26" s="30">
+        <v>7.97</v>
+      </c>
+      <c r="I26" s="30">
+        <v>34.31</v>
+      </c>
+      <c r="J26" s="30">
+        <v>15.64</v>
+      </c>
+      <c r="K26" s="30">
+        <v>55.85</v>
+      </c>
+      <c r="L26" s="30">
         <v>56.42</v>
       </c>
-      <c r="M24" s="45">
+      <c r="M26" s="30">
         <v>39.4</v>
       </c>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B25" s="44" t="s">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B27" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45">
-        <v>0</v>
-      </c>
-      <c r="E25" s="45">
-        <v>0</v>
-      </c>
-      <c r="F25" s="45">
-        <v>0</v>
-      </c>
-      <c r="G25" s="45">
-        <v>0</v>
-      </c>
-      <c r="H25" s="45">
-        <v>0</v>
-      </c>
-      <c r="I25" s="45">
-        <v>0</v>
-      </c>
-      <c r="J25" s="45">
-        <v>0</v>
-      </c>
-      <c r="K25" s="45">
-        <v>0</v>
-      </c>
-      <c r="L25" s="45">
+      <c r="C27" s="30"/>
+      <c r="D27" s="30">
+        <v>85.11</v>
+      </c>
+      <c r="E27" s="30">
+        <v>2.97</v>
+      </c>
+      <c r="F27" s="30">
+        <v>91.42</v>
+      </c>
+      <c r="G27" s="30">
+        <v>21.24</v>
+      </c>
+      <c r="H27" s="30">
+        <v>7.86</v>
+      </c>
+      <c r="I27" s="30">
+        <v>34.380000000000003</v>
+      </c>
+      <c r="J27" s="30">
+        <v>15.65</v>
+      </c>
+      <c r="K27" s="30">
+        <v>55.84</v>
+      </c>
+      <c r="L27" s="30">
         <v>56.43</v>
       </c>
-      <c r="M25" s="45">
+      <c r="M27" s="30">
         <v>40.380000000000003</v>
       </c>
     </row>
-    <row r="26" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C26" s="23" t="s">
+    <row r="28" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D26" s="37"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="37"/>
-      <c r="I26" s="38"/>
-      <c r="J26" s="37"/>
-      <c r="K26" s="38"/>
-      <c r="L26" s="37"/>
-      <c r="M26" s="38"/>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="L27" s="39"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="48"/>
+      <c r="I28" s="49"/>
+      <c r="J28" s="48"/>
+      <c r="K28" s="49"/>
+      <c r="L28" s="48"/>
+      <c r="M28" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:M28"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="B14:M14"/>
@@ -7588,6 +7985,7 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Results_metrics.xlsx
+++ b/Results_metrics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ludovicascaffidi/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aless\OneDrive\Desktop\MaskArchitectureAnomaly_CourseProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97CD21E5-FC13-4B46-BD38-AFD038FE757F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7793EB7C-B546-45B6-9446-9944EBE2863C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="40">
   <si>
     <t>Model</t>
   </si>
@@ -130,6 +119,33 @@
   <si>
     <t>t = 1,1</t>
   </si>
+  <si>
+    <t>t = 3</t>
+  </si>
+  <si>
+    <t>t = 7,5</t>
+  </si>
+  <si>
+    <t>t = 12,5</t>
+  </si>
+  <si>
+    <t>t = 15</t>
+  </si>
+  <si>
+    <t>t = 17,5</t>
+  </si>
+  <si>
+    <t>t = 20</t>
+  </si>
+  <si>
+    <t>t = 22,5</t>
+  </si>
+  <si>
+    <t>t = 25</t>
+  </si>
+  <si>
+    <t>t = 0,25</t>
+  </si>
 </sst>
 </file>
 
@@ -616,7 +632,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
@@ -693,6 +709,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -832,40 +854,49 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$27</c:f>
+              <c:f>Foglio1!$B$17:$B$30</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>t = 0,25</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>t = 0,75</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>t = 0,8</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>t = 1</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>t = 1,1</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>t = 1,2</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>t = 1,5</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>t = 2</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
+                  <c:v>t = 3</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>t = 5</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
+                  <c:v>t = 7,5</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
@@ -873,41 +904,41 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$D$17:$D$27</c:f>
+              <c:f>Foglio1!$D$17:$D$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>34.270000000000003</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>53.99</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>58.57</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>61.18</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>63.39</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>64.27</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>65.13</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>67.64</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>75.12</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>83.89</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="13">
                   <c:v>85.11</c:v>
                 </c:pt>
               </c:numCache>
@@ -960,40 +991,49 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$27</c:f>
+              <c:f>Foglio1!$B$17:$B$30</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>t = 0,25</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>t = 0,75</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>t = 0,8</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>t = 1</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>t = 1,1</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>t = 1,2</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>t = 1,5</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>t = 2</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
+                  <c:v>t = 3</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>t = 5</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
+                  <c:v>t = 7,5</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
@@ -1001,41 +1041,41 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$E$17:$E$27</c:f>
+              <c:f>Foglio1!$E$17:$E$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>91.9</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>30.4</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>28.7</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>28.37</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>27.09</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>26.47</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>25.89</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>24.33</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>9.82</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>3.91</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="13">
                   <c:v>2.97</c:v>
                 </c:pt>
               </c:numCache>
@@ -1319,6 +1359,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1326,7 +1367,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1481,40 +1521,49 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$27</c:f>
+              <c:f>Foglio1!$B$17:$B$30</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>t = 0,25</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>t = 0,75</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>t = 0,8</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>t = 1</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>t = 1,1</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>t = 1,2</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>t = 1,5</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>t = 2</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
+                  <c:v>t = 3</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>t = 5</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
+                  <c:v>t = 7,5</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
@@ -1522,41 +1571,41 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$F$17:$F$27</c:f>
+              <c:f>Foglio1!$F$17:$F$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>33.96</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>75.69</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>78.45</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>79.010000000000005</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>81.23</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>82.27</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>82.23</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>85.54</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>88.34</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>91.31</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="13">
                   <c:v>91.42</c:v>
                 </c:pt>
               </c:numCache>
@@ -1609,40 +1658,49 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$27</c:f>
+              <c:f>Foglio1!$B$17:$B$30</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>t = 0,25</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>t = 0,75</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>t = 0,8</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>t = 1</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>t = 1,1</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>t = 1,2</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>t = 1,5</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>t = 2</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
+                  <c:v>t = 3</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>t = 5</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
+                  <c:v>t = 7,5</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
@@ -1650,41 +1708,41 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$G$17:$G$27</c:f>
+              <c:f>Foglio1!$G$17:$G$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>91.77</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>25.6</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>16.760000000000002</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>16.16</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>13.23</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>10.1</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>9.0399999999999991</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>10.210000000000001</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>11.92</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>17.89</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="13">
                   <c:v>21.24</c:v>
                 </c:pt>
               </c:numCache>
@@ -1968,6 +2026,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1975,7 +2034,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2130,40 +2188,49 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$27</c:f>
+              <c:f>Foglio1!$B$17:$B$30</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>t = 0,25</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>t = 0,75</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>t = 0,8</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>t = 1</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>t = 1,1</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>t = 1,2</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>t = 1,5</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>t = 2</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
+                  <c:v>t = 3</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>t = 5</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
+                  <c:v>t = 7,5</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
@@ -2171,41 +2238,41 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$H$17:$H$27</c:f>
+              <c:f>Foglio1!$H$17:$H$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>1.08</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2.44</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>2.82</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>2.91</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>3.33</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>3.58</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>3.84</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>4.7699999999999996</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>6.37</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>7.97</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="13">
                   <c:v>7.86</c:v>
                 </c:pt>
               </c:numCache>
@@ -2258,40 +2325,49 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$27</c:f>
+              <c:f>Foglio1!$B$17:$B$30</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>t = 0,25</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>t = 0,75</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>t = 0,8</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>t = 1</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>t = 1,1</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>t = 1,2</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>t = 1,5</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>t = 2</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
+                  <c:v>t = 3</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>t = 5</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
+                  <c:v>t = 7,5</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
@@ -2299,41 +2375,41 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$I$17:$I$27</c:f>
+              <c:f>Foglio1!$I$17:$I$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>92.89</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>53.79</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>30.87</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>30.88</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>31.26</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>31.28</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>31.17</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>31.85</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>32.71</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>34.31</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="13">
                   <c:v>34.380000000000003</c:v>
                 </c:pt>
               </c:numCache>
@@ -2617,6 +2693,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2624,7 +2701,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2779,40 +2855,49 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$27</c:f>
+              <c:f>Foglio1!$B$17:$B$30</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>t = 0,25</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>t = 0,75</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>t = 0,8</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>t = 1</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>t = 1,1</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>t = 1,2</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>t = 1,5</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>t = 2</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
+                  <c:v>t = 3</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>t = 5</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
+                  <c:v>t = 7,5</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
@@ -2820,41 +2905,41 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$J$17:$J$27</c:f>
+              <c:f>Foglio1!$J$17:$J$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>4.4800000000000004</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>8.73</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>9.5</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>9.6300000000000008</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>10.29</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>10.68</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>11.13</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>12.55</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>14.47</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>15.64</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="13">
                   <c:v>15.65</c:v>
                 </c:pt>
               </c:numCache>
@@ -2907,40 +2992,49 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$27</c:f>
+              <c:f>Foglio1!$B$17:$B$30</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>t = 0,25</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>t = 0,75</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>t = 0,8</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>t = 1</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>t = 1,1</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>t = 1,2</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>t = 1,5</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>t = 2</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
+                  <c:v>t = 3</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>t = 5</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
+                  <c:v>t = 7,5</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
@@ -2948,41 +3042,41 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$K$17:$K$27</c:f>
+              <c:f>Foglio1!$K$17:$K$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>93.5</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>74.12</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>55.77</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>54.26</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>55.32</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>56.7</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>56.71</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>57.72</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>57.57</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>55.85</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="13">
                   <c:v>55.84</c:v>
                 </c:pt>
               </c:numCache>
@@ -3266,6 +3360,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3273,7 +3368,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3428,40 +3522,49 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$27</c:f>
+              <c:f>Foglio1!$B$17:$B$30</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>t = 0,25</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>t = 0,75</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>t = 0,8</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>t = 1</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>t = 1,1</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>t = 1,2</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>t = 1,5</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>t = 2</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
+                  <c:v>t = 3</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>t = 5</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
+                  <c:v>t = 7,5</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
@@ -3469,41 +3572,41 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$L$17:$L$27</c:f>
+              <c:f>Foglio1!$L$17:$L$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>27.36</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>43.75</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>47.11</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>47.69</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>49.86</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>50.72</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>51.47</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>53.18</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>54.85</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>56.42</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="13">
                   <c:v>56.43</c:v>
                 </c:pt>
               </c:numCache>
@@ -3556,40 +3659,49 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$27</c:f>
+              <c:f>Foglio1!$B$17:$B$30</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>t = 0,25</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>t = 0,75</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>t = 0,8</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>t = 1</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>t = 1,1</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>t = 1,2</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>t = 1,5</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>t = 2</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
+                  <c:v>t = 3</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>t = 5</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
+                  <c:v>t = 7,5</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
@@ -3597,41 +3709,41 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$M$17:$M$27</c:f>
+              <c:f>Foglio1!$M$17:$M$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>91.26</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>51.58</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>46.41</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>46.22</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>44.63</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>44.22</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>43.53</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>42.7</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>41.58</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>39.4</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="13">
                   <c:v>40.380000000000003</c:v>
                 </c:pt>
               </c:numCache>
@@ -3915,6 +4027,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3922,7 +4035,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6720,7 +6832,7 @@
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>503787</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>41331</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6752,13 +6864,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>318304</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>173621</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>146903</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>12396</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6790,13 +6902,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>414760</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>163975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>310878</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>2750</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6828,13 +6940,13 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>598026</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>173621</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>494143</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>12396</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -7128,15 +7240,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:O28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="B1:O37"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="3" max="3" width="13.1640625" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="36" t="s">
         <v>18</v>
       </c>
@@ -7152,7 +7264,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="38"/>
     </row>
-    <row r="3" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
       <c r="C3" s="5"/>
       <c r="D3" s="39" t="s">
@@ -7176,7 +7288,7 @@
       </c>
       <c r="M3" s="40"/>
     </row>
-    <row r="4" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="6" t="s">
         <v>0</v>
       </c>
@@ -7214,7 +7326,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B5" s="41" t="s">
         <v>9</v>
       </c>
@@ -7252,7 +7364,7 @@
         <v>82.58</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B6" s="42"/>
       <c r="C6" s="9" t="s">
         <v>11</v>
@@ -7288,7 +7400,7 @@
         <v>73.25</v>
       </c>
     </row>
-    <row r="7" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="43"/>
       <c r="C7" s="11" t="s">
         <v>12</v>
@@ -7324,7 +7436,7 @@
         <v>82.75</v>
       </c>
     </row>
-    <row r="8" spans="2:13" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B8" s="44" t="s">
         <v>13</v>
       </c>
@@ -7362,7 +7474,7 @@
         <v>44.62</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B9" s="42"/>
       <c r="C9" s="9" t="s">
         <v>11</v>
@@ -7398,7 +7510,7 @@
         <v>19.09</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B10" s="42"/>
       <c r="C10" s="9" t="s">
         <v>12</v>
@@ -7434,7 +7546,7 @@
         <v>44.12</v>
       </c>
     </row>
-    <row r="11" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="45"/>
       <c r="C11" s="10" t="s">
         <v>14</v>
@@ -7470,8 +7582,8 @@
         <v>17.579999999999998</v>
       </c>
     </row>
-    <row r="13" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="14" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="36" t="s">
         <v>19</v>
       </c>
@@ -7487,7 +7599,7 @@
       <c r="L14" s="46"/>
       <c r="M14" s="47"/>
     </row>
-    <row r="15" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="24"/>
       <c r="C15" s="4"/>
       <c r="D15" s="39" t="s">
@@ -7511,7 +7623,7 @@
       </c>
       <c r="M15" s="40"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>16</v>
       </c>
@@ -7549,7 +7661,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" s="29" t="s">
         <v>24</v>
       </c>
@@ -7585,389 +7697,653 @@
         <v>91.26</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B18" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="30"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B19" s="29" t="s">
         <v>20</v>
-      </c>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34">
-        <v>53.99</v>
-      </c>
-      <c r="E18" s="34">
-        <v>30.4</v>
-      </c>
-      <c r="F18" s="34">
-        <v>75.69</v>
-      </c>
-      <c r="G18" s="34">
-        <v>25.6</v>
-      </c>
-      <c r="H18" s="34">
-        <v>2.44</v>
-      </c>
-      <c r="I18" s="34">
-        <v>53.79</v>
-      </c>
-      <c r="J18" s="34">
-        <v>8.73</v>
-      </c>
-      <c r="K18" s="34">
-        <v>74.12</v>
-      </c>
-      <c r="L18" s="34">
-        <v>43.75</v>
-      </c>
-      <c r="M18" s="34">
-        <v>51.58</v>
-      </c>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B19" s="29" t="s">
-        <v>29</v>
       </c>
       <c r="C19" s="34"/>
       <c r="D19" s="34">
+        <v>53.99</v>
+      </c>
+      <c r="E19" s="34">
+        <v>30.4</v>
+      </c>
+      <c r="F19" s="34">
+        <v>75.69</v>
+      </c>
+      <c r="G19" s="34">
+        <v>25.6</v>
+      </c>
+      <c r="H19" s="34">
+        <v>2.44</v>
+      </c>
+      <c r="I19" s="34">
+        <v>53.79</v>
+      </c>
+      <c r="J19" s="34">
+        <v>8.73</v>
+      </c>
+      <c r="K19" s="34">
+        <v>74.12</v>
+      </c>
+      <c r="L19" s="34">
+        <v>43.75</v>
+      </c>
+      <c r="M19" s="34">
+        <v>51.58</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B20" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34">
         <v>58.57</v>
       </c>
-      <c r="E19" s="34">
+      <c r="E20" s="34">
         <v>28.7</v>
       </c>
-      <c r="F19" s="34">
+      <c r="F20" s="34">
         <v>78.45</v>
       </c>
-      <c r="G19" s="34">
+      <c r="G20" s="34">
         <v>16.760000000000002</v>
       </c>
-      <c r="H19" s="34">
+      <c r="H20" s="34">
         <v>2.82</v>
       </c>
-      <c r="I19" s="34">
+      <c r="I20" s="34">
         <v>30.87</v>
       </c>
-      <c r="J19" s="34">
+      <c r="J20" s="34">
         <v>9.5</v>
       </c>
-      <c r="K19" s="34">
+      <c r="K20" s="34">
         <v>55.77</v>
       </c>
-      <c r="L19" s="34">
+      <c r="L20" s="34">
         <v>47.11</v>
       </c>
-      <c r="M19" s="34">
+      <c r="M20" s="34">
         <v>46.41</v>
       </c>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B20" s="29" t="s">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B21" s="29" t="s">
         <v>25</v>
-      </c>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30">
-        <v>61.18</v>
-      </c>
-      <c r="E20" s="30">
-        <v>28.37</v>
-      </c>
-      <c r="F20" s="30">
-        <v>79.010000000000005</v>
-      </c>
-      <c r="G20" s="30">
-        <v>16.16</v>
-      </c>
-      <c r="H20" s="30">
-        <v>2.91</v>
-      </c>
-      <c r="I20" s="30">
-        <v>30.88</v>
-      </c>
-      <c r="J20" s="30">
-        <v>9.6300000000000008</v>
-      </c>
-      <c r="K20" s="30">
-        <v>54.26</v>
-      </c>
-      <c r="L20" s="30">
-        <v>47.69</v>
-      </c>
-      <c r="M20" s="30">
-        <v>46.22</v>
-      </c>
-    </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B21" s="29" t="s">
-        <v>21</v>
       </c>
       <c r="C21" s="30"/>
       <c r="D21" s="30">
+        <v>61.18</v>
+      </c>
+      <c r="E21" s="30">
+        <v>28.37</v>
+      </c>
+      <c r="F21" s="30">
+        <v>79.010000000000005</v>
+      </c>
+      <c r="G21" s="30">
+        <v>16.16</v>
+      </c>
+      <c r="H21" s="30">
+        <v>2.91</v>
+      </c>
+      <c r="I21" s="30">
+        <v>30.88</v>
+      </c>
+      <c r="J21" s="30">
+        <v>9.6300000000000008</v>
+      </c>
+      <c r="K21" s="30">
+        <v>54.26</v>
+      </c>
+      <c r="L21" s="30">
+        <v>47.69</v>
+      </c>
+      <c r="M21" s="30">
+        <v>46.22</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B22" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30">
         <v>63.39</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E22" s="30">
         <v>27.09</v>
       </c>
-      <c r="F21" s="35">
+      <c r="F22" s="35">
         <v>81.23</v>
       </c>
-      <c r="G21" s="30">
+      <c r="G22" s="30">
         <v>13.23</v>
       </c>
-      <c r="H21" s="30">
+      <c r="H22" s="30">
         <v>3.33</v>
       </c>
-      <c r="I21" s="30">
+      <c r="I22" s="30">
         <v>31.26</v>
       </c>
-      <c r="J21" s="30">
+      <c r="J22" s="30">
         <v>10.29</v>
       </c>
-      <c r="K21" s="30">
+      <c r="K22" s="30">
         <v>55.32</v>
       </c>
-      <c r="L21" s="30">
+      <c r="L22" s="30">
         <v>49.86</v>
       </c>
-      <c r="M21" s="30">
+      <c r="M22" s="30">
         <v>44.63</v>
       </c>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B22" s="29" t="s">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B23" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34">
+      <c r="C23" s="34"/>
+      <c r="D23" s="34">
         <v>64.27</v>
       </c>
-      <c r="E22" s="34">
+      <c r="E23" s="34">
         <v>26.47</v>
       </c>
-      <c r="F22" s="34">
+      <c r="F23" s="34">
         <v>82.27</v>
       </c>
-      <c r="G22" s="34">
+      <c r="G23" s="34">
         <v>10.1</v>
       </c>
-      <c r="H22" s="34">
+      <c r="H23" s="34">
         <v>3.58</v>
       </c>
-      <c r="I22" s="34">
+      <c r="I23" s="34">
         <v>31.28</v>
       </c>
-      <c r="J22" s="34">
+      <c r="J23" s="34">
         <v>10.68</v>
       </c>
-      <c r="K22" s="34">
+      <c r="K23" s="34">
         <v>56.7</v>
       </c>
-      <c r="L22" s="34">
+      <c r="L23" s="34">
         <v>50.72</v>
       </c>
-      <c r="M22" s="34">
+      <c r="M23" s="34">
         <v>44.22</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B23" s="29" t="s">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B24" s="29" t="s">
         <v>26</v>
-      </c>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30">
-        <v>65.13</v>
-      </c>
-      <c r="E23" s="30">
-        <v>25.89</v>
-      </c>
-      <c r="F23" s="30">
-        <v>82.23</v>
-      </c>
-      <c r="G23" s="30">
-        <v>9.0399999999999991</v>
-      </c>
-      <c r="H23" s="30">
-        <v>3.84</v>
-      </c>
-      <c r="I23" s="30">
-        <v>31.17</v>
-      </c>
-      <c r="J23" s="30">
-        <v>11.13</v>
-      </c>
-      <c r="K23" s="30">
-        <v>56.71</v>
-      </c>
-      <c r="L23" s="30">
-        <v>51.47</v>
-      </c>
-      <c r="M23" s="30">
-        <v>43.53</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B24" s="29" t="s">
-        <v>22</v>
       </c>
       <c r="C24" s="30"/>
       <c r="D24" s="30">
-        <v>67.64</v>
+        <v>65.13</v>
       </c>
       <c r="E24" s="30">
-        <v>24.33</v>
+        <v>25.89</v>
       </c>
       <c r="F24" s="30">
-        <v>85.54</v>
+        <v>82.23</v>
       </c>
       <c r="G24" s="30">
-        <v>10.210000000000001</v>
+        <v>9.0399999999999991</v>
       </c>
       <c r="H24" s="30">
-        <v>4.7699999999999996</v>
+        <v>3.84</v>
       </c>
       <c r="I24" s="30">
-        <v>31.85</v>
+        <v>31.17</v>
       </c>
       <c r="J24" s="30">
-        <v>12.55</v>
+        <v>11.13</v>
       </c>
       <c r="K24" s="30">
-        <v>57.72</v>
+        <v>56.71</v>
       </c>
       <c r="L24" s="30">
-        <v>53.18</v>
+        <v>51.47</v>
       </c>
       <c r="M24" s="30">
-        <v>42.7</v>
-      </c>
-      <c r="O24" s="33"/>
+        <v>43.53</v>
+      </c>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B25" s="29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C25" s="30"/>
       <c r="D25" s="30">
-        <v>75.12</v>
+        <v>67.64</v>
       </c>
       <c r="E25" s="30">
-        <v>9.82</v>
+        <v>24.33</v>
       </c>
       <c r="F25" s="30">
-        <v>88.34</v>
+        <v>85.54</v>
       </c>
       <c r="G25" s="30">
-        <v>11.92</v>
+        <v>10.210000000000001</v>
       </c>
       <c r="H25" s="30">
-        <v>6.37</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="I25" s="30">
-        <v>32.71</v>
+        <v>31.85</v>
       </c>
       <c r="J25" s="30">
-        <v>14.47</v>
+        <v>12.55</v>
       </c>
       <c r="K25" s="30">
-        <v>57.57</v>
+        <v>57.72</v>
       </c>
       <c r="L25" s="30">
-        <v>54.85</v>
+        <v>53.18</v>
       </c>
       <c r="M25" s="30">
-        <v>41.58</v>
-      </c>
+        <v>42.7</v>
+      </c>
+      <c r="O25" s="33"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B26" s="29" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C26" s="30"/>
       <c r="D26" s="30">
+        <v>75.12</v>
+      </c>
+      <c r="E26" s="30">
+        <v>9.82</v>
+      </c>
+      <c r="F26" s="30">
+        <v>88.34</v>
+      </c>
+      <c r="G26" s="30">
+        <v>11.92</v>
+      </c>
+      <c r="H26" s="30">
+        <v>6.37</v>
+      </c>
+      <c r="I26" s="30">
+        <v>32.71</v>
+      </c>
+      <c r="J26" s="30">
+        <v>14.47</v>
+      </c>
+      <c r="K26" s="30">
+        <v>57.57</v>
+      </c>
+      <c r="L26" s="30">
+        <v>54.85</v>
+      </c>
+      <c r="M26" s="30">
+        <v>41.58</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B27" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+      <c r="M27" s="30"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B28" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30">
         <v>83.89</v>
       </c>
-      <c r="E26" s="30">
+      <c r="E28" s="30">
         <v>3.91</v>
       </c>
-      <c r="F26" s="30">
+      <c r="F28" s="30">
         <v>91.31</v>
       </c>
-      <c r="G26" s="30">
+      <c r="G28" s="30">
         <v>17.89</v>
       </c>
-      <c r="H26" s="30">
+      <c r="H28" s="30">
         <v>7.97</v>
       </c>
-      <c r="I26" s="30">
+      <c r="I28" s="30">
         <v>34.31</v>
       </c>
-      <c r="J26" s="30">
+      <c r="J28" s="30">
         <v>15.64</v>
       </c>
-      <c r="K26" s="30">
+      <c r="K28" s="30">
         <v>55.85</v>
       </c>
-      <c r="L26" s="30">
+      <c r="L28" s="30">
         <v>56.42</v>
       </c>
-      <c r="M26" s="30">
+      <c r="M28" s="30">
         <v>39.4</v>
       </c>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B27" s="29" t="s">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B29" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B30" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30">
+      <c r="C30" s="30"/>
+      <c r="D30" s="30">
         <v>85.11</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E30" s="30">
         <v>2.97</v>
       </c>
-      <c r="F27" s="30">
+      <c r="F30" s="30">
         <v>91.42</v>
       </c>
-      <c r="G27" s="30">
+      <c r="G30" s="30">
         <v>21.24</v>
       </c>
-      <c r="H27" s="30">
+      <c r="H30" s="30">
         <v>7.86</v>
       </c>
-      <c r="I27" s="30">
+      <c r="I30" s="30">
         <v>34.380000000000003</v>
       </c>
-      <c r="J27" s="30">
+      <c r="J30" s="30">
         <v>15.65</v>
       </c>
-      <c r="K27" s="30">
+      <c r="K30" s="30">
         <v>55.84</v>
       </c>
-      <c r="L27" s="30">
+      <c r="L30" s="30">
         <v>56.43</v>
       </c>
-      <c r="M27" s="30">
+      <c r="M30" s="30">
         <v>40.380000000000003</v>
       </c>
     </row>
-    <row r="28" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="23" t="s">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B31" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30">
+        <v>85.11</v>
+      </c>
+      <c r="E31" s="30">
+        <v>2.97</v>
+      </c>
+      <c r="F31" s="30">
+        <v>91.42</v>
+      </c>
+      <c r="G31" s="30">
+        <v>21.24</v>
+      </c>
+      <c r="H31" s="30">
+        <v>7.86</v>
+      </c>
+      <c r="I31" s="30">
+        <v>34.380000000000003</v>
+      </c>
+      <c r="J31" s="30">
+        <v>15.65</v>
+      </c>
+      <c r="K31" s="30">
+        <v>55.84</v>
+      </c>
+      <c r="L31" s="30">
+        <v>56.43</v>
+      </c>
+      <c r="M31" s="30">
+        <v>40.380000000000003</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B32" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30">
+        <v>85.11</v>
+      </c>
+      <c r="E32" s="30">
+        <v>2.97</v>
+      </c>
+      <c r="F32" s="30">
+        <v>91.42</v>
+      </c>
+      <c r="G32" s="30">
+        <v>21.24</v>
+      </c>
+      <c r="H32" s="30">
+        <v>7.86</v>
+      </c>
+      <c r="I32" s="30">
+        <v>34.380000000000003</v>
+      </c>
+      <c r="J32" s="30">
+        <v>15.65</v>
+      </c>
+      <c r="K32" s="30">
+        <v>55.84</v>
+      </c>
+      <c r="L32" s="30">
+        <v>56.43</v>
+      </c>
+      <c r="M32" s="30">
+        <v>40.380000000000003</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B33" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30">
+        <v>85.11</v>
+      </c>
+      <c r="E33" s="30">
+        <v>2.97</v>
+      </c>
+      <c r="F33" s="30">
+        <v>91.42</v>
+      </c>
+      <c r="G33" s="30">
+        <v>21.24</v>
+      </c>
+      <c r="H33" s="30">
+        <v>7.86</v>
+      </c>
+      <c r="I33" s="30">
+        <v>34.380000000000003</v>
+      </c>
+      <c r="J33" s="30">
+        <v>15.65</v>
+      </c>
+      <c r="K33" s="30">
+        <v>55.84</v>
+      </c>
+      <c r="L33" s="30">
+        <v>56.43</v>
+      </c>
+      <c r="M33" s="30">
+        <v>40.380000000000003</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B34" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30">
+        <v>85.11</v>
+      </c>
+      <c r="E34" s="30">
+        <v>2.97</v>
+      </c>
+      <c r="F34" s="30">
+        <v>91.42</v>
+      </c>
+      <c r="G34" s="30">
+        <v>21.24</v>
+      </c>
+      <c r="H34" s="30">
+        <v>7.86</v>
+      </c>
+      <c r="I34" s="30">
+        <v>34.380000000000003</v>
+      </c>
+      <c r="J34" s="30">
+        <v>15.65</v>
+      </c>
+      <c r="K34" s="30">
+        <v>55.84</v>
+      </c>
+      <c r="L34" s="30">
+        <v>56.43</v>
+      </c>
+      <c r="M34" s="30">
+        <v>40.380000000000003</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B35" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30">
+        <v>85.11</v>
+      </c>
+      <c r="E35" s="30">
+        <v>2.97</v>
+      </c>
+      <c r="F35" s="30">
+        <v>91.42</v>
+      </c>
+      <c r="G35" s="30">
+        <v>21.24</v>
+      </c>
+      <c r="H35" s="30">
+        <v>7.86</v>
+      </c>
+      <c r="I35" s="30">
+        <v>34.380000000000003</v>
+      </c>
+      <c r="J35" s="30">
+        <v>15.65</v>
+      </c>
+      <c r="K35" s="30">
+        <v>55.84</v>
+      </c>
+      <c r="L35" s="30">
+        <v>56.43</v>
+      </c>
+      <c r="M35" s="30">
+        <v>40.380000000000003</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B36" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30">
+        <v>85.11</v>
+      </c>
+      <c r="E36" s="30">
+        <v>2.97</v>
+      </c>
+      <c r="F36" s="30">
+        <v>91.42</v>
+      </c>
+      <c r="G36" s="30">
+        <v>21.24</v>
+      </c>
+      <c r="H36" s="30">
+        <v>7.86</v>
+      </c>
+      <c r="I36" s="30">
+        <v>34.380000000000003</v>
+      </c>
+      <c r="J36" s="30">
+        <v>15.65</v>
+      </c>
+      <c r="K36" s="30">
+        <v>55.84</v>
+      </c>
+      <c r="L36" s="30">
+        <v>56.43</v>
+      </c>
+      <c r="M36" s="30">
+        <v>40.380000000000003</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C37" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="48"/>
-      <c r="E28" s="49"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="49"/>
-      <c r="H28" s="48"/>
-      <c r="I28" s="49"/>
-      <c r="J28" s="48"/>
-      <c r="K28" s="49"/>
-      <c r="L28" s="48"/>
-      <c r="M28" s="49"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="49"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="49"/>
+      <c r="H37" s="50"/>
+      <c r="I37" s="51"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="49"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="L37:M37"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="B14:M14"/>

--- a/Results_metrics.xlsx
+++ b/Results_metrics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aless\OneDrive\Desktop\MaskArchitectureAnomaly_CourseProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7793EB7C-B546-45B6-9446-9944EBE2863C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48F19592-3D82-46E9-BDB7-6BDD75B42717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="41">
   <si>
     <t>Model</t>
   </si>
@@ -146,6 +146,9 @@
   <si>
     <t>t = 0,25</t>
   </si>
+  <si>
+    <t>t = 4</t>
+  </si>
 </sst>
 </file>
 
@@ -226,7 +229,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -628,11 +631,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
@@ -669,19 +683,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -699,24 +710,29 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -854,9 +870,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$30</c:f>
+              <c:f>Foglio1!$B$17:$B$31</c:f>
               <c:strCache>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -891,12 +907,15 @@
                   <c:v>t = 3</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>t = 4</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>t = 5</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>t = 7,5</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
@@ -904,15 +923,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$D$17:$D$30</c:f>
+              <c:f>Foglio1!$D$17:$D$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>34.270000000000003</c:v>
+                  <c:v>34.29</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>42.38</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>53.99</c:v>
+                  <c:v>54.02</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>58.57</c:v>
@@ -921,10 +943,10 @@
                   <c:v>61.18</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>63.39</c:v>
+                  <c:v>63.4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>64.27</c:v>
+                  <c:v>64.28</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>65.13</c:v>
@@ -935,11 +957,20 @@
                 <c:pt idx="9">
                   <c:v>75.12</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>79.900000000000006</c:v>
+                </c:pt>
                 <c:pt idx="11">
-                  <c:v>83.89</c:v>
+                  <c:v>82.66</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>83.9</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>85.11</c:v>
+                  <c:v>84.85</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>85.12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -991,9 +1022,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$30</c:f>
+              <c:f>Foglio1!$B$17:$B$31</c:f>
               <c:strCache>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -1028,12 +1059,15 @@
                   <c:v>t = 3</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>t = 4</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>t = 5</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>t = 7,5</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
@@ -1041,21 +1075,24 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$E$17:$E$30</c:f>
+              <c:f>Foglio1!$E$17:$E$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>91.9</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>89.39</c:v>
+                </c:pt>
                 <c:pt idx="2">
                   <c:v>30.4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>28.7</c:v>
+                  <c:v>28.71</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>28.37</c:v>
+                  <c:v>28.38</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>27.09</c:v>
@@ -1067,15 +1104,24 @@
                   <c:v>25.89</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>24.33</c:v>
+                  <c:v>24.34</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>9.82</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.72</c:v>
+                </c:pt>
                 <c:pt idx="11">
+                  <c:v>4.93</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>3.91</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>3.18</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>2.97</c:v>
                 </c:pt>
               </c:numCache>
@@ -1521,9 +1567,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$30</c:f>
+              <c:f>Foglio1!$B$17:$B$31</c:f>
               <c:strCache>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -1558,12 +1604,15 @@
                   <c:v>t = 3</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>t = 4</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>t = 5</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>t = 7,5</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
@@ -1571,42 +1620,54 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$F$17:$F$30</c:f>
+              <c:f>Foglio1!$F$17:$F$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>33.96</c:v>
+                  <c:v>33.64</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>60.22</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>75.69</c:v>
+                  <c:v>75.39</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>78.45</c:v>
+                  <c:v>78.2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>79.010000000000005</c:v>
+                  <c:v>78.75</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>81.23</c:v>
+                  <c:v>80.95</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>82.27</c:v>
+                  <c:v>82</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>82.23</c:v>
+                  <c:v>82.96</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>85.54</c:v>
+                  <c:v>85.28</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>88.34</c:v>
+                  <c:v>88.12</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>90.94</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>91.17</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>91.29</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>91.31</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>91.42</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1658,9 +1719,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$30</c:f>
+              <c:f>Foglio1!$B$17:$B$31</c:f>
               <c:strCache>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -1695,12 +1756,15 @@
                   <c:v>t = 3</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>t = 4</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>t = 5</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>t = 7,5</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
@@ -1708,42 +1772,54 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$G$17:$G$30</c:f>
+              <c:f>Foglio1!$G$17:$G$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>91.77</c:v>
+                  <c:v>91.83</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>82.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>25.6</c:v>
+                  <c:v>26.43</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>16.760000000000002</c:v>
+                  <c:v>17.52</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>16.16</c:v>
+                  <c:v>16.989999999999998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>13.23</c:v>
+                  <c:v>14.95</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>10.1</c:v>
+                  <c:v>14.28</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>9.0399999999999991</c:v>
+                  <c:v>10.92</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>10.210000000000001</c:v>
+                  <c:v>11.74</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>11.92</c:v>
+                  <c:v>12.57</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>15.04</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>17.89</c:v>
+                  <c:v>16.91</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>17.68</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>21.24</c:v>
+                  <c:v>19.440000000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>20.47</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2188,9 +2264,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$30</c:f>
+              <c:f>Foglio1!$B$17:$B$31</c:f>
               <c:strCache>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -2225,12 +2301,15 @@
                   <c:v>t = 3</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>t = 4</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>t = 5</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>t = 7,5</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
@@ -2238,10 +2317,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$H$17:$H$30</c:f>
+              <c:f>Foglio1!$H$17:$H$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.08</c:v>
                 </c:pt>
@@ -2269,10 +2348,10 @@
                 <c:pt idx="9">
                   <c:v>6.37</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>7.97</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>7.86</c:v>
                 </c:pt>
               </c:numCache>
@@ -2325,9 +2404,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$30</c:f>
+              <c:f>Foglio1!$B$17:$B$31</c:f>
               <c:strCache>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -2362,12 +2441,15 @@
                   <c:v>t = 3</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>t = 4</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>t = 5</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>t = 7,5</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
@@ -2375,10 +2457,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$I$17:$I$30</c:f>
+              <c:f>Foglio1!$I$17:$I$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>92.89</c:v>
                 </c:pt>
@@ -2406,10 +2488,10 @@
                 <c:pt idx="9">
                   <c:v>32.71</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>34.31</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>34.380000000000003</c:v>
                 </c:pt>
               </c:numCache>
@@ -2855,9 +2937,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$30</c:f>
+              <c:f>Foglio1!$B$17:$B$31</c:f>
               <c:strCache>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -2892,12 +2974,15 @@
                   <c:v>t = 3</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>t = 4</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>t = 5</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>t = 7,5</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
@@ -2905,42 +2990,54 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$J$17:$J$30</c:f>
+              <c:f>Foglio1!$J$17:$J$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>4.4800000000000004</c:v>
+                  <c:v>4.53</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.84</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.73</c:v>
+                  <c:v>8.7799999999999994</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.5</c:v>
+                  <c:v>9.56</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.6300000000000008</c:v>
+                  <c:v>9.6999999999999993</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>10.29</c:v>
+                  <c:v>10.37</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>10.68</c:v>
+                  <c:v>10.78</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>11.13</c:v>
+                  <c:v>11.22</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>12.55</c:v>
+                  <c:v>12.64</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>14.47</c:v>
+                  <c:v>14.55</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>15.54</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>15.64</c:v>
+                  <c:v>15.66</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>15.69</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>15.65</c:v>
+                  <c:v>15.7</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15.69</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2992,9 +3089,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$30</c:f>
+              <c:f>Foglio1!$B$17:$B$31</c:f>
               <c:strCache>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -3029,12 +3126,15 @@
                   <c:v>t = 3</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>t = 4</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>t = 5</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>t = 7,5</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
@@ -3042,42 +3142,54 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$K$17:$K$30</c:f>
+              <c:f>Foglio1!$K$17:$K$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>93.5</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>90.35</c:v>
+                </c:pt>
                 <c:pt idx="2">
-                  <c:v>74.12</c:v>
+                  <c:v>74.22</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>55.77</c:v>
+                  <c:v>55.75</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>54.26</c:v>
+                  <c:v>54.31</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>55.32</c:v>
+                  <c:v>55.49</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>56.7</c:v>
+                  <c:v>56.77</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>56.71</c:v>
+                  <c:v>56.83</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>57.72</c:v>
+                  <c:v>57.88</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>57.57</c:v>
+                  <c:v>57.56</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>56.61</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>55.85</c:v>
+                  <c:v>56.15</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>55.95</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>55.84</c:v>
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>55.98</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3522,9 +3634,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$30</c:f>
+              <c:f>Foglio1!$B$17:$B$31</c:f>
               <c:strCache>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -3559,12 +3671,15 @@
                   <c:v>t = 3</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>t = 4</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>t = 5</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>t = 7,5</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
@@ -3577,25 +3692,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>27.36</c:v>
+                  <c:v>27.35</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>37.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>43.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>47.11</c:v>
+                  <c:v>47.1</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>47.69</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>49.86</c:v>
+                  <c:v>49.87</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>50.72</c:v>
+                  <c:v>50.73</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>51.47</c:v>
+                  <c:v>51.48</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>53.18</c:v>
@@ -3603,11 +3721,17 @@
                 <c:pt idx="9">
                   <c:v>54.85</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>56.09</c:v>
+                </c:pt>
                 <c:pt idx="11">
-                  <c:v>56.42</c:v>
+                  <c:v>56.37</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>56.43</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>56.43</c:v>
+                  <c:v>56.45</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3659,9 +3783,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$30</c:f>
+              <c:f>Foglio1!$B$17:$B$31</c:f>
               <c:strCache>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -3696,12 +3820,15 @@
                   <c:v>t = 3</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>t = 4</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>t = 5</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>t = 7,5</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>t = 10</c:v>
                 </c:pt>
               </c:strCache>
@@ -3716,32 +3843,41 @@
                 <c:pt idx="0">
                   <c:v>91.26</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>80.5</c:v>
+                </c:pt>
                 <c:pt idx="2">
-                  <c:v>51.58</c:v>
+                  <c:v>51.59</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>46.41</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46.22</c:v>
+                  <c:v>46.21</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>44.63</c:v>
+                  <c:v>44.62</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>44.22</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>43.53</c:v>
+                  <c:v>43.54</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>42.7</c:v>
+                  <c:v>42.69</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>41.58</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>39.799999999999997</c:v>
+                </c:pt>
                 <c:pt idx="11">
-                  <c:v>39.4</c:v>
+                  <c:v>39.11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>39.43</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>40.380000000000003</c:v>
@@ -6832,7 +6968,7 @@
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>503787</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>41331</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6864,13 +7000,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>318304</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>173621</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>146903</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>12396</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6902,13 +7038,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>414760</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>163975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>310878</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>2750</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6940,13 +7076,13 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>598026</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>173621</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>494143</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>12396</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -7240,7 +7376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:O37"/>
+  <dimension ref="B1:O38"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.44140625" customWidth="1"/>
@@ -7249,44 +7385,44 @@
   <sheetData>
     <row r="1" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="38"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="51"/>
     </row>
     <row r="3" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
       <c r="C3" s="5"/>
-      <c r="D3" s="39" t="s">
+      <c r="D3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="40"/>
-      <c r="F3" s="39" t="s">
+      <c r="E3" s="49"/>
+      <c r="F3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="40"/>
-      <c r="H3" s="39" t="s">
+      <c r="G3" s="49"/>
+      <c r="H3" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="40"/>
-      <c r="J3" s="39" t="s">
+      <c r="I3" s="49"/>
+      <c r="J3" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="40"/>
-      <c r="L3" s="39" t="s">
+      <c r="K3" s="49"/>
+      <c r="L3" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="40"/>
+      <c r="M3" s="49"/>
     </row>
     <row r="4" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="6" t="s">
@@ -7327,7 +7463,7 @@
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="40" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -7365,7 +7501,7 @@
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B6" s="42"/>
+      <c r="B6" s="41"/>
       <c r="C6" s="9" t="s">
         <v>11</v>
       </c>
@@ -7401,7 +7537,7 @@
       </c>
     </row>
     <row r="7" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="43"/>
+      <c r="B7" s="42"/>
       <c r="C7" s="11" t="s">
         <v>12</v>
       </c>
@@ -7437,7 +7573,7 @@
       </c>
     </row>
     <row r="8" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="44" t="s">
+      <c r="B8" s="43" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="12" t="s">
@@ -7475,7 +7611,7 @@
       </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B9" s="42"/>
+      <c r="B9" s="41"/>
       <c r="C9" s="9" t="s">
         <v>11</v>
       </c>
@@ -7511,7 +7647,7 @@
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B10" s="42"/>
+      <c r="B10" s="41"/>
       <c r="C10" s="9" t="s">
         <v>12</v>
       </c>
@@ -7547,7 +7683,7 @@
       </c>
     </row>
     <row r="11" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="45"/>
+      <c r="B11" s="44"/>
       <c r="C11" s="10" t="s">
         <v>14</v>
       </c>
@@ -7584,7 +7720,7 @@
     </row>
     <row r="13" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="14" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="36" t="s">
+      <c r="B14" s="45" t="s">
         <v>19</v>
       </c>
       <c r="C14" s="46"/>
@@ -7602,26 +7738,26 @@
     <row r="15" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="24"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="E15" s="40"/>
-      <c r="F15" s="39" t="s">
+      <c r="E15" s="49"/>
+      <c r="F15" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="40"/>
-      <c r="H15" s="39" t="s">
+      <c r="G15" s="49"/>
+      <c r="H15" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="40"/>
-      <c r="J15" s="39" t="s">
+      <c r="I15" s="49"/>
+      <c r="J15" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="40"/>
-      <c r="L15" s="39" t="s">
+      <c r="K15" s="49"/>
+      <c r="L15" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="M15" s="40"/>
+      <c r="M15" s="49"/>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
@@ -7665,18 +7801,20 @@
       <c r="B17" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="30"/>
+      <c r="C17" s="52">
+        <v>0.77429999999999999</v>
+      </c>
       <c r="D17" s="30">
-        <v>34.270000000000003</v>
+        <v>34.29</v>
       </c>
       <c r="E17" s="30">
         <v>91.9</v>
       </c>
       <c r="F17" s="30">
-        <v>33.96</v>
+        <v>33.64</v>
       </c>
       <c r="G17" s="30">
-        <v>91.77</v>
+        <v>91.83</v>
       </c>
       <c r="H17" s="30">
         <v>1.08</v>
@@ -7685,13 +7823,13 @@
         <v>92.89</v>
       </c>
       <c r="J17" s="30">
-        <v>4.4800000000000004</v>
+        <v>4.53</v>
       </c>
       <c r="K17" s="30">
         <v>93.5</v>
       </c>
       <c r="L17" s="30">
-        <v>27.36</v>
+        <v>27.35</v>
       </c>
       <c r="M17" s="30">
         <v>91.26</v>
@@ -7702,16 +7840,32 @@
         <v>39</v>
       </c>
       <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
+      <c r="D18" s="30">
+        <v>42.38</v>
+      </c>
+      <c r="E18" s="30">
+        <v>89.39</v>
+      </c>
+      <c r="F18" s="30">
+        <v>60.22</v>
+      </c>
+      <c r="G18" s="30">
+        <v>82.2</v>
+      </c>
       <c r="H18" s="30"/>
       <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="30"/>
+      <c r="J18" s="30">
+        <v>6.84</v>
+      </c>
+      <c r="K18" s="30">
+        <v>90.35</v>
+      </c>
+      <c r="L18" s="30">
+        <v>37.5</v>
+      </c>
+      <c r="M18" s="30">
+        <v>80.5</v>
+      </c>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B19" s="29" t="s">
@@ -7719,16 +7873,16 @@
       </c>
       <c r="C19" s="34"/>
       <c r="D19" s="34">
-        <v>53.99</v>
+        <v>54.02</v>
       </c>
       <c r="E19" s="34">
         <v>30.4</v>
       </c>
       <c r="F19" s="34">
-        <v>75.69</v>
+        <v>75.39</v>
       </c>
       <c r="G19" s="34">
-        <v>25.6</v>
+        <v>26.43</v>
       </c>
       <c r="H19" s="34">
         <v>2.44</v>
@@ -7737,16 +7891,16 @@
         <v>53.79</v>
       </c>
       <c r="J19" s="34">
-        <v>8.73</v>
+        <v>8.7799999999999994</v>
       </c>
       <c r="K19" s="34">
-        <v>74.12</v>
+        <v>74.22</v>
       </c>
       <c r="L19" s="34">
         <v>43.75</v>
       </c>
       <c r="M19" s="34">
-        <v>51.58</v>
+        <v>51.59</v>
       </c>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.3">
@@ -7758,13 +7912,13 @@
         <v>58.57</v>
       </c>
       <c r="E20" s="34">
-        <v>28.7</v>
+        <v>28.71</v>
       </c>
       <c r="F20" s="34">
-        <v>78.45</v>
+        <v>78.2</v>
       </c>
       <c r="G20" s="34">
-        <v>16.760000000000002</v>
+        <v>17.52</v>
       </c>
       <c r="H20" s="34">
         <v>2.82</v>
@@ -7773,13 +7927,13 @@
         <v>30.87</v>
       </c>
       <c r="J20" s="34">
-        <v>9.5</v>
+        <v>9.56</v>
       </c>
       <c r="K20" s="34">
-        <v>55.77</v>
+        <v>55.75</v>
       </c>
       <c r="L20" s="34">
-        <v>47.11</v>
+        <v>47.1</v>
       </c>
       <c r="M20" s="34">
         <v>46.41</v>
@@ -7794,13 +7948,13 @@
         <v>61.18</v>
       </c>
       <c r="E21" s="30">
-        <v>28.37</v>
+        <v>28.38</v>
       </c>
       <c r="F21" s="30">
-        <v>79.010000000000005</v>
+        <v>78.75</v>
       </c>
       <c r="G21" s="30">
-        <v>16.16</v>
+        <v>16.989999999999998</v>
       </c>
       <c r="H21" s="30">
         <v>2.91</v>
@@ -7809,16 +7963,16 @@
         <v>30.88</v>
       </c>
       <c r="J21" s="30">
-        <v>9.6300000000000008</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="K21" s="30">
-        <v>54.26</v>
+        <v>54.31</v>
       </c>
       <c r="L21" s="30">
         <v>47.69</v>
       </c>
       <c r="M21" s="30">
-        <v>46.22</v>
+        <v>46.21</v>
       </c>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.3">
@@ -7827,16 +7981,16 @@
       </c>
       <c r="C22" s="30"/>
       <c r="D22" s="30">
-        <v>63.39</v>
+        <v>63.4</v>
       </c>
       <c r="E22" s="30">
         <v>27.09</v>
       </c>
       <c r="F22" s="35">
-        <v>81.23</v>
+        <v>80.95</v>
       </c>
       <c r="G22" s="30">
-        <v>13.23</v>
+        <v>14.95</v>
       </c>
       <c r="H22" s="30">
         <v>3.33</v>
@@ -7845,16 +7999,16 @@
         <v>31.26</v>
       </c>
       <c r="J22" s="30">
-        <v>10.29</v>
+        <v>10.37</v>
       </c>
       <c r="K22" s="30">
-        <v>55.32</v>
+        <v>55.49</v>
       </c>
       <c r="L22" s="30">
-        <v>49.86</v>
+        <v>49.87</v>
       </c>
       <c r="M22" s="30">
-        <v>44.63</v>
+        <v>44.62</v>
       </c>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.3">
@@ -7863,16 +8017,16 @@
       </c>
       <c r="C23" s="34"/>
       <c r="D23" s="34">
-        <v>64.27</v>
+        <v>64.28</v>
       </c>
       <c r="E23" s="34">
         <v>26.47</v>
       </c>
       <c r="F23" s="34">
-        <v>82.27</v>
+        <v>82</v>
       </c>
       <c r="G23" s="34">
-        <v>10.1</v>
+        <v>14.28</v>
       </c>
       <c r="H23" s="34">
         <v>3.58</v>
@@ -7881,13 +8035,13 @@
         <v>31.28</v>
       </c>
       <c r="J23" s="34">
-        <v>10.68</v>
+        <v>10.78</v>
       </c>
       <c r="K23" s="34">
-        <v>56.7</v>
+        <v>56.77</v>
       </c>
       <c r="L23" s="34">
-        <v>50.72</v>
+        <v>50.73</v>
       </c>
       <c r="M23" s="34">
         <v>44.22</v>
@@ -7905,10 +8059,10 @@
         <v>25.89</v>
       </c>
       <c r="F24" s="30">
-        <v>82.23</v>
+        <v>82.96</v>
       </c>
       <c r="G24" s="30">
-        <v>9.0399999999999991</v>
+        <v>10.92</v>
       </c>
       <c r="H24" s="30">
         <v>3.84</v>
@@ -7917,16 +8071,16 @@
         <v>31.17</v>
       </c>
       <c r="J24" s="30">
-        <v>11.13</v>
+        <v>11.22</v>
       </c>
       <c r="K24" s="30">
-        <v>56.71</v>
+        <v>56.83</v>
       </c>
       <c r="L24" s="30">
-        <v>51.47</v>
+        <v>51.48</v>
       </c>
       <c r="M24" s="30">
-        <v>43.53</v>
+        <v>43.54</v>
       </c>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.3">
@@ -7938,13 +8092,13 @@
         <v>67.64</v>
       </c>
       <c r="E25" s="30">
-        <v>24.33</v>
-      </c>
-      <c r="F25" s="30">
-        <v>85.54</v>
+        <v>24.34</v>
+      </c>
+      <c r="F25">
+        <v>85.28</v>
       </c>
       <c r="G25" s="30">
-        <v>10.210000000000001</v>
+        <v>11.74</v>
       </c>
       <c r="H25" s="30">
         <v>4.7699999999999996</v>
@@ -7953,16 +8107,16 @@
         <v>31.85</v>
       </c>
       <c r="J25" s="30">
-        <v>12.55</v>
+        <v>12.64</v>
       </c>
       <c r="K25" s="30">
-        <v>57.72</v>
+        <v>57.88</v>
       </c>
       <c r="L25" s="30">
         <v>53.18</v>
       </c>
       <c r="M25" s="30">
-        <v>42.7</v>
+        <v>42.69</v>
       </c>
       <c r="O25" s="33"/>
     </row>
@@ -7978,10 +8132,10 @@
         <v>9.82</v>
       </c>
       <c r="F26" s="30">
-        <v>88.34</v>
+        <v>88.12</v>
       </c>
       <c r="G26" s="30">
-        <v>11.92</v>
+        <v>12.57</v>
       </c>
       <c r="H26" s="30">
         <v>6.37</v>
@@ -7990,10 +8144,10 @@
         <v>32.71</v>
       </c>
       <c r="J26" s="30">
-        <v>14.47</v>
+        <v>14.55</v>
       </c>
       <c r="K26" s="30">
-        <v>57.57</v>
+        <v>57.56</v>
       </c>
       <c r="L26" s="30">
         <v>54.85</v>
@@ -8007,100 +8161,128 @@
         <v>31</v>
       </c>
       <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
+      <c r="D27" s="30">
+        <v>79.900000000000006</v>
+      </c>
+      <c r="E27" s="30">
+        <v>6.72</v>
+      </c>
+      <c r="F27" s="30">
+        <v>90.94</v>
+      </c>
+      <c r="G27" s="30">
+        <v>15.04</v>
+      </c>
       <c r="H27" s="30"/>
       <c r="I27" s="30"/>
-      <c r="J27" s="30"/>
-      <c r="K27" s="30"/>
-      <c r="L27" s="30"/>
-      <c r="M27" s="30"/>
+      <c r="J27" s="30">
+        <v>15.54</v>
+      </c>
+      <c r="K27" s="30">
+        <v>56.61</v>
+      </c>
+      <c r="L27" s="30">
+        <v>56.09</v>
+      </c>
+      <c r="M27" s="30">
+        <v>39.799999999999997</v>
+      </c>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B28" s="29" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C28" s="30"/>
       <c r="D28" s="30">
-        <v>83.89</v>
+        <v>82.66</v>
       </c>
       <c r="E28" s="30">
-        <v>3.91</v>
+        <v>4.93</v>
       </c>
       <c r="F28" s="30">
-        <v>91.31</v>
+        <v>91</v>
       </c>
       <c r="G28" s="30">
-        <v>17.89</v>
-      </c>
-      <c r="H28" s="30">
-        <v>7.97</v>
-      </c>
-      <c r="I28" s="30">
-        <v>34.31</v>
-      </c>
+        <v>16.91</v>
+      </c>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
       <c r="J28" s="30">
-        <v>15.64</v>
+        <v>15.66</v>
       </c>
       <c r="K28" s="30">
-        <v>55.85</v>
+        <v>56.15</v>
       </c>
       <c r="L28" s="30">
-        <v>56.42</v>
+        <v>56.37</v>
       </c>
       <c r="M28" s="30">
-        <v>39.4</v>
+        <v>39.11</v>
       </c>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B29" s="29" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
+      <c r="D29" s="30">
+        <v>83.9</v>
+      </c>
+      <c r="E29" s="30">
+        <v>3.91</v>
+      </c>
+      <c r="F29" s="30">
+        <v>91.17</v>
+      </c>
+      <c r="G29" s="30">
+        <v>17.68</v>
+      </c>
+      <c r="H29" s="30">
+        <v>7.97</v>
+      </c>
+      <c r="I29" s="30">
+        <v>34.31</v>
+      </c>
+      <c r="J29" s="30">
+        <v>15.69</v>
+      </c>
+      <c r="K29" s="30">
+        <v>55.95</v>
+      </c>
+      <c r="L29" s="30">
+        <v>56.43</v>
+      </c>
+      <c r="M29" s="30">
+        <v>39.43</v>
+      </c>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B30" s="29" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C30" s="30"/>
       <c r="D30" s="30">
-        <v>85.11</v>
+        <v>84.85</v>
       </c>
       <c r="E30" s="30">
-        <v>2.97</v>
+        <v>3.18</v>
       </c>
       <c r="F30" s="30">
-        <v>91.42</v>
+        <v>91.29</v>
       </c>
       <c r="G30" s="30">
-        <v>21.24</v>
-      </c>
-      <c r="H30" s="30">
-        <v>7.86</v>
-      </c>
-      <c r="I30" s="30">
-        <v>34.380000000000003</v>
-      </c>
+        <v>19.440000000000001</v>
+      </c>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
       <c r="J30" s="30">
-        <v>15.65</v>
+        <v>15.7</v>
       </c>
       <c r="K30" s="30">
-        <v>55.84</v>
+        <v>56</v>
       </c>
       <c r="L30" s="30">
-        <v>56.43</v>
+        <v>56.45</v>
       </c>
       <c r="M30" s="30">
         <v>40.380000000000003</v>
@@ -8108,20 +8290,20 @@
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B31" s="29" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C31" s="30"/>
       <c r="D31" s="30">
-        <v>85.11</v>
+        <v>85.12</v>
       </c>
       <c r="E31" s="30">
         <v>2.97</v>
       </c>
       <c r="F31" s="30">
-        <v>91.42</v>
+        <v>91.31</v>
       </c>
       <c r="G31" s="30">
-        <v>21.24</v>
+        <v>20.47</v>
       </c>
       <c r="H31" s="30">
         <v>7.86</v>
@@ -8130,34 +8312,34 @@
         <v>34.380000000000003</v>
       </c>
       <c r="J31" s="30">
-        <v>15.65</v>
+        <v>15.69</v>
       </c>
       <c r="K31" s="30">
-        <v>55.84</v>
+        <v>55.98</v>
       </c>
       <c r="L31" s="30">
-        <v>56.43</v>
+        <v>56.44</v>
       </c>
       <c r="M31" s="30">
-        <v>40.380000000000003</v>
+        <v>40.369999999999997</v>
       </c>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B32" s="29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C32" s="30"/>
       <c r="D32" s="30">
-        <v>85.11</v>
+        <v>85.25</v>
       </c>
       <c r="E32" s="30">
-        <v>2.97</v>
+        <v>2.86</v>
       </c>
       <c r="F32" s="30">
-        <v>91.42</v>
+        <v>91.31</v>
       </c>
       <c r="G32" s="30">
-        <v>21.24</v>
+        <v>21.04</v>
       </c>
       <c r="H32" s="30">
         <v>7.86</v>
@@ -8166,10 +8348,10 @@
         <v>34.380000000000003</v>
       </c>
       <c r="J32" s="30">
-        <v>15.65</v>
+        <v>15.69</v>
       </c>
       <c r="K32" s="30">
-        <v>55.84</v>
+        <v>56</v>
       </c>
       <c r="L32" s="30">
         <v>56.43</v>
@@ -8180,20 +8362,20 @@
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" s="29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C33" s="30"/>
       <c r="D33" s="30">
-        <v>85.11</v>
+        <v>85.33</v>
       </c>
       <c r="E33" s="30">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="F33" s="30">
-        <v>91.42</v>
+        <v>91.31</v>
       </c>
       <c r="G33" s="30">
-        <v>21.24</v>
+        <v>21.37</v>
       </c>
       <c r="H33" s="30">
         <v>7.86</v>
@@ -8202,34 +8384,34 @@
         <v>34.380000000000003</v>
       </c>
       <c r="J33" s="30">
-        <v>15.65</v>
+        <v>15.68</v>
       </c>
       <c r="K33" s="30">
-        <v>55.84</v>
+        <v>56.06</v>
       </c>
       <c r="L33" s="30">
-        <v>56.43</v>
+        <v>56.42</v>
       </c>
       <c r="M33" s="30">
-        <v>40.380000000000003</v>
+        <v>40.42</v>
       </c>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" s="29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C34" s="30"/>
       <c r="D34" s="30">
-        <v>85.11</v>
+        <v>85.38</v>
       </c>
       <c r="E34" s="30">
-        <v>2.97</v>
+        <v>2.76</v>
       </c>
       <c r="F34" s="30">
-        <v>91.42</v>
+        <v>91.3</v>
       </c>
       <c r="G34" s="30">
-        <v>21.24</v>
+        <v>21.52</v>
       </c>
       <c r="H34" s="30">
         <v>7.86</v>
@@ -8238,34 +8420,34 @@
         <v>34.380000000000003</v>
       </c>
       <c r="J34" s="30">
-        <v>15.65</v>
+        <v>15.68</v>
       </c>
       <c r="K34" s="30">
-        <v>55.84</v>
+        <v>56.08</v>
       </c>
       <c r="L34" s="30">
-        <v>56.43</v>
+        <v>56.42</v>
       </c>
       <c r="M34" s="30">
-        <v>40.380000000000003</v>
+        <v>40.479999999999997</v>
       </c>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B35" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C35" s="30"/>
       <c r="D35" s="30">
-        <v>85.11</v>
+        <v>85.42</v>
       </c>
       <c r="E35" s="30">
-        <v>2.97</v>
+        <v>2.73</v>
       </c>
       <c r="F35" s="30">
-        <v>91.42</v>
+        <v>91.3</v>
       </c>
       <c r="G35" s="30">
-        <v>21.24</v>
+        <v>21.62</v>
       </c>
       <c r="H35" s="30">
         <v>7.86</v>
@@ -8274,34 +8456,34 @@
         <v>34.380000000000003</v>
       </c>
       <c r="J35" s="30">
-        <v>15.65</v>
+        <v>15.68</v>
       </c>
       <c r="K35" s="30">
-        <v>55.84</v>
+        <v>56.12</v>
       </c>
       <c r="L35" s="30">
-        <v>56.43</v>
+        <v>56.42</v>
       </c>
       <c r="M35" s="30">
-        <v>40.380000000000003</v>
+        <v>41.14</v>
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B36" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C36" s="30"/>
       <c r="D36" s="30">
-        <v>85.11</v>
+        <v>85.45</v>
       </c>
       <c r="E36" s="30">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="F36" s="30">
-        <v>91.42</v>
+        <v>91.3</v>
       </c>
       <c r="G36" s="30">
-        <v>21.24</v>
+        <v>21.75</v>
       </c>
       <c r="H36" s="30">
         <v>7.86</v>
@@ -8310,40 +8492,77 @@
         <v>34.380000000000003</v>
       </c>
       <c r="J36" s="30">
-        <v>15.65</v>
+        <v>15.68</v>
       </c>
       <c r="K36" s="30">
-        <v>55.84</v>
+        <v>56.15</v>
       </c>
       <c r="L36" s="30">
-        <v>56.43</v>
+        <v>56.42</v>
       </c>
       <c r="M36" s="30">
-        <v>40.380000000000003</v>
+        <v>41.32</v>
       </c>
     </row>
-    <row r="37" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C37" s="23" t="s">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B37" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30">
+        <v>85.47</v>
+      </c>
+      <c r="E37" s="30">
+        <v>2.68</v>
+      </c>
+      <c r="F37" s="53">
+        <v>91.29</v>
+      </c>
+      <c r="G37" s="30">
+        <v>21.84</v>
+      </c>
+      <c r="H37" s="30">
+        <v>7.86</v>
+      </c>
+      <c r="I37" s="30">
+        <v>34.380000000000003</v>
+      </c>
+      <c r="J37" s="30">
+        <v>15.68</v>
+      </c>
+      <c r="K37" s="30">
+        <v>56.18</v>
+      </c>
+      <c r="L37" s="30">
+        <v>56.41</v>
+      </c>
+      <c r="M37" s="30">
+        <v>41.43</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C38" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D37" s="48"/>
-      <c r="E37" s="49"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="49"/>
-      <c r="H37" s="50"/>
-      <c r="I37" s="51"/>
-      <c r="J37" s="48"/>
-      <c r="K37" s="49"/>
-      <c r="L37" s="48"/>
-      <c r="M37" s="49"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="37"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="37"/>
+      <c r="H38" s="38"/>
+      <c r="I38" s="39"/>
+      <c r="J38" s="36"/>
+      <c r="K38" s="37"/>
+      <c r="L38" s="36"/>
+      <c r="M38" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="B14:M14"/>
@@ -8352,12 +8571,11 @@
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="J15:K15"/>
     <mergeCell ref="L15:M15"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="L38:M38"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Results_metrics.xlsx
+++ b/Results_metrics.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aless\OneDrive\Desktop\MaskArchitectureAnomaly_CourseProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Enrica\Desktop\Nuovo_ML_Project\MaskArchitectureAnomaly_CourseProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48F19592-3D82-46E9-BDB7-6BDD75B42717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81CAC98D-6556-4752-9F6B-86810F087FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -683,6 +683,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -731,8 +733,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -870,9 +870,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$31</c:f>
+              <c:f>Foglio1!$B$17:$B$37</c:f>
               <c:strCache>
-                <c:ptCount val="15"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -917,16 +917,34 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>t = 10</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>t = 12,5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>t = 15</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>t = 17,5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>t = 20</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>t = 22,5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>t = 25</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$D$17:$D$31</c:f>
+              <c:f>Foglio1!$D$17:$D$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>34.29</c:v>
                 </c:pt>
@@ -971,6 +989,24 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>85.12</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>85.25</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>85.33</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>85.38</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>85.42</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>85.45</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>85.47</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1022,9 +1058,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$31</c:f>
+              <c:f>Foglio1!$B$17:$B$37</c:f>
               <c:strCache>
-                <c:ptCount val="15"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -1069,16 +1105,34 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>t = 10</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>t = 12,5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>t = 15</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>t = 17,5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>t = 20</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>t = 22,5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>t = 25</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$E$17:$E$31</c:f>
+              <c:f>Foglio1!$E$17:$E$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>91.9</c:v>
                 </c:pt>
@@ -1123,6 +1177,24 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>2.97</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.86</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.8</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.76</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.73</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.68</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1567,9 +1639,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$31</c:f>
+              <c:f>Foglio1!$B$17:$B$37</c:f>
               <c:strCache>
-                <c:ptCount val="15"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -1614,16 +1686,34 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>t = 10</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>t = 12,5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>t = 15</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>t = 17,5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>t = 20</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>t = 22,5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>t = 25</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$F$17:$F$31</c:f>
+              <c:f>Foglio1!$F$17:$F$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>33.64</c:v>
                 </c:pt>
@@ -1668,6 +1758,24 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>91.31</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>91.31</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>91.31</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>91.3</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>91.3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>91.3</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>91.29</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1719,9 +1827,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$31</c:f>
+              <c:f>Foglio1!$B$17:$B$37</c:f>
               <c:strCache>
-                <c:ptCount val="15"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -1766,16 +1874,34 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>t = 10</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>t = 12,5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>t = 15</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>t = 17,5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>t = 20</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>t = 22,5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>t = 25</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$G$17:$G$31</c:f>
+              <c:f>Foglio1!$G$17:$G$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>91.83</c:v>
                 </c:pt>
@@ -1820,6 +1946,24 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>20.47</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>21.04</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>21.37</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>21.52</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>21.62</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>21.75</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21.84</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2264,9 +2408,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$31</c:f>
+              <c:f>Foglio1!$B$17:$B$37</c:f>
               <c:strCache>
-                <c:ptCount val="15"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -2311,16 +2455,34 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>t = 10</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>t = 12,5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>t = 15</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>t = 17,5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>t = 20</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>t = 22,5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>t = 25</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$H$17:$H$31</c:f>
+              <c:f>Foglio1!$H$17:$H$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>1.08</c:v>
                 </c:pt>
@@ -2352,6 +2514,24 @@
                   <c:v>7.97</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>7.86</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7.86</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7.86</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>7.86</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>7.86</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>7.86</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>7.86</c:v>
                 </c:pt>
               </c:numCache>
@@ -2404,9 +2584,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$31</c:f>
+              <c:f>Foglio1!$B$17:$B$37</c:f>
               <c:strCache>
-                <c:ptCount val="15"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -2451,16 +2631,34 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>t = 10</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>t = 12,5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>t = 15</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>t = 17,5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>t = 20</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>t = 22,5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>t = 25</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$I$17:$I$31</c:f>
+              <c:f>Foglio1!$I$17:$I$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>92.89</c:v>
                 </c:pt>
@@ -2492,6 +2690,24 @@
                   <c:v>34.31</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>34.380000000000003</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>34.380000000000003</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>34.380000000000003</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>34.380000000000003</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>34.380000000000003</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>34.380000000000003</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>34.380000000000003</c:v>
                 </c:pt>
               </c:numCache>
@@ -2937,9 +3153,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$31</c:f>
+              <c:f>Foglio1!$B$17:$B$37</c:f>
               <c:strCache>
-                <c:ptCount val="15"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -2984,16 +3200,34 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>t = 10</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>t = 12,5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>t = 15</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>t = 17,5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>t = 20</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>t = 22,5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>t = 25</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$J$17:$J$31</c:f>
+              <c:f>Foglio1!$J$17:$J$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>4.53</c:v>
                 </c:pt>
@@ -3038,6 +3272,24 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>15.69</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15.69</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>15.68</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>15.68</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>15.68</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>15.68</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>15.68</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3089,9 +3341,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Foglio1!$B$17:$B$31</c:f>
+              <c:f>Foglio1!$B$17:$B$37</c:f>
               <c:strCache>
-                <c:ptCount val="15"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>t = 0,1</c:v>
                 </c:pt>
@@ -3136,16 +3388,34 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>t = 10</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>t = 12,5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>t = 15</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>t = 17,5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>t = 20</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>t = 22,5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>t = 25</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$K$17:$K$31</c:f>
+              <c:f>Foglio1!$K$17:$K$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>93.5</c:v>
                 </c:pt>
@@ -3190,6 +3460,24 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>55.98</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>56.06</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>56.08</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>56.12</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>56.15</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>56.18</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3687,10 +3975,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$L$17:$L$30</c:f>
+              <c:f>Foglio1!$L$17:$L$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>27.35</c:v>
                 </c:pt>
@@ -3732,6 +4020,27 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>56.45</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>56.44</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>56.43</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>56.42</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>56.42</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>56.42</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>56.42</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>56.41</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3836,10 +4145,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Foglio1!$M$17:$M$30</c:f>
+              <c:f>Foglio1!$M$17:$M$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>91.26</c:v>
                 </c:pt>
@@ -3881,6 +4190,27 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>40.380000000000003</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>40.369999999999997</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>40.380000000000003</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>40.42</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>40.479999999999997</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>41.14</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>41.32</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>41.43</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6930,10 +7260,10 @@
       <xdr:rowOff>151581</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>482279</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>106102</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>27709</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>13854</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6960,16 +7290,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>607670</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>4303</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>67519</xdr:rowOff>
+      <xdr:rowOff>67520</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>503787</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>41331</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>13853</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>138546</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6998,16 +7328,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>318304</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>567685</xdr:colOff>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>173621</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>146903</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>12396</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>83127</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7036,16 +7366,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>414760</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>163975</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>331632</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>177827</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>310878</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>2750</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>207818</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>16603</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7075,15 +7405,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>598026</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>173621</xdr:rowOff>
+      <xdr:colOff>581891</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>35074</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>494143</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>12396</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>96981</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>124691</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7385,44 +7715,44 @@
   <sheetData>
     <row r="1" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="51"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="53"/>
     </row>
     <row r="3" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
       <c r="C3" s="5"/>
-      <c r="D3" s="48" t="s">
+      <c r="D3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="49"/>
-      <c r="F3" s="48" t="s">
+      <c r="E3" s="51"/>
+      <c r="F3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="49"/>
-      <c r="H3" s="48" t="s">
+      <c r="G3" s="51"/>
+      <c r="H3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="49"/>
-      <c r="J3" s="48" t="s">
+      <c r="I3" s="51"/>
+      <c r="J3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="49"/>
-      <c r="L3" s="48" t="s">
+      <c r="K3" s="51"/>
+      <c r="L3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="49"/>
+      <c r="M3" s="51"/>
     </row>
     <row r="4" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="6" t="s">
@@ -7463,7 +7793,7 @@
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="42" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -7501,7 +7831,7 @@
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B6" s="41"/>
+      <c r="B6" s="43"/>
       <c r="C6" s="9" t="s">
         <v>11</v>
       </c>
@@ -7537,7 +7867,7 @@
       </c>
     </row>
     <row r="7" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="42"/>
+      <c r="B7" s="44"/>
       <c r="C7" s="11" t="s">
         <v>12</v>
       </c>
@@ -7573,7 +7903,7 @@
       </c>
     </row>
     <row r="8" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="45" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="12" t="s">
@@ -7611,7 +7941,7 @@
       </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B9" s="41"/>
+      <c r="B9" s="43"/>
       <c r="C9" s="9" t="s">
         <v>11</v>
       </c>
@@ -7647,7 +7977,7 @@
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B10" s="41"/>
+      <c r="B10" s="43"/>
       <c r="C10" s="9" t="s">
         <v>12</v>
       </c>
@@ -7683,7 +8013,7 @@
       </c>
     </row>
     <row r="11" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="44"/>
+      <c r="B11" s="46"/>
       <c r="C11" s="10" t="s">
         <v>14</v>
       </c>
@@ -7720,44 +8050,44 @@
     </row>
     <row r="13" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="14" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="47"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="48"/>
+      <c r="M14" s="49"/>
     </row>
     <row r="15" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="24"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="48" t="s">
+      <c r="D15" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="E15" s="49"/>
-      <c r="F15" s="48" t="s">
+      <c r="E15" s="51"/>
+      <c r="F15" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="49"/>
-      <c r="H15" s="48" t="s">
+      <c r="G15" s="51"/>
+      <c r="H15" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="49"/>
-      <c r="J15" s="48" t="s">
+      <c r="I15" s="51"/>
+      <c r="J15" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="49"/>
-      <c r="L15" s="48" t="s">
+      <c r="K15" s="51"/>
+      <c r="L15" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="M15" s="49"/>
+      <c r="M15" s="51"/>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
@@ -7801,7 +8131,7 @@
       <c r="B17" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="52">
+      <c r="C17" s="36">
         <v>0.77429999999999999</v>
       </c>
       <c r="D17" s="30">
@@ -8515,7 +8845,7 @@
       <c r="E37" s="30">
         <v>2.68</v>
       </c>
-      <c r="F37" s="53">
+      <c r="F37" s="37">
         <v>91.29</v>
       </c>
       <c r="G37" s="30">
@@ -8544,16 +8874,16 @@
       <c r="C38" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="36"/>
-      <c r="E38" s="37"/>
-      <c r="F38" s="36"/>
-      <c r="G38" s="37"/>
-      <c r="H38" s="38"/>
-      <c r="I38" s="39"/>
-      <c r="J38" s="36"/>
-      <c r="K38" s="37"/>
-      <c r="L38" s="36"/>
-      <c r="M38" s="37"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="39"/>
+      <c r="H38" s="40"/>
+      <c r="I38" s="41"/>
+      <c r="J38" s="38"/>
+      <c r="K38" s="39"/>
+      <c r="L38" s="38"/>
+      <c r="M38" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="19">

--- a/Results_metrics.xlsx
+++ b/Results_metrics.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Enrica\Desktop\Nuovo_ML_Project\MaskArchitectureAnomaly_CourseProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aless\OneDrive\Desktop\MaskArchitectureAnomaly_CourseProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81CAC98D-6556-4752-9F6B-86810F087FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC2AED4-255C-4139-A1E8-3BDA6D35D572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -685,16 +685,19 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -712,25 +715,22 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2486,6 +2486,9 @@
                 <c:pt idx="0">
                   <c:v>1.08</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.86</c:v>
+                </c:pt>
                 <c:pt idx="2">
                   <c:v>2.44</c:v>
                 </c:pt>
@@ -2514,24 +2517,6 @@
                   <c:v>7.97</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>7.86</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>7.86</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>7.86</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>7.86</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7.86</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7.86</c:v>
-                </c:pt>
-                <c:pt idx="20">
                   <c:v>7.86</c:v>
                 </c:pt>
               </c:numCache>
@@ -2662,6 +2647,9 @@
                 <c:pt idx="0">
                   <c:v>92.89</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>86.68</c:v>
+                </c:pt>
                 <c:pt idx="2">
                   <c:v>53.79</c:v>
                 </c:pt>
@@ -2690,24 +2678,6 @@
                   <c:v>34.31</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>34.380000000000003</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>34.380000000000003</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>34.380000000000003</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>34.380000000000003</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>34.380000000000003</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>34.380000000000003</c:v>
-                </c:pt>
-                <c:pt idx="20">
                   <c:v>34.380000000000003</c:v>
                 </c:pt>
               </c:numCache>
@@ -7715,44 +7685,44 @@
   <sheetData>
     <row r="1" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="53"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="40"/>
     </row>
     <row r="3" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
       <c r="C3" s="5"/>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50" t="s">
+      <c r="E3" s="42"/>
+      <c r="F3" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="51"/>
-      <c r="H3" s="50" t="s">
+      <c r="G3" s="42"/>
+      <c r="H3" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="51"/>
-      <c r="J3" s="50" t="s">
+      <c r="I3" s="42"/>
+      <c r="J3" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="51"/>
-      <c r="L3" s="50" t="s">
+      <c r="K3" s="42"/>
+      <c r="L3" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="51"/>
+      <c r="M3" s="42"/>
     </row>
     <row r="4" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="6" t="s">
@@ -7793,7 +7763,7 @@
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="43" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -7831,7 +7801,7 @@
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B6" s="43"/>
+      <c r="B6" s="44"/>
       <c r="C6" s="9" t="s">
         <v>11</v>
       </c>
@@ -7867,7 +7837,7 @@
       </c>
     </row>
     <row r="7" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="44"/>
+      <c r="B7" s="45"/>
       <c r="C7" s="11" t="s">
         <v>12</v>
       </c>
@@ -7903,7 +7873,7 @@
       </c>
     </row>
     <row r="8" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="46" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="12" t="s">
@@ -7941,7 +7911,7 @@
       </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B9" s="43"/>
+      <c r="B9" s="44"/>
       <c r="C9" s="9" t="s">
         <v>11</v>
       </c>
@@ -7977,7 +7947,7 @@
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B10" s="43"/>
+      <c r="B10" s="44"/>
       <c r="C10" s="9" t="s">
         <v>12</v>
       </c>
@@ -8013,7 +7983,7 @@
       </c>
     </row>
     <row r="11" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="46"/>
+      <c r="B11" s="47"/>
       <c r="C11" s="10" t="s">
         <v>14</v>
       </c>
@@ -8050,7 +8020,7 @@
     </row>
     <row r="13" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="14" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="47" t="s">
+      <c r="B14" s="38" t="s">
         <v>19</v>
       </c>
       <c r="C14" s="48"/>
@@ -8068,26 +8038,26 @@
     <row r="15" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="24"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="50" t="s">
+      <c r="D15" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="E15" s="51"/>
-      <c r="F15" s="50" t="s">
+      <c r="E15" s="42"/>
+      <c r="F15" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="51"/>
-      <c r="H15" s="50" t="s">
+      <c r="G15" s="42"/>
+      <c r="H15" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="51"/>
-      <c r="J15" s="50" t="s">
+      <c r="I15" s="42"/>
+      <c r="J15" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="51"/>
-      <c r="L15" s="50" t="s">
+      <c r="K15" s="42"/>
+      <c r="L15" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="M15" s="51"/>
+      <c r="M15" s="42"/>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
@@ -8182,8 +8152,12 @@
       <c r="G18" s="30">
         <v>82.2</v>
       </c>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
+      <c r="H18" s="30">
+        <v>1.86</v>
+      </c>
+      <c r="I18" s="30">
+        <v>86.68</v>
+      </c>
       <c r="J18" s="30">
         <v>6.84</v>
       </c>
@@ -8671,12 +8645,8 @@
       <c r="G32" s="30">
         <v>21.04</v>
       </c>
-      <c r="H32" s="30">
-        <v>7.86</v>
-      </c>
-      <c r="I32" s="30">
-        <v>34.380000000000003</v>
-      </c>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
       <c r="J32" s="30">
         <v>15.69</v>
       </c>
@@ -8707,12 +8677,8 @@
       <c r="G33" s="30">
         <v>21.37</v>
       </c>
-      <c r="H33" s="30">
-        <v>7.86</v>
-      </c>
-      <c r="I33" s="30">
-        <v>34.380000000000003</v>
-      </c>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
       <c r="J33" s="30">
         <v>15.68</v>
       </c>
@@ -8743,12 +8709,8 @@
       <c r="G34" s="30">
         <v>21.52</v>
       </c>
-      <c r="H34" s="30">
-        <v>7.86</v>
-      </c>
-      <c r="I34" s="30">
-        <v>34.380000000000003</v>
-      </c>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
       <c r="J34" s="30">
         <v>15.68</v>
       </c>
@@ -8779,12 +8741,8 @@
       <c r="G35" s="30">
         <v>21.62</v>
       </c>
-      <c r="H35" s="30">
-        <v>7.86</v>
-      </c>
-      <c r="I35" s="30">
-        <v>34.380000000000003</v>
-      </c>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
       <c r="J35" s="30">
         <v>15.68</v>
       </c>
@@ -8815,12 +8773,8 @@
       <c r="G36" s="30">
         <v>21.75</v>
       </c>
-      <c r="H36" s="30">
-        <v>7.86</v>
-      </c>
-      <c r="I36" s="30">
-        <v>34.380000000000003</v>
-      </c>
+      <c r="H36" s="30"/>
+      <c r="I36" s="30"/>
       <c r="J36" s="30">
         <v>15.68</v>
       </c>
@@ -8851,12 +8805,8 @@
       <c r="G37" s="30">
         <v>21.84</v>
       </c>
-      <c r="H37" s="30">
-        <v>7.86</v>
-      </c>
-      <c r="I37" s="30">
-        <v>34.380000000000003</v>
-      </c>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
       <c r="J37" s="30">
         <v>15.68</v>
       </c>
@@ -8874,25 +8824,24 @@
       <c r="C38" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="38"/>
-      <c r="E38" s="39"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="39"/>
-      <c r="H38" s="40"/>
-      <c r="I38" s="41"/>
-      <c r="J38" s="38"/>
-      <c r="K38" s="39"/>
-      <c r="L38" s="38"/>
-      <c r="M38" s="39"/>
+      <c r="D38" s="50"/>
+      <c r="E38" s="51"/>
+      <c r="F38" s="50"/>
+      <c r="G38" s="51"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="50"/>
+      <c r="K38" s="51"/>
+      <c r="L38" s="50"/>
+      <c r="M38" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="L38:M38"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="B14:M14"/>
@@ -8901,11 +8850,12 @@
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="J15:K15"/>
     <mergeCell ref="L15:M15"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Results_metrics.xlsx
+++ b/Results_metrics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aless\OneDrive\Desktop\MaskArchitectureAnomaly_CourseProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC2AED4-255C-4139-A1E8-3BDA6D35D572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE53E2DC-B2B5-4A53-8C13-C4FD2B1A0EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -2513,11 +2513,38 @@
                 <c:pt idx="9">
                   <c:v>6.37</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>7.68</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7.94</c:v>
+                </c:pt>
                 <c:pt idx="12">
                   <c:v>7.97</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>7.91</c:v>
+                </c:pt>
                 <c:pt idx="14">
                   <c:v>7.86</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7.82</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7.79</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>7.77</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>7.76</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>7.75</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>7.74</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2674,11 +2701,38 @@
                 <c:pt idx="9">
                   <c:v>32.71</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>34.82</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>34.950000000000003</c:v>
+                </c:pt>
                 <c:pt idx="12">
                   <c:v>34.31</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>34.03</c:v>
+                </c:pt>
                 <c:pt idx="14">
                   <c:v>34.380000000000003</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>34.520000000000003</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>34.729999999999997</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>34.99</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>35.090000000000003</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>35.18</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>35.24</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8477,8 +8531,12 @@
       <c r="G27" s="30">
         <v>15.04</v>
       </c>
-      <c r="H27" s="30"/>
-      <c r="I27" s="30"/>
+      <c r="H27" s="30">
+        <v>7.68</v>
+      </c>
+      <c r="I27" s="30">
+        <v>34.82</v>
+      </c>
       <c r="J27" s="30">
         <v>15.54</v>
       </c>
@@ -8509,8 +8567,12 @@
       <c r="G28" s="30">
         <v>16.91</v>
       </c>
-      <c r="H28" s="30"/>
-      <c r="I28" s="30"/>
+      <c r="H28" s="30">
+        <v>7.94</v>
+      </c>
+      <c r="I28" s="30">
+        <v>34.950000000000003</v>
+      </c>
       <c r="J28" s="30">
         <v>15.66</v>
       </c>
@@ -8577,8 +8639,12 @@
       <c r="G30" s="30">
         <v>19.440000000000001</v>
       </c>
-      <c r="H30" s="30"/>
-      <c r="I30" s="30"/>
+      <c r="H30" s="30">
+        <v>7.91</v>
+      </c>
+      <c r="I30" s="30">
+        <v>34.03</v>
+      </c>
       <c r="J30" s="30">
         <v>15.7</v>
       </c>
@@ -8645,8 +8711,12 @@
       <c r="G32" s="30">
         <v>21.04</v>
       </c>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
+      <c r="H32" s="30">
+        <v>7.82</v>
+      </c>
+      <c r="I32" s="30">
+        <v>34.520000000000003</v>
+      </c>
       <c r="J32" s="30">
         <v>15.69</v>
       </c>
@@ -8677,8 +8747,12 @@
       <c r="G33" s="30">
         <v>21.37</v>
       </c>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
+      <c r="H33" s="30">
+        <v>7.79</v>
+      </c>
+      <c r="I33" s="30">
+        <v>34.729999999999997</v>
+      </c>
       <c r="J33" s="30">
         <v>15.68</v>
       </c>
@@ -8709,8 +8783,12 @@
       <c r="G34" s="30">
         <v>21.52</v>
       </c>
-      <c r="H34" s="30"/>
-      <c r="I34" s="30"/>
+      <c r="H34" s="30">
+        <v>7.77</v>
+      </c>
+      <c r="I34" s="30">
+        <v>34.99</v>
+      </c>
       <c r="J34" s="30">
         <v>15.68</v>
       </c>
@@ -8741,8 +8819,12 @@
       <c r="G35" s="30">
         <v>21.62</v>
       </c>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
+      <c r="H35" s="30">
+        <v>7.76</v>
+      </c>
+      <c r="I35" s="30">
+        <v>35.090000000000003</v>
+      </c>
       <c r="J35" s="30">
         <v>15.68</v>
       </c>
@@ -8773,8 +8855,12 @@
       <c r="G36" s="30">
         <v>21.75</v>
       </c>
-      <c r="H36" s="30"/>
-      <c r="I36" s="30"/>
+      <c r="H36" s="30">
+        <v>7.75</v>
+      </c>
+      <c r="I36" s="30">
+        <v>35.18</v>
+      </c>
       <c r="J36" s="30">
         <v>15.68</v>
       </c>
@@ -8805,8 +8891,12 @@
       <c r="G37" s="30">
         <v>21.84</v>
       </c>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
+      <c r="H37" s="30">
+        <v>7.74</v>
+      </c>
+      <c r="I37" s="30">
+        <v>35.24</v>
+      </c>
       <c r="J37" s="30">
         <v>15.68</v>
       </c>

--- a/Results_metrics.xlsx
+++ b/Results_metrics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aless\OneDrive\Desktop\MaskArchitectureAnomaly_CourseProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Enrica\Desktop\Nuovo_ML_Project\MaskArchitectureAnomaly_CourseProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE53E2DC-B2B5-4A53-8C13-C4FD2B1A0EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1523F03-0172-4C2F-A11F-EE0114E63202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11232" yWindow="0" windowWidth="11808" windowHeight="12072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="49">
   <si>
     <t>Model</t>
   </si>
@@ -148,6 +148,30 @@
   </si>
   <si>
     <t>t = 4</t>
+  </si>
+  <si>
+    <t>RISULTATI METRICHE con Logitnorm tau = 0,01</t>
+  </si>
+  <si>
+    <t>RISULTATI METRICHE per EoMT con TEMPERATURE su MSP con Logitnorm tau=0,01</t>
+  </si>
+  <si>
+    <t>RISULTATI METRICHE con Logitnorm tau = 0,04</t>
+  </si>
+  <si>
+    <t>RISULTATI METRICHE per EoMT con TEMPERATURE su MSP con Logitnorm tau = 0,04</t>
+  </si>
+  <si>
+    <t>RISULTATI METRICHE con Logitnorm tau = 0,07</t>
+  </si>
+  <si>
+    <t>RISULTATI METRICHE per EoMT con TEMPERATURE su MSP con Logitnorm tau = 0,07</t>
+  </si>
+  <si>
+    <t>RISULTATI METRICHE con Logitnorm tau = 0,10</t>
+  </si>
+  <si>
+    <t>RISULTATI METRICHE per EoMT con TEMPERATURE su MSP con Logitnorm tau = 0,10</t>
   </si>
 </sst>
 </file>
@@ -685,42 +709,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -732,6 +720,42 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7730,55 +7754,199 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:O38"/>
+  <dimension ref="B1:CB38"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.44140625" customWidth="1"/>
     <col min="3" max="3" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="38" t="s">
+    <row r="1" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="40"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="51"/>
+      <c r="AA2" s="45" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB2" s="50"/>
+      <c r="AC2" s="50"/>
+      <c r="AD2" s="50"/>
+      <c r="AE2" s="50"/>
+      <c r="AF2" s="50"/>
+      <c r="AG2" s="50"/>
+      <c r="AH2" s="50"/>
+      <c r="AI2" s="50"/>
+      <c r="AJ2" s="50"/>
+      <c r="AK2" s="50"/>
+      <c r="AL2" s="51"/>
+      <c r="AO2" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="AP2" s="50"/>
+      <c r="AQ2" s="50"/>
+      <c r="AR2" s="50"/>
+      <c r="AS2" s="50"/>
+      <c r="AT2" s="50"/>
+      <c r="AU2" s="50"/>
+      <c r="AV2" s="50"/>
+      <c r="AW2" s="50"/>
+      <c r="AX2" s="50"/>
+      <c r="AY2" s="50"/>
+      <c r="AZ2" s="51"/>
+      <c r="BC2" s="45" t="s">
+        <v>45</v>
+      </c>
+      <c r="BD2" s="50"/>
+      <c r="BE2" s="50"/>
+      <c r="BF2" s="50"/>
+      <c r="BG2" s="50"/>
+      <c r="BH2" s="50"/>
+      <c r="BI2" s="50"/>
+      <c r="BJ2" s="50"/>
+      <c r="BK2" s="50"/>
+      <c r="BL2" s="50"/>
+      <c r="BM2" s="50"/>
+      <c r="BN2" s="51"/>
+      <c r="BQ2" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="BR2" s="50"/>
+      <c r="BS2" s="50"/>
+      <c r="BT2" s="50"/>
+      <c r="BU2" s="50"/>
+      <c r="BV2" s="50"/>
+      <c r="BW2" s="50"/>
+      <c r="BX2" s="50"/>
+      <c r="BY2" s="50"/>
+      <c r="BZ2" s="50"/>
+      <c r="CA2" s="50"/>
+      <c r="CB2" s="51"/>
     </row>
-    <row r="3" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
       <c r="C3" s="5"/>
-      <c r="D3" s="41" t="s">
+      <c r="D3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="42"/>
-      <c r="F3" s="41" t="s">
+      <c r="E3" s="49"/>
+      <c r="F3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="42"/>
-      <c r="H3" s="41" t="s">
+      <c r="G3" s="49"/>
+      <c r="H3" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="42"/>
-      <c r="J3" s="41" t="s">
+      <c r="I3" s="49"/>
+      <c r="J3" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="42"/>
-      <c r="L3" s="41" t="s">
+      <c r="K3" s="49"/>
+      <c r="L3" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="42"/>
+      <c r="M3" s="49"/>
+      <c r="AA3" s="1"/>
+      <c r="AB3" s="5"/>
+      <c r="AC3" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD3" s="49"/>
+      <c r="AE3" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF3" s="49"/>
+      <c r="AG3" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH3" s="49"/>
+      <c r="AI3" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ3" s="49"/>
+      <c r="AK3" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="AL3" s="49"/>
+      <c r="AO3" s="1"/>
+      <c r="AP3" s="5"/>
+      <c r="AQ3" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR3" s="49"/>
+      <c r="AS3" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT3" s="49"/>
+      <c r="AU3" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV3" s="49"/>
+      <c r="AW3" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="AX3" s="49"/>
+      <c r="AY3" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="AZ3" s="49"/>
+      <c r="BC3" s="1"/>
+      <c r="BD3" s="5"/>
+      <c r="BE3" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="BF3" s="49"/>
+      <c r="BG3" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="BH3" s="49"/>
+      <c r="BI3" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="BJ3" s="49"/>
+      <c r="BK3" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL3" s="49"/>
+      <c r="BM3" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="BN3" s="49"/>
+      <c r="BQ3" s="1"/>
+      <c r="BR3" s="5"/>
+      <c r="BS3" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT3" s="49"/>
+      <c r="BU3" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="BV3" s="49"/>
+      <c r="BW3" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="BX3" s="49"/>
+      <c r="BY3" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="BZ3" s="49"/>
+      <c r="CA3" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="CB3" s="49"/>
     </row>
-    <row r="4" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="6" t="s">
         <v>0</v>
       </c>
@@ -7815,9 +7983,153 @@
       <c r="M4" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AA4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AR4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AS4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AT4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AU4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AX4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AY4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BC4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BF4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BG4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BI4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BJ4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BK4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BM4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BN4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BQ4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="BR4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="BS4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BU4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BV4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BW4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BY4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BZ4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="CA4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="CB4" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B5" s="43" t="s">
+    <row r="5" spans="2:80" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="52" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -7853,9 +8165,105 @@
       <c r="M5" s="14">
         <v>82.58</v>
       </c>
+      <c r="AA5" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB5" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC5" s="19"/>
+      <c r="AD5" s="20"/>
+      <c r="AE5" s="19">
+        <v>66.739999999999995</v>
+      </c>
+      <c r="AF5" s="20">
+        <v>100</v>
+      </c>
+      <c r="AG5" s="19"/>
+      <c r="AH5" s="20"/>
+      <c r="AI5" s="19"/>
+      <c r="AJ5" s="20"/>
+      <c r="AK5" s="19">
+        <v>70.78</v>
+      </c>
+      <c r="AL5" s="20">
+        <v>19.14</v>
+      </c>
+      <c r="AO5" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP5" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ5" s="19"/>
+      <c r="AR5" s="20"/>
+      <c r="AS5" s="19">
+        <v>77.11</v>
+      </c>
+      <c r="AT5" s="20">
+        <v>100</v>
+      </c>
+      <c r="AU5" s="19"/>
+      <c r="AV5" s="20"/>
+      <c r="AW5" s="19"/>
+      <c r="AX5" s="20"/>
+      <c r="AY5" s="19">
+        <v>72.31</v>
+      </c>
+      <c r="AZ5" s="20">
+        <v>19.829999999999998</v>
+      </c>
+      <c r="BC5" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="BD5" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="BE5" s="19"/>
+      <c r="BF5" s="20"/>
+      <c r="BG5" s="19">
+        <v>80.540000000000006</v>
+      </c>
+      <c r="BH5" s="20">
+        <v>100</v>
+      </c>
+      <c r="BI5" s="19"/>
+      <c r="BJ5" s="20"/>
+      <c r="BK5" s="19"/>
+      <c r="BL5" s="20"/>
+      <c r="BM5" s="19">
+        <v>72.17</v>
+      </c>
+      <c r="BN5" s="20">
+        <v>20.05</v>
+      </c>
+      <c r="BQ5" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="BR5" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="BS5" s="19"/>
+      <c r="BT5" s="20"/>
+      <c r="BU5" s="19">
+        <v>82.9</v>
+      </c>
+      <c r="BV5" s="20">
+        <v>100</v>
+      </c>
+      <c r="BW5" s="19"/>
+      <c r="BX5" s="20"/>
+      <c r="BY5" s="19"/>
+      <c r="BZ5" s="20"/>
+      <c r="CA5" s="19">
+        <v>72.23</v>
+      </c>
+      <c r="CB5" s="20">
+        <v>20.92</v>
+      </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B6" s="44"/>
+    <row r="6" spans="2:80" x14ac:dyDescent="0.3">
+      <c r="B6" s="43"/>
       <c r="C6" s="9" t="s">
         <v>11</v>
       </c>
@@ -7889,9 +8297,97 @@
       <c r="M6" s="32">
         <v>73.25</v>
       </c>
+      <c r="AA6" s="43"/>
+      <c r="AB6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC6" s="15"/>
+      <c r="AD6" s="16"/>
+      <c r="AE6" s="15">
+        <v>66.75</v>
+      </c>
+      <c r="AF6" s="16">
+        <v>100</v>
+      </c>
+      <c r="AG6" s="15"/>
+      <c r="AH6" s="16"/>
+      <c r="AI6" s="15"/>
+      <c r="AJ6" s="16"/>
+      <c r="AK6" s="15">
+        <v>68.72</v>
+      </c>
+      <c r="AL6" s="16">
+        <v>19.14</v>
+      </c>
+      <c r="AO6" s="43"/>
+      <c r="AP6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AQ6" s="15"/>
+      <c r="AR6" s="16"/>
+      <c r="AS6" s="15">
+        <v>77.12</v>
+      </c>
+      <c r="AT6" s="16">
+        <v>100</v>
+      </c>
+      <c r="AU6" s="15"/>
+      <c r="AV6" s="16"/>
+      <c r="AW6" s="15"/>
+      <c r="AX6" s="16"/>
+      <c r="AY6" s="15">
+        <v>69.87</v>
+      </c>
+      <c r="AZ6" s="16">
+        <v>19.829999999999998</v>
+      </c>
+      <c r="BC6" s="43"/>
+      <c r="BD6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="BE6" s="15"/>
+      <c r="BF6" s="16"/>
+      <c r="BG6" s="15">
+        <v>80.55</v>
+      </c>
+      <c r="BH6" s="16">
+        <v>100</v>
+      </c>
+      <c r="BI6" s="15"/>
+      <c r="BJ6" s="16"/>
+      <c r="BK6" s="15"/>
+      <c r="BL6" s="16"/>
+      <c r="BM6" s="15">
+        <v>69.92</v>
+      </c>
+      <c r="BN6" s="16">
+        <v>20.05</v>
+      </c>
+      <c r="BQ6" s="43"/>
+      <c r="BR6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="BS6" s="15"/>
+      <c r="BT6" s="16"/>
+      <c r="BU6" s="15">
+        <v>82.91</v>
+      </c>
+      <c r="BV6" s="16">
+        <v>100</v>
+      </c>
+      <c r="BW6" s="15"/>
+      <c r="BX6" s="16"/>
+      <c r="BY6" s="15"/>
+      <c r="BZ6" s="16"/>
+      <c r="CA6" s="15">
+        <v>70.38</v>
+      </c>
+      <c r="CB6" s="16">
+        <v>20.92</v>
+      </c>
     </row>
-    <row r="7" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="45"/>
+    <row r="7" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="53"/>
       <c r="C7" s="11" t="s">
         <v>12</v>
       </c>
@@ -7925,9 +8421,97 @@
       <c r="M7" s="18">
         <v>82.75</v>
       </c>
+      <c r="AA7" s="43"/>
+      <c r="AB7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC7" s="15"/>
+      <c r="AD7" s="16"/>
+      <c r="AE7" s="15">
+        <v>67.03</v>
+      </c>
+      <c r="AF7" s="16">
+        <v>100</v>
+      </c>
+      <c r="AG7" s="15"/>
+      <c r="AH7" s="16"/>
+      <c r="AI7" s="15"/>
+      <c r="AJ7" s="16"/>
+      <c r="AK7" s="15">
+        <v>71.83</v>
+      </c>
+      <c r="AL7" s="16">
+        <v>17.79</v>
+      </c>
+      <c r="AO7" s="43"/>
+      <c r="AP7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="AQ7" s="15"/>
+      <c r="AR7" s="16"/>
+      <c r="AS7" s="15">
+        <v>77.11</v>
+      </c>
+      <c r="AT7" s="16">
+        <v>100</v>
+      </c>
+      <c r="AU7" s="15"/>
+      <c r="AV7" s="16"/>
+      <c r="AW7" s="15"/>
+      <c r="AX7" s="16"/>
+      <c r="AY7" s="15">
+        <v>73.66</v>
+      </c>
+      <c r="AZ7" s="16">
+        <v>19.29</v>
+      </c>
+      <c r="BC7" s="43"/>
+      <c r="BD7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="BE7" s="15"/>
+      <c r="BF7" s="16"/>
+      <c r="BG7" s="15">
+        <v>80.849999999999994</v>
+      </c>
+      <c r="BH7" s="16">
+        <v>100</v>
+      </c>
+      <c r="BI7" s="15"/>
+      <c r="BJ7" s="16"/>
+      <c r="BK7" s="15"/>
+      <c r="BL7" s="16"/>
+      <c r="BM7" s="15">
+        <v>73.989999999999995</v>
+      </c>
+      <c r="BN7" s="16">
+        <v>19.649999999999999</v>
+      </c>
+      <c r="BQ7" s="43"/>
+      <c r="BR7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="BS7" s="15"/>
+      <c r="BT7" s="16"/>
+      <c r="BU7" s="15">
+        <v>83.73</v>
+      </c>
+      <c r="BV7" s="16">
+        <v>78.91</v>
+      </c>
+      <c r="BW7" s="15"/>
+      <c r="BX7" s="16"/>
+      <c r="BY7" s="15"/>
+      <c r="BZ7" s="16"/>
+      <c r="CA7" s="15">
+        <v>74.599999999999994</v>
+      </c>
+      <c r="CB7" s="16">
+        <v>20.49</v>
+      </c>
     </row>
-    <row r="8" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="46" t="s">
+    <row r="8" spans="2:80" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="42" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="12" t="s">
@@ -7963,9 +8547,97 @@
       <c r="M8" s="20">
         <v>44.62</v>
       </c>
+      <c r="AA8" s="44"/>
+      <c r="AB8" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC8" s="21"/>
+      <c r="AD8" s="22"/>
+      <c r="AE8" s="21">
+        <v>64.2</v>
+      </c>
+      <c r="AF8" s="22">
+        <v>100</v>
+      </c>
+      <c r="AG8" s="21"/>
+      <c r="AH8" s="22"/>
+      <c r="AI8" s="21"/>
+      <c r="AJ8" s="22"/>
+      <c r="AK8" s="21">
+        <v>70.77</v>
+      </c>
+      <c r="AL8" s="22">
+        <v>21.78</v>
+      </c>
+      <c r="AO8" s="44"/>
+      <c r="AP8" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ8" s="21"/>
+      <c r="AR8" s="22"/>
+      <c r="AS8" s="21">
+        <v>75.72</v>
+      </c>
+      <c r="AT8" s="22">
+        <v>99.99</v>
+      </c>
+      <c r="AU8" s="21"/>
+      <c r="AV8" s="22"/>
+      <c r="AW8" s="21"/>
+      <c r="AX8" s="22"/>
+      <c r="AY8" s="21">
+        <v>72.92</v>
+      </c>
+      <c r="AZ8" s="22">
+        <v>19.12</v>
+      </c>
+      <c r="BC8" s="44"/>
+      <c r="BD8" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="BE8" s="21"/>
+      <c r="BF8" s="22"/>
+      <c r="BG8" s="21">
+        <v>80.12</v>
+      </c>
+      <c r="BH8" s="22">
+        <v>99.98</v>
+      </c>
+      <c r="BI8" s="21"/>
+      <c r="BJ8" s="22"/>
+      <c r="BK8" s="21"/>
+      <c r="BL8" s="22"/>
+      <c r="BM8" s="21">
+        <v>72.790000000000006</v>
+      </c>
+      <c r="BN8" s="22">
+        <v>19.13</v>
+      </c>
+      <c r="BQ8" s="44"/>
+      <c r="BR8" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="BS8" s="21"/>
+      <c r="BT8" s="22"/>
+      <c r="BU8" s="21">
+        <v>82.31</v>
+      </c>
+      <c r="BV8" s="22">
+        <v>99.97</v>
+      </c>
+      <c r="BW8" s="21"/>
+      <c r="BX8" s="22"/>
+      <c r="BY8" s="21"/>
+      <c r="BZ8" s="22"/>
+      <c r="CA8" s="21">
+        <v>74.290000000000006</v>
+      </c>
+      <c r="CB8" s="22">
+        <v>19.53</v>
+      </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B9" s="44"/>
+    <row r="9" spans="2:80" x14ac:dyDescent="0.3">
+      <c r="B9" s="43"/>
       <c r="C9" s="9" t="s">
         <v>11</v>
       </c>
@@ -8000,8 +8672,8 @@
         <v>19.09</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B10" s="44"/>
+    <row r="10" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="43"/>
       <c r="C10" s="9" t="s">
         <v>12</v>
       </c>
@@ -8036,8 +8708,8 @@
         <v>44.12</v>
       </c>
     </row>
-    <row r="11" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="47"/>
+    <row r="11" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="44"/>
       <c r="C11" s="10" t="s">
         <v>14</v>
       </c>
@@ -8071,49 +8743,456 @@
       <c r="M11" s="22">
         <v>17.579999999999998</v>
       </c>
+      <c r="AA11" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB11" s="46"/>
+      <c r="AC11" s="46"/>
+      <c r="AD11" s="46"/>
+      <c r="AE11" s="46"/>
+      <c r="AF11" s="46"/>
+      <c r="AG11" s="46"/>
+      <c r="AH11" s="46"/>
+      <c r="AI11" s="46"/>
+      <c r="AJ11" s="46"/>
+      <c r="AK11" s="46"/>
+      <c r="AL11" s="47"/>
+      <c r="AO11" s="45" t="s">
+        <v>44</v>
+      </c>
+      <c r="AP11" s="46"/>
+      <c r="AQ11" s="46"/>
+      <c r="AR11" s="46"/>
+      <c r="AS11" s="46"/>
+      <c r="AT11" s="46"/>
+      <c r="AU11" s="46"/>
+      <c r="AV11" s="46"/>
+      <c r="AW11" s="46"/>
+      <c r="AX11" s="46"/>
+      <c r="AY11" s="46"/>
+      <c r="AZ11" s="47"/>
+      <c r="BC11" s="45" t="s">
+        <v>46</v>
+      </c>
+      <c r="BD11" s="46"/>
+      <c r="BE11" s="46"/>
+      <c r="BF11" s="46"/>
+      <c r="BG11" s="46"/>
+      <c r="BH11" s="46"/>
+      <c r="BI11" s="46"/>
+      <c r="BJ11" s="46"/>
+      <c r="BK11" s="46"/>
+      <c r="BL11" s="46"/>
+      <c r="BM11" s="46"/>
+      <c r="BN11" s="47"/>
+      <c r="BQ11" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="BR11" s="46"/>
+      <c r="BS11" s="46"/>
+      <c r="BT11" s="46"/>
+      <c r="BU11" s="46"/>
+      <c r="BV11" s="46"/>
+      <c r="BW11" s="46"/>
+      <c r="BX11" s="46"/>
+      <c r="BY11" s="46"/>
+      <c r="BZ11" s="46"/>
+      <c r="CA11" s="46"/>
+      <c r="CB11" s="47"/>
     </row>
-    <row r="13" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="14" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="38" t="s">
+    <row r="12" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AA12" s="24"/>
+      <c r="AB12" s="4"/>
+      <c r="AC12" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="49"/>
+      <c r="AE12" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF12" s="49"/>
+      <c r="AG12" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH12" s="49"/>
+      <c r="AI12" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ12" s="49"/>
+      <c r="AK12" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="AL12" s="49"/>
+      <c r="AO12" s="24"/>
+      <c r="AP12" s="4"/>
+      <c r="AQ12" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR12" s="49"/>
+      <c r="AS12" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT12" s="49"/>
+      <c r="AU12" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV12" s="49"/>
+      <c r="AW12" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="AX12" s="49"/>
+      <c r="AY12" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="AZ12" s="49"/>
+      <c r="BC12" s="24"/>
+      <c r="BD12" s="4"/>
+      <c r="BE12" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="BF12" s="49"/>
+      <c r="BG12" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="BH12" s="49"/>
+      <c r="BI12" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="BJ12" s="49"/>
+      <c r="BK12" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL12" s="49"/>
+      <c r="BM12" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="BN12" s="49"/>
+      <c r="BQ12" s="24"/>
+      <c r="BR12" s="4"/>
+      <c r="BS12" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT12" s="49"/>
+      <c r="BU12" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="BV12" s="49"/>
+      <c r="BW12" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="BX12" s="49"/>
+      <c r="BY12" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="BZ12" s="49"/>
+      <c r="CA12" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="CB12" s="49"/>
+    </row>
+    <row r="13" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AA13" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB13" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD13" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF13" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH13" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ13" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL13" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO13" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="AP13" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AR13" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AS13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AT13" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AU13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV13" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AX13" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AY13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ13" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BC13" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="BD13" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="BE13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BF13" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BG13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH13" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BI13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BJ13" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BK13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL13" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BM13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BN13" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BQ13" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="BR13" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="BS13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT13" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BU13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BV13" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BW13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX13" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BY13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BZ13" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="CA13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="CB13" s="28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="48"/>
-      <c r="L14" s="48"/>
-      <c r="M14" s="49"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="47"/>
+      <c r="AA14" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB14" s="36">
+        <v>0.77429999999999999</v>
+      </c>
+      <c r="AC14" s="30"/>
+      <c r="AD14" s="30"/>
+      <c r="AE14" s="30"/>
+      <c r="AF14" s="30"/>
+      <c r="AG14" s="30"/>
+      <c r="AH14" s="30"/>
+      <c r="AI14" s="30"/>
+      <c r="AJ14" s="30"/>
+      <c r="AK14" s="30"/>
+      <c r="AL14" s="30"/>
+      <c r="AO14" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="AP14" s="36"/>
+      <c r="AQ14" s="30"/>
+      <c r="AR14" s="30"/>
+      <c r="AS14" s="30"/>
+      <c r="AT14" s="30"/>
+      <c r="AU14" s="30"/>
+      <c r="AV14" s="30"/>
+      <c r="AW14" s="30"/>
+      <c r="AX14" s="30"/>
+      <c r="AY14" s="30"/>
+      <c r="AZ14" s="30"/>
+      <c r="BC14" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="BD14" s="36"/>
+      <c r="BE14" s="30"/>
+      <c r="BF14" s="30"/>
+      <c r="BG14" s="30"/>
+      <c r="BH14" s="30"/>
+      <c r="BI14" s="30"/>
+      <c r="BJ14" s="30"/>
+      <c r="BK14" s="30"/>
+      <c r="BL14" s="30"/>
+      <c r="BM14" s="30"/>
+      <c r="BN14" s="30"/>
+      <c r="BQ14" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="BR14" s="36">
+        <v>0.77429999999999999</v>
+      </c>
+      <c r="BS14" s="30"/>
+      <c r="BT14" s="30"/>
+      <c r="BU14" s="30"/>
+      <c r="BV14" s="30"/>
+      <c r="BW14" s="30"/>
+      <c r="BX14" s="30"/>
+      <c r="BY14" s="30"/>
+      <c r="BZ14" s="30"/>
+      <c r="CA14" s="30"/>
+      <c r="CB14" s="30"/>
     </row>
-    <row r="15" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="24"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="41" t="s">
+      <c r="D15" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="41" t="s">
+      <c r="E15" s="49"/>
+      <c r="F15" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="42"/>
-      <c r="H15" s="41" t="s">
+      <c r="G15" s="49"/>
+      <c r="H15" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="42"/>
-      <c r="J15" s="41" t="s">
+      <c r="I15" s="49"/>
+      <c r="J15" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="42"/>
-      <c r="L15" s="41" t="s">
+      <c r="K15" s="49"/>
+      <c r="L15" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="M15" s="42"/>
+      <c r="M15" s="49"/>
+      <c r="AA15" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB15" s="30"/>
+      <c r="AC15" s="30"/>
+      <c r="AD15" s="30"/>
+      <c r="AE15" s="30"/>
+      <c r="AF15" s="30"/>
+      <c r="AG15" s="30"/>
+      <c r="AH15" s="30"/>
+      <c r="AI15" s="30"/>
+      <c r="AJ15" s="30"/>
+      <c r="AK15" s="30"/>
+      <c r="AL15" s="30"/>
+      <c r="AO15" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP15" s="30"/>
+      <c r="AQ15" s="30"/>
+      <c r="AR15" s="30"/>
+      <c r="AS15" s="30"/>
+      <c r="AT15" s="30"/>
+      <c r="AU15" s="30"/>
+      <c r="AV15" s="30"/>
+      <c r="AW15" s="30"/>
+      <c r="AX15" s="30"/>
+      <c r="AY15" s="30"/>
+      <c r="AZ15" s="30"/>
+      <c r="BC15" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="BD15" s="30"/>
+      <c r="BE15" s="30"/>
+      <c r="BF15" s="30"/>
+      <c r="BG15" s="30"/>
+      <c r="BH15" s="30"/>
+      <c r="BI15" s="30"/>
+      <c r="BJ15" s="30"/>
+      <c r="BK15" s="30"/>
+      <c r="BL15" s="30"/>
+      <c r="BM15" s="30"/>
+      <c r="BN15" s="30"/>
+      <c r="BQ15" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="BR15" s="30"/>
+      <c r="BS15" s="30"/>
+      <c r="BT15" s="30"/>
+      <c r="BU15" s="30"/>
+      <c r="BV15" s="30"/>
+      <c r="BW15" s="30"/>
+      <c r="BX15" s="30"/>
+      <c r="BY15" s="30"/>
+      <c r="BZ15" s="30"/>
+      <c r="CA15" s="30"/>
+      <c r="CB15" s="30"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>16</v>
       </c>
@@ -8150,8 +9229,64 @@
       <c r="M16" s="28" t="s">
         <v>8</v>
       </c>
+      <c r="AA16" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB16" s="34"/>
+      <c r="AC16" s="34"/>
+      <c r="AD16" s="34"/>
+      <c r="AE16" s="34"/>
+      <c r="AF16" s="34"/>
+      <c r="AG16" s="34"/>
+      <c r="AH16" s="34"/>
+      <c r="AI16" s="34"/>
+      <c r="AJ16" s="34"/>
+      <c r="AK16" s="34"/>
+      <c r="AL16" s="34"/>
+      <c r="AO16" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="AP16" s="34"/>
+      <c r="AQ16" s="34"/>
+      <c r="AR16" s="34"/>
+      <c r="AS16" s="34"/>
+      <c r="AT16" s="34"/>
+      <c r="AU16" s="34"/>
+      <c r="AV16" s="34"/>
+      <c r="AW16" s="34"/>
+      <c r="AX16" s="34"/>
+      <c r="AY16" s="34"/>
+      <c r="AZ16" s="34"/>
+      <c r="BC16" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="BD16" s="34"/>
+      <c r="BE16" s="34"/>
+      <c r="BF16" s="34"/>
+      <c r="BG16" s="34"/>
+      <c r="BH16" s="34"/>
+      <c r="BI16" s="34"/>
+      <c r="BJ16" s="34"/>
+      <c r="BK16" s="34"/>
+      <c r="BL16" s="34"/>
+      <c r="BM16" s="34"/>
+      <c r="BN16" s="34"/>
+      <c r="BQ16" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="BR16" s="34"/>
+      <c r="BS16" s="34"/>
+      <c r="BT16" s="34"/>
+      <c r="BU16" s="34"/>
+      <c r="BV16" s="34"/>
+      <c r="BW16" s="34"/>
+      <c r="BX16" s="34"/>
+      <c r="BY16" s="34"/>
+      <c r="BZ16" s="34"/>
+      <c r="CA16" s="34"/>
+      <c r="CB16" s="34"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B17" s="29" t="s">
         <v>24</v>
       </c>
@@ -8188,8 +9323,64 @@
       <c r="M17" s="30">
         <v>91.26</v>
       </c>
+      <c r="AA17" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB17" s="34"/>
+      <c r="AC17" s="34"/>
+      <c r="AD17" s="34"/>
+      <c r="AE17" s="34"/>
+      <c r="AF17" s="34"/>
+      <c r="AG17" s="34"/>
+      <c r="AH17" s="34"/>
+      <c r="AI17" s="34"/>
+      <c r="AJ17" s="34"/>
+      <c r="AK17" s="34"/>
+      <c r="AL17" s="34"/>
+      <c r="AO17" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="AP17" s="34"/>
+      <c r="AQ17" s="34"/>
+      <c r="AR17" s="34"/>
+      <c r="AS17" s="34"/>
+      <c r="AT17" s="34"/>
+      <c r="AU17" s="34"/>
+      <c r="AV17" s="34"/>
+      <c r="AW17" s="34"/>
+      <c r="AX17" s="34"/>
+      <c r="AY17" s="34"/>
+      <c r="AZ17" s="34"/>
+      <c r="BC17" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="BD17" s="34"/>
+      <c r="BE17" s="34"/>
+      <c r="BF17" s="34"/>
+      <c r="BG17" s="34"/>
+      <c r="BH17" s="34"/>
+      <c r="BI17" s="34"/>
+      <c r="BJ17" s="34"/>
+      <c r="BK17" s="34"/>
+      <c r="BL17" s="34"/>
+      <c r="BM17" s="34"/>
+      <c r="BN17" s="34"/>
+      <c r="BQ17" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="BR17" s="34"/>
+      <c r="BS17" s="34"/>
+      <c r="BT17" s="34"/>
+      <c r="BU17" s="34"/>
+      <c r="BV17" s="34"/>
+      <c r="BW17" s="34"/>
+      <c r="BX17" s="34"/>
+      <c r="BY17" s="34"/>
+      <c r="BZ17" s="34"/>
+      <c r="CA17" s="34"/>
+      <c r="CB17" s="34"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B18" s="29" t="s">
         <v>39</v>
       </c>
@@ -8224,8 +9415,64 @@
       <c r="M18" s="30">
         <v>80.5</v>
       </c>
+      <c r="AA18" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB18" s="30"/>
+      <c r="AC18" s="30"/>
+      <c r="AD18" s="30"/>
+      <c r="AE18" s="30"/>
+      <c r="AF18" s="30"/>
+      <c r="AG18" s="30"/>
+      <c r="AH18" s="30"/>
+      <c r="AI18" s="30"/>
+      <c r="AJ18" s="30"/>
+      <c r="AK18" s="30"/>
+      <c r="AL18" s="30"/>
+      <c r="AO18" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP18" s="30"/>
+      <c r="AQ18" s="30"/>
+      <c r="AR18" s="30"/>
+      <c r="AS18" s="30"/>
+      <c r="AT18" s="30"/>
+      <c r="AU18" s="30"/>
+      <c r="AV18" s="30"/>
+      <c r="AW18" s="30"/>
+      <c r="AX18" s="30"/>
+      <c r="AY18" s="30"/>
+      <c r="AZ18" s="30"/>
+      <c r="BC18" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="BD18" s="30"/>
+      <c r="BE18" s="30"/>
+      <c r="BF18" s="30"/>
+      <c r="BG18" s="30"/>
+      <c r="BH18" s="30"/>
+      <c r="BI18" s="30"/>
+      <c r="BJ18" s="30"/>
+      <c r="BK18" s="30"/>
+      <c r="BL18" s="30"/>
+      <c r="BM18" s="30"/>
+      <c r="BN18" s="30"/>
+      <c r="BQ18" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="BR18" s="30"/>
+      <c r="BS18" s="30"/>
+      <c r="BT18" s="30"/>
+      <c r="BU18" s="30"/>
+      <c r="BV18" s="30"/>
+      <c r="BW18" s="30"/>
+      <c r="BX18" s="30"/>
+      <c r="BY18" s="30"/>
+      <c r="BZ18" s="30"/>
+      <c r="CA18" s="30"/>
+      <c r="CB18" s="30"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B19" s="29" t="s">
         <v>20</v>
       </c>
@@ -8260,8 +9507,64 @@
       <c r="M19" s="34">
         <v>51.59</v>
       </c>
+      <c r="AA19" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB19" s="30"/>
+      <c r="AC19" s="30"/>
+      <c r="AD19" s="30"/>
+      <c r="AE19" s="35"/>
+      <c r="AF19" s="30"/>
+      <c r="AG19" s="30"/>
+      <c r="AH19" s="30"/>
+      <c r="AI19" s="30"/>
+      <c r="AJ19" s="30"/>
+      <c r="AK19" s="30"/>
+      <c r="AL19" s="30"/>
+      <c r="AO19" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="AP19" s="30"/>
+      <c r="AQ19" s="30"/>
+      <c r="AR19" s="30"/>
+      <c r="AS19" s="35"/>
+      <c r="AT19" s="30"/>
+      <c r="AU19" s="30"/>
+      <c r="AV19" s="30"/>
+      <c r="AW19" s="30"/>
+      <c r="AX19" s="30"/>
+      <c r="AY19" s="30"/>
+      <c r="AZ19" s="30"/>
+      <c r="BC19" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="BD19" s="30"/>
+      <c r="BE19" s="30"/>
+      <c r="BF19" s="30"/>
+      <c r="BG19" s="35"/>
+      <c r="BH19" s="30"/>
+      <c r="BI19" s="30"/>
+      <c r="BJ19" s="30"/>
+      <c r="BK19" s="30"/>
+      <c r="BL19" s="30"/>
+      <c r="BM19" s="30"/>
+      <c r="BN19" s="30"/>
+      <c r="BQ19" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="BR19" s="30"/>
+      <c r="BS19" s="30"/>
+      <c r="BT19" s="30"/>
+      <c r="BU19" s="35"/>
+      <c r="BV19" s="30"/>
+      <c r="BW19" s="30"/>
+      <c r="BX19" s="30"/>
+      <c r="BY19" s="30"/>
+      <c r="BZ19" s="30"/>
+      <c r="CA19" s="30"/>
+      <c r="CB19" s="30"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B20" s="29" t="s">
         <v>29</v>
       </c>
@@ -8296,8 +9599,64 @@
       <c r="M20" s="34">
         <v>46.41</v>
       </c>
+      <c r="AA20" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB20" s="34"/>
+      <c r="AC20" s="34"/>
+      <c r="AD20" s="34"/>
+      <c r="AE20" s="34"/>
+      <c r="AF20" s="34"/>
+      <c r="AG20" s="34"/>
+      <c r="AH20" s="34"/>
+      <c r="AI20" s="34"/>
+      <c r="AJ20" s="34"/>
+      <c r="AK20" s="34"/>
+      <c r="AL20" s="34"/>
+      <c r="AO20" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP20" s="34"/>
+      <c r="AQ20" s="34"/>
+      <c r="AR20" s="34"/>
+      <c r="AS20" s="34"/>
+      <c r="AT20" s="34"/>
+      <c r="AU20" s="34"/>
+      <c r="AV20" s="34"/>
+      <c r="AW20" s="34"/>
+      <c r="AX20" s="34"/>
+      <c r="AY20" s="34"/>
+      <c r="AZ20" s="34"/>
+      <c r="BC20" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="BD20" s="34"/>
+      <c r="BE20" s="34"/>
+      <c r="BF20" s="34"/>
+      <c r="BG20" s="34"/>
+      <c r="BH20" s="34"/>
+      <c r="BI20" s="34"/>
+      <c r="BJ20" s="34"/>
+      <c r="BK20" s="34"/>
+      <c r="BL20" s="34"/>
+      <c r="BM20" s="34"/>
+      <c r="BN20" s="34"/>
+      <c r="BQ20" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="BR20" s="34"/>
+      <c r="BS20" s="34"/>
+      <c r="BT20" s="34"/>
+      <c r="BU20" s="34"/>
+      <c r="BV20" s="34"/>
+      <c r="BW20" s="34"/>
+      <c r="BX20" s="34"/>
+      <c r="BY20" s="34"/>
+      <c r="BZ20" s="34"/>
+      <c r="CA20" s="34"/>
+      <c r="CB20" s="34"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B21" s="29" t="s">
         <v>25</v>
       </c>
@@ -8332,8 +9691,64 @@
       <c r="M21" s="30">
         <v>46.21</v>
       </c>
+      <c r="AA21" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB21" s="30"/>
+      <c r="AC21" s="30"/>
+      <c r="AD21" s="30"/>
+      <c r="AE21" s="30"/>
+      <c r="AF21" s="30"/>
+      <c r="AG21" s="30"/>
+      <c r="AH21" s="30"/>
+      <c r="AI21" s="30"/>
+      <c r="AJ21" s="30"/>
+      <c r="AK21" s="30"/>
+      <c r="AL21" s="30"/>
+      <c r="AO21" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP21" s="30"/>
+      <c r="AQ21" s="30"/>
+      <c r="AR21" s="30"/>
+      <c r="AS21" s="30"/>
+      <c r="AT21" s="30"/>
+      <c r="AU21" s="30"/>
+      <c r="AV21" s="30"/>
+      <c r="AW21" s="30"/>
+      <c r="AX21" s="30"/>
+      <c r="AY21" s="30"/>
+      <c r="AZ21" s="30"/>
+      <c r="BC21" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="BD21" s="30"/>
+      <c r="BE21" s="30"/>
+      <c r="BF21" s="30"/>
+      <c r="BG21" s="30"/>
+      <c r="BH21" s="30"/>
+      <c r="BI21" s="30"/>
+      <c r="BJ21" s="30"/>
+      <c r="BK21" s="30"/>
+      <c r="BL21" s="30"/>
+      <c r="BM21" s="30"/>
+      <c r="BN21" s="30"/>
+      <c r="BQ21" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="BR21" s="30"/>
+      <c r="BS21" s="30"/>
+      <c r="BT21" s="30"/>
+      <c r="BU21" s="30"/>
+      <c r="BV21" s="30"/>
+      <c r="BW21" s="30"/>
+      <c r="BX21" s="30"/>
+      <c r="BY21" s="30"/>
+      <c r="BZ21" s="30"/>
+      <c r="CA21" s="30"/>
+      <c r="CB21" s="30"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B22" s="29" t="s">
         <v>21</v>
       </c>
@@ -8368,8 +9783,60 @@
       <c r="M22" s="30">
         <v>44.62</v>
       </c>
+      <c r="AA22" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB22" s="30"/>
+      <c r="AC22" s="30"/>
+      <c r="AD22" s="30"/>
+      <c r="AF22" s="30"/>
+      <c r="AG22" s="30"/>
+      <c r="AH22" s="30"/>
+      <c r="AI22" s="30"/>
+      <c r="AJ22" s="30"/>
+      <c r="AK22" s="30"/>
+      <c r="AL22" s="30"/>
+      <c r="AO22" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="AP22" s="30"/>
+      <c r="AQ22" s="30"/>
+      <c r="AR22" s="30"/>
+      <c r="AT22" s="30"/>
+      <c r="AU22" s="30"/>
+      <c r="AV22" s="30"/>
+      <c r="AW22" s="30"/>
+      <c r="AX22" s="30"/>
+      <c r="AY22" s="30"/>
+      <c r="AZ22" s="30"/>
+      <c r="BC22" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="BD22" s="30"/>
+      <c r="BE22" s="30"/>
+      <c r="BF22" s="30"/>
+      <c r="BH22" s="30"/>
+      <c r="BI22" s="30"/>
+      <c r="BJ22" s="30"/>
+      <c r="BK22" s="30"/>
+      <c r="BL22" s="30"/>
+      <c r="BM22" s="30"/>
+      <c r="BN22" s="30"/>
+      <c r="BQ22" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="BR22" s="30"/>
+      <c r="BS22" s="30"/>
+      <c r="BT22" s="30"/>
+      <c r="BV22" s="30"/>
+      <c r="BW22" s="30"/>
+      <c r="BX22" s="30"/>
+      <c r="BY22" s="30"/>
+      <c r="BZ22" s="30"/>
+      <c r="CA22" s="30"/>
+      <c r="CB22" s="30"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B23" s="29" t="s">
         <v>30</v>
       </c>
@@ -8404,8 +9871,64 @@
       <c r="M23" s="34">
         <v>44.22</v>
       </c>
+      <c r="AA23" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB23" s="30"/>
+      <c r="AC23" s="30"/>
+      <c r="AD23" s="30"/>
+      <c r="AE23" s="30"/>
+      <c r="AF23" s="30"/>
+      <c r="AG23" s="30"/>
+      <c r="AH23" s="30"/>
+      <c r="AI23" s="30"/>
+      <c r="AJ23" s="30"/>
+      <c r="AK23" s="30"/>
+      <c r="AL23" s="30"/>
+      <c r="AO23" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP23" s="30"/>
+      <c r="AQ23" s="30"/>
+      <c r="AR23" s="30"/>
+      <c r="AS23" s="30"/>
+      <c r="AT23" s="30"/>
+      <c r="AU23" s="30"/>
+      <c r="AV23" s="30"/>
+      <c r="AW23" s="30"/>
+      <c r="AX23" s="30"/>
+      <c r="AY23" s="30"/>
+      <c r="AZ23" s="30"/>
+      <c r="BC23" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD23" s="30"/>
+      <c r="BE23" s="30"/>
+      <c r="BF23" s="30"/>
+      <c r="BG23" s="30"/>
+      <c r="BH23" s="30"/>
+      <c r="BI23" s="30"/>
+      <c r="BJ23" s="30"/>
+      <c r="BK23" s="30"/>
+      <c r="BL23" s="30"/>
+      <c r="BM23" s="30"/>
+      <c r="BN23" s="30"/>
+      <c r="BQ23" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="BR23" s="30"/>
+      <c r="BS23" s="30"/>
+      <c r="BT23" s="30"/>
+      <c r="BU23" s="30"/>
+      <c r="BV23" s="30"/>
+      <c r="BW23" s="30"/>
+      <c r="BX23" s="30"/>
+      <c r="BY23" s="30"/>
+      <c r="BZ23" s="30"/>
+      <c r="CA23" s="30"/>
+      <c r="CB23" s="30"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B24" s="29" t="s">
         <v>26</v>
       </c>
@@ -8440,8 +9963,96 @@
       <c r="M24" s="30">
         <v>43.54</v>
       </c>
+      <c r="AA24" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB24" s="30"/>
+      <c r="AC24" s="30"/>
+      <c r="AD24" s="30"/>
+      <c r="AE24" s="30">
+        <v>48.29</v>
+      </c>
+      <c r="AF24" s="30">
+        <v>100</v>
+      </c>
+      <c r="AG24" s="30"/>
+      <c r="AH24" s="30"/>
+      <c r="AI24" s="30"/>
+      <c r="AJ24" s="30"/>
+      <c r="AK24" s="30">
+        <v>64.510000000000005</v>
+      </c>
+      <c r="AL24" s="30">
+        <v>22.63</v>
+      </c>
+      <c r="AO24" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="AP24" s="30"/>
+      <c r="AQ24" s="30"/>
+      <c r="AR24" s="30"/>
+      <c r="AS24" s="30">
+        <v>45.78</v>
+      </c>
+      <c r="AT24" s="30">
+        <v>100</v>
+      </c>
+      <c r="AU24" s="30"/>
+      <c r="AV24" s="30"/>
+      <c r="AW24" s="30"/>
+      <c r="AX24" s="30"/>
+      <c r="AY24" s="30">
+        <v>65.260000000000005</v>
+      </c>
+      <c r="AZ24" s="30">
+        <v>20.66</v>
+      </c>
+      <c r="BC24" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="BD24" s="30"/>
+      <c r="BE24" s="30"/>
+      <c r="BF24" s="30"/>
+      <c r="BG24" s="30">
+        <v>50.06</v>
+      </c>
+      <c r="BH24" s="30">
+        <v>100</v>
+      </c>
+      <c r="BI24" s="30"/>
+      <c r="BJ24" s="30"/>
+      <c r="BK24" s="30"/>
+      <c r="BL24" s="30"/>
+      <c r="BM24" s="30">
+        <v>63.49</v>
+      </c>
+      <c r="BN24" s="30">
+        <v>26.06</v>
+      </c>
+      <c r="BQ24" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="BR24" s="30"/>
+      <c r="BS24" s="30"/>
+      <c r="BT24" s="30"/>
+      <c r="BU24" s="30">
+        <v>50.97</v>
+      </c>
+      <c r="BV24" s="30">
+        <v>100</v>
+      </c>
+      <c r="BW24" s="30"/>
+      <c r="BX24" s="30"/>
+      <c r="BY24" s="30"/>
+      <c r="BZ24" s="30"/>
+      <c r="CA24" s="30">
+        <v>65.540000000000006</v>
+      </c>
+      <c r="CB24" s="30">
+        <v>25.74</v>
+      </c>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B25" s="29" t="s">
         <v>22</v>
       </c>
@@ -8477,8 +10088,96 @@
         <v>42.69</v>
       </c>
       <c r="O25" s="33"/>
+      <c r="AA25" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB25" s="30"/>
+      <c r="AC25" s="30"/>
+      <c r="AD25" s="30"/>
+      <c r="AE25" s="30">
+        <v>44.44</v>
+      </c>
+      <c r="AF25" s="30">
+        <v>100</v>
+      </c>
+      <c r="AG25" s="30"/>
+      <c r="AH25" s="30"/>
+      <c r="AI25" s="30"/>
+      <c r="AJ25" s="30"/>
+      <c r="AK25" s="30">
+        <v>63.16</v>
+      </c>
+      <c r="AL25" s="30">
+        <v>30.49</v>
+      </c>
+      <c r="AO25" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP25" s="30"/>
+      <c r="AQ25" s="30"/>
+      <c r="AR25" s="30"/>
+      <c r="AS25" s="30">
+        <v>41.72</v>
+      </c>
+      <c r="AT25" s="30">
+        <v>100</v>
+      </c>
+      <c r="AU25" s="30"/>
+      <c r="AV25" s="30"/>
+      <c r="AW25" s="30"/>
+      <c r="AX25" s="30"/>
+      <c r="AY25" s="30">
+        <v>63.83</v>
+      </c>
+      <c r="AZ25" s="30">
+        <v>23.65</v>
+      </c>
+      <c r="BC25" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="BD25" s="30"/>
+      <c r="BE25" s="30"/>
+      <c r="BF25" s="30"/>
+      <c r="BG25" s="30">
+        <v>43.56</v>
+      </c>
+      <c r="BH25" s="30">
+        <v>100</v>
+      </c>
+      <c r="BI25" s="30"/>
+      <c r="BJ25" s="30"/>
+      <c r="BK25" s="30"/>
+      <c r="BL25" s="30"/>
+      <c r="BM25" s="30">
+        <v>61.24</v>
+      </c>
+      <c r="BN25" s="30">
+        <v>26.85</v>
+      </c>
+      <c r="BQ25" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="BR25" s="30"/>
+      <c r="BS25" s="30"/>
+      <c r="BT25" s="30"/>
+      <c r="BU25" s="30">
+        <v>43.71</v>
+      </c>
+      <c r="BV25" s="30">
+        <v>100</v>
+      </c>
+      <c r="BW25" s="30"/>
+      <c r="BX25" s="30"/>
+      <c r="BY25" s="30"/>
+      <c r="BZ25" s="30"/>
+      <c r="CA25" s="30">
+        <v>63.4</v>
+      </c>
+      <c r="CB25" s="30">
+        <v>22.59</v>
+      </c>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B26" s="29" t="s">
         <v>23</v>
       </c>
@@ -8513,8 +10212,64 @@
       <c r="M26" s="30">
         <v>41.58</v>
       </c>
+      <c r="AA26" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB26" s="30"/>
+      <c r="AC26" s="30"/>
+      <c r="AD26" s="30"/>
+      <c r="AE26" s="30"/>
+      <c r="AF26" s="30"/>
+      <c r="AG26" s="30"/>
+      <c r="AH26" s="30"/>
+      <c r="AI26" s="30"/>
+      <c r="AJ26" s="30"/>
+      <c r="AK26" s="30"/>
+      <c r="AL26" s="30"/>
+      <c r="AO26" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP26" s="30"/>
+      <c r="AQ26" s="30"/>
+      <c r="AR26" s="30"/>
+      <c r="AS26" s="30"/>
+      <c r="AT26" s="30"/>
+      <c r="AU26" s="30"/>
+      <c r="AV26" s="30"/>
+      <c r="AW26" s="30"/>
+      <c r="AX26" s="30"/>
+      <c r="AY26" s="30"/>
+      <c r="AZ26" s="30"/>
+      <c r="BC26" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD26" s="30"/>
+      <c r="BE26" s="30"/>
+      <c r="BF26" s="30"/>
+      <c r="BG26" s="30"/>
+      <c r="BH26" s="30"/>
+      <c r="BI26" s="30"/>
+      <c r="BJ26" s="30"/>
+      <c r="BK26" s="30"/>
+      <c r="BL26" s="30"/>
+      <c r="BM26" s="30"/>
+      <c r="BN26" s="30"/>
+      <c r="BQ26" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR26" s="30"/>
+      <c r="BS26" s="30"/>
+      <c r="BT26" s="30"/>
+      <c r="BU26" s="30"/>
+      <c r="BV26" s="30"/>
+      <c r="BW26" s="30"/>
+      <c r="BX26" s="30"/>
+      <c r="BY26" s="30"/>
+      <c r="BZ26" s="30"/>
+      <c r="CA26" s="30"/>
+      <c r="CB26" s="30"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B27" s="29" t="s">
         <v>31</v>
       </c>
@@ -8549,8 +10304,96 @@
       <c r="M27" s="30">
         <v>39.799999999999997</v>
       </c>
+      <c r="AA27" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB27" s="30"/>
+      <c r="AC27" s="30"/>
+      <c r="AD27" s="30"/>
+      <c r="AE27" s="30">
+        <v>34.159999999999997</v>
+      </c>
+      <c r="AF27" s="30">
+        <v>100</v>
+      </c>
+      <c r="AG27" s="30"/>
+      <c r="AH27" s="30"/>
+      <c r="AI27" s="30"/>
+      <c r="AJ27" s="30"/>
+      <c r="AK27" s="30">
+        <v>59.73</v>
+      </c>
+      <c r="AL27" s="30">
+        <v>45.45</v>
+      </c>
+      <c r="AO27" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP27" s="30"/>
+      <c r="AQ27" s="30"/>
+      <c r="AR27" s="30"/>
+      <c r="AS27" s="30">
+        <v>33.619999999999997</v>
+      </c>
+      <c r="AT27" s="30">
+        <v>100</v>
+      </c>
+      <c r="AU27" s="30"/>
+      <c r="AV27" s="30"/>
+      <c r="AW27" s="30"/>
+      <c r="AX27" s="30"/>
+      <c r="AY27" s="30">
+        <v>60.08</v>
+      </c>
+      <c r="AZ27" s="30">
+        <v>39.880000000000003</v>
+      </c>
+      <c r="BC27" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD27" s="30"/>
+      <c r="BE27" s="30"/>
+      <c r="BF27" s="30"/>
+      <c r="BG27" s="30">
+        <v>34.56</v>
+      </c>
+      <c r="BH27" s="30">
+        <v>100</v>
+      </c>
+      <c r="BI27" s="30"/>
+      <c r="BJ27" s="30"/>
+      <c r="BK27" s="30"/>
+      <c r="BL27" s="30"/>
+      <c r="BM27" s="30">
+        <v>54.78</v>
+      </c>
+      <c r="BN27" s="30">
+        <v>60.73</v>
+      </c>
+      <c r="BQ27" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="BR27" s="30"/>
+      <c r="BS27" s="30"/>
+      <c r="BT27" s="30"/>
+      <c r="BU27" s="30">
+        <v>35.6</v>
+      </c>
+      <c r="BV27" s="30">
+        <v>100</v>
+      </c>
+      <c r="BW27" s="30"/>
+      <c r="BX27" s="30"/>
+      <c r="BY27" s="30"/>
+      <c r="BZ27" s="30"/>
+      <c r="CA27" s="30">
+        <v>57.19</v>
+      </c>
+      <c r="CB27" s="30">
+        <v>64.8</v>
+      </c>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B28" s="29" t="s">
         <v>40</v>
       </c>
@@ -8585,8 +10428,64 @@
       <c r="M28" s="30">
         <v>39.11</v>
       </c>
+      <c r="AA28" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB28" s="30"/>
+      <c r="AC28" s="30"/>
+      <c r="AD28" s="30"/>
+      <c r="AE28" s="30"/>
+      <c r="AF28" s="30"/>
+      <c r="AG28" s="30"/>
+      <c r="AH28" s="30"/>
+      <c r="AI28" s="30"/>
+      <c r="AJ28" s="30"/>
+      <c r="AK28" s="30"/>
+      <c r="AL28" s="30"/>
+      <c r="AO28" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="AP28" s="30"/>
+      <c r="AQ28" s="30"/>
+      <c r="AR28" s="30"/>
+      <c r="AS28" s="30"/>
+      <c r="AT28" s="30"/>
+      <c r="AU28" s="30"/>
+      <c r="AV28" s="30"/>
+      <c r="AW28" s="30"/>
+      <c r="AX28" s="30"/>
+      <c r="AY28" s="30"/>
+      <c r="AZ28" s="30"/>
+      <c r="BC28" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="BD28" s="30"/>
+      <c r="BE28" s="30"/>
+      <c r="BF28" s="30"/>
+      <c r="BG28" s="30"/>
+      <c r="BH28" s="30"/>
+      <c r="BI28" s="30"/>
+      <c r="BJ28" s="30"/>
+      <c r="BK28" s="30"/>
+      <c r="BL28" s="30"/>
+      <c r="BM28" s="30"/>
+      <c r="BN28" s="30"/>
+      <c r="BQ28" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="BR28" s="30"/>
+      <c r="BS28" s="30"/>
+      <c r="BT28" s="30"/>
+      <c r="BU28" s="30"/>
+      <c r="BV28" s="30"/>
+      <c r="BW28" s="30"/>
+      <c r="BX28" s="30"/>
+      <c r="BY28" s="30"/>
+      <c r="BZ28" s="30"/>
+      <c r="CA28" s="30"/>
+      <c r="CB28" s="30"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B29" s="29" t="s">
         <v>27</v>
       </c>
@@ -8621,8 +10520,96 @@
       <c r="M29" s="30">
         <v>39.43</v>
       </c>
+      <c r="AA29" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB29" s="30"/>
+      <c r="AC29" s="30"/>
+      <c r="AD29" s="30"/>
+      <c r="AE29" s="30">
+        <v>32.31</v>
+      </c>
+      <c r="AF29" s="30">
+        <v>100</v>
+      </c>
+      <c r="AG29" s="30"/>
+      <c r="AH29" s="30"/>
+      <c r="AI29" s="30"/>
+      <c r="AJ29" s="30"/>
+      <c r="AK29" s="30">
+        <v>56.9</v>
+      </c>
+      <c r="AL29" s="30">
+        <v>75.77</v>
+      </c>
+      <c r="AO29" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="AP29" s="30"/>
+      <c r="AQ29" s="30"/>
+      <c r="AR29" s="30"/>
+      <c r="AS29" s="30">
+        <v>30.25</v>
+      </c>
+      <c r="AT29" s="30">
+        <v>100</v>
+      </c>
+      <c r="AU29" s="30"/>
+      <c r="AV29" s="30"/>
+      <c r="AW29" s="30"/>
+      <c r="AX29" s="30"/>
+      <c r="AY29" s="30">
+        <v>56.47</v>
+      </c>
+      <c r="AZ29" s="30">
+        <v>76.81</v>
+      </c>
+      <c r="BC29" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="BD29" s="30"/>
+      <c r="BE29" s="30"/>
+      <c r="BF29" s="30"/>
+      <c r="BG29" s="30">
+        <v>30.12</v>
+      </c>
+      <c r="BH29" s="30">
+        <v>100</v>
+      </c>
+      <c r="BI29" s="30"/>
+      <c r="BJ29" s="30"/>
+      <c r="BK29" s="30"/>
+      <c r="BL29" s="30"/>
+      <c r="BM29" s="30">
+        <v>48.55</v>
+      </c>
+      <c r="BN29" s="30">
+        <v>93.46</v>
+      </c>
+      <c r="BQ29" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="BR29" s="30"/>
+      <c r="BS29" s="30"/>
+      <c r="BT29" s="30"/>
+      <c r="BU29" s="30">
+        <v>31.93</v>
+      </c>
+      <c r="BV29" s="30">
+        <v>100</v>
+      </c>
+      <c r="BW29" s="30"/>
+      <c r="BX29" s="30"/>
+      <c r="BY29" s="30"/>
+      <c r="BZ29" s="30"/>
+      <c r="CA29" s="30">
+        <v>51.5</v>
+      </c>
+      <c r="CB29" s="30">
+        <v>93.76</v>
+      </c>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B30" s="29" t="s">
         <v>32</v>
       </c>
@@ -8657,8 +10644,96 @@
       <c r="M30" s="30">
         <v>40.380000000000003</v>
       </c>
+      <c r="AA30" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB30" s="30"/>
+      <c r="AC30" s="30"/>
+      <c r="AD30" s="30"/>
+      <c r="AE30" s="30">
+        <v>32.01</v>
+      </c>
+      <c r="AF30" s="30">
+        <v>100</v>
+      </c>
+      <c r="AG30" s="30"/>
+      <c r="AH30" s="30"/>
+      <c r="AI30" s="30"/>
+      <c r="AJ30" s="30"/>
+      <c r="AK30" s="30">
+        <v>56.02</v>
+      </c>
+      <c r="AL30" s="30">
+        <v>91.89</v>
+      </c>
+      <c r="AO30" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP30" s="30"/>
+      <c r="AQ30" s="30"/>
+      <c r="AR30" s="30"/>
+      <c r="AS30" s="30">
+        <v>29.66</v>
+      </c>
+      <c r="AT30" s="30">
+        <v>100</v>
+      </c>
+      <c r="AU30" s="30"/>
+      <c r="AV30" s="30"/>
+      <c r="AW30" s="30"/>
+      <c r="AX30" s="30"/>
+      <c r="AY30" s="30">
+        <v>55.24</v>
+      </c>
+      <c r="AZ30" s="30">
+        <v>92.09</v>
+      </c>
+      <c r="BC30" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="BD30" s="30"/>
+      <c r="BE30" s="30"/>
+      <c r="BF30" s="30"/>
+      <c r="BG30" s="30">
+        <v>29.05</v>
+      </c>
+      <c r="BH30" s="30">
+        <v>100</v>
+      </c>
+      <c r="BI30" s="30"/>
+      <c r="BJ30" s="30"/>
+      <c r="BK30" s="30"/>
+      <c r="BL30" s="30"/>
+      <c r="BM30" s="30">
+        <v>46.66</v>
+      </c>
+      <c r="BN30" s="30">
+        <v>93.77</v>
+      </c>
+      <c r="BQ30" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="BR30" s="30"/>
+      <c r="BS30" s="30"/>
+      <c r="BT30" s="30"/>
+      <c r="BU30" s="30">
+        <v>31.23</v>
+      </c>
+      <c r="BV30" s="30">
+        <v>100</v>
+      </c>
+      <c r="BW30" s="30"/>
+      <c r="BX30" s="30"/>
+      <c r="BY30" s="30"/>
+      <c r="BZ30" s="30"/>
+      <c r="CA30" s="30">
+        <v>50</v>
+      </c>
+      <c r="CB30" s="30">
+        <v>93.93</v>
+      </c>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B31" s="29" t="s">
         <v>28</v>
       </c>
@@ -8693,8 +10768,96 @@
       <c r="M31" s="30">
         <v>40.369999999999997</v>
       </c>
+      <c r="AA31" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB31" s="30"/>
+      <c r="AC31" s="30"/>
+      <c r="AD31" s="30"/>
+      <c r="AE31" s="30">
+        <v>31.81</v>
+      </c>
+      <c r="AF31" s="30">
+        <v>100</v>
+      </c>
+      <c r="AG31" s="30"/>
+      <c r="AH31" s="30"/>
+      <c r="AI31" s="30"/>
+      <c r="AJ31" s="30"/>
+      <c r="AK31" s="30">
+        <v>55.36</v>
+      </c>
+      <c r="AL31" s="30">
+        <v>94.02</v>
+      </c>
+      <c r="AO31" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="AP31" s="30"/>
+      <c r="AQ31" s="30"/>
+      <c r="AR31" s="30"/>
+      <c r="AS31" s="30">
+        <v>29.29</v>
+      </c>
+      <c r="AT31" s="30">
+        <v>100</v>
+      </c>
+      <c r="AU31" s="30"/>
+      <c r="AV31" s="30"/>
+      <c r="AW31" s="30"/>
+      <c r="AX31" s="30"/>
+      <c r="AY31" s="30">
+        <v>54.38</v>
+      </c>
+      <c r="AZ31" s="30">
+        <v>93.02</v>
+      </c>
+      <c r="BC31" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="BD31" s="30"/>
+      <c r="BE31" s="30"/>
+      <c r="BF31" s="30"/>
+      <c r="BG31" s="30">
+        <v>28.39</v>
+      </c>
+      <c r="BH31" s="30">
+        <v>100</v>
+      </c>
+      <c r="BI31" s="30"/>
+      <c r="BJ31" s="30"/>
+      <c r="BK31" s="30"/>
+      <c r="BL31" s="30"/>
+      <c r="BM31" s="30">
+        <v>45.3</v>
+      </c>
+      <c r="BN31" s="30">
+        <v>93.93</v>
+      </c>
+      <c r="BQ31" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="BR31" s="30"/>
+      <c r="BS31" s="30"/>
+      <c r="BT31" s="30"/>
+      <c r="BU31" s="30">
+        <v>30.82</v>
+      </c>
+      <c r="BV31" s="30">
+        <v>100</v>
+      </c>
+      <c r="BW31" s="30"/>
+      <c r="BX31" s="30"/>
+      <c r="BY31" s="30"/>
+      <c r="BZ31" s="30"/>
+      <c r="CA31" s="30">
+        <v>48.94</v>
+      </c>
+      <c r="CB31" s="30">
+        <v>94.03</v>
+      </c>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B32" s="29" t="s">
         <v>33</v>
       </c>
@@ -8729,8 +10892,96 @@
       <c r="M32" s="30">
         <v>40.380000000000003</v>
       </c>
+      <c r="AA32" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB32" s="30"/>
+      <c r="AC32" s="30"/>
+      <c r="AD32" s="30"/>
+      <c r="AE32" s="30">
+        <v>31.67</v>
+      </c>
+      <c r="AF32" s="30">
+        <v>100</v>
+      </c>
+      <c r="AG32" s="30"/>
+      <c r="AH32" s="30"/>
+      <c r="AI32" s="30"/>
+      <c r="AJ32" s="30"/>
+      <c r="AK32" s="30">
+        <v>54.86</v>
+      </c>
+      <c r="AL32" s="30">
+        <v>94.18</v>
+      </c>
+      <c r="AO32" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP32" s="30"/>
+      <c r="AQ32" s="30"/>
+      <c r="AR32" s="30"/>
+      <c r="AS32" s="30">
+        <v>29.06</v>
+      </c>
+      <c r="AT32" s="30">
+        <v>100</v>
+      </c>
+      <c r="AU32" s="30"/>
+      <c r="AV32" s="30"/>
+      <c r="AW32" s="30"/>
+      <c r="AX32" s="30"/>
+      <c r="AY32" s="30">
+        <v>53.75</v>
+      </c>
+      <c r="AZ32" s="30">
+        <v>93.19</v>
+      </c>
+      <c r="BC32" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="BD32" s="30"/>
+      <c r="BE32" s="30"/>
+      <c r="BF32" s="30"/>
+      <c r="BG32" s="30">
+        <v>27.96</v>
+      </c>
+      <c r="BH32" s="30">
+        <v>100</v>
+      </c>
+      <c r="BI32" s="30"/>
+      <c r="BJ32" s="30"/>
+      <c r="BK32" s="30"/>
+      <c r="BL32" s="30"/>
+      <c r="BM32" s="30">
+        <v>44.28</v>
+      </c>
+      <c r="BN32" s="30">
+        <v>94.04</v>
+      </c>
+      <c r="BQ32" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="BR32" s="30"/>
+      <c r="BS32" s="30"/>
+      <c r="BT32" s="30"/>
+      <c r="BU32" s="30">
+        <v>30.57</v>
+      </c>
+      <c r="BV32" s="30">
+        <v>100</v>
+      </c>
+      <c r="BW32" s="30"/>
+      <c r="BX32" s="30"/>
+      <c r="BY32" s="30"/>
+      <c r="BZ32" s="30"/>
+      <c r="CA32" s="30">
+        <v>48.15</v>
+      </c>
+      <c r="CB32" s="30">
+        <v>94.09</v>
+      </c>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B33" s="29" t="s">
         <v>34</v>
       </c>
@@ -8765,8 +11016,96 @@
       <c r="M33" s="30">
         <v>40.42</v>
       </c>
+      <c r="AA33" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB33" s="30"/>
+      <c r="AC33" s="30"/>
+      <c r="AD33" s="30"/>
+      <c r="AE33" s="30">
+        <v>31.57</v>
+      </c>
+      <c r="AF33" s="30">
+        <v>100</v>
+      </c>
+      <c r="AG33" s="30"/>
+      <c r="AH33" s="30"/>
+      <c r="AI33" s="30"/>
+      <c r="AJ33" s="30"/>
+      <c r="AK33" s="30">
+        <v>54.47</v>
+      </c>
+      <c r="AL33" s="30">
+        <v>94.29</v>
+      </c>
+      <c r="AO33" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="AP33" s="30"/>
+      <c r="AQ33" s="30"/>
+      <c r="AR33" s="30"/>
+      <c r="AS33" s="30">
+        <v>28.88</v>
+      </c>
+      <c r="AT33" s="30">
+        <v>100</v>
+      </c>
+      <c r="AU33" s="30"/>
+      <c r="AV33" s="30"/>
+      <c r="AW33" s="30"/>
+      <c r="AX33" s="30"/>
+      <c r="AY33" s="30">
+        <v>53.25</v>
+      </c>
+      <c r="AZ33" s="30">
+        <v>93.3</v>
+      </c>
+      <c r="BC33" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="BD33" s="30"/>
+      <c r="BE33" s="30"/>
+      <c r="BF33" s="30"/>
+      <c r="BG33" s="30">
+        <v>27.65</v>
+      </c>
+      <c r="BH33" s="30">
+        <v>100</v>
+      </c>
+      <c r="BI33" s="30"/>
+      <c r="BJ33" s="30"/>
+      <c r="BK33" s="30"/>
+      <c r="BL33" s="30"/>
+      <c r="BM33" s="30">
+        <v>43.48</v>
+      </c>
+      <c r="BN33" s="30">
+        <v>94.11</v>
+      </c>
+      <c r="BQ33" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="BR33" s="30"/>
+      <c r="BS33" s="30"/>
+      <c r="BT33" s="30"/>
+      <c r="BU33" s="30">
+        <v>30.38</v>
+      </c>
+      <c r="BV33" s="30">
+        <v>100</v>
+      </c>
+      <c r="BW33" s="30"/>
+      <c r="BX33" s="30"/>
+      <c r="BY33" s="30"/>
+      <c r="BZ33" s="30"/>
+      <c r="CA33" s="30">
+        <v>47.54</v>
+      </c>
+      <c r="CB33" s="30">
+        <v>94.13</v>
+      </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B34" s="29" t="s">
         <v>35</v>
       </c>
@@ -8801,8 +11140,96 @@
       <c r="M34" s="30">
         <v>40.479999999999997</v>
       </c>
+      <c r="AA34" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB34" s="30"/>
+      <c r="AC34" s="30"/>
+      <c r="AD34" s="30"/>
+      <c r="AE34" s="37">
+        <v>31.5</v>
+      </c>
+      <c r="AF34" s="30">
+        <v>100</v>
+      </c>
+      <c r="AG34" s="30"/>
+      <c r="AH34" s="30"/>
+      <c r="AI34" s="30"/>
+      <c r="AJ34" s="30"/>
+      <c r="AK34" s="30">
+        <v>54.14</v>
+      </c>
+      <c r="AL34" s="30">
+        <v>94.36</v>
+      </c>
+      <c r="AO34" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="AP34" s="30"/>
+      <c r="AQ34" s="30"/>
+      <c r="AR34" s="30"/>
+      <c r="AS34" s="37">
+        <v>28.76</v>
+      </c>
+      <c r="AT34" s="30">
+        <v>100</v>
+      </c>
+      <c r="AU34" s="30"/>
+      <c r="AV34" s="30"/>
+      <c r="AW34" s="30"/>
+      <c r="AX34" s="30"/>
+      <c r="AY34" s="30">
+        <v>52.86</v>
+      </c>
+      <c r="AZ34" s="30">
+        <v>93.38</v>
+      </c>
+      <c r="BC34" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="BD34" s="30"/>
+      <c r="BE34" s="30"/>
+      <c r="BF34" s="30"/>
+      <c r="BG34" s="37">
+        <v>27.43</v>
+      </c>
+      <c r="BH34" s="30">
+        <v>100</v>
+      </c>
+      <c r="BI34" s="30"/>
+      <c r="BJ34" s="30"/>
+      <c r="BK34" s="30"/>
+      <c r="BL34" s="30"/>
+      <c r="BM34" s="30">
+        <v>42.84</v>
+      </c>
+      <c r="BN34" s="30">
+        <v>94.17</v>
+      </c>
+      <c r="BQ34" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="BR34" s="30"/>
+      <c r="BS34" s="30"/>
+      <c r="BT34" s="30"/>
+      <c r="BU34" s="37">
+        <v>30.24</v>
+      </c>
+      <c r="BV34" s="30">
+        <v>100</v>
+      </c>
+      <c r="BW34" s="30"/>
+      <c r="BX34" s="30"/>
+      <c r="BY34" s="30"/>
+      <c r="BZ34" s="30"/>
+      <c r="CA34" s="30">
+        <v>47.06</v>
+      </c>
+      <c r="CB34" s="30">
+        <v>94.16</v>
+      </c>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B35" s="29" t="s">
         <v>36</v>
       </c>
@@ -8837,8 +11264,60 @@
       <c r="M35" s="30">
         <v>41.14</v>
       </c>
+      <c r="AB35" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC35" s="38"/>
+      <c r="AD35" s="39"/>
+      <c r="AE35" s="38"/>
+      <c r="AF35" s="39"/>
+      <c r="AG35" s="40"/>
+      <c r="AH35" s="41"/>
+      <c r="AI35" s="38"/>
+      <c r="AJ35" s="39"/>
+      <c r="AK35" s="38"/>
+      <c r="AL35" s="39"/>
+      <c r="AP35" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ35" s="38"/>
+      <c r="AR35" s="39"/>
+      <c r="AS35" s="38"/>
+      <c r="AT35" s="39"/>
+      <c r="AU35" s="40"/>
+      <c r="AV35" s="41"/>
+      <c r="AW35" s="38"/>
+      <c r="AX35" s="39"/>
+      <c r="AY35" s="38"/>
+      <c r="AZ35" s="39"/>
+      <c r="BD35" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="BE35" s="38"/>
+      <c r="BF35" s="39"/>
+      <c r="BG35" s="38"/>
+      <c r="BH35" s="39"/>
+      <c r="BI35" s="40"/>
+      <c r="BJ35" s="41"/>
+      <c r="BK35" s="38"/>
+      <c r="BL35" s="39"/>
+      <c r="BM35" s="38"/>
+      <c r="BN35" s="39"/>
+      <c r="BR35" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="BS35" s="38"/>
+      <c r="BT35" s="39"/>
+      <c r="BU35" s="38"/>
+      <c r="BV35" s="39"/>
+      <c r="BW35" s="40"/>
+      <c r="BX35" s="41"/>
+      <c r="BY35" s="38"/>
+      <c r="BZ35" s="39"/>
+      <c r="CA35" s="38"/>
+      <c r="CB35" s="39"/>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B36" s="29" t="s">
         <v>37</v>
       </c>
@@ -8874,7 +11353,7 @@
         <v>41.32</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B37" s="29" t="s">
         <v>38</v>
       </c>
@@ -8910,23 +11389,23 @@
         <v>41.43</v>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C38" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="50"/>
-      <c r="E38" s="51"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="51"/>
-      <c r="H38" s="52"/>
-      <c r="I38" s="53"/>
-      <c r="J38" s="50"/>
-      <c r="K38" s="51"/>
-      <c r="L38" s="50"/>
-      <c r="M38" s="51"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="39"/>
+      <c r="H38" s="40"/>
+      <c r="I38" s="41"/>
+      <c r="J38" s="38"/>
+      <c r="K38" s="39"/>
+      <c r="L38" s="38"/>
+      <c r="M38" s="39"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="91">
     <mergeCell ref="D38:E38"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="H38:I38"/>
@@ -8946,6 +11425,78 @@
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="J3:K3"/>
     <mergeCell ref="L3:M3"/>
+    <mergeCell ref="AA2:AL2"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="AG3:AH3"/>
+    <mergeCell ref="AI3:AJ3"/>
+    <mergeCell ref="AK3:AL3"/>
+    <mergeCell ref="AA5:AA8"/>
+    <mergeCell ref="AA11:AL11"/>
+    <mergeCell ref="AC12:AD12"/>
+    <mergeCell ref="AE12:AF12"/>
+    <mergeCell ref="AG12:AH12"/>
+    <mergeCell ref="AI12:AJ12"/>
+    <mergeCell ref="AK12:AL12"/>
+    <mergeCell ref="AC35:AD35"/>
+    <mergeCell ref="AE35:AF35"/>
+    <mergeCell ref="AG35:AH35"/>
+    <mergeCell ref="AI35:AJ35"/>
+    <mergeCell ref="AK35:AL35"/>
+    <mergeCell ref="AO2:AZ2"/>
+    <mergeCell ref="AQ3:AR3"/>
+    <mergeCell ref="AS3:AT3"/>
+    <mergeCell ref="AU3:AV3"/>
+    <mergeCell ref="AW3:AX3"/>
+    <mergeCell ref="AY3:AZ3"/>
+    <mergeCell ref="AO5:AO8"/>
+    <mergeCell ref="AO11:AZ11"/>
+    <mergeCell ref="AQ12:AR12"/>
+    <mergeCell ref="AS12:AT12"/>
+    <mergeCell ref="AU12:AV12"/>
+    <mergeCell ref="AW12:AX12"/>
+    <mergeCell ref="AY12:AZ12"/>
+    <mergeCell ref="AQ35:AR35"/>
+    <mergeCell ref="AS35:AT35"/>
+    <mergeCell ref="AU35:AV35"/>
+    <mergeCell ref="AW35:AX35"/>
+    <mergeCell ref="AY35:AZ35"/>
+    <mergeCell ref="BC2:BN2"/>
+    <mergeCell ref="BE3:BF3"/>
+    <mergeCell ref="BG3:BH3"/>
+    <mergeCell ref="BI3:BJ3"/>
+    <mergeCell ref="BK3:BL3"/>
+    <mergeCell ref="BM3:BN3"/>
+    <mergeCell ref="BC5:BC8"/>
+    <mergeCell ref="BC11:BN11"/>
+    <mergeCell ref="BE12:BF12"/>
+    <mergeCell ref="BG12:BH12"/>
+    <mergeCell ref="BI12:BJ12"/>
+    <mergeCell ref="BK12:BL12"/>
+    <mergeCell ref="BM12:BN12"/>
+    <mergeCell ref="BE35:BF35"/>
+    <mergeCell ref="BG35:BH35"/>
+    <mergeCell ref="BI35:BJ35"/>
+    <mergeCell ref="BK35:BL35"/>
+    <mergeCell ref="BM35:BN35"/>
+    <mergeCell ref="BQ2:CB2"/>
+    <mergeCell ref="BS3:BT3"/>
+    <mergeCell ref="BU3:BV3"/>
+    <mergeCell ref="BW3:BX3"/>
+    <mergeCell ref="BY3:BZ3"/>
+    <mergeCell ref="CA3:CB3"/>
+    <mergeCell ref="BQ5:BQ8"/>
+    <mergeCell ref="BQ11:CB11"/>
+    <mergeCell ref="BS12:BT12"/>
+    <mergeCell ref="BU12:BV12"/>
+    <mergeCell ref="BW12:BX12"/>
+    <mergeCell ref="BY12:BZ12"/>
+    <mergeCell ref="CA12:CB12"/>
+    <mergeCell ref="BS35:BT35"/>
+    <mergeCell ref="BU35:BV35"/>
+    <mergeCell ref="BW35:BX35"/>
+    <mergeCell ref="BY35:BZ35"/>
+    <mergeCell ref="CA35:CB35"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Results_metrics.xlsx
+++ b/Results_metrics.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Enrica\Desktop\Nuovo_ML_Project\MaskArchitectureAnomaly_CourseProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gaiac\Desktop\polito\machine learning\MaskArchitectureAnomaly_CourseProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1523F03-0172-4C2F-A11F-EE0114E63202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E140A3-96B4-4D03-8875-7623017B2363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11232" yWindow="0" windowWidth="11808" windowHeight="12072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="51">
   <si>
     <t>Model</t>
   </si>
@@ -172,6 +172,12 @@
   </si>
   <si>
     <t>RISULTATI METRICHE per EoMT con TEMPERATURE su MSP con Logitnorm tau = 0,10</t>
+  </si>
+  <si>
+    <t>81.7%</t>
+  </si>
+  <si>
+    <t>t = 0,2</t>
   </si>
 </sst>
 </file>
@@ -721,10 +727,16 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -750,12 +762,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -901,7 +907,7 @@
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>t = 0,25</c:v>
+                  <c:v>t = 0,2</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
@@ -970,67 +976,67 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>34.29</c:v>
+                  <c:v>74.77</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>42.38</c:v>
+                  <c:v>74.209999999999994</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>54.02</c:v>
+                  <c:v>73.64</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>58.57</c:v>
+                  <c:v>73.27</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>61.18</c:v>
+                  <c:v>72.95</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>63.4</c:v>
+                  <c:v>73.849999999999994</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>64.28</c:v>
+                  <c:v>74.3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>65.13</c:v>
+                  <c:v>74.650000000000006</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>67.64</c:v>
+                  <c:v>75.36</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>75.12</c:v>
+                  <c:v>79.150000000000006</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>79.900000000000006</c:v>
+                  <c:v>83.99</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>82.66</c:v>
+                  <c:v>84.35</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>83.9</c:v>
+                  <c:v>84.2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>84.85</c:v>
+                  <c:v>83.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>85.12</c:v>
+                  <c:v>82.83</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>85.25</c:v>
+                  <c:v>82.29</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>85.33</c:v>
+                  <c:v>81.849999999999994</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>85.38</c:v>
+                  <c:v>81.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>85.42</c:v>
+                  <c:v>81.2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>85.45</c:v>
+                  <c:v>80.95</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>85.47</c:v>
+                  <c:v>80.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1089,7 +1095,7 @@
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>t = 0,25</c:v>
+                  <c:v>t = 0,2</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
@@ -1158,67 +1164,67 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>91.9</c:v>
+                  <c:v>52.9</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>89.39</c:v>
+                  <c:v>52.9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>30.4</c:v>
+                  <c:v>53.37</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>28.71</c:v>
+                  <c:v>47.2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>28.38</c:v>
+                  <c:v>47.26</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>27.09</c:v>
+                  <c:v>33.659999999999997</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>26.47</c:v>
+                  <c:v>29.93</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>25.89</c:v>
+                  <c:v>27.46</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>24.34</c:v>
+                  <c:v>23.22</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>9.82</c:v>
+                  <c:v>11.57</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6.72</c:v>
+                  <c:v>4.24</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4.93</c:v>
+                  <c:v>3.64</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.91</c:v>
+                  <c:v>3.52</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.18</c:v>
+                  <c:v>3.6</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.97</c:v>
+                  <c:v>3.73</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.86</c:v>
+                  <c:v>3.84</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2.8</c:v>
+                  <c:v>3.93</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2.76</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2.73</c:v>
+                  <c:v>4.07</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2.7</c:v>
+                  <c:v>4.12</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2.68</c:v>
+                  <c:v>4.1900000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1670,7 +1676,7 @@
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>t = 0,25</c:v>
+                  <c:v>t = 0,2</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
@@ -1739,67 +1745,67 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>33.64</c:v>
+                  <c:v>79.37</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60.22</c:v>
+                  <c:v>81.89</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>75.39</c:v>
+                  <c:v>88.05</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>78.2</c:v>
+                  <c:v>89.79</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>78.75</c:v>
+                  <c:v>89.9</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>80.95</c:v>
+                  <c:v>90.08</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>82</c:v>
+                  <c:v>89.98</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>82.96</c:v>
+                  <c:v>89.67</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>85.28</c:v>
+                  <c:v>84.83</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>88.12</c:v>
+                  <c:v>72.66</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>90.94</c:v>
+                  <c:v>63.45</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>91</c:v>
+                  <c:v>56.31</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>91.17</c:v>
+                  <c:v>51.7</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>91.29</c:v>
+                  <c:v>45.62</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>91.31</c:v>
+                  <c:v>42.33</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>91.31</c:v>
+                  <c:v>39.26</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>91.31</c:v>
+                  <c:v>37.42</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>91.3</c:v>
+                  <c:v>36.72</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>91.3</c:v>
+                  <c:v>36.28</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>91.3</c:v>
+                  <c:v>35.979999999999997</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>91.29</c:v>
+                  <c:v>35.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1858,7 +1864,7 @@
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>t = 0,25</c:v>
+                  <c:v>t = 0,2</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
@@ -1927,67 +1933,67 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>91.83</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>82.2</c:v>
+                  <c:v>2.16</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>26.43</c:v>
+                  <c:v>0.61</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>17.52</c:v>
+                  <c:v>0.54</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>16.989999999999998</c:v>
+                  <c:v>0.54</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>14.95</c:v>
+                  <c:v>0.57999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>14.28</c:v>
+                  <c:v>0.62</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>10.92</c:v>
+                  <c:v>0.68</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>11.74</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>12.57</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>15.04</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>16.91</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>17.68</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>19.440000000000001</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>20.47</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>21.04</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>21.37</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>21.52</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>21.62</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>21.75</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>21.84</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2439,7 +2445,7 @@
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>t = 0,25</c:v>
+                  <c:v>t = 0,2</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
@@ -2627,7 +2633,7 @@
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>t = 0,25</c:v>
+                  <c:v>t = 0,2</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
@@ -3208,7 +3214,7 @@
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>t = 0,25</c:v>
+                  <c:v>t = 0,2</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
@@ -3396,7 +3402,7 @@
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>t = 0,25</c:v>
+                  <c:v>t = 0,2</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
@@ -3977,7 +3983,7 @@
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>t = 0,25</c:v>
+                  <c:v>t = 0,2</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
@@ -4147,7 +4153,7 @@
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>t = 0,25</c:v>
+                  <c:v>t = 0,2</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
@@ -7755,198 +7761,198 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:CB38"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.44140625" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" customWidth="1"/>
+    <col min="3" max="3" width="13.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="45" t="s">
+    <row r="1" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="51"/>
-      <c r="AA2" s="45" t="s">
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="53"/>
+      <c r="AA2" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="AB2" s="50"/>
-      <c r="AC2" s="50"/>
-      <c r="AD2" s="50"/>
-      <c r="AE2" s="50"/>
-      <c r="AF2" s="50"/>
-      <c r="AG2" s="50"/>
-      <c r="AH2" s="50"/>
-      <c r="AI2" s="50"/>
-      <c r="AJ2" s="50"/>
-      <c r="AK2" s="50"/>
-      <c r="AL2" s="51"/>
-      <c r="AO2" s="45" t="s">
+      <c r="AB2" s="52"/>
+      <c r="AC2" s="52"/>
+      <c r="AD2" s="52"/>
+      <c r="AE2" s="52"/>
+      <c r="AF2" s="52"/>
+      <c r="AG2" s="52"/>
+      <c r="AH2" s="52"/>
+      <c r="AI2" s="52"/>
+      <c r="AJ2" s="52"/>
+      <c r="AK2" s="52"/>
+      <c r="AL2" s="53"/>
+      <c r="AO2" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="AP2" s="50"/>
-      <c r="AQ2" s="50"/>
-      <c r="AR2" s="50"/>
-      <c r="AS2" s="50"/>
-      <c r="AT2" s="50"/>
-      <c r="AU2" s="50"/>
-      <c r="AV2" s="50"/>
-      <c r="AW2" s="50"/>
-      <c r="AX2" s="50"/>
-      <c r="AY2" s="50"/>
-      <c r="AZ2" s="51"/>
-      <c r="BC2" s="45" t="s">
+      <c r="AP2" s="52"/>
+      <c r="AQ2" s="52"/>
+      <c r="AR2" s="52"/>
+      <c r="AS2" s="52"/>
+      <c r="AT2" s="52"/>
+      <c r="AU2" s="52"/>
+      <c r="AV2" s="52"/>
+      <c r="AW2" s="52"/>
+      <c r="AX2" s="52"/>
+      <c r="AY2" s="52"/>
+      <c r="AZ2" s="53"/>
+      <c r="BC2" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="BD2" s="50"/>
-      <c r="BE2" s="50"/>
-      <c r="BF2" s="50"/>
-      <c r="BG2" s="50"/>
-      <c r="BH2" s="50"/>
-      <c r="BI2" s="50"/>
-      <c r="BJ2" s="50"/>
-      <c r="BK2" s="50"/>
-      <c r="BL2" s="50"/>
-      <c r="BM2" s="50"/>
-      <c r="BN2" s="51"/>
-      <c r="BQ2" s="45" t="s">
+      <c r="BD2" s="52"/>
+      <c r="BE2" s="52"/>
+      <c r="BF2" s="52"/>
+      <c r="BG2" s="52"/>
+      <c r="BH2" s="52"/>
+      <c r="BI2" s="52"/>
+      <c r="BJ2" s="52"/>
+      <c r="BK2" s="52"/>
+      <c r="BL2" s="52"/>
+      <c r="BM2" s="52"/>
+      <c r="BN2" s="53"/>
+      <c r="BQ2" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="BR2" s="50"/>
-      <c r="BS2" s="50"/>
-      <c r="BT2" s="50"/>
-      <c r="BU2" s="50"/>
-      <c r="BV2" s="50"/>
-      <c r="BW2" s="50"/>
-      <c r="BX2" s="50"/>
-      <c r="BY2" s="50"/>
-      <c r="BZ2" s="50"/>
-      <c r="CA2" s="50"/>
-      <c r="CB2" s="51"/>
+      <c r="BR2" s="52"/>
+      <c r="BS2" s="52"/>
+      <c r="BT2" s="52"/>
+      <c r="BU2" s="52"/>
+      <c r="BV2" s="52"/>
+      <c r="BW2" s="52"/>
+      <c r="BX2" s="52"/>
+      <c r="BY2" s="52"/>
+      <c r="BZ2" s="52"/>
+      <c r="CA2" s="52"/>
+      <c r="CB2" s="53"/>
     </row>
-    <row r="3" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="1"/>
       <c r="C3" s="5"/>
-      <c r="D3" s="48" t="s">
+      <c r="D3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="49"/>
-      <c r="F3" s="48" t="s">
+      <c r="E3" s="51"/>
+      <c r="F3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="49"/>
-      <c r="H3" s="48" t="s">
+      <c r="G3" s="51"/>
+      <c r="H3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="49"/>
-      <c r="J3" s="48" t="s">
+      <c r="I3" s="51"/>
+      <c r="J3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="49"/>
-      <c r="L3" s="48" t="s">
+      <c r="K3" s="51"/>
+      <c r="L3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="49"/>
+      <c r="M3" s="51"/>
       <c r="AA3" s="1"/>
       <c r="AB3" s="5"/>
-      <c r="AC3" s="48" t="s">
+      <c r="AC3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="AD3" s="49"/>
-      <c r="AE3" s="48" t="s">
+      <c r="AD3" s="51"/>
+      <c r="AE3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="AF3" s="49"/>
-      <c r="AG3" s="48" t="s">
+      <c r="AF3" s="51"/>
+      <c r="AG3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="AH3" s="49"/>
-      <c r="AI3" s="48" t="s">
+      <c r="AH3" s="51"/>
+      <c r="AI3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AJ3" s="49"/>
-      <c r="AK3" s="48" t="s">
+      <c r="AJ3" s="51"/>
+      <c r="AK3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="49"/>
+      <c r="AL3" s="51"/>
       <c r="AO3" s="1"/>
       <c r="AP3" s="5"/>
-      <c r="AQ3" s="48" t="s">
+      <c r="AQ3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="AR3" s="49"/>
-      <c r="AS3" s="48" t="s">
+      <c r="AR3" s="51"/>
+      <c r="AS3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="AT3" s="49"/>
-      <c r="AU3" s="48" t="s">
+      <c r="AT3" s="51"/>
+      <c r="AU3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="AV3" s="49"/>
-      <c r="AW3" s="48" t="s">
+      <c r="AV3" s="51"/>
+      <c r="AW3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AX3" s="49"/>
-      <c r="AY3" s="48" t="s">
+      <c r="AX3" s="51"/>
+      <c r="AY3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="AZ3" s="49"/>
+      <c r="AZ3" s="51"/>
       <c r="BC3" s="1"/>
       <c r="BD3" s="5"/>
-      <c r="BE3" s="48" t="s">
+      <c r="BE3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="BF3" s="49"/>
-      <c r="BG3" s="48" t="s">
+      <c r="BF3" s="51"/>
+      <c r="BG3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="BH3" s="49"/>
-      <c r="BI3" s="48" t="s">
+      <c r="BH3" s="51"/>
+      <c r="BI3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="BJ3" s="49"/>
-      <c r="BK3" s="48" t="s">
+      <c r="BJ3" s="51"/>
+      <c r="BK3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="BL3" s="49"/>
-      <c r="BM3" s="48" t="s">
+      <c r="BL3" s="51"/>
+      <c r="BM3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="BN3" s="49"/>
+      <c r="BN3" s="51"/>
       <c r="BQ3" s="1"/>
       <c r="BR3" s="5"/>
-      <c r="BS3" s="48" t="s">
+      <c r="BS3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="BT3" s="49"/>
-      <c r="BU3" s="48" t="s">
+      <c r="BT3" s="51"/>
+      <c r="BU3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="BV3" s="49"/>
-      <c r="BW3" s="48" t="s">
+      <c r="BV3" s="51"/>
+      <c r="BW3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="BX3" s="49"/>
-      <c r="BY3" s="48" t="s">
+      <c r="BX3" s="51"/>
+      <c r="BY3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="BZ3" s="49"/>
-      <c r="CA3" s="48" t="s">
+      <c r="BZ3" s="51"/>
+      <c r="CA3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="CB3" s="49"/>
+      <c r="CB3" s="51"/>
     </row>
-    <row r="4" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B4" s="6" t="s">
         <v>0</v>
       </c>
@@ -8128,8 +8134,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:80" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="52" t="s">
+    <row r="5" spans="2:80" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="42" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -8165,7 +8171,7 @@
       <c r="M5" s="14">
         <v>82.58</v>
       </c>
-      <c r="AA5" s="42" t="s">
+      <c r="AA5" s="45" t="s">
         <v>13</v>
       </c>
       <c r="AB5" s="12" t="s">
@@ -8189,7 +8195,7 @@
       <c r="AL5" s="20">
         <v>19.14</v>
       </c>
-      <c r="AO5" s="42" t="s">
+      <c r="AO5" s="45" t="s">
         <v>13</v>
       </c>
       <c r="AP5" s="12" t="s">
@@ -8213,7 +8219,7 @@
       <c r="AZ5" s="20">
         <v>19.829999999999998</v>
       </c>
-      <c r="BC5" s="42" t="s">
+      <c r="BC5" s="45" t="s">
         <v>13</v>
       </c>
       <c r="BD5" s="12" t="s">
@@ -8237,7 +8243,7 @@
       <c r="BN5" s="20">
         <v>20.05</v>
       </c>
-      <c r="BQ5" s="42" t="s">
+      <c r="BQ5" s="45" t="s">
         <v>13</v>
       </c>
       <c r="BR5" s="12" t="s">
@@ -8262,7 +8268,7 @@
         <v>20.92</v>
       </c>
     </row>
-    <row r="6" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:80" x14ac:dyDescent="0.35">
       <c r="B6" s="43"/>
       <c r="C6" s="9" t="s">
         <v>11</v>
@@ -8386,8 +8392,8 @@
         <v>20.92</v>
       </c>
     </row>
-    <row r="7" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="53"/>
+    <row r="7" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="44"/>
       <c r="C7" s="11" t="s">
         <v>12</v>
       </c>
@@ -8510,24 +8516,24 @@
         <v>20.49</v>
       </c>
     </row>
-    <row r="8" spans="2:80" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="42" t="s">
+    <row r="8" spans="2:80" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B8" s="45" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="19">
-        <v>63.4</v>
+        <v>76.11</v>
       </c>
       <c r="E8" s="20">
-        <v>27.09</v>
+        <v>33.9</v>
       </c>
       <c r="F8" s="19">
-        <v>80.95</v>
+        <v>90.04</v>
       </c>
       <c r="G8" s="20">
-        <v>14.95</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H8" s="19">
         <v>3.33</v>
@@ -8547,7 +8553,7 @@
       <c r="M8" s="20">
         <v>44.62</v>
       </c>
-      <c r="AA8" s="44"/>
+      <c r="AA8" s="46"/>
       <c r="AB8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8569,7 +8575,7 @@
       <c r="AL8" s="22">
         <v>21.78</v>
       </c>
-      <c r="AO8" s="44"/>
+      <c r="AO8" s="46"/>
       <c r="AP8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8591,7 +8597,7 @@
       <c r="AZ8" s="22">
         <v>19.12</v>
       </c>
-      <c r="BC8" s="44"/>
+      <c r="BC8" s="46"/>
       <c r="BD8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8613,7 +8619,7 @@
       <c r="BN8" s="22">
         <v>19.13</v>
       </c>
-      <c r="BQ8" s="44"/>
+      <c r="BQ8" s="46"/>
       <c r="BR8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8636,7 +8642,7 @@
         <v>19.53</v>
       </c>
     </row>
-    <row r="9" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:80" x14ac:dyDescent="0.35">
       <c r="B9" s="43"/>
       <c r="C9" s="9" t="s">
         <v>11</v>
@@ -8672,22 +8678,22 @@
         <v>19.09</v>
       </c>
     </row>
-    <row r="10" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B10" s="43"/>
       <c r="C10" s="9" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="15">
-        <v>66.59</v>
+        <v>75.739999999999995</v>
       </c>
       <c r="E10" s="16">
-        <v>26.18</v>
+        <v>33.6</v>
       </c>
       <c r="F10" s="15">
         <v>84.36</v>
       </c>
       <c r="G10" s="16">
-        <v>11.95</v>
+        <v>0.68</v>
       </c>
       <c r="H10" s="15">
         <v>5.58</v>
@@ -8708,8 +8714,8 @@
         <v>44.12</v>
       </c>
     </row>
-    <row r="11" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="44"/>
+    <row r="11" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="46"/>
       <c r="C11" s="10" t="s">
         <v>14</v>
       </c>
@@ -8743,154 +8749,154 @@
       <c r="M11" s="22">
         <v>17.579999999999998</v>
       </c>
-      <c r="AA11" s="45" t="s">
+      <c r="AA11" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="AB11" s="46"/>
-      <c r="AC11" s="46"/>
-      <c r="AD11" s="46"/>
-      <c r="AE11" s="46"/>
-      <c r="AF11" s="46"/>
-      <c r="AG11" s="46"/>
-      <c r="AH11" s="46"/>
-      <c r="AI11" s="46"/>
-      <c r="AJ11" s="46"/>
-      <c r="AK11" s="46"/>
-      <c r="AL11" s="47"/>
-      <c r="AO11" s="45" t="s">
+      <c r="AB11" s="48"/>
+      <c r="AC11" s="48"/>
+      <c r="AD11" s="48"/>
+      <c r="AE11" s="48"/>
+      <c r="AF11" s="48"/>
+      <c r="AG11" s="48"/>
+      <c r="AH11" s="48"/>
+      <c r="AI11" s="48"/>
+      <c r="AJ11" s="48"/>
+      <c r="AK11" s="48"/>
+      <c r="AL11" s="49"/>
+      <c r="AO11" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="AP11" s="46"/>
-      <c r="AQ11" s="46"/>
-      <c r="AR11" s="46"/>
-      <c r="AS11" s="46"/>
-      <c r="AT11" s="46"/>
-      <c r="AU11" s="46"/>
-      <c r="AV11" s="46"/>
-      <c r="AW11" s="46"/>
-      <c r="AX11" s="46"/>
-      <c r="AY11" s="46"/>
-      <c r="AZ11" s="47"/>
-      <c r="BC11" s="45" t="s">
+      <c r="AP11" s="48"/>
+      <c r="AQ11" s="48"/>
+      <c r="AR11" s="48"/>
+      <c r="AS11" s="48"/>
+      <c r="AT11" s="48"/>
+      <c r="AU11" s="48"/>
+      <c r="AV11" s="48"/>
+      <c r="AW11" s="48"/>
+      <c r="AX11" s="48"/>
+      <c r="AY11" s="48"/>
+      <c r="AZ11" s="49"/>
+      <c r="BC11" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="BD11" s="46"/>
-      <c r="BE11" s="46"/>
-      <c r="BF11" s="46"/>
-      <c r="BG11" s="46"/>
-      <c r="BH11" s="46"/>
-      <c r="BI11" s="46"/>
-      <c r="BJ11" s="46"/>
-      <c r="BK11" s="46"/>
-      <c r="BL11" s="46"/>
-      <c r="BM11" s="46"/>
-      <c r="BN11" s="47"/>
-      <c r="BQ11" s="45" t="s">
+      <c r="BD11" s="48"/>
+      <c r="BE11" s="48"/>
+      <c r="BF11" s="48"/>
+      <c r="BG11" s="48"/>
+      <c r="BH11" s="48"/>
+      <c r="BI11" s="48"/>
+      <c r="BJ11" s="48"/>
+      <c r="BK11" s="48"/>
+      <c r="BL11" s="48"/>
+      <c r="BM11" s="48"/>
+      <c r="BN11" s="49"/>
+      <c r="BQ11" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="BR11" s="46"/>
-      <c r="BS11" s="46"/>
-      <c r="BT11" s="46"/>
-      <c r="BU11" s="46"/>
-      <c r="BV11" s="46"/>
-      <c r="BW11" s="46"/>
-      <c r="BX11" s="46"/>
-      <c r="BY11" s="46"/>
-      <c r="BZ11" s="46"/>
-      <c r="CA11" s="46"/>
-      <c r="CB11" s="47"/>
+      <c r="BR11" s="48"/>
+      <c r="BS11" s="48"/>
+      <c r="BT11" s="48"/>
+      <c r="BU11" s="48"/>
+      <c r="BV11" s="48"/>
+      <c r="BW11" s="48"/>
+      <c r="BX11" s="48"/>
+      <c r="BY11" s="48"/>
+      <c r="BZ11" s="48"/>
+      <c r="CA11" s="48"/>
+      <c r="CB11" s="49"/>
     </row>
-    <row r="12" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="AA12" s="24"/>
       <c r="AB12" s="4"/>
-      <c r="AC12" s="48" t="s">
+      <c r="AC12" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="AD12" s="49"/>
-      <c r="AE12" s="48" t="s">
+      <c r="AD12" s="51"/>
+      <c r="AE12" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="AF12" s="49"/>
-      <c r="AG12" s="48" t="s">
+      <c r="AF12" s="51"/>
+      <c r="AG12" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="AH12" s="49"/>
-      <c r="AI12" s="48" t="s">
+      <c r="AH12" s="51"/>
+      <c r="AI12" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AJ12" s="49"/>
-      <c r="AK12" s="48" t="s">
+      <c r="AJ12" s="51"/>
+      <c r="AK12" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="AL12" s="49"/>
+      <c r="AL12" s="51"/>
       <c r="AO12" s="24"/>
       <c r="AP12" s="4"/>
-      <c r="AQ12" s="48" t="s">
+      <c r="AQ12" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="AR12" s="49"/>
-      <c r="AS12" s="48" t="s">
+      <c r="AR12" s="51"/>
+      <c r="AS12" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="AT12" s="49"/>
-      <c r="AU12" s="48" t="s">
+      <c r="AT12" s="51"/>
+      <c r="AU12" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="AV12" s="49"/>
-      <c r="AW12" s="48" t="s">
+      <c r="AV12" s="51"/>
+      <c r="AW12" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AX12" s="49"/>
-      <c r="AY12" s="48" t="s">
+      <c r="AX12" s="51"/>
+      <c r="AY12" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="AZ12" s="49"/>
+      <c r="AZ12" s="51"/>
       <c r="BC12" s="24"/>
       <c r="BD12" s="4"/>
-      <c r="BE12" s="48" t="s">
+      <c r="BE12" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="BF12" s="49"/>
-      <c r="BG12" s="48" t="s">
+      <c r="BF12" s="51"/>
+      <c r="BG12" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="BH12" s="49"/>
-      <c r="BI12" s="48" t="s">
+      <c r="BH12" s="51"/>
+      <c r="BI12" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="BJ12" s="49"/>
-      <c r="BK12" s="48" t="s">
+      <c r="BJ12" s="51"/>
+      <c r="BK12" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="BL12" s="49"/>
-      <c r="BM12" s="48" t="s">
+      <c r="BL12" s="51"/>
+      <c r="BM12" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="BN12" s="49"/>
+      <c r="BN12" s="51"/>
       <c r="BQ12" s="24"/>
       <c r="BR12" s="4"/>
-      <c r="BS12" s="48" t="s">
+      <c r="BS12" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="BT12" s="49"/>
-      <c r="BU12" s="48" t="s">
+      <c r="BT12" s="51"/>
+      <c r="BU12" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="BV12" s="49"/>
-      <c r="BW12" s="48" t="s">
+      <c r="BV12" s="51"/>
+      <c r="BW12" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="BX12" s="49"/>
-      <c r="BY12" s="48" t="s">
+      <c r="BX12" s="51"/>
+      <c r="BY12" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="BZ12" s="49"/>
-      <c r="CA12" s="48" t="s">
+      <c r="BZ12" s="51"/>
+      <c r="CA12" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="CB12" s="49"/>
+      <c r="CB12" s="51"/>
     </row>
-    <row r="13" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="AA13" s="25" t="s">
         <v>16</v>
       </c>
@@ -9036,21 +9042,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="45" t="s">
+    <row r="14" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="47"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="48"/>
+      <c r="M14" s="49"/>
       <c r="AA14" s="29" t="s">
         <v>24</v>
       </c>
@@ -9112,29 +9118,29 @@
       <c r="CA14" s="30"/>
       <c r="CB14" s="30"/>
     </row>
-    <row r="15" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B15" s="24"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="48" t="s">
+      <c r="D15" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="E15" s="49"/>
-      <c r="F15" s="48" t="s">
+      <c r="E15" s="51"/>
+      <c r="F15" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="49"/>
-      <c r="H15" s="48" t="s">
+      <c r="G15" s="51"/>
+      <c r="H15" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="49"/>
-      <c r="J15" s="48" t="s">
+      <c r="I15" s="51"/>
+      <c r="J15" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="49"/>
-      <c r="L15" s="48" t="s">
+      <c r="K15" s="51"/>
+      <c r="L15" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="M15" s="49"/>
+      <c r="M15" s="51"/>
       <c r="AA15" s="29" t="s">
         <v>39</v>
       </c>
@@ -9192,7 +9198,7 @@
       <c r="CA15" s="30"/>
       <c r="CB15" s="30"/>
     </row>
-    <row r="16" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:80" x14ac:dyDescent="0.35">
       <c r="B16" s="25" t="s">
         <v>16</v>
       </c>
@@ -9286,24 +9292,24 @@
       <c r="CA16" s="34"/>
       <c r="CB16" s="34"/>
     </row>
-    <row r="17" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:80" x14ac:dyDescent="0.35">
       <c r="B17" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="36">
-        <v>0.77429999999999999</v>
+      <c r="C17" s="36" t="s">
+        <v>49</v>
       </c>
       <c r="D17" s="30">
-        <v>34.29</v>
+        <v>74.77</v>
       </c>
       <c r="E17" s="30">
-        <v>91.9</v>
+        <v>52.9</v>
       </c>
       <c r="F17" s="30">
-        <v>33.64</v>
+        <v>79.37</v>
       </c>
       <c r="G17" s="30">
-        <v>91.83</v>
+        <v>100</v>
       </c>
       <c r="H17" s="30">
         <v>1.08</v>
@@ -9380,22 +9386,22 @@
       <c r="CA17" s="34"/>
       <c r="CB17" s="34"/>
     </row>
-    <row r="18" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:80" x14ac:dyDescent="0.35">
       <c r="B18" s="29" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="C18" s="30"/>
       <c r="D18" s="30">
-        <v>42.38</v>
+        <v>74.209999999999994</v>
       </c>
       <c r="E18" s="30">
-        <v>89.39</v>
+        <v>52.9</v>
       </c>
       <c r="F18" s="30">
-        <v>60.22</v>
+        <v>81.89</v>
       </c>
       <c r="G18" s="30">
-        <v>82.2</v>
+        <v>2.16</v>
       </c>
       <c r="H18" s="30">
         <v>1.86</v>
@@ -9472,22 +9478,22 @@
       <c r="CA18" s="30"/>
       <c r="CB18" s="30"/>
     </row>
-    <row r="19" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:80" x14ac:dyDescent="0.35">
       <c r="B19" s="29" t="s">
         <v>20</v>
       </c>
       <c r="C19" s="34"/>
       <c r="D19" s="34">
-        <v>54.02</v>
+        <v>73.64</v>
       </c>
       <c r="E19" s="34">
-        <v>30.4</v>
+        <v>53.37</v>
       </c>
       <c r="F19" s="34">
-        <v>75.39</v>
+        <v>88.05</v>
       </c>
       <c r="G19" s="34">
-        <v>26.43</v>
+        <v>0.61</v>
       </c>
       <c r="H19" s="34">
         <v>2.44</v>
@@ -9564,22 +9570,22 @@
       <c r="CA19" s="30"/>
       <c r="CB19" s="30"/>
     </row>
-    <row r="20" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:80" x14ac:dyDescent="0.35">
       <c r="B20" s="29" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="34"/>
       <c r="D20" s="34">
-        <v>58.57</v>
+        <v>73.27</v>
       </c>
       <c r="E20" s="34">
-        <v>28.71</v>
+        <v>47.2</v>
       </c>
       <c r="F20" s="34">
-        <v>78.2</v>
+        <v>89.79</v>
       </c>
       <c r="G20" s="34">
-        <v>17.52</v>
+        <v>0.54</v>
       </c>
       <c r="H20" s="34">
         <v>2.82</v>
@@ -9656,22 +9662,22 @@
       <c r="CA20" s="34"/>
       <c r="CB20" s="34"/>
     </row>
-    <row r="21" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:80" x14ac:dyDescent="0.35">
       <c r="B21" s="29" t="s">
         <v>25</v>
       </c>
       <c r="C21" s="30"/>
       <c r="D21" s="30">
-        <v>61.18</v>
+        <v>72.95</v>
       </c>
       <c r="E21" s="30">
-        <v>28.38</v>
+        <v>47.26</v>
       </c>
       <c r="F21" s="30">
-        <v>78.75</v>
+        <v>89.9</v>
       </c>
       <c r="G21" s="30">
-        <v>16.989999999999998</v>
+        <v>0.54</v>
       </c>
       <c r="H21" s="30">
         <v>2.91</v>
@@ -9748,22 +9754,22 @@
       <c r="CA21" s="30"/>
       <c r="CB21" s="30"/>
     </row>
-    <row r="22" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:80" x14ac:dyDescent="0.35">
       <c r="B22" s="29" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="30"/>
       <c r="D22" s="30">
-        <v>63.4</v>
+        <v>73.849999999999994</v>
       </c>
       <c r="E22" s="30">
-        <v>27.09</v>
+        <v>33.659999999999997</v>
       </c>
       <c r="F22" s="35">
-        <v>80.95</v>
+        <v>90.08</v>
       </c>
       <c r="G22" s="30">
-        <v>14.95</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H22" s="30">
         <v>3.33</v>
@@ -9836,22 +9842,22 @@
       <c r="CA22" s="30"/>
       <c r="CB22" s="30"/>
     </row>
-    <row r="23" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:80" x14ac:dyDescent="0.35">
       <c r="B23" s="29" t="s">
         <v>30</v>
       </c>
       <c r="C23" s="34"/>
       <c r="D23" s="34">
-        <v>64.28</v>
+        <v>74.3</v>
       </c>
       <c r="E23" s="34">
-        <v>26.47</v>
+        <v>29.93</v>
       </c>
       <c r="F23" s="34">
-        <v>82</v>
+        <v>89.98</v>
       </c>
       <c r="G23" s="34">
-        <v>14.28</v>
+        <v>0.62</v>
       </c>
       <c r="H23" s="34">
         <v>3.58</v>
@@ -9928,22 +9934,22 @@
       <c r="CA23" s="30"/>
       <c r="CB23" s="30"/>
     </row>
-    <row r="24" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:80" x14ac:dyDescent="0.35">
       <c r="B24" s="29" t="s">
         <v>26</v>
       </c>
       <c r="C24" s="30"/>
       <c r="D24" s="30">
-        <v>65.13</v>
+        <v>74.650000000000006</v>
       </c>
       <c r="E24" s="30">
-        <v>25.89</v>
+        <v>27.46</v>
       </c>
       <c r="F24" s="30">
-        <v>82.96</v>
+        <v>89.67</v>
       </c>
       <c r="G24" s="30">
-        <v>10.92</v>
+        <v>0.68</v>
       </c>
       <c r="H24" s="30">
         <v>3.84</v>
@@ -10052,22 +10058,22 @@
         <v>25.74</v>
       </c>
     </row>
-    <row r="25" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:80" x14ac:dyDescent="0.35">
       <c r="B25" s="29" t="s">
         <v>22</v>
       </c>
       <c r="C25" s="30"/>
       <c r="D25" s="30">
-        <v>67.64</v>
+        <v>75.36</v>
       </c>
       <c r="E25" s="30">
-        <v>24.34</v>
+        <v>23.22</v>
       </c>
       <c r="F25">
-        <v>85.28</v>
+        <v>84.83</v>
       </c>
       <c r="G25" s="30">
-        <v>11.74</v>
+        <v>100</v>
       </c>
       <c r="H25" s="30">
         <v>4.7699999999999996</v>
@@ -10177,22 +10183,22 @@
         <v>22.59</v>
       </c>
     </row>
-    <row r="26" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:80" x14ac:dyDescent="0.35">
       <c r="B26" s="29" t="s">
         <v>23</v>
       </c>
       <c r="C26" s="30"/>
       <c r="D26" s="30">
-        <v>75.12</v>
+        <v>79.150000000000006</v>
       </c>
       <c r="E26" s="30">
-        <v>9.82</v>
+        <v>11.57</v>
       </c>
       <c r="F26" s="30">
-        <v>88.12</v>
+        <v>72.66</v>
       </c>
       <c r="G26" s="30">
-        <v>12.57</v>
+        <v>100</v>
       </c>
       <c r="H26" s="30">
         <v>6.37</v>
@@ -10269,22 +10275,22 @@
       <c r="CA26" s="30"/>
       <c r="CB26" s="30"/>
     </row>
-    <row r="27" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:80" x14ac:dyDescent="0.35">
       <c r="B27" s="29" t="s">
         <v>31</v>
       </c>
       <c r="C27" s="30"/>
       <c r="D27" s="30">
-        <v>79.900000000000006</v>
+        <v>83.99</v>
       </c>
       <c r="E27" s="30">
-        <v>6.72</v>
+        <v>4.24</v>
       </c>
       <c r="F27" s="30">
-        <v>90.94</v>
+        <v>63.45</v>
       </c>
       <c r="G27" s="30">
-        <v>15.04</v>
+        <v>100</v>
       </c>
       <c r="H27" s="30">
         <v>7.68</v>
@@ -10393,22 +10399,22 @@
         <v>64.8</v>
       </c>
     </row>
-    <row r="28" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:80" x14ac:dyDescent="0.35">
       <c r="B28" s="29" t="s">
         <v>40</v>
       </c>
       <c r="C28" s="30"/>
       <c r="D28" s="30">
-        <v>82.66</v>
+        <v>84.35</v>
       </c>
       <c r="E28" s="30">
-        <v>4.93</v>
+        <v>3.64</v>
       </c>
       <c r="F28" s="30">
-        <v>91</v>
+        <v>56.31</v>
       </c>
       <c r="G28" s="30">
-        <v>16.91</v>
+        <v>100</v>
       </c>
       <c r="H28" s="30">
         <v>7.94</v>
@@ -10485,22 +10491,22 @@
       <c r="CA28" s="30"/>
       <c r="CB28" s="30"/>
     </row>
-    <row r="29" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:80" x14ac:dyDescent="0.35">
       <c r="B29" s="29" t="s">
         <v>27</v>
       </c>
       <c r="C29" s="30"/>
       <c r="D29" s="30">
-        <v>83.9</v>
+        <v>84.2</v>
       </c>
       <c r="E29" s="30">
-        <v>3.91</v>
+        <v>3.52</v>
       </c>
       <c r="F29" s="30">
-        <v>91.17</v>
+        <v>51.7</v>
       </c>
       <c r="G29" s="30">
-        <v>17.68</v>
+        <v>100</v>
       </c>
       <c r="H29" s="30">
         <v>7.97</v>
@@ -10609,22 +10615,22 @@
         <v>93.76</v>
       </c>
     </row>
-    <row r="30" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:80" x14ac:dyDescent="0.35">
       <c r="B30" s="29" t="s">
         <v>32</v>
       </c>
       <c r="C30" s="30"/>
       <c r="D30" s="30">
-        <v>84.85</v>
+        <v>83.5</v>
       </c>
       <c r="E30" s="30">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="F30" s="30">
-        <v>91.29</v>
+        <v>45.62</v>
       </c>
       <c r="G30" s="30">
-        <v>19.440000000000001</v>
+        <v>100</v>
       </c>
       <c r="H30" s="30">
         <v>7.91</v>
@@ -10733,22 +10739,22 @@
         <v>93.93</v>
       </c>
     </row>
-    <row r="31" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:80" x14ac:dyDescent="0.35">
       <c r="B31" s="29" t="s">
         <v>28</v>
       </c>
       <c r="C31" s="30"/>
       <c r="D31" s="30">
-        <v>85.12</v>
+        <v>82.83</v>
       </c>
       <c r="E31" s="30">
-        <v>2.97</v>
+        <v>3.73</v>
       </c>
       <c r="F31" s="30">
-        <v>91.31</v>
+        <v>42.33</v>
       </c>
       <c r="G31" s="30">
-        <v>20.47</v>
+        <v>100</v>
       </c>
       <c r="H31" s="30">
         <v>7.86</v>
@@ -10857,22 +10863,22 @@
         <v>94.03</v>
       </c>
     </row>
-    <row r="32" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:80" x14ac:dyDescent="0.35">
       <c r="B32" s="29" t="s">
         <v>33</v>
       </c>
       <c r="C32" s="30"/>
       <c r="D32" s="30">
-        <v>85.25</v>
+        <v>82.29</v>
       </c>
       <c r="E32" s="30">
-        <v>2.86</v>
+        <v>3.84</v>
       </c>
       <c r="F32" s="30">
-        <v>91.31</v>
+        <v>39.26</v>
       </c>
       <c r="G32" s="30">
-        <v>21.04</v>
+        <v>100</v>
       </c>
       <c r="H32" s="30">
         <v>7.82</v>
@@ -10981,22 +10987,22 @@
         <v>94.09</v>
       </c>
     </row>
-    <row r="33" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:80" x14ac:dyDescent="0.35">
       <c r="B33" s="29" t="s">
         <v>34</v>
       </c>
       <c r="C33" s="30"/>
       <c r="D33" s="30">
-        <v>85.33</v>
+        <v>81.849999999999994</v>
       </c>
       <c r="E33" s="30">
-        <v>2.8</v>
+        <v>3.93</v>
       </c>
       <c r="F33" s="30">
-        <v>91.31</v>
+        <v>37.42</v>
       </c>
       <c r="G33" s="30">
-        <v>21.37</v>
+        <v>100</v>
       </c>
       <c r="H33" s="30">
         <v>7.79</v>
@@ -11105,22 +11111,22 @@
         <v>94.13</v>
       </c>
     </row>
-    <row r="34" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:80" x14ac:dyDescent="0.35">
       <c r="B34" s="29" t="s">
         <v>35</v>
       </c>
       <c r="C34" s="30"/>
       <c r="D34" s="30">
-        <v>85.38</v>
+        <v>81.5</v>
       </c>
       <c r="E34" s="30">
-        <v>2.76</v>
+        <v>4</v>
       </c>
       <c r="F34" s="30">
-        <v>91.3</v>
+        <v>36.72</v>
       </c>
       <c r="G34" s="30">
-        <v>21.52</v>
+        <v>100</v>
       </c>
       <c r="H34" s="30">
         <v>7.77</v>
@@ -11229,22 +11235,22 @@
         <v>94.16</v>
       </c>
     </row>
-    <row r="35" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B35" s="29" t="s">
         <v>36</v>
       </c>
       <c r="C35" s="30"/>
       <c r="D35" s="30">
-        <v>85.42</v>
+        <v>81.2</v>
       </c>
       <c r="E35" s="30">
-        <v>2.73</v>
+        <v>4.07</v>
       </c>
       <c r="F35" s="30">
-        <v>91.3</v>
+        <v>36.28</v>
       </c>
       <c r="G35" s="30">
-        <v>21.62</v>
+        <v>100</v>
       </c>
       <c r="H35" s="30">
         <v>7.76</v>
@@ -11317,22 +11323,22 @@
       <c r="CA35" s="38"/>
       <c r="CB35" s="39"/>
     </row>
-    <row r="36" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:80" x14ac:dyDescent="0.35">
       <c r="B36" s="29" t="s">
         <v>37</v>
       </c>
       <c r="C36" s="30"/>
       <c r="D36" s="30">
-        <v>85.45</v>
+        <v>80.95</v>
       </c>
       <c r="E36" s="30">
-        <v>2.7</v>
+        <v>4.12</v>
       </c>
       <c r="F36" s="30">
-        <v>91.3</v>
+        <v>35.979999999999997</v>
       </c>
       <c r="G36" s="30">
-        <v>21.75</v>
+        <v>100</v>
       </c>
       <c r="H36" s="30">
         <v>7.75</v>
@@ -11353,22 +11359,22 @@
         <v>41.32</v>
       </c>
     </row>
-    <row r="37" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:80" x14ac:dyDescent="0.35">
       <c r="B37" s="29" t="s">
         <v>38</v>
       </c>
       <c r="C37" s="30"/>
       <c r="D37" s="30">
-        <v>85.47</v>
+        <v>80.7</v>
       </c>
       <c r="E37" s="30">
-        <v>2.68</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="F37" s="37">
-        <v>91.29</v>
+        <v>35.75</v>
       </c>
       <c r="G37" s="30">
-        <v>21.84</v>
+        <v>100</v>
       </c>
       <c r="H37" s="30">
         <v>7.74</v>
@@ -11389,7 +11395,7 @@
         <v>41.43</v>
       </c>
     </row>
-    <row r="38" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C38" s="23" t="s">
         <v>17</v>
       </c>
@@ -11406,11 +11412,84 @@
     </row>
   </sheetData>
   <mergeCells count="91">
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="BS35:BT35"/>
+    <mergeCell ref="BU35:BV35"/>
+    <mergeCell ref="BW35:BX35"/>
+    <mergeCell ref="BY35:BZ35"/>
+    <mergeCell ref="CA35:CB35"/>
+    <mergeCell ref="BQ5:BQ8"/>
+    <mergeCell ref="BQ11:CB11"/>
+    <mergeCell ref="BS12:BT12"/>
+    <mergeCell ref="BU12:BV12"/>
+    <mergeCell ref="BW12:BX12"/>
+    <mergeCell ref="BY12:BZ12"/>
+    <mergeCell ref="CA12:CB12"/>
+    <mergeCell ref="BQ2:CB2"/>
+    <mergeCell ref="BS3:BT3"/>
+    <mergeCell ref="BU3:BV3"/>
+    <mergeCell ref="BW3:BX3"/>
+    <mergeCell ref="BY3:BZ3"/>
+    <mergeCell ref="CA3:CB3"/>
+    <mergeCell ref="BE35:BF35"/>
+    <mergeCell ref="BG35:BH35"/>
+    <mergeCell ref="BI35:BJ35"/>
+    <mergeCell ref="BK35:BL35"/>
+    <mergeCell ref="BM35:BN35"/>
+    <mergeCell ref="BC5:BC8"/>
+    <mergeCell ref="BC11:BN11"/>
+    <mergeCell ref="BE12:BF12"/>
+    <mergeCell ref="BG12:BH12"/>
+    <mergeCell ref="BI12:BJ12"/>
+    <mergeCell ref="BK12:BL12"/>
+    <mergeCell ref="BM12:BN12"/>
+    <mergeCell ref="BC2:BN2"/>
+    <mergeCell ref="BE3:BF3"/>
+    <mergeCell ref="BG3:BH3"/>
+    <mergeCell ref="BI3:BJ3"/>
+    <mergeCell ref="BK3:BL3"/>
+    <mergeCell ref="BM3:BN3"/>
+    <mergeCell ref="AQ35:AR35"/>
+    <mergeCell ref="AS35:AT35"/>
+    <mergeCell ref="AU35:AV35"/>
+    <mergeCell ref="AW35:AX35"/>
+    <mergeCell ref="AY35:AZ35"/>
+    <mergeCell ref="AO5:AO8"/>
+    <mergeCell ref="AO11:AZ11"/>
+    <mergeCell ref="AQ12:AR12"/>
+    <mergeCell ref="AS12:AT12"/>
+    <mergeCell ref="AU12:AV12"/>
+    <mergeCell ref="AW12:AX12"/>
+    <mergeCell ref="AY12:AZ12"/>
+    <mergeCell ref="AO2:AZ2"/>
+    <mergeCell ref="AQ3:AR3"/>
+    <mergeCell ref="AS3:AT3"/>
+    <mergeCell ref="AU3:AV3"/>
+    <mergeCell ref="AW3:AX3"/>
+    <mergeCell ref="AY3:AZ3"/>
+    <mergeCell ref="AC35:AD35"/>
+    <mergeCell ref="AE35:AF35"/>
+    <mergeCell ref="AG35:AH35"/>
+    <mergeCell ref="AI35:AJ35"/>
+    <mergeCell ref="AK35:AL35"/>
+    <mergeCell ref="AA5:AA8"/>
+    <mergeCell ref="AA11:AL11"/>
+    <mergeCell ref="AC12:AD12"/>
+    <mergeCell ref="AE12:AF12"/>
+    <mergeCell ref="AG12:AH12"/>
+    <mergeCell ref="AI12:AJ12"/>
+    <mergeCell ref="AK12:AL12"/>
+    <mergeCell ref="AA2:AL2"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="AG3:AH3"/>
+    <mergeCell ref="AI3:AJ3"/>
+    <mergeCell ref="AK3:AL3"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="B14:M14"/>
@@ -11419,84 +11498,11 @@
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="J15:K15"/>
     <mergeCell ref="L15:M15"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="AA2:AL2"/>
-    <mergeCell ref="AC3:AD3"/>
-    <mergeCell ref="AE3:AF3"/>
-    <mergeCell ref="AG3:AH3"/>
-    <mergeCell ref="AI3:AJ3"/>
-    <mergeCell ref="AK3:AL3"/>
-    <mergeCell ref="AA5:AA8"/>
-    <mergeCell ref="AA11:AL11"/>
-    <mergeCell ref="AC12:AD12"/>
-    <mergeCell ref="AE12:AF12"/>
-    <mergeCell ref="AG12:AH12"/>
-    <mergeCell ref="AI12:AJ12"/>
-    <mergeCell ref="AK12:AL12"/>
-    <mergeCell ref="AC35:AD35"/>
-    <mergeCell ref="AE35:AF35"/>
-    <mergeCell ref="AG35:AH35"/>
-    <mergeCell ref="AI35:AJ35"/>
-    <mergeCell ref="AK35:AL35"/>
-    <mergeCell ref="AO2:AZ2"/>
-    <mergeCell ref="AQ3:AR3"/>
-    <mergeCell ref="AS3:AT3"/>
-    <mergeCell ref="AU3:AV3"/>
-    <mergeCell ref="AW3:AX3"/>
-    <mergeCell ref="AY3:AZ3"/>
-    <mergeCell ref="AO5:AO8"/>
-    <mergeCell ref="AO11:AZ11"/>
-    <mergeCell ref="AQ12:AR12"/>
-    <mergeCell ref="AS12:AT12"/>
-    <mergeCell ref="AU12:AV12"/>
-    <mergeCell ref="AW12:AX12"/>
-    <mergeCell ref="AY12:AZ12"/>
-    <mergeCell ref="AQ35:AR35"/>
-    <mergeCell ref="AS35:AT35"/>
-    <mergeCell ref="AU35:AV35"/>
-    <mergeCell ref="AW35:AX35"/>
-    <mergeCell ref="AY35:AZ35"/>
-    <mergeCell ref="BC2:BN2"/>
-    <mergeCell ref="BE3:BF3"/>
-    <mergeCell ref="BG3:BH3"/>
-    <mergeCell ref="BI3:BJ3"/>
-    <mergeCell ref="BK3:BL3"/>
-    <mergeCell ref="BM3:BN3"/>
-    <mergeCell ref="BC5:BC8"/>
-    <mergeCell ref="BC11:BN11"/>
-    <mergeCell ref="BE12:BF12"/>
-    <mergeCell ref="BG12:BH12"/>
-    <mergeCell ref="BI12:BJ12"/>
-    <mergeCell ref="BK12:BL12"/>
-    <mergeCell ref="BM12:BN12"/>
-    <mergeCell ref="BE35:BF35"/>
-    <mergeCell ref="BG35:BH35"/>
-    <mergeCell ref="BI35:BJ35"/>
-    <mergeCell ref="BK35:BL35"/>
-    <mergeCell ref="BM35:BN35"/>
-    <mergeCell ref="BQ2:CB2"/>
-    <mergeCell ref="BS3:BT3"/>
-    <mergeCell ref="BU3:BV3"/>
-    <mergeCell ref="BW3:BX3"/>
-    <mergeCell ref="BY3:BZ3"/>
-    <mergeCell ref="CA3:CB3"/>
-    <mergeCell ref="BQ5:BQ8"/>
-    <mergeCell ref="BQ11:CB11"/>
-    <mergeCell ref="BS12:BT12"/>
-    <mergeCell ref="BU12:BV12"/>
-    <mergeCell ref="BW12:BX12"/>
-    <mergeCell ref="BY12:BZ12"/>
-    <mergeCell ref="CA12:CB12"/>
-    <mergeCell ref="BS35:BT35"/>
-    <mergeCell ref="BU35:BV35"/>
-    <mergeCell ref="BW35:BX35"/>
-    <mergeCell ref="BY35:BZ35"/>
-    <mergeCell ref="CA35:CB35"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="L38:M38"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Results_metrics.xlsx
+++ b/Results_metrics.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gaiac\Desktop\polito\machine learning\MaskArchitectureAnomaly_CourseProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cgarg\Desktop\MaskArchitectureAnomaly_CourseProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E140A3-96B4-4D03-8875-7623017B2363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C23A27A-5209-46DD-876E-338BD132D2BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -727,16 +727,10 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -762,6 +756,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7761,198 +7761,198 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:CB38"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7890625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="14.453125" customWidth="1"/>
-    <col min="3" max="3" width="13.08984375" customWidth="1"/>
+    <col min="2" max="2" width="14.47265625" customWidth="1"/>
+    <col min="3" max="3" width="13.1015625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="47" t="s">
+    <row r="1" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="2" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B2" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="53"/>
-      <c r="AA2" s="47" t="s">
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="51"/>
+      <c r="AA2" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="AB2" s="52"/>
-      <c r="AC2" s="52"/>
-      <c r="AD2" s="52"/>
-      <c r="AE2" s="52"/>
-      <c r="AF2" s="52"/>
-      <c r="AG2" s="52"/>
-      <c r="AH2" s="52"/>
-      <c r="AI2" s="52"/>
-      <c r="AJ2" s="52"/>
-      <c r="AK2" s="52"/>
-      <c r="AL2" s="53"/>
-      <c r="AO2" s="47" t="s">
+      <c r="AB2" s="50"/>
+      <c r="AC2" s="50"/>
+      <c r="AD2" s="50"/>
+      <c r="AE2" s="50"/>
+      <c r="AF2" s="50"/>
+      <c r="AG2" s="50"/>
+      <c r="AH2" s="50"/>
+      <c r="AI2" s="50"/>
+      <c r="AJ2" s="50"/>
+      <c r="AK2" s="50"/>
+      <c r="AL2" s="51"/>
+      <c r="AO2" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AP2" s="52"/>
-      <c r="AQ2" s="52"/>
-      <c r="AR2" s="52"/>
-      <c r="AS2" s="52"/>
-      <c r="AT2" s="52"/>
-      <c r="AU2" s="52"/>
-      <c r="AV2" s="52"/>
-      <c r="AW2" s="52"/>
-      <c r="AX2" s="52"/>
-      <c r="AY2" s="52"/>
-      <c r="AZ2" s="53"/>
-      <c r="BC2" s="47" t="s">
+      <c r="AP2" s="50"/>
+      <c r="AQ2" s="50"/>
+      <c r="AR2" s="50"/>
+      <c r="AS2" s="50"/>
+      <c r="AT2" s="50"/>
+      <c r="AU2" s="50"/>
+      <c r="AV2" s="50"/>
+      <c r="AW2" s="50"/>
+      <c r="AX2" s="50"/>
+      <c r="AY2" s="50"/>
+      <c r="AZ2" s="51"/>
+      <c r="BC2" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="BD2" s="52"/>
-      <c r="BE2" s="52"/>
-      <c r="BF2" s="52"/>
-      <c r="BG2" s="52"/>
-      <c r="BH2" s="52"/>
-      <c r="BI2" s="52"/>
-      <c r="BJ2" s="52"/>
-      <c r="BK2" s="52"/>
-      <c r="BL2" s="52"/>
-      <c r="BM2" s="52"/>
-      <c r="BN2" s="53"/>
-      <c r="BQ2" s="47" t="s">
+      <c r="BD2" s="50"/>
+      <c r="BE2" s="50"/>
+      <c r="BF2" s="50"/>
+      <c r="BG2" s="50"/>
+      <c r="BH2" s="50"/>
+      <c r="BI2" s="50"/>
+      <c r="BJ2" s="50"/>
+      <c r="BK2" s="50"/>
+      <c r="BL2" s="50"/>
+      <c r="BM2" s="50"/>
+      <c r="BN2" s="51"/>
+      <c r="BQ2" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="BR2" s="52"/>
-      <c r="BS2" s="52"/>
-      <c r="BT2" s="52"/>
-      <c r="BU2" s="52"/>
-      <c r="BV2" s="52"/>
-      <c r="BW2" s="52"/>
-      <c r="BX2" s="52"/>
-      <c r="BY2" s="52"/>
-      <c r="BZ2" s="52"/>
-      <c r="CA2" s="52"/>
-      <c r="CB2" s="53"/>
+      <c r="BR2" s="50"/>
+      <c r="BS2" s="50"/>
+      <c r="BT2" s="50"/>
+      <c r="BU2" s="50"/>
+      <c r="BV2" s="50"/>
+      <c r="BW2" s="50"/>
+      <c r="BX2" s="50"/>
+      <c r="BY2" s="50"/>
+      <c r="BZ2" s="50"/>
+      <c r="CA2" s="50"/>
+      <c r="CB2" s="51"/>
     </row>
-    <row r="3" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B3" s="1"/>
       <c r="C3" s="5"/>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50" t="s">
+      <c r="E3" s="49"/>
+      <c r="F3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="51"/>
-      <c r="H3" s="50" t="s">
+      <c r="G3" s="49"/>
+      <c r="H3" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="51"/>
-      <c r="J3" s="50" t="s">
+      <c r="I3" s="49"/>
+      <c r="J3" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="51"/>
-      <c r="L3" s="50" t="s">
+      <c r="K3" s="49"/>
+      <c r="L3" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="51"/>
+      <c r="M3" s="49"/>
       <c r="AA3" s="1"/>
       <c r="AB3" s="5"/>
-      <c r="AC3" s="50" t="s">
+      <c r="AC3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="AD3" s="51"/>
-      <c r="AE3" s="50" t="s">
+      <c r="AD3" s="49"/>
+      <c r="AE3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="AF3" s="51"/>
-      <c r="AG3" s="50" t="s">
+      <c r="AF3" s="49"/>
+      <c r="AG3" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="AH3" s="51"/>
-      <c r="AI3" s="50" t="s">
+      <c r="AH3" s="49"/>
+      <c r="AI3" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="AJ3" s="51"/>
-      <c r="AK3" s="50" t="s">
+      <c r="AJ3" s="49"/>
+      <c r="AK3" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="51"/>
+      <c r="AL3" s="49"/>
       <c r="AO3" s="1"/>
       <c r="AP3" s="5"/>
-      <c r="AQ3" s="50" t="s">
+      <c r="AQ3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="AR3" s="51"/>
-      <c r="AS3" s="50" t="s">
+      <c r="AR3" s="49"/>
+      <c r="AS3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="AT3" s="51"/>
-      <c r="AU3" s="50" t="s">
+      <c r="AT3" s="49"/>
+      <c r="AU3" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="AV3" s="51"/>
-      <c r="AW3" s="50" t="s">
+      <c r="AV3" s="49"/>
+      <c r="AW3" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="AX3" s="51"/>
-      <c r="AY3" s="50" t="s">
+      <c r="AX3" s="49"/>
+      <c r="AY3" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="AZ3" s="51"/>
+      <c r="AZ3" s="49"/>
       <c r="BC3" s="1"/>
       <c r="BD3" s="5"/>
-      <c r="BE3" s="50" t="s">
+      <c r="BE3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="BF3" s="51"/>
-      <c r="BG3" s="50" t="s">
+      <c r="BF3" s="49"/>
+      <c r="BG3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="BH3" s="51"/>
-      <c r="BI3" s="50" t="s">
+      <c r="BH3" s="49"/>
+      <c r="BI3" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="BJ3" s="51"/>
-      <c r="BK3" s="50" t="s">
+      <c r="BJ3" s="49"/>
+      <c r="BK3" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="BL3" s="51"/>
-      <c r="BM3" s="50" t="s">
+      <c r="BL3" s="49"/>
+      <c r="BM3" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="BN3" s="51"/>
+      <c r="BN3" s="49"/>
       <c r="BQ3" s="1"/>
       <c r="BR3" s="5"/>
-      <c r="BS3" s="50" t="s">
+      <c r="BS3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="BT3" s="51"/>
-      <c r="BU3" s="50" t="s">
+      <c r="BT3" s="49"/>
+      <c r="BU3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="BV3" s="51"/>
-      <c r="BW3" s="50" t="s">
+      <c r="BV3" s="49"/>
+      <c r="BW3" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="BX3" s="51"/>
-      <c r="BY3" s="50" t="s">
+      <c r="BX3" s="49"/>
+      <c r="BY3" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="BZ3" s="51"/>
-      <c r="CA3" s="50" t="s">
+      <c r="BZ3" s="49"/>
+      <c r="CA3" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="CB3" s="51"/>
+      <c r="CB3" s="49"/>
     </row>
-    <row r="4" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B4" s="6" t="s">
         <v>0</v>
       </c>
@@ -8134,8 +8134,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:80" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="42" t="s">
+    <row r="5" spans="2:80" ht="14.7" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="52" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -8171,7 +8171,7 @@
       <c r="M5" s="14">
         <v>82.58</v>
       </c>
-      <c r="AA5" s="45" t="s">
+      <c r="AA5" s="42" t="s">
         <v>13</v>
       </c>
       <c r="AB5" s="12" t="s">
@@ -8195,7 +8195,7 @@
       <c r="AL5" s="20">
         <v>19.14</v>
       </c>
-      <c r="AO5" s="45" t="s">
+      <c r="AO5" s="42" t="s">
         <v>13</v>
       </c>
       <c r="AP5" s="12" t="s">
@@ -8219,7 +8219,7 @@
       <c r="AZ5" s="20">
         <v>19.829999999999998</v>
       </c>
-      <c r="BC5" s="45" t="s">
+      <c r="BC5" s="42" t="s">
         <v>13</v>
       </c>
       <c r="BD5" s="12" t="s">
@@ -8243,7 +8243,7 @@
       <c r="BN5" s="20">
         <v>20.05</v>
       </c>
-      <c r="BQ5" s="45" t="s">
+      <c r="BQ5" s="42" t="s">
         <v>13</v>
       </c>
       <c r="BR5" s="12" t="s">
@@ -8268,7 +8268,7 @@
         <v>20.92</v>
       </c>
     </row>
-    <row r="6" spans="2:80" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="43"/>
       <c r="C6" s="9" t="s">
         <v>11</v>
@@ -8392,8 +8392,8 @@
         <v>20.92</v>
       </c>
     </row>
-    <row r="7" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="44"/>
+    <row r="7" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="53"/>
       <c r="C7" s="11" t="s">
         <v>12</v>
       </c>
@@ -8516,8 +8516,8 @@
         <v>20.49</v>
       </c>
     </row>
-    <row r="8" spans="2:80" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="45" t="s">
+    <row r="8" spans="2:80" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B8" s="42" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="12" t="s">
@@ -8553,7 +8553,7 @@
       <c r="M8" s="20">
         <v>44.62</v>
       </c>
-      <c r="AA8" s="46"/>
+      <c r="AA8" s="44"/>
       <c r="AB8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8575,7 +8575,7 @@
       <c r="AL8" s="22">
         <v>21.78</v>
       </c>
-      <c r="AO8" s="46"/>
+      <c r="AO8" s="44"/>
       <c r="AP8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8597,7 +8597,7 @@
       <c r="AZ8" s="22">
         <v>19.12</v>
       </c>
-      <c r="BC8" s="46"/>
+      <c r="BC8" s="44"/>
       <c r="BD8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8619,7 +8619,7 @@
       <c r="BN8" s="22">
         <v>19.13</v>
       </c>
-      <c r="BQ8" s="46"/>
+      <c r="BQ8" s="44"/>
       <c r="BR8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8642,7 +8642,7 @@
         <v>19.53</v>
       </c>
     </row>
-    <row r="9" spans="2:80" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="43"/>
       <c r="C9" s="9" t="s">
         <v>11</v>
@@ -8678,7 +8678,7 @@
         <v>19.09</v>
       </c>
     </row>
-    <row r="10" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B10" s="43"/>
       <c r="C10" s="9" t="s">
         <v>12</v>
@@ -8714,8 +8714,8 @@
         <v>44.12</v>
       </c>
     </row>
-    <row r="11" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="46"/>
+    <row r="11" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B11" s="44"/>
       <c r="C11" s="10" t="s">
         <v>14</v>
       </c>
@@ -8749,154 +8749,154 @@
       <c r="M11" s="22">
         <v>17.579999999999998</v>
       </c>
-      <c r="AA11" s="47" t="s">
+      <c r="AA11" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="AB11" s="48"/>
-      <c r="AC11" s="48"/>
-      <c r="AD11" s="48"/>
-      <c r="AE11" s="48"/>
-      <c r="AF11" s="48"/>
-      <c r="AG11" s="48"/>
-      <c r="AH11" s="48"/>
-      <c r="AI11" s="48"/>
-      <c r="AJ11" s="48"/>
-      <c r="AK11" s="48"/>
-      <c r="AL11" s="49"/>
-      <c r="AO11" s="47" t="s">
+      <c r="AB11" s="46"/>
+      <c r="AC11" s="46"/>
+      <c r="AD11" s="46"/>
+      <c r="AE11" s="46"/>
+      <c r="AF11" s="46"/>
+      <c r="AG11" s="46"/>
+      <c r="AH11" s="46"/>
+      <c r="AI11" s="46"/>
+      <c r="AJ11" s="46"/>
+      <c r="AK11" s="46"/>
+      <c r="AL11" s="47"/>
+      <c r="AO11" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="AP11" s="48"/>
-      <c r="AQ11" s="48"/>
-      <c r="AR11" s="48"/>
-      <c r="AS11" s="48"/>
-      <c r="AT11" s="48"/>
-      <c r="AU11" s="48"/>
-      <c r="AV11" s="48"/>
-      <c r="AW11" s="48"/>
-      <c r="AX11" s="48"/>
-      <c r="AY11" s="48"/>
-      <c r="AZ11" s="49"/>
-      <c r="BC11" s="47" t="s">
+      <c r="AP11" s="46"/>
+      <c r="AQ11" s="46"/>
+      <c r="AR11" s="46"/>
+      <c r="AS11" s="46"/>
+      <c r="AT11" s="46"/>
+      <c r="AU11" s="46"/>
+      <c r="AV11" s="46"/>
+      <c r="AW11" s="46"/>
+      <c r="AX11" s="46"/>
+      <c r="AY11" s="46"/>
+      <c r="AZ11" s="47"/>
+      <c r="BC11" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="BD11" s="48"/>
-      <c r="BE11" s="48"/>
-      <c r="BF11" s="48"/>
-      <c r="BG11" s="48"/>
-      <c r="BH11" s="48"/>
-      <c r="BI11" s="48"/>
-      <c r="BJ11" s="48"/>
-      <c r="BK11" s="48"/>
-      <c r="BL11" s="48"/>
-      <c r="BM11" s="48"/>
-      <c r="BN11" s="49"/>
-      <c r="BQ11" s="47" t="s">
+      <c r="BD11" s="46"/>
+      <c r="BE11" s="46"/>
+      <c r="BF11" s="46"/>
+      <c r="BG11" s="46"/>
+      <c r="BH11" s="46"/>
+      <c r="BI11" s="46"/>
+      <c r="BJ11" s="46"/>
+      <c r="BK11" s="46"/>
+      <c r="BL11" s="46"/>
+      <c r="BM11" s="46"/>
+      <c r="BN11" s="47"/>
+      <c r="BQ11" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="BR11" s="48"/>
-      <c r="BS11" s="48"/>
-      <c r="BT11" s="48"/>
-      <c r="BU11" s="48"/>
-      <c r="BV11" s="48"/>
-      <c r="BW11" s="48"/>
-      <c r="BX11" s="48"/>
-      <c r="BY11" s="48"/>
-      <c r="BZ11" s="48"/>
-      <c r="CA11" s="48"/>
-      <c r="CB11" s="49"/>
+      <c r="BR11" s="46"/>
+      <c r="BS11" s="46"/>
+      <c r="BT11" s="46"/>
+      <c r="BU11" s="46"/>
+      <c r="BV11" s="46"/>
+      <c r="BW11" s="46"/>
+      <c r="BX11" s="46"/>
+      <c r="BY11" s="46"/>
+      <c r="BZ11" s="46"/>
+      <c r="CA11" s="46"/>
+      <c r="CB11" s="47"/>
     </row>
-    <row r="12" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="AA12" s="24"/>
       <c r="AB12" s="4"/>
-      <c r="AC12" s="50" t="s">
+      <c r="AC12" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="AD12" s="51"/>
-      <c r="AE12" s="50" t="s">
+      <c r="AD12" s="49"/>
+      <c r="AE12" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="AF12" s="51"/>
-      <c r="AG12" s="50" t="s">
+      <c r="AF12" s="49"/>
+      <c r="AG12" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="AH12" s="51"/>
-      <c r="AI12" s="50" t="s">
+      <c r="AH12" s="49"/>
+      <c r="AI12" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="AJ12" s="51"/>
-      <c r="AK12" s="50" t="s">
+      <c r="AJ12" s="49"/>
+      <c r="AK12" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="AL12" s="51"/>
+      <c r="AL12" s="49"/>
       <c r="AO12" s="24"/>
       <c r="AP12" s="4"/>
-      <c r="AQ12" s="50" t="s">
+      <c r="AQ12" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="AR12" s="51"/>
-      <c r="AS12" s="50" t="s">
+      <c r="AR12" s="49"/>
+      <c r="AS12" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="AT12" s="51"/>
-      <c r="AU12" s="50" t="s">
+      <c r="AT12" s="49"/>
+      <c r="AU12" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="AV12" s="51"/>
-      <c r="AW12" s="50" t="s">
+      <c r="AV12" s="49"/>
+      <c r="AW12" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="AX12" s="51"/>
-      <c r="AY12" s="50" t="s">
+      <c r="AX12" s="49"/>
+      <c r="AY12" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="AZ12" s="51"/>
+      <c r="AZ12" s="49"/>
       <c r="BC12" s="24"/>
       <c r="BD12" s="4"/>
-      <c r="BE12" s="50" t="s">
+      <c r="BE12" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="BF12" s="51"/>
-      <c r="BG12" s="50" t="s">
+      <c r="BF12" s="49"/>
+      <c r="BG12" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="BH12" s="51"/>
-      <c r="BI12" s="50" t="s">
+      <c r="BH12" s="49"/>
+      <c r="BI12" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="BJ12" s="51"/>
-      <c r="BK12" s="50" t="s">
+      <c r="BJ12" s="49"/>
+      <c r="BK12" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="BL12" s="51"/>
-      <c r="BM12" s="50" t="s">
+      <c r="BL12" s="49"/>
+      <c r="BM12" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="BN12" s="51"/>
+      <c r="BN12" s="49"/>
       <c r="BQ12" s="24"/>
       <c r="BR12" s="4"/>
-      <c r="BS12" s="50" t="s">
+      <c r="BS12" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="BT12" s="51"/>
-      <c r="BU12" s="50" t="s">
+      <c r="BT12" s="49"/>
+      <c r="BU12" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="BV12" s="51"/>
-      <c r="BW12" s="50" t="s">
+      <c r="BV12" s="49"/>
+      <c r="BW12" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="BX12" s="51"/>
-      <c r="BY12" s="50" t="s">
+      <c r="BX12" s="49"/>
+      <c r="BY12" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="BZ12" s="51"/>
-      <c r="CA12" s="50" t="s">
+      <c r="BZ12" s="49"/>
+      <c r="CA12" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="CB12" s="51"/>
+      <c r="CB12" s="49"/>
     </row>
-    <row r="13" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="AA13" s="25" t="s">
         <v>16</v>
       </c>
@@ -9042,21 +9042,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="47" t="s">
+    <row r="14" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B14" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="48"/>
-      <c r="L14" s="48"/>
-      <c r="M14" s="49"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="47"/>
       <c r="AA14" s="29" t="s">
         <v>24</v>
       </c>
@@ -9118,29 +9118,29 @@
       <c r="CA14" s="30"/>
       <c r="CB14" s="30"/>
     </row>
-    <row r="15" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B15" s="24"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="50" t="s">
+      <c r="D15" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="E15" s="51"/>
-      <c r="F15" s="50" t="s">
+      <c r="E15" s="49"/>
+      <c r="F15" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="51"/>
-      <c r="H15" s="50" t="s">
+      <c r="G15" s="49"/>
+      <c r="H15" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="51"/>
-      <c r="J15" s="50" t="s">
+      <c r="I15" s="49"/>
+      <c r="J15" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="51"/>
-      <c r="L15" s="50" t="s">
+      <c r="K15" s="49"/>
+      <c r="L15" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="M15" s="51"/>
+      <c r="M15" s="49"/>
       <c r="AA15" s="29" t="s">
         <v>39</v>
       </c>
@@ -9198,7 +9198,7 @@
       <c r="CA15" s="30"/>
       <c r="CB15" s="30"/>
     </row>
-    <row r="16" spans="2:80" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="25" t="s">
         <v>16</v>
       </c>
@@ -9292,7 +9292,7 @@
       <c r="CA16" s="34"/>
       <c r="CB16" s="34"/>
     </row>
-    <row r="17" spans="2:80" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="29" t="s">
         <v>24</v>
       </c>
@@ -9386,7 +9386,7 @@
       <c r="CA17" s="34"/>
       <c r="CB17" s="34"/>
     </row>
-    <row r="18" spans="2:80" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="29" t="s">
         <v>50</v>
       </c>
@@ -9478,7 +9478,7 @@
       <c r="CA18" s="30"/>
       <c r="CB18" s="30"/>
     </row>
-    <row r="19" spans="2:80" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="29" t="s">
         <v>20</v>
       </c>
@@ -9570,7 +9570,7 @@
       <c r="CA19" s="30"/>
       <c r="CB19" s="30"/>
     </row>
-    <row r="20" spans="2:80" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="29" t="s">
         <v>29</v>
       </c>
@@ -9662,7 +9662,7 @@
       <c r="CA20" s="34"/>
       <c r="CB20" s="34"/>
     </row>
-    <row r="21" spans="2:80" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="29" t="s">
         <v>25</v>
       </c>
@@ -9754,7 +9754,7 @@
       <c r="CA21" s="30"/>
       <c r="CB21" s="30"/>
     </row>
-    <row r="22" spans="2:80" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="29" t="s">
         <v>21</v>
       </c>
@@ -9842,7 +9842,7 @@
       <c r="CA22" s="30"/>
       <c r="CB22" s="30"/>
     </row>
-    <row r="23" spans="2:80" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="29" t="s">
         <v>30</v>
       </c>
@@ -9934,7 +9934,7 @@
       <c r="CA23" s="30"/>
       <c r="CB23" s="30"/>
     </row>
-    <row r="24" spans="2:80" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" s="29" t="s">
         <v>26</v>
       </c>
@@ -10058,7 +10058,7 @@
         <v>25.74</v>
       </c>
     </row>
-    <row r="25" spans="2:80" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="29" t="s">
         <v>22</v>
       </c>
@@ -10183,7 +10183,7 @@
         <v>22.59</v>
       </c>
     </row>
-    <row r="26" spans="2:80" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="29" t="s">
         <v>23</v>
       </c>
@@ -10275,7 +10275,7 @@
       <c r="CA26" s="30"/>
       <c r="CB26" s="30"/>
     </row>
-    <row r="27" spans="2:80" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" s="29" t="s">
         <v>31</v>
       </c>
@@ -10399,7 +10399,7 @@
         <v>64.8</v>
       </c>
     </row>
-    <row r="28" spans="2:80" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="29" t="s">
         <v>40</v>
       </c>
@@ -10491,7 +10491,7 @@
       <c r="CA28" s="30"/>
       <c r="CB28" s="30"/>
     </row>
-    <row r="29" spans="2:80" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="29" t="s">
         <v>27</v>
       </c>
@@ -10615,7 +10615,7 @@
         <v>93.76</v>
       </c>
     </row>
-    <row r="30" spans="2:80" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" s="29" t="s">
         <v>32</v>
       </c>
@@ -10739,7 +10739,7 @@
         <v>93.93</v>
       </c>
     </row>
-    <row r="31" spans="2:80" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" s="29" t="s">
         <v>28</v>
       </c>
@@ -10863,7 +10863,7 @@
         <v>94.03</v>
       </c>
     </row>
-    <row r="32" spans="2:80" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" s="29" t="s">
         <v>33</v>
       </c>
@@ -10987,7 +10987,7 @@
         <v>94.09</v>
       </c>
     </row>
-    <row r="33" spans="2:80" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" s="29" t="s">
         <v>34</v>
       </c>
@@ -11111,7 +11111,7 @@
         <v>94.13</v>
       </c>
     </row>
-    <row r="34" spans="2:80" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" s="29" t="s">
         <v>35</v>
       </c>
@@ -11235,7 +11235,7 @@
         <v>94.16</v>
       </c>
     </row>
-    <row r="35" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B35" s="29" t="s">
         <v>36</v>
       </c>
@@ -11323,7 +11323,7 @@
       <c r="CA35" s="38"/>
       <c r="CB35" s="39"/>
     </row>
-    <row r="36" spans="2:80" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" s="29" t="s">
         <v>37</v>
       </c>
@@ -11359,7 +11359,7 @@
         <v>41.32</v>
       </c>
     </row>
-    <row r="37" spans="2:80" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" s="29" t="s">
         <v>38</v>
       </c>
@@ -11395,11 +11395,13 @@
         <v>41.43</v>
       </c>
     </row>
-    <row r="38" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="C38" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="38"/>
+      <c r="D38" s="38">
+        <v>4</v>
+      </c>
       <c r="E38" s="39"/>
       <c r="F38" s="38"/>
       <c r="G38" s="39"/>
@@ -11412,84 +11414,11 @@
     </row>
   </sheetData>
   <mergeCells count="91">
-    <mergeCell ref="BS35:BT35"/>
-    <mergeCell ref="BU35:BV35"/>
-    <mergeCell ref="BW35:BX35"/>
-    <mergeCell ref="BY35:BZ35"/>
-    <mergeCell ref="CA35:CB35"/>
-    <mergeCell ref="BQ5:BQ8"/>
-    <mergeCell ref="BQ11:CB11"/>
-    <mergeCell ref="BS12:BT12"/>
-    <mergeCell ref="BU12:BV12"/>
-    <mergeCell ref="BW12:BX12"/>
-    <mergeCell ref="BY12:BZ12"/>
-    <mergeCell ref="CA12:CB12"/>
-    <mergeCell ref="BQ2:CB2"/>
-    <mergeCell ref="BS3:BT3"/>
-    <mergeCell ref="BU3:BV3"/>
-    <mergeCell ref="BW3:BX3"/>
-    <mergeCell ref="BY3:BZ3"/>
-    <mergeCell ref="CA3:CB3"/>
-    <mergeCell ref="BE35:BF35"/>
-    <mergeCell ref="BG35:BH35"/>
-    <mergeCell ref="BI35:BJ35"/>
-    <mergeCell ref="BK35:BL35"/>
-    <mergeCell ref="BM35:BN35"/>
-    <mergeCell ref="BC5:BC8"/>
-    <mergeCell ref="BC11:BN11"/>
-    <mergeCell ref="BE12:BF12"/>
-    <mergeCell ref="BG12:BH12"/>
-    <mergeCell ref="BI12:BJ12"/>
-    <mergeCell ref="BK12:BL12"/>
-    <mergeCell ref="BM12:BN12"/>
-    <mergeCell ref="BC2:BN2"/>
-    <mergeCell ref="BE3:BF3"/>
-    <mergeCell ref="BG3:BH3"/>
-    <mergeCell ref="BI3:BJ3"/>
-    <mergeCell ref="BK3:BL3"/>
-    <mergeCell ref="BM3:BN3"/>
-    <mergeCell ref="AQ35:AR35"/>
-    <mergeCell ref="AS35:AT35"/>
-    <mergeCell ref="AU35:AV35"/>
-    <mergeCell ref="AW35:AX35"/>
-    <mergeCell ref="AY35:AZ35"/>
-    <mergeCell ref="AO5:AO8"/>
-    <mergeCell ref="AO11:AZ11"/>
-    <mergeCell ref="AQ12:AR12"/>
-    <mergeCell ref="AS12:AT12"/>
-    <mergeCell ref="AU12:AV12"/>
-    <mergeCell ref="AW12:AX12"/>
-    <mergeCell ref="AY12:AZ12"/>
-    <mergeCell ref="AO2:AZ2"/>
-    <mergeCell ref="AQ3:AR3"/>
-    <mergeCell ref="AS3:AT3"/>
-    <mergeCell ref="AU3:AV3"/>
-    <mergeCell ref="AW3:AX3"/>
-    <mergeCell ref="AY3:AZ3"/>
-    <mergeCell ref="AC35:AD35"/>
-    <mergeCell ref="AE35:AF35"/>
-    <mergeCell ref="AG35:AH35"/>
-    <mergeCell ref="AI35:AJ35"/>
-    <mergeCell ref="AK35:AL35"/>
-    <mergeCell ref="AA5:AA8"/>
-    <mergeCell ref="AA11:AL11"/>
-    <mergeCell ref="AC12:AD12"/>
-    <mergeCell ref="AE12:AF12"/>
-    <mergeCell ref="AG12:AH12"/>
-    <mergeCell ref="AI12:AJ12"/>
-    <mergeCell ref="AK12:AL12"/>
-    <mergeCell ref="AA2:AL2"/>
-    <mergeCell ref="AC3:AD3"/>
-    <mergeCell ref="AE3:AF3"/>
-    <mergeCell ref="AG3:AH3"/>
-    <mergeCell ref="AI3:AJ3"/>
-    <mergeCell ref="AK3:AL3"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="L38:M38"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="B14:M14"/>
@@ -11498,11 +11427,84 @@
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="J15:K15"/>
     <mergeCell ref="L15:M15"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="AA2:AL2"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="AG3:AH3"/>
+    <mergeCell ref="AI3:AJ3"/>
+    <mergeCell ref="AK3:AL3"/>
+    <mergeCell ref="AA5:AA8"/>
+    <mergeCell ref="AA11:AL11"/>
+    <mergeCell ref="AC12:AD12"/>
+    <mergeCell ref="AE12:AF12"/>
+    <mergeCell ref="AG12:AH12"/>
+    <mergeCell ref="AI12:AJ12"/>
+    <mergeCell ref="AK12:AL12"/>
+    <mergeCell ref="AC35:AD35"/>
+    <mergeCell ref="AE35:AF35"/>
+    <mergeCell ref="AG35:AH35"/>
+    <mergeCell ref="AI35:AJ35"/>
+    <mergeCell ref="AK35:AL35"/>
+    <mergeCell ref="AO2:AZ2"/>
+    <mergeCell ref="AQ3:AR3"/>
+    <mergeCell ref="AS3:AT3"/>
+    <mergeCell ref="AU3:AV3"/>
+    <mergeCell ref="AW3:AX3"/>
+    <mergeCell ref="AY3:AZ3"/>
+    <mergeCell ref="AO5:AO8"/>
+    <mergeCell ref="AO11:AZ11"/>
+    <mergeCell ref="AQ12:AR12"/>
+    <mergeCell ref="AS12:AT12"/>
+    <mergeCell ref="AU12:AV12"/>
+    <mergeCell ref="AW12:AX12"/>
+    <mergeCell ref="AY12:AZ12"/>
+    <mergeCell ref="AQ35:AR35"/>
+    <mergeCell ref="AS35:AT35"/>
+    <mergeCell ref="AU35:AV35"/>
+    <mergeCell ref="AW35:AX35"/>
+    <mergeCell ref="AY35:AZ35"/>
+    <mergeCell ref="BC2:BN2"/>
+    <mergeCell ref="BE3:BF3"/>
+    <mergeCell ref="BG3:BH3"/>
+    <mergeCell ref="BI3:BJ3"/>
+    <mergeCell ref="BK3:BL3"/>
+    <mergeCell ref="BM3:BN3"/>
+    <mergeCell ref="BC5:BC8"/>
+    <mergeCell ref="BC11:BN11"/>
+    <mergeCell ref="BE12:BF12"/>
+    <mergeCell ref="BG12:BH12"/>
+    <mergeCell ref="BI12:BJ12"/>
+    <mergeCell ref="BK12:BL12"/>
+    <mergeCell ref="BM12:BN12"/>
+    <mergeCell ref="BE35:BF35"/>
+    <mergeCell ref="BG35:BH35"/>
+    <mergeCell ref="BI35:BJ35"/>
+    <mergeCell ref="BK35:BL35"/>
+    <mergeCell ref="BM35:BN35"/>
+    <mergeCell ref="BQ2:CB2"/>
+    <mergeCell ref="BS3:BT3"/>
+    <mergeCell ref="BU3:BV3"/>
+    <mergeCell ref="BW3:BX3"/>
+    <mergeCell ref="BY3:BZ3"/>
+    <mergeCell ref="CA3:CB3"/>
+    <mergeCell ref="BQ5:BQ8"/>
+    <mergeCell ref="BQ11:CB11"/>
+    <mergeCell ref="BS12:BT12"/>
+    <mergeCell ref="BU12:BV12"/>
+    <mergeCell ref="BW12:BX12"/>
+    <mergeCell ref="BY12:BZ12"/>
+    <mergeCell ref="CA12:CB12"/>
+    <mergeCell ref="BS35:BT35"/>
+    <mergeCell ref="BU35:BV35"/>
+    <mergeCell ref="BW35:BX35"/>
+    <mergeCell ref="BY35:BZ35"/>
+    <mergeCell ref="CA35:CB35"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Results_metrics.xlsx
+++ b/Results_metrics.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cgarg\Desktop\MaskArchitectureAnomaly_CourseProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Enrica\Desktop\Nuovo_ML_Project\MaskArchitectureAnomaly_CourseProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C23A27A-5209-46DD-876E-338BD132D2BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079428C3-2D6C-4630-B9B0-B4192C916057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11232" yWindow="0" windowWidth="11808" windowHeight="12072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -676,7 +676,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
@@ -727,10 +727,16 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -757,12 +763,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -3283,67 +3284,67 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>4.53</c:v>
+                  <c:v>34.51</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.84</c:v>
+                  <c:v>47.33</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.7799999999999994</c:v>
+                  <c:v>52.93</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.56</c:v>
+                  <c:v>54.01</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.6999999999999993</c:v>
+                  <c:v>54.12</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>10.37</c:v>
+                  <c:v>54.46</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>10.78</c:v>
+                  <c:v>54.59</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>11.22</c:v>
+                  <c:v>54.66</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>12.64</c:v>
+                  <c:v>54.68</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>14.55</c:v>
+                  <c:v>54.32</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>15.54</c:v>
+                  <c:v>53.61</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>15.66</c:v>
+                  <c:v>53.44</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>15.69</c:v>
+                  <c:v>53.61</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>15.7</c:v>
+                  <c:v>54.17</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>15.69</c:v>
+                  <c:v>54.55</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>15.69</c:v>
+                  <c:v>54.78</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>15.68</c:v>
+                  <c:v>54.93</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>15.68</c:v>
+                  <c:v>55.02</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>15.68</c:v>
+                  <c:v>55.08</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>15.68</c:v>
+                  <c:v>55.12</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>15.68</c:v>
+                  <c:v>55.15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3471,67 +3472,67 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>93.5</c:v>
+                  <c:v>34.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>90.35</c:v>
+                  <c:v>34.130000000000003</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>74.22</c:v>
+                  <c:v>34.28</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>55.75</c:v>
+                  <c:v>34.32</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>54.31</c:v>
+                  <c:v>34.340000000000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>55.49</c:v>
+                  <c:v>34.69</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>56.77</c:v>
+                  <c:v>35.33</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>56.83</c:v>
+                  <c:v>37.1</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>57.88</c:v>
+                  <c:v>56.82</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>57.56</c:v>
+                  <c:v>73.209999999999994</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>56.61</c:v>
+                  <c:v>73.45</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>56.15</c:v>
+                  <c:v>73.97</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>55.95</c:v>
+                  <c:v>73.09</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>56</c:v>
+                  <c:v>72.709999999999994</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>55.98</c:v>
+                  <c:v>70.14</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>56</c:v>
+                  <c:v>69.540000000000006</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>56.06</c:v>
+                  <c:v>68.540000000000006</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>56.08</c:v>
+                  <c:v>67.91</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>56.12</c:v>
+                  <c:v>66.62</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>56.15</c:v>
+                  <c:v>66.349999999999994</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>56.18</c:v>
+                  <c:v>65.84</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4034,67 +4035,67 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>27.35</c:v>
+                  <c:v>70.22</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>37.5</c:v>
+                  <c:v>73.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>43.75</c:v>
+                  <c:v>74.72</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>47.1</c:v>
+                  <c:v>75.150000000000006</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>47.69</c:v>
+                  <c:v>75.17</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>49.87</c:v>
+                  <c:v>75.16</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>50.73</c:v>
+                  <c:v>75.12</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>51.48</c:v>
+                  <c:v>75.08</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>53.18</c:v>
+                  <c:v>74.91</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>54.85</c:v>
+                  <c:v>74.59</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>56.09</c:v>
+                  <c:v>74.260000000000005</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>56.37</c:v>
+                  <c:v>74.17</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>56.43</c:v>
+                  <c:v>74.16</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>56.45</c:v>
+                  <c:v>74.36</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>56.44</c:v>
+                  <c:v>74.36</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>56.43</c:v>
+                  <c:v>74.3</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>56.42</c:v>
+                  <c:v>74.2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>56.42</c:v>
+                  <c:v>74.11</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>56.42</c:v>
+                  <c:v>74.03</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>56.42</c:v>
+                  <c:v>73.97</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>56.41</c:v>
+                  <c:v>73.91</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4204,67 +4205,67 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>91.26</c:v>
+                  <c:v>25.08</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>80.5</c:v>
+                  <c:v>20.77</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>51.59</c:v>
+                  <c:v>20.66</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46.41</c:v>
+                  <c:v>20.100000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46.21</c:v>
+                  <c:v>20.62</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>44.62</c:v>
+                  <c:v>19.09</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>44.22</c:v>
+                  <c:v>18.010000000000002</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>43.54</c:v>
+                  <c:v>16.82</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>42.69</c:v>
+                  <c:v>14.81</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>41.58</c:v>
+                  <c:v>19.12</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>39.799999999999997</c:v>
+                  <c:v>27.7</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>39.11</c:v>
+                  <c:v>23.92</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>39.43</c:v>
+                  <c:v>21.84</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>40.380000000000003</c:v>
+                  <c:v>17.3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>40.369999999999997</c:v>
+                  <c:v>15.8</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>40.380000000000003</c:v>
+                  <c:v>14.3</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>40.42</c:v>
+                  <c:v>13.86</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>40.479999999999997</c:v>
+                  <c:v>13.66</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>41.14</c:v>
+                  <c:v>13.51</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>41.32</c:v>
+                  <c:v>13.42</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>41.43</c:v>
+                  <c:v>13.38</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7761,198 +7762,198 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:CB38"/>
-  <sheetFormatPr defaultColWidth="8.7890625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.47265625" customWidth="1"/>
-    <col min="3" max="3" width="13.1015625" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="2" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="45" t="s">
+    <row r="1" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="51"/>
-      <c r="AA2" s="45" t="s">
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="53"/>
+      <c r="AA2" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="AB2" s="50"/>
-      <c r="AC2" s="50"/>
-      <c r="AD2" s="50"/>
-      <c r="AE2" s="50"/>
-      <c r="AF2" s="50"/>
-      <c r="AG2" s="50"/>
-      <c r="AH2" s="50"/>
-      <c r="AI2" s="50"/>
-      <c r="AJ2" s="50"/>
-      <c r="AK2" s="50"/>
-      <c r="AL2" s="51"/>
-      <c r="AO2" s="45" t="s">
+      <c r="AB2" s="52"/>
+      <c r="AC2" s="52"/>
+      <c r="AD2" s="52"/>
+      <c r="AE2" s="52"/>
+      <c r="AF2" s="52"/>
+      <c r="AG2" s="52"/>
+      <c r="AH2" s="52"/>
+      <c r="AI2" s="52"/>
+      <c r="AJ2" s="52"/>
+      <c r="AK2" s="52"/>
+      <c r="AL2" s="53"/>
+      <c r="AO2" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="AP2" s="50"/>
-      <c r="AQ2" s="50"/>
-      <c r="AR2" s="50"/>
-      <c r="AS2" s="50"/>
-      <c r="AT2" s="50"/>
-      <c r="AU2" s="50"/>
-      <c r="AV2" s="50"/>
-      <c r="AW2" s="50"/>
-      <c r="AX2" s="50"/>
-      <c r="AY2" s="50"/>
-      <c r="AZ2" s="51"/>
-      <c r="BC2" s="45" t="s">
+      <c r="AP2" s="52"/>
+      <c r="AQ2" s="52"/>
+      <c r="AR2" s="52"/>
+      <c r="AS2" s="52"/>
+      <c r="AT2" s="52"/>
+      <c r="AU2" s="52"/>
+      <c r="AV2" s="52"/>
+      <c r="AW2" s="52"/>
+      <c r="AX2" s="52"/>
+      <c r="AY2" s="52"/>
+      <c r="AZ2" s="53"/>
+      <c r="BC2" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="BD2" s="50"/>
-      <c r="BE2" s="50"/>
-      <c r="BF2" s="50"/>
-      <c r="BG2" s="50"/>
-      <c r="BH2" s="50"/>
-      <c r="BI2" s="50"/>
-      <c r="BJ2" s="50"/>
-      <c r="BK2" s="50"/>
-      <c r="BL2" s="50"/>
-      <c r="BM2" s="50"/>
-      <c r="BN2" s="51"/>
-      <c r="BQ2" s="45" t="s">
+      <c r="BD2" s="52"/>
+      <c r="BE2" s="52"/>
+      <c r="BF2" s="52"/>
+      <c r="BG2" s="52"/>
+      <c r="BH2" s="52"/>
+      <c r="BI2" s="52"/>
+      <c r="BJ2" s="52"/>
+      <c r="BK2" s="52"/>
+      <c r="BL2" s="52"/>
+      <c r="BM2" s="52"/>
+      <c r="BN2" s="53"/>
+      <c r="BQ2" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="BR2" s="50"/>
-      <c r="BS2" s="50"/>
-      <c r="BT2" s="50"/>
-      <c r="BU2" s="50"/>
-      <c r="BV2" s="50"/>
-      <c r="BW2" s="50"/>
-      <c r="BX2" s="50"/>
-      <c r="BY2" s="50"/>
-      <c r="BZ2" s="50"/>
-      <c r="CA2" s="50"/>
-      <c r="CB2" s="51"/>
+      <c r="BR2" s="52"/>
+      <c r="BS2" s="52"/>
+      <c r="BT2" s="52"/>
+      <c r="BU2" s="52"/>
+      <c r="BV2" s="52"/>
+      <c r="BW2" s="52"/>
+      <c r="BX2" s="52"/>
+      <c r="BY2" s="52"/>
+      <c r="BZ2" s="52"/>
+      <c r="CA2" s="52"/>
+      <c r="CB2" s="53"/>
     </row>
-    <row r="3" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
       <c r="C3" s="5"/>
-      <c r="D3" s="48" t="s">
+      <c r="D3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="49"/>
-      <c r="F3" s="48" t="s">
+      <c r="E3" s="51"/>
+      <c r="F3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="49"/>
-      <c r="H3" s="48" t="s">
+      <c r="G3" s="51"/>
+      <c r="H3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="49"/>
-      <c r="J3" s="48" t="s">
+      <c r="I3" s="51"/>
+      <c r="J3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="49"/>
-      <c r="L3" s="48" t="s">
+      <c r="K3" s="51"/>
+      <c r="L3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="49"/>
+      <c r="M3" s="51"/>
       <c r="AA3" s="1"/>
       <c r="AB3" s="5"/>
-      <c r="AC3" s="48" t="s">
+      <c r="AC3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="AD3" s="49"/>
-      <c r="AE3" s="48" t="s">
+      <c r="AD3" s="51"/>
+      <c r="AE3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="AF3" s="49"/>
-      <c r="AG3" s="48" t="s">
+      <c r="AF3" s="51"/>
+      <c r="AG3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="AH3" s="49"/>
-      <c r="AI3" s="48" t="s">
+      <c r="AH3" s="51"/>
+      <c r="AI3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AJ3" s="49"/>
-      <c r="AK3" s="48" t="s">
+      <c r="AJ3" s="51"/>
+      <c r="AK3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="49"/>
+      <c r="AL3" s="51"/>
       <c r="AO3" s="1"/>
       <c r="AP3" s="5"/>
-      <c r="AQ3" s="48" t="s">
+      <c r="AQ3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="AR3" s="49"/>
-      <c r="AS3" s="48" t="s">
+      <c r="AR3" s="51"/>
+      <c r="AS3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="AT3" s="49"/>
-      <c r="AU3" s="48" t="s">
+      <c r="AT3" s="51"/>
+      <c r="AU3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="AV3" s="49"/>
-      <c r="AW3" s="48" t="s">
+      <c r="AV3" s="51"/>
+      <c r="AW3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AX3" s="49"/>
-      <c r="AY3" s="48" t="s">
+      <c r="AX3" s="51"/>
+      <c r="AY3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="AZ3" s="49"/>
+      <c r="AZ3" s="51"/>
       <c r="BC3" s="1"/>
       <c r="BD3" s="5"/>
-      <c r="BE3" s="48" t="s">
+      <c r="BE3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="BF3" s="49"/>
-      <c r="BG3" s="48" t="s">
+      <c r="BF3" s="51"/>
+      <c r="BG3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="BH3" s="49"/>
-      <c r="BI3" s="48" t="s">
+      <c r="BH3" s="51"/>
+      <c r="BI3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="BJ3" s="49"/>
-      <c r="BK3" s="48" t="s">
+      <c r="BJ3" s="51"/>
+      <c r="BK3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="BL3" s="49"/>
-      <c r="BM3" s="48" t="s">
+      <c r="BL3" s="51"/>
+      <c r="BM3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="BN3" s="49"/>
+      <c r="BN3" s="51"/>
       <c r="BQ3" s="1"/>
       <c r="BR3" s="5"/>
-      <c r="BS3" s="48" t="s">
+      <c r="BS3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="BT3" s="49"/>
-      <c r="BU3" s="48" t="s">
+      <c r="BT3" s="51"/>
+      <c r="BU3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="BV3" s="49"/>
-      <c r="BW3" s="48" t="s">
+      <c r="BV3" s="51"/>
+      <c r="BW3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="BX3" s="49"/>
-      <c r="BY3" s="48" t="s">
+      <c r="BX3" s="51"/>
+      <c r="BY3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="BZ3" s="49"/>
-      <c r="CA3" s="48" t="s">
+      <c r="BZ3" s="51"/>
+      <c r="CA3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="CB3" s="49"/>
+      <c r="CB3" s="51"/>
     </row>
-    <row r="4" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="6" t="s">
         <v>0</v>
       </c>
@@ -8134,8 +8135,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:80" ht="14.7" thickTop="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="52" t="s">
+    <row r="5" spans="2:80" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="42" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -8171,7 +8172,7 @@
       <c r="M5" s="14">
         <v>82.58</v>
       </c>
-      <c r="AA5" s="42" t="s">
+      <c r="AA5" s="45" t="s">
         <v>13</v>
       </c>
       <c r="AB5" s="12" t="s">
@@ -8195,7 +8196,7 @@
       <c r="AL5" s="20">
         <v>19.14</v>
       </c>
-      <c r="AO5" s="42" t="s">
+      <c r="AO5" s="45" t="s">
         <v>13</v>
       </c>
       <c r="AP5" s="12" t="s">
@@ -8219,7 +8220,7 @@
       <c r="AZ5" s="20">
         <v>19.829999999999998</v>
       </c>
-      <c r="BC5" s="42" t="s">
+      <c r="BC5" s="45" t="s">
         <v>13</v>
       </c>
       <c r="BD5" s="12" t="s">
@@ -8243,7 +8244,7 @@
       <c r="BN5" s="20">
         <v>20.05</v>
       </c>
-      <c r="BQ5" s="42" t="s">
+      <c r="BQ5" s="45" t="s">
         <v>13</v>
       </c>
       <c r="BR5" s="12" t="s">
@@ -8268,7 +8269,7 @@
         <v>20.92</v>
       </c>
     </row>
-    <row r="6" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B6" s="43"/>
       <c r="C6" s="9" t="s">
         <v>11</v>
@@ -8392,8 +8393,8 @@
         <v>20.92</v>
       </c>
     </row>
-    <row r="7" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="53"/>
+    <row r="7" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="44"/>
       <c r="C7" s="11" t="s">
         <v>12</v>
       </c>
@@ -8516,8 +8517,8 @@
         <v>20.49</v>
       </c>
     </row>
-    <row r="8" spans="2:80" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B8" s="42" t="s">
+    <row r="8" spans="2:80" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="45" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="12" t="s">
@@ -8542,18 +8543,18 @@
         <v>31.26</v>
       </c>
       <c r="J8" s="19">
-        <v>10.37</v>
+        <v>54.1</v>
       </c>
       <c r="K8" s="20">
-        <v>55.49</v>
+        <v>34.57</v>
       </c>
       <c r="L8" s="19">
-        <v>49.87</v>
+        <v>77.260000000000005</v>
       </c>
       <c r="M8" s="20">
-        <v>44.62</v>
-      </c>
-      <c r="AA8" s="44"/>
+        <v>19.09</v>
+      </c>
+      <c r="AA8" s="46"/>
       <c r="AB8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8575,7 +8576,7 @@
       <c r="AL8" s="22">
         <v>21.78</v>
       </c>
-      <c r="AO8" s="44"/>
+      <c r="AO8" s="46"/>
       <c r="AP8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8597,7 +8598,7 @@
       <c r="AZ8" s="22">
         <v>19.12</v>
       </c>
-      <c r="BC8" s="44"/>
+      <c r="BC8" s="46"/>
       <c r="BD8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8619,7 +8620,7 @@
       <c r="BN8" s="22">
         <v>19.13</v>
       </c>
-      <c r="BQ8" s="44"/>
+      <c r="BQ8" s="46"/>
       <c r="BR8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8642,7 +8643,7 @@
         <v>19.53</v>
       </c>
     </row>
-    <row r="9" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B9" s="43"/>
       <c r="C9" s="9" t="s">
         <v>11</v>
@@ -8678,7 +8679,7 @@
         <v>19.09</v>
       </c>
     </row>
-    <row r="10" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="10" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="43"/>
       <c r="C10" s="9" t="s">
         <v>12</v>
@@ -8702,20 +8703,20 @@
         <v>31.27</v>
       </c>
       <c r="J10" s="15">
-        <v>13.74</v>
+        <v>52.74</v>
       </c>
       <c r="K10" s="16">
-        <v>56.77</v>
+        <v>34.82</v>
       </c>
       <c r="L10" s="15">
-        <v>53.55</v>
+        <v>76.69</v>
       </c>
       <c r="M10" s="16">
-        <v>44.12</v>
+        <v>18.829999999999998</v>
       </c>
     </row>
-    <row r="11" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B11" s="44"/>
+    <row r="11" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="46"/>
       <c r="C11" s="10" t="s">
         <v>14</v>
       </c>
@@ -8749,154 +8750,154 @@
       <c r="M11" s="22">
         <v>17.579999999999998</v>
       </c>
-      <c r="AA11" s="45" t="s">
+      <c r="AA11" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="AB11" s="46"/>
-      <c r="AC11" s="46"/>
-      <c r="AD11" s="46"/>
-      <c r="AE11" s="46"/>
-      <c r="AF11" s="46"/>
-      <c r="AG11" s="46"/>
-      <c r="AH11" s="46"/>
-      <c r="AI11" s="46"/>
-      <c r="AJ11" s="46"/>
-      <c r="AK11" s="46"/>
-      <c r="AL11" s="47"/>
-      <c r="AO11" s="45" t="s">
+      <c r="AB11" s="48"/>
+      <c r="AC11" s="48"/>
+      <c r="AD11" s="48"/>
+      <c r="AE11" s="48"/>
+      <c r="AF11" s="48"/>
+      <c r="AG11" s="48"/>
+      <c r="AH11" s="48"/>
+      <c r="AI11" s="48"/>
+      <c r="AJ11" s="48"/>
+      <c r="AK11" s="48"/>
+      <c r="AL11" s="49"/>
+      <c r="AO11" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="AP11" s="46"/>
-      <c r="AQ11" s="46"/>
-      <c r="AR11" s="46"/>
-      <c r="AS11" s="46"/>
-      <c r="AT11" s="46"/>
-      <c r="AU11" s="46"/>
-      <c r="AV11" s="46"/>
-      <c r="AW11" s="46"/>
-      <c r="AX11" s="46"/>
-      <c r="AY11" s="46"/>
-      <c r="AZ11" s="47"/>
-      <c r="BC11" s="45" t="s">
+      <c r="AP11" s="48"/>
+      <c r="AQ11" s="48"/>
+      <c r="AR11" s="48"/>
+      <c r="AS11" s="48"/>
+      <c r="AT11" s="48"/>
+      <c r="AU11" s="48"/>
+      <c r="AV11" s="48"/>
+      <c r="AW11" s="48"/>
+      <c r="AX11" s="48"/>
+      <c r="AY11" s="48"/>
+      <c r="AZ11" s="49"/>
+      <c r="BC11" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="BD11" s="46"/>
-      <c r="BE11" s="46"/>
-      <c r="BF11" s="46"/>
-      <c r="BG11" s="46"/>
-      <c r="BH11" s="46"/>
-      <c r="BI11" s="46"/>
-      <c r="BJ11" s="46"/>
-      <c r="BK11" s="46"/>
-      <c r="BL11" s="46"/>
-      <c r="BM11" s="46"/>
-      <c r="BN11" s="47"/>
-      <c r="BQ11" s="45" t="s">
+      <c r="BD11" s="48"/>
+      <c r="BE11" s="48"/>
+      <c r="BF11" s="48"/>
+      <c r="BG11" s="48"/>
+      <c r="BH11" s="48"/>
+      <c r="BI11" s="48"/>
+      <c r="BJ11" s="48"/>
+      <c r="BK11" s="48"/>
+      <c r="BL11" s="48"/>
+      <c r="BM11" s="48"/>
+      <c r="BN11" s="49"/>
+      <c r="BQ11" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="BR11" s="46"/>
-      <c r="BS11" s="46"/>
-      <c r="BT11" s="46"/>
-      <c r="BU11" s="46"/>
-      <c r="BV11" s="46"/>
-      <c r="BW11" s="46"/>
-      <c r="BX11" s="46"/>
-      <c r="BY11" s="46"/>
-      <c r="BZ11" s="46"/>
-      <c r="CA11" s="46"/>
-      <c r="CB11" s="47"/>
+      <c r="BR11" s="48"/>
+      <c r="BS11" s="48"/>
+      <c r="BT11" s="48"/>
+      <c r="BU11" s="48"/>
+      <c r="BV11" s="48"/>
+      <c r="BW11" s="48"/>
+      <c r="BX11" s="48"/>
+      <c r="BY11" s="48"/>
+      <c r="BZ11" s="48"/>
+      <c r="CA11" s="48"/>
+      <c r="CB11" s="49"/>
     </row>
-    <row r="12" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="12" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="AA12" s="24"/>
       <c r="AB12" s="4"/>
-      <c r="AC12" s="48" t="s">
+      <c r="AC12" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="AD12" s="49"/>
-      <c r="AE12" s="48" t="s">
+      <c r="AD12" s="51"/>
+      <c r="AE12" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="AF12" s="49"/>
-      <c r="AG12" s="48" t="s">
+      <c r="AF12" s="51"/>
+      <c r="AG12" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="AH12" s="49"/>
-      <c r="AI12" s="48" t="s">
+      <c r="AH12" s="51"/>
+      <c r="AI12" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AJ12" s="49"/>
-      <c r="AK12" s="48" t="s">
+      <c r="AJ12" s="51"/>
+      <c r="AK12" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="AL12" s="49"/>
+      <c r="AL12" s="51"/>
       <c r="AO12" s="24"/>
       <c r="AP12" s="4"/>
-      <c r="AQ12" s="48" t="s">
+      <c r="AQ12" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="AR12" s="49"/>
-      <c r="AS12" s="48" t="s">
+      <c r="AR12" s="51"/>
+      <c r="AS12" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="AT12" s="49"/>
-      <c r="AU12" s="48" t="s">
+      <c r="AT12" s="51"/>
+      <c r="AU12" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="AV12" s="49"/>
-      <c r="AW12" s="48" t="s">
+      <c r="AV12" s="51"/>
+      <c r="AW12" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AX12" s="49"/>
-      <c r="AY12" s="48" t="s">
+      <c r="AX12" s="51"/>
+      <c r="AY12" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="AZ12" s="49"/>
+      <c r="AZ12" s="51"/>
       <c r="BC12" s="24"/>
       <c r="BD12" s="4"/>
-      <c r="BE12" s="48" t="s">
+      <c r="BE12" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="BF12" s="49"/>
-      <c r="BG12" s="48" t="s">
+      <c r="BF12" s="51"/>
+      <c r="BG12" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="BH12" s="49"/>
-      <c r="BI12" s="48" t="s">
+      <c r="BH12" s="51"/>
+      <c r="BI12" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="BJ12" s="49"/>
-      <c r="BK12" s="48" t="s">
+      <c r="BJ12" s="51"/>
+      <c r="BK12" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="BL12" s="49"/>
-      <c r="BM12" s="48" t="s">
+      <c r="BL12" s="51"/>
+      <c r="BM12" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="BN12" s="49"/>
+      <c r="BN12" s="51"/>
       <c r="BQ12" s="24"/>
       <c r="BR12" s="4"/>
-      <c r="BS12" s="48" t="s">
+      <c r="BS12" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="BT12" s="49"/>
-      <c r="BU12" s="48" t="s">
+      <c r="BT12" s="51"/>
+      <c r="BU12" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="BV12" s="49"/>
-      <c r="BW12" s="48" t="s">
+      <c r="BV12" s="51"/>
+      <c r="BW12" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="BX12" s="49"/>
-      <c r="BY12" s="48" t="s">
+      <c r="BX12" s="51"/>
+      <c r="BY12" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="BZ12" s="49"/>
-      <c r="CA12" s="48" t="s">
+      <c r="BZ12" s="51"/>
+      <c r="CA12" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="CB12" s="49"/>
+      <c r="CB12" s="51"/>
     </row>
-    <row r="13" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="13" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="AA13" s="25" t="s">
         <v>16</v>
       </c>
@@ -9042,21 +9043,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B14" s="45" t="s">
+    <row r="14" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="47"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="48"/>
+      <c r="M14" s="49"/>
       <c r="AA14" s="29" t="s">
         <v>24</v>
       </c>
@@ -9118,29 +9119,29 @@
       <c r="CA14" s="30"/>
       <c r="CB14" s="30"/>
     </row>
-    <row r="15" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="15" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="24"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="48" t="s">
+      <c r="D15" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="E15" s="49"/>
-      <c r="F15" s="48" t="s">
+      <c r="E15" s="51"/>
+      <c r="F15" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="49"/>
-      <c r="H15" s="48" t="s">
+      <c r="G15" s="51"/>
+      <c r="H15" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="49"/>
-      <c r="J15" s="48" t="s">
+      <c r="I15" s="51"/>
+      <c r="J15" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="49"/>
-      <c r="L15" s="48" t="s">
+      <c r="K15" s="51"/>
+      <c r="L15" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="M15" s="49"/>
+      <c r="M15" s="51"/>
       <c r="AA15" s="29" t="s">
         <v>39</v>
       </c>
@@ -9198,7 +9199,7 @@
       <c r="CA15" s="30"/>
       <c r="CB15" s="30"/>
     </row>
-    <row r="16" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>16</v>
       </c>
@@ -9292,7 +9293,7 @@
       <c r="CA16" s="34"/>
       <c r="CB16" s="34"/>
     </row>
-    <row r="17" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B17" s="29" t="s">
         <v>24</v>
       </c>
@@ -9318,16 +9319,16 @@
         <v>92.89</v>
       </c>
       <c r="J17" s="30">
-        <v>4.53</v>
+        <v>34.51</v>
       </c>
       <c r="K17" s="30">
-        <v>93.5</v>
+        <v>34.1</v>
       </c>
       <c r="L17" s="30">
-        <v>27.35</v>
+        <v>70.22</v>
       </c>
       <c r="M17" s="30">
-        <v>91.26</v>
+        <v>25.08</v>
       </c>
       <c r="AA17" s="29" t="s">
         <v>29</v>
@@ -9386,7 +9387,7 @@
       <c r="CA17" s="34"/>
       <c r="CB17" s="34"/>
     </row>
-    <row r="18" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B18" s="29" t="s">
         <v>50</v>
       </c>
@@ -9410,16 +9411,16 @@
         <v>86.68</v>
       </c>
       <c r="J18" s="30">
-        <v>6.84</v>
+        <v>47.33</v>
       </c>
       <c r="K18" s="30">
-        <v>90.35</v>
+        <v>34.130000000000003</v>
       </c>
       <c r="L18" s="30">
-        <v>37.5</v>
+        <v>73.5</v>
       </c>
       <c r="M18" s="30">
-        <v>80.5</v>
+        <v>20.77</v>
       </c>
       <c r="AA18" s="29" t="s">
         <v>25</v>
@@ -9478,7 +9479,7 @@
       <c r="CA18" s="30"/>
       <c r="CB18" s="30"/>
     </row>
-    <row r="19" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B19" s="29" t="s">
         <v>20</v>
       </c>
@@ -9502,16 +9503,16 @@
         <v>53.79</v>
       </c>
       <c r="J19" s="34">
-        <v>8.7799999999999994</v>
+        <v>52.93</v>
       </c>
       <c r="K19" s="34">
-        <v>74.22</v>
+        <v>34.28</v>
       </c>
       <c r="L19" s="34">
-        <v>43.75</v>
+        <v>74.72</v>
       </c>
       <c r="M19" s="34">
-        <v>51.59</v>
+        <v>20.66</v>
       </c>
       <c r="AA19" s="29" t="s">
         <v>21</v>
@@ -9570,7 +9571,7 @@
       <c r="CA19" s="30"/>
       <c r="CB19" s="30"/>
     </row>
-    <row r="20" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B20" s="29" t="s">
         <v>29</v>
       </c>
@@ -9594,16 +9595,16 @@
         <v>30.87</v>
       </c>
       <c r="J20" s="34">
-        <v>9.56</v>
+        <v>54.01</v>
       </c>
       <c r="K20" s="34">
-        <v>55.75</v>
+        <v>34.32</v>
       </c>
       <c r="L20" s="34">
-        <v>47.1</v>
+        <v>75.150000000000006</v>
       </c>
       <c r="M20" s="34">
-        <v>46.41</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="AA20" s="29" t="s">
         <v>30</v>
@@ -9662,7 +9663,7 @@
       <c r="CA20" s="34"/>
       <c r="CB20" s="34"/>
     </row>
-    <row r="21" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B21" s="29" t="s">
         <v>25</v>
       </c>
@@ -9686,16 +9687,16 @@
         <v>30.88</v>
       </c>
       <c r="J21" s="30">
-        <v>9.6999999999999993</v>
+        <v>54.12</v>
       </c>
       <c r="K21" s="30">
-        <v>54.31</v>
+        <v>34.340000000000003</v>
       </c>
       <c r="L21" s="30">
-        <v>47.69</v>
+        <v>75.17</v>
       </c>
       <c r="M21" s="30">
-        <v>46.21</v>
+        <v>20.62</v>
       </c>
       <c r="AA21" s="29" t="s">
         <v>26</v>
@@ -9754,7 +9755,7 @@
       <c r="CA21" s="30"/>
       <c r="CB21" s="30"/>
     </row>
-    <row r="22" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B22" s="29" t="s">
         <v>21</v>
       </c>
@@ -9778,16 +9779,16 @@
         <v>31.26</v>
       </c>
       <c r="J22" s="30">
-        <v>10.37</v>
+        <v>54.46</v>
       </c>
       <c r="K22" s="30">
-        <v>55.49</v>
+        <v>34.69</v>
       </c>
       <c r="L22" s="30">
-        <v>49.87</v>
+        <v>75.16</v>
       </c>
       <c r="M22" s="30">
-        <v>44.62</v>
+        <v>19.09</v>
       </c>
       <c r="AA22" s="29" t="s">
         <v>22</v>
@@ -9842,7 +9843,7 @@
       <c r="CA22" s="30"/>
       <c r="CB22" s="30"/>
     </row>
-    <row r="23" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B23" s="29" t="s">
         <v>30</v>
       </c>
@@ -9866,16 +9867,16 @@
         <v>31.28</v>
       </c>
       <c r="J23" s="34">
-        <v>10.78</v>
+        <v>54.59</v>
       </c>
       <c r="K23" s="34">
-        <v>56.77</v>
+        <v>35.33</v>
       </c>
       <c r="L23" s="34">
-        <v>50.73</v>
+        <v>75.12</v>
       </c>
       <c r="M23" s="34">
-        <v>44.22</v>
+        <v>18.010000000000002</v>
       </c>
       <c r="AA23" s="29" t="s">
         <v>23</v>
@@ -9934,7 +9935,7 @@
       <c r="CA23" s="30"/>
       <c r="CB23" s="30"/>
     </row>
-    <row r="24" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B24" s="29" t="s">
         <v>26</v>
       </c>
@@ -9958,16 +9959,16 @@
         <v>31.17</v>
       </c>
       <c r="J24" s="30">
-        <v>11.22</v>
+        <v>54.66</v>
       </c>
       <c r="K24" s="30">
-        <v>56.83</v>
+        <v>37.1</v>
       </c>
       <c r="L24" s="30">
-        <v>51.48</v>
+        <v>75.08</v>
       </c>
       <c r="M24" s="30">
-        <v>43.54</v>
+        <v>16.82</v>
       </c>
       <c r="AA24" s="29" t="s">
         <v>31</v>
@@ -10058,7 +10059,7 @@
         <v>25.74</v>
       </c>
     </row>
-    <row r="25" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B25" s="29" t="s">
         <v>22</v>
       </c>
@@ -10082,16 +10083,16 @@
         <v>31.85</v>
       </c>
       <c r="J25" s="30">
-        <v>12.64</v>
+        <v>54.68</v>
       </c>
       <c r="K25" s="30">
-        <v>57.88</v>
+        <v>56.82</v>
       </c>
       <c r="L25" s="30">
-        <v>53.18</v>
+        <v>74.91</v>
       </c>
       <c r="M25" s="30">
-        <v>42.69</v>
+        <v>14.81</v>
       </c>
       <c r="O25" s="33"/>
       <c r="AA25" s="29" t="s">
@@ -10183,7 +10184,7 @@
         <v>22.59</v>
       </c>
     </row>
-    <row r="26" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B26" s="29" t="s">
         <v>23</v>
       </c>
@@ -10207,16 +10208,16 @@
         <v>32.71</v>
       </c>
       <c r="J26" s="30">
-        <v>14.55</v>
+        <v>54.32</v>
       </c>
       <c r="K26" s="30">
-        <v>57.56</v>
+        <v>73.209999999999994</v>
       </c>
       <c r="L26" s="30">
-        <v>54.85</v>
+        <v>74.59</v>
       </c>
       <c r="M26" s="30">
-        <v>41.58</v>
+        <v>19.12</v>
       </c>
       <c r="AA26" s="29" t="s">
         <v>27</v>
@@ -10275,7 +10276,7 @@
       <c r="CA26" s="30"/>
       <c r="CB26" s="30"/>
     </row>
-    <row r="27" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B27" s="29" t="s">
         <v>31</v>
       </c>
@@ -10299,16 +10300,16 @@
         <v>34.82</v>
       </c>
       <c r="J27" s="30">
-        <v>15.54</v>
+        <v>53.61</v>
       </c>
       <c r="K27" s="30">
-        <v>56.61</v>
+        <v>73.45</v>
       </c>
       <c r="L27" s="30">
-        <v>56.09</v>
+        <v>74.260000000000005</v>
       </c>
       <c r="M27" s="30">
-        <v>39.799999999999997</v>
+        <v>27.7</v>
       </c>
       <c r="AA27" s="29" t="s">
         <v>32</v>
@@ -10399,7 +10400,7 @@
         <v>64.8</v>
       </c>
     </row>
-    <row r="28" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B28" s="29" t="s">
         <v>40</v>
       </c>
@@ -10423,16 +10424,16 @@
         <v>34.950000000000003</v>
       </c>
       <c r="J28" s="30">
-        <v>15.66</v>
+        <v>53.44</v>
       </c>
       <c r="K28" s="30">
-        <v>56.15</v>
+        <v>73.97</v>
       </c>
       <c r="L28" s="30">
-        <v>56.37</v>
+        <v>74.17</v>
       </c>
       <c r="M28" s="30">
-        <v>39.11</v>
+        <v>23.92</v>
       </c>
       <c r="AA28" s="29" t="s">
         <v>28</v>
@@ -10491,7 +10492,7 @@
       <c r="CA28" s="30"/>
       <c r="CB28" s="30"/>
     </row>
-    <row r="29" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B29" s="29" t="s">
         <v>27</v>
       </c>
@@ -10515,16 +10516,16 @@
         <v>34.31</v>
       </c>
       <c r="J29" s="30">
-        <v>15.69</v>
+        <v>53.61</v>
       </c>
       <c r="K29" s="30">
-        <v>55.95</v>
+        <v>73.09</v>
       </c>
       <c r="L29" s="30">
-        <v>56.43</v>
+        <v>74.16</v>
       </c>
       <c r="M29" s="30">
-        <v>39.43</v>
+        <v>21.84</v>
       </c>
       <c r="AA29" s="29" t="s">
         <v>33</v>
@@ -10615,7 +10616,7 @@
         <v>93.76</v>
       </c>
     </row>
-    <row r="30" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B30" s="29" t="s">
         <v>32</v>
       </c>
@@ -10639,16 +10640,16 @@
         <v>34.03</v>
       </c>
       <c r="J30" s="30">
-        <v>15.7</v>
+        <v>54.17</v>
       </c>
       <c r="K30" s="30">
-        <v>56</v>
-      </c>
-      <c r="L30" s="30">
-        <v>56.45</v>
-      </c>
-      <c r="M30" s="30">
-        <v>40.380000000000003</v>
+        <v>72.709999999999994</v>
+      </c>
+      <c r="L30" s="54">
+        <v>74.36</v>
+      </c>
+      <c r="M30" s="54">
+        <v>17.3</v>
       </c>
       <c r="AA30" s="29" t="s">
         <v>34</v>
@@ -10739,7 +10740,7 @@
         <v>93.93</v>
       </c>
     </row>
-    <row r="31" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B31" s="29" t="s">
         <v>28</v>
       </c>
@@ -10763,16 +10764,16 @@
         <v>34.380000000000003</v>
       </c>
       <c r="J31" s="30">
-        <v>15.69</v>
+        <v>54.55</v>
       </c>
       <c r="K31" s="30">
-        <v>55.98</v>
+        <v>70.14</v>
       </c>
       <c r="L31" s="30">
-        <v>56.44</v>
+        <v>74.36</v>
       </c>
       <c r="M31" s="30">
-        <v>40.369999999999997</v>
+        <v>15.8</v>
       </c>
       <c r="AA31" s="29" t="s">
         <v>35</v>
@@ -10863,7 +10864,7 @@
         <v>94.03</v>
       </c>
     </row>
-    <row r="32" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B32" s="29" t="s">
         <v>33</v>
       </c>
@@ -10887,16 +10888,16 @@
         <v>34.520000000000003</v>
       </c>
       <c r="J32" s="30">
-        <v>15.69</v>
+        <v>54.78</v>
       </c>
       <c r="K32" s="30">
-        <v>56</v>
+        <v>69.540000000000006</v>
       </c>
       <c r="L32" s="30">
-        <v>56.43</v>
+        <v>74.3</v>
       </c>
       <c r="M32" s="30">
-        <v>40.380000000000003</v>
+        <v>14.3</v>
       </c>
       <c r="AA32" s="29" t="s">
         <v>36</v>
@@ -10987,7 +10988,7 @@
         <v>94.09</v>
       </c>
     </row>
-    <row r="33" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B33" s="29" t="s">
         <v>34</v>
       </c>
@@ -11011,16 +11012,16 @@
         <v>34.729999999999997</v>
       </c>
       <c r="J33" s="30">
-        <v>15.68</v>
+        <v>54.93</v>
       </c>
       <c r="K33" s="30">
-        <v>56.06</v>
+        <v>68.540000000000006</v>
       </c>
       <c r="L33" s="30">
-        <v>56.42</v>
+        <v>74.2</v>
       </c>
       <c r="M33" s="30">
-        <v>40.42</v>
+        <v>13.86</v>
       </c>
       <c r="AA33" s="29" t="s">
         <v>37</v>
@@ -11111,7 +11112,7 @@
         <v>94.13</v>
       </c>
     </row>
-    <row r="34" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B34" s="29" t="s">
         <v>35</v>
       </c>
@@ -11135,16 +11136,16 @@
         <v>34.99</v>
       </c>
       <c r="J34" s="30">
-        <v>15.68</v>
+        <v>55.02</v>
       </c>
       <c r="K34" s="30">
-        <v>56.08</v>
+        <v>67.91</v>
       </c>
       <c r="L34" s="30">
-        <v>56.42</v>
+        <v>74.11</v>
       </c>
       <c r="M34" s="30">
-        <v>40.479999999999997</v>
+        <v>13.66</v>
       </c>
       <c r="AA34" s="29" t="s">
         <v>38</v>
@@ -11235,7 +11236,7 @@
         <v>94.16</v>
       </c>
     </row>
-    <row r="35" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="35" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B35" s="29" t="s">
         <v>36</v>
       </c>
@@ -11259,16 +11260,16 @@
         <v>35.090000000000003</v>
       </c>
       <c r="J35" s="30">
-        <v>15.68</v>
+        <v>55.08</v>
       </c>
       <c r="K35" s="30">
-        <v>56.12</v>
+        <v>66.62</v>
       </c>
       <c r="L35" s="30">
-        <v>56.42</v>
+        <v>74.03</v>
       </c>
       <c r="M35" s="30">
-        <v>41.14</v>
+        <v>13.51</v>
       </c>
       <c r="AB35" s="23" t="s">
         <v>17</v>
@@ -11323,7 +11324,7 @@
       <c r="CA35" s="38"/>
       <c r="CB35" s="39"/>
     </row>
-    <row r="36" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B36" s="29" t="s">
         <v>37</v>
       </c>
@@ -11347,19 +11348,19 @@
         <v>35.18</v>
       </c>
       <c r="J36" s="30">
-        <v>15.68</v>
+        <v>55.12</v>
       </c>
       <c r="K36" s="30">
-        <v>56.15</v>
+        <v>66.349999999999994</v>
       </c>
       <c r="L36" s="30">
-        <v>56.42</v>
+        <v>73.97</v>
       </c>
       <c r="M36" s="30">
-        <v>41.32</v>
+        <v>13.42</v>
       </c>
     </row>
-    <row r="37" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B37" s="29" t="s">
         <v>38</v>
       </c>
@@ -11383,19 +11384,19 @@
         <v>35.24</v>
       </c>
       <c r="J37" s="30">
-        <v>15.68</v>
+        <v>55.15</v>
       </c>
       <c r="K37" s="30">
-        <v>56.18</v>
+        <v>65.84</v>
       </c>
       <c r="L37" s="30">
-        <v>56.41</v>
+        <v>73.91</v>
       </c>
       <c r="M37" s="30">
-        <v>41.43</v>
+        <v>13.38</v>
       </c>
     </row>
-    <row r="38" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="38" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C38" s="23" t="s">
         <v>17</v>
       </c>
@@ -11414,11 +11415,84 @@
     </row>
   </sheetData>
   <mergeCells count="91">
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="BS35:BT35"/>
+    <mergeCell ref="BU35:BV35"/>
+    <mergeCell ref="BW35:BX35"/>
+    <mergeCell ref="BY35:BZ35"/>
+    <mergeCell ref="CA35:CB35"/>
+    <mergeCell ref="BQ5:BQ8"/>
+    <mergeCell ref="BQ11:CB11"/>
+    <mergeCell ref="BS12:BT12"/>
+    <mergeCell ref="BU12:BV12"/>
+    <mergeCell ref="BW12:BX12"/>
+    <mergeCell ref="BY12:BZ12"/>
+    <mergeCell ref="CA12:CB12"/>
+    <mergeCell ref="BQ2:CB2"/>
+    <mergeCell ref="BS3:BT3"/>
+    <mergeCell ref="BU3:BV3"/>
+    <mergeCell ref="BW3:BX3"/>
+    <mergeCell ref="BY3:BZ3"/>
+    <mergeCell ref="CA3:CB3"/>
+    <mergeCell ref="BE35:BF35"/>
+    <mergeCell ref="BG35:BH35"/>
+    <mergeCell ref="BI35:BJ35"/>
+    <mergeCell ref="BK35:BL35"/>
+    <mergeCell ref="BM35:BN35"/>
+    <mergeCell ref="BC5:BC8"/>
+    <mergeCell ref="BC11:BN11"/>
+    <mergeCell ref="BE12:BF12"/>
+    <mergeCell ref="BG12:BH12"/>
+    <mergeCell ref="BI12:BJ12"/>
+    <mergeCell ref="BK12:BL12"/>
+    <mergeCell ref="BM12:BN12"/>
+    <mergeCell ref="BC2:BN2"/>
+    <mergeCell ref="BE3:BF3"/>
+    <mergeCell ref="BG3:BH3"/>
+    <mergeCell ref="BI3:BJ3"/>
+    <mergeCell ref="BK3:BL3"/>
+    <mergeCell ref="BM3:BN3"/>
+    <mergeCell ref="AQ35:AR35"/>
+    <mergeCell ref="AS35:AT35"/>
+    <mergeCell ref="AU35:AV35"/>
+    <mergeCell ref="AW35:AX35"/>
+    <mergeCell ref="AY35:AZ35"/>
+    <mergeCell ref="AO5:AO8"/>
+    <mergeCell ref="AO11:AZ11"/>
+    <mergeCell ref="AQ12:AR12"/>
+    <mergeCell ref="AS12:AT12"/>
+    <mergeCell ref="AU12:AV12"/>
+    <mergeCell ref="AW12:AX12"/>
+    <mergeCell ref="AY12:AZ12"/>
+    <mergeCell ref="AO2:AZ2"/>
+    <mergeCell ref="AQ3:AR3"/>
+    <mergeCell ref="AS3:AT3"/>
+    <mergeCell ref="AU3:AV3"/>
+    <mergeCell ref="AW3:AX3"/>
+    <mergeCell ref="AY3:AZ3"/>
+    <mergeCell ref="AC35:AD35"/>
+    <mergeCell ref="AE35:AF35"/>
+    <mergeCell ref="AG35:AH35"/>
+    <mergeCell ref="AI35:AJ35"/>
+    <mergeCell ref="AK35:AL35"/>
+    <mergeCell ref="AA5:AA8"/>
+    <mergeCell ref="AA11:AL11"/>
+    <mergeCell ref="AC12:AD12"/>
+    <mergeCell ref="AE12:AF12"/>
+    <mergeCell ref="AG12:AH12"/>
+    <mergeCell ref="AI12:AJ12"/>
+    <mergeCell ref="AK12:AL12"/>
+    <mergeCell ref="AA2:AL2"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="AG3:AH3"/>
+    <mergeCell ref="AI3:AJ3"/>
+    <mergeCell ref="AK3:AL3"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="B14:M14"/>
@@ -11427,84 +11501,11 @@
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="J15:K15"/>
     <mergeCell ref="L15:M15"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="AA2:AL2"/>
-    <mergeCell ref="AC3:AD3"/>
-    <mergeCell ref="AE3:AF3"/>
-    <mergeCell ref="AG3:AH3"/>
-    <mergeCell ref="AI3:AJ3"/>
-    <mergeCell ref="AK3:AL3"/>
-    <mergeCell ref="AA5:AA8"/>
-    <mergeCell ref="AA11:AL11"/>
-    <mergeCell ref="AC12:AD12"/>
-    <mergeCell ref="AE12:AF12"/>
-    <mergeCell ref="AG12:AH12"/>
-    <mergeCell ref="AI12:AJ12"/>
-    <mergeCell ref="AK12:AL12"/>
-    <mergeCell ref="AC35:AD35"/>
-    <mergeCell ref="AE35:AF35"/>
-    <mergeCell ref="AG35:AH35"/>
-    <mergeCell ref="AI35:AJ35"/>
-    <mergeCell ref="AK35:AL35"/>
-    <mergeCell ref="AO2:AZ2"/>
-    <mergeCell ref="AQ3:AR3"/>
-    <mergeCell ref="AS3:AT3"/>
-    <mergeCell ref="AU3:AV3"/>
-    <mergeCell ref="AW3:AX3"/>
-    <mergeCell ref="AY3:AZ3"/>
-    <mergeCell ref="AO5:AO8"/>
-    <mergeCell ref="AO11:AZ11"/>
-    <mergeCell ref="AQ12:AR12"/>
-    <mergeCell ref="AS12:AT12"/>
-    <mergeCell ref="AU12:AV12"/>
-    <mergeCell ref="AW12:AX12"/>
-    <mergeCell ref="AY12:AZ12"/>
-    <mergeCell ref="AQ35:AR35"/>
-    <mergeCell ref="AS35:AT35"/>
-    <mergeCell ref="AU35:AV35"/>
-    <mergeCell ref="AW35:AX35"/>
-    <mergeCell ref="AY35:AZ35"/>
-    <mergeCell ref="BC2:BN2"/>
-    <mergeCell ref="BE3:BF3"/>
-    <mergeCell ref="BG3:BH3"/>
-    <mergeCell ref="BI3:BJ3"/>
-    <mergeCell ref="BK3:BL3"/>
-    <mergeCell ref="BM3:BN3"/>
-    <mergeCell ref="BC5:BC8"/>
-    <mergeCell ref="BC11:BN11"/>
-    <mergeCell ref="BE12:BF12"/>
-    <mergeCell ref="BG12:BH12"/>
-    <mergeCell ref="BI12:BJ12"/>
-    <mergeCell ref="BK12:BL12"/>
-    <mergeCell ref="BM12:BN12"/>
-    <mergeCell ref="BE35:BF35"/>
-    <mergeCell ref="BG35:BH35"/>
-    <mergeCell ref="BI35:BJ35"/>
-    <mergeCell ref="BK35:BL35"/>
-    <mergeCell ref="BM35:BN35"/>
-    <mergeCell ref="BQ2:CB2"/>
-    <mergeCell ref="BS3:BT3"/>
-    <mergeCell ref="BU3:BV3"/>
-    <mergeCell ref="BW3:BX3"/>
-    <mergeCell ref="BY3:BZ3"/>
-    <mergeCell ref="CA3:CB3"/>
-    <mergeCell ref="BQ5:BQ8"/>
-    <mergeCell ref="BQ11:CB11"/>
-    <mergeCell ref="BS12:BT12"/>
-    <mergeCell ref="BU12:BV12"/>
-    <mergeCell ref="BW12:BX12"/>
-    <mergeCell ref="BY12:BZ12"/>
-    <mergeCell ref="CA12:CB12"/>
-    <mergeCell ref="BS35:BT35"/>
-    <mergeCell ref="BU35:BV35"/>
-    <mergeCell ref="BW35:BX35"/>
-    <mergeCell ref="BY35:BZ35"/>
-    <mergeCell ref="CA35:CB35"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="L38:M38"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Results_metrics.xlsx
+++ b/Results_metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Enrica\Desktop\Nuovo_ML_Project\MaskArchitectureAnomaly_CourseProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079428C3-2D6C-4630-B9B0-B4192C916057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D19AD126-7316-45FF-91D3-412443DA5F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11232" yWindow="0" windowWidth="11808" windowHeight="12072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -676,7 +676,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
@@ -727,16 +727,10 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -763,7 +757,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -2515,25 +2514,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>1.08</c:v>
+                  <c:v>21.45</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.86</c:v>
+                  <c:v>21.42</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.44</c:v>
+                  <c:v>21.7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.82</c:v>
+                  <c:v>23.99</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.91</c:v>
+                  <c:v>24.37</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.33</c:v>
+                  <c:v>25.44</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.58</c:v>
+                  <c:v>25.8</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>3.84</c:v>
@@ -2703,25 +2702,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>92.89</c:v>
+                  <c:v>19.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>86.68</c:v>
+                  <c:v>19.72</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>53.79</c:v>
+                  <c:v>19.38</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>30.87</c:v>
+                  <c:v>15.81</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>30.88</c:v>
+                  <c:v>14.51</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>31.26</c:v>
+                  <c:v>14.65</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>31.28</c:v>
+                  <c:v>14.93</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>31.17</c:v>
@@ -7770,188 +7769,188 @@
   <sheetData>
     <row r="1" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="53"/>
-      <c r="AA2" s="47" t="s">
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="51"/>
+      <c r="AA2" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="AB2" s="52"/>
-      <c r="AC2" s="52"/>
-      <c r="AD2" s="52"/>
-      <c r="AE2" s="52"/>
-      <c r="AF2" s="52"/>
-      <c r="AG2" s="52"/>
-      <c r="AH2" s="52"/>
-      <c r="AI2" s="52"/>
-      <c r="AJ2" s="52"/>
-      <c r="AK2" s="52"/>
-      <c r="AL2" s="53"/>
-      <c r="AO2" s="47" t="s">
+      <c r="AB2" s="50"/>
+      <c r="AC2" s="50"/>
+      <c r="AD2" s="50"/>
+      <c r="AE2" s="50"/>
+      <c r="AF2" s="50"/>
+      <c r="AG2" s="50"/>
+      <c r="AH2" s="50"/>
+      <c r="AI2" s="50"/>
+      <c r="AJ2" s="50"/>
+      <c r="AK2" s="50"/>
+      <c r="AL2" s="51"/>
+      <c r="AO2" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AP2" s="52"/>
-      <c r="AQ2" s="52"/>
-      <c r="AR2" s="52"/>
-      <c r="AS2" s="52"/>
-      <c r="AT2" s="52"/>
-      <c r="AU2" s="52"/>
-      <c r="AV2" s="52"/>
-      <c r="AW2" s="52"/>
-      <c r="AX2" s="52"/>
-      <c r="AY2" s="52"/>
-      <c r="AZ2" s="53"/>
-      <c r="BC2" s="47" t="s">
+      <c r="AP2" s="50"/>
+      <c r="AQ2" s="50"/>
+      <c r="AR2" s="50"/>
+      <c r="AS2" s="50"/>
+      <c r="AT2" s="50"/>
+      <c r="AU2" s="50"/>
+      <c r="AV2" s="50"/>
+      <c r="AW2" s="50"/>
+      <c r="AX2" s="50"/>
+      <c r="AY2" s="50"/>
+      <c r="AZ2" s="51"/>
+      <c r="BC2" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="BD2" s="52"/>
-      <c r="BE2" s="52"/>
-      <c r="BF2" s="52"/>
-      <c r="BG2" s="52"/>
-      <c r="BH2" s="52"/>
-      <c r="BI2" s="52"/>
-      <c r="BJ2" s="52"/>
-      <c r="BK2" s="52"/>
-      <c r="BL2" s="52"/>
-      <c r="BM2" s="52"/>
-      <c r="BN2" s="53"/>
-      <c r="BQ2" s="47" t="s">
+      <c r="BD2" s="50"/>
+      <c r="BE2" s="50"/>
+      <c r="BF2" s="50"/>
+      <c r="BG2" s="50"/>
+      <c r="BH2" s="50"/>
+      <c r="BI2" s="50"/>
+      <c r="BJ2" s="50"/>
+      <c r="BK2" s="50"/>
+      <c r="BL2" s="50"/>
+      <c r="BM2" s="50"/>
+      <c r="BN2" s="51"/>
+      <c r="BQ2" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="BR2" s="52"/>
-      <c r="BS2" s="52"/>
-      <c r="BT2" s="52"/>
-      <c r="BU2" s="52"/>
-      <c r="BV2" s="52"/>
-      <c r="BW2" s="52"/>
-      <c r="BX2" s="52"/>
-      <c r="BY2" s="52"/>
-      <c r="BZ2" s="52"/>
-      <c r="CA2" s="52"/>
-      <c r="CB2" s="53"/>
+      <c r="BR2" s="50"/>
+      <c r="BS2" s="50"/>
+      <c r="BT2" s="50"/>
+      <c r="BU2" s="50"/>
+      <c r="BV2" s="50"/>
+      <c r="BW2" s="50"/>
+      <c r="BX2" s="50"/>
+      <c r="BY2" s="50"/>
+      <c r="BZ2" s="50"/>
+      <c r="CA2" s="50"/>
+      <c r="CB2" s="51"/>
     </row>
     <row r="3" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
       <c r="C3" s="5"/>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50" t="s">
+      <c r="E3" s="49"/>
+      <c r="F3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="51"/>
-      <c r="H3" s="50" t="s">
+      <c r="G3" s="49"/>
+      <c r="H3" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="51"/>
-      <c r="J3" s="50" t="s">
+      <c r="I3" s="49"/>
+      <c r="J3" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="51"/>
-      <c r="L3" s="50" t="s">
+      <c r="K3" s="49"/>
+      <c r="L3" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="51"/>
+      <c r="M3" s="49"/>
       <c r="AA3" s="1"/>
       <c r="AB3" s="5"/>
-      <c r="AC3" s="50" t="s">
+      <c r="AC3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="AD3" s="51"/>
-      <c r="AE3" s="50" t="s">
+      <c r="AD3" s="49"/>
+      <c r="AE3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="AF3" s="51"/>
-      <c r="AG3" s="50" t="s">
+      <c r="AF3" s="49"/>
+      <c r="AG3" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="AH3" s="51"/>
-      <c r="AI3" s="50" t="s">
+      <c r="AH3" s="49"/>
+      <c r="AI3" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="AJ3" s="51"/>
-      <c r="AK3" s="50" t="s">
+      <c r="AJ3" s="49"/>
+      <c r="AK3" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="51"/>
+      <c r="AL3" s="49"/>
       <c r="AO3" s="1"/>
       <c r="AP3" s="5"/>
-      <c r="AQ3" s="50" t="s">
+      <c r="AQ3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="AR3" s="51"/>
-      <c r="AS3" s="50" t="s">
+      <c r="AR3" s="49"/>
+      <c r="AS3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="AT3" s="51"/>
-      <c r="AU3" s="50" t="s">
+      <c r="AT3" s="49"/>
+      <c r="AU3" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="AV3" s="51"/>
-      <c r="AW3" s="50" t="s">
+      <c r="AV3" s="49"/>
+      <c r="AW3" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="AX3" s="51"/>
-      <c r="AY3" s="50" t="s">
+      <c r="AX3" s="49"/>
+      <c r="AY3" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="AZ3" s="51"/>
+      <c r="AZ3" s="49"/>
       <c r="BC3" s="1"/>
       <c r="BD3" s="5"/>
-      <c r="BE3" s="50" t="s">
+      <c r="BE3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="BF3" s="51"/>
-      <c r="BG3" s="50" t="s">
+      <c r="BF3" s="49"/>
+      <c r="BG3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="BH3" s="51"/>
-      <c r="BI3" s="50" t="s">
+      <c r="BH3" s="49"/>
+      <c r="BI3" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="BJ3" s="51"/>
-      <c r="BK3" s="50" t="s">
+      <c r="BJ3" s="49"/>
+      <c r="BK3" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="BL3" s="51"/>
-      <c r="BM3" s="50" t="s">
+      <c r="BL3" s="49"/>
+      <c r="BM3" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="BN3" s="51"/>
+      <c r="BN3" s="49"/>
       <c r="BQ3" s="1"/>
       <c r="BR3" s="5"/>
-      <c r="BS3" s="50" t="s">
+      <c r="BS3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="BT3" s="51"/>
-      <c r="BU3" s="50" t="s">
+      <c r="BT3" s="49"/>
+      <c r="BU3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="BV3" s="51"/>
-      <c r="BW3" s="50" t="s">
+      <c r="BV3" s="49"/>
+      <c r="BW3" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="BX3" s="51"/>
-      <c r="BY3" s="50" t="s">
+      <c r="BX3" s="49"/>
+      <c r="BY3" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="BZ3" s="51"/>
-      <c r="CA3" s="50" t="s">
+      <c r="BZ3" s="49"/>
+      <c r="CA3" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="CB3" s="51"/>
+      <c r="CB3" s="49"/>
     </row>
     <row r="4" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="6" t="s">
@@ -8136,7 +8135,7 @@
       </c>
     </row>
     <row r="5" spans="2:80" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="52" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -8172,7 +8171,7 @@
       <c r="M5" s="14">
         <v>82.58</v>
       </c>
-      <c r="AA5" s="45" t="s">
+      <c r="AA5" s="42" t="s">
         <v>13</v>
       </c>
       <c r="AB5" s="12" t="s">
@@ -8196,7 +8195,7 @@
       <c r="AL5" s="20">
         <v>19.14</v>
       </c>
-      <c r="AO5" s="45" t="s">
+      <c r="AO5" s="42" t="s">
         <v>13</v>
       </c>
       <c r="AP5" s="12" t="s">
@@ -8220,7 +8219,7 @@
       <c r="AZ5" s="20">
         <v>19.829999999999998</v>
       </c>
-      <c r="BC5" s="45" t="s">
+      <c r="BC5" s="42" t="s">
         <v>13</v>
       </c>
       <c r="BD5" s="12" t="s">
@@ -8244,7 +8243,7 @@
       <c r="BN5" s="20">
         <v>20.05</v>
       </c>
-      <c r="BQ5" s="45" t="s">
+      <c r="BQ5" s="42" t="s">
         <v>13</v>
       </c>
       <c r="BR5" s="12" t="s">
@@ -8394,7 +8393,7 @@
       </c>
     </row>
     <row r="7" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="44"/>
+      <c r="B7" s="53"/>
       <c r="C7" s="11" t="s">
         <v>12</v>
       </c>
@@ -8518,7 +8517,7 @@
       </c>
     </row>
     <row r="8" spans="2:80" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="42" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="12" t="s">
@@ -8537,10 +8536,10 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="H8" s="19">
-        <v>3.33</v>
+        <v>27.2</v>
       </c>
       <c r="I8" s="20">
-        <v>31.26</v>
+        <v>14.65</v>
       </c>
       <c r="J8" s="19">
         <v>54.1</v>
@@ -8554,7 +8553,7 @@
       <c r="M8" s="20">
         <v>19.09</v>
       </c>
-      <c r="AA8" s="46"/>
+      <c r="AA8" s="44"/>
       <c r="AB8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8576,7 +8575,7 @@
       <c r="AL8" s="22">
         <v>21.78</v>
       </c>
-      <c r="AO8" s="46"/>
+      <c r="AO8" s="44"/>
       <c r="AP8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8598,7 +8597,7 @@
       <c r="AZ8" s="22">
         <v>19.12</v>
       </c>
-      <c r="BC8" s="46"/>
+      <c r="BC8" s="44"/>
       <c r="BD8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8620,7 +8619,7 @@
       <c r="BN8" s="22">
         <v>19.13</v>
       </c>
-      <c r="BQ8" s="46"/>
+      <c r="BQ8" s="44"/>
       <c r="BR8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8697,10 +8696,10 @@
         <v>0.68</v>
       </c>
       <c r="H10" s="15">
-        <v>5.58</v>
+        <v>27.54</v>
       </c>
       <c r="I10" s="16">
-        <v>31.27</v>
+        <v>14.72</v>
       </c>
       <c r="J10" s="15">
         <v>52.74</v>
@@ -8716,7 +8715,7 @@
       </c>
     </row>
     <row r="11" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="46"/>
+      <c r="B11" s="44"/>
       <c r="C11" s="10" t="s">
         <v>14</v>
       </c>
@@ -8750,152 +8749,152 @@
       <c r="M11" s="22">
         <v>17.579999999999998</v>
       </c>
-      <c r="AA11" s="47" t="s">
+      <c r="AA11" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="AB11" s="48"/>
-      <c r="AC11" s="48"/>
-      <c r="AD11" s="48"/>
-      <c r="AE11" s="48"/>
-      <c r="AF11" s="48"/>
-      <c r="AG11" s="48"/>
-      <c r="AH11" s="48"/>
-      <c r="AI11" s="48"/>
-      <c r="AJ11" s="48"/>
-      <c r="AK11" s="48"/>
-      <c r="AL11" s="49"/>
-      <c r="AO11" s="47" t="s">
+      <c r="AB11" s="46"/>
+      <c r="AC11" s="46"/>
+      <c r="AD11" s="46"/>
+      <c r="AE11" s="46"/>
+      <c r="AF11" s="46"/>
+      <c r="AG11" s="46"/>
+      <c r="AH11" s="46"/>
+      <c r="AI11" s="46"/>
+      <c r="AJ11" s="46"/>
+      <c r="AK11" s="46"/>
+      <c r="AL11" s="47"/>
+      <c r="AO11" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="AP11" s="48"/>
-      <c r="AQ11" s="48"/>
-      <c r="AR11" s="48"/>
-      <c r="AS11" s="48"/>
-      <c r="AT11" s="48"/>
-      <c r="AU11" s="48"/>
-      <c r="AV11" s="48"/>
-      <c r="AW11" s="48"/>
-      <c r="AX11" s="48"/>
-      <c r="AY11" s="48"/>
-      <c r="AZ11" s="49"/>
-      <c r="BC11" s="47" t="s">
+      <c r="AP11" s="46"/>
+      <c r="AQ11" s="46"/>
+      <c r="AR11" s="46"/>
+      <c r="AS11" s="46"/>
+      <c r="AT11" s="46"/>
+      <c r="AU11" s="46"/>
+      <c r="AV11" s="46"/>
+      <c r="AW11" s="46"/>
+      <c r="AX11" s="46"/>
+      <c r="AY11" s="46"/>
+      <c r="AZ11" s="47"/>
+      <c r="BC11" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="BD11" s="48"/>
-      <c r="BE11" s="48"/>
-      <c r="BF11" s="48"/>
-      <c r="BG11" s="48"/>
-      <c r="BH11" s="48"/>
-      <c r="BI11" s="48"/>
-      <c r="BJ11" s="48"/>
-      <c r="BK11" s="48"/>
-      <c r="BL11" s="48"/>
-      <c r="BM11" s="48"/>
-      <c r="BN11" s="49"/>
-      <c r="BQ11" s="47" t="s">
+      <c r="BD11" s="46"/>
+      <c r="BE11" s="46"/>
+      <c r="BF11" s="46"/>
+      <c r="BG11" s="46"/>
+      <c r="BH11" s="46"/>
+      <c r="BI11" s="46"/>
+      <c r="BJ11" s="46"/>
+      <c r="BK11" s="46"/>
+      <c r="BL11" s="46"/>
+      <c r="BM11" s="46"/>
+      <c r="BN11" s="47"/>
+      <c r="BQ11" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="BR11" s="48"/>
-      <c r="BS11" s="48"/>
-      <c r="BT11" s="48"/>
-      <c r="BU11" s="48"/>
-      <c r="BV11" s="48"/>
-      <c r="BW11" s="48"/>
-      <c r="BX11" s="48"/>
-      <c r="BY11" s="48"/>
-      <c r="BZ11" s="48"/>
-      <c r="CA11" s="48"/>
-      <c r="CB11" s="49"/>
+      <c r="BR11" s="46"/>
+      <c r="BS11" s="46"/>
+      <c r="BT11" s="46"/>
+      <c r="BU11" s="46"/>
+      <c r="BV11" s="46"/>
+      <c r="BW11" s="46"/>
+      <c r="BX11" s="46"/>
+      <c r="BY11" s="46"/>
+      <c r="BZ11" s="46"/>
+      <c r="CA11" s="46"/>
+      <c r="CB11" s="47"/>
     </row>
     <row r="12" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="AA12" s="24"/>
       <c r="AB12" s="4"/>
-      <c r="AC12" s="50" t="s">
+      <c r="AC12" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="AD12" s="51"/>
-      <c r="AE12" s="50" t="s">
+      <c r="AD12" s="49"/>
+      <c r="AE12" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="AF12" s="51"/>
-      <c r="AG12" s="50" t="s">
+      <c r="AF12" s="49"/>
+      <c r="AG12" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="AH12" s="51"/>
-      <c r="AI12" s="50" t="s">
+      <c r="AH12" s="49"/>
+      <c r="AI12" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="AJ12" s="51"/>
-      <c r="AK12" s="50" t="s">
+      <c r="AJ12" s="49"/>
+      <c r="AK12" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="AL12" s="51"/>
+      <c r="AL12" s="49"/>
       <c r="AO12" s="24"/>
       <c r="AP12" s="4"/>
-      <c r="AQ12" s="50" t="s">
+      <c r="AQ12" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="AR12" s="51"/>
-      <c r="AS12" s="50" t="s">
+      <c r="AR12" s="49"/>
+      <c r="AS12" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="AT12" s="51"/>
-      <c r="AU12" s="50" t="s">
+      <c r="AT12" s="49"/>
+      <c r="AU12" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="AV12" s="51"/>
-      <c r="AW12" s="50" t="s">
+      <c r="AV12" s="49"/>
+      <c r="AW12" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="AX12" s="51"/>
-      <c r="AY12" s="50" t="s">
+      <c r="AX12" s="49"/>
+      <c r="AY12" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="AZ12" s="51"/>
+      <c r="AZ12" s="49"/>
       <c r="BC12" s="24"/>
       <c r="BD12" s="4"/>
-      <c r="BE12" s="50" t="s">
+      <c r="BE12" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="BF12" s="51"/>
-      <c r="BG12" s="50" t="s">
+      <c r="BF12" s="49"/>
+      <c r="BG12" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="BH12" s="51"/>
-      <c r="BI12" s="50" t="s">
+      <c r="BH12" s="49"/>
+      <c r="BI12" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="BJ12" s="51"/>
-      <c r="BK12" s="50" t="s">
+      <c r="BJ12" s="49"/>
+      <c r="BK12" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="BL12" s="51"/>
-      <c r="BM12" s="50" t="s">
+      <c r="BL12" s="49"/>
+      <c r="BM12" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="BN12" s="51"/>
+      <c r="BN12" s="49"/>
       <c r="BQ12" s="24"/>
       <c r="BR12" s="4"/>
-      <c r="BS12" s="50" t="s">
+      <c r="BS12" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="BT12" s="51"/>
-      <c r="BU12" s="50" t="s">
+      <c r="BT12" s="49"/>
+      <c r="BU12" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="BV12" s="51"/>
-      <c r="BW12" s="50" t="s">
+      <c r="BV12" s="49"/>
+      <c r="BW12" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="BX12" s="51"/>
-      <c r="BY12" s="50" t="s">
+      <c r="BX12" s="49"/>
+      <c r="BY12" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="BZ12" s="51"/>
-      <c r="CA12" s="50" t="s">
+      <c r="BZ12" s="49"/>
+      <c r="CA12" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="CB12" s="51"/>
+      <c r="CB12" s="49"/>
     </row>
     <row r="13" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="AA13" s="25" t="s">
@@ -9044,20 +9043,20 @@
       </c>
     </row>
     <row r="14" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="47" t="s">
+      <c r="B14" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="48"/>
-      <c r="L14" s="48"/>
-      <c r="M14" s="49"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="47"/>
       <c r="AA14" s="29" t="s">
         <v>24</v>
       </c>
@@ -9122,26 +9121,26 @@
     <row r="15" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="24"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="50" t="s">
+      <c r="D15" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="E15" s="51"/>
-      <c r="F15" s="50" t="s">
+      <c r="E15" s="49"/>
+      <c r="F15" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="51"/>
-      <c r="H15" s="50" t="s">
+      <c r="G15" s="49"/>
+      <c r="H15" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="51"/>
-      <c r="J15" s="50" t="s">
+      <c r="I15" s="49"/>
+      <c r="J15" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="51"/>
-      <c r="L15" s="50" t="s">
+      <c r="K15" s="49"/>
+      <c r="L15" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="M15" s="51"/>
+      <c r="M15" s="49"/>
       <c r="AA15" s="29" t="s">
         <v>39</v>
       </c>
@@ -9313,10 +9312,10 @@
         <v>100</v>
       </c>
       <c r="H17" s="30">
-        <v>1.08</v>
+        <v>21.45</v>
       </c>
       <c r="I17" s="30">
-        <v>92.89</v>
+        <v>19.5</v>
       </c>
       <c r="J17" s="30">
         <v>34.51</v>
@@ -9405,10 +9404,10 @@
         <v>2.16</v>
       </c>
       <c r="H18" s="30">
-        <v>1.86</v>
+        <v>21.42</v>
       </c>
       <c r="I18" s="30">
-        <v>86.68</v>
+        <v>19.72</v>
       </c>
       <c r="J18" s="30">
         <v>47.33</v>
@@ -9497,10 +9496,10 @@
         <v>0.61</v>
       </c>
       <c r="H19" s="34">
-        <v>2.44</v>
+        <v>21.7</v>
       </c>
       <c r="I19" s="34">
-        <v>53.79</v>
+        <v>19.38</v>
       </c>
       <c r="J19" s="34">
         <v>52.93</v>
@@ -9589,10 +9588,10 @@
         <v>0.54</v>
       </c>
       <c r="H20" s="34">
-        <v>2.82</v>
+        <v>23.99</v>
       </c>
       <c r="I20" s="34">
-        <v>30.87</v>
+        <v>15.81</v>
       </c>
       <c r="J20" s="34">
         <v>54.01</v>
@@ -9681,10 +9680,10 @@
         <v>0.54</v>
       </c>
       <c r="H21" s="30">
-        <v>2.91</v>
+        <v>24.37</v>
       </c>
       <c r="I21" s="30">
-        <v>30.88</v>
+        <v>14.51</v>
       </c>
       <c r="J21" s="30">
         <v>54.12</v>
@@ -9773,10 +9772,10 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="H22" s="30">
-        <v>3.33</v>
+        <v>25.44</v>
       </c>
       <c r="I22" s="30">
-        <v>31.26</v>
+        <v>14.65</v>
       </c>
       <c r="J22" s="30">
         <v>54.46</v>
@@ -9861,10 +9860,10 @@
         <v>0.62</v>
       </c>
       <c r="H23" s="34">
-        <v>3.58</v>
+        <v>25.8</v>
       </c>
       <c r="I23" s="34">
-        <v>31.28</v>
+        <v>14.93</v>
       </c>
       <c r="J23" s="34">
         <v>54.59</v>
@@ -10645,10 +10644,10 @@
       <c r="K30" s="30">
         <v>72.709999999999994</v>
       </c>
-      <c r="L30" s="54">
+      <c r="L30" s="37">
         <v>74.36</v>
       </c>
-      <c r="M30" s="54">
+      <c r="M30" s="37">
         <v>17.3</v>
       </c>
       <c r="AA30" s="29" t="s">
@@ -11415,84 +11414,11 @@
     </row>
   </sheetData>
   <mergeCells count="91">
-    <mergeCell ref="BS35:BT35"/>
-    <mergeCell ref="BU35:BV35"/>
-    <mergeCell ref="BW35:BX35"/>
-    <mergeCell ref="BY35:BZ35"/>
-    <mergeCell ref="CA35:CB35"/>
-    <mergeCell ref="BQ5:BQ8"/>
-    <mergeCell ref="BQ11:CB11"/>
-    <mergeCell ref="BS12:BT12"/>
-    <mergeCell ref="BU12:BV12"/>
-    <mergeCell ref="BW12:BX12"/>
-    <mergeCell ref="BY12:BZ12"/>
-    <mergeCell ref="CA12:CB12"/>
-    <mergeCell ref="BQ2:CB2"/>
-    <mergeCell ref="BS3:BT3"/>
-    <mergeCell ref="BU3:BV3"/>
-    <mergeCell ref="BW3:BX3"/>
-    <mergeCell ref="BY3:BZ3"/>
-    <mergeCell ref="CA3:CB3"/>
-    <mergeCell ref="BE35:BF35"/>
-    <mergeCell ref="BG35:BH35"/>
-    <mergeCell ref="BI35:BJ35"/>
-    <mergeCell ref="BK35:BL35"/>
-    <mergeCell ref="BM35:BN35"/>
-    <mergeCell ref="BC5:BC8"/>
-    <mergeCell ref="BC11:BN11"/>
-    <mergeCell ref="BE12:BF12"/>
-    <mergeCell ref="BG12:BH12"/>
-    <mergeCell ref="BI12:BJ12"/>
-    <mergeCell ref="BK12:BL12"/>
-    <mergeCell ref="BM12:BN12"/>
-    <mergeCell ref="BC2:BN2"/>
-    <mergeCell ref="BE3:BF3"/>
-    <mergeCell ref="BG3:BH3"/>
-    <mergeCell ref="BI3:BJ3"/>
-    <mergeCell ref="BK3:BL3"/>
-    <mergeCell ref="BM3:BN3"/>
-    <mergeCell ref="AQ35:AR35"/>
-    <mergeCell ref="AS35:AT35"/>
-    <mergeCell ref="AU35:AV35"/>
-    <mergeCell ref="AW35:AX35"/>
-    <mergeCell ref="AY35:AZ35"/>
-    <mergeCell ref="AO5:AO8"/>
-    <mergeCell ref="AO11:AZ11"/>
-    <mergeCell ref="AQ12:AR12"/>
-    <mergeCell ref="AS12:AT12"/>
-    <mergeCell ref="AU12:AV12"/>
-    <mergeCell ref="AW12:AX12"/>
-    <mergeCell ref="AY12:AZ12"/>
-    <mergeCell ref="AO2:AZ2"/>
-    <mergeCell ref="AQ3:AR3"/>
-    <mergeCell ref="AS3:AT3"/>
-    <mergeCell ref="AU3:AV3"/>
-    <mergeCell ref="AW3:AX3"/>
-    <mergeCell ref="AY3:AZ3"/>
-    <mergeCell ref="AC35:AD35"/>
-    <mergeCell ref="AE35:AF35"/>
-    <mergeCell ref="AG35:AH35"/>
-    <mergeCell ref="AI35:AJ35"/>
-    <mergeCell ref="AK35:AL35"/>
-    <mergeCell ref="AA5:AA8"/>
-    <mergeCell ref="AA11:AL11"/>
-    <mergeCell ref="AC12:AD12"/>
-    <mergeCell ref="AE12:AF12"/>
-    <mergeCell ref="AG12:AH12"/>
-    <mergeCell ref="AI12:AJ12"/>
-    <mergeCell ref="AK12:AL12"/>
-    <mergeCell ref="AA2:AL2"/>
-    <mergeCell ref="AC3:AD3"/>
-    <mergeCell ref="AE3:AF3"/>
-    <mergeCell ref="AG3:AH3"/>
-    <mergeCell ref="AI3:AJ3"/>
-    <mergeCell ref="AK3:AL3"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="L38:M38"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="B14:M14"/>
@@ -11501,11 +11427,84 @@
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="J15:K15"/>
     <mergeCell ref="L15:M15"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="AA2:AL2"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="AG3:AH3"/>
+    <mergeCell ref="AI3:AJ3"/>
+    <mergeCell ref="AK3:AL3"/>
+    <mergeCell ref="AA5:AA8"/>
+    <mergeCell ref="AA11:AL11"/>
+    <mergeCell ref="AC12:AD12"/>
+    <mergeCell ref="AE12:AF12"/>
+    <mergeCell ref="AG12:AH12"/>
+    <mergeCell ref="AI12:AJ12"/>
+    <mergeCell ref="AK12:AL12"/>
+    <mergeCell ref="AC35:AD35"/>
+    <mergeCell ref="AE35:AF35"/>
+    <mergeCell ref="AG35:AH35"/>
+    <mergeCell ref="AI35:AJ35"/>
+    <mergeCell ref="AK35:AL35"/>
+    <mergeCell ref="AO2:AZ2"/>
+    <mergeCell ref="AQ3:AR3"/>
+    <mergeCell ref="AS3:AT3"/>
+    <mergeCell ref="AU3:AV3"/>
+    <mergeCell ref="AW3:AX3"/>
+    <mergeCell ref="AY3:AZ3"/>
+    <mergeCell ref="AO5:AO8"/>
+    <mergeCell ref="AO11:AZ11"/>
+    <mergeCell ref="AQ12:AR12"/>
+    <mergeCell ref="AS12:AT12"/>
+    <mergeCell ref="AU12:AV12"/>
+    <mergeCell ref="AW12:AX12"/>
+    <mergeCell ref="AY12:AZ12"/>
+    <mergeCell ref="AQ35:AR35"/>
+    <mergeCell ref="AS35:AT35"/>
+    <mergeCell ref="AU35:AV35"/>
+    <mergeCell ref="AW35:AX35"/>
+    <mergeCell ref="AY35:AZ35"/>
+    <mergeCell ref="BC2:BN2"/>
+    <mergeCell ref="BE3:BF3"/>
+    <mergeCell ref="BG3:BH3"/>
+    <mergeCell ref="BI3:BJ3"/>
+    <mergeCell ref="BK3:BL3"/>
+    <mergeCell ref="BM3:BN3"/>
+    <mergeCell ref="BC5:BC8"/>
+    <mergeCell ref="BC11:BN11"/>
+    <mergeCell ref="BE12:BF12"/>
+    <mergeCell ref="BG12:BH12"/>
+    <mergeCell ref="BI12:BJ12"/>
+    <mergeCell ref="BK12:BL12"/>
+    <mergeCell ref="BM12:BN12"/>
+    <mergeCell ref="BE35:BF35"/>
+    <mergeCell ref="BG35:BH35"/>
+    <mergeCell ref="BI35:BJ35"/>
+    <mergeCell ref="BK35:BL35"/>
+    <mergeCell ref="BM35:BN35"/>
+    <mergeCell ref="BQ2:CB2"/>
+    <mergeCell ref="BS3:BT3"/>
+    <mergeCell ref="BU3:BV3"/>
+    <mergeCell ref="BW3:BX3"/>
+    <mergeCell ref="BY3:BZ3"/>
+    <mergeCell ref="CA3:CB3"/>
+    <mergeCell ref="BQ5:BQ8"/>
+    <mergeCell ref="BQ11:CB11"/>
+    <mergeCell ref="BS12:BT12"/>
+    <mergeCell ref="BU12:BV12"/>
+    <mergeCell ref="BW12:BX12"/>
+    <mergeCell ref="BY12:BZ12"/>
+    <mergeCell ref="CA12:CB12"/>
+    <mergeCell ref="BS35:BT35"/>
+    <mergeCell ref="BU35:BV35"/>
+    <mergeCell ref="BW35:BX35"/>
+    <mergeCell ref="BY35:BZ35"/>
+    <mergeCell ref="CA35:CB35"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Results_metrics.xlsx
+++ b/Results_metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Enrica\Desktop\Nuovo_ML_Project\MaskArchitectureAnomaly_CourseProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D19AD126-7316-45FF-91D3-412443DA5F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C961665-BCC3-42D3-9616-C489647191AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11232" yWindow="0" windowWidth="11808" windowHeight="12072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -727,10 +727,16 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -756,12 +762,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7769,188 +7769,188 @@
   <sheetData>
     <row r="1" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="51"/>
-      <c r="AA2" s="45" t="s">
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="53"/>
+      <c r="AA2" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="AB2" s="50"/>
-      <c r="AC2" s="50"/>
-      <c r="AD2" s="50"/>
-      <c r="AE2" s="50"/>
-      <c r="AF2" s="50"/>
-      <c r="AG2" s="50"/>
-      <c r="AH2" s="50"/>
-      <c r="AI2" s="50"/>
-      <c r="AJ2" s="50"/>
-      <c r="AK2" s="50"/>
-      <c r="AL2" s="51"/>
-      <c r="AO2" s="45" t="s">
+      <c r="AB2" s="52"/>
+      <c r="AC2" s="52"/>
+      <c r="AD2" s="52"/>
+      <c r="AE2" s="52"/>
+      <c r="AF2" s="52"/>
+      <c r="AG2" s="52"/>
+      <c r="AH2" s="52"/>
+      <c r="AI2" s="52"/>
+      <c r="AJ2" s="52"/>
+      <c r="AK2" s="52"/>
+      <c r="AL2" s="53"/>
+      <c r="AO2" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="AP2" s="50"/>
-      <c r="AQ2" s="50"/>
-      <c r="AR2" s="50"/>
-      <c r="AS2" s="50"/>
-      <c r="AT2" s="50"/>
-      <c r="AU2" s="50"/>
-      <c r="AV2" s="50"/>
-      <c r="AW2" s="50"/>
-      <c r="AX2" s="50"/>
-      <c r="AY2" s="50"/>
-      <c r="AZ2" s="51"/>
-      <c r="BC2" s="45" t="s">
+      <c r="AP2" s="52"/>
+      <c r="AQ2" s="52"/>
+      <c r="AR2" s="52"/>
+      <c r="AS2" s="52"/>
+      <c r="AT2" s="52"/>
+      <c r="AU2" s="52"/>
+      <c r="AV2" s="52"/>
+      <c r="AW2" s="52"/>
+      <c r="AX2" s="52"/>
+      <c r="AY2" s="52"/>
+      <c r="AZ2" s="53"/>
+      <c r="BC2" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="BD2" s="50"/>
-      <c r="BE2" s="50"/>
-      <c r="BF2" s="50"/>
-      <c r="BG2" s="50"/>
-      <c r="BH2" s="50"/>
-      <c r="BI2" s="50"/>
-      <c r="BJ2" s="50"/>
-      <c r="BK2" s="50"/>
-      <c r="BL2" s="50"/>
-      <c r="BM2" s="50"/>
-      <c r="BN2" s="51"/>
-      <c r="BQ2" s="45" t="s">
+      <c r="BD2" s="52"/>
+      <c r="BE2" s="52"/>
+      <c r="BF2" s="52"/>
+      <c r="BG2" s="52"/>
+      <c r="BH2" s="52"/>
+      <c r="BI2" s="52"/>
+      <c r="BJ2" s="52"/>
+      <c r="BK2" s="52"/>
+      <c r="BL2" s="52"/>
+      <c r="BM2" s="52"/>
+      <c r="BN2" s="53"/>
+      <c r="BQ2" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="BR2" s="50"/>
-      <c r="BS2" s="50"/>
-      <c r="BT2" s="50"/>
-      <c r="BU2" s="50"/>
-      <c r="BV2" s="50"/>
-      <c r="BW2" s="50"/>
-      <c r="BX2" s="50"/>
-      <c r="BY2" s="50"/>
-      <c r="BZ2" s="50"/>
-      <c r="CA2" s="50"/>
-      <c r="CB2" s="51"/>
+      <c r="BR2" s="52"/>
+      <c r="BS2" s="52"/>
+      <c r="BT2" s="52"/>
+      <c r="BU2" s="52"/>
+      <c r="BV2" s="52"/>
+      <c r="BW2" s="52"/>
+      <c r="BX2" s="52"/>
+      <c r="BY2" s="52"/>
+      <c r="BZ2" s="52"/>
+      <c r="CA2" s="52"/>
+      <c r="CB2" s="53"/>
     </row>
     <row r="3" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
       <c r="C3" s="5"/>
-      <c r="D3" s="48" t="s">
+      <c r="D3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="49"/>
-      <c r="F3" s="48" t="s">
+      <c r="E3" s="51"/>
+      <c r="F3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="49"/>
-      <c r="H3" s="48" t="s">
+      <c r="G3" s="51"/>
+      <c r="H3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="49"/>
-      <c r="J3" s="48" t="s">
+      <c r="I3" s="51"/>
+      <c r="J3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="49"/>
-      <c r="L3" s="48" t="s">
+      <c r="K3" s="51"/>
+      <c r="L3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="49"/>
+      <c r="M3" s="51"/>
       <c r="AA3" s="1"/>
       <c r="AB3" s="5"/>
-      <c r="AC3" s="48" t="s">
+      <c r="AC3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="AD3" s="49"/>
-      <c r="AE3" s="48" t="s">
+      <c r="AD3" s="51"/>
+      <c r="AE3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="AF3" s="49"/>
-      <c r="AG3" s="48" t="s">
+      <c r="AF3" s="51"/>
+      <c r="AG3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="AH3" s="49"/>
-      <c r="AI3" s="48" t="s">
+      <c r="AH3" s="51"/>
+      <c r="AI3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AJ3" s="49"/>
-      <c r="AK3" s="48" t="s">
+      <c r="AJ3" s="51"/>
+      <c r="AK3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="49"/>
+      <c r="AL3" s="51"/>
       <c r="AO3" s="1"/>
       <c r="AP3" s="5"/>
-      <c r="AQ3" s="48" t="s">
+      <c r="AQ3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="AR3" s="49"/>
-      <c r="AS3" s="48" t="s">
+      <c r="AR3" s="51"/>
+      <c r="AS3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="AT3" s="49"/>
-      <c r="AU3" s="48" t="s">
+      <c r="AT3" s="51"/>
+      <c r="AU3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="AV3" s="49"/>
-      <c r="AW3" s="48" t="s">
+      <c r="AV3" s="51"/>
+      <c r="AW3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AX3" s="49"/>
-      <c r="AY3" s="48" t="s">
+      <c r="AX3" s="51"/>
+      <c r="AY3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="AZ3" s="49"/>
+      <c r="AZ3" s="51"/>
       <c r="BC3" s="1"/>
       <c r="BD3" s="5"/>
-      <c r="BE3" s="48" t="s">
+      <c r="BE3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="BF3" s="49"/>
-      <c r="BG3" s="48" t="s">
+      <c r="BF3" s="51"/>
+      <c r="BG3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="BH3" s="49"/>
-      <c r="BI3" s="48" t="s">
+      <c r="BH3" s="51"/>
+      <c r="BI3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="BJ3" s="49"/>
-      <c r="BK3" s="48" t="s">
+      <c r="BJ3" s="51"/>
+      <c r="BK3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="BL3" s="49"/>
-      <c r="BM3" s="48" t="s">
+      <c r="BL3" s="51"/>
+      <c r="BM3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="BN3" s="49"/>
+      <c r="BN3" s="51"/>
       <c r="BQ3" s="1"/>
       <c r="BR3" s="5"/>
-      <c r="BS3" s="48" t="s">
+      <c r="BS3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="BT3" s="49"/>
-      <c r="BU3" s="48" t="s">
+      <c r="BT3" s="51"/>
+      <c r="BU3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="BV3" s="49"/>
-      <c r="BW3" s="48" t="s">
+      <c r="BV3" s="51"/>
+      <c r="BW3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="BX3" s="49"/>
-      <c r="BY3" s="48" t="s">
+      <c r="BX3" s="51"/>
+      <c r="BY3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="BZ3" s="49"/>
-      <c r="CA3" s="48" t="s">
+      <c r="BZ3" s="51"/>
+      <c r="CA3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="CB3" s="49"/>
+      <c r="CB3" s="51"/>
     </row>
     <row r="4" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="6" t="s">
@@ -8135,7 +8135,7 @@
       </c>
     </row>
     <row r="5" spans="2:80" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="42" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -8171,7 +8171,7 @@
       <c r="M5" s="14">
         <v>82.58</v>
       </c>
-      <c r="AA5" s="42" t="s">
+      <c r="AA5" s="45" t="s">
         <v>13</v>
       </c>
       <c r="AB5" s="12" t="s">
@@ -8195,7 +8195,7 @@
       <c r="AL5" s="20">
         <v>19.14</v>
       </c>
-      <c r="AO5" s="42" t="s">
+      <c r="AO5" s="45" t="s">
         <v>13</v>
       </c>
       <c r="AP5" s="12" t="s">
@@ -8219,7 +8219,7 @@
       <c r="AZ5" s="20">
         <v>19.829999999999998</v>
       </c>
-      <c r="BC5" s="42" t="s">
+      <c r="BC5" s="45" t="s">
         <v>13</v>
       </c>
       <c r="BD5" s="12" t="s">
@@ -8243,7 +8243,7 @@
       <c r="BN5" s="20">
         <v>20.05</v>
       </c>
-      <c r="BQ5" s="42" t="s">
+      <c r="BQ5" s="45" t="s">
         <v>13</v>
       </c>
       <c r="BR5" s="12" t="s">
@@ -8393,7 +8393,7 @@
       </c>
     </row>
     <row r="7" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="53"/>
+      <c r="B7" s="44"/>
       <c r="C7" s="11" t="s">
         <v>12</v>
       </c>
@@ -8517,7 +8517,7 @@
       </c>
     </row>
     <row r="8" spans="2:80" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="45" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="12" t="s">
@@ -8553,7 +8553,7 @@
       <c r="M8" s="20">
         <v>19.09</v>
       </c>
-      <c r="AA8" s="44"/>
+      <c r="AA8" s="46"/>
       <c r="AB8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8575,7 +8575,7 @@
       <c r="AL8" s="22">
         <v>21.78</v>
       </c>
-      <c r="AO8" s="44"/>
+      <c r="AO8" s="46"/>
       <c r="AP8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8597,7 +8597,7 @@
       <c r="AZ8" s="22">
         <v>19.12</v>
       </c>
-      <c r="BC8" s="44"/>
+      <c r="BC8" s="46"/>
       <c r="BD8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8619,7 +8619,7 @@
       <c r="BN8" s="22">
         <v>19.13</v>
       </c>
-      <c r="BQ8" s="44"/>
+      <c r="BQ8" s="46"/>
       <c r="BR8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8715,7 +8715,7 @@
       </c>
     </row>
     <row r="11" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="44"/>
+      <c r="B11" s="46"/>
       <c r="C11" s="10" t="s">
         <v>14</v>
       </c>
@@ -8749,152 +8749,152 @@
       <c r="M11" s="22">
         <v>17.579999999999998</v>
       </c>
-      <c r="AA11" s="45" t="s">
+      <c r="AA11" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="AB11" s="46"/>
-      <c r="AC11" s="46"/>
-      <c r="AD11" s="46"/>
-      <c r="AE11" s="46"/>
-      <c r="AF11" s="46"/>
-      <c r="AG11" s="46"/>
-      <c r="AH11" s="46"/>
-      <c r="AI11" s="46"/>
-      <c r="AJ11" s="46"/>
-      <c r="AK11" s="46"/>
-      <c r="AL11" s="47"/>
-      <c r="AO11" s="45" t="s">
+      <c r="AB11" s="48"/>
+      <c r="AC11" s="48"/>
+      <c r="AD11" s="48"/>
+      <c r="AE11" s="48"/>
+      <c r="AF11" s="48"/>
+      <c r="AG11" s="48"/>
+      <c r="AH11" s="48"/>
+      <c r="AI11" s="48"/>
+      <c r="AJ11" s="48"/>
+      <c r="AK11" s="48"/>
+      <c r="AL11" s="49"/>
+      <c r="AO11" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="AP11" s="46"/>
-      <c r="AQ11" s="46"/>
-      <c r="AR11" s="46"/>
-      <c r="AS11" s="46"/>
-      <c r="AT11" s="46"/>
-      <c r="AU11" s="46"/>
-      <c r="AV11" s="46"/>
-      <c r="AW11" s="46"/>
-      <c r="AX11" s="46"/>
-      <c r="AY11" s="46"/>
-      <c r="AZ11" s="47"/>
-      <c r="BC11" s="45" t="s">
+      <c r="AP11" s="48"/>
+      <c r="AQ11" s="48"/>
+      <c r="AR11" s="48"/>
+      <c r="AS11" s="48"/>
+      <c r="AT11" s="48"/>
+      <c r="AU11" s="48"/>
+      <c r="AV11" s="48"/>
+      <c r="AW11" s="48"/>
+      <c r="AX11" s="48"/>
+      <c r="AY11" s="48"/>
+      <c r="AZ11" s="49"/>
+      <c r="BC11" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="BD11" s="46"/>
-      <c r="BE11" s="46"/>
-      <c r="BF11" s="46"/>
-      <c r="BG11" s="46"/>
-      <c r="BH11" s="46"/>
-      <c r="BI11" s="46"/>
-      <c r="BJ11" s="46"/>
-      <c r="BK11" s="46"/>
-      <c r="BL11" s="46"/>
-      <c r="BM11" s="46"/>
-      <c r="BN11" s="47"/>
-      <c r="BQ11" s="45" t="s">
+      <c r="BD11" s="48"/>
+      <c r="BE11" s="48"/>
+      <c r="BF11" s="48"/>
+      <c r="BG11" s="48"/>
+      <c r="BH11" s="48"/>
+      <c r="BI11" s="48"/>
+      <c r="BJ11" s="48"/>
+      <c r="BK11" s="48"/>
+      <c r="BL11" s="48"/>
+      <c r="BM11" s="48"/>
+      <c r="BN11" s="49"/>
+      <c r="BQ11" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="BR11" s="46"/>
-      <c r="BS11" s="46"/>
-      <c r="BT11" s="46"/>
-      <c r="BU11" s="46"/>
-      <c r="BV11" s="46"/>
-      <c r="BW11" s="46"/>
-      <c r="BX11" s="46"/>
-      <c r="BY11" s="46"/>
-      <c r="BZ11" s="46"/>
-      <c r="CA11" s="46"/>
-      <c r="CB11" s="47"/>
+      <c r="BR11" s="48"/>
+      <c r="BS11" s="48"/>
+      <c r="BT11" s="48"/>
+      <c r="BU11" s="48"/>
+      <c r="BV11" s="48"/>
+      <c r="BW11" s="48"/>
+      <c r="BX11" s="48"/>
+      <c r="BY11" s="48"/>
+      <c r="BZ11" s="48"/>
+      <c r="CA11" s="48"/>
+      <c r="CB11" s="49"/>
     </row>
     <row r="12" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="AA12" s="24"/>
       <c r="AB12" s="4"/>
-      <c r="AC12" s="48" t="s">
+      <c r="AC12" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="AD12" s="49"/>
-      <c r="AE12" s="48" t="s">
+      <c r="AD12" s="51"/>
+      <c r="AE12" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="AF12" s="49"/>
-      <c r="AG12" s="48" t="s">
+      <c r="AF12" s="51"/>
+      <c r="AG12" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="AH12" s="49"/>
-      <c r="AI12" s="48" t="s">
+      <c r="AH12" s="51"/>
+      <c r="AI12" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AJ12" s="49"/>
-      <c r="AK12" s="48" t="s">
+      <c r="AJ12" s="51"/>
+      <c r="AK12" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="AL12" s="49"/>
+      <c r="AL12" s="51"/>
       <c r="AO12" s="24"/>
       <c r="AP12" s="4"/>
-      <c r="AQ12" s="48" t="s">
+      <c r="AQ12" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="AR12" s="49"/>
-      <c r="AS12" s="48" t="s">
+      <c r="AR12" s="51"/>
+      <c r="AS12" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="AT12" s="49"/>
-      <c r="AU12" s="48" t="s">
+      <c r="AT12" s="51"/>
+      <c r="AU12" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="AV12" s="49"/>
-      <c r="AW12" s="48" t="s">
+      <c r="AV12" s="51"/>
+      <c r="AW12" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AX12" s="49"/>
-      <c r="AY12" s="48" t="s">
+      <c r="AX12" s="51"/>
+      <c r="AY12" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="AZ12" s="49"/>
+      <c r="AZ12" s="51"/>
       <c r="BC12" s="24"/>
       <c r="BD12" s="4"/>
-      <c r="BE12" s="48" t="s">
+      <c r="BE12" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="BF12" s="49"/>
-      <c r="BG12" s="48" t="s">
+      <c r="BF12" s="51"/>
+      <c r="BG12" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="BH12" s="49"/>
-      <c r="BI12" s="48" t="s">
+      <c r="BH12" s="51"/>
+      <c r="BI12" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="BJ12" s="49"/>
-      <c r="BK12" s="48" t="s">
+      <c r="BJ12" s="51"/>
+      <c r="BK12" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="BL12" s="49"/>
-      <c r="BM12" s="48" t="s">
+      <c r="BL12" s="51"/>
+      <c r="BM12" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="BN12" s="49"/>
+      <c r="BN12" s="51"/>
       <c r="BQ12" s="24"/>
       <c r="BR12" s="4"/>
-      <c r="BS12" s="48" t="s">
+      <c r="BS12" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="BT12" s="49"/>
-      <c r="BU12" s="48" t="s">
+      <c r="BT12" s="51"/>
+      <c r="BU12" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="BV12" s="49"/>
-      <c r="BW12" s="48" t="s">
+      <c r="BV12" s="51"/>
+      <c r="BW12" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="BX12" s="49"/>
-      <c r="BY12" s="48" t="s">
+      <c r="BX12" s="51"/>
+      <c r="BY12" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="BZ12" s="49"/>
-      <c r="CA12" s="48" t="s">
+      <c r="BZ12" s="51"/>
+      <c r="CA12" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="CB12" s="49"/>
+      <c r="CB12" s="51"/>
     </row>
     <row r="13" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="AA13" s="25" t="s">
@@ -9043,20 +9043,20 @@
       </c>
     </row>
     <row r="14" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="47"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="48"/>
+      <c r="M14" s="49"/>
       <c r="AA14" s="29" t="s">
         <v>24</v>
       </c>
@@ -9121,26 +9121,26 @@
     <row r="15" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="24"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="48" t="s">
+      <c r="D15" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="E15" s="49"/>
-      <c r="F15" s="48" t="s">
+      <c r="E15" s="51"/>
+      <c r="F15" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="49"/>
-      <c r="H15" s="48" t="s">
+      <c r="G15" s="51"/>
+      <c r="H15" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="49"/>
-      <c r="J15" s="48" t="s">
+      <c r="I15" s="51"/>
+      <c r="J15" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="49"/>
-      <c r="L15" s="48" t="s">
+      <c r="K15" s="51"/>
+      <c r="L15" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="M15" s="49"/>
+      <c r="M15" s="51"/>
       <c r="AA15" s="29" t="s">
         <v>39</v>
       </c>
@@ -11414,11 +11414,84 @@
     </row>
   </sheetData>
   <mergeCells count="91">
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="BS35:BT35"/>
+    <mergeCell ref="BU35:BV35"/>
+    <mergeCell ref="BW35:BX35"/>
+    <mergeCell ref="BY35:BZ35"/>
+    <mergeCell ref="CA35:CB35"/>
+    <mergeCell ref="BQ5:BQ8"/>
+    <mergeCell ref="BQ11:CB11"/>
+    <mergeCell ref="BS12:BT12"/>
+    <mergeCell ref="BU12:BV12"/>
+    <mergeCell ref="BW12:BX12"/>
+    <mergeCell ref="BY12:BZ12"/>
+    <mergeCell ref="CA12:CB12"/>
+    <mergeCell ref="BQ2:CB2"/>
+    <mergeCell ref="BS3:BT3"/>
+    <mergeCell ref="BU3:BV3"/>
+    <mergeCell ref="BW3:BX3"/>
+    <mergeCell ref="BY3:BZ3"/>
+    <mergeCell ref="CA3:CB3"/>
+    <mergeCell ref="BE35:BF35"/>
+    <mergeCell ref="BG35:BH35"/>
+    <mergeCell ref="BI35:BJ35"/>
+    <mergeCell ref="BK35:BL35"/>
+    <mergeCell ref="BM35:BN35"/>
+    <mergeCell ref="BC5:BC8"/>
+    <mergeCell ref="BC11:BN11"/>
+    <mergeCell ref="BE12:BF12"/>
+    <mergeCell ref="BG12:BH12"/>
+    <mergeCell ref="BI12:BJ12"/>
+    <mergeCell ref="BK12:BL12"/>
+    <mergeCell ref="BM12:BN12"/>
+    <mergeCell ref="BC2:BN2"/>
+    <mergeCell ref="BE3:BF3"/>
+    <mergeCell ref="BG3:BH3"/>
+    <mergeCell ref="BI3:BJ3"/>
+    <mergeCell ref="BK3:BL3"/>
+    <mergeCell ref="BM3:BN3"/>
+    <mergeCell ref="AQ35:AR35"/>
+    <mergeCell ref="AS35:AT35"/>
+    <mergeCell ref="AU35:AV35"/>
+    <mergeCell ref="AW35:AX35"/>
+    <mergeCell ref="AY35:AZ35"/>
+    <mergeCell ref="AO5:AO8"/>
+    <mergeCell ref="AO11:AZ11"/>
+    <mergeCell ref="AQ12:AR12"/>
+    <mergeCell ref="AS12:AT12"/>
+    <mergeCell ref="AU12:AV12"/>
+    <mergeCell ref="AW12:AX12"/>
+    <mergeCell ref="AY12:AZ12"/>
+    <mergeCell ref="AO2:AZ2"/>
+    <mergeCell ref="AQ3:AR3"/>
+    <mergeCell ref="AS3:AT3"/>
+    <mergeCell ref="AU3:AV3"/>
+    <mergeCell ref="AW3:AX3"/>
+    <mergeCell ref="AY3:AZ3"/>
+    <mergeCell ref="AC35:AD35"/>
+    <mergeCell ref="AE35:AF35"/>
+    <mergeCell ref="AG35:AH35"/>
+    <mergeCell ref="AI35:AJ35"/>
+    <mergeCell ref="AK35:AL35"/>
+    <mergeCell ref="AA5:AA8"/>
+    <mergeCell ref="AA11:AL11"/>
+    <mergeCell ref="AC12:AD12"/>
+    <mergeCell ref="AE12:AF12"/>
+    <mergeCell ref="AG12:AH12"/>
+    <mergeCell ref="AI12:AJ12"/>
+    <mergeCell ref="AK12:AL12"/>
+    <mergeCell ref="AA2:AL2"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="AG3:AH3"/>
+    <mergeCell ref="AI3:AJ3"/>
+    <mergeCell ref="AK3:AL3"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="B14:M14"/>
@@ -11427,84 +11500,11 @@
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="J15:K15"/>
     <mergeCell ref="L15:M15"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="AA2:AL2"/>
-    <mergeCell ref="AC3:AD3"/>
-    <mergeCell ref="AE3:AF3"/>
-    <mergeCell ref="AG3:AH3"/>
-    <mergeCell ref="AI3:AJ3"/>
-    <mergeCell ref="AK3:AL3"/>
-    <mergeCell ref="AA5:AA8"/>
-    <mergeCell ref="AA11:AL11"/>
-    <mergeCell ref="AC12:AD12"/>
-    <mergeCell ref="AE12:AF12"/>
-    <mergeCell ref="AG12:AH12"/>
-    <mergeCell ref="AI12:AJ12"/>
-    <mergeCell ref="AK12:AL12"/>
-    <mergeCell ref="AC35:AD35"/>
-    <mergeCell ref="AE35:AF35"/>
-    <mergeCell ref="AG35:AH35"/>
-    <mergeCell ref="AI35:AJ35"/>
-    <mergeCell ref="AK35:AL35"/>
-    <mergeCell ref="AO2:AZ2"/>
-    <mergeCell ref="AQ3:AR3"/>
-    <mergeCell ref="AS3:AT3"/>
-    <mergeCell ref="AU3:AV3"/>
-    <mergeCell ref="AW3:AX3"/>
-    <mergeCell ref="AY3:AZ3"/>
-    <mergeCell ref="AO5:AO8"/>
-    <mergeCell ref="AO11:AZ11"/>
-    <mergeCell ref="AQ12:AR12"/>
-    <mergeCell ref="AS12:AT12"/>
-    <mergeCell ref="AU12:AV12"/>
-    <mergeCell ref="AW12:AX12"/>
-    <mergeCell ref="AY12:AZ12"/>
-    <mergeCell ref="AQ35:AR35"/>
-    <mergeCell ref="AS35:AT35"/>
-    <mergeCell ref="AU35:AV35"/>
-    <mergeCell ref="AW35:AX35"/>
-    <mergeCell ref="AY35:AZ35"/>
-    <mergeCell ref="BC2:BN2"/>
-    <mergeCell ref="BE3:BF3"/>
-    <mergeCell ref="BG3:BH3"/>
-    <mergeCell ref="BI3:BJ3"/>
-    <mergeCell ref="BK3:BL3"/>
-    <mergeCell ref="BM3:BN3"/>
-    <mergeCell ref="BC5:BC8"/>
-    <mergeCell ref="BC11:BN11"/>
-    <mergeCell ref="BE12:BF12"/>
-    <mergeCell ref="BG12:BH12"/>
-    <mergeCell ref="BI12:BJ12"/>
-    <mergeCell ref="BK12:BL12"/>
-    <mergeCell ref="BM12:BN12"/>
-    <mergeCell ref="BE35:BF35"/>
-    <mergeCell ref="BG35:BH35"/>
-    <mergeCell ref="BI35:BJ35"/>
-    <mergeCell ref="BK35:BL35"/>
-    <mergeCell ref="BM35:BN35"/>
-    <mergeCell ref="BQ2:CB2"/>
-    <mergeCell ref="BS3:BT3"/>
-    <mergeCell ref="BU3:BV3"/>
-    <mergeCell ref="BW3:BX3"/>
-    <mergeCell ref="BY3:BZ3"/>
-    <mergeCell ref="CA3:CB3"/>
-    <mergeCell ref="BQ5:BQ8"/>
-    <mergeCell ref="BQ11:CB11"/>
-    <mergeCell ref="BS12:BT12"/>
-    <mergeCell ref="BU12:BV12"/>
-    <mergeCell ref="BW12:BX12"/>
-    <mergeCell ref="BY12:BZ12"/>
-    <mergeCell ref="CA12:CB12"/>
-    <mergeCell ref="BS35:BT35"/>
-    <mergeCell ref="BU35:BV35"/>
-    <mergeCell ref="BW35:BX35"/>
-    <mergeCell ref="BY35:BZ35"/>
-    <mergeCell ref="CA35:CB35"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="L38:M38"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Results_metrics.xlsx
+++ b/Results_metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Enrica\Desktop\Nuovo_ML_Project\MaskArchitectureAnomaly_CourseProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C961665-BCC3-42D3-9616-C489647191AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A776971-DE7D-47EC-B3F9-2C72D87D9871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11232" yWindow="0" windowWidth="11808" windowHeight="12072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -727,16 +727,10 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -762,6 +756,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2534,48 +2534,6 @@
                 <c:pt idx="6">
                   <c:v>25.8</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>3.84</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4.7699999999999996</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>6.37</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>7.68</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>7.94</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>7.97</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>7.91</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>7.86</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>7.82</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>7.79</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>7.77</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7.76</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7.75</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>7.74</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2721,48 +2679,6 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>14.93</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>31.17</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>31.85</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>32.71</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>34.82</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>34.950000000000003</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>34.31</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>34.03</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>34.380000000000003</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>34.520000000000003</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>34.729999999999997</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>34.99</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>35.090000000000003</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>35.18</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>35.24</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7769,188 +7685,188 @@
   <sheetData>
     <row r="1" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="53"/>
-      <c r="AA2" s="47" t="s">
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="51"/>
+      <c r="AA2" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="AB2" s="52"/>
-      <c r="AC2" s="52"/>
-      <c r="AD2" s="52"/>
-      <c r="AE2" s="52"/>
-      <c r="AF2" s="52"/>
-      <c r="AG2" s="52"/>
-      <c r="AH2" s="52"/>
-      <c r="AI2" s="52"/>
-      <c r="AJ2" s="52"/>
-      <c r="AK2" s="52"/>
-      <c r="AL2" s="53"/>
-      <c r="AO2" s="47" t="s">
+      <c r="AB2" s="50"/>
+      <c r="AC2" s="50"/>
+      <c r="AD2" s="50"/>
+      <c r="AE2" s="50"/>
+      <c r="AF2" s="50"/>
+      <c r="AG2" s="50"/>
+      <c r="AH2" s="50"/>
+      <c r="AI2" s="50"/>
+      <c r="AJ2" s="50"/>
+      <c r="AK2" s="50"/>
+      <c r="AL2" s="51"/>
+      <c r="AO2" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AP2" s="52"/>
-      <c r="AQ2" s="52"/>
-      <c r="AR2" s="52"/>
-      <c r="AS2" s="52"/>
-      <c r="AT2" s="52"/>
-      <c r="AU2" s="52"/>
-      <c r="AV2" s="52"/>
-      <c r="AW2" s="52"/>
-      <c r="AX2" s="52"/>
-      <c r="AY2" s="52"/>
-      <c r="AZ2" s="53"/>
-      <c r="BC2" s="47" t="s">
+      <c r="AP2" s="50"/>
+      <c r="AQ2" s="50"/>
+      <c r="AR2" s="50"/>
+      <c r="AS2" s="50"/>
+      <c r="AT2" s="50"/>
+      <c r="AU2" s="50"/>
+      <c r="AV2" s="50"/>
+      <c r="AW2" s="50"/>
+      <c r="AX2" s="50"/>
+      <c r="AY2" s="50"/>
+      <c r="AZ2" s="51"/>
+      <c r="BC2" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="BD2" s="52"/>
-      <c r="BE2" s="52"/>
-      <c r="BF2" s="52"/>
-      <c r="BG2" s="52"/>
-      <c r="BH2" s="52"/>
-      <c r="BI2" s="52"/>
-      <c r="BJ2" s="52"/>
-      <c r="BK2" s="52"/>
-      <c r="BL2" s="52"/>
-      <c r="BM2" s="52"/>
-      <c r="BN2" s="53"/>
-      <c r="BQ2" s="47" t="s">
+      <c r="BD2" s="50"/>
+      <c r="BE2" s="50"/>
+      <c r="BF2" s="50"/>
+      <c r="BG2" s="50"/>
+      <c r="BH2" s="50"/>
+      <c r="BI2" s="50"/>
+      <c r="BJ2" s="50"/>
+      <c r="BK2" s="50"/>
+      <c r="BL2" s="50"/>
+      <c r="BM2" s="50"/>
+      <c r="BN2" s="51"/>
+      <c r="BQ2" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="BR2" s="52"/>
-      <c r="BS2" s="52"/>
-      <c r="BT2" s="52"/>
-      <c r="BU2" s="52"/>
-      <c r="BV2" s="52"/>
-      <c r="BW2" s="52"/>
-      <c r="BX2" s="52"/>
-      <c r="BY2" s="52"/>
-      <c r="BZ2" s="52"/>
-      <c r="CA2" s="52"/>
-      <c r="CB2" s="53"/>
+      <c r="BR2" s="50"/>
+      <c r="BS2" s="50"/>
+      <c r="BT2" s="50"/>
+      <c r="BU2" s="50"/>
+      <c r="BV2" s="50"/>
+      <c r="BW2" s="50"/>
+      <c r="BX2" s="50"/>
+      <c r="BY2" s="50"/>
+      <c r="BZ2" s="50"/>
+      <c r="CA2" s="50"/>
+      <c r="CB2" s="51"/>
     </row>
     <row r="3" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
       <c r="C3" s="5"/>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50" t="s">
+      <c r="E3" s="49"/>
+      <c r="F3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="51"/>
-      <c r="H3" s="50" t="s">
+      <c r="G3" s="49"/>
+      <c r="H3" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="51"/>
-      <c r="J3" s="50" t="s">
+      <c r="I3" s="49"/>
+      <c r="J3" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="51"/>
-      <c r="L3" s="50" t="s">
+      <c r="K3" s="49"/>
+      <c r="L3" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="51"/>
+      <c r="M3" s="49"/>
       <c r="AA3" s="1"/>
       <c r="AB3" s="5"/>
-      <c r="AC3" s="50" t="s">
+      <c r="AC3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="AD3" s="51"/>
-      <c r="AE3" s="50" t="s">
+      <c r="AD3" s="49"/>
+      <c r="AE3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="AF3" s="51"/>
-      <c r="AG3" s="50" t="s">
+      <c r="AF3" s="49"/>
+      <c r="AG3" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="AH3" s="51"/>
-      <c r="AI3" s="50" t="s">
+      <c r="AH3" s="49"/>
+      <c r="AI3" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="AJ3" s="51"/>
-      <c r="AK3" s="50" t="s">
+      <c r="AJ3" s="49"/>
+      <c r="AK3" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="51"/>
+      <c r="AL3" s="49"/>
       <c r="AO3" s="1"/>
       <c r="AP3" s="5"/>
-      <c r="AQ3" s="50" t="s">
+      <c r="AQ3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="AR3" s="51"/>
-      <c r="AS3" s="50" t="s">
+      <c r="AR3" s="49"/>
+      <c r="AS3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="AT3" s="51"/>
-      <c r="AU3" s="50" t="s">
+      <c r="AT3" s="49"/>
+      <c r="AU3" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="AV3" s="51"/>
-      <c r="AW3" s="50" t="s">
+      <c r="AV3" s="49"/>
+      <c r="AW3" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="AX3" s="51"/>
-      <c r="AY3" s="50" t="s">
+      <c r="AX3" s="49"/>
+      <c r="AY3" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="AZ3" s="51"/>
+      <c r="AZ3" s="49"/>
       <c r="BC3" s="1"/>
       <c r="BD3" s="5"/>
-      <c r="BE3" s="50" t="s">
+      <c r="BE3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="BF3" s="51"/>
-      <c r="BG3" s="50" t="s">
+      <c r="BF3" s="49"/>
+      <c r="BG3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="BH3" s="51"/>
-      <c r="BI3" s="50" t="s">
+      <c r="BH3" s="49"/>
+      <c r="BI3" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="BJ3" s="51"/>
-      <c r="BK3" s="50" t="s">
+      <c r="BJ3" s="49"/>
+      <c r="BK3" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="BL3" s="51"/>
-      <c r="BM3" s="50" t="s">
+      <c r="BL3" s="49"/>
+      <c r="BM3" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="BN3" s="51"/>
+      <c r="BN3" s="49"/>
       <c r="BQ3" s="1"/>
       <c r="BR3" s="5"/>
-      <c r="BS3" s="50" t="s">
+      <c r="BS3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="BT3" s="51"/>
-      <c r="BU3" s="50" t="s">
+      <c r="BT3" s="49"/>
+      <c r="BU3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="BV3" s="51"/>
-      <c r="BW3" s="50" t="s">
+      <c r="BV3" s="49"/>
+      <c r="BW3" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="BX3" s="51"/>
-      <c r="BY3" s="50" t="s">
+      <c r="BX3" s="49"/>
+      <c r="BY3" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="BZ3" s="51"/>
-      <c r="CA3" s="50" t="s">
+      <c r="BZ3" s="49"/>
+      <c r="CA3" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="CB3" s="51"/>
+      <c r="CB3" s="49"/>
     </row>
     <row r="4" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="6" t="s">
@@ -8135,7 +8051,7 @@
       </c>
     </row>
     <row r="5" spans="2:80" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="52" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -8171,7 +8087,7 @@
       <c r="M5" s="14">
         <v>82.58</v>
       </c>
-      <c r="AA5" s="45" t="s">
+      <c r="AA5" s="42" t="s">
         <v>13</v>
       </c>
       <c r="AB5" s="12" t="s">
@@ -8195,7 +8111,7 @@
       <c r="AL5" s="20">
         <v>19.14</v>
       </c>
-      <c r="AO5" s="45" t="s">
+      <c r="AO5" s="42" t="s">
         <v>13</v>
       </c>
       <c r="AP5" s="12" t="s">
@@ -8219,7 +8135,7 @@
       <c r="AZ5" s="20">
         <v>19.829999999999998</v>
       </c>
-      <c r="BC5" s="45" t="s">
+      <c r="BC5" s="42" t="s">
         <v>13</v>
       </c>
       <c r="BD5" s="12" t="s">
@@ -8243,7 +8159,7 @@
       <c r="BN5" s="20">
         <v>20.05</v>
       </c>
-      <c r="BQ5" s="45" t="s">
+      <c r="BQ5" s="42" t="s">
         <v>13</v>
       </c>
       <c r="BR5" s="12" t="s">
@@ -8393,7 +8309,7 @@
       </c>
     </row>
     <row r="7" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="44"/>
+      <c r="B7" s="53"/>
       <c r="C7" s="11" t="s">
         <v>12</v>
       </c>
@@ -8517,7 +8433,7 @@
       </c>
     </row>
     <row r="8" spans="2:80" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="42" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="12" t="s">
@@ -8553,7 +8469,7 @@
       <c r="M8" s="20">
         <v>19.09</v>
       </c>
-      <c r="AA8" s="46"/>
+      <c r="AA8" s="44"/>
       <c r="AB8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8575,7 +8491,7 @@
       <c r="AL8" s="22">
         <v>21.78</v>
       </c>
-      <c r="AO8" s="46"/>
+      <c r="AO8" s="44"/>
       <c r="AP8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8597,7 +8513,7 @@
       <c r="AZ8" s="22">
         <v>19.12</v>
       </c>
-      <c r="BC8" s="46"/>
+      <c r="BC8" s="44"/>
       <c r="BD8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8619,7 +8535,7 @@
       <c r="BN8" s="22">
         <v>19.13</v>
       </c>
-      <c r="BQ8" s="46"/>
+      <c r="BQ8" s="44"/>
       <c r="BR8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8715,7 +8631,7 @@
       </c>
     </row>
     <row r="11" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="46"/>
+      <c r="B11" s="44"/>
       <c r="C11" s="10" t="s">
         <v>14</v>
       </c>
@@ -8749,152 +8665,152 @@
       <c r="M11" s="22">
         <v>17.579999999999998</v>
       </c>
-      <c r="AA11" s="47" t="s">
+      <c r="AA11" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="AB11" s="48"/>
-      <c r="AC11" s="48"/>
-      <c r="AD11" s="48"/>
-      <c r="AE11" s="48"/>
-      <c r="AF11" s="48"/>
-      <c r="AG11" s="48"/>
-      <c r="AH11" s="48"/>
-      <c r="AI11" s="48"/>
-      <c r="AJ11" s="48"/>
-      <c r="AK11" s="48"/>
-      <c r="AL11" s="49"/>
-      <c r="AO11" s="47" t="s">
+      <c r="AB11" s="46"/>
+      <c r="AC11" s="46"/>
+      <c r="AD11" s="46"/>
+      <c r="AE11" s="46"/>
+      <c r="AF11" s="46"/>
+      <c r="AG11" s="46"/>
+      <c r="AH11" s="46"/>
+      <c r="AI11" s="46"/>
+      <c r="AJ11" s="46"/>
+      <c r="AK11" s="46"/>
+      <c r="AL11" s="47"/>
+      <c r="AO11" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="AP11" s="48"/>
-      <c r="AQ11" s="48"/>
-      <c r="AR11" s="48"/>
-      <c r="AS11" s="48"/>
-      <c r="AT11" s="48"/>
-      <c r="AU11" s="48"/>
-      <c r="AV11" s="48"/>
-      <c r="AW11" s="48"/>
-      <c r="AX11" s="48"/>
-      <c r="AY11" s="48"/>
-      <c r="AZ11" s="49"/>
-      <c r="BC11" s="47" t="s">
+      <c r="AP11" s="46"/>
+      <c r="AQ11" s="46"/>
+      <c r="AR11" s="46"/>
+      <c r="AS11" s="46"/>
+      <c r="AT11" s="46"/>
+      <c r="AU11" s="46"/>
+      <c r="AV11" s="46"/>
+      <c r="AW11" s="46"/>
+      <c r="AX11" s="46"/>
+      <c r="AY11" s="46"/>
+      <c r="AZ11" s="47"/>
+      <c r="BC11" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="BD11" s="48"/>
-      <c r="BE11" s="48"/>
-      <c r="BF11" s="48"/>
-      <c r="BG11" s="48"/>
-      <c r="BH11" s="48"/>
-      <c r="BI11" s="48"/>
-      <c r="BJ11" s="48"/>
-      <c r="BK11" s="48"/>
-      <c r="BL11" s="48"/>
-      <c r="BM11" s="48"/>
-      <c r="BN11" s="49"/>
-      <c r="BQ11" s="47" t="s">
+      <c r="BD11" s="46"/>
+      <c r="BE11" s="46"/>
+      <c r="BF11" s="46"/>
+      <c r="BG11" s="46"/>
+      <c r="BH11" s="46"/>
+      <c r="BI11" s="46"/>
+      <c r="BJ11" s="46"/>
+      <c r="BK11" s="46"/>
+      <c r="BL11" s="46"/>
+      <c r="BM11" s="46"/>
+      <c r="BN11" s="47"/>
+      <c r="BQ11" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="BR11" s="48"/>
-      <c r="BS11" s="48"/>
-      <c r="BT11" s="48"/>
-      <c r="BU11" s="48"/>
-      <c r="BV11" s="48"/>
-      <c r="BW11" s="48"/>
-      <c r="BX11" s="48"/>
-      <c r="BY11" s="48"/>
-      <c r="BZ11" s="48"/>
-      <c r="CA11" s="48"/>
-      <c r="CB11" s="49"/>
+      <c r="BR11" s="46"/>
+      <c r="BS11" s="46"/>
+      <c r="BT11" s="46"/>
+      <c r="BU11" s="46"/>
+      <c r="BV11" s="46"/>
+      <c r="BW11" s="46"/>
+      <c r="BX11" s="46"/>
+      <c r="BY11" s="46"/>
+      <c r="BZ11" s="46"/>
+      <c r="CA11" s="46"/>
+      <c r="CB11" s="47"/>
     </row>
     <row r="12" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="AA12" s="24"/>
       <c r="AB12" s="4"/>
-      <c r="AC12" s="50" t="s">
+      <c r="AC12" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="AD12" s="51"/>
-      <c r="AE12" s="50" t="s">
+      <c r="AD12" s="49"/>
+      <c r="AE12" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="AF12" s="51"/>
-      <c r="AG12" s="50" t="s">
+      <c r="AF12" s="49"/>
+      <c r="AG12" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="AH12" s="51"/>
-      <c r="AI12" s="50" t="s">
+      <c r="AH12" s="49"/>
+      <c r="AI12" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="AJ12" s="51"/>
-      <c r="AK12" s="50" t="s">
+      <c r="AJ12" s="49"/>
+      <c r="AK12" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="AL12" s="51"/>
+      <c r="AL12" s="49"/>
       <c r="AO12" s="24"/>
       <c r="AP12" s="4"/>
-      <c r="AQ12" s="50" t="s">
+      <c r="AQ12" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="AR12" s="51"/>
-      <c r="AS12" s="50" t="s">
+      <c r="AR12" s="49"/>
+      <c r="AS12" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="AT12" s="51"/>
-      <c r="AU12" s="50" t="s">
+      <c r="AT12" s="49"/>
+      <c r="AU12" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="AV12" s="51"/>
-      <c r="AW12" s="50" t="s">
+      <c r="AV12" s="49"/>
+      <c r="AW12" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="AX12" s="51"/>
-      <c r="AY12" s="50" t="s">
+      <c r="AX12" s="49"/>
+      <c r="AY12" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="AZ12" s="51"/>
+      <c r="AZ12" s="49"/>
       <c r="BC12" s="24"/>
       <c r="BD12" s="4"/>
-      <c r="BE12" s="50" t="s">
+      <c r="BE12" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="BF12" s="51"/>
-      <c r="BG12" s="50" t="s">
+      <c r="BF12" s="49"/>
+      <c r="BG12" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="BH12" s="51"/>
-      <c r="BI12" s="50" t="s">
+      <c r="BH12" s="49"/>
+      <c r="BI12" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="BJ12" s="51"/>
-      <c r="BK12" s="50" t="s">
+      <c r="BJ12" s="49"/>
+      <c r="BK12" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="BL12" s="51"/>
-      <c r="BM12" s="50" t="s">
+      <c r="BL12" s="49"/>
+      <c r="BM12" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="BN12" s="51"/>
+      <c r="BN12" s="49"/>
       <c r="BQ12" s="24"/>
       <c r="BR12" s="4"/>
-      <c r="BS12" s="50" t="s">
+      <c r="BS12" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="BT12" s="51"/>
-      <c r="BU12" s="50" t="s">
+      <c r="BT12" s="49"/>
+      <c r="BU12" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="BV12" s="51"/>
-      <c r="BW12" s="50" t="s">
+      <c r="BV12" s="49"/>
+      <c r="BW12" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="BX12" s="51"/>
-      <c r="BY12" s="50" t="s">
+      <c r="BX12" s="49"/>
+      <c r="BY12" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="BZ12" s="51"/>
-      <c r="CA12" s="50" t="s">
+      <c r="BZ12" s="49"/>
+      <c r="CA12" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="CB12" s="51"/>
+      <c r="CB12" s="49"/>
     </row>
     <row r="13" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="AA13" s="25" t="s">
@@ -9043,20 +8959,20 @@
       </c>
     </row>
     <row r="14" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="47" t="s">
+      <c r="B14" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="48"/>
-      <c r="L14" s="48"/>
-      <c r="M14" s="49"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="47"/>
       <c r="AA14" s="29" t="s">
         <v>24</v>
       </c>
@@ -9121,26 +9037,26 @@
     <row r="15" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="24"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="50" t="s">
+      <c r="D15" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="E15" s="51"/>
-      <c r="F15" s="50" t="s">
+      <c r="E15" s="49"/>
+      <c r="F15" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="51"/>
-      <c r="H15" s="50" t="s">
+      <c r="G15" s="49"/>
+      <c r="H15" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="51"/>
-      <c r="J15" s="50" t="s">
+      <c r="I15" s="49"/>
+      <c r="J15" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="51"/>
-      <c r="L15" s="50" t="s">
+      <c r="K15" s="49"/>
+      <c r="L15" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="M15" s="51"/>
+      <c r="M15" s="49"/>
       <c r="AA15" s="29" t="s">
         <v>39</v>
       </c>
@@ -9951,12 +9867,8 @@
       <c r="G24" s="30">
         <v>0.68</v>
       </c>
-      <c r="H24" s="30">
-        <v>3.84</v>
-      </c>
-      <c r="I24" s="30">
-        <v>31.17</v>
-      </c>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
       <c r="J24" s="30">
         <v>54.66</v>
       </c>
@@ -10075,12 +9987,8 @@
       <c r="G25" s="30">
         <v>100</v>
       </c>
-      <c r="H25" s="30">
-        <v>4.7699999999999996</v>
-      </c>
-      <c r="I25" s="30">
-        <v>31.85</v>
-      </c>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
       <c r="J25" s="30">
         <v>54.68</v>
       </c>
@@ -10200,12 +10108,8 @@
       <c r="G26" s="30">
         <v>100</v>
       </c>
-      <c r="H26" s="30">
-        <v>6.37</v>
-      </c>
-      <c r="I26" s="30">
-        <v>32.71</v>
-      </c>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
       <c r="J26" s="30">
         <v>54.32</v>
       </c>
@@ -10292,12 +10196,8 @@
       <c r="G27" s="30">
         <v>100</v>
       </c>
-      <c r="H27" s="30">
-        <v>7.68</v>
-      </c>
-      <c r="I27" s="30">
-        <v>34.82</v>
-      </c>
+      <c r="H27" s="30"/>
+      <c r="I27" s="30"/>
       <c r="J27" s="30">
         <v>53.61</v>
       </c>
@@ -10416,12 +10316,8 @@
       <c r="G28" s="30">
         <v>100</v>
       </c>
-      <c r="H28" s="30">
-        <v>7.94</v>
-      </c>
-      <c r="I28" s="30">
-        <v>34.950000000000003</v>
-      </c>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
       <c r="J28" s="30">
         <v>53.44</v>
       </c>
@@ -10508,12 +10404,8 @@
       <c r="G29" s="30">
         <v>100</v>
       </c>
-      <c r="H29" s="30">
-        <v>7.97</v>
-      </c>
-      <c r="I29" s="30">
-        <v>34.31</v>
-      </c>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
       <c r="J29" s="30">
         <v>53.61</v>
       </c>
@@ -10632,12 +10524,8 @@
       <c r="G30" s="30">
         <v>100</v>
       </c>
-      <c r="H30" s="30">
-        <v>7.91</v>
-      </c>
-      <c r="I30" s="30">
-        <v>34.03</v>
-      </c>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
       <c r="J30" s="30">
         <v>54.17</v>
       </c>
@@ -10756,12 +10644,8 @@
       <c r="G31" s="30">
         <v>100</v>
       </c>
-      <c r="H31" s="30">
-        <v>7.86</v>
-      </c>
-      <c r="I31" s="30">
-        <v>34.380000000000003</v>
-      </c>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
       <c r="J31" s="30">
         <v>54.55</v>
       </c>
@@ -10880,12 +10764,8 @@
       <c r="G32" s="30">
         <v>100</v>
       </c>
-      <c r="H32" s="30">
-        <v>7.82</v>
-      </c>
-      <c r="I32" s="30">
-        <v>34.520000000000003</v>
-      </c>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
       <c r="J32" s="30">
         <v>54.78</v>
       </c>
@@ -11004,12 +10884,8 @@
       <c r="G33" s="30">
         <v>100</v>
       </c>
-      <c r="H33" s="30">
-        <v>7.79</v>
-      </c>
-      <c r="I33" s="30">
-        <v>34.729999999999997</v>
-      </c>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
       <c r="J33" s="30">
         <v>54.93</v>
       </c>
@@ -11128,12 +11004,8 @@
       <c r="G34" s="30">
         <v>100</v>
       </c>
-      <c r="H34" s="30">
-        <v>7.77</v>
-      </c>
-      <c r="I34" s="30">
-        <v>34.99</v>
-      </c>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
       <c r="J34" s="30">
         <v>55.02</v>
       </c>
@@ -11252,12 +11124,8 @@
       <c r="G35" s="30">
         <v>100</v>
       </c>
-      <c r="H35" s="30">
-        <v>7.76</v>
-      </c>
-      <c r="I35" s="30">
-        <v>35.090000000000003</v>
-      </c>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
       <c r="J35" s="30">
         <v>55.08</v>
       </c>
@@ -11340,12 +11208,8 @@
       <c r="G36" s="30">
         <v>100</v>
       </c>
-      <c r="H36" s="30">
-        <v>7.75</v>
-      </c>
-      <c r="I36" s="30">
-        <v>35.18</v>
-      </c>
+      <c r="H36" s="30"/>
+      <c r="I36" s="30"/>
       <c r="J36" s="30">
         <v>55.12</v>
       </c>
@@ -11376,12 +11240,8 @@
       <c r="G37" s="30">
         <v>100</v>
       </c>
-      <c r="H37" s="30">
-        <v>7.74</v>
-      </c>
-      <c r="I37" s="30">
-        <v>35.24</v>
-      </c>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
       <c r="J37" s="30">
         <v>55.15</v>
       </c>
@@ -11414,84 +11274,11 @@
     </row>
   </sheetData>
   <mergeCells count="91">
-    <mergeCell ref="BS35:BT35"/>
-    <mergeCell ref="BU35:BV35"/>
-    <mergeCell ref="BW35:BX35"/>
-    <mergeCell ref="BY35:BZ35"/>
-    <mergeCell ref="CA35:CB35"/>
-    <mergeCell ref="BQ5:BQ8"/>
-    <mergeCell ref="BQ11:CB11"/>
-    <mergeCell ref="BS12:BT12"/>
-    <mergeCell ref="BU12:BV12"/>
-    <mergeCell ref="BW12:BX12"/>
-    <mergeCell ref="BY12:BZ12"/>
-    <mergeCell ref="CA12:CB12"/>
-    <mergeCell ref="BQ2:CB2"/>
-    <mergeCell ref="BS3:BT3"/>
-    <mergeCell ref="BU3:BV3"/>
-    <mergeCell ref="BW3:BX3"/>
-    <mergeCell ref="BY3:BZ3"/>
-    <mergeCell ref="CA3:CB3"/>
-    <mergeCell ref="BE35:BF35"/>
-    <mergeCell ref="BG35:BH35"/>
-    <mergeCell ref="BI35:BJ35"/>
-    <mergeCell ref="BK35:BL35"/>
-    <mergeCell ref="BM35:BN35"/>
-    <mergeCell ref="BC5:BC8"/>
-    <mergeCell ref="BC11:BN11"/>
-    <mergeCell ref="BE12:BF12"/>
-    <mergeCell ref="BG12:BH12"/>
-    <mergeCell ref="BI12:BJ12"/>
-    <mergeCell ref="BK12:BL12"/>
-    <mergeCell ref="BM12:BN12"/>
-    <mergeCell ref="BC2:BN2"/>
-    <mergeCell ref="BE3:BF3"/>
-    <mergeCell ref="BG3:BH3"/>
-    <mergeCell ref="BI3:BJ3"/>
-    <mergeCell ref="BK3:BL3"/>
-    <mergeCell ref="BM3:BN3"/>
-    <mergeCell ref="AQ35:AR35"/>
-    <mergeCell ref="AS35:AT35"/>
-    <mergeCell ref="AU35:AV35"/>
-    <mergeCell ref="AW35:AX35"/>
-    <mergeCell ref="AY35:AZ35"/>
-    <mergeCell ref="AO5:AO8"/>
-    <mergeCell ref="AO11:AZ11"/>
-    <mergeCell ref="AQ12:AR12"/>
-    <mergeCell ref="AS12:AT12"/>
-    <mergeCell ref="AU12:AV12"/>
-    <mergeCell ref="AW12:AX12"/>
-    <mergeCell ref="AY12:AZ12"/>
-    <mergeCell ref="AO2:AZ2"/>
-    <mergeCell ref="AQ3:AR3"/>
-    <mergeCell ref="AS3:AT3"/>
-    <mergeCell ref="AU3:AV3"/>
-    <mergeCell ref="AW3:AX3"/>
-    <mergeCell ref="AY3:AZ3"/>
-    <mergeCell ref="AC35:AD35"/>
-    <mergeCell ref="AE35:AF35"/>
-    <mergeCell ref="AG35:AH35"/>
-    <mergeCell ref="AI35:AJ35"/>
-    <mergeCell ref="AK35:AL35"/>
-    <mergeCell ref="AA5:AA8"/>
-    <mergeCell ref="AA11:AL11"/>
-    <mergeCell ref="AC12:AD12"/>
-    <mergeCell ref="AE12:AF12"/>
-    <mergeCell ref="AG12:AH12"/>
-    <mergeCell ref="AI12:AJ12"/>
-    <mergeCell ref="AK12:AL12"/>
-    <mergeCell ref="AA2:AL2"/>
-    <mergeCell ref="AC3:AD3"/>
-    <mergeCell ref="AE3:AF3"/>
-    <mergeCell ref="AG3:AH3"/>
-    <mergeCell ref="AI3:AJ3"/>
-    <mergeCell ref="AK3:AL3"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="L38:M38"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="B14:M14"/>
@@ -11500,11 +11287,84 @@
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="J15:K15"/>
     <mergeCell ref="L15:M15"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="AA2:AL2"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="AG3:AH3"/>
+    <mergeCell ref="AI3:AJ3"/>
+    <mergeCell ref="AK3:AL3"/>
+    <mergeCell ref="AA5:AA8"/>
+    <mergeCell ref="AA11:AL11"/>
+    <mergeCell ref="AC12:AD12"/>
+    <mergeCell ref="AE12:AF12"/>
+    <mergeCell ref="AG12:AH12"/>
+    <mergeCell ref="AI12:AJ12"/>
+    <mergeCell ref="AK12:AL12"/>
+    <mergeCell ref="AC35:AD35"/>
+    <mergeCell ref="AE35:AF35"/>
+    <mergeCell ref="AG35:AH35"/>
+    <mergeCell ref="AI35:AJ35"/>
+    <mergeCell ref="AK35:AL35"/>
+    <mergeCell ref="AO2:AZ2"/>
+    <mergeCell ref="AQ3:AR3"/>
+    <mergeCell ref="AS3:AT3"/>
+    <mergeCell ref="AU3:AV3"/>
+    <mergeCell ref="AW3:AX3"/>
+    <mergeCell ref="AY3:AZ3"/>
+    <mergeCell ref="AO5:AO8"/>
+    <mergeCell ref="AO11:AZ11"/>
+    <mergeCell ref="AQ12:AR12"/>
+    <mergeCell ref="AS12:AT12"/>
+    <mergeCell ref="AU12:AV12"/>
+    <mergeCell ref="AW12:AX12"/>
+    <mergeCell ref="AY12:AZ12"/>
+    <mergeCell ref="AQ35:AR35"/>
+    <mergeCell ref="AS35:AT35"/>
+    <mergeCell ref="AU35:AV35"/>
+    <mergeCell ref="AW35:AX35"/>
+    <mergeCell ref="AY35:AZ35"/>
+    <mergeCell ref="BC2:BN2"/>
+    <mergeCell ref="BE3:BF3"/>
+    <mergeCell ref="BG3:BH3"/>
+    <mergeCell ref="BI3:BJ3"/>
+    <mergeCell ref="BK3:BL3"/>
+    <mergeCell ref="BM3:BN3"/>
+    <mergeCell ref="BC5:BC8"/>
+    <mergeCell ref="BC11:BN11"/>
+    <mergeCell ref="BE12:BF12"/>
+    <mergeCell ref="BG12:BH12"/>
+    <mergeCell ref="BI12:BJ12"/>
+    <mergeCell ref="BK12:BL12"/>
+    <mergeCell ref="BM12:BN12"/>
+    <mergeCell ref="BE35:BF35"/>
+    <mergeCell ref="BG35:BH35"/>
+    <mergeCell ref="BI35:BJ35"/>
+    <mergeCell ref="BK35:BL35"/>
+    <mergeCell ref="BM35:BN35"/>
+    <mergeCell ref="BQ2:CB2"/>
+    <mergeCell ref="BS3:BT3"/>
+    <mergeCell ref="BU3:BV3"/>
+    <mergeCell ref="BW3:BX3"/>
+    <mergeCell ref="BY3:BZ3"/>
+    <mergeCell ref="CA3:CB3"/>
+    <mergeCell ref="BQ5:BQ8"/>
+    <mergeCell ref="BQ11:CB11"/>
+    <mergeCell ref="BS12:BT12"/>
+    <mergeCell ref="BU12:BV12"/>
+    <mergeCell ref="BW12:BX12"/>
+    <mergeCell ref="BY12:BZ12"/>
+    <mergeCell ref="CA12:CB12"/>
+    <mergeCell ref="BS35:BT35"/>
+    <mergeCell ref="BU35:BV35"/>
+    <mergeCell ref="BW35:BX35"/>
+    <mergeCell ref="BY35:BZ35"/>
+    <mergeCell ref="CA35:CB35"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Results_metrics.xlsx
+++ b/Results_metrics.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Enrica\Desktop\Nuovo_ML_Project\MaskArchitectureAnomaly_CourseProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aless\OneDrive\Desktop\MaskArchitectureAnomaly_CourseProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A776971-DE7D-47EC-B3F9-2C72D87D9871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51BA8912-0CF5-4B29-A165-4C2B8D6A4791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11232" yWindow="0" windowWidth="11808" windowHeight="12072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -177,7 +177,7 @@
     <t>81.7%</t>
   </si>
   <si>
-    <t>t = 0,2</t>
+    <t>t = 0,275</t>
   </si>
 </sst>
 </file>
@@ -727,10 +727,16 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -756,12 +762,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -907,7 +907,7 @@
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>t = 0,2</c:v>
+                  <c:v>t = 0,275</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
@@ -1095,7 +1095,7 @@
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>t = 0,2</c:v>
+                  <c:v>t = 0,275</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
@@ -1676,7 +1676,7 @@
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>t = 0,2</c:v>
+                  <c:v>t = 0,275</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
@@ -1864,7 +1864,7 @@
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>t = 0,2</c:v>
+                  <c:v>t = 0,275</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
@@ -2445,7 +2445,7 @@
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>t = 0,2</c:v>
+                  <c:v>t = 0,275</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
@@ -2591,7 +2591,7 @@
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>t = 0,2</c:v>
+                  <c:v>t = 0,275</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
@@ -3130,7 +3130,7 @@
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>t = 0,2</c:v>
+                  <c:v>t = 0,275</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
@@ -3318,7 +3318,7 @@
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>t = 0,2</c:v>
+                  <c:v>t = 0,275</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
@@ -3899,7 +3899,7 @@
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>t = 0,2</c:v>
+                  <c:v>t = 0,275</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
@@ -4069,7 +4069,7 @@
                   <c:v>t = 0,1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>t = 0,2</c:v>
+                  <c:v>t = 0,275</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>t = 0,5</c:v>
@@ -7685,188 +7685,188 @@
   <sheetData>
     <row r="1" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="51"/>
-      <c r="AA2" s="45" t="s">
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="53"/>
+      <c r="AA2" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="AB2" s="50"/>
-      <c r="AC2" s="50"/>
-      <c r="AD2" s="50"/>
-      <c r="AE2" s="50"/>
-      <c r="AF2" s="50"/>
-      <c r="AG2" s="50"/>
-      <c r="AH2" s="50"/>
-      <c r="AI2" s="50"/>
-      <c r="AJ2" s="50"/>
-      <c r="AK2" s="50"/>
-      <c r="AL2" s="51"/>
-      <c r="AO2" s="45" t="s">
+      <c r="AB2" s="52"/>
+      <c r="AC2" s="52"/>
+      <c r="AD2" s="52"/>
+      <c r="AE2" s="52"/>
+      <c r="AF2" s="52"/>
+      <c r="AG2" s="52"/>
+      <c r="AH2" s="52"/>
+      <c r="AI2" s="52"/>
+      <c r="AJ2" s="52"/>
+      <c r="AK2" s="52"/>
+      <c r="AL2" s="53"/>
+      <c r="AO2" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="AP2" s="50"/>
-      <c r="AQ2" s="50"/>
-      <c r="AR2" s="50"/>
-      <c r="AS2" s="50"/>
-      <c r="AT2" s="50"/>
-      <c r="AU2" s="50"/>
-      <c r="AV2" s="50"/>
-      <c r="AW2" s="50"/>
-      <c r="AX2" s="50"/>
-      <c r="AY2" s="50"/>
-      <c r="AZ2" s="51"/>
-      <c r="BC2" s="45" t="s">
+      <c r="AP2" s="52"/>
+      <c r="AQ2" s="52"/>
+      <c r="AR2" s="52"/>
+      <c r="AS2" s="52"/>
+      <c r="AT2" s="52"/>
+      <c r="AU2" s="52"/>
+      <c r="AV2" s="52"/>
+      <c r="AW2" s="52"/>
+      <c r="AX2" s="52"/>
+      <c r="AY2" s="52"/>
+      <c r="AZ2" s="53"/>
+      <c r="BC2" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="BD2" s="50"/>
-      <c r="BE2" s="50"/>
-      <c r="BF2" s="50"/>
-      <c r="BG2" s="50"/>
-      <c r="BH2" s="50"/>
-      <c r="BI2" s="50"/>
-      <c r="BJ2" s="50"/>
-      <c r="BK2" s="50"/>
-      <c r="BL2" s="50"/>
-      <c r="BM2" s="50"/>
-      <c r="BN2" s="51"/>
-      <c r="BQ2" s="45" t="s">
+      <c r="BD2" s="52"/>
+      <c r="BE2" s="52"/>
+      <c r="BF2" s="52"/>
+      <c r="BG2" s="52"/>
+      <c r="BH2" s="52"/>
+      <c r="BI2" s="52"/>
+      <c r="BJ2" s="52"/>
+      <c r="BK2" s="52"/>
+      <c r="BL2" s="52"/>
+      <c r="BM2" s="52"/>
+      <c r="BN2" s="53"/>
+      <c r="BQ2" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="BR2" s="50"/>
-      <c r="BS2" s="50"/>
-      <c r="BT2" s="50"/>
-      <c r="BU2" s="50"/>
-      <c r="BV2" s="50"/>
-      <c r="BW2" s="50"/>
-      <c r="BX2" s="50"/>
-      <c r="BY2" s="50"/>
-      <c r="BZ2" s="50"/>
-      <c r="CA2" s="50"/>
-      <c r="CB2" s="51"/>
+      <c r="BR2" s="52"/>
+      <c r="BS2" s="52"/>
+      <c r="BT2" s="52"/>
+      <c r="BU2" s="52"/>
+      <c r="BV2" s="52"/>
+      <c r="BW2" s="52"/>
+      <c r="BX2" s="52"/>
+      <c r="BY2" s="52"/>
+      <c r="BZ2" s="52"/>
+      <c r="CA2" s="52"/>
+      <c r="CB2" s="53"/>
     </row>
     <row r="3" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
       <c r="C3" s="5"/>
-      <c r="D3" s="48" t="s">
+      <c r="D3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="49"/>
-      <c r="F3" s="48" t="s">
+      <c r="E3" s="51"/>
+      <c r="F3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="49"/>
-      <c r="H3" s="48" t="s">
+      <c r="G3" s="51"/>
+      <c r="H3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="49"/>
-      <c r="J3" s="48" t="s">
+      <c r="I3" s="51"/>
+      <c r="J3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="49"/>
-      <c r="L3" s="48" t="s">
+      <c r="K3" s="51"/>
+      <c r="L3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="49"/>
+      <c r="M3" s="51"/>
       <c r="AA3" s="1"/>
       <c r="AB3" s="5"/>
-      <c r="AC3" s="48" t="s">
+      <c r="AC3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="AD3" s="49"/>
-      <c r="AE3" s="48" t="s">
+      <c r="AD3" s="51"/>
+      <c r="AE3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="AF3" s="49"/>
-      <c r="AG3" s="48" t="s">
+      <c r="AF3" s="51"/>
+      <c r="AG3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="AH3" s="49"/>
-      <c r="AI3" s="48" t="s">
+      <c r="AH3" s="51"/>
+      <c r="AI3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AJ3" s="49"/>
-      <c r="AK3" s="48" t="s">
+      <c r="AJ3" s="51"/>
+      <c r="AK3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="49"/>
+      <c r="AL3" s="51"/>
       <c r="AO3" s="1"/>
       <c r="AP3" s="5"/>
-      <c r="AQ3" s="48" t="s">
+      <c r="AQ3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="AR3" s="49"/>
-      <c r="AS3" s="48" t="s">
+      <c r="AR3" s="51"/>
+      <c r="AS3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="AT3" s="49"/>
-      <c r="AU3" s="48" t="s">
+      <c r="AT3" s="51"/>
+      <c r="AU3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="AV3" s="49"/>
-      <c r="AW3" s="48" t="s">
+      <c r="AV3" s="51"/>
+      <c r="AW3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AX3" s="49"/>
-      <c r="AY3" s="48" t="s">
+      <c r="AX3" s="51"/>
+      <c r="AY3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="AZ3" s="49"/>
+      <c r="AZ3" s="51"/>
       <c r="BC3" s="1"/>
       <c r="BD3" s="5"/>
-      <c r="BE3" s="48" t="s">
+      <c r="BE3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="BF3" s="49"/>
-      <c r="BG3" s="48" t="s">
+      <c r="BF3" s="51"/>
+      <c r="BG3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="BH3" s="49"/>
-      <c r="BI3" s="48" t="s">
+      <c r="BH3" s="51"/>
+      <c r="BI3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="BJ3" s="49"/>
-      <c r="BK3" s="48" t="s">
+      <c r="BJ3" s="51"/>
+      <c r="BK3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="BL3" s="49"/>
-      <c r="BM3" s="48" t="s">
+      <c r="BL3" s="51"/>
+      <c r="BM3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="BN3" s="49"/>
+      <c r="BN3" s="51"/>
       <c r="BQ3" s="1"/>
       <c r="BR3" s="5"/>
-      <c r="BS3" s="48" t="s">
+      <c r="BS3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="BT3" s="49"/>
-      <c r="BU3" s="48" t="s">
+      <c r="BT3" s="51"/>
+      <c r="BU3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="BV3" s="49"/>
-      <c r="BW3" s="48" t="s">
+      <c r="BV3" s="51"/>
+      <c r="BW3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="BX3" s="49"/>
-      <c r="BY3" s="48" t="s">
+      <c r="BX3" s="51"/>
+      <c r="BY3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="BZ3" s="49"/>
-      <c r="CA3" s="48" t="s">
+      <c r="BZ3" s="51"/>
+      <c r="CA3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="CB3" s="49"/>
+      <c r="CB3" s="51"/>
     </row>
     <row r="4" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="6" t="s">
@@ -8051,7 +8051,7 @@
       </c>
     </row>
     <row r="5" spans="2:80" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="42" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -8087,7 +8087,7 @@
       <c r="M5" s="14">
         <v>82.58</v>
       </c>
-      <c r="AA5" s="42" t="s">
+      <c r="AA5" s="45" t="s">
         <v>13</v>
       </c>
       <c r="AB5" s="12" t="s">
@@ -8111,7 +8111,7 @@
       <c r="AL5" s="20">
         <v>19.14</v>
       </c>
-      <c r="AO5" s="42" t="s">
+      <c r="AO5" s="45" t="s">
         <v>13</v>
       </c>
       <c r="AP5" s="12" t="s">
@@ -8135,7 +8135,7 @@
       <c r="AZ5" s="20">
         <v>19.829999999999998</v>
       </c>
-      <c r="BC5" s="42" t="s">
+      <c r="BC5" s="45" t="s">
         <v>13</v>
       </c>
       <c r="BD5" s="12" t="s">
@@ -8159,7 +8159,7 @@
       <c r="BN5" s="20">
         <v>20.05</v>
       </c>
-      <c r="BQ5" s="42" t="s">
+      <c r="BQ5" s="45" t="s">
         <v>13</v>
       </c>
       <c r="BR5" s="12" t="s">
@@ -8309,7 +8309,7 @@
       </c>
     </row>
     <row r="7" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="53"/>
+      <c r="B7" s="44"/>
       <c r="C7" s="11" t="s">
         <v>12</v>
       </c>
@@ -8433,23 +8433,23 @@
       </c>
     </row>
     <row r="8" spans="2:80" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="45" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="19">
-        <v>76.11</v>
+        <v>74.38</v>
       </c>
       <c r="E8" s="20">
-        <v>33.9</v>
+        <v>33.729999999999997</v>
       </c>
       <c r="F8" s="19">
-        <v>90.04</v>
+        <v>90.11</v>
       </c>
       <c r="G8" s="20">
-        <v>0.57999999999999996</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="H8" s="19">
         <v>27.2</v>
@@ -8458,18 +8458,18 @@
         <v>14.65</v>
       </c>
       <c r="J8" s="19">
-        <v>54.1</v>
+        <v>54.32</v>
       </c>
       <c r="K8" s="20">
-        <v>34.57</v>
+        <v>34.909999999999997</v>
       </c>
       <c r="L8" s="19">
-        <v>77.260000000000005</v>
+        <v>75.67</v>
       </c>
       <c r="M8" s="20">
-        <v>19.09</v>
-      </c>
-      <c r="AA8" s="44"/>
+        <v>19.34</v>
+      </c>
+      <c r="AA8" s="46"/>
       <c r="AB8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8491,7 +8491,7 @@
       <c r="AL8" s="22">
         <v>21.78</v>
       </c>
-      <c r="AO8" s="44"/>
+      <c r="AO8" s="46"/>
       <c r="AP8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8513,7 +8513,7 @@
       <c r="AZ8" s="22">
         <v>19.12</v>
       </c>
-      <c r="BC8" s="44"/>
+      <c r="BC8" s="46"/>
       <c r="BD8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8535,7 +8535,7 @@
       <c r="BN8" s="22">
         <v>19.13</v>
       </c>
-      <c r="BQ8" s="44"/>
+      <c r="BQ8" s="46"/>
       <c r="BR8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8564,10 +8564,10 @@
         <v>11</v>
       </c>
       <c r="D9" s="15">
-        <v>73.989999999999995</v>
+        <v>74</v>
       </c>
       <c r="E9" s="16">
-        <v>33.9</v>
+        <v>33.89</v>
       </c>
       <c r="F9" s="15">
         <v>90.05</v>
@@ -8600,13 +8600,13 @@
         <v>12</v>
       </c>
       <c r="D10" s="15">
-        <v>75.739999999999995</v>
+        <v>77.75</v>
       </c>
       <c r="E10" s="16">
         <v>33.6</v>
       </c>
       <c r="F10" s="15">
-        <v>84.36</v>
+        <v>90.01</v>
       </c>
       <c r="G10" s="16">
         <v>0.68</v>
@@ -8631,7 +8631,7 @@
       </c>
     </row>
     <row r="11" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="44"/>
+      <c r="B11" s="46"/>
       <c r="C11" s="10" t="s">
         <v>14</v>
       </c>
@@ -8665,152 +8665,152 @@
       <c r="M11" s="22">
         <v>17.579999999999998</v>
       </c>
-      <c r="AA11" s="45" t="s">
+      <c r="AA11" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="AB11" s="46"/>
-      <c r="AC11" s="46"/>
-      <c r="AD11" s="46"/>
-      <c r="AE11" s="46"/>
-      <c r="AF11" s="46"/>
-      <c r="AG11" s="46"/>
-      <c r="AH11" s="46"/>
-      <c r="AI11" s="46"/>
-      <c r="AJ11" s="46"/>
-      <c r="AK11" s="46"/>
-      <c r="AL11" s="47"/>
-      <c r="AO11" s="45" t="s">
+      <c r="AB11" s="48"/>
+      <c r="AC11" s="48"/>
+      <c r="AD11" s="48"/>
+      <c r="AE11" s="48"/>
+      <c r="AF11" s="48"/>
+      <c r="AG11" s="48"/>
+      <c r="AH11" s="48"/>
+      <c r="AI11" s="48"/>
+      <c r="AJ11" s="48"/>
+      <c r="AK11" s="48"/>
+      <c r="AL11" s="49"/>
+      <c r="AO11" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="AP11" s="46"/>
-      <c r="AQ11" s="46"/>
-      <c r="AR11" s="46"/>
-      <c r="AS11" s="46"/>
-      <c r="AT11" s="46"/>
-      <c r="AU11" s="46"/>
-      <c r="AV11" s="46"/>
-      <c r="AW11" s="46"/>
-      <c r="AX11" s="46"/>
-      <c r="AY11" s="46"/>
-      <c r="AZ11" s="47"/>
-      <c r="BC11" s="45" t="s">
+      <c r="AP11" s="48"/>
+      <c r="AQ11" s="48"/>
+      <c r="AR11" s="48"/>
+      <c r="AS11" s="48"/>
+      <c r="AT11" s="48"/>
+      <c r="AU11" s="48"/>
+      <c r="AV11" s="48"/>
+      <c r="AW11" s="48"/>
+      <c r="AX11" s="48"/>
+      <c r="AY11" s="48"/>
+      <c r="AZ11" s="49"/>
+      <c r="BC11" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="BD11" s="46"/>
-      <c r="BE11" s="46"/>
-      <c r="BF11" s="46"/>
-      <c r="BG11" s="46"/>
-      <c r="BH11" s="46"/>
-      <c r="BI11" s="46"/>
-      <c r="BJ11" s="46"/>
-      <c r="BK11" s="46"/>
-      <c r="BL11" s="46"/>
-      <c r="BM11" s="46"/>
-      <c r="BN11" s="47"/>
-      <c r="BQ11" s="45" t="s">
+      <c r="BD11" s="48"/>
+      <c r="BE11" s="48"/>
+      <c r="BF11" s="48"/>
+      <c r="BG11" s="48"/>
+      <c r="BH11" s="48"/>
+      <c r="BI11" s="48"/>
+      <c r="BJ11" s="48"/>
+      <c r="BK11" s="48"/>
+      <c r="BL11" s="48"/>
+      <c r="BM11" s="48"/>
+      <c r="BN11" s="49"/>
+      <c r="BQ11" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="BR11" s="46"/>
-      <c r="BS11" s="46"/>
-      <c r="BT11" s="46"/>
-      <c r="BU11" s="46"/>
-      <c r="BV11" s="46"/>
-      <c r="BW11" s="46"/>
-      <c r="BX11" s="46"/>
-      <c r="BY11" s="46"/>
-      <c r="BZ11" s="46"/>
-      <c r="CA11" s="46"/>
-      <c r="CB11" s="47"/>
+      <c r="BR11" s="48"/>
+      <c r="BS11" s="48"/>
+      <c r="BT11" s="48"/>
+      <c r="BU11" s="48"/>
+      <c r="BV11" s="48"/>
+      <c r="BW11" s="48"/>
+      <c r="BX11" s="48"/>
+      <c r="BY11" s="48"/>
+      <c r="BZ11" s="48"/>
+      <c r="CA11" s="48"/>
+      <c r="CB11" s="49"/>
     </row>
     <row r="12" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="AA12" s="24"/>
       <c r="AB12" s="4"/>
-      <c r="AC12" s="48" t="s">
+      <c r="AC12" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="AD12" s="49"/>
-      <c r="AE12" s="48" t="s">
+      <c r="AD12" s="51"/>
+      <c r="AE12" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="AF12" s="49"/>
-      <c r="AG12" s="48" t="s">
+      <c r="AF12" s="51"/>
+      <c r="AG12" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="AH12" s="49"/>
-      <c r="AI12" s="48" t="s">
+      <c r="AH12" s="51"/>
+      <c r="AI12" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AJ12" s="49"/>
-      <c r="AK12" s="48" t="s">
+      <c r="AJ12" s="51"/>
+      <c r="AK12" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="AL12" s="49"/>
+      <c r="AL12" s="51"/>
       <c r="AO12" s="24"/>
       <c r="AP12" s="4"/>
-      <c r="AQ12" s="48" t="s">
+      <c r="AQ12" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="AR12" s="49"/>
-      <c r="AS12" s="48" t="s">
+      <c r="AR12" s="51"/>
+      <c r="AS12" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="AT12" s="49"/>
-      <c r="AU12" s="48" t="s">
+      <c r="AT12" s="51"/>
+      <c r="AU12" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="AV12" s="49"/>
-      <c r="AW12" s="48" t="s">
+      <c r="AV12" s="51"/>
+      <c r="AW12" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AX12" s="49"/>
-      <c r="AY12" s="48" t="s">
+      <c r="AX12" s="51"/>
+      <c r="AY12" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="AZ12" s="49"/>
+      <c r="AZ12" s="51"/>
       <c r="BC12" s="24"/>
       <c r="BD12" s="4"/>
-      <c r="BE12" s="48" t="s">
+      <c r="BE12" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="BF12" s="49"/>
-      <c r="BG12" s="48" t="s">
+      <c r="BF12" s="51"/>
+      <c r="BG12" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="BH12" s="49"/>
-      <c r="BI12" s="48" t="s">
+      <c r="BH12" s="51"/>
+      <c r="BI12" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="BJ12" s="49"/>
-      <c r="BK12" s="48" t="s">
+      <c r="BJ12" s="51"/>
+      <c r="BK12" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="BL12" s="49"/>
-      <c r="BM12" s="48" t="s">
+      <c r="BL12" s="51"/>
+      <c r="BM12" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="BN12" s="49"/>
+      <c r="BN12" s="51"/>
       <c r="BQ12" s="24"/>
       <c r="BR12" s="4"/>
-      <c r="BS12" s="48" t="s">
+      <c r="BS12" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="BT12" s="49"/>
-      <c r="BU12" s="48" t="s">
+      <c r="BT12" s="51"/>
+      <c r="BU12" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="BV12" s="49"/>
-      <c r="BW12" s="48" t="s">
+      <c r="BV12" s="51"/>
+      <c r="BW12" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="BX12" s="49"/>
-      <c r="BY12" s="48" t="s">
+      <c r="BX12" s="51"/>
+      <c r="BY12" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="BZ12" s="49"/>
-      <c r="CA12" s="48" t="s">
+      <c r="BZ12" s="51"/>
+      <c r="CA12" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="CB12" s="49"/>
+      <c r="CB12" s="51"/>
     </row>
     <row r="13" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="AA13" s="25" t="s">
@@ -8959,20 +8959,20 @@
       </c>
     </row>
     <row r="14" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="47"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="48"/>
+      <c r="M14" s="49"/>
       <c r="AA14" s="29" t="s">
         <v>24</v>
       </c>
@@ -9037,26 +9037,26 @@
     <row r="15" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="24"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="48" t="s">
+      <c r="D15" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="E15" s="49"/>
-      <c r="F15" s="48" t="s">
+      <c r="E15" s="51"/>
+      <c r="F15" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="49"/>
-      <c r="H15" s="48" t="s">
+      <c r="G15" s="51"/>
+      <c r="H15" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="49"/>
-      <c r="J15" s="48" t="s">
+      <c r="I15" s="51"/>
+      <c r="J15" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="49"/>
-      <c r="L15" s="48" t="s">
+      <c r="K15" s="51"/>
+      <c r="L15" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="M15" s="49"/>
+      <c r="M15" s="51"/>
       <c r="AA15" s="29" t="s">
         <v>39</v>
       </c>
@@ -11274,11 +11274,84 @@
     </row>
   </sheetData>
   <mergeCells count="91">
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="BS35:BT35"/>
+    <mergeCell ref="BU35:BV35"/>
+    <mergeCell ref="BW35:BX35"/>
+    <mergeCell ref="BY35:BZ35"/>
+    <mergeCell ref="CA35:CB35"/>
+    <mergeCell ref="BQ5:BQ8"/>
+    <mergeCell ref="BQ11:CB11"/>
+    <mergeCell ref="BS12:BT12"/>
+    <mergeCell ref="BU12:BV12"/>
+    <mergeCell ref="BW12:BX12"/>
+    <mergeCell ref="BY12:BZ12"/>
+    <mergeCell ref="CA12:CB12"/>
+    <mergeCell ref="BQ2:CB2"/>
+    <mergeCell ref="BS3:BT3"/>
+    <mergeCell ref="BU3:BV3"/>
+    <mergeCell ref="BW3:BX3"/>
+    <mergeCell ref="BY3:BZ3"/>
+    <mergeCell ref="CA3:CB3"/>
+    <mergeCell ref="BE35:BF35"/>
+    <mergeCell ref="BG35:BH35"/>
+    <mergeCell ref="BI35:BJ35"/>
+    <mergeCell ref="BK35:BL35"/>
+    <mergeCell ref="BM35:BN35"/>
+    <mergeCell ref="BC5:BC8"/>
+    <mergeCell ref="BC11:BN11"/>
+    <mergeCell ref="BE12:BF12"/>
+    <mergeCell ref="BG12:BH12"/>
+    <mergeCell ref="BI12:BJ12"/>
+    <mergeCell ref="BK12:BL12"/>
+    <mergeCell ref="BM12:BN12"/>
+    <mergeCell ref="BC2:BN2"/>
+    <mergeCell ref="BE3:BF3"/>
+    <mergeCell ref="BG3:BH3"/>
+    <mergeCell ref="BI3:BJ3"/>
+    <mergeCell ref="BK3:BL3"/>
+    <mergeCell ref="BM3:BN3"/>
+    <mergeCell ref="AQ35:AR35"/>
+    <mergeCell ref="AS35:AT35"/>
+    <mergeCell ref="AU35:AV35"/>
+    <mergeCell ref="AW35:AX35"/>
+    <mergeCell ref="AY35:AZ35"/>
+    <mergeCell ref="AO5:AO8"/>
+    <mergeCell ref="AO11:AZ11"/>
+    <mergeCell ref="AQ12:AR12"/>
+    <mergeCell ref="AS12:AT12"/>
+    <mergeCell ref="AU12:AV12"/>
+    <mergeCell ref="AW12:AX12"/>
+    <mergeCell ref="AY12:AZ12"/>
+    <mergeCell ref="AO2:AZ2"/>
+    <mergeCell ref="AQ3:AR3"/>
+    <mergeCell ref="AS3:AT3"/>
+    <mergeCell ref="AU3:AV3"/>
+    <mergeCell ref="AW3:AX3"/>
+    <mergeCell ref="AY3:AZ3"/>
+    <mergeCell ref="AC35:AD35"/>
+    <mergeCell ref="AE35:AF35"/>
+    <mergeCell ref="AG35:AH35"/>
+    <mergeCell ref="AI35:AJ35"/>
+    <mergeCell ref="AK35:AL35"/>
+    <mergeCell ref="AA5:AA8"/>
+    <mergeCell ref="AA11:AL11"/>
+    <mergeCell ref="AC12:AD12"/>
+    <mergeCell ref="AE12:AF12"/>
+    <mergeCell ref="AG12:AH12"/>
+    <mergeCell ref="AI12:AJ12"/>
+    <mergeCell ref="AK12:AL12"/>
+    <mergeCell ref="AA2:AL2"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="AG3:AH3"/>
+    <mergeCell ref="AI3:AJ3"/>
+    <mergeCell ref="AK3:AL3"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="B14:M14"/>
@@ -11287,84 +11360,11 @@
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="J15:K15"/>
     <mergeCell ref="L15:M15"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="AA2:AL2"/>
-    <mergeCell ref="AC3:AD3"/>
-    <mergeCell ref="AE3:AF3"/>
-    <mergeCell ref="AG3:AH3"/>
-    <mergeCell ref="AI3:AJ3"/>
-    <mergeCell ref="AK3:AL3"/>
-    <mergeCell ref="AA5:AA8"/>
-    <mergeCell ref="AA11:AL11"/>
-    <mergeCell ref="AC12:AD12"/>
-    <mergeCell ref="AE12:AF12"/>
-    <mergeCell ref="AG12:AH12"/>
-    <mergeCell ref="AI12:AJ12"/>
-    <mergeCell ref="AK12:AL12"/>
-    <mergeCell ref="AC35:AD35"/>
-    <mergeCell ref="AE35:AF35"/>
-    <mergeCell ref="AG35:AH35"/>
-    <mergeCell ref="AI35:AJ35"/>
-    <mergeCell ref="AK35:AL35"/>
-    <mergeCell ref="AO2:AZ2"/>
-    <mergeCell ref="AQ3:AR3"/>
-    <mergeCell ref="AS3:AT3"/>
-    <mergeCell ref="AU3:AV3"/>
-    <mergeCell ref="AW3:AX3"/>
-    <mergeCell ref="AY3:AZ3"/>
-    <mergeCell ref="AO5:AO8"/>
-    <mergeCell ref="AO11:AZ11"/>
-    <mergeCell ref="AQ12:AR12"/>
-    <mergeCell ref="AS12:AT12"/>
-    <mergeCell ref="AU12:AV12"/>
-    <mergeCell ref="AW12:AX12"/>
-    <mergeCell ref="AY12:AZ12"/>
-    <mergeCell ref="AQ35:AR35"/>
-    <mergeCell ref="AS35:AT35"/>
-    <mergeCell ref="AU35:AV35"/>
-    <mergeCell ref="AW35:AX35"/>
-    <mergeCell ref="AY35:AZ35"/>
-    <mergeCell ref="BC2:BN2"/>
-    <mergeCell ref="BE3:BF3"/>
-    <mergeCell ref="BG3:BH3"/>
-    <mergeCell ref="BI3:BJ3"/>
-    <mergeCell ref="BK3:BL3"/>
-    <mergeCell ref="BM3:BN3"/>
-    <mergeCell ref="BC5:BC8"/>
-    <mergeCell ref="BC11:BN11"/>
-    <mergeCell ref="BE12:BF12"/>
-    <mergeCell ref="BG12:BH12"/>
-    <mergeCell ref="BI12:BJ12"/>
-    <mergeCell ref="BK12:BL12"/>
-    <mergeCell ref="BM12:BN12"/>
-    <mergeCell ref="BE35:BF35"/>
-    <mergeCell ref="BG35:BH35"/>
-    <mergeCell ref="BI35:BJ35"/>
-    <mergeCell ref="BK35:BL35"/>
-    <mergeCell ref="BM35:BN35"/>
-    <mergeCell ref="BQ2:CB2"/>
-    <mergeCell ref="BS3:BT3"/>
-    <mergeCell ref="BU3:BV3"/>
-    <mergeCell ref="BW3:BX3"/>
-    <mergeCell ref="BY3:BZ3"/>
-    <mergeCell ref="CA3:CB3"/>
-    <mergeCell ref="BQ5:BQ8"/>
-    <mergeCell ref="BQ11:CB11"/>
-    <mergeCell ref="BS12:BT12"/>
-    <mergeCell ref="BU12:BV12"/>
-    <mergeCell ref="BW12:BX12"/>
-    <mergeCell ref="BY12:BZ12"/>
-    <mergeCell ref="CA12:CB12"/>
-    <mergeCell ref="BS35:BT35"/>
-    <mergeCell ref="BU35:BV35"/>
-    <mergeCell ref="BW35:BX35"/>
-    <mergeCell ref="BY35:BZ35"/>
-    <mergeCell ref="CA35:CB35"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="L38:M38"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Results_metrics.xlsx
+++ b/Results_metrics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10608"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aless\OneDrive\Desktop\MaskArchitectureAnomaly_CourseProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ludovicascaffidi/Desktop/Università/Magistrale/Secondo Anno/Secondo Semestre/Machine Learning for Mathematical Engineering/Progetto/MaskArchitectureAnomaly_CourseProject/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51BA8912-0CF5-4B29-A165-4C2B8D6A4791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E602311C-DCBC-F649-AD7D-8F8F41C583C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1043" uniqueCount="56">
   <si>
     <t>Model</t>
   </si>
@@ -159,32 +159,47 @@
     <t>RISULTATI METRICHE con Logitnorm tau = 0,04</t>
   </si>
   <si>
-    <t>RISULTATI METRICHE per EoMT con TEMPERATURE su MSP con Logitnorm tau = 0,04</t>
-  </si>
-  <si>
-    <t>RISULTATI METRICHE con Logitnorm tau = 0,07</t>
-  </si>
-  <si>
-    <t>RISULTATI METRICHE per EoMT con TEMPERATURE su MSP con Logitnorm tau = 0,07</t>
-  </si>
-  <si>
-    <t>RISULTATI METRICHE con Logitnorm tau = 0,10</t>
-  </si>
-  <si>
-    <t>RISULTATI METRICHE per EoMT con TEMPERATURE su MSP con Logitnorm tau = 0,10</t>
-  </si>
-  <si>
     <t>81.7%</t>
   </si>
   <si>
     <t>t = 0,275</t>
+  </si>
+  <si>
+    <t>RISULTATI METRICHE con Logitnorm tau = 0,001</t>
+  </si>
+  <si>
+    <t>RISULTATI METRICHE per EoMT con TEMPERATURE su MSP con Logitnorm tau=0,001</t>
+  </si>
+  <si>
+    <t>RISULTATI METRICHE con Logitnorm tau = 0,025</t>
+  </si>
+  <si>
+    <t>RISULTATI METRICHE per EoMT con TEMPERATURE su MSP con Logitnorm tau=0,025</t>
+  </si>
+  <si>
+    <t>RISULTATI METRICHE per EoMT con TEMPERATURE su MSP con Logitnorm tau=0,04</t>
+  </si>
+  <si>
+    <t>RISULTATI METRICHE con Logitnorm tau = 0,05</t>
+  </si>
+  <si>
+    <t>RISULTATI METRICHE per EoMT con TEMPERATURE su MSP con Logitnorm tau=0,05</t>
+  </si>
+  <si>
+    <t>HEAD_ONLY</t>
+  </si>
+  <si>
+    <t>QUERIES_ONLY</t>
+  </si>
+  <si>
+    <t>NONE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -210,6 +225,13 @@
       <u/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -676,7 +698,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
@@ -715,6 +737,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -727,20 +750,11 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -751,17 +765,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1507,7 +1530,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1515,6 +1537,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2276,7 +2299,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2284,6 +2306,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2961,7 +2984,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2969,6 +2991,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3730,7 +3753,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3738,6 +3760,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4463,7 +4486,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4471,6 +4493,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7676,199 +7699,250 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:CB38"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:CP107"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="14.44140625" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="2" max="2" width="14.5" customWidth="1"/>
+    <col min="3" max="3" width="13.1640625" customWidth="1"/>
+    <col min="28" max="28" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="47" t="s">
+    <row r="1" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="53"/>
-      <c r="AA2" s="47" t="s">
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="52"/>
+      <c r="AA2" s="45" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="51"/>
+      <c r="AF2" s="51"/>
+      <c r="AG2" s="51"/>
+      <c r="AH2" s="51"/>
+      <c r="AI2" s="51"/>
+      <c r="AJ2" s="51"/>
+      <c r="AK2" s="51"/>
+      <c r="AL2" s="52"/>
+      <c r="AO2" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="AB2" s="52"/>
-      <c r="AC2" s="52"/>
-      <c r="AD2" s="52"/>
-      <c r="AE2" s="52"/>
-      <c r="AF2" s="52"/>
-      <c r="AG2" s="52"/>
-      <c r="AH2" s="52"/>
-      <c r="AI2" s="52"/>
-      <c r="AJ2" s="52"/>
-      <c r="AK2" s="52"/>
-      <c r="AL2" s="53"/>
-      <c r="AO2" s="47" t="s">
+      <c r="AP2" s="51"/>
+      <c r="AQ2" s="51"/>
+      <c r="AR2" s="51"/>
+      <c r="AS2" s="51"/>
+      <c r="AT2" s="51"/>
+      <c r="AU2" s="51"/>
+      <c r="AV2" s="51"/>
+      <c r="AW2" s="51"/>
+      <c r="AX2" s="51"/>
+      <c r="AY2" s="51"/>
+      <c r="AZ2" s="52"/>
+      <c r="BC2" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="BD2" s="51"/>
+      <c r="BE2" s="51"/>
+      <c r="BF2" s="51"/>
+      <c r="BG2" s="51"/>
+      <c r="BH2" s="51"/>
+      <c r="BI2" s="51"/>
+      <c r="BJ2" s="51"/>
+      <c r="BK2" s="51"/>
+      <c r="BL2" s="51"/>
+      <c r="BM2" s="51"/>
+      <c r="BN2" s="52"/>
+      <c r="BQ2" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AP2" s="52"/>
-      <c r="AQ2" s="52"/>
-      <c r="AR2" s="52"/>
-      <c r="AS2" s="52"/>
-      <c r="AT2" s="52"/>
-      <c r="AU2" s="52"/>
-      <c r="AV2" s="52"/>
-      <c r="AW2" s="52"/>
-      <c r="AX2" s="52"/>
-      <c r="AY2" s="52"/>
-      <c r="AZ2" s="53"/>
-      <c r="BC2" s="47" t="s">
-        <v>45</v>
-      </c>
-      <c r="BD2" s="52"/>
-      <c r="BE2" s="52"/>
-      <c r="BF2" s="52"/>
-      <c r="BG2" s="52"/>
-      <c r="BH2" s="52"/>
-      <c r="BI2" s="52"/>
-      <c r="BJ2" s="52"/>
-      <c r="BK2" s="52"/>
-      <c r="BL2" s="52"/>
-      <c r="BM2" s="52"/>
-      <c r="BN2" s="53"/>
-      <c r="BQ2" s="47" t="s">
-        <v>47</v>
-      </c>
-      <c r="BR2" s="52"/>
-      <c r="BS2" s="52"/>
-      <c r="BT2" s="52"/>
-      <c r="BU2" s="52"/>
-      <c r="BV2" s="52"/>
-      <c r="BW2" s="52"/>
-      <c r="BX2" s="52"/>
-      <c r="BY2" s="52"/>
-      <c r="BZ2" s="52"/>
-      <c r="CA2" s="52"/>
-      <c r="CB2" s="53"/>
+      <c r="BR2" s="51"/>
+      <c r="BS2" s="51"/>
+      <c r="BT2" s="51"/>
+      <c r="BU2" s="51"/>
+      <c r="BV2" s="51"/>
+      <c r="BW2" s="51"/>
+      <c r="BX2" s="51"/>
+      <c r="BY2" s="51"/>
+      <c r="BZ2" s="51"/>
+      <c r="CA2" s="51"/>
+      <c r="CB2" s="52"/>
+      <c r="CE2" s="45" t="s">
+        <v>51</v>
+      </c>
+      <c r="CF2" s="51"/>
+      <c r="CG2" s="51"/>
+      <c r="CH2" s="51"/>
+      <c r="CI2" s="51"/>
+      <c r="CJ2" s="51"/>
+      <c r="CK2" s="51"/>
+      <c r="CL2" s="51"/>
+      <c r="CM2" s="51"/>
+      <c r="CN2" s="51"/>
+      <c r="CO2" s="51"/>
+      <c r="CP2" s="52"/>
     </row>
-    <row r="3" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="5"/>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50" t="s">
+      <c r="E3" s="44"/>
+      <c r="F3" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="51"/>
-      <c r="H3" s="50" t="s">
+      <c r="G3" s="44"/>
+      <c r="H3" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="51"/>
-      <c r="J3" s="50" t="s">
+      <c r="I3" s="44"/>
+      <c r="J3" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="51"/>
-      <c r="L3" s="50" t="s">
+      <c r="K3" s="44"/>
+      <c r="L3" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="51"/>
+      <c r="M3" s="44"/>
       <c r="AA3" s="1"/>
-      <c r="AB3" s="5"/>
-      <c r="AC3" s="50" t="s">
+      <c r="AB3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC3" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="AD3" s="51"/>
-      <c r="AE3" s="50" t="s">
+      <c r="AD3" s="44"/>
+      <c r="AE3" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="AF3" s="51"/>
-      <c r="AG3" s="50" t="s">
+      <c r="AF3" s="44"/>
+      <c r="AG3" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="AH3" s="51"/>
-      <c r="AI3" s="50" t="s">
+      <c r="AH3" s="44"/>
+      <c r="AI3" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="AJ3" s="51"/>
-      <c r="AK3" s="50" t="s">
+      <c r="AJ3" s="44"/>
+      <c r="AK3" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="51"/>
+      <c r="AL3" s="44"/>
       <c r="AO3" s="1"/>
-      <c r="AP3" s="5"/>
-      <c r="AQ3" s="50" t="s">
+      <c r="AP3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ3" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="AR3" s="51"/>
-      <c r="AS3" s="50" t="s">
+      <c r="AR3" s="44"/>
+      <c r="AS3" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="AT3" s="51"/>
-      <c r="AU3" s="50" t="s">
+      <c r="AT3" s="44"/>
+      <c r="AU3" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="AV3" s="51"/>
-      <c r="AW3" s="50" t="s">
+      <c r="AV3" s="44"/>
+      <c r="AW3" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="AX3" s="51"/>
-      <c r="AY3" s="50" t="s">
+      <c r="AX3" s="44"/>
+      <c r="AY3" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="AZ3" s="51"/>
+      <c r="AZ3" s="44"/>
       <c r="BC3" s="1"/>
-      <c r="BD3" s="5"/>
-      <c r="BE3" s="50" t="s">
+      <c r="BD3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="BE3" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="BF3" s="51"/>
-      <c r="BG3" s="50" t="s">
+      <c r="BF3" s="44"/>
+      <c r="BG3" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="BH3" s="51"/>
-      <c r="BI3" s="50" t="s">
+      <c r="BH3" s="44"/>
+      <c r="BI3" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="BJ3" s="51"/>
-      <c r="BK3" s="50" t="s">
+      <c r="BJ3" s="44"/>
+      <c r="BK3" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="BL3" s="51"/>
-      <c r="BM3" s="50" t="s">
+      <c r="BL3" s="44"/>
+      <c r="BM3" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="BN3" s="51"/>
+      <c r="BN3" s="44"/>
       <c r="BQ3" s="1"/>
-      <c r="BR3" s="5"/>
-      <c r="BS3" s="50" t="s">
+      <c r="BR3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="BS3" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="BT3" s="51"/>
-      <c r="BU3" s="50" t="s">
+      <c r="BT3" s="44"/>
+      <c r="BU3" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="BV3" s="51"/>
-      <c r="BW3" s="50" t="s">
+      <c r="BV3" s="44"/>
+      <c r="BW3" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="BX3" s="51"/>
-      <c r="BY3" s="50" t="s">
+      <c r="BX3" s="44"/>
+      <c r="BY3" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="BZ3" s="51"/>
-      <c r="CA3" s="50" t="s">
+      <c r="BZ3" s="44"/>
+      <c r="CA3" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="CB3" s="51"/>
+      <c r="CB3" s="44"/>
+      <c r="CE3" s="1"/>
+      <c r="CF3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="CG3" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="CH3" s="44"/>
+      <c r="CI3" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="CJ3" s="44"/>
+      <c r="CK3" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL3" s="44"/>
+      <c r="CM3" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="CN3" s="44"/>
+      <c r="CO3" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="CP3" s="44"/>
     </row>
-    <row r="4" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
         <v>0</v>
       </c>
@@ -8049,9 +8123,45 @@
       <c r="CB4" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="CE4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="CF4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="CG4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="CH4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="CI4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="CJ4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="CK4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="CL4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="CM4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="CN4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="CO4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="CP4" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="5" spans="2:80" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="42" t="s">
+    <row r="5" spans="2:94" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="53" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -8087,7 +8197,7 @@
       <c r="M5" s="14">
         <v>82.58</v>
       </c>
-      <c r="AA5" s="45" t="s">
+      <c r="AA5" s="48" t="s">
         <v>13</v>
       </c>
       <c r="AB5" s="12" t="s">
@@ -8095,23 +8205,15 @@
       </c>
       <c r="AC5" s="19"/>
       <c r="AD5" s="20"/>
-      <c r="AE5" s="19">
-        <v>66.739999999999995</v>
-      </c>
-      <c r="AF5" s="20">
-        <v>100</v>
-      </c>
+      <c r="AE5" s="19"/>
+      <c r="AF5" s="20"/>
       <c r="AG5" s="19"/>
       <c r="AH5" s="20"/>
       <c r="AI5" s="19"/>
       <c r="AJ5" s="20"/>
-      <c r="AK5" s="19">
-        <v>70.78</v>
-      </c>
-      <c r="AL5" s="20">
-        <v>19.14</v>
-      </c>
-      <c r="AO5" s="45" t="s">
+      <c r="AK5" s="19"/>
+      <c r="AL5" s="20"/>
+      <c r="AO5" s="48" t="s">
         <v>13</v>
       </c>
       <c r="AP5" s="12" t="s">
@@ -8119,23 +8221,15 @@
       </c>
       <c r="AQ5" s="19"/>
       <c r="AR5" s="20"/>
-      <c r="AS5" s="19">
-        <v>77.11</v>
-      </c>
-      <c r="AT5" s="20">
-        <v>100</v>
-      </c>
+      <c r="AS5" s="19"/>
+      <c r="AT5" s="20"/>
       <c r="AU5" s="19"/>
       <c r="AV5" s="20"/>
       <c r="AW5" s="19"/>
       <c r="AX5" s="20"/>
-      <c r="AY5" s="19">
-        <v>72.31</v>
-      </c>
-      <c r="AZ5" s="20">
-        <v>19.829999999999998</v>
-      </c>
-      <c r="BC5" s="45" t="s">
+      <c r="AY5" s="19"/>
+      <c r="AZ5" s="20"/>
+      <c r="BC5" s="48" t="s">
         <v>13</v>
       </c>
       <c r="BD5" s="12" t="s">
@@ -8143,23 +8237,15 @@
       </c>
       <c r="BE5" s="19"/>
       <c r="BF5" s="20"/>
-      <c r="BG5" s="19">
-        <v>80.540000000000006</v>
-      </c>
-      <c r="BH5" s="20">
-        <v>100</v>
-      </c>
+      <c r="BG5" s="19"/>
+      <c r="BH5" s="20"/>
       <c r="BI5" s="19"/>
       <c r="BJ5" s="20"/>
       <c r="BK5" s="19"/>
       <c r="BL5" s="20"/>
-      <c r="BM5" s="19">
-        <v>72.17</v>
-      </c>
-      <c r="BN5" s="20">
-        <v>20.05</v>
-      </c>
-      <c r="BQ5" s="45" t="s">
+      <c r="BM5" s="19"/>
+      <c r="BN5" s="20"/>
+      <c r="BQ5" s="48" t="s">
         <v>13</v>
       </c>
       <c r="BR5" s="12" t="s">
@@ -8167,25 +8253,33 @@
       </c>
       <c r="BS5" s="19"/>
       <c r="BT5" s="20"/>
-      <c r="BU5" s="19">
-        <v>82.9</v>
-      </c>
-      <c r="BV5" s="20">
-        <v>100</v>
-      </c>
+      <c r="BU5" s="19"/>
+      <c r="BV5" s="20"/>
       <c r="BW5" s="19"/>
       <c r="BX5" s="20"/>
       <c r="BY5" s="19"/>
       <c r="BZ5" s="20"/>
-      <c r="CA5" s="19">
-        <v>72.23</v>
-      </c>
-      <c r="CB5" s="20">
-        <v>20.92</v>
-      </c>
+      <c r="CA5" s="19"/>
+      <c r="CB5" s="20"/>
+      <c r="CE5" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="CF5" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="CG5" s="19"/>
+      <c r="CH5" s="20"/>
+      <c r="CI5" s="19"/>
+      <c r="CJ5" s="20"/>
+      <c r="CK5" s="19"/>
+      <c r="CL5" s="20"/>
+      <c r="CM5" s="19"/>
+      <c r="CN5" s="20"/>
+      <c r="CO5" s="19"/>
+      <c r="CP5" s="20"/>
     </row>
-    <row r="6" spans="2:80" x14ac:dyDescent="0.3">
-      <c r="B6" s="43"/>
+    <row r="6" spans="2:94" x14ac:dyDescent="0.2">
+      <c r="B6" s="49"/>
       <c r="C6" s="9" t="s">
         <v>11</v>
       </c>
@@ -8219,97 +8313,79 @@
       <c r="M6" s="32">
         <v>73.25</v>
       </c>
-      <c r="AA6" s="43"/>
+      <c r="AA6" s="49"/>
       <c r="AB6" s="9" t="s">
         <v>11</v>
       </c>
       <c r="AC6" s="15"/>
       <c r="AD6" s="16"/>
-      <c r="AE6" s="15">
-        <v>66.75</v>
-      </c>
-      <c r="AF6" s="16">
-        <v>100</v>
-      </c>
+      <c r="AE6" s="15"/>
+      <c r="AF6" s="16"/>
       <c r="AG6" s="15"/>
       <c r="AH6" s="16"/>
       <c r="AI6" s="15"/>
       <c r="AJ6" s="16"/>
-      <c r="AK6" s="15">
-        <v>68.72</v>
-      </c>
-      <c r="AL6" s="16">
-        <v>19.14</v>
-      </c>
-      <c r="AO6" s="43"/>
+      <c r="AK6" s="15"/>
+      <c r="AL6" s="16"/>
+      <c r="AO6" s="49"/>
       <c r="AP6" s="9" t="s">
         <v>11</v>
       </c>
       <c r="AQ6" s="15"/>
       <c r="AR6" s="16"/>
-      <c r="AS6" s="15">
-        <v>77.12</v>
-      </c>
-      <c r="AT6" s="16">
-        <v>100</v>
-      </c>
+      <c r="AS6" s="15"/>
+      <c r="AT6" s="16"/>
       <c r="AU6" s="15"/>
       <c r="AV6" s="16"/>
       <c r="AW6" s="15"/>
       <c r="AX6" s="16"/>
-      <c r="AY6" s="15">
-        <v>69.87</v>
-      </c>
-      <c r="AZ6" s="16">
-        <v>19.829999999999998</v>
-      </c>
-      <c r="BC6" s="43"/>
+      <c r="AY6" s="15"/>
+      <c r="AZ6" s="16"/>
+      <c r="BC6" s="49"/>
       <c r="BD6" s="9" t="s">
         <v>11</v>
       </c>
       <c r="BE6" s="15"/>
       <c r="BF6" s="16"/>
-      <c r="BG6" s="15">
-        <v>80.55</v>
-      </c>
-      <c r="BH6" s="16">
-        <v>100</v>
-      </c>
+      <c r="BG6" s="15"/>
+      <c r="BH6" s="16"/>
       <c r="BI6" s="15"/>
       <c r="BJ6" s="16"/>
       <c r="BK6" s="15"/>
       <c r="BL6" s="16"/>
-      <c r="BM6" s="15">
-        <v>69.92</v>
-      </c>
-      <c r="BN6" s="16">
-        <v>20.05</v>
-      </c>
-      <c r="BQ6" s="43"/>
+      <c r="BM6" s="15"/>
+      <c r="BN6" s="16"/>
+      <c r="BQ6" s="49"/>
       <c r="BR6" s="9" t="s">
         <v>11</v>
       </c>
       <c r="BS6" s="15"/>
       <c r="BT6" s="16"/>
-      <c r="BU6" s="15">
-        <v>82.91</v>
-      </c>
-      <c r="BV6" s="16">
-        <v>100</v>
-      </c>
+      <c r="BU6" s="15"/>
+      <c r="BV6" s="16"/>
       <c r="BW6" s="15"/>
       <c r="BX6" s="16"/>
       <c r="BY6" s="15"/>
       <c r="BZ6" s="16"/>
-      <c r="CA6" s="15">
-        <v>70.38</v>
-      </c>
-      <c r="CB6" s="16">
-        <v>20.92</v>
-      </c>
+      <c r="CA6" s="15"/>
+      <c r="CB6" s="16"/>
+      <c r="CE6" s="49"/>
+      <c r="CF6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="CG6" s="15"/>
+      <c r="CH6" s="16"/>
+      <c r="CI6" s="15"/>
+      <c r="CJ6" s="16"/>
+      <c r="CK6" s="15"/>
+      <c r="CL6" s="16"/>
+      <c r="CM6" s="15"/>
+      <c r="CN6" s="16"/>
+      <c r="CO6" s="15"/>
+      <c r="CP6" s="16"/>
     </row>
-    <row r="7" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="44"/>
+    <row r="7" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="54"/>
       <c r="C7" s="11" t="s">
         <v>12</v>
       </c>
@@ -8343,97 +8419,79 @@
       <c r="M7" s="18">
         <v>82.75</v>
       </c>
-      <c r="AA7" s="43"/>
+      <c r="AA7" s="49"/>
       <c r="AB7" s="9" t="s">
         <v>12</v>
       </c>
       <c r="AC7" s="15"/>
       <c r="AD7" s="16"/>
-      <c r="AE7" s="15">
-        <v>67.03</v>
-      </c>
-      <c r="AF7" s="16">
-        <v>100</v>
-      </c>
+      <c r="AE7" s="15"/>
+      <c r="AF7" s="16"/>
       <c r="AG7" s="15"/>
       <c r="AH7" s="16"/>
       <c r="AI7" s="15"/>
       <c r="AJ7" s="16"/>
-      <c r="AK7" s="15">
-        <v>71.83</v>
-      </c>
-      <c r="AL7" s="16">
-        <v>17.79</v>
-      </c>
-      <c r="AO7" s="43"/>
+      <c r="AK7" s="15"/>
+      <c r="AL7" s="16"/>
+      <c r="AO7" s="49"/>
       <c r="AP7" s="9" t="s">
         <v>12</v>
       </c>
       <c r="AQ7" s="15"/>
       <c r="AR7" s="16"/>
-      <c r="AS7" s="15">
-        <v>77.11</v>
-      </c>
-      <c r="AT7" s="16">
-        <v>100</v>
-      </c>
+      <c r="AS7" s="15"/>
+      <c r="AT7" s="16"/>
       <c r="AU7" s="15"/>
       <c r="AV7" s="16"/>
       <c r="AW7" s="15"/>
       <c r="AX7" s="16"/>
-      <c r="AY7" s="15">
-        <v>73.66</v>
-      </c>
-      <c r="AZ7" s="16">
-        <v>19.29</v>
-      </c>
-      <c r="BC7" s="43"/>
+      <c r="AY7" s="15"/>
+      <c r="AZ7" s="16"/>
+      <c r="BC7" s="49"/>
       <c r="BD7" s="9" t="s">
         <v>12</v>
       </c>
       <c r="BE7" s="15"/>
       <c r="BF7" s="16"/>
-      <c r="BG7" s="15">
-        <v>80.849999999999994</v>
-      </c>
-      <c r="BH7" s="16">
-        <v>100</v>
-      </c>
+      <c r="BG7" s="15"/>
+      <c r="BH7" s="16"/>
       <c r="BI7" s="15"/>
       <c r="BJ7" s="16"/>
       <c r="BK7" s="15"/>
       <c r="BL7" s="16"/>
-      <c r="BM7" s="15">
-        <v>73.989999999999995</v>
-      </c>
-      <c r="BN7" s="16">
-        <v>19.649999999999999</v>
-      </c>
-      <c r="BQ7" s="43"/>
+      <c r="BM7" s="15"/>
+      <c r="BN7" s="16"/>
+      <c r="BQ7" s="49"/>
       <c r="BR7" s="9" t="s">
         <v>12</v>
       </c>
       <c r="BS7" s="15"/>
       <c r="BT7" s="16"/>
-      <c r="BU7" s="15">
-        <v>83.73</v>
-      </c>
-      <c r="BV7" s="16">
-        <v>78.91</v>
-      </c>
+      <c r="BU7" s="15"/>
+      <c r="BV7" s="16"/>
       <c r="BW7" s="15"/>
       <c r="BX7" s="16"/>
       <c r="BY7" s="15"/>
       <c r="BZ7" s="16"/>
-      <c r="CA7" s="15">
-        <v>74.599999999999994</v>
-      </c>
-      <c r="CB7" s="16">
-        <v>20.49</v>
-      </c>
+      <c r="CA7" s="15"/>
+      <c r="CB7" s="16"/>
+      <c r="CE7" s="49"/>
+      <c r="CF7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="CG7" s="15"/>
+      <c r="CH7" s="16"/>
+      <c r="CI7" s="15"/>
+      <c r="CJ7" s="16"/>
+      <c r="CK7" s="15"/>
+      <c r="CL7" s="16"/>
+      <c r="CM7" s="15"/>
+      <c r="CN7" s="16"/>
+      <c r="CO7" s="15"/>
+      <c r="CP7" s="16"/>
     </row>
-    <row r="8" spans="2:80" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="45" t="s">
+    <row r="8" spans="2:94" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="48" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="12" t="s">
@@ -8469,97 +8527,79 @@
       <c r="M8" s="20">
         <v>19.34</v>
       </c>
-      <c r="AA8" s="46"/>
+      <c r="AA8" s="50"/>
       <c r="AB8" s="10" t="s">
         <v>14</v>
       </c>
       <c r="AC8" s="21"/>
       <c r="AD8" s="22"/>
-      <c r="AE8" s="21">
-        <v>64.2</v>
-      </c>
-      <c r="AF8" s="22">
-        <v>100</v>
-      </c>
+      <c r="AE8" s="21"/>
+      <c r="AF8" s="22"/>
       <c r="AG8" s="21"/>
       <c r="AH8" s="22"/>
       <c r="AI8" s="21"/>
       <c r="AJ8" s="22"/>
-      <c r="AK8" s="21">
-        <v>70.77</v>
-      </c>
-      <c r="AL8" s="22">
-        <v>21.78</v>
-      </c>
-      <c r="AO8" s="46"/>
+      <c r="AK8" s="21"/>
+      <c r="AL8" s="22"/>
+      <c r="AO8" s="50"/>
       <c r="AP8" s="10" t="s">
         <v>14</v>
       </c>
       <c r="AQ8" s="21"/>
       <c r="AR8" s="22"/>
-      <c r="AS8" s="21">
-        <v>75.72</v>
-      </c>
-      <c r="AT8" s="22">
-        <v>99.99</v>
-      </c>
+      <c r="AS8" s="21"/>
+      <c r="AT8" s="22"/>
       <c r="AU8" s="21"/>
       <c r="AV8" s="22"/>
       <c r="AW8" s="21"/>
       <c r="AX8" s="22"/>
-      <c r="AY8" s="21">
-        <v>72.92</v>
-      </c>
-      <c r="AZ8" s="22">
-        <v>19.12</v>
-      </c>
-      <c r="BC8" s="46"/>
+      <c r="AY8" s="21"/>
+      <c r="AZ8" s="22"/>
+      <c r="BC8" s="50"/>
       <c r="BD8" s="10" t="s">
         <v>14</v>
       </c>
       <c r="BE8" s="21"/>
       <c r="BF8" s="22"/>
-      <c r="BG8" s="21">
-        <v>80.12</v>
-      </c>
-      <c r="BH8" s="22">
-        <v>99.98</v>
-      </c>
+      <c r="BG8" s="21"/>
+      <c r="BH8" s="22"/>
       <c r="BI8" s="21"/>
       <c r="BJ8" s="22"/>
       <c r="BK8" s="21"/>
       <c r="BL8" s="22"/>
-      <c r="BM8" s="21">
-        <v>72.790000000000006</v>
-      </c>
-      <c r="BN8" s="22">
-        <v>19.13</v>
-      </c>
-      <c r="BQ8" s="46"/>
+      <c r="BM8" s="21"/>
+      <c r="BN8" s="22"/>
+      <c r="BQ8" s="50"/>
       <c r="BR8" s="10" t="s">
         <v>14</v>
       </c>
       <c r="BS8" s="21"/>
       <c r="BT8" s="22"/>
-      <c r="BU8" s="21">
-        <v>82.31</v>
-      </c>
-      <c r="BV8" s="22">
-        <v>99.97</v>
-      </c>
+      <c r="BU8" s="21"/>
+      <c r="BV8" s="22"/>
       <c r="BW8" s="21"/>
       <c r="BX8" s="22"/>
       <c r="BY8" s="21"/>
       <c r="BZ8" s="22"/>
-      <c r="CA8" s="21">
-        <v>74.290000000000006</v>
-      </c>
-      <c r="CB8" s="22">
-        <v>19.53</v>
-      </c>
+      <c r="CA8" s="21"/>
+      <c r="CB8" s="22"/>
+      <c r="CE8" s="50"/>
+      <c r="CF8" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="CG8" s="21"/>
+      <c r="CH8" s="22"/>
+      <c r="CI8" s="21"/>
+      <c r="CJ8" s="22"/>
+      <c r="CK8" s="21"/>
+      <c r="CL8" s="22"/>
+      <c r="CM8" s="21"/>
+      <c r="CN8" s="22"/>
+      <c r="CO8" s="21"/>
+      <c r="CP8" s="22"/>
     </row>
-    <row r="9" spans="2:80" x14ac:dyDescent="0.3">
-      <c r="B9" s="43"/>
+    <row r="9" spans="2:94" x14ac:dyDescent="0.2">
+      <c r="B9" s="49"/>
       <c r="C9" s="9" t="s">
         <v>11</v>
       </c>
@@ -8594,8 +8634,8 @@
         <v>19.09</v>
       </c>
     </row>
-    <row r="10" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="43"/>
+    <row r="10" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="49"/>
       <c r="C10" s="9" t="s">
         <v>12</v>
       </c>
@@ -8630,8 +8670,8 @@
         <v>18.829999999999998</v>
       </c>
     </row>
-    <row r="11" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="46"/>
+    <row r="11" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="50"/>
       <c r="C11" s="10" t="s">
         <v>14</v>
       </c>
@@ -8665,154 +8705,200 @@
       <c r="M11" s="22">
         <v>17.579999999999998</v>
       </c>
-      <c r="AA11" s="47" t="s">
+      <c r="AA11" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB11" s="46"/>
+      <c r="AC11" s="46"/>
+      <c r="AD11" s="46"/>
+      <c r="AE11" s="46"/>
+      <c r="AF11" s="46"/>
+      <c r="AG11" s="46"/>
+      <c r="AH11" s="46"/>
+      <c r="AI11" s="46"/>
+      <c r="AJ11" s="46"/>
+      <c r="AK11" s="46"/>
+      <c r="AL11" s="47"/>
+      <c r="AO11" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="AB11" s="48"/>
-      <c r="AC11" s="48"/>
-      <c r="AD11" s="48"/>
-      <c r="AE11" s="48"/>
-      <c r="AF11" s="48"/>
-      <c r="AG11" s="48"/>
-      <c r="AH11" s="48"/>
-      <c r="AI11" s="48"/>
-      <c r="AJ11" s="48"/>
-      <c r="AK11" s="48"/>
-      <c r="AL11" s="49"/>
-      <c r="AO11" s="47" t="s">
-        <v>44</v>
-      </c>
-      <c r="AP11" s="48"/>
-      <c r="AQ11" s="48"/>
-      <c r="AR11" s="48"/>
-      <c r="AS11" s="48"/>
-      <c r="AT11" s="48"/>
-      <c r="AU11" s="48"/>
-      <c r="AV11" s="48"/>
-      <c r="AW11" s="48"/>
-      <c r="AX11" s="48"/>
-      <c r="AY11" s="48"/>
-      <c r="AZ11" s="49"/>
-      <c r="BC11" s="47" t="s">
-        <v>46</v>
-      </c>
-      <c r="BD11" s="48"/>
-      <c r="BE11" s="48"/>
-      <c r="BF11" s="48"/>
-      <c r="BG11" s="48"/>
-      <c r="BH11" s="48"/>
-      <c r="BI11" s="48"/>
-      <c r="BJ11" s="48"/>
-      <c r="BK11" s="48"/>
-      <c r="BL11" s="48"/>
-      <c r="BM11" s="48"/>
-      <c r="BN11" s="49"/>
-      <c r="BQ11" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="BR11" s="48"/>
-      <c r="BS11" s="48"/>
-      <c r="BT11" s="48"/>
-      <c r="BU11" s="48"/>
-      <c r="BV11" s="48"/>
-      <c r="BW11" s="48"/>
-      <c r="BX11" s="48"/>
-      <c r="BY11" s="48"/>
-      <c r="BZ11" s="48"/>
-      <c r="CA11" s="48"/>
-      <c r="CB11" s="49"/>
+      <c r="AP11" s="46"/>
+      <c r="AQ11" s="46"/>
+      <c r="AR11" s="46"/>
+      <c r="AS11" s="46"/>
+      <c r="AT11" s="46"/>
+      <c r="AU11" s="46"/>
+      <c r="AV11" s="46"/>
+      <c r="AW11" s="46"/>
+      <c r="AX11" s="46"/>
+      <c r="AY11" s="46"/>
+      <c r="AZ11" s="47"/>
+      <c r="BC11" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="BD11" s="46"/>
+      <c r="BE11" s="46"/>
+      <c r="BF11" s="46"/>
+      <c r="BG11" s="46"/>
+      <c r="BH11" s="46"/>
+      <c r="BI11" s="46"/>
+      <c r="BJ11" s="46"/>
+      <c r="BK11" s="46"/>
+      <c r="BL11" s="46"/>
+      <c r="BM11" s="46"/>
+      <c r="BN11" s="47"/>
+      <c r="BQ11" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="BR11" s="46"/>
+      <c r="BS11" s="46"/>
+      <c r="BT11" s="46"/>
+      <c r="BU11" s="46"/>
+      <c r="BV11" s="46"/>
+      <c r="BW11" s="46"/>
+      <c r="BX11" s="46"/>
+      <c r="BY11" s="46"/>
+      <c r="BZ11" s="46"/>
+      <c r="CA11" s="46"/>
+      <c r="CB11" s="47"/>
+      <c r="CE11" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="CF11" s="46"/>
+      <c r="CG11" s="46"/>
+      <c r="CH11" s="46"/>
+      <c r="CI11" s="46"/>
+      <c r="CJ11" s="46"/>
+      <c r="CK11" s="46"/>
+      <c r="CL11" s="46"/>
+      <c r="CM11" s="46"/>
+      <c r="CN11" s="46"/>
+      <c r="CO11" s="46"/>
+      <c r="CP11" s="47"/>
     </row>
-    <row r="12" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="AA12" s="24"/>
-      <c r="AB12" s="4"/>
-      <c r="AC12" s="50" t="s">
+      <c r="AB12" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC12" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="AD12" s="51"/>
-      <c r="AE12" s="50" t="s">
+      <c r="AD12" s="44"/>
+      <c r="AE12" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="AF12" s="51"/>
-      <c r="AG12" s="50" t="s">
+      <c r="AF12" s="44"/>
+      <c r="AG12" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="AH12" s="51"/>
-      <c r="AI12" s="50" t="s">
+      <c r="AH12" s="44"/>
+      <c r="AI12" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="AJ12" s="51"/>
-      <c r="AK12" s="50" t="s">
+      <c r="AJ12" s="44"/>
+      <c r="AK12" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="AL12" s="51"/>
+      <c r="AL12" s="44"/>
       <c r="AO12" s="24"/>
-      <c r="AP12" s="4"/>
-      <c r="AQ12" s="50" t="s">
+      <c r="AP12" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ12" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="AR12" s="51"/>
-      <c r="AS12" s="50" t="s">
+      <c r="AR12" s="44"/>
+      <c r="AS12" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="AT12" s="51"/>
-      <c r="AU12" s="50" t="s">
+      <c r="AT12" s="44"/>
+      <c r="AU12" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="AV12" s="51"/>
-      <c r="AW12" s="50" t="s">
+      <c r="AV12" s="44"/>
+      <c r="AW12" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="AX12" s="51"/>
-      <c r="AY12" s="50" t="s">
+      <c r="AX12" s="44"/>
+      <c r="AY12" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="AZ12" s="51"/>
+      <c r="AZ12" s="44"/>
       <c r="BC12" s="24"/>
-      <c r="BD12" s="4"/>
-      <c r="BE12" s="50" t="s">
+      <c r="BD12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BE12" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="BF12" s="51"/>
-      <c r="BG12" s="50" t="s">
+      <c r="BF12" s="44"/>
+      <c r="BG12" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="BH12" s="51"/>
-      <c r="BI12" s="50" t="s">
+      <c r="BH12" s="44"/>
+      <c r="BI12" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="BJ12" s="51"/>
-      <c r="BK12" s="50" t="s">
+      <c r="BJ12" s="44"/>
+      <c r="BK12" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="BL12" s="51"/>
-      <c r="BM12" s="50" t="s">
+      <c r="BL12" s="44"/>
+      <c r="BM12" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="BN12" s="51"/>
+      <c r="BN12" s="44"/>
       <c r="BQ12" s="24"/>
-      <c r="BR12" s="4"/>
-      <c r="BS12" s="50" t="s">
+      <c r="BR12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BS12" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="BT12" s="51"/>
-      <c r="BU12" s="50" t="s">
+      <c r="BT12" s="44"/>
+      <c r="BU12" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="BV12" s="51"/>
-      <c r="BW12" s="50" t="s">
+      <c r="BV12" s="44"/>
+      <c r="BW12" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="BX12" s="51"/>
-      <c r="BY12" s="50" t="s">
+      <c r="BX12" s="44"/>
+      <c r="BY12" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="BZ12" s="51"/>
-      <c r="CA12" s="50" t="s">
+      <c r="BZ12" s="44"/>
+      <c r="CA12" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="CB12" s="51"/>
+      <c r="CB12" s="44"/>
+      <c r="CE12" s="24"/>
+      <c r="CF12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="CG12" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="CH12" s="44"/>
+      <c r="CI12" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="CJ12" s="44"/>
+      <c r="CK12" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL12" s="44"/>
+      <c r="CM12" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="CN12" s="44"/>
+      <c r="CO12" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="CP12" s="44"/>
     </row>
-    <row r="13" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="AA13" s="25" t="s">
         <v>16</v>
       </c>
@@ -8957,28 +9043,62 @@
       <c r="CB13" s="28" t="s">
         <v>8</v>
       </c>
+      <c r="CE13" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="CF13" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="CG13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="CH13" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="CI13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="CJ13" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="CK13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="CL13" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="CM13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="CN13" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="CO13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="CP13" s="28" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="14" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="47" t="s">
+    <row r="14" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="48"/>
-      <c r="L14" s="48"/>
-      <c r="M14" s="49"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="47"/>
       <c r="AA14" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="AB14" s="36">
-        <v>0.77429999999999999</v>
-      </c>
+      <c r="AB14" s="36"/>
       <c r="AC14" s="30"/>
       <c r="AD14" s="30"/>
       <c r="AE14" s="30"/>
@@ -9020,9 +9140,7 @@
       <c r="BQ14" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="BR14" s="36">
-        <v>0.77429999999999999</v>
-      </c>
+      <c r="BR14" s="36"/>
       <c r="BS14" s="30"/>
       <c r="BT14" s="30"/>
       <c r="BU14" s="30"/>
@@ -9033,30 +9151,44 @@
       <c r="BZ14" s="30"/>
       <c r="CA14" s="30"/>
       <c r="CB14" s="30"/>
+      <c r="CE14" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="CF14" s="36"/>
+      <c r="CG14" s="30"/>
+      <c r="CH14" s="30"/>
+      <c r="CI14" s="30"/>
+      <c r="CJ14" s="30"/>
+      <c r="CK14" s="30"/>
+      <c r="CL14" s="30"/>
+      <c r="CM14" s="30"/>
+      <c r="CN14" s="30"/>
+      <c r="CO14" s="30"/>
+      <c r="CP14" s="30"/>
     </row>
-    <row r="15" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="24"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="50" t="s">
+      <c r="D15" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="E15" s="51"/>
-      <c r="F15" s="50" t="s">
+      <c r="E15" s="44"/>
+      <c r="F15" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="51"/>
-      <c r="H15" s="50" t="s">
+      <c r="G15" s="44"/>
+      <c r="H15" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="51"/>
-      <c r="J15" s="50" t="s">
+      <c r="I15" s="44"/>
+      <c r="J15" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="51"/>
-      <c r="L15" s="50" t="s">
+      <c r="K15" s="44"/>
+      <c r="L15" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="M15" s="51"/>
+      <c r="M15" s="44"/>
       <c r="AA15" s="29" t="s">
         <v>39</v>
       </c>
@@ -9113,8 +9245,22 @@
       <c r="BZ15" s="30"/>
       <c r="CA15" s="30"/>
       <c r="CB15" s="30"/>
+      <c r="CE15" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="CF15" s="30"/>
+      <c r="CG15" s="30"/>
+      <c r="CH15" s="30"/>
+      <c r="CI15" s="30"/>
+      <c r="CJ15" s="30"/>
+      <c r="CK15" s="30"/>
+      <c r="CL15" s="30"/>
+      <c r="CM15" s="30"/>
+      <c r="CN15" s="30"/>
+      <c r="CO15" s="30"/>
+      <c r="CP15" s="30"/>
     </row>
-    <row r="16" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:94" x14ac:dyDescent="0.2">
       <c r="B16" s="25" t="s">
         <v>16</v>
       </c>
@@ -9207,13 +9353,27 @@
       <c r="BZ16" s="34"/>
       <c r="CA16" s="34"/>
       <c r="CB16" s="34"/>
+      <c r="CE16" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="CF16" s="34"/>
+      <c r="CG16" s="34"/>
+      <c r="CH16" s="34"/>
+      <c r="CI16" s="34"/>
+      <c r="CJ16" s="34"/>
+      <c r="CK16" s="34"/>
+      <c r="CL16" s="34"/>
+      <c r="CM16" s="34"/>
+      <c r="CN16" s="34"/>
+      <c r="CO16" s="34"/>
+      <c r="CP16" s="34"/>
     </row>
-    <row r="17" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:94" x14ac:dyDescent="0.2">
       <c r="B17" s="29" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D17" s="30">
         <v>74.77</v>
@@ -9301,10 +9461,24 @@
       <c r="BZ17" s="34"/>
       <c r="CA17" s="34"/>
       <c r="CB17" s="34"/>
+      <c r="CE17" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="CF17" s="34"/>
+      <c r="CG17" s="34"/>
+      <c r="CH17" s="34"/>
+      <c r="CI17" s="34"/>
+      <c r="CJ17" s="34"/>
+      <c r="CK17" s="34"/>
+      <c r="CL17" s="34"/>
+      <c r="CM17" s="34"/>
+      <c r="CN17" s="34"/>
+      <c r="CO17" s="34"/>
+      <c r="CP17" s="34"/>
     </row>
-    <row r="18" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:94" x14ac:dyDescent="0.2">
       <c r="B18" s="29" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C18" s="30"/>
       <c r="D18" s="30">
@@ -9393,8 +9567,22 @@
       <c r="BZ18" s="30"/>
       <c r="CA18" s="30"/>
       <c r="CB18" s="30"/>
+      <c r="CE18" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="CF18" s="30"/>
+      <c r="CG18" s="30"/>
+      <c r="CH18" s="30"/>
+      <c r="CI18" s="30"/>
+      <c r="CJ18" s="30"/>
+      <c r="CK18" s="30"/>
+      <c r="CL18" s="30"/>
+      <c r="CM18" s="30"/>
+      <c r="CN18" s="30"/>
+      <c r="CO18" s="30"/>
+      <c r="CP18" s="30"/>
     </row>
-    <row r="19" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:94" x14ac:dyDescent="0.2">
       <c r="B19" s="29" t="s">
         <v>20</v>
       </c>
@@ -9485,8 +9673,22 @@
       <c r="BZ19" s="30"/>
       <c r="CA19" s="30"/>
       <c r="CB19" s="30"/>
+      <c r="CE19" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="CF19" s="30"/>
+      <c r="CG19" s="30"/>
+      <c r="CH19" s="30"/>
+      <c r="CI19" s="35"/>
+      <c r="CJ19" s="30"/>
+      <c r="CK19" s="30"/>
+      <c r="CL19" s="30"/>
+      <c r="CM19" s="30"/>
+      <c r="CN19" s="30"/>
+      <c r="CO19" s="30"/>
+      <c r="CP19" s="30"/>
     </row>
-    <row r="20" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:94" x14ac:dyDescent="0.2">
       <c r="B20" s="29" t="s">
         <v>29</v>
       </c>
@@ -9577,8 +9779,22 @@
       <c r="BZ20" s="34"/>
       <c r="CA20" s="34"/>
       <c r="CB20" s="34"/>
+      <c r="CE20" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="CF20" s="34"/>
+      <c r="CG20" s="34"/>
+      <c r="CH20" s="34"/>
+      <c r="CI20" s="34"/>
+      <c r="CJ20" s="34"/>
+      <c r="CK20" s="34"/>
+      <c r="CL20" s="34"/>
+      <c r="CM20" s="34"/>
+      <c r="CN20" s="34"/>
+      <c r="CO20" s="34"/>
+      <c r="CP20" s="34"/>
     </row>
-    <row r="21" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:94" x14ac:dyDescent="0.2">
       <c r="B21" s="29" t="s">
         <v>25</v>
       </c>
@@ -9669,8 +9885,22 @@
       <c r="BZ21" s="30"/>
       <c r="CA21" s="30"/>
       <c r="CB21" s="30"/>
+      <c r="CE21" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="CF21" s="30"/>
+      <c r="CG21" s="30"/>
+      <c r="CH21" s="30"/>
+      <c r="CI21" s="30"/>
+      <c r="CJ21" s="30"/>
+      <c r="CK21" s="30"/>
+      <c r="CL21" s="30"/>
+      <c r="CM21" s="30"/>
+      <c r="CN21" s="30"/>
+      <c r="CO21" s="30"/>
+      <c r="CP21" s="30"/>
     </row>
-    <row r="22" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:94" x14ac:dyDescent="0.2">
       <c r="B22" s="29" t="s">
         <v>21</v>
       </c>
@@ -9757,8 +9987,21 @@
       <c r="BZ22" s="30"/>
       <c r="CA22" s="30"/>
       <c r="CB22" s="30"/>
+      <c r="CE22" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="CF22" s="30"/>
+      <c r="CG22" s="30"/>
+      <c r="CH22" s="30"/>
+      <c r="CJ22" s="30"/>
+      <c r="CK22" s="30"/>
+      <c r="CL22" s="30"/>
+      <c r="CM22" s="30"/>
+      <c r="CN22" s="30"/>
+      <c r="CO22" s="30"/>
+      <c r="CP22" s="30"/>
     </row>
-    <row r="23" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:94" x14ac:dyDescent="0.2">
       <c r="B23" s="29" t="s">
         <v>30</v>
       </c>
@@ -9849,8 +10092,22 @@
       <c r="BZ23" s="30"/>
       <c r="CA23" s="30"/>
       <c r="CB23" s="30"/>
+      <c r="CE23" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="CF23" s="30"/>
+      <c r="CG23" s="30"/>
+      <c r="CH23" s="30"/>
+      <c r="CI23" s="30"/>
+      <c r="CJ23" s="30"/>
+      <c r="CK23" s="30"/>
+      <c r="CL23" s="30"/>
+      <c r="CM23" s="30"/>
+      <c r="CN23" s="30"/>
+      <c r="CO23" s="30"/>
+      <c r="CP23" s="30"/>
     </row>
-    <row r="24" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:94" x14ac:dyDescent="0.2">
       <c r="B24" s="29" t="s">
         <v>26</v>
       </c>
@@ -9887,90 +10144,72 @@
       <c r="AB24" s="30"/>
       <c r="AC24" s="30"/>
       <c r="AD24" s="30"/>
-      <c r="AE24" s="30">
-        <v>48.29</v>
-      </c>
-      <c r="AF24" s="30">
-        <v>100</v>
-      </c>
+      <c r="AE24" s="30"/>
+      <c r="AF24" s="30"/>
       <c r="AG24" s="30"/>
       <c r="AH24" s="30"/>
       <c r="AI24" s="30"/>
       <c r="AJ24" s="30"/>
-      <c r="AK24" s="30">
-        <v>64.510000000000005</v>
-      </c>
-      <c r="AL24" s="30">
-        <v>22.63</v>
-      </c>
+      <c r="AK24" s="30"/>
+      <c r="AL24" s="30"/>
       <c r="AO24" s="29" t="s">
         <v>31</v>
       </c>
       <c r="AP24" s="30"/>
       <c r="AQ24" s="30"/>
       <c r="AR24" s="30"/>
-      <c r="AS24" s="30">
-        <v>45.78</v>
-      </c>
-      <c r="AT24" s="30">
-        <v>100</v>
-      </c>
+      <c r="AS24" s="30"/>
+      <c r="AT24" s="30"/>
       <c r="AU24" s="30"/>
       <c r="AV24" s="30"/>
       <c r="AW24" s="30"/>
       <c r="AX24" s="30"/>
-      <c r="AY24" s="30">
-        <v>65.260000000000005</v>
-      </c>
-      <c r="AZ24" s="30">
-        <v>20.66</v>
-      </c>
+      <c r="AY24" s="30"/>
+      <c r="AZ24" s="30"/>
       <c r="BC24" s="29" t="s">
         <v>31</v>
       </c>
       <c r="BD24" s="30"/>
       <c r="BE24" s="30"/>
       <c r="BF24" s="30"/>
-      <c r="BG24" s="30">
-        <v>50.06</v>
-      </c>
-      <c r="BH24" s="30">
-        <v>100</v>
-      </c>
+      <c r="BG24" s="30"/>
+      <c r="BH24" s="30"/>
       <c r="BI24" s="30"/>
       <c r="BJ24" s="30"/>
       <c r="BK24" s="30"/>
       <c r="BL24" s="30"/>
-      <c r="BM24" s="30">
-        <v>63.49</v>
-      </c>
-      <c r="BN24" s="30">
-        <v>26.06</v>
-      </c>
+      <c r="BM24" s="30"/>
+      <c r="BN24" s="30"/>
       <c r="BQ24" s="29" t="s">
         <v>31</v>
       </c>
       <c r="BR24" s="30"/>
       <c r="BS24" s="30"/>
       <c r="BT24" s="30"/>
-      <c r="BU24" s="30">
-        <v>50.97</v>
-      </c>
-      <c r="BV24" s="30">
-        <v>100</v>
-      </c>
+      <c r="BU24" s="30"/>
+      <c r="BV24" s="30"/>
       <c r="BW24" s="30"/>
       <c r="BX24" s="30"/>
       <c r="BY24" s="30"/>
       <c r="BZ24" s="30"/>
-      <c r="CA24" s="30">
-        <v>65.540000000000006</v>
-      </c>
-      <c r="CB24" s="30">
-        <v>25.74</v>
-      </c>
+      <c r="CA24" s="30"/>
+      <c r="CB24" s="30"/>
+      <c r="CE24" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="CF24" s="30"/>
+      <c r="CG24" s="30"/>
+      <c r="CH24" s="30"/>
+      <c r="CI24" s="30"/>
+      <c r="CJ24" s="30"/>
+      <c r="CK24" s="30"/>
+      <c r="CL24" s="30"/>
+      <c r="CM24" s="30"/>
+      <c r="CN24" s="30"/>
+      <c r="CO24" s="30"/>
+      <c r="CP24" s="30"/>
     </row>
-    <row r="25" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:94" x14ac:dyDescent="0.2">
       <c r="B25" s="29" t="s">
         <v>22</v>
       </c>
@@ -10008,90 +10247,72 @@
       <c r="AB25" s="30"/>
       <c r="AC25" s="30"/>
       <c r="AD25" s="30"/>
-      <c r="AE25" s="30">
-        <v>44.44</v>
-      </c>
-      <c r="AF25" s="30">
-        <v>100</v>
-      </c>
+      <c r="AE25" s="30"/>
+      <c r="AF25" s="30"/>
       <c r="AG25" s="30"/>
       <c r="AH25" s="30"/>
       <c r="AI25" s="30"/>
       <c r="AJ25" s="30"/>
-      <c r="AK25" s="30">
-        <v>63.16</v>
-      </c>
-      <c r="AL25" s="30">
-        <v>30.49</v>
-      </c>
+      <c r="AK25" s="30"/>
+      <c r="AL25" s="30"/>
       <c r="AO25" s="29" t="s">
         <v>40</v>
       </c>
       <c r="AP25" s="30"/>
       <c r="AQ25" s="30"/>
       <c r="AR25" s="30"/>
-      <c r="AS25" s="30">
-        <v>41.72</v>
-      </c>
-      <c r="AT25" s="30">
-        <v>100</v>
-      </c>
+      <c r="AS25" s="30"/>
+      <c r="AT25" s="30"/>
       <c r="AU25" s="30"/>
       <c r="AV25" s="30"/>
       <c r="AW25" s="30"/>
       <c r="AX25" s="30"/>
-      <c r="AY25" s="30">
-        <v>63.83</v>
-      </c>
-      <c r="AZ25" s="30">
-        <v>23.65</v>
-      </c>
+      <c r="AY25" s="30"/>
+      <c r="AZ25" s="30"/>
       <c r="BC25" s="29" t="s">
         <v>40</v>
       </c>
       <c r="BD25" s="30"/>
       <c r="BE25" s="30"/>
       <c r="BF25" s="30"/>
-      <c r="BG25" s="30">
-        <v>43.56</v>
-      </c>
-      <c r="BH25" s="30">
-        <v>100</v>
-      </c>
+      <c r="BG25" s="30"/>
+      <c r="BH25" s="30"/>
       <c r="BI25" s="30"/>
       <c r="BJ25" s="30"/>
       <c r="BK25" s="30"/>
       <c r="BL25" s="30"/>
-      <c r="BM25" s="30">
-        <v>61.24</v>
-      </c>
-      <c r="BN25" s="30">
-        <v>26.85</v>
-      </c>
+      <c r="BM25" s="30"/>
+      <c r="BN25" s="30"/>
       <c r="BQ25" s="29" t="s">
         <v>40</v>
       </c>
       <c r="BR25" s="30"/>
       <c r="BS25" s="30"/>
       <c r="BT25" s="30"/>
-      <c r="BU25" s="30">
-        <v>43.71</v>
-      </c>
-      <c r="BV25" s="30">
-        <v>100</v>
-      </c>
+      <c r="BU25" s="30"/>
+      <c r="BV25" s="30"/>
       <c r="BW25" s="30"/>
       <c r="BX25" s="30"/>
       <c r="BY25" s="30"/>
       <c r="BZ25" s="30"/>
-      <c r="CA25" s="30">
-        <v>63.4</v>
-      </c>
-      <c r="CB25" s="30">
-        <v>22.59</v>
-      </c>
+      <c r="CA25" s="30"/>
+      <c r="CB25" s="30"/>
+      <c r="CE25" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="CF25" s="30"/>
+      <c r="CG25" s="30"/>
+      <c r="CH25" s="30"/>
+      <c r="CI25" s="30"/>
+      <c r="CJ25" s="30"/>
+      <c r="CK25" s="30"/>
+      <c r="CL25" s="30"/>
+      <c r="CM25" s="30"/>
+      <c r="CN25" s="30"/>
+      <c r="CO25" s="30"/>
+      <c r="CP25" s="30"/>
     </row>
-    <row r="26" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:94" x14ac:dyDescent="0.2">
       <c r="B26" s="29" t="s">
         <v>23</v>
       </c>
@@ -10178,8 +10399,22 @@
       <c r="BZ26" s="30"/>
       <c r="CA26" s="30"/>
       <c r="CB26" s="30"/>
+      <c r="CE26" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="CF26" s="30"/>
+      <c r="CG26" s="30"/>
+      <c r="CH26" s="30"/>
+      <c r="CI26" s="30"/>
+      <c r="CJ26" s="30"/>
+      <c r="CK26" s="30"/>
+      <c r="CL26" s="30"/>
+      <c r="CM26" s="30"/>
+      <c r="CN26" s="30"/>
+      <c r="CO26" s="30"/>
+      <c r="CP26" s="30"/>
     </row>
-    <row r="27" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:94" x14ac:dyDescent="0.2">
       <c r="B27" s="29" t="s">
         <v>31</v>
       </c>
@@ -10216,90 +10451,72 @@
       <c r="AB27" s="30"/>
       <c r="AC27" s="30"/>
       <c r="AD27" s="30"/>
-      <c r="AE27" s="30">
-        <v>34.159999999999997</v>
-      </c>
-      <c r="AF27" s="30">
-        <v>100</v>
-      </c>
+      <c r="AE27" s="30"/>
+      <c r="AF27" s="30"/>
       <c r="AG27" s="30"/>
       <c r="AH27" s="30"/>
       <c r="AI27" s="30"/>
       <c r="AJ27" s="30"/>
-      <c r="AK27" s="30">
-        <v>59.73</v>
-      </c>
-      <c r="AL27" s="30">
-        <v>45.45</v>
-      </c>
+      <c r="AK27" s="30"/>
+      <c r="AL27" s="30"/>
       <c r="AO27" s="29" t="s">
         <v>32</v>
       </c>
       <c r="AP27" s="30"/>
       <c r="AQ27" s="30"/>
       <c r="AR27" s="30"/>
-      <c r="AS27" s="30">
-        <v>33.619999999999997</v>
-      </c>
-      <c r="AT27" s="30">
-        <v>100</v>
-      </c>
+      <c r="AS27" s="30"/>
+      <c r="AT27" s="30"/>
       <c r="AU27" s="30"/>
       <c r="AV27" s="30"/>
       <c r="AW27" s="30"/>
       <c r="AX27" s="30"/>
-      <c r="AY27" s="30">
-        <v>60.08</v>
-      </c>
-      <c r="AZ27" s="30">
-        <v>39.880000000000003</v>
-      </c>
+      <c r="AY27" s="30"/>
+      <c r="AZ27" s="30"/>
       <c r="BC27" s="29" t="s">
         <v>32</v>
       </c>
       <c r="BD27" s="30"/>
       <c r="BE27" s="30"/>
       <c r="BF27" s="30"/>
-      <c r="BG27" s="30">
-        <v>34.56</v>
-      </c>
-      <c r="BH27" s="30">
-        <v>100</v>
-      </c>
+      <c r="BG27" s="30"/>
+      <c r="BH27" s="30"/>
       <c r="BI27" s="30"/>
       <c r="BJ27" s="30"/>
       <c r="BK27" s="30"/>
       <c r="BL27" s="30"/>
-      <c r="BM27" s="30">
-        <v>54.78</v>
-      </c>
-      <c r="BN27" s="30">
-        <v>60.73</v>
-      </c>
+      <c r="BM27" s="30"/>
+      <c r="BN27" s="30"/>
       <c r="BQ27" s="29" t="s">
         <v>32</v>
       </c>
       <c r="BR27" s="30"/>
       <c r="BS27" s="30"/>
       <c r="BT27" s="30"/>
-      <c r="BU27" s="30">
-        <v>35.6</v>
-      </c>
-      <c r="BV27" s="30">
-        <v>100</v>
-      </c>
+      <c r="BU27" s="30"/>
+      <c r="BV27" s="30"/>
       <c r="BW27" s="30"/>
       <c r="BX27" s="30"/>
       <c r="BY27" s="30"/>
       <c r="BZ27" s="30"/>
-      <c r="CA27" s="30">
-        <v>57.19</v>
-      </c>
-      <c r="CB27" s="30">
-        <v>64.8</v>
-      </c>
+      <c r="CA27" s="30"/>
+      <c r="CB27" s="30"/>
+      <c r="CE27" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="CF27" s="30"/>
+      <c r="CG27" s="30"/>
+      <c r="CH27" s="30"/>
+      <c r="CI27" s="30"/>
+      <c r="CJ27" s="30"/>
+      <c r="CK27" s="30"/>
+      <c r="CL27" s="30"/>
+      <c r="CM27" s="30"/>
+      <c r="CN27" s="30"/>
+      <c r="CO27" s="30"/>
+      <c r="CP27" s="30"/>
     </row>
-    <row r="28" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:94" x14ac:dyDescent="0.2">
       <c r="B28" s="29" t="s">
         <v>40</v>
       </c>
@@ -10386,8 +10603,22 @@
       <c r="BZ28" s="30"/>
       <c r="CA28" s="30"/>
       <c r="CB28" s="30"/>
+      <c r="CE28" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="CF28" s="30"/>
+      <c r="CG28" s="30"/>
+      <c r="CH28" s="30"/>
+      <c r="CI28" s="30"/>
+      <c r="CJ28" s="30"/>
+      <c r="CK28" s="30"/>
+      <c r="CL28" s="30"/>
+      <c r="CM28" s="30"/>
+      <c r="CN28" s="30"/>
+      <c r="CO28" s="30"/>
+      <c r="CP28" s="30"/>
     </row>
-    <row r="29" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:94" x14ac:dyDescent="0.2">
       <c r="B29" s="29" t="s">
         <v>27</v>
       </c>
@@ -10424,90 +10655,72 @@
       <c r="AB29" s="30"/>
       <c r="AC29" s="30"/>
       <c r="AD29" s="30"/>
-      <c r="AE29" s="30">
-        <v>32.31</v>
-      </c>
-      <c r="AF29" s="30">
-        <v>100</v>
-      </c>
+      <c r="AE29" s="30"/>
+      <c r="AF29" s="30"/>
       <c r="AG29" s="30"/>
       <c r="AH29" s="30"/>
       <c r="AI29" s="30"/>
       <c r="AJ29" s="30"/>
-      <c r="AK29" s="30">
-        <v>56.9</v>
-      </c>
-      <c r="AL29" s="30">
-        <v>75.77</v>
-      </c>
+      <c r="AK29" s="30"/>
+      <c r="AL29" s="30"/>
       <c r="AO29" s="29" t="s">
         <v>33</v>
       </c>
       <c r="AP29" s="30"/>
       <c r="AQ29" s="30"/>
       <c r="AR29" s="30"/>
-      <c r="AS29" s="30">
-        <v>30.25</v>
-      </c>
-      <c r="AT29" s="30">
-        <v>100</v>
-      </c>
+      <c r="AS29" s="30"/>
+      <c r="AT29" s="30"/>
       <c r="AU29" s="30"/>
       <c r="AV29" s="30"/>
       <c r="AW29" s="30"/>
       <c r="AX29" s="30"/>
-      <c r="AY29" s="30">
-        <v>56.47</v>
-      </c>
-      <c r="AZ29" s="30">
-        <v>76.81</v>
-      </c>
+      <c r="AY29" s="30"/>
+      <c r="AZ29" s="30"/>
       <c r="BC29" s="29" t="s">
         <v>33</v>
       </c>
       <c r="BD29" s="30"/>
       <c r="BE29" s="30"/>
       <c r="BF29" s="30"/>
-      <c r="BG29" s="30">
-        <v>30.12</v>
-      </c>
-      <c r="BH29" s="30">
-        <v>100</v>
-      </c>
+      <c r="BG29" s="30"/>
+      <c r="BH29" s="30"/>
       <c r="BI29" s="30"/>
       <c r="BJ29" s="30"/>
       <c r="BK29" s="30"/>
       <c r="BL29" s="30"/>
-      <c r="BM29" s="30">
-        <v>48.55</v>
-      </c>
-      <c r="BN29" s="30">
-        <v>93.46</v>
-      </c>
+      <c r="BM29" s="30"/>
+      <c r="BN29" s="30"/>
       <c r="BQ29" s="29" t="s">
         <v>33</v>
       </c>
       <c r="BR29" s="30"/>
       <c r="BS29" s="30"/>
       <c r="BT29" s="30"/>
-      <c r="BU29" s="30">
-        <v>31.93</v>
-      </c>
-      <c r="BV29" s="30">
-        <v>100</v>
-      </c>
+      <c r="BU29" s="30"/>
+      <c r="BV29" s="30"/>
       <c r="BW29" s="30"/>
       <c r="BX29" s="30"/>
       <c r="BY29" s="30"/>
       <c r="BZ29" s="30"/>
-      <c r="CA29" s="30">
-        <v>51.5</v>
-      </c>
-      <c r="CB29" s="30">
-        <v>93.76</v>
-      </c>
+      <c r="CA29" s="30"/>
+      <c r="CB29" s="30"/>
+      <c r="CE29" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="CF29" s="30"/>
+      <c r="CG29" s="30"/>
+      <c r="CH29" s="30"/>
+      <c r="CI29" s="30"/>
+      <c r="CJ29" s="30"/>
+      <c r="CK29" s="30"/>
+      <c r="CL29" s="30"/>
+      <c r="CM29" s="30"/>
+      <c r="CN29" s="30"/>
+      <c r="CO29" s="30"/>
+      <c r="CP29" s="30"/>
     </row>
-    <row r="30" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:94" x14ac:dyDescent="0.2">
       <c r="B30" s="29" t="s">
         <v>32</v>
       </c>
@@ -10544,90 +10757,72 @@
       <c r="AB30" s="30"/>
       <c r="AC30" s="30"/>
       <c r="AD30" s="30"/>
-      <c r="AE30" s="30">
-        <v>32.01</v>
-      </c>
-      <c r="AF30" s="30">
-        <v>100</v>
-      </c>
+      <c r="AE30" s="30"/>
+      <c r="AF30" s="30"/>
       <c r="AG30" s="30"/>
       <c r="AH30" s="30"/>
       <c r="AI30" s="30"/>
       <c r="AJ30" s="30"/>
-      <c r="AK30" s="30">
-        <v>56.02</v>
-      </c>
-      <c r="AL30" s="30">
-        <v>91.89</v>
-      </c>
+      <c r="AK30" s="30"/>
+      <c r="AL30" s="30"/>
       <c r="AO30" s="29" t="s">
         <v>34</v>
       </c>
       <c r="AP30" s="30"/>
       <c r="AQ30" s="30"/>
       <c r="AR30" s="30"/>
-      <c r="AS30" s="30">
-        <v>29.66</v>
-      </c>
-      <c r="AT30" s="30">
-        <v>100</v>
-      </c>
+      <c r="AS30" s="30"/>
+      <c r="AT30" s="30"/>
       <c r="AU30" s="30"/>
       <c r="AV30" s="30"/>
       <c r="AW30" s="30"/>
       <c r="AX30" s="30"/>
-      <c r="AY30" s="30">
-        <v>55.24</v>
-      </c>
-      <c r="AZ30" s="30">
-        <v>92.09</v>
-      </c>
+      <c r="AY30" s="30"/>
+      <c r="AZ30" s="30"/>
       <c r="BC30" s="29" t="s">
         <v>34</v>
       </c>
       <c r="BD30" s="30"/>
       <c r="BE30" s="30"/>
       <c r="BF30" s="30"/>
-      <c r="BG30" s="30">
-        <v>29.05</v>
-      </c>
-      <c r="BH30" s="30">
-        <v>100</v>
-      </c>
+      <c r="BG30" s="30"/>
+      <c r="BH30" s="30"/>
       <c r="BI30" s="30"/>
       <c r="BJ30" s="30"/>
       <c r="BK30" s="30"/>
       <c r="BL30" s="30"/>
-      <c r="BM30" s="30">
-        <v>46.66</v>
-      </c>
-      <c r="BN30" s="30">
-        <v>93.77</v>
-      </c>
+      <c r="BM30" s="30"/>
+      <c r="BN30" s="30"/>
       <c r="BQ30" s="29" t="s">
         <v>34</v>
       </c>
       <c r="BR30" s="30"/>
       <c r="BS30" s="30"/>
       <c r="BT30" s="30"/>
-      <c r="BU30" s="30">
-        <v>31.23</v>
-      </c>
-      <c r="BV30" s="30">
-        <v>100</v>
-      </c>
+      <c r="BU30" s="30"/>
+      <c r="BV30" s="30"/>
       <c r="BW30" s="30"/>
       <c r="BX30" s="30"/>
       <c r="BY30" s="30"/>
       <c r="BZ30" s="30"/>
-      <c r="CA30" s="30">
-        <v>50</v>
-      </c>
-      <c r="CB30" s="30">
-        <v>93.93</v>
-      </c>
+      <c r="CA30" s="30"/>
+      <c r="CB30" s="30"/>
+      <c r="CE30" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="CF30" s="30"/>
+      <c r="CG30" s="30"/>
+      <c r="CH30" s="30"/>
+      <c r="CI30" s="30"/>
+      <c r="CJ30" s="30"/>
+      <c r="CK30" s="30"/>
+      <c r="CL30" s="30"/>
+      <c r="CM30" s="30"/>
+      <c r="CN30" s="30"/>
+      <c r="CO30" s="30"/>
+      <c r="CP30" s="30"/>
     </row>
-    <row r="31" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:94" x14ac:dyDescent="0.2">
       <c r="B31" s="29" t="s">
         <v>28</v>
       </c>
@@ -10664,90 +10859,72 @@
       <c r="AB31" s="30"/>
       <c r="AC31" s="30"/>
       <c r="AD31" s="30"/>
-      <c r="AE31" s="30">
-        <v>31.81</v>
-      </c>
-      <c r="AF31" s="30">
-        <v>100</v>
-      </c>
+      <c r="AE31" s="30"/>
+      <c r="AF31" s="30"/>
       <c r="AG31" s="30"/>
       <c r="AH31" s="30"/>
       <c r="AI31" s="30"/>
       <c r="AJ31" s="30"/>
-      <c r="AK31" s="30">
-        <v>55.36</v>
-      </c>
-      <c r="AL31" s="30">
-        <v>94.02</v>
-      </c>
+      <c r="AK31" s="30"/>
+      <c r="AL31" s="30"/>
       <c r="AO31" s="29" t="s">
         <v>35</v>
       </c>
       <c r="AP31" s="30"/>
       <c r="AQ31" s="30"/>
       <c r="AR31" s="30"/>
-      <c r="AS31" s="30">
-        <v>29.29</v>
-      </c>
-      <c r="AT31" s="30">
-        <v>100</v>
-      </c>
+      <c r="AS31" s="30"/>
+      <c r="AT31" s="30"/>
       <c r="AU31" s="30"/>
       <c r="AV31" s="30"/>
       <c r="AW31" s="30"/>
       <c r="AX31" s="30"/>
-      <c r="AY31" s="30">
-        <v>54.38</v>
-      </c>
-      <c r="AZ31" s="30">
-        <v>93.02</v>
-      </c>
+      <c r="AY31" s="30"/>
+      <c r="AZ31" s="30"/>
       <c r="BC31" s="29" t="s">
         <v>35</v>
       </c>
       <c r="BD31" s="30"/>
       <c r="BE31" s="30"/>
       <c r="BF31" s="30"/>
-      <c r="BG31" s="30">
-        <v>28.39</v>
-      </c>
-      <c r="BH31" s="30">
-        <v>100</v>
-      </c>
+      <c r="BG31" s="30"/>
+      <c r="BH31" s="30"/>
       <c r="BI31" s="30"/>
       <c r="BJ31" s="30"/>
       <c r="BK31" s="30"/>
       <c r="BL31" s="30"/>
-      <c r="BM31" s="30">
-        <v>45.3</v>
-      </c>
-      <c r="BN31" s="30">
-        <v>93.93</v>
-      </c>
+      <c r="BM31" s="30"/>
+      <c r="BN31" s="30"/>
       <c r="BQ31" s="29" t="s">
         <v>35</v>
       </c>
       <c r="BR31" s="30"/>
       <c r="BS31" s="30"/>
       <c r="BT31" s="30"/>
-      <c r="BU31" s="30">
-        <v>30.82</v>
-      </c>
-      <c r="BV31" s="30">
-        <v>100</v>
-      </c>
+      <c r="BU31" s="30"/>
+      <c r="BV31" s="30"/>
       <c r="BW31" s="30"/>
       <c r="BX31" s="30"/>
       <c r="BY31" s="30"/>
       <c r="BZ31" s="30"/>
-      <c r="CA31" s="30">
-        <v>48.94</v>
-      </c>
-      <c r="CB31" s="30">
-        <v>94.03</v>
-      </c>
+      <c r="CA31" s="30"/>
+      <c r="CB31" s="30"/>
+      <c r="CE31" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="CF31" s="30"/>
+      <c r="CG31" s="30"/>
+      <c r="CH31" s="30"/>
+      <c r="CI31" s="30"/>
+      <c r="CJ31" s="30"/>
+      <c r="CK31" s="30"/>
+      <c r="CL31" s="30"/>
+      <c r="CM31" s="30"/>
+      <c r="CN31" s="30"/>
+      <c r="CO31" s="30"/>
+      <c r="CP31" s="30"/>
     </row>
-    <row r="32" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:94" x14ac:dyDescent="0.2">
       <c r="B32" s="29" t="s">
         <v>33</v>
       </c>
@@ -10784,90 +10961,72 @@
       <c r="AB32" s="30"/>
       <c r="AC32" s="30"/>
       <c r="AD32" s="30"/>
-      <c r="AE32" s="30">
-        <v>31.67</v>
-      </c>
-      <c r="AF32" s="30">
-        <v>100</v>
-      </c>
+      <c r="AE32" s="30"/>
+      <c r="AF32" s="30"/>
       <c r="AG32" s="30"/>
       <c r="AH32" s="30"/>
       <c r="AI32" s="30"/>
       <c r="AJ32" s="30"/>
-      <c r="AK32" s="30">
-        <v>54.86</v>
-      </c>
-      <c r="AL32" s="30">
-        <v>94.18</v>
-      </c>
+      <c r="AK32" s="30"/>
+      <c r="AL32" s="30"/>
       <c r="AO32" s="29" t="s">
         <v>36</v>
       </c>
       <c r="AP32" s="30"/>
       <c r="AQ32" s="30"/>
       <c r="AR32" s="30"/>
-      <c r="AS32" s="30">
-        <v>29.06</v>
-      </c>
-      <c r="AT32" s="30">
-        <v>100</v>
-      </c>
+      <c r="AS32" s="30"/>
+      <c r="AT32" s="30"/>
       <c r="AU32" s="30"/>
       <c r="AV32" s="30"/>
       <c r="AW32" s="30"/>
       <c r="AX32" s="30"/>
-      <c r="AY32" s="30">
-        <v>53.75</v>
-      </c>
-      <c r="AZ32" s="30">
-        <v>93.19</v>
-      </c>
+      <c r="AY32" s="30"/>
+      <c r="AZ32" s="30"/>
       <c r="BC32" s="29" t="s">
         <v>36</v>
       </c>
       <c r="BD32" s="30"/>
       <c r="BE32" s="30"/>
       <c r="BF32" s="30"/>
-      <c r="BG32" s="30">
-        <v>27.96</v>
-      </c>
-      <c r="BH32" s="30">
-        <v>100</v>
-      </c>
+      <c r="BG32" s="30"/>
+      <c r="BH32" s="30"/>
       <c r="BI32" s="30"/>
       <c r="BJ32" s="30"/>
       <c r="BK32" s="30"/>
       <c r="BL32" s="30"/>
-      <c r="BM32" s="30">
-        <v>44.28</v>
-      </c>
-      <c r="BN32" s="30">
-        <v>94.04</v>
-      </c>
+      <c r="BM32" s="30"/>
+      <c r="BN32" s="30"/>
       <c r="BQ32" s="29" t="s">
         <v>36</v>
       </c>
       <c r="BR32" s="30"/>
       <c r="BS32" s="30"/>
       <c r="BT32" s="30"/>
-      <c r="BU32" s="30">
-        <v>30.57</v>
-      </c>
-      <c r="BV32" s="30">
-        <v>100</v>
-      </c>
+      <c r="BU32" s="30"/>
+      <c r="BV32" s="30"/>
       <c r="BW32" s="30"/>
       <c r="BX32" s="30"/>
       <c r="BY32" s="30"/>
       <c r="BZ32" s="30"/>
-      <c r="CA32" s="30">
-        <v>48.15</v>
-      </c>
-      <c r="CB32" s="30">
-        <v>94.09</v>
-      </c>
+      <c r="CA32" s="30"/>
+      <c r="CB32" s="30"/>
+      <c r="CE32" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="CF32" s="30"/>
+      <c r="CG32" s="30"/>
+      <c r="CH32" s="30"/>
+      <c r="CI32" s="30"/>
+      <c r="CJ32" s="30"/>
+      <c r="CK32" s="30"/>
+      <c r="CL32" s="30"/>
+      <c r="CM32" s="30"/>
+      <c r="CN32" s="30"/>
+      <c r="CO32" s="30"/>
+      <c r="CP32" s="30"/>
     </row>
-    <row r="33" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:94" x14ac:dyDescent="0.2">
       <c r="B33" s="29" t="s">
         <v>34</v>
       </c>
@@ -10904,90 +11063,72 @@
       <c r="AB33" s="30"/>
       <c r="AC33" s="30"/>
       <c r="AD33" s="30"/>
-      <c r="AE33" s="30">
-        <v>31.57</v>
-      </c>
-      <c r="AF33" s="30">
-        <v>100</v>
-      </c>
+      <c r="AE33" s="30"/>
+      <c r="AF33" s="30"/>
       <c r="AG33" s="30"/>
       <c r="AH33" s="30"/>
       <c r="AI33" s="30"/>
       <c r="AJ33" s="30"/>
-      <c r="AK33" s="30">
-        <v>54.47</v>
-      </c>
-      <c r="AL33" s="30">
-        <v>94.29</v>
-      </c>
+      <c r="AK33" s="30"/>
+      <c r="AL33" s="30"/>
       <c r="AO33" s="29" t="s">
         <v>37</v>
       </c>
       <c r="AP33" s="30"/>
       <c r="AQ33" s="30"/>
       <c r="AR33" s="30"/>
-      <c r="AS33" s="30">
-        <v>28.88</v>
-      </c>
-      <c r="AT33" s="30">
-        <v>100</v>
-      </c>
+      <c r="AS33" s="30"/>
+      <c r="AT33" s="30"/>
       <c r="AU33" s="30"/>
       <c r="AV33" s="30"/>
       <c r="AW33" s="30"/>
       <c r="AX33" s="30"/>
-      <c r="AY33" s="30">
-        <v>53.25</v>
-      </c>
-      <c r="AZ33" s="30">
-        <v>93.3</v>
-      </c>
+      <c r="AY33" s="30"/>
+      <c r="AZ33" s="30"/>
       <c r="BC33" s="29" t="s">
         <v>37</v>
       </c>
       <c r="BD33" s="30"/>
       <c r="BE33" s="30"/>
       <c r="BF33" s="30"/>
-      <c r="BG33" s="30">
-        <v>27.65</v>
-      </c>
-      <c r="BH33" s="30">
-        <v>100</v>
-      </c>
+      <c r="BG33" s="30"/>
+      <c r="BH33" s="30"/>
       <c r="BI33" s="30"/>
       <c r="BJ33" s="30"/>
       <c r="BK33" s="30"/>
       <c r="BL33" s="30"/>
-      <c r="BM33" s="30">
-        <v>43.48</v>
-      </c>
-      <c r="BN33" s="30">
-        <v>94.11</v>
-      </c>
+      <c r="BM33" s="30"/>
+      <c r="BN33" s="30"/>
       <c r="BQ33" s="29" t="s">
         <v>37</v>
       </c>
       <c r="BR33" s="30"/>
       <c r="BS33" s="30"/>
       <c r="BT33" s="30"/>
-      <c r="BU33" s="30">
-        <v>30.38</v>
-      </c>
-      <c r="BV33" s="30">
-        <v>100</v>
-      </c>
+      <c r="BU33" s="30"/>
+      <c r="BV33" s="30"/>
       <c r="BW33" s="30"/>
       <c r="BX33" s="30"/>
       <c r="BY33" s="30"/>
       <c r="BZ33" s="30"/>
-      <c r="CA33" s="30">
-        <v>47.54</v>
-      </c>
-      <c r="CB33" s="30">
-        <v>94.13</v>
-      </c>
+      <c r="CA33" s="30"/>
+      <c r="CB33" s="30"/>
+      <c r="CE33" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="CF33" s="30"/>
+      <c r="CG33" s="30"/>
+      <c r="CH33" s="30"/>
+      <c r="CI33" s="30"/>
+      <c r="CJ33" s="30"/>
+      <c r="CK33" s="30"/>
+      <c r="CL33" s="30"/>
+      <c r="CM33" s="30"/>
+      <c r="CN33" s="30"/>
+      <c r="CO33" s="30"/>
+      <c r="CP33" s="30"/>
     </row>
-    <row r="34" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:94" x14ac:dyDescent="0.2">
       <c r="B34" s="29" t="s">
         <v>35</v>
       </c>
@@ -11024,90 +11165,72 @@
       <c r="AB34" s="30"/>
       <c r="AC34" s="30"/>
       <c r="AD34" s="30"/>
-      <c r="AE34" s="37">
-        <v>31.5</v>
-      </c>
-      <c r="AF34" s="30">
-        <v>100</v>
-      </c>
+      <c r="AE34" s="37"/>
+      <c r="AF34" s="30"/>
       <c r="AG34" s="30"/>
       <c r="AH34" s="30"/>
       <c r="AI34" s="30"/>
       <c r="AJ34" s="30"/>
-      <c r="AK34" s="30">
-        <v>54.14</v>
-      </c>
-      <c r="AL34" s="30">
-        <v>94.36</v>
-      </c>
+      <c r="AK34" s="30"/>
+      <c r="AL34" s="30"/>
       <c r="AO34" s="29" t="s">
         <v>38</v>
       </c>
       <c r="AP34" s="30"/>
       <c r="AQ34" s="30"/>
       <c r="AR34" s="30"/>
-      <c r="AS34" s="37">
-        <v>28.76</v>
-      </c>
-      <c r="AT34" s="30">
-        <v>100</v>
-      </c>
+      <c r="AS34" s="37"/>
+      <c r="AT34" s="30"/>
       <c r="AU34" s="30"/>
       <c r="AV34" s="30"/>
       <c r="AW34" s="30"/>
       <c r="AX34" s="30"/>
-      <c r="AY34" s="30">
-        <v>52.86</v>
-      </c>
-      <c r="AZ34" s="30">
-        <v>93.38</v>
-      </c>
+      <c r="AY34" s="30"/>
+      <c r="AZ34" s="30"/>
       <c r="BC34" s="29" t="s">
         <v>38</v>
       </c>
       <c r="BD34" s="30"/>
       <c r="BE34" s="30"/>
       <c r="BF34" s="30"/>
-      <c r="BG34" s="37">
-        <v>27.43</v>
-      </c>
-      <c r="BH34" s="30">
-        <v>100</v>
-      </c>
+      <c r="BG34" s="37"/>
+      <c r="BH34" s="30"/>
       <c r="BI34" s="30"/>
       <c r="BJ34" s="30"/>
       <c r="BK34" s="30"/>
       <c r="BL34" s="30"/>
-      <c r="BM34" s="30">
-        <v>42.84</v>
-      </c>
-      <c r="BN34" s="30">
-        <v>94.17</v>
-      </c>
+      <c r="BM34" s="30"/>
+      <c r="BN34" s="30"/>
       <c r="BQ34" s="29" t="s">
         <v>38</v>
       </c>
       <c r="BR34" s="30"/>
       <c r="BS34" s="30"/>
       <c r="BT34" s="30"/>
-      <c r="BU34" s="37">
-        <v>30.24</v>
-      </c>
-      <c r="BV34" s="30">
-        <v>100</v>
-      </c>
+      <c r="BU34" s="37"/>
+      <c r="BV34" s="30"/>
       <c r="BW34" s="30"/>
       <c r="BX34" s="30"/>
       <c r="BY34" s="30"/>
       <c r="BZ34" s="30"/>
-      <c r="CA34" s="30">
-        <v>47.06</v>
-      </c>
-      <c r="CB34" s="30">
-        <v>94.16</v>
-      </c>
+      <c r="CA34" s="30"/>
+      <c r="CB34" s="30"/>
+      <c r="CE34" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="CF34" s="30"/>
+      <c r="CG34" s="30"/>
+      <c r="CH34" s="30"/>
+      <c r="CI34" s="37"/>
+      <c r="CJ34" s="30"/>
+      <c r="CK34" s="30"/>
+      <c r="CL34" s="30"/>
+      <c r="CM34" s="30"/>
+      <c r="CN34" s="30"/>
+      <c r="CO34" s="30"/>
+      <c r="CP34" s="30"/>
     </row>
-    <row r="35" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B35" s="29" t="s">
         <v>36</v>
       </c>
@@ -11141,57 +11264,70 @@
       <c r="AB35" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="AC35" s="38"/>
-      <c r="AD35" s="39"/>
-      <c r="AE35" s="38"/>
-      <c r="AF35" s="39"/>
-      <c r="AG35" s="40"/>
-      <c r="AH35" s="41"/>
-      <c r="AI35" s="38"/>
-      <c r="AJ35" s="39"/>
-      <c r="AK35" s="38"/>
-      <c r="AL35" s="39"/>
+      <c r="AC35" s="39"/>
+      <c r="AD35" s="40"/>
+      <c r="AE35" s="39"/>
+      <c r="AF35" s="40"/>
+      <c r="AG35" s="41"/>
+      <c r="AH35" s="42"/>
+      <c r="AI35" s="39"/>
+      <c r="AJ35" s="40"/>
+      <c r="AK35" s="39"/>
+      <c r="AL35" s="40"/>
       <c r="AP35" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="AQ35" s="38"/>
-      <c r="AR35" s="39"/>
-      <c r="AS35" s="38"/>
-      <c r="AT35" s="39"/>
-      <c r="AU35" s="40"/>
-      <c r="AV35" s="41"/>
-      <c r="AW35" s="38"/>
-      <c r="AX35" s="39"/>
-      <c r="AY35" s="38"/>
-      <c r="AZ35" s="39"/>
+      <c r="AQ35" s="39"/>
+      <c r="AR35" s="40"/>
+      <c r="AS35" s="39"/>
+      <c r="AT35" s="40"/>
+      <c r="AU35" s="41"/>
+      <c r="AV35" s="42"/>
+      <c r="AW35" s="39"/>
+      <c r="AX35" s="40"/>
+      <c r="AY35" s="39"/>
+      <c r="AZ35" s="40"/>
       <c r="BD35" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="BE35" s="38"/>
-      <c r="BF35" s="39"/>
-      <c r="BG35" s="38"/>
-      <c r="BH35" s="39"/>
-      <c r="BI35" s="40"/>
-      <c r="BJ35" s="41"/>
-      <c r="BK35" s="38"/>
-      <c r="BL35" s="39"/>
-      <c r="BM35" s="38"/>
-      <c r="BN35" s="39"/>
+      <c r="BE35" s="39"/>
+      <c r="BF35" s="40"/>
+      <c r="BG35" s="39"/>
+      <c r="BH35" s="40"/>
+      <c r="BI35" s="41"/>
+      <c r="BJ35" s="42"/>
+      <c r="BK35" s="39"/>
+      <c r="BL35" s="40"/>
+      <c r="BM35" s="39"/>
+      <c r="BN35" s="40"/>
       <c r="BR35" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="BS35" s="38"/>
-      <c r="BT35" s="39"/>
-      <c r="BU35" s="38"/>
-      <c r="BV35" s="39"/>
-      <c r="BW35" s="40"/>
-      <c r="BX35" s="41"/>
-      <c r="BY35" s="38"/>
-      <c r="BZ35" s="39"/>
-      <c r="CA35" s="38"/>
-      <c r="CB35" s="39"/>
+      <c r="BS35" s="39"/>
+      <c r="BT35" s="40"/>
+      <c r="BU35" s="39"/>
+      <c r="BV35" s="40"/>
+      <c r="BW35" s="41"/>
+      <c r="BX35" s="42"/>
+      <c r="BY35" s="39"/>
+      <c r="BZ35" s="40"/>
+      <c r="CA35" s="39"/>
+      <c r="CB35" s="40"/>
+      <c r="CF35" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="CG35" s="39"/>
+      <c r="CH35" s="40"/>
+      <c r="CI35" s="39"/>
+      <c r="CJ35" s="40"/>
+      <c r="CK35" s="41"/>
+      <c r="CL35" s="42"/>
+      <c r="CM35" s="39"/>
+      <c r="CN35" s="40"/>
+      <c r="CO35" s="39"/>
+      <c r="CP35" s="40"/>
     </row>
-    <row r="36" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:94" x14ac:dyDescent="0.2">
       <c r="B36" s="29" t="s">
         <v>37</v>
       </c>
@@ -11223,7 +11359,7 @@
         <v>13.42</v>
       </c>
     </row>
-    <row r="37" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B37" s="29" t="s">
         <v>38</v>
       </c>
@@ -11255,30 +11391,5285 @@
         <v>13.38</v>
       </c>
     </row>
-    <row r="38" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C38" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="38">
+      <c r="D38" s="39">
         <v>4</v>
       </c>
-      <c r="E38" s="39"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="39"/>
-      <c r="H38" s="40"/>
-      <c r="I38" s="41"/>
-      <c r="J38" s="38"/>
-      <c r="K38" s="39"/>
-      <c r="L38" s="38"/>
-      <c r="M38" s="39"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="40"/>
+      <c r="H38" s="41"/>
+      <c r="I38" s="42"/>
+      <c r="J38" s="39"/>
+      <c r="K38" s="40"/>
+      <c r="L38" s="39"/>
+      <c r="M38" s="40"/>
+      <c r="AA38" s="45" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB38" s="51"/>
+      <c r="AC38" s="51"/>
+      <c r="AD38" s="51"/>
+      <c r="AE38" s="51"/>
+      <c r="AF38" s="51"/>
+      <c r="AG38" s="51"/>
+      <c r="AH38" s="51"/>
+      <c r="AI38" s="51"/>
+      <c r="AJ38" s="51"/>
+      <c r="AK38" s="51"/>
+      <c r="AL38" s="52"/>
+      <c r="AO38" s="45" t="s">
+        <v>41</v>
+      </c>
+      <c r="AP38" s="51"/>
+      <c r="AQ38" s="51"/>
+      <c r="AR38" s="51"/>
+      <c r="AS38" s="51"/>
+      <c r="AT38" s="51"/>
+      <c r="AU38" s="51"/>
+      <c r="AV38" s="51"/>
+      <c r="AW38" s="51"/>
+      <c r="AX38" s="51"/>
+      <c r="AY38" s="51"/>
+      <c r="AZ38" s="52"/>
+      <c r="BC38" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="BD38" s="51"/>
+      <c r="BE38" s="51"/>
+      <c r="BF38" s="51"/>
+      <c r="BG38" s="51"/>
+      <c r="BH38" s="51"/>
+      <c r="BI38" s="51"/>
+      <c r="BJ38" s="51"/>
+      <c r="BK38" s="51"/>
+      <c r="BL38" s="51"/>
+      <c r="BM38" s="51"/>
+      <c r="BN38" s="52"/>
+      <c r="BQ38" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="BR38" s="51"/>
+      <c r="BS38" s="51"/>
+      <c r="BT38" s="51"/>
+      <c r="BU38" s="51"/>
+      <c r="BV38" s="51"/>
+      <c r="BW38" s="51"/>
+      <c r="BX38" s="51"/>
+      <c r="BY38" s="51"/>
+      <c r="BZ38" s="51"/>
+      <c r="CA38" s="51"/>
+      <c r="CB38" s="52"/>
+      <c r="CE38" s="45" t="s">
+        <v>51</v>
+      </c>
+      <c r="CF38" s="51"/>
+      <c r="CG38" s="51"/>
+      <c r="CH38" s="51"/>
+      <c r="CI38" s="51"/>
+      <c r="CJ38" s="51"/>
+      <c r="CK38" s="51"/>
+      <c r="CL38" s="51"/>
+      <c r="CM38" s="51"/>
+      <c r="CN38" s="51"/>
+      <c r="CO38" s="51"/>
+      <c r="CP38" s="52"/>
+    </row>
+    <row r="39" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AA39" s="1"/>
+      <c r="AB39" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC39" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD39" s="44"/>
+      <c r="AE39" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF39" s="44"/>
+      <c r="AG39" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH39" s="44"/>
+      <c r="AI39" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ39" s="44"/>
+      <c r="AK39" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="AL39" s="44"/>
+      <c r="AO39" s="1"/>
+      <c r="AP39" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AQ39" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR39" s="44"/>
+      <c r="AS39" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT39" s="44"/>
+      <c r="AU39" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV39" s="44"/>
+      <c r="AW39" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="AX39" s="44"/>
+      <c r="AY39" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="AZ39" s="44"/>
+      <c r="BC39" s="1"/>
+      <c r="BD39" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="BE39" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="BF39" s="44"/>
+      <c r="BG39" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="BH39" s="44"/>
+      <c r="BI39" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="BJ39" s="44"/>
+      <c r="BK39" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL39" s="44"/>
+      <c r="BM39" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="BN39" s="44"/>
+      <c r="BQ39" s="1"/>
+      <c r="BR39" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="BS39" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT39" s="44"/>
+      <c r="BU39" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="BV39" s="44"/>
+      <c r="BW39" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="BX39" s="44"/>
+      <c r="BY39" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="BZ39" s="44"/>
+      <c r="CA39" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="CB39" s="44"/>
+      <c r="CE39" s="1"/>
+      <c r="CF39" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="CG39" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="CH39" s="44"/>
+      <c r="CI39" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="CJ39" s="44"/>
+      <c r="CK39" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL39" s="44"/>
+      <c r="CM39" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="CN39" s="44"/>
+      <c r="CO39" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="CP39" s="44"/>
+    </row>
+    <row r="40" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AA40" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO40" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="AP40" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AR40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AS40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AT40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AU40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AX40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AY40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BC40" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD40" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BF40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BG40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BI40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BJ40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BK40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BM40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BN40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BQ40" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="BR40" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="BS40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BU40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BV40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BW40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BY40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BZ40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="CA40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="CB40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="CE40" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="CF40" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="CG40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="CH40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="CI40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="CJ40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="CK40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="CL40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="CM40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="CN40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="CO40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="CP40" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="2:94" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="AA41" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB41" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC41" s="19"/>
+      <c r="AD41" s="20"/>
+      <c r="AE41" s="19"/>
+      <c r="AF41" s="20"/>
+      <c r="AG41" s="19"/>
+      <c r="AH41" s="20"/>
+      <c r="AI41" s="19"/>
+      <c r="AJ41" s="20"/>
+      <c r="AK41" s="19"/>
+      <c r="AL41" s="20"/>
+      <c r="AO41" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP41" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ41" s="19"/>
+      <c r="AR41" s="20"/>
+      <c r="AS41" s="19"/>
+      <c r="AT41" s="20"/>
+      <c r="AU41" s="19"/>
+      <c r="AV41" s="20"/>
+      <c r="AW41" s="19"/>
+      <c r="AX41" s="20"/>
+      <c r="AY41" s="19"/>
+      <c r="AZ41" s="20"/>
+      <c r="BC41" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="BD41" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="BE41" s="19"/>
+      <c r="BF41" s="20"/>
+      <c r="BG41" s="19"/>
+      <c r="BH41" s="20"/>
+      <c r="BI41" s="19"/>
+      <c r="BJ41" s="20"/>
+      <c r="BK41" s="19"/>
+      <c r="BL41" s="20"/>
+      <c r="BM41" s="19"/>
+      <c r="BN41" s="20"/>
+      <c r="BQ41" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="BR41" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="BS41" s="19"/>
+      <c r="BT41" s="20"/>
+      <c r="BU41" s="19"/>
+      <c r="BV41" s="20"/>
+      <c r="BW41" s="19"/>
+      <c r="BX41" s="20"/>
+      <c r="BY41" s="19"/>
+      <c r="BZ41" s="20"/>
+      <c r="CA41" s="19"/>
+      <c r="CB41" s="20"/>
+      <c r="CE41" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="CF41" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="CG41" s="19"/>
+      <c r="CH41" s="20"/>
+      <c r="CI41" s="19"/>
+      <c r="CJ41" s="20"/>
+      <c r="CK41" s="19"/>
+      <c r="CL41" s="20"/>
+      <c r="CM41" s="19"/>
+      <c r="CN41" s="20"/>
+      <c r="CO41" s="19"/>
+      <c r="CP41" s="20"/>
+    </row>
+    <row r="42" spans="2:94" x14ac:dyDescent="0.2">
+      <c r="AA42" s="49"/>
+      <c r="AB42" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC42" s="15"/>
+      <c r="AD42" s="16"/>
+      <c r="AE42" s="15"/>
+      <c r="AF42" s="16"/>
+      <c r="AG42" s="15"/>
+      <c r="AH42" s="16"/>
+      <c r="AI42" s="15"/>
+      <c r="AJ42" s="16"/>
+      <c r="AK42" s="15"/>
+      <c r="AL42" s="16"/>
+      <c r="AO42" s="49"/>
+      <c r="AP42" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AQ42" s="15"/>
+      <c r="AR42" s="16"/>
+      <c r="AS42" s="15"/>
+      <c r="AT42" s="16"/>
+      <c r="AU42" s="15"/>
+      <c r="AV42" s="16"/>
+      <c r="AW42" s="15"/>
+      <c r="AX42" s="16"/>
+      <c r="AY42" s="15"/>
+      <c r="AZ42" s="16"/>
+      <c r="BC42" s="49"/>
+      <c r="BD42" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="BE42" s="15"/>
+      <c r="BF42" s="16"/>
+      <c r="BG42" s="15"/>
+      <c r="BH42" s="16"/>
+      <c r="BI42" s="15"/>
+      <c r="BJ42" s="16"/>
+      <c r="BK42" s="15"/>
+      <c r="BL42" s="16"/>
+      <c r="BM42" s="15"/>
+      <c r="BN42" s="16"/>
+      <c r="BQ42" s="49"/>
+      <c r="BR42" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="BS42" s="15"/>
+      <c r="BT42" s="16"/>
+      <c r="BU42" s="15"/>
+      <c r="BV42" s="16"/>
+      <c r="BW42" s="15"/>
+      <c r="BX42" s="16"/>
+      <c r="BY42" s="15"/>
+      <c r="BZ42" s="16"/>
+      <c r="CA42" s="15"/>
+      <c r="CB42" s="16"/>
+      <c r="CE42" s="49"/>
+      <c r="CF42" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="CG42" s="15"/>
+      <c r="CH42" s="16"/>
+      <c r="CI42" s="15"/>
+      <c r="CJ42" s="16"/>
+      <c r="CK42" s="15"/>
+      <c r="CL42" s="16"/>
+      <c r="CM42" s="15"/>
+      <c r="CN42" s="16"/>
+      <c r="CO42" s="15"/>
+      <c r="CP42" s="16"/>
+    </row>
+    <row r="43" spans="2:94" x14ac:dyDescent="0.2">
+      <c r="AA43" s="49"/>
+      <c r="AB43" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC43" s="15"/>
+      <c r="AD43" s="16"/>
+      <c r="AE43" s="15"/>
+      <c r="AF43" s="16"/>
+      <c r="AG43" s="15"/>
+      <c r="AH43" s="16"/>
+      <c r="AI43" s="15"/>
+      <c r="AJ43" s="16"/>
+      <c r="AK43" s="15"/>
+      <c r="AL43" s="16"/>
+      <c r="AO43" s="49"/>
+      <c r="AP43" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="AQ43" s="15"/>
+      <c r="AR43" s="16"/>
+      <c r="AS43" s="15"/>
+      <c r="AT43" s="16"/>
+      <c r="AU43" s="15"/>
+      <c r="AV43" s="16"/>
+      <c r="AW43" s="15"/>
+      <c r="AX43" s="16"/>
+      <c r="AY43" s="15"/>
+      <c r="AZ43" s="16"/>
+      <c r="BC43" s="49"/>
+      <c r="BD43" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="BE43" s="15"/>
+      <c r="BF43" s="16"/>
+      <c r="BG43" s="15"/>
+      <c r="BH43" s="16"/>
+      <c r="BI43" s="15"/>
+      <c r="BJ43" s="16"/>
+      <c r="BK43" s="15"/>
+      <c r="BL43" s="16"/>
+      <c r="BM43" s="15"/>
+      <c r="BN43" s="16"/>
+      <c r="BQ43" s="49"/>
+      <c r="BR43" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="BS43" s="15"/>
+      <c r="BT43" s="16"/>
+      <c r="BU43" s="15"/>
+      <c r="BV43" s="16"/>
+      <c r="BW43" s="15"/>
+      <c r="BX43" s="16"/>
+      <c r="BY43" s="15"/>
+      <c r="BZ43" s="16"/>
+      <c r="CA43" s="15"/>
+      <c r="CB43" s="16"/>
+      <c r="CE43" s="49"/>
+      <c r="CF43" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="CG43" s="15"/>
+      <c r="CH43" s="16"/>
+      <c r="CI43" s="15"/>
+      <c r="CJ43" s="16"/>
+      <c r="CK43" s="15"/>
+      <c r="CL43" s="16"/>
+      <c r="CM43" s="15"/>
+      <c r="CN43" s="16"/>
+      <c r="CO43" s="15"/>
+      <c r="CP43" s="16"/>
+    </row>
+    <row r="44" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AA44" s="50"/>
+      <c r="AB44" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC44" s="21"/>
+      <c r="AD44" s="22"/>
+      <c r="AE44" s="21"/>
+      <c r="AF44" s="22"/>
+      <c r="AG44" s="21"/>
+      <c r="AH44" s="22"/>
+      <c r="AI44" s="21"/>
+      <c r="AJ44" s="22"/>
+      <c r="AK44" s="21"/>
+      <c r="AL44" s="22"/>
+      <c r="AO44" s="50"/>
+      <c r="AP44" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ44" s="21"/>
+      <c r="AR44" s="22"/>
+      <c r="AS44" s="21"/>
+      <c r="AT44" s="22"/>
+      <c r="AU44" s="21"/>
+      <c r="AV44" s="22"/>
+      <c r="AW44" s="21"/>
+      <c r="AX44" s="22"/>
+      <c r="AY44" s="21"/>
+      <c r="AZ44" s="22"/>
+      <c r="BC44" s="50"/>
+      <c r="BD44" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="BE44" s="21"/>
+      <c r="BF44" s="22"/>
+      <c r="BG44" s="21"/>
+      <c r="BH44" s="22"/>
+      <c r="BI44" s="21"/>
+      <c r="BJ44" s="22"/>
+      <c r="BK44" s="21"/>
+      <c r="BL44" s="22"/>
+      <c r="BM44" s="21"/>
+      <c r="BN44" s="22"/>
+      <c r="BQ44" s="50"/>
+      <c r="BR44" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="BS44" s="21"/>
+      <c r="BT44" s="22"/>
+      <c r="BU44" s="21"/>
+      <c r="BV44" s="22"/>
+      <c r="BW44" s="21"/>
+      <c r="BX44" s="22"/>
+      <c r="BY44" s="21"/>
+      <c r="BZ44" s="22"/>
+      <c r="CA44" s="21"/>
+      <c r="CB44" s="22"/>
+      <c r="CE44" s="50"/>
+      <c r="CF44" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="CG44" s="21"/>
+      <c r="CH44" s="22"/>
+      <c r="CI44" s="21"/>
+      <c r="CJ44" s="22"/>
+      <c r="CK44" s="21"/>
+      <c r="CL44" s="22"/>
+      <c r="CM44" s="21"/>
+      <c r="CN44" s="22"/>
+      <c r="CO44" s="21"/>
+      <c r="CP44" s="22"/>
+    </row>
+    <row r="46" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AA47" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB47" s="46"/>
+      <c r="AC47" s="46"/>
+      <c r="AD47" s="46"/>
+      <c r="AE47" s="46"/>
+      <c r="AF47" s="46"/>
+      <c r="AG47" s="46"/>
+      <c r="AH47" s="46"/>
+      <c r="AI47" s="46"/>
+      <c r="AJ47" s="46"/>
+      <c r="AK47" s="46"/>
+      <c r="AL47" s="47"/>
+      <c r="AO47" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP47" s="46"/>
+      <c r="AQ47" s="46"/>
+      <c r="AR47" s="46"/>
+      <c r="AS47" s="46"/>
+      <c r="AT47" s="46"/>
+      <c r="AU47" s="46"/>
+      <c r="AV47" s="46"/>
+      <c r="AW47" s="46"/>
+      <c r="AX47" s="46"/>
+      <c r="AY47" s="46"/>
+      <c r="AZ47" s="47"/>
+      <c r="BC47" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="BD47" s="46"/>
+      <c r="BE47" s="46"/>
+      <c r="BF47" s="46"/>
+      <c r="BG47" s="46"/>
+      <c r="BH47" s="46"/>
+      <c r="BI47" s="46"/>
+      <c r="BJ47" s="46"/>
+      <c r="BK47" s="46"/>
+      <c r="BL47" s="46"/>
+      <c r="BM47" s="46"/>
+      <c r="BN47" s="47"/>
+      <c r="BQ47" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="BR47" s="46"/>
+      <c r="BS47" s="46"/>
+      <c r="BT47" s="46"/>
+      <c r="BU47" s="46"/>
+      <c r="BV47" s="46"/>
+      <c r="BW47" s="46"/>
+      <c r="BX47" s="46"/>
+      <c r="BY47" s="46"/>
+      <c r="BZ47" s="46"/>
+      <c r="CA47" s="46"/>
+      <c r="CB47" s="47"/>
+      <c r="CE47" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="CF47" s="46"/>
+      <c r="CG47" s="46"/>
+      <c r="CH47" s="46"/>
+      <c r="CI47" s="46"/>
+      <c r="CJ47" s="46"/>
+      <c r="CK47" s="46"/>
+      <c r="CL47" s="46"/>
+      <c r="CM47" s="46"/>
+      <c r="CN47" s="46"/>
+      <c r="CO47" s="46"/>
+      <c r="CP47" s="47"/>
+    </row>
+    <row r="48" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AA48" s="24"/>
+      <c r="AB48" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC48" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD48" s="44"/>
+      <c r="AE48" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF48" s="44"/>
+      <c r="AG48" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH48" s="44"/>
+      <c r="AI48" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ48" s="44"/>
+      <c r="AK48" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="AL48" s="44"/>
+      <c r="AO48" s="24"/>
+      <c r="AP48" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="AQ48" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR48" s="44"/>
+      <c r="AS48" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT48" s="44"/>
+      <c r="AU48" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV48" s="44"/>
+      <c r="AW48" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="AX48" s="44"/>
+      <c r="AY48" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="AZ48" s="44"/>
+      <c r="BC48" s="24"/>
+      <c r="BD48" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="BE48" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="BF48" s="44"/>
+      <c r="BG48" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="BH48" s="44"/>
+      <c r="BI48" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="BJ48" s="44"/>
+      <c r="BK48" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL48" s="44"/>
+      <c r="BM48" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="BN48" s="44"/>
+      <c r="BQ48" s="24"/>
+      <c r="BR48" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="BS48" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT48" s="44"/>
+      <c r="BU48" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="BV48" s="44"/>
+      <c r="BW48" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="BX48" s="44"/>
+      <c r="BY48" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="BZ48" s="44"/>
+      <c r="CA48" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="CB48" s="44"/>
+      <c r="CE48" s="24"/>
+      <c r="CF48" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="CG48" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="CH48" s="44"/>
+      <c r="CI48" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="CJ48" s="44"/>
+      <c r="CK48" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL48" s="44"/>
+      <c r="CM48" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="CN48" s="44"/>
+      <c r="CO48" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="CP48" s="44"/>
+    </row>
+    <row r="49" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA49" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB49" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC49" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD49" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE49" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF49" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG49" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH49" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI49" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ49" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK49" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL49" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO49" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="AP49" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ49" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AR49" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AS49" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AT49" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AU49" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV49" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW49" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AX49" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AY49" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ49" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BC49" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="BD49" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="BE49" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BF49" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BG49" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH49" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BI49" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BJ49" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BK49" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL49" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BM49" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BN49" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BQ49" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="BR49" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="BS49" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT49" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BU49" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BV49" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BW49" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX49" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BY49" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BZ49" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="CA49" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="CB49" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="CE49" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="CF49" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="CG49" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="CH49" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="CI49" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="CJ49" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="CK49" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="CL49" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="CM49" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="CN49" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="CO49" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="CP49" s="28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA50" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB50" s="36"/>
+      <c r="AC50" s="30"/>
+      <c r="AD50" s="30"/>
+      <c r="AE50" s="30"/>
+      <c r="AF50" s="30"/>
+      <c r="AG50" s="30"/>
+      <c r="AH50" s="30"/>
+      <c r="AI50" s="30"/>
+      <c r="AJ50" s="30"/>
+      <c r="AK50" s="30"/>
+      <c r="AL50" s="30"/>
+      <c r="AO50" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="AP50" s="36"/>
+      <c r="AQ50" s="30"/>
+      <c r="AR50" s="30"/>
+      <c r="AS50" s="30"/>
+      <c r="AT50" s="30"/>
+      <c r="AU50" s="30"/>
+      <c r="AV50" s="30"/>
+      <c r="AW50" s="30"/>
+      <c r="AX50" s="30"/>
+      <c r="AY50" s="30"/>
+      <c r="AZ50" s="30"/>
+      <c r="BC50" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="BD50" s="36"/>
+      <c r="BE50" s="30"/>
+      <c r="BF50" s="30"/>
+      <c r="BG50" s="30"/>
+      <c r="BH50" s="30"/>
+      <c r="BI50" s="30"/>
+      <c r="BJ50" s="30"/>
+      <c r="BK50" s="30"/>
+      <c r="BL50" s="30"/>
+      <c r="BM50" s="30"/>
+      <c r="BN50" s="30"/>
+      <c r="BQ50" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="BR50" s="36"/>
+      <c r="BS50" s="30"/>
+      <c r="BT50" s="30"/>
+      <c r="BU50" s="30"/>
+      <c r="BV50" s="30"/>
+      <c r="BW50" s="30"/>
+      <c r="BX50" s="30"/>
+      <c r="BY50" s="30"/>
+      <c r="BZ50" s="30"/>
+      <c r="CA50" s="30"/>
+      <c r="CB50" s="30"/>
+      <c r="CE50" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="CF50" s="36"/>
+      <c r="CG50" s="30"/>
+      <c r="CH50" s="30"/>
+      <c r="CI50" s="30"/>
+      <c r="CJ50" s="30"/>
+      <c r="CK50" s="30"/>
+      <c r="CL50" s="30"/>
+      <c r="CM50" s="30"/>
+      <c r="CN50" s="30"/>
+      <c r="CO50" s="30"/>
+      <c r="CP50" s="30"/>
+    </row>
+    <row r="51" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA51" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB51" s="30"/>
+      <c r="AC51" s="30"/>
+      <c r="AD51" s="30"/>
+      <c r="AE51" s="30"/>
+      <c r="AF51" s="30"/>
+      <c r="AG51" s="30"/>
+      <c r="AH51" s="30"/>
+      <c r="AI51" s="30"/>
+      <c r="AJ51" s="30"/>
+      <c r="AK51" s="30"/>
+      <c r="AL51" s="30"/>
+      <c r="AO51" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP51" s="30"/>
+      <c r="AQ51" s="30"/>
+      <c r="AR51" s="30"/>
+      <c r="AS51" s="30"/>
+      <c r="AT51" s="30"/>
+      <c r="AU51" s="30"/>
+      <c r="AV51" s="30"/>
+      <c r="AW51" s="30"/>
+      <c r="AX51" s="30"/>
+      <c r="AY51" s="30"/>
+      <c r="AZ51" s="30"/>
+      <c r="BC51" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="BD51" s="30"/>
+      <c r="BE51" s="30"/>
+      <c r="BF51" s="30"/>
+      <c r="BG51" s="30"/>
+      <c r="BH51" s="30"/>
+      <c r="BI51" s="30"/>
+      <c r="BJ51" s="30"/>
+      <c r="BK51" s="30"/>
+      <c r="BL51" s="30"/>
+      <c r="BM51" s="30"/>
+      <c r="BN51" s="30"/>
+      <c r="BQ51" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="BR51" s="30"/>
+      <c r="BS51" s="30"/>
+      <c r="BT51" s="30"/>
+      <c r="BU51" s="30"/>
+      <c r="BV51" s="30"/>
+      <c r="BW51" s="30"/>
+      <c r="BX51" s="30"/>
+      <c r="BY51" s="30"/>
+      <c r="BZ51" s="30"/>
+      <c r="CA51" s="30"/>
+      <c r="CB51" s="30"/>
+      <c r="CE51" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="CF51" s="30"/>
+      <c r="CG51" s="30"/>
+      <c r="CH51" s="30"/>
+      <c r="CI51" s="30"/>
+      <c r="CJ51" s="30"/>
+      <c r="CK51" s="30"/>
+      <c r="CL51" s="30"/>
+      <c r="CM51" s="30"/>
+      <c r="CN51" s="30"/>
+      <c r="CO51" s="30"/>
+      <c r="CP51" s="30"/>
+    </row>
+    <row r="52" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA52" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB52" s="34"/>
+      <c r="AC52" s="34"/>
+      <c r="AD52" s="34"/>
+      <c r="AE52" s="34"/>
+      <c r="AF52" s="34"/>
+      <c r="AG52" s="34"/>
+      <c r="AH52" s="34"/>
+      <c r="AI52" s="34"/>
+      <c r="AJ52" s="34"/>
+      <c r="AK52" s="34"/>
+      <c r="AL52" s="34"/>
+      <c r="AO52" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="AP52" s="34"/>
+      <c r="AQ52" s="34"/>
+      <c r="AR52" s="34"/>
+      <c r="AS52" s="34"/>
+      <c r="AT52" s="34"/>
+      <c r="AU52" s="34"/>
+      <c r="AV52" s="34"/>
+      <c r="AW52" s="34"/>
+      <c r="AX52" s="34"/>
+      <c r="AY52" s="34"/>
+      <c r="AZ52" s="34"/>
+      <c r="BC52" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="BD52" s="34"/>
+      <c r="BE52" s="34"/>
+      <c r="BF52" s="34"/>
+      <c r="BG52" s="34"/>
+      <c r="BH52" s="34"/>
+      <c r="BI52" s="34"/>
+      <c r="BJ52" s="34"/>
+      <c r="BK52" s="34"/>
+      <c r="BL52" s="34"/>
+      <c r="BM52" s="34"/>
+      <c r="BN52" s="34"/>
+      <c r="BQ52" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="BR52" s="34"/>
+      <c r="BS52" s="34"/>
+      <c r="BT52" s="34"/>
+      <c r="BU52" s="34"/>
+      <c r="BV52" s="34"/>
+      <c r="BW52" s="34"/>
+      <c r="BX52" s="34"/>
+      <c r="BY52" s="34"/>
+      <c r="BZ52" s="34"/>
+      <c r="CA52" s="34"/>
+      <c r="CB52" s="34"/>
+      <c r="CE52" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="CF52" s="34"/>
+      <c r="CG52" s="34"/>
+      <c r="CH52" s="34"/>
+      <c r="CI52" s="34"/>
+      <c r="CJ52" s="34"/>
+      <c r="CK52" s="34"/>
+      <c r="CL52" s="34"/>
+      <c r="CM52" s="34"/>
+      <c r="CN52" s="34"/>
+      <c r="CO52" s="34"/>
+      <c r="CP52" s="34"/>
+    </row>
+    <row r="53" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA53" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB53" s="34"/>
+      <c r="AC53" s="34"/>
+      <c r="AD53" s="34"/>
+      <c r="AE53" s="34"/>
+      <c r="AF53" s="34"/>
+      <c r="AG53" s="34"/>
+      <c r="AH53" s="34"/>
+      <c r="AI53" s="34"/>
+      <c r="AJ53" s="34"/>
+      <c r="AK53" s="34"/>
+      <c r="AL53" s="34"/>
+      <c r="AO53" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="AP53" s="34"/>
+      <c r="AQ53" s="34"/>
+      <c r="AR53" s="34"/>
+      <c r="AS53" s="34"/>
+      <c r="AT53" s="34"/>
+      <c r="AU53" s="34"/>
+      <c r="AV53" s="34"/>
+      <c r="AW53" s="34"/>
+      <c r="AX53" s="34"/>
+      <c r="AY53" s="34"/>
+      <c r="AZ53" s="34"/>
+      <c r="BC53" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="BD53" s="34"/>
+      <c r="BE53" s="34"/>
+      <c r="BF53" s="34"/>
+      <c r="BG53" s="34"/>
+      <c r="BH53" s="34"/>
+      <c r="BI53" s="34"/>
+      <c r="BJ53" s="34"/>
+      <c r="BK53" s="34"/>
+      <c r="BL53" s="34"/>
+      <c r="BM53" s="34"/>
+      <c r="BN53" s="34"/>
+      <c r="BQ53" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="BR53" s="34"/>
+      <c r="BS53" s="34"/>
+      <c r="BT53" s="34"/>
+      <c r="BU53" s="34"/>
+      <c r="BV53" s="34"/>
+      <c r="BW53" s="34"/>
+      <c r="BX53" s="34"/>
+      <c r="BY53" s="34"/>
+      <c r="BZ53" s="34"/>
+      <c r="CA53" s="34"/>
+      <c r="CB53" s="34"/>
+      <c r="CE53" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="CF53" s="34"/>
+      <c r="CG53" s="34"/>
+      <c r="CH53" s="34"/>
+      <c r="CI53" s="34"/>
+      <c r="CJ53" s="34"/>
+      <c r="CK53" s="34"/>
+      <c r="CL53" s="34"/>
+      <c r="CM53" s="34"/>
+      <c r="CN53" s="34"/>
+      <c r="CO53" s="34"/>
+      <c r="CP53" s="34"/>
+    </row>
+    <row r="54" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA54" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB54" s="30"/>
+      <c r="AC54" s="30"/>
+      <c r="AD54" s="30"/>
+      <c r="AE54" s="30"/>
+      <c r="AF54" s="30"/>
+      <c r="AG54" s="30"/>
+      <c r="AH54" s="30"/>
+      <c r="AI54" s="30"/>
+      <c r="AJ54" s="30"/>
+      <c r="AK54" s="30"/>
+      <c r="AL54" s="30"/>
+      <c r="AO54" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP54" s="30"/>
+      <c r="AQ54" s="30"/>
+      <c r="AR54" s="30"/>
+      <c r="AS54" s="30"/>
+      <c r="AT54" s="30"/>
+      <c r="AU54" s="30"/>
+      <c r="AV54" s="30"/>
+      <c r="AW54" s="30"/>
+      <c r="AX54" s="30"/>
+      <c r="AY54" s="30"/>
+      <c r="AZ54" s="30"/>
+      <c r="BC54" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="BD54" s="30"/>
+      <c r="BE54" s="30"/>
+      <c r="BF54" s="30"/>
+      <c r="BG54" s="30"/>
+      <c r="BH54" s="30"/>
+      <c r="BI54" s="30"/>
+      <c r="BJ54" s="30"/>
+      <c r="BK54" s="30"/>
+      <c r="BL54" s="30"/>
+      <c r="BM54" s="30"/>
+      <c r="BN54" s="30"/>
+      <c r="BQ54" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="BR54" s="30"/>
+      <c r="BS54" s="30"/>
+      <c r="BT54" s="30"/>
+      <c r="BU54" s="30"/>
+      <c r="BV54" s="30"/>
+      <c r="BW54" s="30"/>
+      <c r="BX54" s="30"/>
+      <c r="BY54" s="30"/>
+      <c r="BZ54" s="30"/>
+      <c r="CA54" s="30"/>
+      <c r="CB54" s="30"/>
+      <c r="CE54" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="CF54" s="30"/>
+      <c r="CG54" s="30"/>
+      <c r="CH54" s="30"/>
+      <c r="CI54" s="30"/>
+      <c r="CJ54" s="30"/>
+      <c r="CK54" s="30"/>
+      <c r="CL54" s="30"/>
+      <c r="CM54" s="30"/>
+      <c r="CN54" s="30"/>
+      <c r="CO54" s="30"/>
+      <c r="CP54" s="30"/>
+    </row>
+    <row r="55" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA55" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB55" s="30"/>
+      <c r="AC55" s="30"/>
+      <c r="AD55" s="30"/>
+      <c r="AE55" s="35"/>
+      <c r="AF55" s="30"/>
+      <c r="AG55" s="30"/>
+      <c r="AH55" s="30"/>
+      <c r="AI55" s="30"/>
+      <c r="AJ55" s="30"/>
+      <c r="AK55" s="30"/>
+      <c r="AL55" s="30"/>
+      <c r="AO55" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="AP55" s="30"/>
+      <c r="AQ55" s="30"/>
+      <c r="AR55" s="30"/>
+      <c r="AS55" s="35"/>
+      <c r="AT55" s="30"/>
+      <c r="AU55" s="30"/>
+      <c r="AV55" s="30"/>
+      <c r="AW55" s="30"/>
+      <c r="AX55" s="30"/>
+      <c r="AY55" s="30"/>
+      <c r="AZ55" s="30"/>
+      <c r="BC55" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="BD55" s="30"/>
+      <c r="BE55" s="30"/>
+      <c r="BF55" s="30"/>
+      <c r="BG55" s="35"/>
+      <c r="BH55" s="30"/>
+      <c r="BI55" s="30"/>
+      <c r="BJ55" s="30"/>
+      <c r="BK55" s="30"/>
+      <c r="BL55" s="30"/>
+      <c r="BM55" s="30"/>
+      <c r="BN55" s="30"/>
+      <c r="BQ55" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="BR55" s="30"/>
+      <c r="BS55" s="30"/>
+      <c r="BT55" s="30"/>
+      <c r="BU55" s="35"/>
+      <c r="BV55" s="30"/>
+      <c r="BW55" s="30"/>
+      <c r="BX55" s="30"/>
+      <c r="BY55" s="30"/>
+      <c r="BZ55" s="30"/>
+      <c r="CA55" s="30"/>
+      <c r="CB55" s="30"/>
+      <c r="CE55" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="CF55" s="30"/>
+      <c r="CG55" s="30"/>
+      <c r="CH55" s="30"/>
+      <c r="CI55" s="35"/>
+      <c r="CJ55" s="30"/>
+      <c r="CK55" s="30"/>
+      <c r="CL55" s="30"/>
+      <c r="CM55" s="30"/>
+      <c r="CN55" s="30"/>
+      <c r="CO55" s="30"/>
+      <c r="CP55" s="30"/>
+    </row>
+    <row r="56" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA56" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB56" s="34"/>
+      <c r="AC56" s="34"/>
+      <c r="AD56" s="34"/>
+      <c r="AE56" s="34"/>
+      <c r="AF56" s="34"/>
+      <c r="AG56" s="34"/>
+      <c r="AH56" s="34"/>
+      <c r="AI56" s="34"/>
+      <c r="AJ56" s="34"/>
+      <c r="AK56" s="34"/>
+      <c r="AL56" s="34"/>
+      <c r="AO56" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP56" s="34"/>
+      <c r="AQ56" s="34"/>
+      <c r="AR56" s="34"/>
+      <c r="AS56" s="34"/>
+      <c r="AT56" s="34"/>
+      <c r="AU56" s="34"/>
+      <c r="AV56" s="34"/>
+      <c r="AW56" s="34"/>
+      <c r="AX56" s="34"/>
+      <c r="AY56" s="34"/>
+      <c r="AZ56" s="34"/>
+      <c r="BC56" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="BD56" s="34"/>
+      <c r="BE56" s="34"/>
+      <c r="BF56" s="34"/>
+      <c r="BG56" s="34"/>
+      <c r="BH56" s="34"/>
+      <c r="BI56" s="34"/>
+      <c r="BJ56" s="34"/>
+      <c r="BK56" s="34"/>
+      <c r="BL56" s="34"/>
+      <c r="BM56" s="34"/>
+      <c r="BN56" s="34"/>
+      <c r="BQ56" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="BR56" s="34"/>
+      <c r="BS56" s="34"/>
+      <c r="BT56" s="34"/>
+      <c r="BU56" s="34"/>
+      <c r="BV56" s="34"/>
+      <c r="BW56" s="34"/>
+      <c r="BX56" s="34"/>
+      <c r="BY56" s="34"/>
+      <c r="BZ56" s="34"/>
+      <c r="CA56" s="34"/>
+      <c r="CB56" s="34"/>
+      <c r="CE56" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="CF56" s="34"/>
+      <c r="CG56" s="34"/>
+      <c r="CH56" s="34"/>
+      <c r="CI56" s="34"/>
+      <c r="CJ56" s="34"/>
+      <c r="CK56" s="34"/>
+      <c r="CL56" s="34"/>
+      <c r="CM56" s="34"/>
+      <c r="CN56" s="34"/>
+      <c r="CO56" s="34"/>
+      <c r="CP56" s="34"/>
+    </row>
+    <row r="57" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA57" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB57" s="30"/>
+      <c r="AC57" s="30"/>
+      <c r="AD57" s="30"/>
+      <c r="AE57" s="30"/>
+      <c r="AF57" s="30"/>
+      <c r="AG57" s="30"/>
+      <c r="AH57" s="30"/>
+      <c r="AI57" s="30"/>
+      <c r="AJ57" s="30"/>
+      <c r="AK57" s="30"/>
+      <c r="AL57" s="30"/>
+      <c r="AO57" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP57" s="30"/>
+      <c r="AQ57" s="30"/>
+      <c r="AR57" s="30"/>
+      <c r="AS57" s="30"/>
+      <c r="AT57" s="30"/>
+      <c r="AU57" s="30"/>
+      <c r="AV57" s="30"/>
+      <c r="AW57" s="30"/>
+      <c r="AX57" s="30"/>
+      <c r="AY57" s="30"/>
+      <c r="AZ57" s="30"/>
+      <c r="BC57" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="BD57" s="30"/>
+      <c r="BE57" s="30"/>
+      <c r="BF57" s="30"/>
+      <c r="BG57" s="30"/>
+      <c r="BH57" s="30"/>
+      <c r="BI57" s="30"/>
+      <c r="BJ57" s="30"/>
+      <c r="BK57" s="30"/>
+      <c r="BL57" s="30"/>
+      <c r="BM57" s="30"/>
+      <c r="BN57" s="30"/>
+      <c r="BQ57" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="BR57" s="30"/>
+      <c r="BS57" s="30"/>
+      <c r="BT57" s="30"/>
+      <c r="BU57" s="30"/>
+      <c r="BV57" s="30"/>
+      <c r="BW57" s="30"/>
+      <c r="BX57" s="30"/>
+      <c r="BY57" s="30"/>
+      <c r="BZ57" s="30"/>
+      <c r="CA57" s="30"/>
+      <c r="CB57" s="30"/>
+      <c r="CE57" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="CF57" s="30"/>
+      <c r="CG57" s="30"/>
+      <c r="CH57" s="30"/>
+      <c r="CI57" s="30"/>
+      <c r="CJ57" s="30"/>
+      <c r="CK57" s="30"/>
+      <c r="CL57" s="30"/>
+      <c r="CM57" s="30"/>
+      <c r="CN57" s="30"/>
+      <c r="CO57" s="30"/>
+      <c r="CP57" s="30"/>
+    </row>
+    <row r="58" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA58" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB58" s="30"/>
+      <c r="AC58" s="30"/>
+      <c r="AD58" s="30"/>
+      <c r="AF58" s="30"/>
+      <c r="AG58" s="30"/>
+      <c r="AH58" s="30"/>
+      <c r="AI58" s="30"/>
+      <c r="AJ58" s="30"/>
+      <c r="AK58" s="30"/>
+      <c r="AL58" s="30"/>
+      <c r="AO58" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="AP58" s="30"/>
+      <c r="AQ58" s="30"/>
+      <c r="AR58" s="30"/>
+      <c r="AT58" s="30"/>
+      <c r="AU58" s="30"/>
+      <c r="AV58" s="30"/>
+      <c r="AW58" s="30"/>
+      <c r="AX58" s="30"/>
+      <c r="AY58" s="30"/>
+      <c r="AZ58" s="30"/>
+      <c r="BC58" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="BD58" s="30"/>
+      <c r="BE58" s="30"/>
+      <c r="BF58" s="30"/>
+      <c r="BH58" s="30"/>
+      <c r="BI58" s="30"/>
+      <c r="BJ58" s="30"/>
+      <c r="BK58" s="30"/>
+      <c r="BL58" s="30"/>
+      <c r="BM58" s="30"/>
+      <c r="BN58" s="30"/>
+      <c r="BQ58" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="BR58" s="30"/>
+      <c r="BS58" s="30"/>
+      <c r="BT58" s="30"/>
+      <c r="BV58" s="30"/>
+      <c r="BW58" s="30"/>
+      <c r="BX58" s="30"/>
+      <c r="BY58" s="30"/>
+      <c r="BZ58" s="30"/>
+      <c r="CA58" s="30"/>
+      <c r="CB58" s="30"/>
+      <c r="CE58" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="CF58" s="30"/>
+      <c r="CG58" s="30"/>
+      <c r="CH58" s="30"/>
+      <c r="CJ58" s="30"/>
+      <c r="CK58" s="30"/>
+      <c r="CL58" s="30"/>
+      <c r="CM58" s="30"/>
+      <c r="CN58" s="30"/>
+      <c r="CO58" s="30"/>
+      <c r="CP58" s="30"/>
+    </row>
+    <row r="59" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA59" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB59" s="30"/>
+      <c r="AC59" s="30"/>
+      <c r="AD59" s="30"/>
+      <c r="AE59" s="30"/>
+      <c r="AF59" s="30"/>
+      <c r="AG59" s="30"/>
+      <c r="AH59" s="30"/>
+      <c r="AI59" s="30"/>
+      <c r="AJ59" s="30"/>
+      <c r="AK59" s="30"/>
+      <c r="AL59" s="30"/>
+      <c r="AO59" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP59" s="30"/>
+      <c r="AQ59" s="30"/>
+      <c r="AR59" s="30"/>
+      <c r="AS59" s="30"/>
+      <c r="AT59" s="30"/>
+      <c r="AU59" s="30"/>
+      <c r="AV59" s="30"/>
+      <c r="AW59" s="30"/>
+      <c r="AX59" s="30"/>
+      <c r="AY59" s="30"/>
+      <c r="AZ59" s="30"/>
+      <c r="BC59" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD59" s="30"/>
+      <c r="BE59" s="30"/>
+      <c r="BF59" s="30"/>
+      <c r="BG59" s="30"/>
+      <c r="BH59" s="30"/>
+      <c r="BI59" s="30"/>
+      <c r="BJ59" s="30"/>
+      <c r="BK59" s="30"/>
+      <c r="BL59" s="30"/>
+      <c r="BM59" s="30"/>
+      <c r="BN59" s="30"/>
+      <c r="BQ59" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="BR59" s="30"/>
+      <c r="BS59" s="30"/>
+      <c r="BT59" s="30"/>
+      <c r="BU59" s="30"/>
+      <c r="BV59" s="30"/>
+      <c r="BW59" s="30"/>
+      <c r="BX59" s="30"/>
+      <c r="BY59" s="30"/>
+      <c r="BZ59" s="30"/>
+      <c r="CA59" s="30"/>
+      <c r="CB59" s="30"/>
+      <c r="CE59" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="CF59" s="30"/>
+      <c r="CG59" s="30"/>
+      <c r="CH59" s="30"/>
+      <c r="CI59" s="30"/>
+      <c r="CJ59" s="30"/>
+      <c r="CK59" s="30"/>
+      <c r="CL59" s="30"/>
+      <c r="CM59" s="30"/>
+      <c r="CN59" s="30"/>
+      <c r="CO59" s="30"/>
+      <c r="CP59" s="30"/>
+    </row>
+    <row r="60" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA60" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB60" s="30"/>
+      <c r="AC60" s="30"/>
+      <c r="AD60" s="30"/>
+      <c r="AE60" s="30"/>
+      <c r="AF60" s="30"/>
+      <c r="AG60" s="30"/>
+      <c r="AH60" s="30"/>
+      <c r="AI60" s="30"/>
+      <c r="AJ60" s="30"/>
+      <c r="AK60" s="30"/>
+      <c r="AL60" s="30"/>
+      <c r="AO60" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="AP60" s="30"/>
+      <c r="AQ60" s="30"/>
+      <c r="AR60" s="30"/>
+      <c r="AS60" s="30"/>
+      <c r="AT60" s="30"/>
+      <c r="AU60" s="30"/>
+      <c r="AV60" s="30"/>
+      <c r="AW60" s="30"/>
+      <c r="AX60" s="30"/>
+      <c r="AY60" s="30"/>
+      <c r="AZ60" s="30"/>
+      <c r="BC60" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="BD60" s="30"/>
+      <c r="BE60" s="30"/>
+      <c r="BF60" s="30"/>
+      <c r="BG60" s="30"/>
+      <c r="BH60" s="30"/>
+      <c r="BI60" s="30"/>
+      <c r="BJ60" s="30"/>
+      <c r="BK60" s="30"/>
+      <c r="BL60" s="30"/>
+      <c r="BM60" s="30"/>
+      <c r="BN60" s="30"/>
+      <c r="BQ60" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="BR60" s="30"/>
+      <c r="BS60" s="30"/>
+      <c r="BT60" s="30"/>
+      <c r="BU60" s="30"/>
+      <c r="BV60" s="30"/>
+      <c r="BW60" s="30"/>
+      <c r="BX60" s="30"/>
+      <c r="BY60" s="30"/>
+      <c r="BZ60" s="30"/>
+      <c r="CA60" s="30"/>
+      <c r="CB60" s="30"/>
+      <c r="CE60" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="CF60" s="30"/>
+      <c r="CG60" s="30"/>
+      <c r="CH60" s="30"/>
+      <c r="CI60" s="30"/>
+      <c r="CJ60" s="30"/>
+      <c r="CK60" s="30"/>
+      <c r="CL60" s="30"/>
+      <c r="CM60" s="30"/>
+      <c r="CN60" s="30"/>
+      <c r="CO60" s="30"/>
+      <c r="CP60" s="30"/>
+    </row>
+    <row r="61" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA61" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB61" s="30"/>
+      <c r="AC61" s="30"/>
+      <c r="AD61" s="30"/>
+      <c r="AE61" s="30"/>
+      <c r="AF61" s="30"/>
+      <c r="AG61" s="30"/>
+      <c r="AH61" s="30"/>
+      <c r="AI61" s="30"/>
+      <c r="AJ61" s="30"/>
+      <c r="AK61" s="30"/>
+      <c r="AL61" s="30"/>
+      <c r="AO61" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP61" s="30"/>
+      <c r="AQ61" s="30"/>
+      <c r="AR61" s="30"/>
+      <c r="AS61" s="30"/>
+      <c r="AT61" s="30"/>
+      <c r="AU61" s="30"/>
+      <c r="AV61" s="30"/>
+      <c r="AW61" s="30"/>
+      <c r="AX61" s="30"/>
+      <c r="AY61" s="30"/>
+      <c r="AZ61" s="30"/>
+      <c r="BC61" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="BD61" s="30"/>
+      <c r="BE61" s="30"/>
+      <c r="BF61" s="30"/>
+      <c r="BG61" s="30"/>
+      <c r="BH61" s="30"/>
+      <c r="BI61" s="30"/>
+      <c r="BJ61" s="30"/>
+      <c r="BK61" s="30"/>
+      <c r="BL61" s="30"/>
+      <c r="BM61" s="30"/>
+      <c r="BN61" s="30"/>
+      <c r="BQ61" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="BR61" s="30"/>
+      <c r="BS61" s="30"/>
+      <c r="BT61" s="30"/>
+      <c r="BU61" s="30"/>
+      <c r="BV61" s="30"/>
+      <c r="BW61" s="30"/>
+      <c r="BX61" s="30"/>
+      <c r="BY61" s="30"/>
+      <c r="BZ61" s="30"/>
+      <c r="CA61" s="30"/>
+      <c r="CB61" s="30"/>
+      <c r="CE61" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="CF61" s="30"/>
+      <c r="CG61" s="30"/>
+      <c r="CH61" s="30"/>
+      <c r="CI61" s="30"/>
+      <c r="CJ61" s="30"/>
+      <c r="CK61" s="30"/>
+      <c r="CL61" s="30"/>
+      <c r="CM61" s="30"/>
+      <c r="CN61" s="30"/>
+      <c r="CO61" s="30"/>
+      <c r="CP61" s="30"/>
+    </row>
+    <row r="62" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA62" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB62" s="30"/>
+      <c r="AC62" s="30"/>
+      <c r="AD62" s="30"/>
+      <c r="AE62" s="30"/>
+      <c r="AF62" s="30"/>
+      <c r="AG62" s="30"/>
+      <c r="AH62" s="30"/>
+      <c r="AI62" s="30"/>
+      <c r="AJ62" s="30"/>
+      <c r="AK62" s="30"/>
+      <c r="AL62" s="30"/>
+      <c r="AO62" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP62" s="30"/>
+      <c r="AQ62" s="30"/>
+      <c r="AR62" s="30"/>
+      <c r="AS62" s="30"/>
+      <c r="AT62" s="30"/>
+      <c r="AU62" s="30"/>
+      <c r="AV62" s="30"/>
+      <c r="AW62" s="30"/>
+      <c r="AX62" s="30"/>
+      <c r="AY62" s="30"/>
+      <c r="AZ62" s="30"/>
+      <c r="BC62" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD62" s="30"/>
+      <c r="BE62" s="30"/>
+      <c r="BF62" s="30"/>
+      <c r="BG62" s="30"/>
+      <c r="BH62" s="30"/>
+      <c r="BI62" s="30"/>
+      <c r="BJ62" s="30"/>
+      <c r="BK62" s="30"/>
+      <c r="BL62" s="30"/>
+      <c r="BM62" s="30"/>
+      <c r="BN62" s="30"/>
+      <c r="BQ62" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR62" s="30"/>
+      <c r="BS62" s="30"/>
+      <c r="BT62" s="30"/>
+      <c r="BU62" s="30"/>
+      <c r="BV62" s="30"/>
+      <c r="BW62" s="30"/>
+      <c r="BX62" s="30"/>
+      <c r="BY62" s="30"/>
+      <c r="BZ62" s="30"/>
+      <c r="CA62" s="30"/>
+      <c r="CB62" s="30"/>
+      <c r="CE62" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="CF62" s="30"/>
+      <c r="CG62" s="30"/>
+      <c r="CH62" s="30"/>
+      <c r="CI62" s="30"/>
+      <c r="CJ62" s="30"/>
+      <c r="CK62" s="30"/>
+      <c r="CL62" s="30"/>
+      <c r="CM62" s="30"/>
+      <c r="CN62" s="30"/>
+      <c r="CO62" s="30"/>
+      <c r="CP62" s="30"/>
+    </row>
+    <row r="63" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA63" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB63" s="30"/>
+      <c r="AC63" s="30"/>
+      <c r="AD63" s="30"/>
+      <c r="AE63" s="30"/>
+      <c r="AF63" s="30"/>
+      <c r="AG63" s="30"/>
+      <c r="AH63" s="30"/>
+      <c r="AI63" s="30"/>
+      <c r="AJ63" s="30"/>
+      <c r="AK63" s="30"/>
+      <c r="AL63" s="30"/>
+      <c r="AO63" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP63" s="30"/>
+      <c r="AQ63" s="30"/>
+      <c r="AR63" s="30"/>
+      <c r="AS63" s="30"/>
+      <c r="AT63" s="30"/>
+      <c r="AU63" s="30"/>
+      <c r="AV63" s="30"/>
+      <c r="AW63" s="30"/>
+      <c r="AX63" s="30"/>
+      <c r="AY63" s="30"/>
+      <c r="AZ63" s="30"/>
+      <c r="BC63" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD63" s="30"/>
+      <c r="BE63" s="30"/>
+      <c r="BF63" s="30"/>
+      <c r="BG63" s="30"/>
+      <c r="BH63" s="30"/>
+      <c r="BI63" s="30"/>
+      <c r="BJ63" s="30"/>
+      <c r="BK63" s="30"/>
+      <c r="BL63" s="30"/>
+      <c r="BM63" s="30"/>
+      <c r="BN63" s="30"/>
+      <c r="BQ63" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="BR63" s="30"/>
+      <c r="BS63" s="30"/>
+      <c r="BT63" s="30"/>
+      <c r="BU63" s="30"/>
+      <c r="BV63" s="30"/>
+      <c r="BW63" s="30"/>
+      <c r="BX63" s="30"/>
+      <c r="BY63" s="30"/>
+      <c r="BZ63" s="30"/>
+      <c r="CA63" s="30"/>
+      <c r="CB63" s="30"/>
+      <c r="CE63" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="CF63" s="30"/>
+      <c r="CG63" s="30"/>
+      <c r="CH63" s="30"/>
+      <c r="CI63" s="30"/>
+      <c r="CJ63" s="30"/>
+      <c r="CK63" s="30"/>
+      <c r="CL63" s="30"/>
+      <c r="CM63" s="30"/>
+      <c r="CN63" s="30"/>
+      <c r="CO63" s="30"/>
+      <c r="CP63" s="30"/>
+    </row>
+    <row r="64" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA64" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB64" s="30"/>
+      <c r="AC64" s="30"/>
+      <c r="AD64" s="30"/>
+      <c r="AE64" s="30"/>
+      <c r="AF64" s="30"/>
+      <c r="AG64" s="30"/>
+      <c r="AH64" s="30"/>
+      <c r="AI64" s="30"/>
+      <c r="AJ64" s="30"/>
+      <c r="AK64" s="30"/>
+      <c r="AL64" s="30"/>
+      <c r="AO64" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="AP64" s="30"/>
+      <c r="AQ64" s="30"/>
+      <c r="AR64" s="30"/>
+      <c r="AS64" s="30"/>
+      <c r="AT64" s="30"/>
+      <c r="AU64" s="30"/>
+      <c r="AV64" s="30"/>
+      <c r="AW64" s="30"/>
+      <c r="AX64" s="30"/>
+      <c r="AY64" s="30"/>
+      <c r="AZ64" s="30"/>
+      <c r="BC64" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="BD64" s="30"/>
+      <c r="BE64" s="30"/>
+      <c r="BF64" s="30"/>
+      <c r="BG64" s="30"/>
+      <c r="BH64" s="30"/>
+      <c r="BI64" s="30"/>
+      <c r="BJ64" s="30"/>
+      <c r="BK64" s="30"/>
+      <c r="BL64" s="30"/>
+      <c r="BM64" s="30"/>
+      <c r="BN64" s="30"/>
+      <c r="BQ64" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="BR64" s="30"/>
+      <c r="BS64" s="30"/>
+      <c r="BT64" s="30"/>
+      <c r="BU64" s="30"/>
+      <c r="BV64" s="30"/>
+      <c r="BW64" s="30"/>
+      <c r="BX64" s="30"/>
+      <c r="BY64" s="30"/>
+      <c r="BZ64" s="30"/>
+      <c r="CA64" s="30"/>
+      <c r="CB64" s="30"/>
+      <c r="CE64" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="CF64" s="30"/>
+      <c r="CG64" s="30"/>
+      <c r="CH64" s="30"/>
+      <c r="CI64" s="30"/>
+      <c r="CJ64" s="30"/>
+      <c r="CK64" s="30"/>
+      <c r="CL64" s="30"/>
+      <c r="CM64" s="30"/>
+      <c r="CN64" s="30"/>
+      <c r="CO64" s="30"/>
+      <c r="CP64" s="30"/>
+    </row>
+    <row r="65" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA65" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB65" s="30"/>
+      <c r="AC65" s="30"/>
+      <c r="AD65" s="30"/>
+      <c r="AE65" s="30"/>
+      <c r="AF65" s="30"/>
+      <c r="AG65" s="30"/>
+      <c r="AH65" s="30"/>
+      <c r="AI65" s="30"/>
+      <c r="AJ65" s="30"/>
+      <c r="AK65" s="30"/>
+      <c r="AL65" s="30"/>
+      <c r="AO65" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="AP65" s="30"/>
+      <c r="AQ65" s="30"/>
+      <c r="AR65" s="30"/>
+      <c r="AS65" s="30"/>
+      <c r="AT65" s="30"/>
+      <c r="AU65" s="30"/>
+      <c r="AV65" s="30"/>
+      <c r="AW65" s="30"/>
+      <c r="AX65" s="30"/>
+      <c r="AY65" s="30"/>
+      <c r="AZ65" s="30"/>
+      <c r="BC65" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="BD65" s="30"/>
+      <c r="BE65" s="30"/>
+      <c r="BF65" s="30"/>
+      <c r="BG65" s="30"/>
+      <c r="BH65" s="30"/>
+      <c r="BI65" s="30"/>
+      <c r="BJ65" s="30"/>
+      <c r="BK65" s="30"/>
+      <c r="BL65" s="30"/>
+      <c r="BM65" s="30"/>
+      <c r="BN65" s="30"/>
+      <c r="BQ65" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="BR65" s="30"/>
+      <c r="BS65" s="30"/>
+      <c r="BT65" s="30"/>
+      <c r="BU65" s="30"/>
+      <c r="BV65" s="30"/>
+      <c r="BW65" s="30"/>
+      <c r="BX65" s="30"/>
+      <c r="BY65" s="30"/>
+      <c r="BZ65" s="30"/>
+      <c r="CA65" s="30"/>
+      <c r="CB65" s="30"/>
+      <c r="CE65" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="CF65" s="30"/>
+      <c r="CG65" s="30"/>
+      <c r="CH65" s="30"/>
+      <c r="CI65" s="30"/>
+      <c r="CJ65" s="30"/>
+      <c r="CK65" s="30"/>
+      <c r="CL65" s="30"/>
+      <c r="CM65" s="30"/>
+      <c r="CN65" s="30"/>
+      <c r="CO65" s="30"/>
+      <c r="CP65" s="30"/>
+    </row>
+    <row r="66" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA66" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB66" s="30"/>
+      <c r="AC66" s="30"/>
+      <c r="AD66" s="30"/>
+      <c r="AE66" s="30"/>
+      <c r="AF66" s="30"/>
+      <c r="AG66" s="30"/>
+      <c r="AH66" s="30"/>
+      <c r="AI66" s="30"/>
+      <c r="AJ66" s="30"/>
+      <c r="AK66" s="30"/>
+      <c r="AL66" s="30"/>
+      <c r="AO66" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP66" s="30"/>
+      <c r="AQ66" s="30"/>
+      <c r="AR66" s="30"/>
+      <c r="AS66" s="30"/>
+      <c r="AT66" s="30"/>
+      <c r="AU66" s="30"/>
+      <c r="AV66" s="30"/>
+      <c r="AW66" s="30"/>
+      <c r="AX66" s="30"/>
+      <c r="AY66" s="30"/>
+      <c r="AZ66" s="30"/>
+      <c r="BC66" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="BD66" s="30"/>
+      <c r="BE66" s="30"/>
+      <c r="BF66" s="30"/>
+      <c r="BG66" s="30"/>
+      <c r="BH66" s="30"/>
+      <c r="BI66" s="30"/>
+      <c r="BJ66" s="30"/>
+      <c r="BK66" s="30"/>
+      <c r="BL66" s="30"/>
+      <c r="BM66" s="30"/>
+      <c r="BN66" s="30"/>
+      <c r="BQ66" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="BR66" s="30"/>
+      <c r="BS66" s="30"/>
+      <c r="BT66" s="30"/>
+      <c r="BU66" s="30"/>
+      <c r="BV66" s="30"/>
+      <c r="BW66" s="30"/>
+      <c r="BX66" s="30"/>
+      <c r="BY66" s="30"/>
+      <c r="BZ66" s="30"/>
+      <c r="CA66" s="30"/>
+      <c r="CB66" s="30"/>
+      <c r="CE66" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="CF66" s="30"/>
+      <c r="CG66" s="30"/>
+      <c r="CH66" s="30"/>
+      <c r="CI66" s="30"/>
+      <c r="CJ66" s="30"/>
+      <c r="CK66" s="30"/>
+      <c r="CL66" s="30"/>
+      <c r="CM66" s="30"/>
+      <c r="CN66" s="30"/>
+      <c r="CO66" s="30"/>
+      <c r="CP66" s="30"/>
+    </row>
+    <row r="67" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA67" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB67" s="30"/>
+      <c r="AC67" s="30"/>
+      <c r="AD67" s="30"/>
+      <c r="AE67" s="30"/>
+      <c r="AF67" s="30"/>
+      <c r="AG67" s="30"/>
+      <c r="AH67" s="30"/>
+      <c r="AI67" s="30"/>
+      <c r="AJ67" s="30"/>
+      <c r="AK67" s="30"/>
+      <c r="AL67" s="30"/>
+      <c r="AO67" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="AP67" s="30"/>
+      <c r="AQ67" s="30"/>
+      <c r="AR67" s="30"/>
+      <c r="AS67" s="30"/>
+      <c r="AT67" s="30"/>
+      <c r="AU67" s="30"/>
+      <c r="AV67" s="30"/>
+      <c r="AW67" s="30"/>
+      <c r="AX67" s="30"/>
+      <c r="AY67" s="30"/>
+      <c r="AZ67" s="30"/>
+      <c r="BC67" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="BD67" s="30"/>
+      <c r="BE67" s="30"/>
+      <c r="BF67" s="30"/>
+      <c r="BG67" s="30"/>
+      <c r="BH67" s="30"/>
+      <c r="BI67" s="30"/>
+      <c r="BJ67" s="30"/>
+      <c r="BK67" s="30"/>
+      <c r="BL67" s="30"/>
+      <c r="BM67" s="30"/>
+      <c r="BN67" s="30"/>
+      <c r="BQ67" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="BR67" s="30"/>
+      <c r="BS67" s="30"/>
+      <c r="BT67" s="30"/>
+      <c r="BU67" s="30"/>
+      <c r="BV67" s="30"/>
+      <c r="BW67" s="30"/>
+      <c r="BX67" s="30"/>
+      <c r="BY67" s="30"/>
+      <c r="BZ67" s="30"/>
+      <c r="CA67" s="30"/>
+      <c r="CB67" s="30"/>
+      <c r="CE67" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="CF67" s="30"/>
+      <c r="CG67" s="30"/>
+      <c r="CH67" s="30"/>
+      <c r="CI67" s="30"/>
+      <c r="CJ67" s="30"/>
+      <c r="CK67" s="30"/>
+      <c r="CL67" s="30"/>
+      <c r="CM67" s="30"/>
+      <c r="CN67" s="30"/>
+      <c r="CO67" s="30"/>
+      <c r="CP67" s="30"/>
+    </row>
+    <row r="68" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA68" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB68" s="30"/>
+      <c r="AC68" s="30"/>
+      <c r="AD68" s="30"/>
+      <c r="AE68" s="30"/>
+      <c r="AF68" s="30"/>
+      <c r="AG68" s="30"/>
+      <c r="AH68" s="30"/>
+      <c r="AI68" s="30"/>
+      <c r="AJ68" s="30"/>
+      <c r="AK68" s="30"/>
+      <c r="AL68" s="30"/>
+      <c r="AO68" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP68" s="30"/>
+      <c r="AQ68" s="30"/>
+      <c r="AR68" s="30"/>
+      <c r="AS68" s="30"/>
+      <c r="AT68" s="30"/>
+      <c r="AU68" s="30"/>
+      <c r="AV68" s="30"/>
+      <c r="AW68" s="30"/>
+      <c r="AX68" s="30"/>
+      <c r="AY68" s="30"/>
+      <c r="AZ68" s="30"/>
+      <c r="BC68" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="BD68" s="30"/>
+      <c r="BE68" s="30"/>
+      <c r="BF68" s="30"/>
+      <c r="BG68" s="30"/>
+      <c r="BH68" s="30"/>
+      <c r="BI68" s="30"/>
+      <c r="BJ68" s="30"/>
+      <c r="BK68" s="30"/>
+      <c r="BL68" s="30"/>
+      <c r="BM68" s="30"/>
+      <c r="BN68" s="30"/>
+      <c r="BQ68" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="BR68" s="30"/>
+      <c r="BS68" s="30"/>
+      <c r="BT68" s="30"/>
+      <c r="BU68" s="30"/>
+      <c r="BV68" s="30"/>
+      <c r="BW68" s="30"/>
+      <c r="BX68" s="30"/>
+      <c r="BY68" s="30"/>
+      <c r="BZ68" s="30"/>
+      <c r="CA68" s="30"/>
+      <c r="CB68" s="30"/>
+      <c r="CE68" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="CF68" s="30"/>
+      <c r="CG68" s="30"/>
+      <c r="CH68" s="30"/>
+      <c r="CI68" s="30"/>
+      <c r="CJ68" s="30"/>
+      <c r="CK68" s="30"/>
+      <c r="CL68" s="30"/>
+      <c r="CM68" s="30"/>
+      <c r="CN68" s="30"/>
+      <c r="CO68" s="30"/>
+      <c r="CP68" s="30"/>
+    </row>
+    <row r="69" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA69" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB69" s="30"/>
+      <c r="AC69" s="30"/>
+      <c r="AD69" s="30"/>
+      <c r="AE69" s="30"/>
+      <c r="AF69" s="30"/>
+      <c r="AG69" s="30"/>
+      <c r="AH69" s="30"/>
+      <c r="AI69" s="30"/>
+      <c r="AJ69" s="30"/>
+      <c r="AK69" s="30"/>
+      <c r="AL69" s="30"/>
+      <c r="AO69" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="AP69" s="30"/>
+      <c r="AQ69" s="30"/>
+      <c r="AR69" s="30"/>
+      <c r="AS69" s="30"/>
+      <c r="AT69" s="30"/>
+      <c r="AU69" s="30"/>
+      <c r="AV69" s="30"/>
+      <c r="AW69" s="30"/>
+      <c r="AX69" s="30"/>
+      <c r="AY69" s="30"/>
+      <c r="AZ69" s="30"/>
+      <c r="BC69" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="BD69" s="30"/>
+      <c r="BE69" s="30"/>
+      <c r="BF69" s="30"/>
+      <c r="BG69" s="30"/>
+      <c r="BH69" s="30"/>
+      <c r="BI69" s="30"/>
+      <c r="BJ69" s="30"/>
+      <c r="BK69" s="30"/>
+      <c r="BL69" s="30"/>
+      <c r="BM69" s="30"/>
+      <c r="BN69" s="30"/>
+      <c r="BQ69" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="BR69" s="30"/>
+      <c r="BS69" s="30"/>
+      <c r="BT69" s="30"/>
+      <c r="BU69" s="30"/>
+      <c r="BV69" s="30"/>
+      <c r="BW69" s="30"/>
+      <c r="BX69" s="30"/>
+      <c r="BY69" s="30"/>
+      <c r="BZ69" s="30"/>
+      <c r="CA69" s="30"/>
+      <c r="CB69" s="30"/>
+      <c r="CE69" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="CF69" s="30"/>
+      <c r="CG69" s="30"/>
+      <c r="CH69" s="30"/>
+      <c r="CI69" s="30"/>
+      <c r="CJ69" s="30"/>
+      <c r="CK69" s="30"/>
+      <c r="CL69" s="30"/>
+      <c r="CM69" s="30"/>
+      <c r="CN69" s="30"/>
+      <c r="CO69" s="30"/>
+      <c r="CP69" s="30"/>
+    </row>
+    <row r="70" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA70" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB70" s="30"/>
+      <c r="AC70" s="30"/>
+      <c r="AD70" s="30"/>
+      <c r="AE70" s="37"/>
+      <c r="AF70" s="30"/>
+      <c r="AG70" s="30"/>
+      <c r="AH70" s="30"/>
+      <c r="AI70" s="30"/>
+      <c r="AJ70" s="30"/>
+      <c r="AK70" s="30"/>
+      <c r="AL70" s="30"/>
+      <c r="AO70" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="AP70" s="30"/>
+      <c r="AQ70" s="30"/>
+      <c r="AR70" s="30"/>
+      <c r="AS70" s="37"/>
+      <c r="AT70" s="30"/>
+      <c r="AU70" s="30"/>
+      <c r="AV70" s="30"/>
+      <c r="AW70" s="30"/>
+      <c r="AX70" s="30"/>
+      <c r="AY70" s="30"/>
+      <c r="AZ70" s="30"/>
+      <c r="BC70" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="BD70" s="30"/>
+      <c r="BE70" s="30"/>
+      <c r="BF70" s="30"/>
+      <c r="BG70" s="37"/>
+      <c r="BH70" s="30"/>
+      <c r="BI70" s="30"/>
+      <c r="BJ70" s="30"/>
+      <c r="BK70" s="30"/>
+      <c r="BL70" s="30"/>
+      <c r="BM70" s="30"/>
+      <c r="BN70" s="30"/>
+      <c r="BQ70" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="BR70" s="30"/>
+      <c r="BS70" s="30"/>
+      <c r="BT70" s="30"/>
+      <c r="BU70" s="37"/>
+      <c r="BV70" s="30"/>
+      <c r="BW70" s="30"/>
+      <c r="BX70" s="30"/>
+      <c r="BY70" s="30"/>
+      <c r="BZ70" s="30"/>
+      <c r="CA70" s="30"/>
+      <c r="CB70" s="30"/>
+      <c r="CE70" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="CF70" s="30"/>
+      <c r="CG70" s="30"/>
+      <c r="CH70" s="30"/>
+      <c r="CI70" s="37"/>
+      <c r="CJ70" s="30"/>
+      <c r="CK70" s="30"/>
+      <c r="CL70" s="30"/>
+      <c r="CM70" s="30"/>
+      <c r="CN70" s="30"/>
+      <c r="CO70" s="30"/>
+      <c r="CP70" s="30"/>
+    </row>
+    <row r="71" spans="27:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AB71" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC71" s="39"/>
+      <c r="AD71" s="40"/>
+      <c r="AE71" s="39"/>
+      <c r="AF71" s="40"/>
+      <c r="AG71" s="41"/>
+      <c r="AH71" s="42"/>
+      <c r="AI71" s="39"/>
+      <c r="AJ71" s="40"/>
+      <c r="AK71" s="39"/>
+      <c r="AL71" s="40"/>
+      <c r="AP71" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ71" s="39"/>
+      <c r="AR71" s="40"/>
+      <c r="AS71" s="39"/>
+      <c r="AT71" s="40"/>
+      <c r="AU71" s="41"/>
+      <c r="AV71" s="42"/>
+      <c r="AW71" s="39"/>
+      <c r="AX71" s="40"/>
+      <c r="AY71" s="39"/>
+      <c r="AZ71" s="40"/>
+      <c r="BD71" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="BE71" s="39"/>
+      <c r="BF71" s="40"/>
+      <c r="BG71" s="39"/>
+      <c r="BH71" s="40"/>
+      <c r="BI71" s="41"/>
+      <c r="BJ71" s="42"/>
+      <c r="BK71" s="39"/>
+      <c r="BL71" s="40"/>
+      <c r="BM71" s="39"/>
+      <c r="BN71" s="40"/>
+      <c r="BR71" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="BS71" s="39"/>
+      <c r="BT71" s="40"/>
+      <c r="BU71" s="39"/>
+      <c r="BV71" s="40"/>
+      <c r="BW71" s="41"/>
+      <c r="BX71" s="42"/>
+      <c r="BY71" s="39"/>
+      <c r="BZ71" s="40"/>
+      <c r="CA71" s="39"/>
+      <c r="CB71" s="40"/>
+      <c r="CF71" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="CG71" s="39"/>
+      <c r="CH71" s="40"/>
+      <c r="CI71" s="39"/>
+      <c r="CJ71" s="40"/>
+      <c r="CK71" s="41"/>
+      <c r="CL71" s="42"/>
+      <c r="CM71" s="39"/>
+      <c r="CN71" s="40"/>
+      <c r="CO71" s="39"/>
+      <c r="CP71" s="40"/>
+    </row>
+    <row r="73" spans="27:94" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="27:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AA74" s="45" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB74" s="51"/>
+      <c r="AC74" s="51"/>
+      <c r="AD74" s="51"/>
+      <c r="AE74" s="51"/>
+      <c r="AF74" s="51"/>
+      <c r="AG74" s="51"/>
+      <c r="AH74" s="51"/>
+      <c r="AI74" s="51"/>
+      <c r="AJ74" s="51"/>
+      <c r="AK74" s="51"/>
+      <c r="AL74" s="52"/>
+      <c r="AO74" s="45" t="s">
+        <v>41</v>
+      </c>
+      <c r="AP74" s="51"/>
+      <c r="AQ74" s="51"/>
+      <c r="AR74" s="51"/>
+      <c r="AS74" s="51"/>
+      <c r="AT74" s="51"/>
+      <c r="AU74" s="51"/>
+      <c r="AV74" s="51"/>
+      <c r="AW74" s="51"/>
+      <c r="AX74" s="51"/>
+      <c r="AY74" s="51"/>
+      <c r="AZ74" s="52"/>
+      <c r="BC74" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="BD74" s="51"/>
+      <c r="BE74" s="51"/>
+      <c r="BF74" s="51"/>
+      <c r="BG74" s="51"/>
+      <c r="BH74" s="51"/>
+      <c r="BI74" s="51"/>
+      <c r="BJ74" s="51"/>
+      <c r="BK74" s="51"/>
+      <c r="BL74" s="51"/>
+      <c r="BM74" s="51"/>
+      <c r="BN74" s="52"/>
+      <c r="BQ74" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="BR74" s="51"/>
+      <c r="BS74" s="51"/>
+      <c r="BT74" s="51"/>
+      <c r="BU74" s="51"/>
+      <c r="BV74" s="51"/>
+      <c r="BW74" s="51"/>
+      <c r="BX74" s="51"/>
+      <c r="BY74" s="51"/>
+      <c r="BZ74" s="51"/>
+      <c r="CA74" s="51"/>
+      <c r="CB74" s="52"/>
+      <c r="CE74" s="45" t="s">
+        <v>51</v>
+      </c>
+      <c r="CF74" s="51"/>
+      <c r="CG74" s="51"/>
+      <c r="CH74" s="51"/>
+      <c r="CI74" s="51"/>
+      <c r="CJ74" s="51"/>
+      <c r="CK74" s="51"/>
+      <c r="CL74" s="51"/>
+      <c r="CM74" s="51"/>
+      <c r="CN74" s="51"/>
+      <c r="CO74" s="51"/>
+      <c r="CP74" s="52"/>
+    </row>
+    <row r="75" spans="27:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AA75" s="1"/>
+      <c r="AB75" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC75" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD75" s="44"/>
+      <c r="AE75" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF75" s="44"/>
+      <c r="AG75" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH75" s="44"/>
+      <c r="AI75" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ75" s="44"/>
+      <c r="AK75" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="AL75" s="44"/>
+      <c r="AO75" s="1"/>
+      <c r="AP75" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AQ75" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR75" s="44"/>
+      <c r="AS75" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT75" s="44"/>
+      <c r="AU75" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV75" s="44"/>
+      <c r="AW75" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="AX75" s="44"/>
+      <c r="AY75" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="AZ75" s="44"/>
+      <c r="BC75" s="1"/>
+      <c r="BD75" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE75" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="BF75" s="44"/>
+      <c r="BG75" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="BH75" s="44"/>
+      <c r="BI75" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="BJ75" s="44"/>
+      <c r="BK75" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL75" s="44"/>
+      <c r="BM75" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="BN75" s="44"/>
+      <c r="BQ75" s="1"/>
+      <c r="BR75" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS75" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT75" s="44"/>
+      <c r="BU75" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="BV75" s="44"/>
+      <c r="BW75" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="BX75" s="44"/>
+      <c r="BY75" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="BZ75" s="44"/>
+      <c r="CA75" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="CB75" s="44"/>
+      <c r="CE75" s="1"/>
+      <c r="CF75" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="CG75" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="CH75" s="44"/>
+      <c r="CI75" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="CJ75" s="44"/>
+      <c r="CK75" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL75" s="44"/>
+      <c r="CM75" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="CN75" s="44"/>
+      <c r="CO75" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="CP75" s="44"/>
+    </row>
+    <row r="76" spans="27:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AA76" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB76" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO76" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="AP76" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AR76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AS76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AT76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AU76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AX76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AY76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BC76" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD76" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BF76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BG76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BI76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BJ76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BK76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BM76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BN76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BQ76" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="BR76" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="BS76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BU76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BV76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BW76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BY76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BZ76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="CA76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="CB76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="CE76" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="CF76" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="CG76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="CH76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="CI76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="CJ76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="CK76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="CL76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="CM76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="CN76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="CO76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="CP76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="27:94" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="AA77" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB77" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC77" s="19"/>
+      <c r="AD77" s="20"/>
+      <c r="AE77" s="19"/>
+      <c r="AF77" s="20"/>
+      <c r="AG77" s="19"/>
+      <c r="AH77" s="20"/>
+      <c r="AI77" s="19"/>
+      <c r="AJ77" s="20"/>
+      <c r="AK77" s="19"/>
+      <c r="AL77" s="20"/>
+      <c r="AO77" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP77" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ77" s="19"/>
+      <c r="AR77" s="20"/>
+      <c r="AS77" s="19"/>
+      <c r="AT77" s="20"/>
+      <c r="AU77" s="19"/>
+      <c r="AV77" s="20"/>
+      <c r="AW77" s="19"/>
+      <c r="AX77" s="20"/>
+      <c r="AY77" s="19"/>
+      <c r="AZ77" s="20"/>
+      <c r="BC77" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="BD77" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="BE77" s="19"/>
+      <c r="BF77" s="20"/>
+      <c r="BG77" s="19"/>
+      <c r="BH77" s="20"/>
+      <c r="BI77" s="19"/>
+      <c r="BJ77" s="20"/>
+      <c r="BK77" s="19"/>
+      <c r="BL77" s="20"/>
+      <c r="BM77" s="19"/>
+      <c r="BN77" s="20"/>
+      <c r="BQ77" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="BR77" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="BS77" s="19"/>
+      <c r="BT77" s="20"/>
+      <c r="BU77" s="19"/>
+      <c r="BV77" s="20"/>
+      <c r="BW77" s="19"/>
+      <c r="BX77" s="20"/>
+      <c r="BY77" s="19"/>
+      <c r="BZ77" s="20"/>
+      <c r="CA77" s="19"/>
+      <c r="CB77" s="20"/>
+      <c r="CE77" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="CF77" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="CG77" s="19"/>
+      <c r="CH77" s="20"/>
+      <c r="CI77" s="19"/>
+      <c r="CJ77" s="20"/>
+      <c r="CK77" s="19"/>
+      <c r="CL77" s="20"/>
+      <c r="CM77" s="19"/>
+      <c r="CN77" s="20"/>
+      <c r="CO77" s="19"/>
+      <c r="CP77" s="20"/>
+    </row>
+    <row r="78" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA78" s="49"/>
+      <c r="AB78" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC78" s="15"/>
+      <c r="AD78" s="16"/>
+      <c r="AE78" s="15"/>
+      <c r="AF78" s="16"/>
+      <c r="AG78" s="15"/>
+      <c r="AH78" s="16"/>
+      <c r="AI78" s="15"/>
+      <c r="AJ78" s="16"/>
+      <c r="AK78" s="15"/>
+      <c r="AL78" s="16"/>
+      <c r="AO78" s="49"/>
+      <c r="AP78" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AQ78" s="15"/>
+      <c r="AR78" s="16"/>
+      <c r="AS78" s="15"/>
+      <c r="AT78" s="16"/>
+      <c r="AU78" s="15"/>
+      <c r="AV78" s="16"/>
+      <c r="AW78" s="15"/>
+      <c r="AX78" s="16"/>
+      <c r="AY78" s="15"/>
+      <c r="AZ78" s="16"/>
+      <c r="BC78" s="49"/>
+      <c r="BD78" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="BE78" s="15"/>
+      <c r="BF78" s="16"/>
+      <c r="BG78" s="15"/>
+      <c r="BH78" s="16"/>
+      <c r="BI78" s="15"/>
+      <c r="BJ78" s="16"/>
+      <c r="BK78" s="15"/>
+      <c r="BL78" s="16"/>
+      <c r="BM78" s="15"/>
+      <c r="BN78" s="16"/>
+      <c r="BQ78" s="49"/>
+      <c r="BR78" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="BS78" s="15"/>
+      <c r="BT78" s="16"/>
+      <c r="BU78" s="15"/>
+      <c r="BV78" s="16"/>
+      <c r="BW78" s="15"/>
+      <c r="BX78" s="16"/>
+      <c r="BY78" s="15"/>
+      <c r="BZ78" s="16"/>
+      <c r="CA78" s="15"/>
+      <c r="CB78" s="16"/>
+      <c r="CE78" s="49"/>
+      <c r="CF78" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="CG78" s="15"/>
+      <c r="CH78" s="16"/>
+      <c r="CI78" s="15"/>
+      <c r="CJ78" s="16"/>
+      <c r="CK78" s="15"/>
+      <c r="CL78" s="16"/>
+      <c r="CM78" s="15"/>
+      <c r="CN78" s="16"/>
+      <c r="CO78" s="15"/>
+      <c r="CP78" s="16"/>
+    </row>
+    <row r="79" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA79" s="49"/>
+      <c r="AB79" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC79" s="15"/>
+      <c r="AD79" s="16"/>
+      <c r="AE79" s="15"/>
+      <c r="AF79" s="16"/>
+      <c r="AG79" s="15"/>
+      <c r="AH79" s="16"/>
+      <c r="AI79" s="15"/>
+      <c r="AJ79" s="16"/>
+      <c r="AK79" s="15"/>
+      <c r="AL79" s="16"/>
+      <c r="AO79" s="49"/>
+      <c r="AP79" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="AQ79" s="15"/>
+      <c r="AR79" s="16"/>
+      <c r="AS79" s="15"/>
+      <c r="AT79" s="16"/>
+      <c r="AU79" s="15"/>
+      <c r="AV79" s="16"/>
+      <c r="AW79" s="15"/>
+      <c r="AX79" s="16"/>
+      <c r="AY79" s="15"/>
+      <c r="AZ79" s="16"/>
+      <c r="BC79" s="49"/>
+      <c r="BD79" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="BE79" s="15"/>
+      <c r="BF79" s="16"/>
+      <c r="BG79" s="15"/>
+      <c r="BH79" s="16"/>
+      <c r="BI79" s="15"/>
+      <c r="BJ79" s="16"/>
+      <c r="BK79" s="15"/>
+      <c r="BL79" s="16"/>
+      <c r="BM79" s="15"/>
+      <c r="BN79" s="16"/>
+      <c r="BQ79" s="49"/>
+      <c r="BR79" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="BS79" s="15"/>
+      <c r="BT79" s="16"/>
+      <c r="BU79" s="15"/>
+      <c r="BV79" s="16"/>
+      <c r="BW79" s="15"/>
+      <c r="BX79" s="16"/>
+      <c r="BY79" s="15"/>
+      <c r="BZ79" s="16"/>
+      <c r="CA79" s="15"/>
+      <c r="CB79" s="16"/>
+      <c r="CE79" s="49"/>
+      <c r="CF79" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="CG79" s="15"/>
+      <c r="CH79" s="16"/>
+      <c r="CI79" s="15"/>
+      <c r="CJ79" s="16"/>
+      <c r="CK79" s="15"/>
+      <c r="CL79" s="16"/>
+      <c r="CM79" s="15"/>
+      <c r="CN79" s="16"/>
+      <c r="CO79" s="15"/>
+      <c r="CP79" s="16"/>
+    </row>
+    <row r="80" spans="27:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AA80" s="50"/>
+      <c r="AB80" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC80" s="21"/>
+      <c r="AD80" s="22"/>
+      <c r="AE80" s="21"/>
+      <c r="AF80" s="22"/>
+      <c r="AG80" s="21"/>
+      <c r="AH80" s="22"/>
+      <c r="AI80" s="21"/>
+      <c r="AJ80" s="22"/>
+      <c r="AK80" s="21"/>
+      <c r="AL80" s="22"/>
+      <c r="AO80" s="50"/>
+      <c r="AP80" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ80" s="21"/>
+      <c r="AR80" s="22"/>
+      <c r="AS80" s="21"/>
+      <c r="AT80" s="22"/>
+      <c r="AU80" s="21"/>
+      <c r="AV80" s="22"/>
+      <c r="AW80" s="21"/>
+      <c r="AX80" s="22"/>
+      <c r="AY80" s="21"/>
+      <c r="AZ80" s="22"/>
+      <c r="BC80" s="50"/>
+      <c r="BD80" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="BE80" s="21"/>
+      <c r="BF80" s="22"/>
+      <c r="BG80" s="21"/>
+      <c r="BH80" s="22"/>
+      <c r="BI80" s="21"/>
+      <c r="BJ80" s="22"/>
+      <c r="BK80" s="21"/>
+      <c r="BL80" s="22"/>
+      <c r="BM80" s="21"/>
+      <c r="BN80" s="22"/>
+      <c r="BQ80" s="50"/>
+      <c r="BR80" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="BS80" s="21"/>
+      <c r="BT80" s="22"/>
+      <c r="BU80" s="21"/>
+      <c r="BV80" s="22"/>
+      <c r="BW80" s="21"/>
+      <c r="BX80" s="22"/>
+      <c r="BY80" s="21"/>
+      <c r="BZ80" s="22"/>
+      <c r="CA80" s="21"/>
+      <c r="CB80" s="22"/>
+      <c r="CE80" s="50"/>
+      <c r="CF80" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="CG80" s="21"/>
+      <c r="CH80" s="22"/>
+      <c r="CI80" s="21"/>
+      <c r="CJ80" s="22"/>
+      <c r="CK80" s="21"/>
+      <c r="CL80" s="22"/>
+      <c r="CM80" s="21"/>
+      <c r="CN80" s="22"/>
+      <c r="CO80" s="21"/>
+      <c r="CP80" s="22"/>
+    </row>
+    <row r="82" spans="27:94" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="27:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AA83" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB83" s="46"/>
+      <c r="AC83" s="46"/>
+      <c r="AD83" s="46"/>
+      <c r="AE83" s="46"/>
+      <c r="AF83" s="46"/>
+      <c r="AG83" s="46"/>
+      <c r="AH83" s="46"/>
+      <c r="AI83" s="46"/>
+      <c r="AJ83" s="46"/>
+      <c r="AK83" s="46"/>
+      <c r="AL83" s="47"/>
+      <c r="AO83" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP83" s="46"/>
+      <c r="AQ83" s="46"/>
+      <c r="AR83" s="46"/>
+      <c r="AS83" s="46"/>
+      <c r="AT83" s="46"/>
+      <c r="AU83" s="46"/>
+      <c r="AV83" s="46"/>
+      <c r="AW83" s="46"/>
+      <c r="AX83" s="46"/>
+      <c r="AY83" s="46"/>
+      <c r="AZ83" s="47"/>
+      <c r="BC83" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="BD83" s="46"/>
+      <c r="BE83" s="46"/>
+      <c r="BF83" s="46"/>
+      <c r="BG83" s="46"/>
+      <c r="BH83" s="46"/>
+      <c r="BI83" s="46"/>
+      <c r="BJ83" s="46"/>
+      <c r="BK83" s="46"/>
+      <c r="BL83" s="46"/>
+      <c r="BM83" s="46"/>
+      <c r="BN83" s="47"/>
+      <c r="BQ83" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="BR83" s="46"/>
+      <c r="BS83" s="46"/>
+      <c r="BT83" s="46"/>
+      <c r="BU83" s="46"/>
+      <c r="BV83" s="46"/>
+      <c r="BW83" s="46"/>
+      <c r="BX83" s="46"/>
+      <c r="BY83" s="46"/>
+      <c r="BZ83" s="46"/>
+      <c r="CA83" s="46"/>
+      <c r="CB83" s="47"/>
+      <c r="CE83" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="CF83" s="46"/>
+      <c r="CG83" s="46"/>
+      <c r="CH83" s="46"/>
+      <c r="CI83" s="46"/>
+      <c r="CJ83" s="46"/>
+      <c r="CK83" s="46"/>
+      <c r="CL83" s="46"/>
+      <c r="CM83" s="46"/>
+      <c r="CN83" s="46"/>
+      <c r="CO83" s="46"/>
+      <c r="CP83" s="47"/>
+    </row>
+    <row r="84" spans="27:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AA84" s="24"/>
+      <c r="AB84" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC84" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD84" s="44"/>
+      <c r="AE84" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF84" s="44"/>
+      <c r="AG84" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH84" s="44"/>
+      <c r="AI84" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ84" s="44"/>
+      <c r="AK84" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="AL84" s="44"/>
+      <c r="AO84" s="24"/>
+      <c r="AP84" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AQ84" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR84" s="44"/>
+      <c r="AS84" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT84" s="44"/>
+      <c r="AU84" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV84" s="44"/>
+      <c r="AW84" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="AX84" s="44"/>
+      <c r="AY84" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="AZ84" s="44"/>
+      <c r="BC84" s="24"/>
+      <c r="BD84" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE84" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="BF84" s="44"/>
+      <c r="BG84" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="BH84" s="44"/>
+      <c r="BI84" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="BJ84" s="44"/>
+      <c r="BK84" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL84" s="44"/>
+      <c r="BM84" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="BN84" s="44"/>
+      <c r="BQ84" s="24"/>
+      <c r="BR84" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS84" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT84" s="44"/>
+      <c r="BU84" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="BV84" s="44"/>
+      <c r="BW84" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="BX84" s="44"/>
+      <c r="BY84" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="BZ84" s="44"/>
+      <c r="CA84" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="CB84" s="44"/>
+      <c r="CE84" s="24"/>
+      <c r="CF84" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="CG84" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="CH84" s="44"/>
+      <c r="CI84" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="CJ84" s="44"/>
+      <c r="CK84" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL84" s="44"/>
+      <c r="CM84" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="CN84" s="44"/>
+      <c r="CO84" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="CP84" s="44"/>
+    </row>
+    <row r="85" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA85" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB85" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC85" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD85" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE85" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF85" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG85" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH85" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI85" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ85" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK85" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL85" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO85" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="AP85" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ85" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AR85" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AS85" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AT85" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AU85" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV85" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW85" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AX85" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AY85" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ85" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BC85" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="BD85" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="BE85" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BF85" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BG85" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH85" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BI85" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BJ85" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BK85" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL85" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BM85" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BN85" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BQ85" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="BR85" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="BS85" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT85" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BU85" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BV85" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BW85" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX85" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="BY85" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="BZ85" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="CA85" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="CB85" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="CE85" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="CF85" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="CG85" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="CH85" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="CI85" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="CJ85" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="CK85" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="CL85" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="CM85" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="CN85" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="CO85" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="CP85" s="28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA86" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB86" s="36"/>
+      <c r="AC86" s="30"/>
+      <c r="AD86" s="30"/>
+      <c r="AE86" s="30"/>
+      <c r="AF86" s="30"/>
+      <c r="AG86" s="30"/>
+      <c r="AH86" s="30"/>
+      <c r="AI86" s="30"/>
+      <c r="AJ86" s="30"/>
+      <c r="AK86" s="30"/>
+      <c r="AL86" s="30"/>
+      <c r="AO86" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="AP86" s="36"/>
+      <c r="AQ86" s="30"/>
+      <c r="AR86" s="30"/>
+      <c r="AS86" s="30"/>
+      <c r="AT86" s="30"/>
+      <c r="AU86" s="30"/>
+      <c r="AV86" s="30"/>
+      <c r="AW86" s="30"/>
+      <c r="AX86" s="30"/>
+      <c r="AY86" s="30"/>
+      <c r="AZ86" s="30"/>
+      <c r="BC86" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="BD86" s="36"/>
+      <c r="BE86" s="30"/>
+      <c r="BF86" s="30"/>
+      <c r="BG86" s="30"/>
+      <c r="BH86" s="30"/>
+      <c r="BI86" s="30"/>
+      <c r="BJ86" s="30"/>
+      <c r="BK86" s="30"/>
+      <c r="BL86" s="30"/>
+      <c r="BM86" s="30"/>
+      <c r="BN86" s="30"/>
+      <c r="BQ86" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="BR86" s="36"/>
+      <c r="BS86" s="30"/>
+      <c r="BT86" s="30"/>
+      <c r="BU86" s="30"/>
+      <c r="BV86" s="30"/>
+      <c r="BW86" s="30"/>
+      <c r="BX86" s="30"/>
+      <c r="BY86" s="30"/>
+      <c r="BZ86" s="30"/>
+      <c r="CA86" s="30"/>
+      <c r="CB86" s="30"/>
+      <c r="CE86" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="CF86" s="36"/>
+      <c r="CG86" s="30"/>
+      <c r="CH86" s="30"/>
+      <c r="CI86" s="30"/>
+      <c r="CJ86" s="30"/>
+      <c r="CK86" s="30"/>
+      <c r="CL86" s="30"/>
+      <c r="CM86" s="30"/>
+      <c r="CN86" s="30"/>
+      <c r="CO86" s="30"/>
+      <c r="CP86" s="30"/>
+    </row>
+    <row r="87" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA87" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB87" s="30"/>
+      <c r="AC87" s="30"/>
+      <c r="AD87" s="30"/>
+      <c r="AE87" s="30"/>
+      <c r="AF87" s="30"/>
+      <c r="AG87" s="30"/>
+      <c r="AH87" s="30"/>
+      <c r="AI87" s="30"/>
+      <c r="AJ87" s="30"/>
+      <c r="AK87" s="30"/>
+      <c r="AL87" s="30"/>
+      <c r="AO87" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP87" s="30"/>
+      <c r="AQ87" s="30"/>
+      <c r="AR87" s="30"/>
+      <c r="AS87" s="30"/>
+      <c r="AT87" s="30"/>
+      <c r="AU87" s="30"/>
+      <c r="AV87" s="30"/>
+      <c r="AW87" s="30"/>
+      <c r="AX87" s="30"/>
+      <c r="AY87" s="30"/>
+      <c r="AZ87" s="30"/>
+      <c r="BC87" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="BD87" s="30"/>
+      <c r="BE87" s="30"/>
+      <c r="BF87" s="30"/>
+      <c r="BG87" s="30"/>
+      <c r="BH87" s="30"/>
+      <c r="BI87" s="30"/>
+      <c r="BJ87" s="30"/>
+      <c r="BK87" s="30"/>
+      <c r="BL87" s="30"/>
+      <c r="BM87" s="30"/>
+      <c r="BN87" s="30"/>
+      <c r="BQ87" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="BR87" s="30"/>
+      <c r="BS87" s="30"/>
+      <c r="BT87" s="30"/>
+      <c r="BU87" s="30"/>
+      <c r="BV87" s="30"/>
+      <c r="BW87" s="30"/>
+      <c r="BX87" s="30"/>
+      <c r="BY87" s="30"/>
+      <c r="BZ87" s="30"/>
+      <c r="CA87" s="30"/>
+      <c r="CB87" s="30"/>
+      <c r="CE87" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="CF87" s="30"/>
+      <c r="CG87" s="30"/>
+      <c r="CH87" s="30"/>
+      <c r="CI87" s="30"/>
+      <c r="CJ87" s="30"/>
+      <c r="CK87" s="30"/>
+      <c r="CL87" s="30"/>
+      <c r="CM87" s="30"/>
+      <c r="CN87" s="30"/>
+      <c r="CO87" s="30"/>
+      <c r="CP87" s="30"/>
+    </row>
+    <row r="88" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA88" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB88" s="34"/>
+      <c r="AC88" s="34"/>
+      <c r="AD88" s="34"/>
+      <c r="AE88" s="34"/>
+      <c r="AF88" s="34"/>
+      <c r="AG88" s="34"/>
+      <c r="AH88" s="34"/>
+      <c r="AI88" s="34"/>
+      <c r="AJ88" s="34"/>
+      <c r="AK88" s="34"/>
+      <c r="AL88" s="34"/>
+      <c r="AO88" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="AP88" s="34"/>
+      <c r="AQ88" s="34"/>
+      <c r="AR88" s="34"/>
+      <c r="AS88" s="34"/>
+      <c r="AT88" s="34"/>
+      <c r="AU88" s="34"/>
+      <c r="AV88" s="34"/>
+      <c r="AW88" s="34"/>
+      <c r="AX88" s="34"/>
+      <c r="AY88" s="34"/>
+      <c r="AZ88" s="34"/>
+      <c r="BC88" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="BD88" s="34"/>
+      <c r="BE88" s="34"/>
+      <c r="BF88" s="34"/>
+      <c r="BG88" s="34"/>
+      <c r="BH88" s="34"/>
+      <c r="BI88" s="34"/>
+      <c r="BJ88" s="34"/>
+      <c r="BK88" s="34"/>
+      <c r="BL88" s="34"/>
+      <c r="BM88" s="34"/>
+      <c r="BN88" s="34"/>
+      <c r="BQ88" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="BR88" s="34"/>
+      <c r="BS88" s="34"/>
+      <c r="BT88" s="34"/>
+      <c r="BU88" s="34"/>
+      <c r="BV88" s="34"/>
+      <c r="BW88" s="34"/>
+      <c r="BX88" s="34"/>
+      <c r="BY88" s="34"/>
+      <c r="BZ88" s="34"/>
+      <c r="CA88" s="34"/>
+      <c r="CB88" s="34"/>
+      <c r="CE88" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="CF88" s="34"/>
+      <c r="CG88" s="34"/>
+      <c r="CH88" s="34"/>
+      <c r="CI88" s="34"/>
+      <c r="CJ88" s="34"/>
+      <c r="CK88" s="34"/>
+      <c r="CL88" s="34"/>
+      <c r="CM88" s="34"/>
+      <c r="CN88" s="34"/>
+      <c r="CO88" s="34"/>
+      <c r="CP88" s="34"/>
+    </row>
+    <row r="89" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA89" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB89" s="34"/>
+      <c r="AC89" s="34"/>
+      <c r="AD89" s="34"/>
+      <c r="AE89" s="34"/>
+      <c r="AF89" s="34"/>
+      <c r="AG89" s="34"/>
+      <c r="AH89" s="34"/>
+      <c r="AI89" s="34"/>
+      <c r="AJ89" s="34"/>
+      <c r="AK89" s="34"/>
+      <c r="AL89" s="34"/>
+      <c r="AO89" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="AP89" s="34"/>
+      <c r="AQ89" s="34"/>
+      <c r="AR89" s="34"/>
+      <c r="AS89" s="34"/>
+      <c r="AT89" s="34"/>
+      <c r="AU89" s="34"/>
+      <c r="AV89" s="34"/>
+      <c r="AW89" s="34"/>
+      <c r="AX89" s="34"/>
+      <c r="AY89" s="34"/>
+      <c r="AZ89" s="34"/>
+      <c r="BC89" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="BD89" s="34"/>
+      <c r="BE89" s="34"/>
+      <c r="BF89" s="34"/>
+      <c r="BG89" s="34"/>
+      <c r="BH89" s="34"/>
+      <c r="BI89" s="34"/>
+      <c r="BJ89" s="34"/>
+      <c r="BK89" s="34"/>
+      <c r="BL89" s="34"/>
+      <c r="BM89" s="34"/>
+      <c r="BN89" s="34"/>
+      <c r="BQ89" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="BR89" s="34"/>
+      <c r="BS89" s="34"/>
+      <c r="BT89" s="34"/>
+      <c r="BU89" s="34"/>
+      <c r="BV89" s="34"/>
+      <c r="BW89" s="34"/>
+      <c r="BX89" s="34"/>
+      <c r="BY89" s="34"/>
+      <c r="BZ89" s="34"/>
+      <c r="CA89" s="34"/>
+      <c r="CB89" s="34"/>
+      <c r="CE89" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="CF89" s="34"/>
+      <c r="CG89" s="34"/>
+      <c r="CH89" s="34"/>
+      <c r="CI89" s="34"/>
+      <c r="CJ89" s="34"/>
+      <c r="CK89" s="34"/>
+      <c r="CL89" s="34"/>
+      <c r="CM89" s="34"/>
+      <c r="CN89" s="34"/>
+      <c r="CO89" s="34"/>
+      <c r="CP89" s="34"/>
+    </row>
+    <row r="90" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA90" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB90" s="30"/>
+      <c r="AC90" s="30"/>
+      <c r="AD90" s="30"/>
+      <c r="AE90" s="30"/>
+      <c r="AF90" s="30"/>
+      <c r="AG90" s="30"/>
+      <c r="AH90" s="30"/>
+      <c r="AI90" s="30"/>
+      <c r="AJ90" s="30"/>
+      <c r="AK90" s="30"/>
+      <c r="AL90" s="30"/>
+      <c r="AO90" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP90" s="30"/>
+      <c r="AQ90" s="30"/>
+      <c r="AR90" s="30"/>
+      <c r="AS90" s="30"/>
+      <c r="AT90" s="30"/>
+      <c r="AU90" s="30"/>
+      <c r="AV90" s="30"/>
+      <c r="AW90" s="30"/>
+      <c r="AX90" s="30"/>
+      <c r="AY90" s="30"/>
+      <c r="AZ90" s="30"/>
+      <c r="BC90" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="BD90" s="30"/>
+      <c r="BE90" s="30"/>
+      <c r="BF90" s="30"/>
+      <c r="BG90" s="30"/>
+      <c r="BH90" s="30"/>
+      <c r="BI90" s="30"/>
+      <c r="BJ90" s="30"/>
+      <c r="BK90" s="30"/>
+      <c r="BL90" s="30"/>
+      <c r="BM90" s="30"/>
+      <c r="BN90" s="30"/>
+      <c r="BQ90" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="BR90" s="30"/>
+      <c r="BS90" s="30"/>
+      <c r="BT90" s="30"/>
+      <c r="BU90" s="30"/>
+      <c r="BV90" s="30"/>
+      <c r="BW90" s="30"/>
+      <c r="BX90" s="30"/>
+      <c r="BY90" s="30"/>
+      <c r="BZ90" s="30"/>
+      <c r="CA90" s="30"/>
+      <c r="CB90" s="30"/>
+      <c r="CE90" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="CF90" s="30"/>
+      <c r="CG90" s="30"/>
+      <c r="CH90" s="30"/>
+      <c r="CI90" s="30"/>
+      <c r="CJ90" s="30"/>
+      <c r="CK90" s="30"/>
+      <c r="CL90" s="30"/>
+      <c r="CM90" s="30"/>
+      <c r="CN90" s="30"/>
+      <c r="CO90" s="30"/>
+      <c r="CP90" s="30"/>
+    </row>
+    <row r="91" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA91" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB91" s="30"/>
+      <c r="AC91" s="30"/>
+      <c r="AD91" s="30"/>
+      <c r="AE91" s="35"/>
+      <c r="AF91" s="30"/>
+      <c r="AG91" s="30"/>
+      <c r="AH91" s="30"/>
+      <c r="AI91" s="30"/>
+      <c r="AJ91" s="30"/>
+      <c r="AK91" s="30"/>
+      <c r="AL91" s="30"/>
+      <c r="AO91" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="AP91" s="30"/>
+      <c r="AQ91" s="30"/>
+      <c r="AR91" s="30"/>
+      <c r="AS91" s="35"/>
+      <c r="AT91" s="30"/>
+      <c r="AU91" s="30"/>
+      <c r="AV91" s="30"/>
+      <c r="AW91" s="30"/>
+      <c r="AX91" s="30"/>
+      <c r="AY91" s="30"/>
+      <c r="AZ91" s="30"/>
+      <c r="BC91" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="BD91" s="30"/>
+      <c r="BE91" s="30"/>
+      <c r="BF91" s="30"/>
+      <c r="BG91" s="35"/>
+      <c r="BH91" s="30"/>
+      <c r="BI91" s="30"/>
+      <c r="BJ91" s="30"/>
+      <c r="BK91" s="30"/>
+      <c r="BL91" s="30"/>
+      <c r="BM91" s="30"/>
+      <c r="BN91" s="30"/>
+      <c r="BQ91" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="BR91" s="30"/>
+      <c r="BS91" s="30"/>
+      <c r="BT91" s="30"/>
+      <c r="BU91" s="35"/>
+      <c r="BV91" s="30"/>
+      <c r="BW91" s="30"/>
+      <c r="BX91" s="30"/>
+      <c r="BY91" s="30"/>
+      <c r="BZ91" s="30"/>
+      <c r="CA91" s="30"/>
+      <c r="CB91" s="30"/>
+      <c r="CE91" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="CF91" s="30"/>
+      <c r="CG91" s="30"/>
+      <c r="CH91" s="30"/>
+      <c r="CI91" s="35"/>
+      <c r="CJ91" s="30"/>
+      <c r="CK91" s="30"/>
+      <c r="CL91" s="30"/>
+      <c r="CM91" s="30"/>
+      <c r="CN91" s="30"/>
+      <c r="CO91" s="30"/>
+      <c r="CP91" s="30"/>
+    </row>
+    <row r="92" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA92" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB92" s="34"/>
+      <c r="AC92" s="34"/>
+      <c r="AD92" s="34"/>
+      <c r="AE92" s="34"/>
+      <c r="AF92" s="34"/>
+      <c r="AG92" s="34"/>
+      <c r="AH92" s="34"/>
+      <c r="AI92" s="34"/>
+      <c r="AJ92" s="34"/>
+      <c r="AK92" s="34"/>
+      <c r="AL92" s="34"/>
+      <c r="AO92" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP92" s="34"/>
+      <c r="AQ92" s="34"/>
+      <c r="AR92" s="34"/>
+      <c r="AS92" s="34"/>
+      <c r="AT92" s="34"/>
+      <c r="AU92" s="34"/>
+      <c r="AV92" s="34"/>
+      <c r="AW92" s="34"/>
+      <c r="AX92" s="34"/>
+      <c r="AY92" s="34"/>
+      <c r="AZ92" s="34"/>
+      <c r="BC92" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="BD92" s="34"/>
+      <c r="BE92" s="34"/>
+      <c r="BF92" s="34"/>
+      <c r="BG92" s="34"/>
+      <c r="BH92" s="34"/>
+      <c r="BI92" s="34"/>
+      <c r="BJ92" s="34"/>
+      <c r="BK92" s="34"/>
+      <c r="BL92" s="34"/>
+      <c r="BM92" s="34"/>
+      <c r="BN92" s="34"/>
+      <c r="BQ92" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="BR92" s="34"/>
+      <c r="BS92" s="34"/>
+      <c r="BT92" s="34"/>
+      <c r="BU92" s="34"/>
+      <c r="BV92" s="34"/>
+      <c r="BW92" s="34"/>
+      <c r="BX92" s="34"/>
+      <c r="BY92" s="34"/>
+      <c r="BZ92" s="34"/>
+      <c r="CA92" s="34"/>
+      <c r="CB92" s="34"/>
+      <c r="CE92" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="CF92" s="34"/>
+      <c r="CG92" s="34"/>
+      <c r="CH92" s="34"/>
+      <c r="CI92" s="34"/>
+      <c r="CJ92" s="34"/>
+      <c r="CK92" s="34"/>
+      <c r="CL92" s="34"/>
+      <c r="CM92" s="34"/>
+      <c r="CN92" s="34"/>
+      <c r="CO92" s="34"/>
+      <c r="CP92" s="34"/>
+    </row>
+    <row r="93" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA93" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB93" s="30"/>
+      <c r="AC93" s="30"/>
+      <c r="AD93" s="30"/>
+      <c r="AE93" s="30"/>
+      <c r="AF93" s="30"/>
+      <c r="AG93" s="30"/>
+      <c r="AH93" s="30"/>
+      <c r="AI93" s="30"/>
+      <c r="AJ93" s="30"/>
+      <c r="AK93" s="30"/>
+      <c r="AL93" s="30"/>
+      <c r="AO93" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP93" s="30"/>
+      <c r="AQ93" s="30"/>
+      <c r="AR93" s="30"/>
+      <c r="AS93" s="30"/>
+      <c r="AT93" s="30"/>
+      <c r="AU93" s="30"/>
+      <c r="AV93" s="30"/>
+      <c r="AW93" s="30"/>
+      <c r="AX93" s="30"/>
+      <c r="AY93" s="30"/>
+      <c r="AZ93" s="30"/>
+      <c r="BC93" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="BD93" s="30"/>
+      <c r="BE93" s="30"/>
+      <c r="BF93" s="30"/>
+      <c r="BG93" s="30"/>
+      <c r="BH93" s="30"/>
+      <c r="BI93" s="30"/>
+      <c r="BJ93" s="30"/>
+      <c r="BK93" s="30"/>
+      <c r="BL93" s="30"/>
+      <c r="BM93" s="30"/>
+      <c r="BN93" s="30"/>
+      <c r="BQ93" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="BR93" s="30"/>
+      <c r="BS93" s="30"/>
+      <c r="BT93" s="30"/>
+      <c r="BU93" s="30"/>
+      <c r="BV93" s="30"/>
+      <c r="BW93" s="30"/>
+      <c r="BX93" s="30"/>
+      <c r="BY93" s="30"/>
+      <c r="BZ93" s="30"/>
+      <c r="CA93" s="30"/>
+      <c r="CB93" s="30"/>
+      <c r="CE93" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="CF93" s="30"/>
+      <c r="CG93" s="30"/>
+      <c r="CH93" s="30"/>
+      <c r="CI93" s="30"/>
+      <c r="CJ93" s="30"/>
+      <c r="CK93" s="30"/>
+      <c r="CL93" s="30"/>
+      <c r="CM93" s="30"/>
+      <c r="CN93" s="30"/>
+      <c r="CO93" s="30"/>
+      <c r="CP93" s="30"/>
+    </row>
+    <row r="94" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA94" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB94" s="30"/>
+      <c r="AC94" s="30"/>
+      <c r="AD94" s="30"/>
+      <c r="AF94" s="30"/>
+      <c r="AG94" s="30"/>
+      <c r="AH94" s="30"/>
+      <c r="AI94" s="30"/>
+      <c r="AJ94" s="30"/>
+      <c r="AK94" s="30"/>
+      <c r="AL94" s="30"/>
+      <c r="AO94" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="AP94" s="30"/>
+      <c r="AQ94" s="30"/>
+      <c r="AR94" s="30"/>
+      <c r="AT94" s="30"/>
+      <c r="AU94" s="30"/>
+      <c r="AV94" s="30"/>
+      <c r="AW94" s="30"/>
+      <c r="AX94" s="30"/>
+      <c r="AY94" s="30"/>
+      <c r="AZ94" s="30"/>
+      <c r="BC94" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="BD94" s="30"/>
+      <c r="BE94" s="30"/>
+      <c r="BF94" s="30"/>
+      <c r="BH94" s="30"/>
+      <c r="BI94" s="30"/>
+      <c r="BJ94" s="30"/>
+      <c r="BK94" s="30"/>
+      <c r="BL94" s="30"/>
+      <c r="BM94" s="30"/>
+      <c r="BN94" s="30"/>
+      <c r="BQ94" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="BR94" s="30"/>
+      <c r="BS94" s="30"/>
+      <c r="BT94" s="30"/>
+      <c r="BV94" s="30"/>
+      <c r="BW94" s="30"/>
+      <c r="BX94" s="30"/>
+      <c r="BY94" s="30"/>
+      <c r="BZ94" s="30"/>
+      <c r="CA94" s="30"/>
+      <c r="CB94" s="30"/>
+      <c r="CE94" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="CF94" s="30"/>
+      <c r="CG94" s="30"/>
+      <c r="CH94" s="30"/>
+      <c r="CJ94" s="30"/>
+      <c r="CK94" s="30"/>
+      <c r="CL94" s="30"/>
+      <c r="CM94" s="30"/>
+      <c r="CN94" s="30"/>
+      <c r="CO94" s="30"/>
+      <c r="CP94" s="30"/>
+    </row>
+    <row r="95" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA95" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB95" s="30"/>
+      <c r="AC95" s="30"/>
+      <c r="AD95" s="30"/>
+      <c r="AE95" s="30"/>
+      <c r="AF95" s="30"/>
+      <c r="AG95" s="30"/>
+      <c r="AH95" s="30"/>
+      <c r="AI95" s="30"/>
+      <c r="AJ95" s="30"/>
+      <c r="AK95" s="30"/>
+      <c r="AL95" s="30"/>
+      <c r="AO95" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP95" s="30"/>
+      <c r="AQ95" s="30"/>
+      <c r="AR95" s="30"/>
+      <c r="AS95" s="30"/>
+      <c r="AT95" s="30"/>
+      <c r="AU95" s="30"/>
+      <c r="AV95" s="30"/>
+      <c r="AW95" s="30"/>
+      <c r="AX95" s="30"/>
+      <c r="AY95" s="30"/>
+      <c r="AZ95" s="30"/>
+      <c r="BC95" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD95" s="30"/>
+      <c r="BE95" s="30"/>
+      <c r="BF95" s="30"/>
+      <c r="BG95" s="30"/>
+      <c r="BH95" s="30"/>
+      <c r="BI95" s="30"/>
+      <c r="BJ95" s="30"/>
+      <c r="BK95" s="30"/>
+      <c r="BL95" s="30"/>
+      <c r="BM95" s="30"/>
+      <c r="BN95" s="30"/>
+      <c r="BQ95" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="BR95" s="30"/>
+      <c r="BS95" s="30"/>
+      <c r="BT95" s="30"/>
+      <c r="BU95" s="30"/>
+      <c r="BV95" s="30"/>
+      <c r="BW95" s="30"/>
+      <c r="BX95" s="30"/>
+      <c r="BY95" s="30"/>
+      <c r="BZ95" s="30"/>
+      <c r="CA95" s="30"/>
+      <c r="CB95" s="30"/>
+      <c r="CE95" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="CF95" s="30"/>
+      <c r="CG95" s="30"/>
+      <c r="CH95" s="30"/>
+      <c r="CI95" s="30"/>
+      <c r="CJ95" s="30"/>
+      <c r="CK95" s="30"/>
+      <c r="CL95" s="30"/>
+      <c r="CM95" s="30"/>
+      <c r="CN95" s="30"/>
+      <c r="CO95" s="30"/>
+      <c r="CP95" s="30"/>
+    </row>
+    <row r="96" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA96" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB96" s="30"/>
+      <c r="AC96" s="30"/>
+      <c r="AD96" s="30"/>
+      <c r="AE96" s="30"/>
+      <c r="AF96" s="30"/>
+      <c r="AG96" s="30"/>
+      <c r="AH96" s="30"/>
+      <c r="AI96" s="30"/>
+      <c r="AJ96" s="30"/>
+      <c r="AK96" s="30"/>
+      <c r="AL96" s="30"/>
+      <c r="AO96" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="AP96" s="30"/>
+      <c r="AQ96" s="30"/>
+      <c r="AR96" s="30"/>
+      <c r="AS96" s="30"/>
+      <c r="AT96" s="30"/>
+      <c r="AU96" s="30"/>
+      <c r="AV96" s="30"/>
+      <c r="AW96" s="30"/>
+      <c r="AX96" s="30"/>
+      <c r="AY96" s="30"/>
+      <c r="AZ96" s="30"/>
+      <c r="BC96" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="BD96" s="30"/>
+      <c r="BE96" s="30"/>
+      <c r="BF96" s="30"/>
+      <c r="BG96" s="30"/>
+      <c r="BH96" s="30"/>
+      <c r="BI96" s="30"/>
+      <c r="BJ96" s="30"/>
+      <c r="BK96" s="30"/>
+      <c r="BL96" s="30"/>
+      <c r="BM96" s="30"/>
+      <c r="BN96" s="30"/>
+      <c r="BQ96" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="BR96" s="30"/>
+      <c r="BS96" s="30"/>
+      <c r="BT96" s="30"/>
+      <c r="BU96" s="30"/>
+      <c r="BV96" s="30"/>
+      <c r="BW96" s="30"/>
+      <c r="BX96" s="30"/>
+      <c r="BY96" s="30"/>
+      <c r="BZ96" s="30"/>
+      <c r="CA96" s="30"/>
+      <c r="CB96" s="30"/>
+      <c r="CE96" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="CF96" s="30"/>
+      <c r="CG96" s="30"/>
+      <c r="CH96" s="30"/>
+      <c r="CI96" s="30"/>
+      <c r="CJ96" s="30"/>
+      <c r="CK96" s="30"/>
+      <c r="CL96" s="30"/>
+      <c r="CM96" s="30"/>
+      <c r="CN96" s="30"/>
+      <c r="CO96" s="30"/>
+      <c r="CP96" s="30"/>
+    </row>
+    <row r="97" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA97" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB97" s="30"/>
+      <c r="AC97" s="30"/>
+      <c r="AD97" s="30"/>
+      <c r="AE97" s="30"/>
+      <c r="AF97" s="30"/>
+      <c r="AG97" s="30"/>
+      <c r="AH97" s="30"/>
+      <c r="AI97" s="30"/>
+      <c r="AJ97" s="30"/>
+      <c r="AK97" s="30"/>
+      <c r="AL97" s="30"/>
+      <c r="AO97" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP97" s="30"/>
+      <c r="AQ97" s="30"/>
+      <c r="AR97" s="30"/>
+      <c r="AS97" s="30"/>
+      <c r="AT97" s="30"/>
+      <c r="AU97" s="30"/>
+      <c r="AV97" s="30"/>
+      <c r="AW97" s="30"/>
+      <c r="AX97" s="30"/>
+      <c r="AY97" s="30"/>
+      <c r="AZ97" s="30"/>
+      <c r="BC97" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="BD97" s="30"/>
+      <c r="BE97" s="30"/>
+      <c r="BF97" s="30"/>
+      <c r="BG97" s="30"/>
+      <c r="BH97" s="30"/>
+      <c r="BI97" s="30"/>
+      <c r="BJ97" s="30"/>
+      <c r="BK97" s="30"/>
+      <c r="BL97" s="30"/>
+      <c r="BM97" s="30"/>
+      <c r="BN97" s="30"/>
+      <c r="BQ97" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="BR97" s="30"/>
+      <c r="BS97" s="30"/>
+      <c r="BT97" s="30"/>
+      <c r="BU97" s="30"/>
+      <c r="BV97" s="30"/>
+      <c r="BW97" s="30"/>
+      <c r="BX97" s="30"/>
+      <c r="BY97" s="30"/>
+      <c r="BZ97" s="30"/>
+      <c r="CA97" s="30"/>
+      <c r="CB97" s="30"/>
+      <c r="CE97" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="CF97" s="30"/>
+      <c r="CG97" s="30"/>
+      <c r="CH97" s="30"/>
+      <c r="CI97" s="30"/>
+      <c r="CJ97" s="30"/>
+      <c r="CK97" s="30"/>
+      <c r="CL97" s="30"/>
+      <c r="CM97" s="30"/>
+      <c r="CN97" s="30"/>
+      <c r="CO97" s="30"/>
+      <c r="CP97" s="30"/>
+    </row>
+    <row r="98" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA98" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB98" s="30"/>
+      <c r="AC98" s="30"/>
+      <c r="AD98" s="30"/>
+      <c r="AE98" s="30"/>
+      <c r="AF98" s="30"/>
+      <c r="AG98" s="30"/>
+      <c r="AH98" s="30"/>
+      <c r="AI98" s="30"/>
+      <c r="AJ98" s="30"/>
+      <c r="AK98" s="30"/>
+      <c r="AL98" s="30"/>
+      <c r="AO98" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP98" s="30"/>
+      <c r="AQ98" s="30"/>
+      <c r="AR98" s="30"/>
+      <c r="AS98" s="30"/>
+      <c r="AT98" s="30"/>
+      <c r="AU98" s="30"/>
+      <c r="AV98" s="30"/>
+      <c r="AW98" s="30"/>
+      <c r="AX98" s="30"/>
+      <c r="AY98" s="30"/>
+      <c r="AZ98" s="30"/>
+      <c r="BC98" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD98" s="30"/>
+      <c r="BE98" s="30"/>
+      <c r="BF98" s="30"/>
+      <c r="BG98" s="30"/>
+      <c r="BH98" s="30"/>
+      <c r="BI98" s="30"/>
+      <c r="BJ98" s="30"/>
+      <c r="BK98" s="30"/>
+      <c r="BL98" s="30"/>
+      <c r="BM98" s="30"/>
+      <c r="BN98" s="30"/>
+      <c r="BQ98" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR98" s="30"/>
+      <c r="BS98" s="30"/>
+      <c r="BT98" s="30"/>
+      <c r="BU98" s="30"/>
+      <c r="BV98" s="30"/>
+      <c r="BW98" s="30"/>
+      <c r="BX98" s="30"/>
+      <c r="BY98" s="30"/>
+      <c r="BZ98" s="30"/>
+      <c r="CA98" s="30"/>
+      <c r="CB98" s="30"/>
+      <c r="CE98" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="CF98" s="30"/>
+      <c r="CG98" s="30"/>
+      <c r="CH98" s="30"/>
+      <c r="CI98" s="30"/>
+      <c r="CJ98" s="30"/>
+      <c r="CK98" s="30"/>
+      <c r="CL98" s="30"/>
+      <c r="CM98" s="30"/>
+      <c r="CN98" s="30"/>
+      <c r="CO98" s="30"/>
+      <c r="CP98" s="30"/>
+    </row>
+    <row r="99" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA99" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB99" s="30"/>
+      <c r="AC99" s="30"/>
+      <c r="AD99" s="30"/>
+      <c r="AE99" s="30"/>
+      <c r="AF99" s="30"/>
+      <c r="AG99" s="30"/>
+      <c r="AH99" s="30"/>
+      <c r="AI99" s="30"/>
+      <c r="AJ99" s="30"/>
+      <c r="AK99" s="30"/>
+      <c r="AL99" s="30"/>
+      <c r="AO99" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP99" s="30"/>
+      <c r="AQ99" s="30"/>
+      <c r="AR99" s="30"/>
+      <c r="AS99" s="30"/>
+      <c r="AT99" s="30"/>
+      <c r="AU99" s="30"/>
+      <c r="AV99" s="30"/>
+      <c r="AW99" s="30"/>
+      <c r="AX99" s="30"/>
+      <c r="AY99" s="30"/>
+      <c r="AZ99" s="30"/>
+      <c r="BC99" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD99" s="30"/>
+      <c r="BE99" s="30"/>
+      <c r="BF99" s="30"/>
+      <c r="BG99" s="30"/>
+      <c r="BH99" s="30"/>
+      <c r="BI99" s="30"/>
+      <c r="BJ99" s="30"/>
+      <c r="BK99" s="30"/>
+      <c r="BL99" s="30"/>
+      <c r="BM99" s="30"/>
+      <c r="BN99" s="30"/>
+      <c r="BQ99" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="BR99" s="30"/>
+      <c r="BS99" s="30"/>
+      <c r="BT99" s="30"/>
+      <c r="BU99" s="30"/>
+      <c r="BV99" s="30"/>
+      <c r="BW99" s="30"/>
+      <c r="BX99" s="30"/>
+      <c r="BY99" s="30"/>
+      <c r="BZ99" s="30"/>
+      <c r="CA99" s="30"/>
+      <c r="CB99" s="30"/>
+      <c r="CE99" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="CF99" s="30"/>
+      <c r="CG99" s="30"/>
+      <c r="CH99" s="30"/>
+      <c r="CI99" s="30"/>
+      <c r="CJ99" s="30"/>
+      <c r="CK99" s="30"/>
+      <c r="CL99" s="30"/>
+      <c r="CM99" s="30"/>
+      <c r="CN99" s="30"/>
+      <c r="CO99" s="30"/>
+      <c r="CP99" s="30"/>
+    </row>
+    <row r="100" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA100" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB100" s="30"/>
+      <c r="AC100" s="30"/>
+      <c r="AD100" s="30"/>
+      <c r="AE100" s="30"/>
+      <c r="AF100" s="30"/>
+      <c r="AG100" s="30"/>
+      <c r="AH100" s="30"/>
+      <c r="AI100" s="30"/>
+      <c r="AJ100" s="30"/>
+      <c r="AK100" s="30"/>
+      <c r="AL100" s="30"/>
+      <c r="AO100" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="AP100" s="30"/>
+      <c r="AQ100" s="30"/>
+      <c r="AR100" s="30"/>
+      <c r="AS100" s="30"/>
+      <c r="AT100" s="30"/>
+      <c r="AU100" s="30"/>
+      <c r="AV100" s="30"/>
+      <c r="AW100" s="30"/>
+      <c r="AX100" s="30"/>
+      <c r="AY100" s="30"/>
+      <c r="AZ100" s="30"/>
+      <c r="BC100" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="BD100" s="30"/>
+      <c r="BE100" s="30"/>
+      <c r="BF100" s="30"/>
+      <c r="BG100" s="30"/>
+      <c r="BH100" s="30"/>
+      <c r="BI100" s="30"/>
+      <c r="BJ100" s="30"/>
+      <c r="BK100" s="30"/>
+      <c r="BL100" s="30"/>
+      <c r="BM100" s="30"/>
+      <c r="BN100" s="30"/>
+      <c r="BQ100" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="BR100" s="30"/>
+      <c r="BS100" s="30"/>
+      <c r="BT100" s="30"/>
+      <c r="BU100" s="30"/>
+      <c r="BV100" s="30"/>
+      <c r="BW100" s="30"/>
+      <c r="BX100" s="30"/>
+      <c r="BY100" s="30"/>
+      <c r="BZ100" s="30"/>
+      <c r="CA100" s="30"/>
+      <c r="CB100" s="30"/>
+      <c r="CE100" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="CF100" s="30"/>
+      <c r="CG100" s="30"/>
+      <c r="CH100" s="30"/>
+      <c r="CI100" s="30"/>
+      <c r="CJ100" s="30"/>
+      <c r="CK100" s="30"/>
+      <c r="CL100" s="30"/>
+      <c r="CM100" s="30"/>
+      <c r="CN100" s="30"/>
+      <c r="CO100" s="30"/>
+      <c r="CP100" s="30"/>
+    </row>
+    <row r="101" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA101" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB101" s="30"/>
+      <c r="AC101" s="30"/>
+      <c r="AD101" s="30"/>
+      <c r="AE101" s="30"/>
+      <c r="AF101" s="30"/>
+      <c r="AG101" s="30"/>
+      <c r="AH101" s="30"/>
+      <c r="AI101" s="30"/>
+      <c r="AJ101" s="30"/>
+      <c r="AK101" s="30"/>
+      <c r="AL101" s="30"/>
+      <c r="AO101" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="AP101" s="30"/>
+      <c r="AQ101" s="30"/>
+      <c r="AR101" s="30"/>
+      <c r="AS101" s="30"/>
+      <c r="AT101" s="30"/>
+      <c r="AU101" s="30"/>
+      <c r="AV101" s="30"/>
+      <c r="AW101" s="30"/>
+      <c r="AX101" s="30"/>
+      <c r="AY101" s="30"/>
+      <c r="AZ101" s="30"/>
+      <c r="BC101" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="BD101" s="30"/>
+      <c r="BE101" s="30"/>
+      <c r="BF101" s="30"/>
+      <c r="BG101" s="30"/>
+      <c r="BH101" s="30"/>
+      <c r="BI101" s="30"/>
+      <c r="BJ101" s="30"/>
+      <c r="BK101" s="30"/>
+      <c r="BL101" s="30"/>
+      <c r="BM101" s="30"/>
+      <c r="BN101" s="30"/>
+      <c r="BQ101" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="BR101" s="30"/>
+      <c r="BS101" s="30"/>
+      <c r="BT101" s="30"/>
+      <c r="BU101" s="30"/>
+      <c r="BV101" s="30"/>
+      <c r="BW101" s="30"/>
+      <c r="BX101" s="30"/>
+      <c r="BY101" s="30"/>
+      <c r="BZ101" s="30"/>
+      <c r="CA101" s="30"/>
+      <c r="CB101" s="30"/>
+      <c r="CE101" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="CF101" s="30"/>
+      <c r="CG101" s="30"/>
+      <c r="CH101" s="30"/>
+      <c r="CI101" s="30"/>
+      <c r="CJ101" s="30"/>
+      <c r="CK101" s="30"/>
+      <c r="CL101" s="30"/>
+      <c r="CM101" s="30"/>
+      <c r="CN101" s="30"/>
+      <c r="CO101" s="30"/>
+      <c r="CP101" s="30"/>
+    </row>
+    <row r="102" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA102" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB102" s="30"/>
+      <c r="AC102" s="30"/>
+      <c r="AD102" s="30"/>
+      <c r="AE102" s="30"/>
+      <c r="AF102" s="30"/>
+      <c r="AG102" s="30"/>
+      <c r="AH102" s="30"/>
+      <c r="AI102" s="30"/>
+      <c r="AJ102" s="30"/>
+      <c r="AK102" s="30"/>
+      <c r="AL102" s="30"/>
+      <c r="AO102" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP102" s="30"/>
+      <c r="AQ102" s="30"/>
+      <c r="AR102" s="30"/>
+      <c r="AS102" s="30"/>
+      <c r="AT102" s="30"/>
+      <c r="AU102" s="30"/>
+      <c r="AV102" s="30"/>
+      <c r="AW102" s="30"/>
+      <c r="AX102" s="30"/>
+      <c r="AY102" s="30"/>
+      <c r="AZ102" s="30"/>
+      <c r="BC102" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="BD102" s="30"/>
+      <c r="BE102" s="30"/>
+      <c r="BF102" s="30"/>
+      <c r="BG102" s="30"/>
+      <c r="BH102" s="30"/>
+      <c r="BI102" s="30"/>
+      <c r="BJ102" s="30"/>
+      <c r="BK102" s="30"/>
+      <c r="BL102" s="30"/>
+      <c r="BM102" s="30"/>
+      <c r="BN102" s="30"/>
+      <c r="BQ102" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="BR102" s="30"/>
+      <c r="BS102" s="30"/>
+      <c r="BT102" s="30"/>
+      <c r="BU102" s="30"/>
+      <c r="BV102" s="30"/>
+      <c r="BW102" s="30"/>
+      <c r="BX102" s="30"/>
+      <c r="BY102" s="30"/>
+      <c r="BZ102" s="30"/>
+      <c r="CA102" s="30"/>
+      <c r="CB102" s="30"/>
+      <c r="CE102" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="CF102" s="30"/>
+      <c r="CG102" s="30"/>
+      <c r="CH102" s="30"/>
+      <c r="CI102" s="30"/>
+      <c r="CJ102" s="30"/>
+      <c r="CK102" s="30"/>
+      <c r="CL102" s="30"/>
+      <c r="CM102" s="30"/>
+      <c r="CN102" s="30"/>
+      <c r="CO102" s="30"/>
+      <c r="CP102" s="30"/>
+    </row>
+    <row r="103" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA103" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB103" s="30"/>
+      <c r="AC103" s="30"/>
+      <c r="AD103" s="30"/>
+      <c r="AE103" s="30"/>
+      <c r="AF103" s="30"/>
+      <c r="AG103" s="30"/>
+      <c r="AH103" s="30"/>
+      <c r="AI103" s="30"/>
+      <c r="AJ103" s="30"/>
+      <c r="AK103" s="30"/>
+      <c r="AL103" s="30"/>
+      <c r="AO103" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="AP103" s="30"/>
+      <c r="AQ103" s="30"/>
+      <c r="AR103" s="30"/>
+      <c r="AS103" s="30"/>
+      <c r="AT103" s="30"/>
+      <c r="AU103" s="30"/>
+      <c r="AV103" s="30"/>
+      <c r="AW103" s="30"/>
+      <c r="AX103" s="30"/>
+      <c r="AY103" s="30"/>
+      <c r="AZ103" s="30"/>
+      <c r="BC103" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="BD103" s="30"/>
+      <c r="BE103" s="30"/>
+      <c r="BF103" s="30"/>
+      <c r="BG103" s="30"/>
+      <c r="BH103" s="30"/>
+      <c r="BI103" s="30"/>
+      <c r="BJ103" s="30"/>
+      <c r="BK103" s="30"/>
+      <c r="BL103" s="30"/>
+      <c r="BM103" s="30"/>
+      <c r="BN103" s="30"/>
+      <c r="BQ103" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="BR103" s="30"/>
+      <c r="BS103" s="30"/>
+      <c r="BT103" s="30"/>
+      <c r="BU103" s="30"/>
+      <c r="BV103" s="30"/>
+      <c r="BW103" s="30"/>
+      <c r="BX103" s="30"/>
+      <c r="BY103" s="30"/>
+      <c r="BZ103" s="30"/>
+      <c r="CA103" s="30"/>
+      <c r="CB103" s="30"/>
+      <c r="CE103" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="CF103" s="30"/>
+      <c r="CG103" s="30"/>
+      <c r="CH103" s="30"/>
+      <c r="CI103" s="30"/>
+      <c r="CJ103" s="30"/>
+      <c r="CK103" s="30"/>
+      <c r="CL103" s="30"/>
+      <c r="CM103" s="30"/>
+      <c r="CN103" s="30"/>
+      <c r="CO103" s="30"/>
+      <c r="CP103" s="30"/>
+    </row>
+    <row r="104" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA104" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB104" s="30"/>
+      <c r="AC104" s="30"/>
+      <c r="AD104" s="30"/>
+      <c r="AE104" s="30"/>
+      <c r="AF104" s="30"/>
+      <c r="AG104" s="30"/>
+      <c r="AH104" s="30"/>
+      <c r="AI104" s="30"/>
+      <c r="AJ104" s="30"/>
+      <c r="AK104" s="30"/>
+      <c r="AL104" s="30"/>
+      <c r="AO104" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP104" s="30"/>
+      <c r="AQ104" s="30"/>
+      <c r="AR104" s="30"/>
+      <c r="AS104" s="30"/>
+      <c r="AT104" s="30"/>
+      <c r="AU104" s="30"/>
+      <c r="AV104" s="30"/>
+      <c r="AW104" s="30"/>
+      <c r="AX104" s="30"/>
+      <c r="AY104" s="30"/>
+      <c r="AZ104" s="30"/>
+      <c r="BC104" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="BD104" s="30"/>
+      <c r="BE104" s="30"/>
+      <c r="BF104" s="30"/>
+      <c r="BG104" s="30"/>
+      <c r="BH104" s="30"/>
+      <c r="BI104" s="30"/>
+      <c r="BJ104" s="30"/>
+      <c r="BK104" s="30"/>
+      <c r="BL104" s="30"/>
+      <c r="BM104" s="30"/>
+      <c r="BN104" s="30"/>
+      <c r="BQ104" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="BR104" s="30"/>
+      <c r="BS104" s="30"/>
+      <c r="BT104" s="30"/>
+      <c r="BU104" s="30"/>
+      <c r="BV104" s="30"/>
+      <c r="BW104" s="30"/>
+      <c r="BX104" s="30"/>
+      <c r="BY104" s="30"/>
+      <c r="BZ104" s="30"/>
+      <c r="CA104" s="30"/>
+      <c r="CB104" s="30"/>
+      <c r="CE104" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="CF104" s="30"/>
+      <c r="CG104" s="30"/>
+      <c r="CH104" s="30"/>
+      <c r="CI104" s="30"/>
+      <c r="CJ104" s="30"/>
+      <c r="CK104" s="30"/>
+      <c r="CL104" s="30"/>
+      <c r="CM104" s="30"/>
+      <c r="CN104" s="30"/>
+      <c r="CO104" s="30"/>
+      <c r="CP104" s="30"/>
+    </row>
+    <row r="105" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA105" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB105" s="30"/>
+      <c r="AC105" s="30"/>
+      <c r="AD105" s="30"/>
+      <c r="AE105" s="30"/>
+      <c r="AF105" s="30"/>
+      <c r="AG105" s="30"/>
+      <c r="AH105" s="30"/>
+      <c r="AI105" s="30"/>
+      <c r="AJ105" s="30"/>
+      <c r="AK105" s="30"/>
+      <c r="AL105" s="30"/>
+      <c r="AO105" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="AP105" s="30"/>
+      <c r="AQ105" s="30"/>
+      <c r="AR105" s="30"/>
+      <c r="AS105" s="30"/>
+      <c r="AT105" s="30"/>
+      <c r="AU105" s="30"/>
+      <c r="AV105" s="30"/>
+      <c r="AW105" s="30"/>
+      <c r="AX105" s="30"/>
+      <c r="AY105" s="30"/>
+      <c r="AZ105" s="30"/>
+      <c r="BC105" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="BD105" s="30"/>
+      <c r="BE105" s="30"/>
+      <c r="BF105" s="30"/>
+      <c r="BG105" s="30"/>
+      <c r="BH105" s="30"/>
+      <c r="BI105" s="30"/>
+      <c r="BJ105" s="30"/>
+      <c r="BK105" s="30"/>
+      <c r="BL105" s="30"/>
+      <c r="BM105" s="30"/>
+      <c r="BN105" s="30"/>
+      <c r="BQ105" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="BR105" s="30"/>
+      <c r="BS105" s="30"/>
+      <c r="BT105" s="30"/>
+      <c r="BU105" s="30"/>
+      <c r="BV105" s="30"/>
+      <c r="BW105" s="30"/>
+      <c r="BX105" s="30"/>
+      <c r="BY105" s="30"/>
+      <c r="BZ105" s="30"/>
+      <c r="CA105" s="30"/>
+      <c r="CB105" s="30"/>
+      <c r="CE105" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="CF105" s="30"/>
+      <c r="CG105" s="30"/>
+      <c r="CH105" s="30"/>
+      <c r="CI105" s="30"/>
+      <c r="CJ105" s="30"/>
+      <c r="CK105" s="30"/>
+      <c r="CL105" s="30"/>
+      <c r="CM105" s="30"/>
+      <c r="CN105" s="30"/>
+      <c r="CO105" s="30"/>
+      <c r="CP105" s="30"/>
+    </row>
+    <row r="106" spans="27:94" x14ac:dyDescent="0.2">
+      <c r="AA106" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB106" s="30"/>
+      <c r="AC106" s="30"/>
+      <c r="AD106" s="30"/>
+      <c r="AE106" s="37"/>
+      <c r="AF106" s="30"/>
+      <c r="AG106" s="30"/>
+      <c r="AH106" s="30"/>
+      <c r="AI106" s="30"/>
+      <c r="AJ106" s="30"/>
+      <c r="AK106" s="30"/>
+      <c r="AL106" s="30"/>
+      <c r="AO106" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="AP106" s="30"/>
+      <c r="AQ106" s="30"/>
+      <c r="AR106" s="30"/>
+      <c r="AS106" s="37"/>
+      <c r="AT106" s="30"/>
+      <c r="AU106" s="30"/>
+      <c r="AV106" s="30"/>
+      <c r="AW106" s="30"/>
+      <c r="AX106" s="30"/>
+      <c r="AY106" s="30"/>
+      <c r="AZ106" s="30"/>
+      <c r="BC106" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="BD106" s="30"/>
+      <c r="BE106" s="30"/>
+      <c r="BF106" s="30"/>
+      <c r="BG106" s="37"/>
+      <c r="BH106" s="30"/>
+      <c r="BI106" s="30"/>
+      <c r="BJ106" s="30"/>
+      <c r="BK106" s="30"/>
+      <c r="BL106" s="30"/>
+      <c r="BM106" s="30"/>
+      <c r="BN106" s="30"/>
+      <c r="BQ106" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="BR106" s="30"/>
+      <c r="BS106" s="30"/>
+      <c r="BT106" s="30"/>
+      <c r="BU106" s="37"/>
+      <c r="BV106" s="30"/>
+      <c r="BW106" s="30"/>
+      <c r="BX106" s="30"/>
+      <c r="BY106" s="30"/>
+      <c r="BZ106" s="30"/>
+      <c r="CA106" s="30"/>
+      <c r="CB106" s="30"/>
+      <c r="CE106" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="CF106" s="30"/>
+      <c r="CG106" s="30"/>
+      <c r="CH106" s="30"/>
+      <c r="CI106" s="37"/>
+      <c r="CJ106" s="30"/>
+      <c r="CK106" s="30"/>
+      <c r="CL106" s="30"/>
+      <c r="CM106" s="30"/>
+      <c r="CN106" s="30"/>
+      <c r="CO106" s="30"/>
+      <c r="CP106" s="30"/>
+    </row>
+    <row r="107" spans="27:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AB107" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC107" s="39"/>
+      <c r="AD107" s="40"/>
+      <c r="AE107" s="39"/>
+      <c r="AF107" s="40"/>
+      <c r="AG107" s="41"/>
+      <c r="AH107" s="42"/>
+      <c r="AI107" s="39"/>
+      <c r="AJ107" s="40"/>
+      <c r="AK107" s="39"/>
+      <c r="AL107" s="40"/>
+      <c r="AP107" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ107" s="39"/>
+      <c r="AR107" s="40"/>
+      <c r="AS107" s="39"/>
+      <c r="AT107" s="40"/>
+      <c r="AU107" s="41"/>
+      <c r="AV107" s="42"/>
+      <c r="AW107" s="39"/>
+      <c r="AX107" s="40"/>
+      <c r="AY107" s="39"/>
+      <c r="AZ107" s="40"/>
+      <c r="BD107" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="BE107" s="39"/>
+      <c r="BF107" s="40"/>
+      <c r="BG107" s="39"/>
+      <c r="BH107" s="40"/>
+      <c r="BI107" s="41"/>
+      <c r="BJ107" s="42"/>
+      <c r="BK107" s="39"/>
+      <c r="BL107" s="40"/>
+      <c r="BM107" s="39"/>
+      <c r="BN107" s="40"/>
+      <c r="BR107" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="BS107" s="39"/>
+      <c r="BT107" s="40"/>
+      <c r="BU107" s="39"/>
+      <c r="BV107" s="40"/>
+      <c r="BW107" s="41"/>
+      <c r="BX107" s="42"/>
+      <c r="BY107" s="39"/>
+      <c r="BZ107" s="40"/>
+      <c r="CA107" s="39"/>
+      <c r="CB107" s="40"/>
+      <c r="CF107" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="CG107" s="39"/>
+      <c r="CH107" s="40"/>
+      <c r="CI107" s="39"/>
+      <c r="CJ107" s="40"/>
+      <c r="CK107" s="41"/>
+      <c r="CL107" s="42"/>
+      <c r="CM107" s="39"/>
+      <c r="CN107" s="40"/>
+      <c r="CO107" s="39"/>
+      <c r="CP107" s="40"/>
     </row>
   </sheetData>
-  <mergeCells count="91">
-    <mergeCell ref="BS35:BT35"/>
-    <mergeCell ref="BU35:BV35"/>
-    <mergeCell ref="BW35:BX35"/>
-    <mergeCell ref="BY35:BZ35"/>
-    <mergeCell ref="CA35:CB35"/>
+  <mergeCells count="289">
+    <mergeCell ref="BE35:BF35"/>
+    <mergeCell ref="BG35:BH35"/>
+    <mergeCell ref="BI35:BJ35"/>
+    <mergeCell ref="BK35:BL35"/>
+    <mergeCell ref="BM35:BN35"/>
+    <mergeCell ref="BQ2:CB2"/>
+    <mergeCell ref="BS3:BT3"/>
+    <mergeCell ref="BU3:BV3"/>
+    <mergeCell ref="BW3:BX3"/>
+    <mergeCell ref="BY3:BZ3"/>
+    <mergeCell ref="CA3:CB3"/>
     <mergeCell ref="BQ5:BQ8"/>
     <mergeCell ref="BQ11:CB11"/>
     <mergeCell ref="BS12:BT12"/>
@@ -11286,17 +16677,17 @@
     <mergeCell ref="BW12:BX12"/>
     <mergeCell ref="BY12:BZ12"/>
     <mergeCell ref="CA12:CB12"/>
-    <mergeCell ref="BQ2:CB2"/>
-    <mergeCell ref="BS3:BT3"/>
-    <mergeCell ref="BU3:BV3"/>
-    <mergeCell ref="BW3:BX3"/>
-    <mergeCell ref="BY3:BZ3"/>
-    <mergeCell ref="CA3:CB3"/>
-    <mergeCell ref="BE35:BF35"/>
-    <mergeCell ref="BG35:BH35"/>
-    <mergeCell ref="BI35:BJ35"/>
-    <mergeCell ref="BK35:BL35"/>
-    <mergeCell ref="BM35:BN35"/>
+    <mergeCell ref="BS35:BT35"/>
+    <mergeCell ref="BU35:BV35"/>
+    <mergeCell ref="BW35:BX35"/>
+    <mergeCell ref="BY35:BZ35"/>
+    <mergeCell ref="CA35:CB35"/>
+    <mergeCell ref="BC2:BN2"/>
+    <mergeCell ref="BE3:BF3"/>
+    <mergeCell ref="BG3:BH3"/>
+    <mergeCell ref="BI3:BJ3"/>
+    <mergeCell ref="BK3:BL3"/>
+    <mergeCell ref="BM3:BN3"/>
     <mergeCell ref="BC5:BC8"/>
     <mergeCell ref="BC11:BN11"/>
     <mergeCell ref="BE12:BF12"/>
@@ -11304,17 +16695,17 @@
     <mergeCell ref="BI12:BJ12"/>
     <mergeCell ref="BK12:BL12"/>
     <mergeCell ref="BM12:BN12"/>
-    <mergeCell ref="BC2:BN2"/>
-    <mergeCell ref="BE3:BF3"/>
-    <mergeCell ref="BG3:BH3"/>
-    <mergeCell ref="BI3:BJ3"/>
-    <mergeCell ref="BK3:BL3"/>
-    <mergeCell ref="BM3:BN3"/>
-    <mergeCell ref="AQ35:AR35"/>
-    <mergeCell ref="AS35:AT35"/>
-    <mergeCell ref="AU35:AV35"/>
-    <mergeCell ref="AW35:AX35"/>
-    <mergeCell ref="AY35:AZ35"/>
+    <mergeCell ref="AC35:AD35"/>
+    <mergeCell ref="AE35:AF35"/>
+    <mergeCell ref="AG35:AH35"/>
+    <mergeCell ref="AI35:AJ35"/>
+    <mergeCell ref="AK35:AL35"/>
+    <mergeCell ref="AO2:AZ2"/>
+    <mergeCell ref="AQ3:AR3"/>
+    <mergeCell ref="AS3:AT3"/>
+    <mergeCell ref="AU3:AV3"/>
+    <mergeCell ref="AW3:AX3"/>
+    <mergeCell ref="AY3:AZ3"/>
     <mergeCell ref="AO5:AO8"/>
     <mergeCell ref="AO11:AZ11"/>
     <mergeCell ref="AQ12:AR12"/>
@@ -11322,36 +16713,11 @@
     <mergeCell ref="AU12:AV12"/>
     <mergeCell ref="AW12:AX12"/>
     <mergeCell ref="AY12:AZ12"/>
-    <mergeCell ref="AO2:AZ2"/>
-    <mergeCell ref="AQ3:AR3"/>
-    <mergeCell ref="AS3:AT3"/>
-    <mergeCell ref="AU3:AV3"/>
-    <mergeCell ref="AW3:AX3"/>
-    <mergeCell ref="AY3:AZ3"/>
-    <mergeCell ref="AC35:AD35"/>
-    <mergeCell ref="AE35:AF35"/>
-    <mergeCell ref="AG35:AH35"/>
-    <mergeCell ref="AI35:AJ35"/>
-    <mergeCell ref="AK35:AL35"/>
-    <mergeCell ref="AA5:AA8"/>
-    <mergeCell ref="AA11:AL11"/>
-    <mergeCell ref="AC12:AD12"/>
-    <mergeCell ref="AE12:AF12"/>
-    <mergeCell ref="AG12:AH12"/>
-    <mergeCell ref="AI12:AJ12"/>
-    <mergeCell ref="AK12:AL12"/>
-    <mergeCell ref="AA2:AL2"/>
-    <mergeCell ref="AC3:AD3"/>
-    <mergeCell ref="AE3:AF3"/>
-    <mergeCell ref="AG3:AH3"/>
-    <mergeCell ref="AI3:AJ3"/>
-    <mergeCell ref="AK3:AL3"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="AQ35:AR35"/>
+    <mergeCell ref="AS35:AT35"/>
+    <mergeCell ref="AU35:AV35"/>
+    <mergeCell ref="AW35:AX35"/>
+    <mergeCell ref="AY35:AZ35"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="B14:M14"/>
@@ -11360,11 +16726,228 @@
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="J15:K15"/>
     <mergeCell ref="L15:M15"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="CE2:CP2"/>
+    <mergeCell ref="CG3:CH3"/>
+    <mergeCell ref="CI3:CJ3"/>
+    <mergeCell ref="CK3:CL3"/>
+    <mergeCell ref="CM3:CN3"/>
+    <mergeCell ref="CO3:CP3"/>
     <mergeCell ref="D38:E38"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="H38:I38"/>
     <mergeCell ref="J38:K38"/>
     <mergeCell ref="L38:M38"/>
+    <mergeCell ref="AA2:AL2"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="AG3:AH3"/>
+    <mergeCell ref="AI3:AJ3"/>
+    <mergeCell ref="AK3:AL3"/>
+    <mergeCell ref="AA5:AA8"/>
+    <mergeCell ref="AA11:AL11"/>
+    <mergeCell ref="AC12:AD12"/>
+    <mergeCell ref="AE12:AF12"/>
+    <mergeCell ref="AG12:AH12"/>
+    <mergeCell ref="AI12:AJ12"/>
+    <mergeCell ref="AK12:AL12"/>
+    <mergeCell ref="CE38:CP38"/>
+    <mergeCell ref="CG35:CH35"/>
+    <mergeCell ref="CI35:CJ35"/>
+    <mergeCell ref="CK35:CL35"/>
+    <mergeCell ref="CM35:CN35"/>
+    <mergeCell ref="CO35:CP35"/>
+    <mergeCell ref="CE5:CE8"/>
+    <mergeCell ref="CE11:CP11"/>
+    <mergeCell ref="CG12:CH12"/>
+    <mergeCell ref="CI12:CJ12"/>
+    <mergeCell ref="CK12:CL12"/>
+    <mergeCell ref="CM12:CN12"/>
+    <mergeCell ref="CO12:CP12"/>
+    <mergeCell ref="AC39:AD39"/>
+    <mergeCell ref="AE39:AF39"/>
+    <mergeCell ref="AG39:AH39"/>
+    <mergeCell ref="AI39:AJ39"/>
+    <mergeCell ref="AK39:AL39"/>
+    <mergeCell ref="AA38:AL38"/>
+    <mergeCell ref="AO38:AZ38"/>
+    <mergeCell ref="BC38:BN38"/>
+    <mergeCell ref="BQ38:CB38"/>
+    <mergeCell ref="BE39:BF39"/>
+    <mergeCell ref="BG39:BH39"/>
+    <mergeCell ref="BI39:BJ39"/>
+    <mergeCell ref="BK39:BL39"/>
+    <mergeCell ref="BM39:BN39"/>
+    <mergeCell ref="AQ39:AR39"/>
+    <mergeCell ref="AS39:AT39"/>
+    <mergeCell ref="AU39:AV39"/>
+    <mergeCell ref="AW39:AX39"/>
+    <mergeCell ref="AY39:AZ39"/>
+    <mergeCell ref="CG39:CH39"/>
+    <mergeCell ref="CI39:CJ39"/>
+    <mergeCell ref="CK39:CL39"/>
+    <mergeCell ref="CM39:CN39"/>
+    <mergeCell ref="CO39:CP39"/>
+    <mergeCell ref="BS39:BT39"/>
+    <mergeCell ref="BU39:BV39"/>
+    <mergeCell ref="BW39:BX39"/>
+    <mergeCell ref="BY39:BZ39"/>
+    <mergeCell ref="CA39:CB39"/>
+    <mergeCell ref="AA47:AL47"/>
+    <mergeCell ref="AO47:AZ47"/>
+    <mergeCell ref="BC47:BN47"/>
+    <mergeCell ref="BQ47:CB47"/>
+    <mergeCell ref="CE47:CP47"/>
+    <mergeCell ref="AA41:AA44"/>
+    <mergeCell ref="AO41:AO44"/>
+    <mergeCell ref="BC41:BC44"/>
+    <mergeCell ref="BQ41:BQ44"/>
+    <mergeCell ref="CE41:CE44"/>
+    <mergeCell ref="CO48:CP48"/>
+    <mergeCell ref="BS48:BT48"/>
+    <mergeCell ref="BU48:BV48"/>
+    <mergeCell ref="BW48:BX48"/>
+    <mergeCell ref="BY48:BZ48"/>
+    <mergeCell ref="CA48:CB48"/>
+    <mergeCell ref="BE48:BF48"/>
+    <mergeCell ref="BG48:BH48"/>
+    <mergeCell ref="BI48:BJ48"/>
+    <mergeCell ref="BK48:BL48"/>
+    <mergeCell ref="BM48:BN48"/>
+    <mergeCell ref="AC71:AD71"/>
+    <mergeCell ref="AE71:AF71"/>
+    <mergeCell ref="AG71:AH71"/>
+    <mergeCell ref="AI71:AJ71"/>
+    <mergeCell ref="AK71:AL71"/>
+    <mergeCell ref="CG48:CH48"/>
+    <mergeCell ref="CI48:CJ48"/>
+    <mergeCell ref="CK48:CL48"/>
+    <mergeCell ref="CM48:CN48"/>
+    <mergeCell ref="AQ48:AR48"/>
+    <mergeCell ref="AS48:AT48"/>
+    <mergeCell ref="AU48:AV48"/>
+    <mergeCell ref="AW48:AX48"/>
+    <mergeCell ref="AY48:AZ48"/>
+    <mergeCell ref="AC48:AD48"/>
+    <mergeCell ref="AE48:AF48"/>
+    <mergeCell ref="AG48:AH48"/>
+    <mergeCell ref="AI48:AJ48"/>
+    <mergeCell ref="AK48:AL48"/>
+    <mergeCell ref="BE71:BF71"/>
+    <mergeCell ref="BG71:BH71"/>
+    <mergeCell ref="BI71:BJ71"/>
+    <mergeCell ref="BK71:BL71"/>
+    <mergeCell ref="BM71:BN71"/>
+    <mergeCell ref="AQ71:AR71"/>
+    <mergeCell ref="AS71:AT71"/>
+    <mergeCell ref="AU71:AV71"/>
+    <mergeCell ref="AW71:AX71"/>
+    <mergeCell ref="AY71:AZ71"/>
+    <mergeCell ref="CE74:CP74"/>
+    <mergeCell ref="CG71:CH71"/>
+    <mergeCell ref="CI71:CJ71"/>
+    <mergeCell ref="CK71:CL71"/>
+    <mergeCell ref="CM71:CN71"/>
+    <mergeCell ref="CO71:CP71"/>
+    <mergeCell ref="BS71:BT71"/>
+    <mergeCell ref="BU71:BV71"/>
+    <mergeCell ref="BW71:BX71"/>
+    <mergeCell ref="BY71:BZ71"/>
+    <mergeCell ref="CA71:CB71"/>
+    <mergeCell ref="AC75:AD75"/>
+    <mergeCell ref="AE75:AF75"/>
+    <mergeCell ref="AG75:AH75"/>
+    <mergeCell ref="AI75:AJ75"/>
+    <mergeCell ref="AK75:AL75"/>
+    <mergeCell ref="AA74:AL74"/>
+    <mergeCell ref="AO74:AZ74"/>
+    <mergeCell ref="BC74:BN74"/>
+    <mergeCell ref="BQ74:CB74"/>
+    <mergeCell ref="BE75:BF75"/>
+    <mergeCell ref="BG75:BH75"/>
+    <mergeCell ref="BI75:BJ75"/>
+    <mergeCell ref="BK75:BL75"/>
+    <mergeCell ref="BM75:BN75"/>
+    <mergeCell ref="AQ75:AR75"/>
+    <mergeCell ref="AS75:AT75"/>
+    <mergeCell ref="AU75:AV75"/>
+    <mergeCell ref="AW75:AX75"/>
+    <mergeCell ref="AY75:AZ75"/>
+    <mergeCell ref="CG75:CH75"/>
+    <mergeCell ref="CI75:CJ75"/>
+    <mergeCell ref="CK75:CL75"/>
+    <mergeCell ref="CM75:CN75"/>
+    <mergeCell ref="CO75:CP75"/>
+    <mergeCell ref="BS75:BT75"/>
+    <mergeCell ref="BU75:BV75"/>
+    <mergeCell ref="BW75:BX75"/>
+    <mergeCell ref="BY75:BZ75"/>
+    <mergeCell ref="CA75:CB75"/>
+    <mergeCell ref="AA83:AL83"/>
+    <mergeCell ref="AO83:AZ83"/>
+    <mergeCell ref="BC83:BN83"/>
+    <mergeCell ref="BQ83:CB83"/>
+    <mergeCell ref="CE83:CP83"/>
+    <mergeCell ref="AA77:AA80"/>
+    <mergeCell ref="AO77:AO80"/>
+    <mergeCell ref="BC77:BC80"/>
+    <mergeCell ref="BQ77:BQ80"/>
+    <mergeCell ref="CE77:CE80"/>
+    <mergeCell ref="CO84:CP84"/>
+    <mergeCell ref="BS84:BT84"/>
+    <mergeCell ref="BU84:BV84"/>
+    <mergeCell ref="BW84:BX84"/>
+    <mergeCell ref="BY84:BZ84"/>
+    <mergeCell ref="CA84:CB84"/>
+    <mergeCell ref="BE84:BF84"/>
+    <mergeCell ref="BG84:BH84"/>
+    <mergeCell ref="BI84:BJ84"/>
+    <mergeCell ref="BK84:BL84"/>
+    <mergeCell ref="BM84:BN84"/>
+    <mergeCell ref="AC107:AD107"/>
+    <mergeCell ref="AE107:AF107"/>
+    <mergeCell ref="AG107:AH107"/>
+    <mergeCell ref="AI107:AJ107"/>
+    <mergeCell ref="AK107:AL107"/>
+    <mergeCell ref="CG84:CH84"/>
+    <mergeCell ref="CI84:CJ84"/>
+    <mergeCell ref="CK84:CL84"/>
+    <mergeCell ref="CM84:CN84"/>
+    <mergeCell ref="AQ84:AR84"/>
+    <mergeCell ref="AS84:AT84"/>
+    <mergeCell ref="AU84:AV84"/>
+    <mergeCell ref="AW84:AX84"/>
+    <mergeCell ref="AY84:AZ84"/>
+    <mergeCell ref="AC84:AD84"/>
+    <mergeCell ref="AE84:AF84"/>
+    <mergeCell ref="AG84:AH84"/>
+    <mergeCell ref="AI84:AJ84"/>
+    <mergeCell ref="AK84:AL84"/>
+    <mergeCell ref="BE107:BF107"/>
+    <mergeCell ref="BG107:BH107"/>
+    <mergeCell ref="BI107:BJ107"/>
+    <mergeCell ref="BK107:BL107"/>
+    <mergeCell ref="BM107:BN107"/>
+    <mergeCell ref="AQ107:AR107"/>
+    <mergeCell ref="AS107:AT107"/>
+    <mergeCell ref="AU107:AV107"/>
+    <mergeCell ref="AW107:AX107"/>
+    <mergeCell ref="AY107:AZ107"/>
+    <mergeCell ref="CG107:CH107"/>
+    <mergeCell ref="CI107:CJ107"/>
+    <mergeCell ref="CK107:CL107"/>
+    <mergeCell ref="CM107:CN107"/>
+    <mergeCell ref="CO107:CP107"/>
+    <mergeCell ref="BS107:BT107"/>
+    <mergeCell ref="BU107:BV107"/>
+    <mergeCell ref="BW107:BX107"/>
+    <mergeCell ref="BY107:BZ107"/>
+    <mergeCell ref="CA107:CB107"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Results_metrics.xlsx
+++ b/Results_metrics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ludovicascaffidi/Desktop/Università/Magistrale/Secondo Anno/Secondo Semestre/Machine Learning for Mathematical Engineering/Progetto/MaskArchitectureAnomaly_CourseProject/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a8875455940b8c0f/Desktop/UNI/MACHINE LEARNING/Progetto/MaskArchitectureAnomaly_CourseProject/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E602311C-DCBC-F649-AD7D-8F8F41C583C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{E602311C-DCBC-F649-AD7D-8F8F41C583C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DEB2989-C1CF-4D72-BB4E-D1E39A7C3C83}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4220" yWindow="620" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -199,7 +199,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -235,6 +235,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Calibri "/>
     </font>
   </fonts>
   <fills count="8">
@@ -698,7 +703,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
@@ -786,6 +791,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1530,6 +1536,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1537,7 +1544,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2299,6 +2305,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2306,7 +2313,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2557,6 +2563,27 @@
                 <c:pt idx="6">
                   <c:v>25.8</c:v>
                 </c:pt>
+                <c:pt idx="7">
+                  <c:v>26.09</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>26.67</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>27.15</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>27.59</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>27.96</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>28.28</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>28.74</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2702,6 +2729,27 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>14.93</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>15.37</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>15.61</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>13.71</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>16.43</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>16.16</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>16.940000000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>29.06</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2984,6 +3032,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2991,7 +3040,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3753,6 +3801,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3760,7 +3809,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4486,6 +4534,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4493,7 +4542,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7436,6 +7484,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -7700,19 +7752,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:CP107"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="3" max="3" width="13.1640625" customWidth="1"/>
-    <col min="28" max="28" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" customWidth="1"/>
+    <col min="3" max="3" width="13.1796875" customWidth="1"/>
+    <col min="28" max="28" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="12.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:94" ht="15" thickBot="1"/>
+    <row r="2" spans="2:94" ht="15" thickBot="1">
       <c r="B2" s="45" t="s">
         <v>18</v>
       </c>
@@ -7798,7 +7850,7 @@
       <c r="CO2" s="51"/>
       <c r="CP2" s="52"/>
     </row>
-    <row r="3" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:94" ht="15" thickBot="1">
       <c r="B3" s="1"/>
       <c r="C3" s="5"/>
       <c r="D3" s="43" t="s">
@@ -7942,7 +7994,7 @@
       </c>
       <c r="CP3" s="44"/>
     </row>
-    <row r="4" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:94" ht="15" thickBot="1">
       <c r="B4" s="6" t="s">
         <v>0</v>
       </c>
@@ -8160,7 +8212,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:94" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:94" ht="15" thickTop="1">
       <c r="B5" s="53" t="s">
         <v>9</v>
       </c>
@@ -8278,7 +8330,7 @@
       <c r="CO5" s="19"/>
       <c r="CP5" s="20"/>
     </row>
-    <row r="6" spans="2:94" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:94">
       <c r="B6" s="49"/>
       <c r="C6" s="9" t="s">
         <v>11</v>
@@ -8384,7 +8436,7 @@
       <c r="CO6" s="15"/>
       <c r="CP6" s="16"/>
     </row>
-    <row r="7" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:94" ht="15" thickBot="1">
       <c r="B7" s="54"/>
       <c r="C7" s="11" t="s">
         <v>12</v>
@@ -8490,7 +8542,7 @@
       <c r="CO7" s="15"/>
       <c r="CP7" s="16"/>
     </row>
-    <row r="8" spans="2:94" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:94" ht="15.5" thickTop="1" thickBot="1">
       <c r="B8" s="48" t="s">
         <v>13</v>
       </c>
@@ -8598,7 +8650,7 @@
       <c r="CO8" s="21"/>
       <c r="CP8" s="22"/>
     </row>
-    <row r="9" spans="2:94" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:94">
       <c r="B9" s="49"/>
       <c r="C9" s="9" t="s">
         <v>11</v>
@@ -8634,7 +8686,7 @@
         <v>19.09</v>
       </c>
     </row>
-    <row r="10" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:94" ht="15" thickBot="1">
       <c r="B10" s="49"/>
       <c r="C10" s="9" t="s">
         <v>12</v>
@@ -8670,7 +8722,7 @@
         <v>18.829999999999998</v>
       </c>
     </row>
-    <row r="11" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:94" ht="15" thickBot="1">
       <c r="B11" s="50"/>
       <c r="C11" s="10" t="s">
         <v>14</v>
@@ -8776,7 +8828,7 @@
       <c r="CO11" s="46"/>
       <c r="CP11" s="47"/>
     </row>
-    <row r="12" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:94" ht="15" thickBot="1">
       <c r="AA12" s="24"/>
       <c r="AB12" s="5" t="s">
         <v>53</v>
@@ -8898,7 +8950,7 @@
       </c>
       <c r="CP12" s="44"/>
     </row>
-    <row r="13" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:94" ht="15" thickBot="1">
       <c r="AA13" s="25" t="s">
         <v>16</v>
       </c>
@@ -9080,7 +9132,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:94" ht="15" thickBot="1">
       <c r="B14" s="45" t="s">
         <v>19</v>
       </c>
@@ -9166,7 +9218,7 @@
       <c r="CO14" s="30"/>
       <c r="CP14" s="30"/>
     </row>
-    <row r="15" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:94" ht="15" thickBot="1">
       <c r="B15" s="24"/>
       <c r="C15" s="4"/>
       <c r="D15" s="43" t="s">
@@ -9260,7 +9312,7 @@
       <c r="CO15" s="30"/>
       <c r="CP15" s="30"/>
     </row>
-    <row r="16" spans="2:94" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:94">
       <c r="B16" s="25" t="s">
         <v>16</v>
       </c>
@@ -9368,7 +9420,7 @@
       <c r="CO16" s="34"/>
       <c r="CP16" s="34"/>
     </row>
-    <row r="17" spans="2:94" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:94">
       <c r="B17" s="29" t="s">
         <v>24</v>
       </c>
@@ -9476,7 +9528,7 @@
       <c r="CO17" s="34"/>
       <c r="CP17" s="34"/>
     </row>
-    <row r="18" spans="2:94" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:94">
       <c r="B18" s="29" t="s">
         <v>45</v>
       </c>
@@ -9582,7 +9634,7 @@
       <c r="CO18" s="30"/>
       <c r="CP18" s="30"/>
     </row>
-    <row r="19" spans="2:94" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:94">
       <c r="B19" s="29" t="s">
         <v>20</v>
       </c>
@@ -9688,7 +9740,7 @@
       <c r="CO19" s="30"/>
       <c r="CP19" s="30"/>
     </row>
-    <row r="20" spans="2:94" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:94">
       <c r="B20" s="29" t="s">
         <v>29</v>
       </c>
@@ -9794,7 +9846,7 @@
       <c r="CO20" s="34"/>
       <c r="CP20" s="34"/>
     </row>
-    <row r="21" spans="2:94" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:94">
       <c r="B21" s="29" t="s">
         <v>25</v>
       </c>
@@ -9900,7 +9952,7 @@
       <c r="CO21" s="30"/>
       <c r="CP21" s="30"/>
     </row>
-    <row r="22" spans="2:94" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:94">
       <c r="B22" s="29" t="s">
         <v>21</v>
       </c>
@@ -10001,7 +10053,7 @@
       <c r="CO22" s="30"/>
       <c r="CP22" s="30"/>
     </row>
-    <row r="23" spans="2:94" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:94">
       <c r="B23" s="29" t="s">
         <v>30</v>
       </c>
@@ -10107,7 +10159,7 @@
       <c r="CO23" s="30"/>
       <c r="CP23" s="30"/>
     </row>
-    <row r="24" spans="2:94" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:94">
       <c r="B24" s="29" t="s">
         <v>26</v>
       </c>
@@ -10124,8 +10176,12 @@
       <c r="G24" s="30">
         <v>0.68</v>
       </c>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
+      <c r="H24" s="55">
+        <v>26.09</v>
+      </c>
+      <c r="I24" s="30">
+        <v>15.37</v>
+      </c>
       <c r="J24" s="30">
         <v>54.66</v>
       </c>
@@ -10209,7 +10265,7 @@
       <c r="CO24" s="30"/>
       <c r="CP24" s="30"/>
     </row>
-    <row r="25" spans="2:94" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:94">
       <c r="B25" s="29" t="s">
         <v>22</v>
       </c>
@@ -10226,8 +10282,12 @@
       <c r="G25" s="30">
         <v>100</v>
       </c>
-      <c r="H25" s="30"/>
-      <c r="I25" s="30"/>
+      <c r="H25" s="30">
+        <v>26.67</v>
+      </c>
+      <c r="I25" s="30">
+        <v>15.61</v>
+      </c>
       <c r="J25" s="30">
         <v>54.68</v>
       </c>
@@ -10312,7 +10372,7 @@
       <c r="CO25" s="30"/>
       <c r="CP25" s="30"/>
     </row>
-    <row r="26" spans="2:94" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:94">
       <c r="B26" s="29" t="s">
         <v>23</v>
       </c>
@@ -10329,8 +10389,12 @@
       <c r="G26" s="30">
         <v>100</v>
       </c>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
+      <c r="H26" s="30">
+        <v>27.15</v>
+      </c>
+      <c r="I26" s="30">
+        <v>13.71</v>
+      </c>
       <c r="J26" s="30">
         <v>54.32</v>
       </c>
@@ -10414,7 +10478,7 @@
       <c r="CO26" s="30"/>
       <c r="CP26" s="30"/>
     </row>
-    <row r="27" spans="2:94" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:94">
       <c r="B27" s="29" t="s">
         <v>31</v>
       </c>
@@ -10431,8 +10495,12 @@
       <c r="G27" s="30">
         <v>100</v>
       </c>
-      <c r="H27" s="30"/>
-      <c r="I27" s="30"/>
+      <c r="H27" s="30">
+        <v>27.59</v>
+      </c>
+      <c r="I27" s="30">
+        <v>16.43</v>
+      </c>
       <c r="J27" s="30">
         <v>53.61</v>
       </c>
@@ -10516,7 +10584,7 @@
       <c r="CO27" s="30"/>
       <c r="CP27" s="30"/>
     </row>
-    <row r="28" spans="2:94" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:94">
       <c r="B28" s="29" t="s">
         <v>40</v>
       </c>
@@ -10533,8 +10601,12 @@
       <c r="G28" s="30">
         <v>100</v>
       </c>
-      <c r="H28" s="30"/>
-      <c r="I28" s="30"/>
+      <c r="H28" s="30">
+        <v>27.96</v>
+      </c>
+      <c r="I28" s="30">
+        <v>16.16</v>
+      </c>
       <c r="J28" s="30">
         <v>53.44</v>
       </c>
@@ -10618,7 +10690,7 @@
       <c r="CO28" s="30"/>
       <c r="CP28" s="30"/>
     </row>
-    <row r="29" spans="2:94" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:94">
       <c r="B29" s="29" t="s">
         <v>27</v>
       </c>
@@ -10635,8 +10707,12 @@
       <c r="G29" s="30">
         <v>100</v>
       </c>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
+      <c r="H29" s="30">
+        <v>28.28</v>
+      </c>
+      <c r="I29" s="30">
+        <v>16.940000000000001</v>
+      </c>
       <c r="J29" s="30">
         <v>53.61</v>
       </c>
@@ -10720,7 +10796,7 @@
       <c r="CO29" s="30"/>
       <c r="CP29" s="30"/>
     </row>
-    <row r="30" spans="2:94" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:94">
       <c r="B30" s="29" t="s">
         <v>32</v>
       </c>
@@ -10737,8 +10813,12 @@
       <c r="G30" s="30">
         <v>100</v>
       </c>
-      <c r="H30" s="30"/>
-      <c r="I30" s="30"/>
+      <c r="H30" s="30">
+        <v>28.74</v>
+      </c>
+      <c r="I30" s="30">
+        <v>29.06</v>
+      </c>
       <c r="J30" s="30">
         <v>54.17</v>
       </c>
@@ -10822,7 +10902,7 @@
       <c r="CO30" s="30"/>
       <c r="CP30" s="30"/>
     </row>
-    <row r="31" spans="2:94" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:94">
       <c r="B31" s="29" t="s">
         <v>28</v>
       </c>
@@ -10924,7 +11004,7 @@
       <c r="CO31" s="30"/>
       <c r="CP31" s="30"/>
     </row>
-    <row r="32" spans="2:94" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:94">
       <c r="B32" s="29" t="s">
         <v>33</v>
       </c>
@@ -11026,7 +11106,7 @@
       <c r="CO32" s="30"/>
       <c r="CP32" s="30"/>
     </row>
-    <row r="33" spans="2:94" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:94">
       <c r="B33" s="29" t="s">
         <v>34</v>
       </c>
@@ -11128,7 +11208,7 @@
       <c r="CO33" s="30"/>
       <c r="CP33" s="30"/>
     </row>
-    <row r="34" spans="2:94" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:94">
       <c r="B34" s="29" t="s">
         <v>35</v>
       </c>
@@ -11230,7 +11310,7 @@
       <c r="CO34" s="30"/>
       <c r="CP34" s="30"/>
     </row>
-    <row r="35" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:94" ht="15" thickBot="1">
       <c r="B35" s="29" t="s">
         <v>36</v>
       </c>
@@ -11327,7 +11407,7 @@
       <c r="CO35" s="39"/>
       <c r="CP35" s="40"/>
     </row>
-    <row r="36" spans="2:94" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:94">
       <c r="B36" s="29" t="s">
         <v>37</v>
       </c>
@@ -11359,7 +11439,7 @@
         <v>13.42</v>
       </c>
     </row>
-    <row r="37" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:94" ht="15" thickBot="1">
       <c r="B37" s="29" t="s">
         <v>38</v>
       </c>
@@ -11391,7 +11471,7 @@
         <v>13.38</v>
       </c>
     </row>
-    <row r="38" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:94" ht="15" thickBot="1">
       <c r="C38" s="23" t="s">
         <v>17</v>
       </c>
@@ -11478,7 +11558,7 @@
       <c r="CO38" s="51"/>
       <c r="CP38" s="52"/>
     </row>
-    <row r="39" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:94" ht="15" thickBot="1">
       <c r="AA39" s="1"/>
       <c r="AB39" s="5" t="s">
         <v>54</v>
@@ -11600,7 +11680,7 @@
       </c>
       <c r="CP39" s="44"/>
     </row>
-    <row r="40" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:94" ht="15" thickBot="1">
       <c r="AA40" s="6" t="s">
         <v>0</v>
       </c>
@@ -11782,7 +11862,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="2:94" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:94" ht="15" thickTop="1">
       <c r="AA41" s="48" t="s">
         <v>13</v>
       </c>
@@ -11864,7 +11944,7 @@
       <c r="CO41" s="19"/>
       <c r="CP41" s="20"/>
     </row>
-    <row r="42" spans="2:94" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:94">
       <c r="AA42" s="49"/>
       <c r="AB42" s="9" t="s">
         <v>11</v>
@@ -11936,7 +12016,7 @@
       <c r="CO42" s="15"/>
       <c r="CP42" s="16"/>
     </row>
-    <row r="43" spans="2:94" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:94">
       <c r="AA43" s="49"/>
       <c r="AB43" s="9" t="s">
         <v>12</v>
@@ -12008,7 +12088,7 @@
       <c r="CO43" s="15"/>
       <c r="CP43" s="16"/>
     </row>
-    <row r="44" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:94" ht="15" thickBot="1">
       <c r="AA44" s="50"/>
       <c r="AB44" s="10" t="s">
         <v>14</v>
@@ -12080,8 +12160,8 @@
       <c r="CO44" s="21"/>
       <c r="CP44" s="22"/>
     </row>
-    <row r="46" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:94" ht="15" thickBot="1"/>
+    <row r="47" spans="2:94" ht="15" thickBot="1">
       <c r="AA47" s="45" t="s">
         <v>47</v>
       </c>
@@ -12153,7 +12233,7 @@
       <c r="CO47" s="46"/>
       <c r="CP47" s="47"/>
     </row>
-    <row r="48" spans="2:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:94" ht="15" thickBot="1">
       <c r="AA48" s="24"/>
       <c r="AB48" s="5" t="s">
         <v>54</v>
@@ -12275,7 +12355,7 @@
       </c>
       <c r="CP48" s="44"/>
     </row>
-    <row r="49" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="49" spans="27:94">
       <c r="AA49" s="25" t="s">
         <v>16</v>
       </c>
@@ -12457,7 +12537,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="50" spans="27:94">
       <c r="AA50" s="29" t="s">
         <v>24</v>
       </c>
@@ -12529,7 +12609,7 @@
       <c r="CO50" s="30"/>
       <c r="CP50" s="30"/>
     </row>
-    <row r="51" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="51" spans="27:94">
       <c r="AA51" s="29" t="s">
         <v>39</v>
       </c>
@@ -12601,7 +12681,7 @@
       <c r="CO51" s="30"/>
       <c r="CP51" s="30"/>
     </row>
-    <row r="52" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="52" spans="27:94">
       <c r="AA52" s="29" t="s">
         <v>20</v>
       </c>
@@ -12673,7 +12753,7 @@
       <c r="CO52" s="34"/>
       <c r="CP52" s="34"/>
     </row>
-    <row r="53" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="53" spans="27:94">
       <c r="AA53" s="29" t="s">
         <v>29</v>
       </c>
@@ -12745,7 +12825,7 @@
       <c r="CO53" s="34"/>
       <c r="CP53" s="34"/>
     </row>
-    <row r="54" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="54" spans="27:94">
       <c r="AA54" s="29" t="s">
         <v>25</v>
       </c>
@@ -12817,7 +12897,7 @@
       <c r="CO54" s="30"/>
       <c r="CP54" s="30"/>
     </row>
-    <row r="55" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="55" spans="27:94">
       <c r="AA55" s="29" t="s">
         <v>21</v>
       </c>
@@ -12889,7 +12969,7 @@
       <c r="CO55" s="30"/>
       <c r="CP55" s="30"/>
     </row>
-    <row r="56" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="56" spans="27:94">
       <c r="AA56" s="29" t="s">
         <v>30</v>
       </c>
@@ -12961,7 +13041,7 @@
       <c r="CO56" s="34"/>
       <c r="CP56" s="34"/>
     </row>
-    <row r="57" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="57" spans="27:94">
       <c r="AA57" s="29" t="s">
         <v>26</v>
       </c>
@@ -13033,7 +13113,7 @@
       <c r="CO57" s="30"/>
       <c r="CP57" s="30"/>
     </row>
-    <row r="58" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="58" spans="27:94">
       <c r="AA58" s="29" t="s">
         <v>22</v>
       </c>
@@ -13100,7 +13180,7 @@
       <c r="CO58" s="30"/>
       <c r="CP58" s="30"/>
     </row>
-    <row r="59" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="59" spans="27:94">
       <c r="AA59" s="29" t="s">
         <v>23</v>
       </c>
@@ -13172,7 +13252,7 @@
       <c r="CO59" s="30"/>
       <c r="CP59" s="30"/>
     </row>
-    <row r="60" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="60" spans="27:94">
       <c r="AA60" s="29" t="s">
         <v>31</v>
       </c>
@@ -13244,7 +13324,7 @@
       <c r="CO60" s="30"/>
       <c r="CP60" s="30"/>
     </row>
-    <row r="61" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="61" spans="27:94">
       <c r="AA61" s="29" t="s">
         <v>40</v>
       </c>
@@ -13316,7 +13396,7 @@
       <c r="CO61" s="30"/>
       <c r="CP61" s="30"/>
     </row>
-    <row r="62" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="62" spans="27:94">
       <c r="AA62" s="29" t="s">
         <v>27</v>
       </c>
@@ -13388,7 +13468,7 @@
       <c r="CO62" s="30"/>
       <c r="CP62" s="30"/>
     </row>
-    <row r="63" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="63" spans="27:94">
       <c r="AA63" s="29" t="s">
         <v>32</v>
       </c>
@@ -13460,7 +13540,7 @@
       <c r="CO63" s="30"/>
       <c r="CP63" s="30"/>
     </row>
-    <row r="64" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="64" spans="27:94">
       <c r="AA64" s="29" t="s">
         <v>28</v>
       </c>
@@ -13532,7 +13612,7 @@
       <c r="CO64" s="30"/>
       <c r="CP64" s="30"/>
     </row>
-    <row r="65" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="65" spans="27:94">
       <c r="AA65" s="29" t="s">
         <v>33</v>
       </c>
@@ -13604,7 +13684,7 @@
       <c r="CO65" s="30"/>
       <c r="CP65" s="30"/>
     </row>
-    <row r="66" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="66" spans="27:94">
       <c r="AA66" s="29" t="s">
         <v>34</v>
       </c>
@@ -13676,7 +13756,7 @@
       <c r="CO66" s="30"/>
       <c r="CP66" s="30"/>
     </row>
-    <row r="67" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="67" spans="27:94">
       <c r="AA67" s="29" t="s">
         <v>35</v>
       </c>
@@ -13748,7 +13828,7 @@
       <c r="CO67" s="30"/>
       <c r="CP67" s="30"/>
     </row>
-    <row r="68" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="68" spans="27:94">
       <c r="AA68" s="29" t="s">
         <v>36</v>
       </c>
@@ -13820,7 +13900,7 @@
       <c r="CO68" s="30"/>
       <c r="CP68" s="30"/>
     </row>
-    <row r="69" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="69" spans="27:94">
       <c r="AA69" s="29" t="s">
         <v>37</v>
       </c>
@@ -13892,7 +13972,7 @@
       <c r="CO69" s="30"/>
       <c r="CP69" s="30"/>
     </row>
-    <row r="70" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="70" spans="27:94">
       <c r="AA70" s="29" t="s">
         <v>38</v>
       </c>
@@ -13964,7 +14044,7 @@
       <c r="CO70" s="30"/>
       <c r="CP70" s="30"/>
     </row>
-    <row r="71" spans="27:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="27:94" ht="15" thickBot="1">
       <c r="AB71" s="23" t="s">
         <v>17</v>
       </c>
@@ -14031,8 +14111,8 @@
       <c r="CO71" s="39"/>
       <c r="CP71" s="40"/>
     </row>
-    <row r="73" spans="27:94" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="27:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="27:94" ht="15" thickBot="1"/>
+    <row r="74" spans="27:94" ht="15" thickBot="1">
       <c r="AA74" s="45" t="s">
         <v>46</v>
       </c>
@@ -14104,7 +14184,7 @@
       <c r="CO74" s="51"/>
       <c r="CP74" s="52"/>
     </row>
-    <row r="75" spans="27:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="27:94" ht="15" thickBot="1">
       <c r="AA75" s="1"/>
       <c r="AB75" s="5" t="s">
         <v>55</v>
@@ -14226,7 +14306,7 @@
       </c>
       <c r="CP75" s="44"/>
     </row>
-    <row r="76" spans="27:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="27:94" ht="15" thickBot="1">
       <c r="AA76" s="6" t="s">
         <v>0</v>
       </c>
@@ -14408,7 +14488,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="27:94" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="27:94" ht="15" thickTop="1">
       <c r="AA77" s="48" t="s">
         <v>13</v>
       </c>
@@ -14490,7 +14570,7 @@
       <c r="CO77" s="19"/>
       <c r="CP77" s="20"/>
     </row>
-    <row r="78" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="78" spans="27:94">
       <c r="AA78" s="49"/>
       <c r="AB78" s="9" t="s">
         <v>11</v>
@@ -14562,7 +14642,7 @@
       <c r="CO78" s="15"/>
       <c r="CP78" s="16"/>
     </row>
-    <row r="79" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="79" spans="27:94">
       <c r="AA79" s="49"/>
       <c r="AB79" s="9" t="s">
         <v>12</v>
@@ -14634,7 +14714,7 @@
       <c r="CO79" s="15"/>
       <c r="CP79" s="16"/>
     </row>
-    <row r="80" spans="27:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="27:94" ht="15" thickBot="1">
       <c r="AA80" s="50"/>
       <c r="AB80" s="10" t="s">
         <v>14</v>
@@ -14706,8 +14786,8 @@
       <c r="CO80" s="21"/>
       <c r="CP80" s="22"/>
     </row>
-    <row r="82" spans="27:94" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="27:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="27:94" ht="15" thickBot="1"/>
+    <row r="83" spans="27:94" ht="15" thickBot="1">
       <c r="AA83" s="45" t="s">
         <v>47</v>
       </c>
@@ -14779,7 +14859,7 @@
       <c r="CO83" s="46"/>
       <c r="CP83" s="47"/>
     </row>
-    <row r="84" spans="27:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="27:94" ht="15" thickBot="1">
       <c r="AA84" s="24"/>
       <c r="AB84" s="5" t="s">
         <v>55</v>
@@ -14901,7 +14981,7 @@
       </c>
       <c r="CP84" s="44"/>
     </row>
-    <row r="85" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="85" spans="27:94">
       <c r="AA85" s="25" t="s">
         <v>16</v>
       </c>
@@ -15083,7 +15163,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="86" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="86" spans="27:94">
       <c r="AA86" s="29" t="s">
         <v>24</v>
       </c>
@@ -15155,7 +15235,7 @@
       <c r="CO86" s="30"/>
       <c r="CP86" s="30"/>
     </row>
-    <row r="87" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="87" spans="27:94">
       <c r="AA87" s="29" t="s">
         <v>39</v>
       </c>
@@ -15227,7 +15307,7 @@
       <c r="CO87" s="30"/>
       <c r="CP87" s="30"/>
     </row>
-    <row r="88" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="88" spans="27:94">
       <c r="AA88" s="29" t="s">
         <v>20</v>
       </c>
@@ -15299,7 +15379,7 @@
       <c r="CO88" s="34"/>
       <c r="CP88" s="34"/>
     </row>
-    <row r="89" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="89" spans="27:94">
       <c r="AA89" s="29" t="s">
         <v>29</v>
       </c>
@@ -15371,7 +15451,7 @@
       <c r="CO89" s="34"/>
       <c r="CP89" s="34"/>
     </row>
-    <row r="90" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="90" spans="27:94">
       <c r="AA90" s="29" t="s">
         <v>25</v>
       </c>
@@ -15443,7 +15523,7 @@
       <c r="CO90" s="30"/>
       <c r="CP90" s="30"/>
     </row>
-    <row r="91" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="91" spans="27:94">
       <c r="AA91" s="29" t="s">
         <v>21</v>
       </c>
@@ -15515,7 +15595,7 @@
       <c r="CO91" s="30"/>
       <c r="CP91" s="30"/>
     </row>
-    <row r="92" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="92" spans="27:94">
       <c r="AA92" s="29" t="s">
         <v>30</v>
       </c>
@@ -15587,7 +15667,7 @@
       <c r="CO92" s="34"/>
       <c r="CP92" s="34"/>
     </row>
-    <row r="93" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="93" spans="27:94">
       <c r="AA93" s="29" t="s">
         <v>26</v>
       </c>
@@ -15659,7 +15739,7 @@
       <c r="CO93" s="30"/>
       <c r="CP93" s="30"/>
     </row>
-    <row r="94" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="94" spans="27:94">
       <c r="AA94" s="29" t="s">
         <v>22</v>
       </c>
@@ -15726,7 +15806,7 @@
       <c r="CO94" s="30"/>
       <c r="CP94" s="30"/>
     </row>
-    <row r="95" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="95" spans="27:94">
       <c r="AA95" s="29" t="s">
         <v>23</v>
       </c>
@@ -15798,7 +15878,7 @@
       <c r="CO95" s="30"/>
       <c r="CP95" s="30"/>
     </row>
-    <row r="96" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="96" spans="27:94">
       <c r="AA96" s="29" t="s">
         <v>31</v>
       </c>
@@ -15870,7 +15950,7 @@
       <c r="CO96" s="30"/>
       <c r="CP96" s="30"/>
     </row>
-    <row r="97" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="97" spans="27:94">
       <c r="AA97" s="29" t="s">
         <v>40</v>
       </c>
@@ -15942,7 +16022,7 @@
       <c r="CO97" s="30"/>
       <c r="CP97" s="30"/>
     </row>
-    <row r="98" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="98" spans="27:94">
       <c r="AA98" s="29" t="s">
         <v>27</v>
       </c>
@@ -16014,7 +16094,7 @@
       <c r="CO98" s="30"/>
       <c r="CP98" s="30"/>
     </row>
-    <row r="99" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="99" spans="27:94">
       <c r="AA99" s="29" t="s">
         <v>32</v>
       </c>
@@ -16086,7 +16166,7 @@
       <c r="CO99" s="30"/>
       <c r="CP99" s="30"/>
     </row>
-    <row r="100" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="100" spans="27:94">
       <c r="AA100" s="29" t="s">
         <v>28</v>
       </c>
@@ -16158,7 +16238,7 @@
       <c r="CO100" s="30"/>
       <c r="CP100" s="30"/>
     </row>
-    <row r="101" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="101" spans="27:94">
       <c r="AA101" s="29" t="s">
         <v>33</v>
       </c>
@@ -16230,7 +16310,7 @@
       <c r="CO101" s="30"/>
       <c r="CP101" s="30"/>
     </row>
-    <row r="102" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="102" spans="27:94">
       <c r="AA102" s="29" t="s">
         <v>34</v>
       </c>
@@ -16302,7 +16382,7 @@
       <c r="CO102" s="30"/>
       <c r="CP102" s="30"/>
     </row>
-    <row r="103" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="103" spans="27:94">
       <c r="AA103" s="29" t="s">
         <v>35</v>
       </c>
@@ -16374,7 +16454,7 @@
       <c r="CO103" s="30"/>
       <c r="CP103" s="30"/>
     </row>
-    <row r="104" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="104" spans="27:94">
       <c r="AA104" s="29" t="s">
         <v>36</v>
       </c>
@@ -16446,7 +16526,7 @@
       <c r="CO104" s="30"/>
       <c r="CP104" s="30"/>
     </row>
-    <row r="105" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="105" spans="27:94">
       <c r="AA105" s="29" t="s">
         <v>37</v>
       </c>
@@ -16518,7 +16598,7 @@
       <c r="CO105" s="30"/>
       <c r="CP105" s="30"/>
     </row>
-    <row r="106" spans="27:94" x14ac:dyDescent="0.2">
+    <row r="106" spans="27:94">
       <c r="AA106" s="29" t="s">
         <v>38</v>
       </c>
@@ -16590,7 +16670,7 @@
       <c r="CO106" s="30"/>
       <c r="CP106" s="30"/>
     </row>
-    <row r="107" spans="27:94" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="27:94" ht="15" thickBot="1">
       <c r="AB107" s="23" t="s">
         <v>17</v>
       </c>
@@ -16933,6 +17013,12 @@
     <mergeCell ref="BI107:BJ107"/>
     <mergeCell ref="BK107:BL107"/>
     <mergeCell ref="BM107:BN107"/>
+    <mergeCell ref="CO107:CP107"/>
+    <mergeCell ref="BS107:BT107"/>
+    <mergeCell ref="BU107:BV107"/>
+    <mergeCell ref="BW107:BX107"/>
+    <mergeCell ref="BY107:BZ107"/>
+    <mergeCell ref="CA107:CB107"/>
     <mergeCell ref="AQ107:AR107"/>
     <mergeCell ref="AS107:AT107"/>
     <mergeCell ref="AU107:AV107"/>
@@ -16942,12 +17028,6 @@
     <mergeCell ref="CI107:CJ107"/>
     <mergeCell ref="CK107:CL107"/>
     <mergeCell ref="CM107:CN107"/>
-    <mergeCell ref="CO107:CP107"/>
-    <mergeCell ref="BS107:BT107"/>
-    <mergeCell ref="BU107:BV107"/>
-    <mergeCell ref="BW107:BX107"/>
-    <mergeCell ref="BY107:BZ107"/>
-    <mergeCell ref="CA107:CB107"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Results_metrics.xlsx
+++ b/Results_metrics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a8875455940b8c0f/Desktop/UNI/MACHINE LEARNING/Progetto/MaskArchitectureAnomaly_CourseProject/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{E602311C-DCBC-F649-AD7D-8F8F41C583C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DEB2989-C1CF-4D72-BB4E-D1E39A7C3C83}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:1_{E602311C-DCBC-F649-AD7D-8F8F41C583C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EBE5BF3-B6C8-43B3-B470-1E5D71C6A754}"/>
   <bookViews>
-    <workbookView xWindow="4220" yWindow="620" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -743,6 +743,7 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -755,19 +756,19 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -779,10 +780,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -791,7 +792,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -2584,6 +2584,24 @@
                 <c:pt idx="13">
                   <c:v>28.74</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>28.98</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>29.01</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>29.03</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>29.05</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>29.05</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>29.06</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2750,6 +2768,24 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>29.06</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>59.98</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>60.44</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>60.69</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>60.86</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>60.91</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>61.01</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7765,234 +7801,234 @@
   <sheetData>
     <row r="1" spans="2:94" ht="15" thickBot="1"/>
     <row r="2" spans="2:94" ht="15" thickBot="1">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="52"/>
-      <c r="AA2" s="45" t="s">
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="46"/>
+      <c r="AA2" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="51"/>
-      <c r="AE2" s="51"/>
-      <c r="AF2" s="51"/>
-      <c r="AG2" s="51"/>
-      <c r="AH2" s="51"/>
-      <c r="AI2" s="51"/>
-      <c r="AJ2" s="51"/>
-      <c r="AK2" s="51"/>
-      <c r="AL2" s="52"/>
-      <c r="AO2" s="45" t="s">
+      <c r="AB2" s="45"/>
+      <c r="AC2" s="45"/>
+      <c r="AD2" s="45"/>
+      <c r="AE2" s="45"/>
+      <c r="AF2" s="45"/>
+      <c r="AG2" s="45"/>
+      <c r="AH2" s="45"/>
+      <c r="AI2" s="45"/>
+      <c r="AJ2" s="45"/>
+      <c r="AK2" s="45"/>
+      <c r="AL2" s="46"/>
+      <c r="AO2" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="AP2" s="51"/>
-      <c r="AQ2" s="51"/>
-      <c r="AR2" s="51"/>
-      <c r="AS2" s="51"/>
-      <c r="AT2" s="51"/>
-      <c r="AU2" s="51"/>
-      <c r="AV2" s="51"/>
-      <c r="AW2" s="51"/>
-      <c r="AX2" s="51"/>
-      <c r="AY2" s="51"/>
-      <c r="AZ2" s="52"/>
-      <c r="BC2" s="45" t="s">
+      <c r="AP2" s="45"/>
+      <c r="AQ2" s="45"/>
+      <c r="AR2" s="45"/>
+      <c r="AS2" s="45"/>
+      <c r="AT2" s="45"/>
+      <c r="AU2" s="45"/>
+      <c r="AV2" s="45"/>
+      <c r="AW2" s="45"/>
+      <c r="AX2" s="45"/>
+      <c r="AY2" s="45"/>
+      <c r="AZ2" s="46"/>
+      <c r="BC2" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="BD2" s="51"/>
-      <c r="BE2" s="51"/>
-      <c r="BF2" s="51"/>
-      <c r="BG2" s="51"/>
-      <c r="BH2" s="51"/>
-      <c r="BI2" s="51"/>
-      <c r="BJ2" s="51"/>
-      <c r="BK2" s="51"/>
-      <c r="BL2" s="51"/>
-      <c r="BM2" s="51"/>
-      <c r="BN2" s="52"/>
-      <c r="BQ2" s="45" t="s">
+      <c r="BD2" s="45"/>
+      <c r="BE2" s="45"/>
+      <c r="BF2" s="45"/>
+      <c r="BG2" s="45"/>
+      <c r="BH2" s="45"/>
+      <c r="BI2" s="45"/>
+      <c r="BJ2" s="45"/>
+      <c r="BK2" s="45"/>
+      <c r="BL2" s="45"/>
+      <c r="BM2" s="45"/>
+      <c r="BN2" s="46"/>
+      <c r="BQ2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="BR2" s="51"/>
-      <c r="BS2" s="51"/>
-      <c r="BT2" s="51"/>
-      <c r="BU2" s="51"/>
-      <c r="BV2" s="51"/>
-      <c r="BW2" s="51"/>
-      <c r="BX2" s="51"/>
-      <c r="BY2" s="51"/>
-      <c r="BZ2" s="51"/>
-      <c r="CA2" s="51"/>
-      <c r="CB2" s="52"/>
-      <c r="CE2" s="45" t="s">
+      <c r="BR2" s="45"/>
+      <c r="BS2" s="45"/>
+      <c r="BT2" s="45"/>
+      <c r="BU2" s="45"/>
+      <c r="BV2" s="45"/>
+      <c r="BW2" s="45"/>
+      <c r="BX2" s="45"/>
+      <c r="BY2" s="45"/>
+      <c r="BZ2" s="45"/>
+      <c r="CA2" s="45"/>
+      <c r="CB2" s="46"/>
+      <c r="CE2" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="CF2" s="51"/>
-      <c r="CG2" s="51"/>
-      <c r="CH2" s="51"/>
-      <c r="CI2" s="51"/>
-      <c r="CJ2" s="51"/>
-      <c r="CK2" s="51"/>
-      <c r="CL2" s="51"/>
-      <c r="CM2" s="51"/>
-      <c r="CN2" s="51"/>
-      <c r="CO2" s="51"/>
-      <c r="CP2" s="52"/>
+      <c r="CF2" s="45"/>
+      <c r="CG2" s="45"/>
+      <c r="CH2" s="45"/>
+      <c r="CI2" s="45"/>
+      <c r="CJ2" s="45"/>
+      <c r="CK2" s="45"/>
+      <c r="CL2" s="45"/>
+      <c r="CM2" s="45"/>
+      <c r="CN2" s="45"/>
+      <c r="CO2" s="45"/>
+      <c r="CP2" s="46"/>
     </row>
     <row r="3" spans="2:94" ht="15" thickBot="1">
       <c r="B3" s="1"/>
       <c r="C3" s="5"/>
-      <c r="D3" s="43" t="s">
+      <c r="D3" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="44"/>
-      <c r="F3" s="43" t="s">
+      <c r="E3" s="48"/>
+      <c r="F3" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="44"/>
-      <c r="H3" s="43" t="s">
+      <c r="G3" s="48"/>
+      <c r="H3" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="44"/>
-      <c r="J3" s="43" t="s">
+      <c r="I3" s="48"/>
+      <c r="J3" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="44"/>
-      <c r="L3" s="43" t="s">
+      <c r="K3" s="48"/>
+      <c r="L3" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="44"/>
+      <c r="M3" s="48"/>
       <c r="AA3" s="1"/>
       <c r="AB3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AC3" s="43" t="s">
+      <c r="AC3" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AD3" s="44"/>
-      <c r="AE3" s="43" t="s">
+      <c r="AD3" s="48"/>
+      <c r="AE3" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="AF3" s="44"/>
-      <c r="AG3" s="43" t="s">
+      <c r="AF3" s="48"/>
+      <c r="AG3" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="AH3" s="44"/>
-      <c r="AI3" s="43" t="s">
+      <c r="AH3" s="48"/>
+      <c r="AI3" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="AJ3" s="44"/>
-      <c r="AK3" s="43" t="s">
+      <c r="AJ3" s="48"/>
+      <c r="AK3" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="44"/>
+      <c r="AL3" s="48"/>
       <c r="AO3" s="1"/>
       <c r="AP3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AQ3" s="43" t="s">
+      <c r="AQ3" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AR3" s="44"/>
-      <c r="AS3" s="43" t="s">
+      <c r="AR3" s="48"/>
+      <c r="AS3" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="AT3" s="44"/>
-      <c r="AU3" s="43" t="s">
+      <c r="AT3" s="48"/>
+      <c r="AU3" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="AV3" s="44"/>
-      <c r="AW3" s="43" t="s">
+      <c r="AV3" s="48"/>
+      <c r="AW3" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="AX3" s="44"/>
-      <c r="AY3" s="43" t="s">
+      <c r="AX3" s="48"/>
+      <c r="AY3" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="AZ3" s="44"/>
+      <c r="AZ3" s="48"/>
       <c r="BC3" s="1"/>
       <c r="BD3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="BE3" s="43" t="s">
+      <c r="BE3" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="BF3" s="44"/>
-      <c r="BG3" s="43" t="s">
+      <c r="BF3" s="48"/>
+      <c r="BG3" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="BH3" s="44"/>
-      <c r="BI3" s="43" t="s">
+      <c r="BH3" s="48"/>
+      <c r="BI3" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="BJ3" s="44"/>
-      <c r="BK3" s="43" t="s">
+      <c r="BJ3" s="48"/>
+      <c r="BK3" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="BL3" s="44"/>
-      <c r="BM3" s="43" t="s">
+      <c r="BL3" s="48"/>
+      <c r="BM3" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="BN3" s="44"/>
+      <c r="BN3" s="48"/>
       <c r="BQ3" s="1"/>
       <c r="BR3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="BS3" s="43" t="s">
+      <c r="BS3" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="BT3" s="44"/>
-      <c r="BU3" s="43" t="s">
+      <c r="BT3" s="48"/>
+      <c r="BU3" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="BV3" s="44"/>
-      <c r="BW3" s="43" t="s">
+      <c r="BV3" s="48"/>
+      <c r="BW3" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="BX3" s="44"/>
-      <c r="BY3" s="43" t="s">
+      <c r="BX3" s="48"/>
+      <c r="BY3" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="BZ3" s="44"/>
-      <c r="CA3" s="43" t="s">
+      <c r="BZ3" s="48"/>
+      <c r="CA3" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="CB3" s="44"/>
+      <c r="CB3" s="48"/>
       <c r="CE3" s="1"/>
       <c r="CF3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="CG3" s="43" t="s">
+      <c r="CG3" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="CH3" s="44"/>
-      <c r="CI3" s="43" t="s">
+      <c r="CH3" s="48"/>
+      <c r="CI3" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="CJ3" s="44"/>
-      <c r="CK3" s="43" t="s">
+      <c r="CJ3" s="48"/>
+      <c r="CK3" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="CL3" s="44"/>
-      <c r="CM3" s="43" t="s">
+      <c r="CL3" s="48"/>
+      <c r="CM3" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="CN3" s="44"/>
-      <c r="CO3" s="43" t="s">
+      <c r="CN3" s="48"/>
+      <c r="CO3" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="CP3" s="44"/>
+      <c r="CP3" s="48"/>
     </row>
     <row r="4" spans="2:94" ht="15" thickBot="1">
       <c r="B4" s="6" t="s">
@@ -8213,7 +8249,7 @@
       </c>
     </row>
     <row r="5" spans="2:94" ht="15" thickTop="1">
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="54" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -8249,7 +8285,7 @@
       <c r="M5" s="14">
         <v>82.58</v>
       </c>
-      <c r="AA5" s="48" t="s">
+      <c r="AA5" s="49" t="s">
         <v>13</v>
       </c>
       <c r="AB5" s="12" t="s">
@@ -8265,7 +8301,7 @@
       <c r="AJ5" s="20"/>
       <c r="AK5" s="19"/>
       <c r="AL5" s="20"/>
-      <c r="AO5" s="48" t="s">
+      <c r="AO5" s="49" t="s">
         <v>13</v>
       </c>
       <c r="AP5" s="12" t="s">
@@ -8281,7 +8317,7 @@
       <c r="AX5" s="20"/>
       <c r="AY5" s="19"/>
       <c r="AZ5" s="20"/>
-      <c r="BC5" s="48" t="s">
+      <c r="BC5" s="49" t="s">
         <v>13</v>
       </c>
       <c r="BD5" s="12" t="s">
@@ -8297,7 +8333,7 @@
       <c r="BL5" s="20"/>
       <c r="BM5" s="19"/>
       <c r="BN5" s="20"/>
-      <c r="BQ5" s="48" t="s">
+      <c r="BQ5" s="49" t="s">
         <v>13</v>
       </c>
       <c r="BR5" s="12" t="s">
@@ -8313,7 +8349,7 @@
       <c r="BZ5" s="20"/>
       <c r="CA5" s="19"/>
       <c r="CB5" s="20"/>
-      <c r="CE5" s="48" t="s">
+      <c r="CE5" s="49" t="s">
         <v>13</v>
       </c>
       <c r="CF5" s="12" t="s">
@@ -8331,7 +8367,7 @@
       <c r="CP5" s="20"/>
     </row>
     <row r="6" spans="2:94">
-      <c r="B6" s="49"/>
+      <c r="B6" s="50"/>
       <c r="C6" s="9" t="s">
         <v>11</v>
       </c>
@@ -8365,7 +8401,7 @@
       <c r="M6" s="32">
         <v>73.25</v>
       </c>
-      <c r="AA6" s="49"/>
+      <c r="AA6" s="50"/>
       <c r="AB6" s="9" t="s">
         <v>11</v>
       </c>
@@ -8379,7 +8415,7 @@
       <c r="AJ6" s="16"/>
       <c r="AK6" s="15"/>
       <c r="AL6" s="16"/>
-      <c r="AO6" s="49"/>
+      <c r="AO6" s="50"/>
       <c r="AP6" s="9" t="s">
         <v>11</v>
       </c>
@@ -8393,7 +8429,7 @@
       <c r="AX6" s="16"/>
       <c r="AY6" s="15"/>
       <c r="AZ6" s="16"/>
-      <c r="BC6" s="49"/>
+      <c r="BC6" s="50"/>
       <c r="BD6" s="9" t="s">
         <v>11</v>
       </c>
@@ -8407,7 +8443,7 @@
       <c r="BL6" s="16"/>
       <c r="BM6" s="15"/>
       <c r="BN6" s="16"/>
-      <c r="BQ6" s="49"/>
+      <c r="BQ6" s="50"/>
       <c r="BR6" s="9" t="s">
         <v>11</v>
       </c>
@@ -8421,7 +8457,7 @@
       <c r="BZ6" s="16"/>
       <c r="CA6" s="15"/>
       <c r="CB6" s="16"/>
-      <c r="CE6" s="49"/>
+      <c r="CE6" s="50"/>
       <c r="CF6" s="9" t="s">
         <v>11</v>
       </c>
@@ -8437,7 +8473,7 @@
       <c r="CP6" s="16"/>
     </row>
     <row r="7" spans="2:94" ht="15" thickBot="1">
-      <c r="B7" s="54"/>
+      <c r="B7" s="55"/>
       <c r="C7" s="11" t="s">
         <v>12</v>
       </c>
@@ -8471,7 +8507,7 @@
       <c r="M7" s="18">
         <v>82.75</v>
       </c>
-      <c r="AA7" s="49"/>
+      <c r="AA7" s="50"/>
       <c r="AB7" s="9" t="s">
         <v>12</v>
       </c>
@@ -8485,7 +8521,7 @@
       <c r="AJ7" s="16"/>
       <c r="AK7" s="15"/>
       <c r="AL7" s="16"/>
-      <c r="AO7" s="49"/>
+      <c r="AO7" s="50"/>
       <c r="AP7" s="9" t="s">
         <v>12</v>
       </c>
@@ -8499,7 +8535,7 @@
       <c r="AX7" s="16"/>
       <c r="AY7" s="15"/>
       <c r="AZ7" s="16"/>
-      <c r="BC7" s="49"/>
+      <c r="BC7" s="50"/>
       <c r="BD7" s="9" t="s">
         <v>12</v>
       </c>
@@ -8513,7 +8549,7 @@
       <c r="BL7" s="16"/>
       <c r="BM7" s="15"/>
       <c r="BN7" s="16"/>
-      <c r="BQ7" s="49"/>
+      <c r="BQ7" s="50"/>
       <c r="BR7" s="9" t="s">
         <v>12</v>
       </c>
@@ -8527,7 +8563,7 @@
       <c r="BZ7" s="16"/>
       <c r="CA7" s="15"/>
       <c r="CB7" s="16"/>
-      <c r="CE7" s="49"/>
+      <c r="CE7" s="50"/>
       <c r="CF7" s="9" t="s">
         <v>12</v>
       </c>
@@ -8543,7 +8579,7 @@
       <c r="CP7" s="16"/>
     </row>
     <row r="8" spans="2:94" ht="15.5" thickTop="1" thickBot="1">
-      <c r="B8" s="48" t="s">
+      <c r="B8" s="49" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="12" t="s">
@@ -8562,10 +8598,10 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="H8" s="19">
-        <v>27.2</v>
+        <v>25.42</v>
       </c>
       <c r="I8" s="20">
-        <v>14.65</v>
+        <v>14.9</v>
       </c>
       <c r="J8" s="19">
         <v>54.32</v>
@@ -8579,7 +8615,7 @@
       <c r="M8" s="20">
         <v>19.34</v>
       </c>
-      <c r="AA8" s="50"/>
+      <c r="AA8" s="51"/>
       <c r="AB8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8593,7 +8629,7 @@
       <c r="AJ8" s="22"/>
       <c r="AK8" s="21"/>
       <c r="AL8" s="22"/>
-      <c r="AO8" s="50"/>
+      <c r="AO8" s="51"/>
       <c r="AP8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8607,7 +8643,7 @@
       <c r="AX8" s="22"/>
       <c r="AY8" s="21"/>
       <c r="AZ8" s="22"/>
-      <c r="BC8" s="50"/>
+      <c r="BC8" s="51"/>
       <c r="BD8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8621,7 +8657,7 @@
       <c r="BL8" s="22"/>
       <c r="BM8" s="21"/>
       <c r="BN8" s="22"/>
-      <c r="BQ8" s="50"/>
+      <c r="BQ8" s="51"/>
       <c r="BR8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8635,7 +8671,7 @@
       <c r="BZ8" s="22"/>
       <c r="CA8" s="21"/>
       <c r="CB8" s="22"/>
-      <c r="CE8" s="50"/>
+      <c r="CE8" s="51"/>
       <c r="CF8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8651,7 +8687,7 @@
       <c r="CP8" s="22"/>
     </row>
     <row r="9" spans="2:94">
-      <c r="B9" s="49"/>
+      <c r="B9" s="50"/>
       <c r="C9" s="9" t="s">
         <v>11</v>
       </c>
@@ -8687,7 +8723,7 @@
       </c>
     </row>
     <row r="10" spans="2:94" ht="15" thickBot="1">
-      <c r="B10" s="49"/>
+      <c r="B10" s="50"/>
       <c r="C10" s="9" t="s">
         <v>12</v>
       </c>
@@ -8723,7 +8759,7 @@
       </c>
     </row>
     <row r="11" spans="2:94" ht="15" thickBot="1">
-      <c r="B11" s="50"/>
+      <c r="B11" s="51"/>
       <c r="C11" s="10" t="s">
         <v>14</v>
       </c>
@@ -8757,198 +8793,198 @@
       <c r="M11" s="22">
         <v>17.579999999999998</v>
       </c>
-      <c r="AA11" s="45" t="s">
+      <c r="AA11" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="AB11" s="46"/>
-      <c r="AC11" s="46"/>
-      <c r="AD11" s="46"/>
-      <c r="AE11" s="46"/>
-      <c r="AF11" s="46"/>
-      <c r="AG11" s="46"/>
-      <c r="AH11" s="46"/>
-      <c r="AI11" s="46"/>
-      <c r="AJ11" s="46"/>
-      <c r="AK11" s="46"/>
-      <c r="AL11" s="47"/>
-      <c r="AO11" s="45" t="s">
+      <c r="AB11" s="52"/>
+      <c r="AC11" s="52"/>
+      <c r="AD11" s="52"/>
+      <c r="AE11" s="52"/>
+      <c r="AF11" s="52"/>
+      <c r="AG11" s="52"/>
+      <c r="AH11" s="52"/>
+      <c r="AI11" s="52"/>
+      <c r="AJ11" s="52"/>
+      <c r="AK11" s="52"/>
+      <c r="AL11" s="53"/>
+      <c r="AO11" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="AP11" s="46"/>
-      <c r="AQ11" s="46"/>
-      <c r="AR11" s="46"/>
-      <c r="AS11" s="46"/>
-      <c r="AT11" s="46"/>
-      <c r="AU11" s="46"/>
-      <c r="AV11" s="46"/>
-      <c r="AW11" s="46"/>
-      <c r="AX11" s="46"/>
-      <c r="AY11" s="46"/>
-      <c r="AZ11" s="47"/>
-      <c r="BC11" s="45" t="s">
+      <c r="AP11" s="52"/>
+      <c r="AQ11" s="52"/>
+      <c r="AR11" s="52"/>
+      <c r="AS11" s="52"/>
+      <c r="AT11" s="52"/>
+      <c r="AU11" s="52"/>
+      <c r="AV11" s="52"/>
+      <c r="AW11" s="52"/>
+      <c r="AX11" s="52"/>
+      <c r="AY11" s="52"/>
+      <c r="AZ11" s="53"/>
+      <c r="BC11" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="BD11" s="46"/>
-      <c r="BE11" s="46"/>
-      <c r="BF11" s="46"/>
-      <c r="BG11" s="46"/>
-      <c r="BH11" s="46"/>
-      <c r="BI11" s="46"/>
-      <c r="BJ11" s="46"/>
-      <c r="BK11" s="46"/>
-      <c r="BL11" s="46"/>
-      <c r="BM11" s="46"/>
-      <c r="BN11" s="47"/>
-      <c r="BQ11" s="45" t="s">
+      <c r="BD11" s="52"/>
+      <c r="BE11" s="52"/>
+      <c r="BF11" s="52"/>
+      <c r="BG11" s="52"/>
+      <c r="BH11" s="52"/>
+      <c r="BI11" s="52"/>
+      <c r="BJ11" s="52"/>
+      <c r="BK11" s="52"/>
+      <c r="BL11" s="52"/>
+      <c r="BM11" s="52"/>
+      <c r="BN11" s="53"/>
+      <c r="BQ11" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="BR11" s="46"/>
-      <c r="BS11" s="46"/>
-      <c r="BT11" s="46"/>
-      <c r="BU11" s="46"/>
-      <c r="BV11" s="46"/>
-      <c r="BW11" s="46"/>
-      <c r="BX11" s="46"/>
-      <c r="BY11" s="46"/>
-      <c r="BZ11" s="46"/>
-      <c r="CA11" s="46"/>
-      <c r="CB11" s="47"/>
-      <c r="CE11" s="45" t="s">
+      <c r="BR11" s="52"/>
+      <c r="BS11" s="52"/>
+      <c r="BT11" s="52"/>
+      <c r="BU11" s="52"/>
+      <c r="BV11" s="52"/>
+      <c r="BW11" s="52"/>
+      <c r="BX11" s="52"/>
+      <c r="BY11" s="52"/>
+      <c r="BZ11" s="52"/>
+      <c r="CA11" s="52"/>
+      <c r="CB11" s="53"/>
+      <c r="CE11" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="CF11" s="46"/>
-      <c r="CG11" s="46"/>
-      <c r="CH11" s="46"/>
-      <c r="CI11" s="46"/>
-      <c r="CJ11" s="46"/>
-      <c r="CK11" s="46"/>
-      <c r="CL11" s="46"/>
-      <c r="CM11" s="46"/>
-      <c r="CN11" s="46"/>
-      <c r="CO11" s="46"/>
-      <c r="CP11" s="47"/>
+      <c r="CF11" s="52"/>
+      <c r="CG11" s="52"/>
+      <c r="CH11" s="52"/>
+      <c r="CI11" s="52"/>
+      <c r="CJ11" s="52"/>
+      <c r="CK11" s="52"/>
+      <c r="CL11" s="52"/>
+      <c r="CM11" s="52"/>
+      <c r="CN11" s="52"/>
+      <c r="CO11" s="52"/>
+      <c r="CP11" s="53"/>
     </row>
     <row r="12" spans="2:94" ht="15" thickBot="1">
       <c r="AA12" s="24"/>
       <c r="AB12" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AC12" s="43" t="s">
+      <c r="AC12" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AD12" s="44"/>
-      <c r="AE12" s="43" t="s">
+      <c r="AD12" s="48"/>
+      <c r="AE12" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="AF12" s="44"/>
-      <c r="AG12" s="43" t="s">
+      <c r="AF12" s="48"/>
+      <c r="AG12" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="AH12" s="44"/>
-      <c r="AI12" s="43" t="s">
+      <c r="AH12" s="48"/>
+      <c r="AI12" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="AJ12" s="44"/>
-      <c r="AK12" s="43" t="s">
+      <c r="AJ12" s="48"/>
+      <c r="AK12" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="AL12" s="44"/>
+      <c r="AL12" s="48"/>
       <c r="AO12" s="24"/>
       <c r="AP12" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AQ12" s="43" t="s">
+      <c r="AQ12" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AR12" s="44"/>
-      <c r="AS12" s="43" t="s">
+      <c r="AR12" s="48"/>
+      <c r="AS12" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="AT12" s="44"/>
-      <c r="AU12" s="43" t="s">
+      <c r="AT12" s="48"/>
+      <c r="AU12" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="AV12" s="44"/>
-      <c r="AW12" s="43" t="s">
+      <c r="AV12" s="48"/>
+      <c r="AW12" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="AX12" s="44"/>
-      <c r="AY12" s="43" t="s">
+      <c r="AX12" s="48"/>
+      <c r="AY12" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="AZ12" s="44"/>
+      <c r="AZ12" s="48"/>
       <c r="BC12" s="24"/>
       <c r="BD12" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="BE12" s="43" t="s">
+      <c r="BE12" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="BF12" s="44"/>
-      <c r="BG12" s="43" t="s">
+      <c r="BF12" s="48"/>
+      <c r="BG12" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="BH12" s="44"/>
-      <c r="BI12" s="43" t="s">
+      <c r="BH12" s="48"/>
+      <c r="BI12" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="BJ12" s="44"/>
-      <c r="BK12" s="43" t="s">
+      <c r="BJ12" s="48"/>
+      <c r="BK12" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="BL12" s="44"/>
-      <c r="BM12" s="43" t="s">
+      <c r="BL12" s="48"/>
+      <c r="BM12" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="BN12" s="44"/>
+      <c r="BN12" s="48"/>
       <c r="BQ12" s="24"/>
       <c r="BR12" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="BS12" s="43" t="s">
+      <c r="BS12" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="BT12" s="44"/>
-      <c r="BU12" s="43" t="s">
+      <c r="BT12" s="48"/>
+      <c r="BU12" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="BV12" s="44"/>
-      <c r="BW12" s="43" t="s">
+      <c r="BV12" s="48"/>
+      <c r="BW12" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="BX12" s="44"/>
-      <c r="BY12" s="43" t="s">
+      <c r="BX12" s="48"/>
+      <c r="BY12" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="BZ12" s="44"/>
-      <c r="CA12" s="43" t="s">
+      <c r="BZ12" s="48"/>
+      <c r="CA12" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="CB12" s="44"/>
+      <c r="CB12" s="48"/>
       <c r="CE12" s="24"/>
       <c r="CF12" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="CG12" s="43" t="s">
+      <c r="CG12" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="CH12" s="44"/>
-      <c r="CI12" s="43" t="s">
+      <c r="CH12" s="48"/>
+      <c r="CI12" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="CJ12" s="44"/>
-      <c r="CK12" s="43" t="s">
+      <c r="CJ12" s="48"/>
+      <c r="CK12" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="CL12" s="44"/>
-      <c r="CM12" s="43" t="s">
+      <c r="CL12" s="48"/>
+      <c r="CM12" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="CN12" s="44"/>
-      <c r="CO12" s="43" t="s">
+      <c r="CN12" s="48"/>
+      <c r="CO12" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="CP12" s="44"/>
+      <c r="CP12" s="48"/>
     </row>
     <row r="13" spans="2:94" ht="15" thickBot="1">
       <c r="AA13" s="25" t="s">
@@ -9133,20 +9169,20 @@
       </c>
     </row>
     <row r="14" spans="2:94" ht="15" thickBot="1">
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="47"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="52"/>
+      <c r="K14" s="52"/>
+      <c r="L14" s="52"/>
+      <c r="M14" s="53"/>
       <c r="AA14" s="29" t="s">
         <v>24</v>
       </c>
@@ -9221,26 +9257,26 @@
     <row r="15" spans="2:94" ht="15" thickBot="1">
       <c r="B15" s="24"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="43" t="s">
+      <c r="D15" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E15" s="44"/>
-      <c r="F15" s="43" t="s">
+      <c r="E15" s="48"/>
+      <c r="F15" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="44"/>
-      <c r="H15" s="43" t="s">
+      <c r="G15" s="48"/>
+      <c r="H15" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="44"/>
-      <c r="J15" s="43" t="s">
+      <c r="I15" s="48"/>
+      <c r="J15" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="44"/>
-      <c r="L15" s="43" t="s">
+      <c r="K15" s="48"/>
+      <c r="L15" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="M15" s="44"/>
+      <c r="M15" s="48"/>
       <c r="AA15" s="29" t="s">
         <v>39</v>
       </c>
@@ -10176,7 +10212,7 @@
       <c r="G24" s="30">
         <v>0.68</v>
       </c>
-      <c r="H24" s="55">
+      <c r="H24" s="39">
         <v>26.09</v>
       </c>
       <c r="I24" s="30">
@@ -11021,8 +11057,12 @@
       <c r="G32" s="30">
         <v>100</v>
       </c>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
+      <c r="H32" s="30">
+        <v>28.98</v>
+      </c>
+      <c r="I32" s="30">
+        <v>59.98</v>
+      </c>
       <c r="J32" s="30">
         <v>54.78</v>
       </c>
@@ -11123,8 +11163,12 @@
       <c r="G33" s="30">
         <v>100</v>
       </c>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
+      <c r="H33" s="30">
+        <v>29.01</v>
+      </c>
+      <c r="I33" s="30">
+        <v>60.44</v>
+      </c>
       <c r="J33" s="30">
         <v>54.93</v>
       </c>
@@ -11225,8 +11269,12 @@
       <c r="G34" s="30">
         <v>100</v>
       </c>
-      <c r="H34" s="30"/>
-      <c r="I34" s="30"/>
+      <c r="H34" s="30">
+        <v>29.03</v>
+      </c>
+      <c r="I34" s="30">
+        <v>60.69</v>
+      </c>
       <c r="J34" s="30">
         <v>55.02</v>
       </c>
@@ -11327,8 +11375,12 @@
       <c r="G35" s="30">
         <v>100</v>
       </c>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
+      <c r="H35" s="30">
+        <v>29.05</v>
+      </c>
+      <c r="I35" s="30">
+        <v>60.86</v>
+      </c>
       <c r="J35" s="30">
         <v>55.08</v>
       </c>
@@ -11344,68 +11396,68 @@
       <c r="AB35" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="AC35" s="39"/>
-      <c r="AD35" s="40"/>
-      <c r="AE35" s="39"/>
-      <c r="AF35" s="40"/>
-      <c r="AG35" s="41"/>
-      <c r="AH35" s="42"/>
-      <c r="AI35" s="39"/>
-      <c r="AJ35" s="40"/>
-      <c r="AK35" s="39"/>
-      <c r="AL35" s="40"/>
+      <c r="AC35" s="40"/>
+      <c r="AD35" s="41"/>
+      <c r="AE35" s="40"/>
+      <c r="AF35" s="41"/>
+      <c r="AG35" s="42"/>
+      <c r="AH35" s="43"/>
+      <c r="AI35" s="40"/>
+      <c r="AJ35" s="41"/>
+      <c r="AK35" s="40"/>
+      <c r="AL35" s="41"/>
       <c r="AP35" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="AQ35" s="39"/>
-      <c r="AR35" s="40"/>
-      <c r="AS35" s="39"/>
-      <c r="AT35" s="40"/>
-      <c r="AU35" s="41"/>
-      <c r="AV35" s="42"/>
-      <c r="AW35" s="39"/>
-      <c r="AX35" s="40"/>
-      <c r="AY35" s="39"/>
-      <c r="AZ35" s="40"/>
+      <c r="AQ35" s="40"/>
+      <c r="AR35" s="41"/>
+      <c r="AS35" s="40"/>
+      <c r="AT35" s="41"/>
+      <c r="AU35" s="42"/>
+      <c r="AV35" s="43"/>
+      <c r="AW35" s="40"/>
+      <c r="AX35" s="41"/>
+      <c r="AY35" s="40"/>
+      <c r="AZ35" s="41"/>
       <c r="BD35" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="BE35" s="39"/>
-      <c r="BF35" s="40"/>
-      <c r="BG35" s="39"/>
-      <c r="BH35" s="40"/>
-      <c r="BI35" s="41"/>
-      <c r="BJ35" s="42"/>
-      <c r="BK35" s="39"/>
-      <c r="BL35" s="40"/>
-      <c r="BM35" s="39"/>
-      <c r="BN35" s="40"/>
+      <c r="BE35" s="40"/>
+      <c r="BF35" s="41"/>
+      <c r="BG35" s="40"/>
+      <c r="BH35" s="41"/>
+      <c r="BI35" s="42"/>
+      <c r="BJ35" s="43"/>
+      <c r="BK35" s="40"/>
+      <c r="BL35" s="41"/>
+      <c r="BM35" s="40"/>
+      <c r="BN35" s="41"/>
       <c r="BR35" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="BS35" s="39"/>
-      <c r="BT35" s="40"/>
-      <c r="BU35" s="39"/>
-      <c r="BV35" s="40"/>
-      <c r="BW35" s="41"/>
-      <c r="BX35" s="42"/>
-      <c r="BY35" s="39"/>
-      <c r="BZ35" s="40"/>
-      <c r="CA35" s="39"/>
-      <c r="CB35" s="40"/>
+      <c r="BS35" s="40"/>
+      <c r="BT35" s="41"/>
+      <c r="BU35" s="40"/>
+      <c r="BV35" s="41"/>
+      <c r="BW35" s="42"/>
+      <c r="BX35" s="43"/>
+      <c r="BY35" s="40"/>
+      <c r="BZ35" s="41"/>
+      <c r="CA35" s="40"/>
+      <c r="CB35" s="41"/>
       <c r="CF35" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="CG35" s="39"/>
-      <c r="CH35" s="40"/>
-      <c r="CI35" s="39"/>
-      <c r="CJ35" s="40"/>
-      <c r="CK35" s="41"/>
-      <c r="CL35" s="42"/>
-      <c r="CM35" s="39"/>
-      <c r="CN35" s="40"/>
-      <c r="CO35" s="39"/>
-      <c r="CP35" s="40"/>
+      <c r="CG35" s="40"/>
+      <c r="CH35" s="41"/>
+      <c r="CI35" s="40"/>
+      <c r="CJ35" s="41"/>
+      <c r="CK35" s="42"/>
+      <c r="CL35" s="43"/>
+      <c r="CM35" s="40"/>
+      <c r="CN35" s="41"/>
+      <c r="CO35" s="40"/>
+      <c r="CP35" s="41"/>
     </row>
     <row r="36" spans="2:94">
       <c r="B36" s="29" t="s">
@@ -11424,8 +11476,12 @@
       <c r="G36" s="30">
         <v>100</v>
       </c>
-      <c r="H36" s="30"/>
-      <c r="I36" s="30"/>
+      <c r="H36" s="30">
+        <v>29.05</v>
+      </c>
+      <c r="I36" s="30">
+        <v>60.91</v>
+      </c>
       <c r="J36" s="30">
         <v>55.12</v>
       </c>
@@ -11456,8 +11512,12 @@
       <c r="G37" s="30">
         <v>100</v>
       </c>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
+      <c r="H37" s="30">
+        <v>29.06</v>
+      </c>
+      <c r="I37" s="30">
+        <v>61.01</v>
+      </c>
       <c r="J37" s="30">
         <v>55.15</v>
       </c>
@@ -11475,210 +11535,210 @@
       <c r="C38" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="39">
+      <c r="D38" s="40">
         <v>4</v>
       </c>
-      <c r="E38" s="40"/>
-      <c r="F38" s="39"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="41"/>
-      <c r="I38" s="42"/>
-      <c r="J38" s="39"/>
-      <c r="K38" s="40"/>
-      <c r="L38" s="39"/>
-      <c r="M38" s="40"/>
-      <c r="AA38" s="45" t="s">
+      <c r="E38" s="41"/>
+      <c r="F38" s="40"/>
+      <c r="G38" s="41"/>
+      <c r="H38" s="42"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="40"/>
+      <c r="K38" s="41"/>
+      <c r="L38" s="40"/>
+      <c r="M38" s="41"/>
+      <c r="AA38" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="AB38" s="51"/>
-      <c r="AC38" s="51"/>
-      <c r="AD38" s="51"/>
-      <c r="AE38" s="51"/>
-      <c r="AF38" s="51"/>
-      <c r="AG38" s="51"/>
-      <c r="AH38" s="51"/>
-      <c r="AI38" s="51"/>
-      <c r="AJ38" s="51"/>
-      <c r="AK38" s="51"/>
-      <c r="AL38" s="52"/>
-      <c r="AO38" s="45" t="s">
+      <c r="AB38" s="45"/>
+      <c r="AC38" s="45"/>
+      <c r="AD38" s="45"/>
+      <c r="AE38" s="45"/>
+      <c r="AF38" s="45"/>
+      <c r="AG38" s="45"/>
+      <c r="AH38" s="45"/>
+      <c r="AI38" s="45"/>
+      <c r="AJ38" s="45"/>
+      <c r="AK38" s="45"/>
+      <c r="AL38" s="46"/>
+      <c r="AO38" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="AP38" s="51"/>
-      <c r="AQ38" s="51"/>
-      <c r="AR38" s="51"/>
-      <c r="AS38" s="51"/>
-      <c r="AT38" s="51"/>
-      <c r="AU38" s="51"/>
-      <c r="AV38" s="51"/>
-      <c r="AW38" s="51"/>
-      <c r="AX38" s="51"/>
-      <c r="AY38" s="51"/>
-      <c r="AZ38" s="52"/>
-      <c r="BC38" s="45" t="s">
+      <c r="AP38" s="45"/>
+      <c r="AQ38" s="45"/>
+      <c r="AR38" s="45"/>
+      <c r="AS38" s="45"/>
+      <c r="AT38" s="45"/>
+      <c r="AU38" s="45"/>
+      <c r="AV38" s="45"/>
+      <c r="AW38" s="45"/>
+      <c r="AX38" s="45"/>
+      <c r="AY38" s="45"/>
+      <c r="AZ38" s="46"/>
+      <c r="BC38" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="BD38" s="51"/>
-      <c r="BE38" s="51"/>
-      <c r="BF38" s="51"/>
-      <c r="BG38" s="51"/>
-      <c r="BH38" s="51"/>
-      <c r="BI38" s="51"/>
-      <c r="BJ38" s="51"/>
-      <c r="BK38" s="51"/>
-      <c r="BL38" s="51"/>
-      <c r="BM38" s="51"/>
-      <c r="BN38" s="52"/>
-      <c r="BQ38" s="45" t="s">
+      <c r="BD38" s="45"/>
+      <c r="BE38" s="45"/>
+      <c r="BF38" s="45"/>
+      <c r="BG38" s="45"/>
+      <c r="BH38" s="45"/>
+      <c r="BI38" s="45"/>
+      <c r="BJ38" s="45"/>
+      <c r="BK38" s="45"/>
+      <c r="BL38" s="45"/>
+      <c r="BM38" s="45"/>
+      <c r="BN38" s="46"/>
+      <c r="BQ38" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="BR38" s="51"/>
-      <c r="BS38" s="51"/>
-      <c r="BT38" s="51"/>
-      <c r="BU38" s="51"/>
-      <c r="BV38" s="51"/>
-      <c r="BW38" s="51"/>
-      <c r="BX38" s="51"/>
-      <c r="BY38" s="51"/>
-      <c r="BZ38" s="51"/>
-      <c r="CA38" s="51"/>
-      <c r="CB38" s="52"/>
-      <c r="CE38" s="45" t="s">
+      <c r="BR38" s="45"/>
+      <c r="BS38" s="45"/>
+      <c r="BT38" s="45"/>
+      <c r="BU38" s="45"/>
+      <c r="BV38" s="45"/>
+      <c r="BW38" s="45"/>
+      <c r="BX38" s="45"/>
+      <c r="BY38" s="45"/>
+      <c r="BZ38" s="45"/>
+      <c r="CA38" s="45"/>
+      <c r="CB38" s="46"/>
+      <c r="CE38" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="CF38" s="51"/>
-      <c r="CG38" s="51"/>
-      <c r="CH38" s="51"/>
-      <c r="CI38" s="51"/>
-      <c r="CJ38" s="51"/>
-      <c r="CK38" s="51"/>
-      <c r="CL38" s="51"/>
-      <c r="CM38" s="51"/>
-      <c r="CN38" s="51"/>
-      <c r="CO38" s="51"/>
-      <c r="CP38" s="52"/>
+      <c r="CF38" s="45"/>
+      <c r="CG38" s="45"/>
+      <c r="CH38" s="45"/>
+      <c r="CI38" s="45"/>
+      <c r="CJ38" s="45"/>
+      <c r="CK38" s="45"/>
+      <c r="CL38" s="45"/>
+      <c r="CM38" s="45"/>
+      <c r="CN38" s="45"/>
+      <c r="CO38" s="45"/>
+      <c r="CP38" s="46"/>
     </row>
     <row r="39" spans="2:94" ht="15" thickBot="1">
       <c r="AA39" s="1"/>
       <c r="AB39" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="AC39" s="43" t="s">
+      <c r="AC39" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AD39" s="44"/>
-      <c r="AE39" s="43" t="s">
+      <c r="AD39" s="48"/>
+      <c r="AE39" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="AF39" s="44"/>
-      <c r="AG39" s="43" t="s">
+      <c r="AF39" s="48"/>
+      <c r="AG39" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="AH39" s="44"/>
-      <c r="AI39" s="43" t="s">
+      <c r="AH39" s="48"/>
+      <c r="AI39" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="AJ39" s="44"/>
-      <c r="AK39" s="43" t="s">
+      <c r="AJ39" s="48"/>
+      <c r="AK39" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="AL39" s="44"/>
+      <c r="AL39" s="48"/>
       <c r="AO39" s="1"/>
       <c r="AP39" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="AQ39" s="43" t="s">
+      <c r="AQ39" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AR39" s="44"/>
-      <c r="AS39" s="43" t="s">
+      <c r="AR39" s="48"/>
+      <c r="AS39" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="AT39" s="44"/>
-      <c r="AU39" s="43" t="s">
+      <c r="AT39" s="48"/>
+      <c r="AU39" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="AV39" s="44"/>
-      <c r="AW39" s="43" t="s">
+      <c r="AV39" s="48"/>
+      <c r="AW39" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="AX39" s="44"/>
-      <c r="AY39" s="43" t="s">
+      <c r="AX39" s="48"/>
+      <c r="AY39" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="AZ39" s="44"/>
+      <c r="AZ39" s="48"/>
       <c r="BC39" s="1"/>
       <c r="BD39" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="BE39" s="43" t="s">
+      <c r="BE39" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="BF39" s="44"/>
-      <c r="BG39" s="43" t="s">
+      <c r="BF39" s="48"/>
+      <c r="BG39" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="BH39" s="44"/>
-      <c r="BI39" s="43" t="s">
+      <c r="BH39" s="48"/>
+      <c r="BI39" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="BJ39" s="44"/>
-      <c r="BK39" s="43" t="s">
+      <c r="BJ39" s="48"/>
+      <c r="BK39" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="BL39" s="44"/>
-      <c r="BM39" s="43" t="s">
+      <c r="BL39" s="48"/>
+      <c r="BM39" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="BN39" s="44"/>
+      <c r="BN39" s="48"/>
       <c r="BQ39" s="1"/>
       <c r="BR39" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="BS39" s="43" t="s">
+      <c r="BS39" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="BT39" s="44"/>
-      <c r="BU39" s="43" t="s">
+      <c r="BT39" s="48"/>
+      <c r="BU39" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="BV39" s="44"/>
-      <c r="BW39" s="43" t="s">
+      <c r="BV39" s="48"/>
+      <c r="BW39" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="BX39" s="44"/>
-      <c r="BY39" s="43" t="s">
+      <c r="BX39" s="48"/>
+      <c r="BY39" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="BZ39" s="44"/>
-      <c r="CA39" s="43" t="s">
+      <c r="BZ39" s="48"/>
+      <c r="CA39" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="CB39" s="44"/>
+      <c r="CB39" s="48"/>
       <c r="CE39" s="1"/>
       <c r="CF39" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="CG39" s="43" t="s">
+      <c r="CG39" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="CH39" s="44"/>
-      <c r="CI39" s="43" t="s">
+      <c r="CH39" s="48"/>
+      <c r="CI39" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="CJ39" s="44"/>
-      <c r="CK39" s="43" t="s">
+      <c r="CJ39" s="48"/>
+      <c r="CK39" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="CL39" s="44"/>
-      <c r="CM39" s="43" t="s">
+      <c r="CL39" s="48"/>
+      <c r="CM39" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="CN39" s="44"/>
-      <c r="CO39" s="43" t="s">
+      <c r="CN39" s="48"/>
+      <c r="CO39" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="CP39" s="44"/>
+      <c r="CP39" s="48"/>
     </row>
     <row r="40" spans="2:94" ht="15" thickBot="1">
       <c r="AA40" s="6" t="s">
@@ -11863,7 +11923,7 @@
       </c>
     </row>
     <row r="41" spans="2:94" ht="15" thickTop="1">
-      <c r="AA41" s="48" t="s">
+      <c r="AA41" s="49" t="s">
         <v>13</v>
       </c>
       <c r="AB41" s="12" t="s">
@@ -11879,7 +11939,7 @@
       <c r="AJ41" s="20"/>
       <c r="AK41" s="19"/>
       <c r="AL41" s="20"/>
-      <c r="AO41" s="48" t="s">
+      <c r="AO41" s="49" t="s">
         <v>13</v>
       </c>
       <c r="AP41" s="12" t="s">
@@ -11895,7 +11955,7 @@
       <c r="AX41" s="20"/>
       <c r="AY41" s="19"/>
       <c r="AZ41" s="20"/>
-      <c r="BC41" s="48" t="s">
+      <c r="BC41" s="49" t="s">
         <v>13</v>
       </c>
       <c r="BD41" s="12" t="s">
@@ -11911,7 +11971,7 @@
       <c r="BL41" s="20"/>
       <c r="BM41" s="19"/>
       <c r="BN41" s="20"/>
-      <c r="BQ41" s="48" t="s">
+      <c r="BQ41" s="49" t="s">
         <v>13</v>
       </c>
       <c r="BR41" s="12" t="s">
@@ -11927,7 +11987,7 @@
       <c r="BZ41" s="20"/>
       <c r="CA41" s="19"/>
       <c r="CB41" s="20"/>
-      <c r="CE41" s="48" t="s">
+      <c r="CE41" s="49" t="s">
         <v>13</v>
       </c>
       <c r="CF41" s="12" t="s">
@@ -11945,7 +12005,7 @@
       <c r="CP41" s="20"/>
     </row>
     <row r="42" spans="2:94">
-      <c r="AA42" s="49"/>
+      <c r="AA42" s="50"/>
       <c r="AB42" s="9" t="s">
         <v>11</v>
       </c>
@@ -11959,7 +12019,7 @@
       <c r="AJ42" s="16"/>
       <c r="AK42" s="15"/>
       <c r="AL42" s="16"/>
-      <c r="AO42" s="49"/>
+      <c r="AO42" s="50"/>
       <c r="AP42" s="9" t="s">
         <v>11</v>
       </c>
@@ -11973,7 +12033,7 @@
       <c r="AX42" s="16"/>
       <c r="AY42" s="15"/>
       <c r="AZ42" s="16"/>
-      <c r="BC42" s="49"/>
+      <c r="BC42" s="50"/>
       <c r="BD42" s="9" t="s">
         <v>11</v>
       </c>
@@ -11987,7 +12047,7 @@
       <c r="BL42" s="16"/>
       <c r="BM42" s="15"/>
       <c r="BN42" s="16"/>
-      <c r="BQ42" s="49"/>
+      <c r="BQ42" s="50"/>
       <c r="BR42" s="9" t="s">
         <v>11</v>
       </c>
@@ -12001,7 +12061,7 @@
       <c r="BZ42" s="16"/>
       <c r="CA42" s="15"/>
       <c r="CB42" s="16"/>
-      <c r="CE42" s="49"/>
+      <c r="CE42" s="50"/>
       <c r="CF42" s="9" t="s">
         <v>11</v>
       </c>
@@ -12017,7 +12077,7 @@
       <c r="CP42" s="16"/>
     </row>
     <row r="43" spans="2:94">
-      <c r="AA43" s="49"/>
+      <c r="AA43" s="50"/>
       <c r="AB43" s="9" t="s">
         <v>12</v>
       </c>
@@ -12031,7 +12091,7 @@
       <c r="AJ43" s="16"/>
       <c r="AK43" s="15"/>
       <c r="AL43" s="16"/>
-      <c r="AO43" s="49"/>
+      <c r="AO43" s="50"/>
       <c r="AP43" s="9" t="s">
         <v>12</v>
       </c>
@@ -12045,7 +12105,7 @@
       <c r="AX43" s="16"/>
       <c r="AY43" s="15"/>
       <c r="AZ43" s="16"/>
-      <c r="BC43" s="49"/>
+      <c r="BC43" s="50"/>
       <c r="BD43" s="9" t="s">
         <v>12</v>
       </c>
@@ -12059,7 +12119,7 @@
       <c r="BL43" s="16"/>
       <c r="BM43" s="15"/>
       <c r="BN43" s="16"/>
-      <c r="BQ43" s="49"/>
+      <c r="BQ43" s="50"/>
       <c r="BR43" s="9" t="s">
         <v>12</v>
       </c>
@@ -12073,7 +12133,7 @@
       <c r="BZ43" s="16"/>
       <c r="CA43" s="15"/>
       <c r="CB43" s="16"/>
-      <c r="CE43" s="49"/>
+      <c r="CE43" s="50"/>
       <c r="CF43" s="9" t="s">
         <v>12</v>
       </c>
@@ -12089,7 +12149,7 @@
       <c r="CP43" s="16"/>
     </row>
     <row r="44" spans="2:94" ht="15" thickBot="1">
-      <c r="AA44" s="50"/>
+      <c r="AA44" s="51"/>
       <c r="AB44" s="10" t="s">
         <v>14</v>
       </c>
@@ -12103,7 +12163,7 @@
       <c r="AJ44" s="22"/>
       <c r="AK44" s="21"/>
       <c r="AL44" s="22"/>
-      <c r="AO44" s="50"/>
+      <c r="AO44" s="51"/>
       <c r="AP44" s="10" t="s">
         <v>14</v>
       </c>
@@ -12117,7 +12177,7 @@
       <c r="AX44" s="22"/>
       <c r="AY44" s="21"/>
       <c r="AZ44" s="22"/>
-      <c r="BC44" s="50"/>
+      <c r="BC44" s="51"/>
       <c r="BD44" s="10" t="s">
         <v>14</v>
       </c>
@@ -12131,7 +12191,7 @@
       <c r="BL44" s="22"/>
       <c r="BM44" s="21"/>
       <c r="BN44" s="22"/>
-      <c r="BQ44" s="50"/>
+      <c r="BQ44" s="51"/>
       <c r="BR44" s="10" t="s">
         <v>14</v>
       </c>
@@ -12145,7 +12205,7 @@
       <c r="BZ44" s="22"/>
       <c r="CA44" s="21"/>
       <c r="CB44" s="22"/>
-      <c r="CE44" s="50"/>
+      <c r="CE44" s="51"/>
       <c r="CF44" s="10" t="s">
         <v>14</v>
       </c>
@@ -12162,198 +12222,198 @@
     </row>
     <row r="46" spans="2:94" ht="15" thickBot="1"/>
     <row r="47" spans="2:94" ht="15" thickBot="1">
-      <c r="AA47" s="45" t="s">
+      <c r="AA47" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="AB47" s="46"/>
-      <c r="AC47" s="46"/>
-      <c r="AD47" s="46"/>
-      <c r="AE47" s="46"/>
-      <c r="AF47" s="46"/>
-      <c r="AG47" s="46"/>
-      <c r="AH47" s="46"/>
-      <c r="AI47" s="46"/>
-      <c r="AJ47" s="46"/>
-      <c r="AK47" s="46"/>
-      <c r="AL47" s="47"/>
-      <c r="AO47" s="45" t="s">
+      <c r="AB47" s="52"/>
+      <c r="AC47" s="52"/>
+      <c r="AD47" s="52"/>
+      <c r="AE47" s="52"/>
+      <c r="AF47" s="52"/>
+      <c r="AG47" s="52"/>
+      <c r="AH47" s="52"/>
+      <c r="AI47" s="52"/>
+      <c r="AJ47" s="52"/>
+      <c r="AK47" s="52"/>
+      <c r="AL47" s="53"/>
+      <c r="AO47" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="AP47" s="46"/>
-      <c r="AQ47" s="46"/>
-      <c r="AR47" s="46"/>
-      <c r="AS47" s="46"/>
-      <c r="AT47" s="46"/>
-      <c r="AU47" s="46"/>
-      <c r="AV47" s="46"/>
-      <c r="AW47" s="46"/>
-      <c r="AX47" s="46"/>
-      <c r="AY47" s="46"/>
-      <c r="AZ47" s="47"/>
-      <c r="BC47" s="45" t="s">
+      <c r="AP47" s="52"/>
+      <c r="AQ47" s="52"/>
+      <c r="AR47" s="52"/>
+      <c r="AS47" s="52"/>
+      <c r="AT47" s="52"/>
+      <c r="AU47" s="52"/>
+      <c r="AV47" s="52"/>
+      <c r="AW47" s="52"/>
+      <c r="AX47" s="52"/>
+      <c r="AY47" s="52"/>
+      <c r="AZ47" s="53"/>
+      <c r="BC47" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="BD47" s="46"/>
-      <c r="BE47" s="46"/>
-      <c r="BF47" s="46"/>
-      <c r="BG47" s="46"/>
-      <c r="BH47" s="46"/>
-      <c r="BI47" s="46"/>
-      <c r="BJ47" s="46"/>
-      <c r="BK47" s="46"/>
-      <c r="BL47" s="46"/>
-      <c r="BM47" s="46"/>
-      <c r="BN47" s="47"/>
-      <c r="BQ47" s="45" t="s">
+      <c r="BD47" s="52"/>
+      <c r="BE47" s="52"/>
+      <c r="BF47" s="52"/>
+      <c r="BG47" s="52"/>
+      <c r="BH47" s="52"/>
+      <c r="BI47" s="52"/>
+      <c r="BJ47" s="52"/>
+      <c r="BK47" s="52"/>
+      <c r="BL47" s="52"/>
+      <c r="BM47" s="52"/>
+      <c r="BN47" s="53"/>
+      <c r="BQ47" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="BR47" s="46"/>
-      <c r="BS47" s="46"/>
-      <c r="BT47" s="46"/>
-      <c r="BU47" s="46"/>
-      <c r="BV47" s="46"/>
-      <c r="BW47" s="46"/>
-      <c r="BX47" s="46"/>
-      <c r="BY47" s="46"/>
-      <c r="BZ47" s="46"/>
-      <c r="CA47" s="46"/>
-      <c r="CB47" s="47"/>
-      <c r="CE47" s="45" t="s">
+      <c r="BR47" s="52"/>
+      <c r="BS47" s="52"/>
+      <c r="BT47" s="52"/>
+      <c r="BU47" s="52"/>
+      <c r="BV47" s="52"/>
+      <c r="BW47" s="52"/>
+      <c r="BX47" s="52"/>
+      <c r="BY47" s="52"/>
+      <c r="BZ47" s="52"/>
+      <c r="CA47" s="52"/>
+      <c r="CB47" s="53"/>
+      <c r="CE47" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="CF47" s="46"/>
-      <c r="CG47" s="46"/>
-      <c r="CH47" s="46"/>
-      <c r="CI47" s="46"/>
-      <c r="CJ47" s="46"/>
-      <c r="CK47" s="46"/>
-      <c r="CL47" s="46"/>
-      <c r="CM47" s="46"/>
-      <c r="CN47" s="46"/>
-      <c r="CO47" s="46"/>
-      <c r="CP47" s="47"/>
+      <c r="CF47" s="52"/>
+      <c r="CG47" s="52"/>
+      <c r="CH47" s="52"/>
+      <c r="CI47" s="52"/>
+      <c r="CJ47" s="52"/>
+      <c r="CK47" s="52"/>
+      <c r="CL47" s="52"/>
+      <c r="CM47" s="52"/>
+      <c r="CN47" s="52"/>
+      <c r="CO47" s="52"/>
+      <c r="CP47" s="53"/>
     </row>
     <row r="48" spans="2:94" ht="15" thickBot="1">
       <c r="AA48" s="24"/>
       <c r="AB48" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="AC48" s="43" t="s">
+      <c r="AC48" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AD48" s="44"/>
-      <c r="AE48" s="43" t="s">
+      <c r="AD48" s="48"/>
+      <c r="AE48" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="AF48" s="44"/>
-      <c r="AG48" s="43" t="s">
+      <c r="AF48" s="48"/>
+      <c r="AG48" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="AH48" s="44"/>
-      <c r="AI48" s="43" t="s">
+      <c r="AH48" s="48"/>
+      <c r="AI48" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="AJ48" s="44"/>
-      <c r="AK48" s="43" t="s">
+      <c r="AJ48" s="48"/>
+      <c r="AK48" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="AL48" s="44"/>
+      <c r="AL48" s="48"/>
       <c r="AO48" s="24"/>
       <c r="AP48" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="AQ48" s="43" t="s">
+      <c r="AQ48" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AR48" s="44"/>
-      <c r="AS48" s="43" t="s">
+      <c r="AR48" s="48"/>
+      <c r="AS48" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="AT48" s="44"/>
-      <c r="AU48" s="43" t="s">
+      <c r="AT48" s="48"/>
+      <c r="AU48" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="AV48" s="44"/>
-      <c r="AW48" s="43" t="s">
+      <c r="AV48" s="48"/>
+      <c r="AW48" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="AX48" s="44"/>
-      <c r="AY48" s="43" t="s">
+      <c r="AX48" s="48"/>
+      <c r="AY48" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="AZ48" s="44"/>
+      <c r="AZ48" s="48"/>
       <c r="BC48" s="24"/>
       <c r="BD48" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="BE48" s="43" t="s">
+      <c r="BE48" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="BF48" s="44"/>
-      <c r="BG48" s="43" t="s">
+      <c r="BF48" s="48"/>
+      <c r="BG48" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="BH48" s="44"/>
-      <c r="BI48" s="43" t="s">
+      <c r="BH48" s="48"/>
+      <c r="BI48" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="BJ48" s="44"/>
-      <c r="BK48" s="43" t="s">
+      <c r="BJ48" s="48"/>
+      <c r="BK48" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="BL48" s="44"/>
-      <c r="BM48" s="43" t="s">
+      <c r="BL48" s="48"/>
+      <c r="BM48" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="BN48" s="44"/>
+      <c r="BN48" s="48"/>
       <c r="BQ48" s="24"/>
       <c r="BR48" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="BS48" s="43" t="s">
+      <c r="BS48" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="BT48" s="44"/>
-      <c r="BU48" s="43" t="s">
+      <c r="BT48" s="48"/>
+      <c r="BU48" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="BV48" s="44"/>
-      <c r="BW48" s="43" t="s">
+      <c r="BV48" s="48"/>
+      <c r="BW48" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="BX48" s="44"/>
-      <c r="BY48" s="43" t="s">
+      <c r="BX48" s="48"/>
+      <c r="BY48" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="BZ48" s="44"/>
-      <c r="CA48" s="43" t="s">
+      <c r="BZ48" s="48"/>
+      <c r="CA48" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="CB48" s="44"/>
+      <c r="CB48" s="48"/>
       <c r="CE48" s="24"/>
       <c r="CF48" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="CG48" s="43" t="s">
+      <c r="CG48" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="CH48" s="44"/>
-      <c r="CI48" s="43" t="s">
+      <c r="CH48" s="48"/>
+      <c r="CI48" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="CJ48" s="44"/>
-      <c r="CK48" s="43" t="s">
+      <c r="CJ48" s="48"/>
+      <c r="CK48" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="CL48" s="44"/>
-      <c r="CM48" s="43" t="s">
+      <c r="CL48" s="48"/>
+      <c r="CM48" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="CN48" s="44"/>
-      <c r="CO48" s="43" t="s">
+      <c r="CN48" s="48"/>
+      <c r="CO48" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="CP48" s="44"/>
+      <c r="CP48" s="48"/>
     </row>
     <row r="49" spans="27:94">
       <c r="AA49" s="25" t="s">
@@ -14048,263 +14108,263 @@
       <c r="AB71" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="AC71" s="39"/>
-      <c r="AD71" s="40"/>
-      <c r="AE71" s="39"/>
-      <c r="AF71" s="40"/>
-      <c r="AG71" s="41"/>
-      <c r="AH71" s="42"/>
-      <c r="AI71" s="39"/>
-      <c r="AJ71" s="40"/>
-      <c r="AK71" s="39"/>
-      <c r="AL71" s="40"/>
+      <c r="AC71" s="40"/>
+      <c r="AD71" s="41"/>
+      <c r="AE71" s="40"/>
+      <c r="AF71" s="41"/>
+      <c r="AG71" s="42"/>
+      <c r="AH71" s="43"/>
+      <c r="AI71" s="40"/>
+      <c r="AJ71" s="41"/>
+      <c r="AK71" s="40"/>
+      <c r="AL71" s="41"/>
       <c r="AP71" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="AQ71" s="39"/>
-      <c r="AR71" s="40"/>
-      <c r="AS71" s="39"/>
-      <c r="AT71" s="40"/>
-      <c r="AU71" s="41"/>
-      <c r="AV71" s="42"/>
-      <c r="AW71" s="39"/>
-      <c r="AX71" s="40"/>
-      <c r="AY71" s="39"/>
-      <c r="AZ71" s="40"/>
+      <c r="AQ71" s="40"/>
+      <c r="AR71" s="41"/>
+      <c r="AS71" s="40"/>
+      <c r="AT71" s="41"/>
+      <c r="AU71" s="42"/>
+      <c r="AV71" s="43"/>
+      <c r="AW71" s="40"/>
+      <c r="AX71" s="41"/>
+      <c r="AY71" s="40"/>
+      <c r="AZ71" s="41"/>
       <c r="BD71" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="BE71" s="39"/>
-      <c r="BF71" s="40"/>
-      <c r="BG71" s="39"/>
-      <c r="BH71" s="40"/>
-      <c r="BI71" s="41"/>
-      <c r="BJ71" s="42"/>
-      <c r="BK71" s="39"/>
-      <c r="BL71" s="40"/>
-      <c r="BM71" s="39"/>
-      <c r="BN71" s="40"/>
+      <c r="BE71" s="40"/>
+      <c r="BF71" s="41"/>
+      <c r="BG71" s="40"/>
+      <c r="BH71" s="41"/>
+      <c r="BI71" s="42"/>
+      <c r="BJ71" s="43"/>
+      <c r="BK71" s="40"/>
+      <c r="BL71" s="41"/>
+      <c r="BM71" s="40"/>
+      <c r="BN71" s="41"/>
       <c r="BR71" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="BS71" s="39"/>
-      <c r="BT71" s="40"/>
-      <c r="BU71" s="39"/>
-      <c r="BV71" s="40"/>
-      <c r="BW71" s="41"/>
-      <c r="BX71" s="42"/>
-      <c r="BY71" s="39"/>
-      <c r="BZ71" s="40"/>
-      <c r="CA71" s="39"/>
-      <c r="CB71" s="40"/>
+      <c r="BS71" s="40"/>
+      <c r="BT71" s="41"/>
+      <c r="BU71" s="40"/>
+      <c r="BV71" s="41"/>
+      <c r="BW71" s="42"/>
+      <c r="BX71" s="43"/>
+      <c r="BY71" s="40"/>
+      <c r="BZ71" s="41"/>
+      <c r="CA71" s="40"/>
+      <c r="CB71" s="41"/>
       <c r="CF71" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="CG71" s="39"/>
-      <c r="CH71" s="40"/>
-      <c r="CI71" s="39"/>
-      <c r="CJ71" s="40"/>
-      <c r="CK71" s="41"/>
-      <c r="CL71" s="42"/>
-      <c r="CM71" s="39"/>
-      <c r="CN71" s="40"/>
-      <c r="CO71" s="39"/>
-      <c r="CP71" s="40"/>
+      <c r="CG71" s="40"/>
+      <c r="CH71" s="41"/>
+      <c r="CI71" s="40"/>
+      <c r="CJ71" s="41"/>
+      <c r="CK71" s="42"/>
+      <c r="CL71" s="43"/>
+      <c r="CM71" s="40"/>
+      <c r="CN71" s="41"/>
+      <c r="CO71" s="40"/>
+      <c r="CP71" s="41"/>
     </row>
     <row r="73" spans="27:94" ht="15" thickBot="1"/>
     <row r="74" spans="27:94" ht="15" thickBot="1">
-      <c r="AA74" s="45" t="s">
+      <c r="AA74" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="AB74" s="51"/>
-      <c r="AC74" s="51"/>
-      <c r="AD74" s="51"/>
-      <c r="AE74" s="51"/>
-      <c r="AF74" s="51"/>
-      <c r="AG74" s="51"/>
-      <c r="AH74" s="51"/>
-      <c r="AI74" s="51"/>
-      <c r="AJ74" s="51"/>
-      <c r="AK74" s="51"/>
-      <c r="AL74" s="52"/>
-      <c r="AO74" s="45" t="s">
+      <c r="AB74" s="45"/>
+      <c r="AC74" s="45"/>
+      <c r="AD74" s="45"/>
+      <c r="AE74" s="45"/>
+      <c r="AF74" s="45"/>
+      <c r="AG74" s="45"/>
+      <c r="AH74" s="45"/>
+      <c r="AI74" s="45"/>
+      <c r="AJ74" s="45"/>
+      <c r="AK74" s="45"/>
+      <c r="AL74" s="46"/>
+      <c r="AO74" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="AP74" s="51"/>
-      <c r="AQ74" s="51"/>
-      <c r="AR74" s="51"/>
-      <c r="AS74" s="51"/>
-      <c r="AT74" s="51"/>
-      <c r="AU74" s="51"/>
-      <c r="AV74" s="51"/>
-      <c r="AW74" s="51"/>
-      <c r="AX74" s="51"/>
-      <c r="AY74" s="51"/>
-      <c r="AZ74" s="52"/>
-      <c r="BC74" s="45" t="s">
+      <c r="AP74" s="45"/>
+      <c r="AQ74" s="45"/>
+      <c r="AR74" s="45"/>
+      <c r="AS74" s="45"/>
+      <c r="AT74" s="45"/>
+      <c r="AU74" s="45"/>
+      <c r="AV74" s="45"/>
+      <c r="AW74" s="45"/>
+      <c r="AX74" s="45"/>
+      <c r="AY74" s="45"/>
+      <c r="AZ74" s="46"/>
+      <c r="BC74" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="BD74" s="51"/>
-      <c r="BE74" s="51"/>
-      <c r="BF74" s="51"/>
-      <c r="BG74" s="51"/>
-      <c r="BH74" s="51"/>
-      <c r="BI74" s="51"/>
-      <c r="BJ74" s="51"/>
-      <c r="BK74" s="51"/>
-      <c r="BL74" s="51"/>
-      <c r="BM74" s="51"/>
-      <c r="BN74" s="52"/>
-      <c r="BQ74" s="45" t="s">
+      <c r="BD74" s="45"/>
+      <c r="BE74" s="45"/>
+      <c r="BF74" s="45"/>
+      <c r="BG74" s="45"/>
+      <c r="BH74" s="45"/>
+      <c r="BI74" s="45"/>
+      <c r="BJ74" s="45"/>
+      <c r="BK74" s="45"/>
+      <c r="BL74" s="45"/>
+      <c r="BM74" s="45"/>
+      <c r="BN74" s="46"/>
+      <c r="BQ74" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="BR74" s="51"/>
-      <c r="BS74" s="51"/>
-      <c r="BT74" s="51"/>
-      <c r="BU74" s="51"/>
-      <c r="BV74" s="51"/>
-      <c r="BW74" s="51"/>
-      <c r="BX74" s="51"/>
-      <c r="BY74" s="51"/>
-      <c r="BZ74" s="51"/>
-      <c r="CA74" s="51"/>
-      <c r="CB74" s="52"/>
-      <c r="CE74" s="45" t="s">
+      <c r="BR74" s="45"/>
+      <c r="BS74" s="45"/>
+      <c r="BT74" s="45"/>
+      <c r="BU74" s="45"/>
+      <c r="BV74" s="45"/>
+      <c r="BW74" s="45"/>
+      <c r="BX74" s="45"/>
+      <c r="BY74" s="45"/>
+      <c r="BZ74" s="45"/>
+      <c r="CA74" s="45"/>
+      <c r="CB74" s="46"/>
+      <c r="CE74" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="CF74" s="51"/>
-      <c r="CG74" s="51"/>
-      <c r="CH74" s="51"/>
-      <c r="CI74" s="51"/>
-      <c r="CJ74" s="51"/>
-      <c r="CK74" s="51"/>
-      <c r="CL74" s="51"/>
-      <c r="CM74" s="51"/>
-      <c r="CN74" s="51"/>
-      <c r="CO74" s="51"/>
-      <c r="CP74" s="52"/>
+      <c r="CF74" s="45"/>
+      <c r="CG74" s="45"/>
+      <c r="CH74" s="45"/>
+      <c r="CI74" s="45"/>
+      <c r="CJ74" s="45"/>
+      <c r="CK74" s="45"/>
+      <c r="CL74" s="45"/>
+      <c r="CM74" s="45"/>
+      <c r="CN74" s="45"/>
+      <c r="CO74" s="45"/>
+      <c r="CP74" s="46"/>
     </row>
     <row r="75" spans="27:94" ht="15" thickBot="1">
       <c r="AA75" s="1"/>
       <c r="AB75" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="AC75" s="43" t="s">
+      <c r="AC75" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AD75" s="44"/>
-      <c r="AE75" s="43" t="s">
+      <c r="AD75" s="48"/>
+      <c r="AE75" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="AF75" s="44"/>
-      <c r="AG75" s="43" t="s">
+      <c r="AF75" s="48"/>
+      <c r="AG75" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="AH75" s="44"/>
-      <c r="AI75" s="43" t="s">
+      <c r="AH75" s="48"/>
+      <c r="AI75" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="AJ75" s="44"/>
-      <c r="AK75" s="43" t="s">
+      <c r="AJ75" s="48"/>
+      <c r="AK75" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="AL75" s="44"/>
+      <c r="AL75" s="48"/>
       <c r="AO75" s="1"/>
       <c r="AP75" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="AQ75" s="43" t="s">
+      <c r="AQ75" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AR75" s="44"/>
-      <c r="AS75" s="43" t="s">
+      <c r="AR75" s="48"/>
+      <c r="AS75" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="AT75" s="44"/>
-      <c r="AU75" s="43" t="s">
+      <c r="AT75" s="48"/>
+      <c r="AU75" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="AV75" s="44"/>
-      <c r="AW75" s="43" t="s">
+      <c r="AV75" s="48"/>
+      <c r="AW75" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="AX75" s="44"/>
-      <c r="AY75" s="43" t="s">
+      <c r="AX75" s="48"/>
+      <c r="AY75" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="AZ75" s="44"/>
+      <c r="AZ75" s="48"/>
       <c r="BC75" s="1"/>
       <c r="BD75" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="BE75" s="43" t="s">
+      <c r="BE75" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="BF75" s="44"/>
-      <c r="BG75" s="43" t="s">
+      <c r="BF75" s="48"/>
+      <c r="BG75" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="BH75" s="44"/>
-      <c r="BI75" s="43" t="s">
+      <c r="BH75" s="48"/>
+      <c r="BI75" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="BJ75" s="44"/>
-      <c r="BK75" s="43" t="s">
+      <c r="BJ75" s="48"/>
+      <c r="BK75" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="BL75" s="44"/>
-      <c r="BM75" s="43" t="s">
+      <c r="BL75" s="48"/>
+      <c r="BM75" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="BN75" s="44"/>
+      <c r="BN75" s="48"/>
       <c r="BQ75" s="1"/>
       <c r="BR75" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="BS75" s="43" t="s">
+      <c r="BS75" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="BT75" s="44"/>
-      <c r="BU75" s="43" t="s">
+      <c r="BT75" s="48"/>
+      <c r="BU75" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="BV75" s="44"/>
-      <c r="BW75" s="43" t="s">
+      <c r="BV75" s="48"/>
+      <c r="BW75" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="BX75" s="44"/>
-      <c r="BY75" s="43" t="s">
+      <c r="BX75" s="48"/>
+      <c r="BY75" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="BZ75" s="44"/>
-      <c r="CA75" s="43" t="s">
+      <c r="BZ75" s="48"/>
+      <c r="CA75" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="CB75" s="44"/>
+      <c r="CB75" s="48"/>
       <c r="CE75" s="1"/>
       <c r="CF75" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="CG75" s="43" t="s">
+      <c r="CG75" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="CH75" s="44"/>
-      <c r="CI75" s="43" t="s">
+      <c r="CH75" s="48"/>
+      <c r="CI75" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="CJ75" s="44"/>
-      <c r="CK75" s="43" t="s">
+      <c r="CJ75" s="48"/>
+      <c r="CK75" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="CL75" s="44"/>
-      <c r="CM75" s="43" t="s">
+      <c r="CL75" s="48"/>
+      <c r="CM75" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="CN75" s="44"/>
-      <c r="CO75" s="43" t="s">
+      <c r="CN75" s="48"/>
+      <c r="CO75" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="CP75" s="44"/>
+      <c r="CP75" s="48"/>
     </row>
     <row r="76" spans="27:94" ht="15" thickBot="1">
       <c r="AA76" s="6" t="s">
@@ -14489,7 +14549,7 @@
       </c>
     </row>
     <row r="77" spans="27:94" ht="15" thickTop="1">
-      <c r="AA77" s="48" t="s">
+      <c r="AA77" s="49" t="s">
         <v>13</v>
       </c>
       <c r="AB77" s="12" t="s">
@@ -14505,7 +14565,7 @@
       <c r="AJ77" s="20"/>
       <c r="AK77" s="19"/>
       <c r="AL77" s="20"/>
-      <c r="AO77" s="48" t="s">
+      <c r="AO77" s="49" t="s">
         <v>13</v>
       </c>
       <c r="AP77" s="12" t="s">
@@ -14521,7 +14581,7 @@
       <c r="AX77" s="20"/>
       <c r="AY77" s="19"/>
       <c r="AZ77" s="20"/>
-      <c r="BC77" s="48" t="s">
+      <c r="BC77" s="49" t="s">
         <v>13</v>
       </c>
       <c r="BD77" s="12" t="s">
@@ -14537,7 +14597,7 @@
       <c r="BL77" s="20"/>
       <c r="BM77" s="19"/>
       <c r="BN77" s="20"/>
-      <c r="BQ77" s="48" t="s">
+      <c r="BQ77" s="49" t="s">
         <v>13</v>
       </c>
       <c r="BR77" s="12" t="s">
@@ -14553,7 +14613,7 @@
       <c r="BZ77" s="20"/>
       <c r="CA77" s="19"/>
       <c r="CB77" s="20"/>
-      <c r="CE77" s="48" t="s">
+      <c r="CE77" s="49" t="s">
         <v>13</v>
       </c>
       <c r="CF77" s="12" t="s">
@@ -14571,7 +14631,7 @@
       <c r="CP77" s="20"/>
     </row>
     <row r="78" spans="27:94">
-      <c r="AA78" s="49"/>
+      <c r="AA78" s="50"/>
       <c r="AB78" s="9" t="s">
         <v>11</v>
       </c>
@@ -14585,7 +14645,7 @@
       <c r="AJ78" s="16"/>
       <c r="AK78" s="15"/>
       <c r="AL78" s="16"/>
-      <c r="AO78" s="49"/>
+      <c r="AO78" s="50"/>
       <c r="AP78" s="9" t="s">
         <v>11</v>
       </c>
@@ -14599,7 +14659,7 @@
       <c r="AX78" s="16"/>
       <c r="AY78" s="15"/>
       <c r="AZ78" s="16"/>
-      <c r="BC78" s="49"/>
+      <c r="BC78" s="50"/>
       <c r="BD78" s="9" t="s">
         <v>11</v>
       </c>
@@ -14613,7 +14673,7 @@
       <c r="BL78" s="16"/>
       <c r="BM78" s="15"/>
       <c r="BN78" s="16"/>
-      <c r="BQ78" s="49"/>
+      <c r="BQ78" s="50"/>
       <c r="BR78" s="9" t="s">
         <v>11</v>
       </c>
@@ -14627,7 +14687,7 @@
       <c r="BZ78" s="16"/>
       <c r="CA78" s="15"/>
       <c r="CB78" s="16"/>
-      <c r="CE78" s="49"/>
+      <c r="CE78" s="50"/>
       <c r="CF78" s="9" t="s">
         <v>11</v>
       </c>
@@ -14643,7 +14703,7 @@
       <c r="CP78" s="16"/>
     </row>
     <row r="79" spans="27:94">
-      <c r="AA79" s="49"/>
+      <c r="AA79" s="50"/>
       <c r="AB79" s="9" t="s">
         <v>12</v>
       </c>
@@ -14657,7 +14717,7 @@
       <c r="AJ79" s="16"/>
       <c r="AK79" s="15"/>
       <c r="AL79" s="16"/>
-      <c r="AO79" s="49"/>
+      <c r="AO79" s="50"/>
       <c r="AP79" s="9" t="s">
         <v>12</v>
       </c>
@@ -14671,7 +14731,7 @@
       <c r="AX79" s="16"/>
       <c r="AY79" s="15"/>
       <c r="AZ79" s="16"/>
-      <c r="BC79" s="49"/>
+      <c r="BC79" s="50"/>
       <c r="BD79" s="9" t="s">
         <v>12</v>
       </c>
@@ -14685,7 +14745,7 @@
       <c r="BL79" s="16"/>
       <c r="BM79" s="15"/>
       <c r="BN79" s="16"/>
-      <c r="BQ79" s="49"/>
+      <c r="BQ79" s="50"/>
       <c r="BR79" s="9" t="s">
         <v>12</v>
       </c>
@@ -14699,7 +14759,7 @@
       <c r="BZ79" s="16"/>
       <c r="CA79" s="15"/>
       <c r="CB79" s="16"/>
-      <c r="CE79" s="49"/>
+      <c r="CE79" s="50"/>
       <c r="CF79" s="9" t="s">
         <v>12</v>
       </c>
@@ -14715,7 +14775,7 @@
       <c r="CP79" s="16"/>
     </row>
     <row r="80" spans="27:94" ht="15" thickBot="1">
-      <c r="AA80" s="50"/>
+      <c r="AA80" s="51"/>
       <c r="AB80" s="10" t="s">
         <v>14</v>
       </c>
@@ -14729,7 +14789,7 @@
       <c r="AJ80" s="22"/>
       <c r="AK80" s="21"/>
       <c r="AL80" s="22"/>
-      <c r="AO80" s="50"/>
+      <c r="AO80" s="51"/>
       <c r="AP80" s="10" t="s">
         <v>14</v>
       </c>
@@ -14743,7 +14803,7 @@
       <c r="AX80" s="22"/>
       <c r="AY80" s="21"/>
       <c r="AZ80" s="22"/>
-      <c r="BC80" s="50"/>
+      <c r="BC80" s="51"/>
       <c r="BD80" s="10" t="s">
         <v>14</v>
       </c>
@@ -14757,7 +14817,7 @@
       <c r="BL80" s="22"/>
       <c r="BM80" s="21"/>
       <c r="BN80" s="22"/>
-      <c r="BQ80" s="50"/>
+      <c r="BQ80" s="51"/>
       <c r="BR80" s="10" t="s">
         <v>14</v>
       </c>
@@ -14771,7 +14831,7 @@
       <c r="BZ80" s="22"/>
       <c r="CA80" s="21"/>
       <c r="CB80" s="22"/>
-      <c r="CE80" s="50"/>
+      <c r="CE80" s="51"/>
       <c r="CF80" s="10" t="s">
         <v>14</v>
       </c>
@@ -14788,198 +14848,198 @@
     </row>
     <row r="82" spans="27:94" ht="15" thickBot="1"/>
     <row r="83" spans="27:94" ht="15" thickBot="1">
-      <c r="AA83" s="45" t="s">
+      <c r="AA83" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="AB83" s="46"/>
-      <c r="AC83" s="46"/>
-      <c r="AD83" s="46"/>
-      <c r="AE83" s="46"/>
-      <c r="AF83" s="46"/>
-      <c r="AG83" s="46"/>
-      <c r="AH83" s="46"/>
-      <c r="AI83" s="46"/>
-      <c r="AJ83" s="46"/>
-      <c r="AK83" s="46"/>
-      <c r="AL83" s="47"/>
-      <c r="AO83" s="45" t="s">
+      <c r="AB83" s="52"/>
+      <c r="AC83" s="52"/>
+      <c r="AD83" s="52"/>
+      <c r="AE83" s="52"/>
+      <c r="AF83" s="52"/>
+      <c r="AG83" s="52"/>
+      <c r="AH83" s="52"/>
+      <c r="AI83" s="52"/>
+      <c r="AJ83" s="52"/>
+      <c r="AK83" s="52"/>
+      <c r="AL83" s="53"/>
+      <c r="AO83" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="AP83" s="46"/>
-      <c r="AQ83" s="46"/>
-      <c r="AR83" s="46"/>
-      <c r="AS83" s="46"/>
-      <c r="AT83" s="46"/>
-      <c r="AU83" s="46"/>
-      <c r="AV83" s="46"/>
-      <c r="AW83" s="46"/>
-      <c r="AX83" s="46"/>
-      <c r="AY83" s="46"/>
-      <c r="AZ83" s="47"/>
-      <c r="BC83" s="45" t="s">
+      <c r="AP83" s="52"/>
+      <c r="AQ83" s="52"/>
+      <c r="AR83" s="52"/>
+      <c r="AS83" s="52"/>
+      <c r="AT83" s="52"/>
+      <c r="AU83" s="52"/>
+      <c r="AV83" s="52"/>
+      <c r="AW83" s="52"/>
+      <c r="AX83" s="52"/>
+      <c r="AY83" s="52"/>
+      <c r="AZ83" s="53"/>
+      <c r="BC83" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="BD83" s="46"/>
-      <c r="BE83" s="46"/>
-      <c r="BF83" s="46"/>
-      <c r="BG83" s="46"/>
-      <c r="BH83" s="46"/>
-      <c r="BI83" s="46"/>
-      <c r="BJ83" s="46"/>
-      <c r="BK83" s="46"/>
-      <c r="BL83" s="46"/>
-      <c r="BM83" s="46"/>
-      <c r="BN83" s="47"/>
-      <c r="BQ83" s="45" t="s">
+      <c r="BD83" s="52"/>
+      <c r="BE83" s="52"/>
+      <c r="BF83" s="52"/>
+      <c r="BG83" s="52"/>
+      <c r="BH83" s="52"/>
+      <c r="BI83" s="52"/>
+      <c r="BJ83" s="52"/>
+      <c r="BK83" s="52"/>
+      <c r="BL83" s="52"/>
+      <c r="BM83" s="52"/>
+      <c r="BN83" s="53"/>
+      <c r="BQ83" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="BR83" s="46"/>
-      <c r="BS83" s="46"/>
-      <c r="BT83" s="46"/>
-      <c r="BU83" s="46"/>
-      <c r="BV83" s="46"/>
-      <c r="BW83" s="46"/>
-      <c r="BX83" s="46"/>
-      <c r="BY83" s="46"/>
-      <c r="BZ83" s="46"/>
-      <c r="CA83" s="46"/>
-      <c r="CB83" s="47"/>
-      <c r="CE83" s="45" t="s">
+      <c r="BR83" s="52"/>
+      <c r="BS83" s="52"/>
+      <c r="BT83" s="52"/>
+      <c r="BU83" s="52"/>
+      <c r="BV83" s="52"/>
+      <c r="BW83" s="52"/>
+      <c r="BX83" s="52"/>
+      <c r="BY83" s="52"/>
+      <c r="BZ83" s="52"/>
+      <c r="CA83" s="52"/>
+      <c r="CB83" s="53"/>
+      <c r="CE83" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="CF83" s="46"/>
-      <c r="CG83" s="46"/>
-      <c r="CH83" s="46"/>
-      <c r="CI83" s="46"/>
-      <c r="CJ83" s="46"/>
-      <c r="CK83" s="46"/>
-      <c r="CL83" s="46"/>
-      <c r="CM83" s="46"/>
-      <c r="CN83" s="46"/>
-      <c r="CO83" s="46"/>
-      <c r="CP83" s="47"/>
+      <c r="CF83" s="52"/>
+      <c r="CG83" s="52"/>
+      <c r="CH83" s="52"/>
+      <c r="CI83" s="52"/>
+      <c r="CJ83" s="52"/>
+      <c r="CK83" s="52"/>
+      <c r="CL83" s="52"/>
+      <c r="CM83" s="52"/>
+      <c r="CN83" s="52"/>
+      <c r="CO83" s="52"/>
+      <c r="CP83" s="53"/>
     </row>
     <row r="84" spans="27:94" ht="15" thickBot="1">
       <c r="AA84" s="24"/>
       <c r="AB84" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="AC84" s="43" t="s">
+      <c r="AC84" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AD84" s="44"/>
-      <c r="AE84" s="43" t="s">
+      <c r="AD84" s="48"/>
+      <c r="AE84" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="AF84" s="44"/>
-      <c r="AG84" s="43" t="s">
+      <c r="AF84" s="48"/>
+      <c r="AG84" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="AH84" s="44"/>
-      <c r="AI84" s="43" t="s">
+      <c r="AH84" s="48"/>
+      <c r="AI84" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="AJ84" s="44"/>
-      <c r="AK84" s="43" t="s">
+      <c r="AJ84" s="48"/>
+      <c r="AK84" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="AL84" s="44"/>
+      <c r="AL84" s="48"/>
       <c r="AO84" s="24"/>
       <c r="AP84" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="AQ84" s="43" t="s">
+      <c r="AQ84" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AR84" s="44"/>
-      <c r="AS84" s="43" t="s">
+      <c r="AR84" s="48"/>
+      <c r="AS84" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="AT84" s="44"/>
-      <c r="AU84" s="43" t="s">
+      <c r="AT84" s="48"/>
+      <c r="AU84" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="AV84" s="44"/>
-      <c r="AW84" s="43" t="s">
+      <c r="AV84" s="48"/>
+      <c r="AW84" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="AX84" s="44"/>
-      <c r="AY84" s="43" t="s">
+      <c r="AX84" s="48"/>
+      <c r="AY84" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="AZ84" s="44"/>
+      <c r="AZ84" s="48"/>
       <c r="BC84" s="24"/>
       <c r="BD84" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="BE84" s="43" t="s">
+      <c r="BE84" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="BF84" s="44"/>
-      <c r="BG84" s="43" t="s">
+      <c r="BF84" s="48"/>
+      <c r="BG84" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="BH84" s="44"/>
-      <c r="BI84" s="43" t="s">
+      <c r="BH84" s="48"/>
+      <c r="BI84" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="BJ84" s="44"/>
-      <c r="BK84" s="43" t="s">
+      <c r="BJ84" s="48"/>
+      <c r="BK84" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="BL84" s="44"/>
-      <c r="BM84" s="43" t="s">
+      <c r="BL84" s="48"/>
+      <c r="BM84" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="BN84" s="44"/>
+      <c r="BN84" s="48"/>
       <c r="BQ84" s="24"/>
       <c r="BR84" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="BS84" s="43" t="s">
+      <c r="BS84" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="BT84" s="44"/>
-      <c r="BU84" s="43" t="s">
+      <c r="BT84" s="48"/>
+      <c r="BU84" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="BV84" s="44"/>
-      <c r="BW84" s="43" t="s">
+      <c r="BV84" s="48"/>
+      <c r="BW84" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="BX84" s="44"/>
-      <c r="BY84" s="43" t="s">
+      <c r="BX84" s="48"/>
+      <c r="BY84" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="BZ84" s="44"/>
-      <c r="CA84" s="43" t="s">
+      <c r="BZ84" s="48"/>
+      <c r="CA84" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="CB84" s="44"/>
+      <c r="CB84" s="48"/>
       <c r="CE84" s="24"/>
       <c r="CF84" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="CG84" s="43" t="s">
+      <c r="CG84" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="CH84" s="44"/>
-      <c r="CI84" s="43" t="s">
+      <c r="CH84" s="48"/>
+      <c r="CI84" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="CJ84" s="44"/>
-      <c r="CK84" s="43" t="s">
+      <c r="CJ84" s="48"/>
+      <c r="CK84" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="CL84" s="44"/>
-      <c r="CM84" s="43" t="s">
+      <c r="CL84" s="48"/>
+      <c r="CM84" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="CN84" s="44"/>
-      <c r="CO84" s="43" t="s">
+      <c r="CN84" s="48"/>
+      <c r="CO84" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="CP84" s="44"/>
+      <c r="CP84" s="48"/>
     </row>
     <row r="85" spans="27:94">
       <c r="AA85" s="25" t="s">
@@ -16674,71 +16734,336 @@
       <c r="AB107" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="AC107" s="39"/>
-      <c r="AD107" s="40"/>
-      <c r="AE107" s="39"/>
-      <c r="AF107" s="40"/>
-      <c r="AG107" s="41"/>
-      <c r="AH107" s="42"/>
-      <c r="AI107" s="39"/>
-      <c r="AJ107" s="40"/>
-      <c r="AK107" s="39"/>
-      <c r="AL107" s="40"/>
+      <c r="AC107" s="40"/>
+      <c r="AD107" s="41"/>
+      <c r="AE107" s="40"/>
+      <c r="AF107" s="41"/>
+      <c r="AG107" s="42"/>
+      <c r="AH107" s="43"/>
+      <c r="AI107" s="40"/>
+      <c r="AJ107" s="41"/>
+      <c r="AK107" s="40"/>
+      <c r="AL107" s="41"/>
       <c r="AP107" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="AQ107" s="39"/>
-      <c r="AR107" s="40"/>
-      <c r="AS107" s="39"/>
-      <c r="AT107" s="40"/>
-      <c r="AU107" s="41"/>
-      <c r="AV107" s="42"/>
-      <c r="AW107" s="39"/>
-      <c r="AX107" s="40"/>
-      <c r="AY107" s="39"/>
-      <c r="AZ107" s="40"/>
+      <c r="AQ107" s="40"/>
+      <c r="AR107" s="41"/>
+      <c r="AS107" s="40"/>
+      <c r="AT107" s="41"/>
+      <c r="AU107" s="42"/>
+      <c r="AV107" s="43"/>
+      <c r="AW107" s="40"/>
+      <c r="AX107" s="41"/>
+      <c r="AY107" s="40"/>
+      <c r="AZ107" s="41"/>
       <c r="BD107" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="BE107" s="39"/>
-      <c r="BF107" s="40"/>
-      <c r="BG107" s="39"/>
-      <c r="BH107" s="40"/>
-      <c r="BI107" s="41"/>
-      <c r="BJ107" s="42"/>
-      <c r="BK107" s="39"/>
-      <c r="BL107" s="40"/>
-      <c r="BM107" s="39"/>
-      <c r="BN107" s="40"/>
+      <c r="BE107" s="40"/>
+      <c r="BF107" s="41"/>
+      <c r="BG107" s="40"/>
+      <c r="BH107" s="41"/>
+      <c r="BI107" s="42"/>
+      <c r="BJ107" s="43"/>
+      <c r="BK107" s="40"/>
+      <c r="BL107" s="41"/>
+      <c r="BM107" s="40"/>
+      <c r="BN107" s="41"/>
       <c r="BR107" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="BS107" s="39"/>
-      <c r="BT107" s="40"/>
-      <c r="BU107" s="39"/>
-      <c r="BV107" s="40"/>
-      <c r="BW107" s="41"/>
-      <c r="BX107" s="42"/>
-      <c r="BY107" s="39"/>
-      <c r="BZ107" s="40"/>
-      <c r="CA107" s="39"/>
-      <c r="CB107" s="40"/>
+      <c r="BS107" s="40"/>
+      <c r="BT107" s="41"/>
+      <c r="BU107" s="40"/>
+      <c r="BV107" s="41"/>
+      <c r="BW107" s="42"/>
+      <c r="BX107" s="43"/>
+      <c r="BY107" s="40"/>
+      <c r="BZ107" s="41"/>
+      <c r="CA107" s="40"/>
+      <c r="CB107" s="41"/>
       <c r="CF107" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="CG107" s="39"/>
-      <c r="CH107" s="40"/>
-      <c r="CI107" s="39"/>
-      <c r="CJ107" s="40"/>
-      <c r="CK107" s="41"/>
-      <c r="CL107" s="42"/>
-      <c r="CM107" s="39"/>
-      <c r="CN107" s="40"/>
-      <c r="CO107" s="39"/>
-      <c r="CP107" s="40"/>
+      <c r="CG107" s="40"/>
+      <c r="CH107" s="41"/>
+      <c r="CI107" s="40"/>
+      <c r="CJ107" s="41"/>
+      <c r="CK107" s="42"/>
+      <c r="CL107" s="43"/>
+      <c r="CM107" s="40"/>
+      <c r="CN107" s="41"/>
+      <c r="CO107" s="40"/>
+      <c r="CP107" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="289">
+    <mergeCell ref="CO107:CP107"/>
+    <mergeCell ref="BS107:BT107"/>
+    <mergeCell ref="BU107:BV107"/>
+    <mergeCell ref="BW107:BX107"/>
+    <mergeCell ref="BY107:BZ107"/>
+    <mergeCell ref="CA107:CB107"/>
+    <mergeCell ref="AQ107:AR107"/>
+    <mergeCell ref="AS107:AT107"/>
+    <mergeCell ref="AU107:AV107"/>
+    <mergeCell ref="AW107:AX107"/>
+    <mergeCell ref="AY107:AZ107"/>
+    <mergeCell ref="CG107:CH107"/>
+    <mergeCell ref="CI107:CJ107"/>
+    <mergeCell ref="CK107:CL107"/>
+    <mergeCell ref="CM107:CN107"/>
+    <mergeCell ref="AC107:AD107"/>
+    <mergeCell ref="AE107:AF107"/>
+    <mergeCell ref="AG107:AH107"/>
+    <mergeCell ref="AI107:AJ107"/>
+    <mergeCell ref="AK107:AL107"/>
+    <mergeCell ref="CG84:CH84"/>
+    <mergeCell ref="CI84:CJ84"/>
+    <mergeCell ref="CK84:CL84"/>
+    <mergeCell ref="CM84:CN84"/>
+    <mergeCell ref="AQ84:AR84"/>
+    <mergeCell ref="AS84:AT84"/>
+    <mergeCell ref="AU84:AV84"/>
+    <mergeCell ref="AW84:AX84"/>
+    <mergeCell ref="AY84:AZ84"/>
+    <mergeCell ref="AC84:AD84"/>
+    <mergeCell ref="AE84:AF84"/>
+    <mergeCell ref="AG84:AH84"/>
+    <mergeCell ref="AI84:AJ84"/>
+    <mergeCell ref="AK84:AL84"/>
+    <mergeCell ref="BE107:BF107"/>
+    <mergeCell ref="BG107:BH107"/>
+    <mergeCell ref="BI107:BJ107"/>
+    <mergeCell ref="BK107:BL107"/>
+    <mergeCell ref="BM107:BN107"/>
+    <mergeCell ref="CO84:CP84"/>
+    <mergeCell ref="BS84:BT84"/>
+    <mergeCell ref="BU84:BV84"/>
+    <mergeCell ref="BW84:BX84"/>
+    <mergeCell ref="BY84:BZ84"/>
+    <mergeCell ref="CA84:CB84"/>
+    <mergeCell ref="BE84:BF84"/>
+    <mergeCell ref="BG84:BH84"/>
+    <mergeCell ref="BI84:BJ84"/>
+    <mergeCell ref="BK84:BL84"/>
+    <mergeCell ref="BM84:BN84"/>
+    <mergeCell ref="AA83:AL83"/>
+    <mergeCell ref="AO83:AZ83"/>
+    <mergeCell ref="BC83:BN83"/>
+    <mergeCell ref="BQ83:CB83"/>
+    <mergeCell ref="CE83:CP83"/>
+    <mergeCell ref="AA77:AA80"/>
+    <mergeCell ref="AO77:AO80"/>
+    <mergeCell ref="BC77:BC80"/>
+    <mergeCell ref="BQ77:BQ80"/>
+    <mergeCell ref="CE77:CE80"/>
+    <mergeCell ref="CG75:CH75"/>
+    <mergeCell ref="CI75:CJ75"/>
+    <mergeCell ref="CK75:CL75"/>
+    <mergeCell ref="CM75:CN75"/>
+    <mergeCell ref="CO75:CP75"/>
+    <mergeCell ref="BS75:BT75"/>
+    <mergeCell ref="BU75:BV75"/>
+    <mergeCell ref="BW75:BX75"/>
+    <mergeCell ref="BY75:BZ75"/>
+    <mergeCell ref="CA75:CB75"/>
+    <mergeCell ref="AC75:AD75"/>
+    <mergeCell ref="AE75:AF75"/>
+    <mergeCell ref="AG75:AH75"/>
+    <mergeCell ref="AI75:AJ75"/>
+    <mergeCell ref="AK75:AL75"/>
+    <mergeCell ref="AA74:AL74"/>
+    <mergeCell ref="AO74:AZ74"/>
+    <mergeCell ref="BC74:BN74"/>
+    <mergeCell ref="BQ74:CB74"/>
+    <mergeCell ref="BE75:BF75"/>
+    <mergeCell ref="BG75:BH75"/>
+    <mergeCell ref="BI75:BJ75"/>
+    <mergeCell ref="BK75:BL75"/>
+    <mergeCell ref="BM75:BN75"/>
+    <mergeCell ref="AQ75:AR75"/>
+    <mergeCell ref="AS75:AT75"/>
+    <mergeCell ref="AU75:AV75"/>
+    <mergeCell ref="AW75:AX75"/>
+    <mergeCell ref="AY75:AZ75"/>
+    <mergeCell ref="AQ71:AR71"/>
+    <mergeCell ref="AS71:AT71"/>
+    <mergeCell ref="AU71:AV71"/>
+    <mergeCell ref="AW71:AX71"/>
+    <mergeCell ref="AY71:AZ71"/>
+    <mergeCell ref="CE74:CP74"/>
+    <mergeCell ref="CG71:CH71"/>
+    <mergeCell ref="CI71:CJ71"/>
+    <mergeCell ref="CK71:CL71"/>
+    <mergeCell ref="CM71:CN71"/>
+    <mergeCell ref="CO71:CP71"/>
+    <mergeCell ref="BS71:BT71"/>
+    <mergeCell ref="BU71:BV71"/>
+    <mergeCell ref="BW71:BX71"/>
+    <mergeCell ref="BY71:BZ71"/>
+    <mergeCell ref="CA71:CB71"/>
+    <mergeCell ref="AC71:AD71"/>
+    <mergeCell ref="AE71:AF71"/>
+    <mergeCell ref="AG71:AH71"/>
+    <mergeCell ref="AI71:AJ71"/>
+    <mergeCell ref="AK71:AL71"/>
+    <mergeCell ref="CG48:CH48"/>
+    <mergeCell ref="CI48:CJ48"/>
+    <mergeCell ref="CK48:CL48"/>
+    <mergeCell ref="CM48:CN48"/>
+    <mergeCell ref="AQ48:AR48"/>
+    <mergeCell ref="AS48:AT48"/>
+    <mergeCell ref="AU48:AV48"/>
+    <mergeCell ref="AW48:AX48"/>
+    <mergeCell ref="AY48:AZ48"/>
+    <mergeCell ref="AC48:AD48"/>
+    <mergeCell ref="AE48:AF48"/>
+    <mergeCell ref="AG48:AH48"/>
+    <mergeCell ref="AI48:AJ48"/>
+    <mergeCell ref="AK48:AL48"/>
+    <mergeCell ref="BE71:BF71"/>
+    <mergeCell ref="BG71:BH71"/>
+    <mergeCell ref="BI71:BJ71"/>
+    <mergeCell ref="BK71:BL71"/>
+    <mergeCell ref="BM71:BN71"/>
+    <mergeCell ref="CO48:CP48"/>
+    <mergeCell ref="BS48:BT48"/>
+    <mergeCell ref="BU48:BV48"/>
+    <mergeCell ref="BW48:BX48"/>
+    <mergeCell ref="BY48:BZ48"/>
+    <mergeCell ref="CA48:CB48"/>
+    <mergeCell ref="BE48:BF48"/>
+    <mergeCell ref="BG48:BH48"/>
+    <mergeCell ref="BI48:BJ48"/>
+    <mergeCell ref="BK48:BL48"/>
+    <mergeCell ref="BM48:BN48"/>
+    <mergeCell ref="AA47:AL47"/>
+    <mergeCell ref="AO47:AZ47"/>
+    <mergeCell ref="BC47:BN47"/>
+    <mergeCell ref="BQ47:CB47"/>
+    <mergeCell ref="CE47:CP47"/>
+    <mergeCell ref="AA41:AA44"/>
+    <mergeCell ref="AO41:AO44"/>
+    <mergeCell ref="BC41:BC44"/>
+    <mergeCell ref="BQ41:BQ44"/>
+    <mergeCell ref="CE41:CE44"/>
+    <mergeCell ref="CG39:CH39"/>
+    <mergeCell ref="CI39:CJ39"/>
+    <mergeCell ref="CK39:CL39"/>
+    <mergeCell ref="CM39:CN39"/>
+    <mergeCell ref="CO39:CP39"/>
+    <mergeCell ref="BS39:BT39"/>
+    <mergeCell ref="BU39:BV39"/>
+    <mergeCell ref="BW39:BX39"/>
+    <mergeCell ref="BY39:BZ39"/>
+    <mergeCell ref="CA39:CB39"/>
+    <mergeCell ref="AC39:AD39"/>
+    <mergeCell ref="AE39:AF39"/>
+    <mergeCell ref="AG39:AH39"/>
+    <mergeCell ref="AI39:AJ39"/>
+    <mergeCell ref="AK39:AL39"/>
+    <mergeCell ref="AA38:AL38"/>
+    <mergeCell ref="AO38:AZ38"/>
+    <mergeCell ref="BC38:BN38"/>
+    <mergeCell ref="BQ38:CB38"/>
+    <mergeCell ref="BE39:BF39"/>
+    <mergeCell ref="BG39:BH39"/>
+    <mergeCell ref="BI39:BJ39"/>
+    <mergeCell ref="BK39:BL39"/>
+    <mergeCell ref="BM39:BN39"/>
+    <mergeCell ref="AQ39:AR39"/>
+    <mergeCell ref="AS39:AT39"/>
+    <mergeCell ref="AU39:AV39"/>
+    <mergeCell ref="AW39:AX39"/>
+    <mergeCell ref="AY39:AZ39"/>
+    <mergeCell ref="CE38:CP38"/>
+    <mergeCell ref="CG35:CH35"/>
+    <mergeCell ref="CI35:CJ35"/>
+    <mergeCell ref="CK35:CL35"/>
+    <mergeCell ref="CM35:CN35"/>
+    <mergeCell ref="CO35:CP35"/>
+    <mergeCell ref="CE5:CE8"/>
+    <mergeCell ref="CE11:CP11"/>
+    <mergeCell ref="CG12:CH12"/>
+    <mergeCell ref="CI12:CJ12"/>
+    <mergeCell ref="CK12:CL12"/>
+    <mergeCell ref="CM12:CN12"/>
+    <mergeCell ref="CO12:CP12"/>
+    <mergeCell ref="CE2:CP2"/>
+    <mergeCell ref="CG3:CH3"/>
+    <mergeCell ref="CI3:CJ3"/>
+    <mergeCell ref="CK3:CL3"/>
+    <mergeCell ref="CM3:CN3"/>
+    <mergeCell ref="CO3:CP3"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="AA2:AL2"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="AG3:AH3"/>
+    <mergeCell ref="AI3:AJ3"/>
+    <mergeCell ref="AK3:AL3"/>
+    <mergeCell ref="AA5:AA8"/>
+    <mergeCell ref="AA11:AL11"/>
+    <mergeCell ref="AC12:AD12"/>
+    <mergeCell ref="AE12:AF12"/>
+    <mergeCell ref="AG12:AH12"/>
+    <mergeCell ref="AI12:AJ12"/>
+    <mergeCell ref="AK12:AL12"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="B14:M14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="AC35:AD35"/>
+    <mergeCell ref="AE35:AF35"/>
+    <mergeCell ref="AG35:AH35"/>
+    <mergeCell ref="AI35:AJ35"/>
+    <mergeCell ref="AK35:AL35"/>
+    <mergeCell ref="AO2:AZ2"/>
+    <mergeCell ref="AQ3:AR3"/>
+    <mergeCell ref="AS3:AT3"/>
+    <mergeCell ref="AU3:AV3"/>
+    <mergeCell ref="AW3:AX3"/>
+    <mergeCell ref="AY3:AZ3"/>
+    <mergeCell ref="AO5:AO8"/>
+    <mergeCell ref="AO11:AZ11"/>
+    <mergeCell ref="AQ12:AR12"/>
+    <mergeCell ref="AS12:AT12"/>
+    <mergeCell ref="AU12:AV12"/>
+    <mergeCell ref="AW12:AX12"/>
+    <mergeCell ref="AY12:AZ12"/>
+    <mergeCell ref="AQ35:AR35"/>
+    <mergeCell ref="AS35:AT35"/>
+    <mergeCell ref="AU35:AV35"/>
+    <mergeCell ref="AW35:AX35"/>
+    <mergeCell ref="AY35:AZ35"/>
+    <mergeCell ref="BE3:BF3"/>
+    <mergeCell ref="BG3:BH3"/>
+    <mergeCell ref="BI3:BJ3"/>
+    <mergeCell ref="BK3:BL3"/>
+    <mergeCell ref="BM3:BN3"/>
+    <mergeCell ref="BC5:BC8"/>
+    <mergeCell ref="BC11:BN11"/>
+    <mergeCell ref="BE12:BF12"/>
+    <mergeCell ref="BG12:BH12"/>
+    <mergeCell ref="BI12:BJ12"/>
+    <mergeCell ref="BK12:BL12"/>
+    <mergeCell ref="BM12:BN12"/>
     <mergeCell ref="BE35:BF35"/>
     <mergeCell ref="BG35:BH35"/>
     <mergeCell ref="BI35:BJ35"/>
@@ -16763,271 +17088,6 @@
     <mergeCell ref="BY35:BZ35"/>
     <mergeCell ref="CA35:CB35"/>
     <mergeCell ref="BC2:BN2"/>
-    <mergeCell ref="BE3:BF3"/>
-    <mergeCell ref="BG3:BH3"/>
-    <mergeCell ref="BI3:BJ3"/>
-    <mergeCell ref="BK3:BL3"/>
-    <mergeCell ref="BM3:BN3"/>
-    <mergeCell ref="BC5:BC8"/>
-    <mergeCell ref="BC11:BN11"/>
-    <mergeCell ref="BE12:BF12"/>
-    <mergeCell ref="BG12:BH12"/>
-    <mergeCell ref="BI12:BJ12"/>
-    <mergeCell ref="BK12:BL12"/>
-    <mergeCell ref="BM12:BN12"/>
-    <mergeCell ref="AC35:AD35"/>
-    <mergeCell ref="AE35:AF35"/>
-    <mergeCell ref="AG35:AH35"/>
-    <mergeCell ref="AI35:AJ35"/>
-    <mergeCell ref="AK35:AL35"/>
-    <mergeCell ref="AO2:AZ2"/>
-    <mergeCell ref="AQ3:AR3"/>
-    <mergeCell ref="AS3:AT3"/>
-    <mergeCell ref="AU3:AV3"/>
-    <mergeCell ref="AW3:AX3"/>
-    <mergeCell ref="AY3:AZ3"/>
-    <mergeCell ref="AO5:AO8"/>
-    <mergeCell ref="AO11:AZ11"/>
-    <mergeCell ref="AQ12:AR12"/>
-    <mergeCell ref="AS12:AT12"/>
-    <mergeCell ref="AU12:AV12"/>
-    <mergeCell ref="AW12:AX12"/>
-    <mergeCell ref="AY12:AZ12"/>
-    <mergeCell ref="AQ35:AR35"/>
-    <mergeCell ref="AS35:AT35"/>
-    <mergeCell ref="AU35:AV35"/>
-    <mergeCell ref="AW35:AX35"/>
-    <mergeCell ref="AY35:AZ35"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="B14:M14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="CE2:CP2"/>
-    <mergeCell ref="CG3:CH3"/>
-    <mergeCell ref="CI3:CJ3"/>
-    <mergeCell ref="CK3:CL3"/>
-    <mergeCell ref="CM3:CN3"/>
-    <mergeCell ref="CO3:CP3"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="AA2:AL2"/>
-    <mergeCell ref="AC3:AD3"/>
-    <mergeCell ref="AE3:AF3"/>
-    <mergeCell ref="AG3:AH3"/>
-    <mergeCell ref="AI3:AJ3"/>
-    <mergeCell ref="AK3:AL3"/>
-    <mergeCell ref="AA5:AA8"/>
-    <mergeCell ref="AA11:AL11"/>
-    <mergeCell ref="AC12:AD12"/>
-    <mergeCell ref="AE12:AF12"/>
-    <mergeCell ref="AG12:AH12"/>
-    <mergeCell ref="AI12:AJ12"/>
-    <mergeCell ref="AK12:AL12"/>
-    <mergeCell ref="CE38:CP38"/>
-    <mergeCell ref="CG35:CH35"/>
-    <mergeCell ref="CI35:CJ35"/>
-    <mergeCell ref="CK35:CL35"/>
-    <mergeCell ref="CM35:CN35"/>
-    <mergeCell ref="CO35:CP35"/>
-    <mergeCell ref="CE5:CE8"/>
-    <mergeCell ref="CE11:CP11"/>
-    <mergeCell ref="CG12:CH12"/>
-    <mergeCell ref="CI12:CJ12"/>
-    <mergeCell ref="CK12:CL12"/>
-    <mergeCell ref="CM12:CN12"/>
-    <mergeCell ref="CO12:CP12"/>
-    <mergeCell ref="AC39:AD39"/>
-    <mergeCell ref="AE39:AF39"/>
-    <mergeCell ref="AG39:AH39"/>
-    <mergeCell ref="AI39:AJ39"/>
-    <mergeCell ref="AK39:AL39"/>
-    <mergeCell ref="AA38:AL38"/>
-    <mergeCell ref="AO38:AZ38"/>
-    <mergeCell ref="BC38:BN38"/>
-    <mergeCell ref="BQ38:CB38"/>
-    <mergeCell ref="BE39:BF39"/>
-    <mergeCell ref="BG39:BH39"/>
-    <mergeCell ref="BI39:BJ39"/>
-    <mergeCell ref="BK39:BL39"/>
-    <mergeCell ref="BM39:BN39"/>
-    <mergeCell ref="AQ39:AR39"/>
-    <mergeCell ref="AS39:AT39"/>
-    <mergeCell ref="AU39:AV39"/>
-    <mergeCell ref="AW39:AX39"/>
-    <mergeCell ref="AY39:AZ39"/>
-    <mergeCell ref="CG39:CH39"/>
-    <mergeCell ref="CI39:CJ39"/>
-    <mergeCell ref="CK39:CL39"/>
-    <mergeCell ref="CM39:CN39"/>
-    <mergeCell ref="CO39:CP39"/>
-    <mergeCell ref="BS39:BT39"/>
-    <mergeCell ref="BU39:BV39"/>
-    <mergeCell ref="BW39:BX39"/>
-    <mergeCell ref="BY39:BZ39"/>
-    <mergeCell ref="CA39:CB39"/>
-    <mergeCell ref="AA47:AL47"/>
-    <mergeCell ref="AO47:AZ47"/>
-    <mergeCell ref="BC47:BN47"/>
-    <mergeCell ref="BQ47:CB47"/>
-    <mergeCell ref="CE47:CP47"/>
-    <mergeCell ref="AA41:AA44"/>
-    <mergeCell ref="AO41:AO44"/>
-    <mergeCell ref="BC41:BC44"/>
-    <mergeCell ref="BQ41:BQ44"/>
-    <mergeCell ref="CE41:CE44"/>
-    <mergeCell ref="CO48:CP48"/>
-    <mergeCell ref="BS48:BT48"/>
-    <mergeCell ref="BU48:BV48"/>
-    <mergeCell ref="BW48:BX48"/>
-    <mergeCell ref="BY48:BZ48"/>
-    <mergeCell ref="CA48:CB48"/>
-    <mergeCell ref="BE48:BF48"/>
-    <mergeCell ref="BG48:BH48"/>
-    <mergeCell ref="BI48:BJ48"/>
-    <mergeCell ref="BK48:BL48"/>
-    <mergeCell ref="BM48:BN48"/>
-    <mergeCell ref="AC71:AD71"/>
-    <mergeCell ref="AE71:AF71"/>
-    <mergeCell ref="AG71:AH71"/>
-    <mergeCell ref="AI71:AJ71"/>
-    <mergeCell ref="AK71:AL71"/>
-    <mergeCell ref="CG48:CH48"/>
-    <mergeCell ref="CI48:CJ48"/>
-    <mergeCell ref="CK48:CL48"/>
-    <mergeCell ref="CM48:CN48"/>
-    <mergeCell ref="AQ48:AR48"/>
-    <mergeCell ref="AS48:AT48"/>
-    <mergeCell ref="AU48:AV48"/>
-    <mergeCell ref="AW48:AX48"/>
-    <mergeCell ref="AY48:AZ48"/>
-    <mergeCell ref="AC48:AD48"/>
-    <mergeCell ref="AE48:AF48"/>
-    <mergeCell ref="AG48:AH48"/>
-    <mergeCell ref="AI48:AJ48"/>
-    <mergeCell ref="AK48:AL48"/>
-    <mergeCell ref="BE71:BF71"/>
-    <mergeCell ref="BG71:BH71"/>
-    <mergeCell ref="BI71:BJ71"/>
-    <mergeCell ref="BK71:BL71"/>
-    <mergeCell ref="BM71:BN71"/>
-    <mergeCell ref="AQ71:AR71"/>
-    <mergeCell ref="AS71:AT71"/>
-    <mergeCell ref="AU71:AV71"/>
-    <mergeCell ref="AW71:AX71"/>
-    <mergeCell ref="AY71:AZ71"/>
-    <mergeCell ref="CE74:CP74"/>
-    <mergeCell ref="CG71:CH71"/>
-    <mergeCell ref="CI71:CJ71"/>
-    <mergeCell ref="CK71:CL71"/>
-    <mergeCell ref="CM71:CN71"/>
-    <mergeCell ref="CO71:CP71"/>
-    <mergeCell ref="BS71:BT71"/>
-    <mergeCell ref="BU71:BV71"/>
-    <mergeCell ref="BW71:BX71"/>
-    <mergeCell ref="BY71:BZ71"/>
-    <mergeCell ref="CA71:CB71"/>
-    <mergeCell ref="AC75:AD75"/>
-    <mergeCell ref="AE75:AF75"/>
-    <mergeCell ref="AG75:AH75"/>
-    <mergeCell ref="AI75:AJ75"/>
-    <mergeCell ref="AK75:AL75"/>
-    <mergeCell ref="AA74:AL74"/>
-    <mergeCell ref="AO74:AZ74"/>
-    <mergeCell ref="BC74:BN74"/>
-    <mergeCell ref="BQ74:CB74"/>
-    <mergeCell ref="BE75:BF75"/>
-    <mergeCell ref="BG75:BH75"/>
-    <mergeCell ref="BI75:BJ75"/>
-    <mergeCell ref="BK75:BL75"/>
-    <mergeCell ref="BM75:BN75"/>
-    <mergeCell ref="AQ75:AR75"/>
-    <mergeCell ref="AS75:AT75"/>
-    <mergeCell ref="AU75:AV75"/>
-    <mergeCell ref="AW75:AX75"/>
-    <mergeCell ref="AY75:AZ75"/>
-    <mergeCell ref="CG75:CH75"/>
-    <mergeCell ref="CI75:CJ75"/>
-    <mergeCell ref="CK75:CL75"/>
-    <mergeCell ref="CM75:CN75"/>
-    <mergeCell ref="CO75:CP75"/>
-    <mergeCell ref="BS75:BT75"/>
-    <mergeCell ref="BU75:BV75"/>
-    <mergeCell ref="BW75:BX75"/>
-    <mergeCell ref="BY75:BZ75"/>
-    <mergeCell ref="CA75:CB75"/>
-    <mergeCell ref="AA83:AL83"/>
-    <mergeCell ref="AO83:AZ83"/>
-    <mergeCell ref="BC83:BN83"/>
-    <mergeCell ref="BQ83:CB83"/>
-    <mergeCell ref="CE83:CP83"/>
-    <mergeCell ref="AA77:AA80"/>
-    <mergeCell ref="AO77:AO80"/>
-    <mergeCell ref="BC77:BC80"/>
-    <mergeCell ref="BQ77:BQ80"/>
-    <mergeCell ref="CE77:CE80"/>
-    <mergeCell ref="CO84:CP84"/>
-    <mergeCell ref="BS84:BT84"/>
-    <mergeCell ref="BU84:BV84"/>
-    <mergeCell ref="BW84:BX84"/>
-    <mergeCell ref="BY84:BZ84"/>
-    <mergeCell ref="CA84:CB84"/>
-    <mergeCell ref="BE84:BF84"/>
-    <mergeCell ref="BG84:BH84"/>
-    <mergeCell ref="BI84:BJ84"/>
-    <mergeCell ref="BK84:BL84"/>
-    <mergeCell ref="BM84:BN84"/>
-    <mergeCell ref="AC107:AD107"/>
-    <mergeCell ref="AE107:AF107"/>
-    <mergeCell ref="AG107:AH107"/>
-    <mergeCell ref="AI107:AJ107"/>
-    <mergeCell ref="AK107:AL107"/>
-    <mergeCell ref="CG84:CH84"/>
-    <mergeCell ref="CI84:CJ84"/>
-    <mergeCell ref="CK84:CL84"/>
-    <mergeCell ref="CM84:CN84"/>
-    <mergeCell ref="AQ84:AR84"/>
-    <mergeCell ref="AS84:AT84"/>
-    <mergeCell ref="AU84:AV84"/>
-    <mergeCell ref="AW84:AX84"/>
-    <mergeCell ref="AY84:AZ84"/>
-    <mergeCell ref="AC84:AD84"/>
-    <mergeCell ref="AE84:AF84"/>
-    <mergeCell ref="AG84:AH84"/>
-    <mergeCell ref="AI84:AJ84"/>
-    <mergeCell ref="AK84:AL84"/>
-    <mergeCell ref="BE107:BF107"/>
-    <mergeCell ref="BG107:BH107"/>
-    <mergeCell ref="BI107:BJ107"/>
-    <mergeCell ref="BK107:BL107"/>
-    <mergeCell ref="BM107:BN107"/>
-    <mergeCell ref="CO107:CP107"/>
-    <mergeCell ref="BS107:BT107"/>
-    <mergeCell ref="BU107:BV107"/>
-    <mergeCell ref="BW107:BX107"/>
-    <mergeCell ref="BY107:BZ107"/>
-    <mergeCell ref="CA107:CB107"/>
-    <mergeCell ref="AQ107:AR107"/>
-    <mergeCell ref="AS107:AT107"/>
-    <mergeCell ref="AU107:AV107"/>
-    <mergeCell ref="AW107:AX107"/>
-    <mergeCell ref="AY107:AZ107"/>
-    <mergeCell ref="CG107:CH107"/>
-    <mergeCell ref="CI107:CJ107"/>
-    <mergeCell ref="CK107:CL107"/>
-    <mergeCell ref="CM107:CN107"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Results_metrics.xlsx
+++ b/Results_metrics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10608"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a8875455940b8c0f/Desktop/UNI/MACHINE LEARNING/Progetto/MaskArchitectureAnomaly_CourseProject/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ludovicascaffidi/Desktop/Università/Magistrale/Secondo Anno/Secondo Semestre/Machine Learning for Mathematical Engineering/Progetto/MaskArchitectureAnomaly_CourseProject/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:1_{E602311C-DCBC-F649-AD7D-8F8F41C583C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EBE5BF3-B6C8-43B3-B470-1E5D71C6A754}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D22808C4-6D33-5445-B624-8E0512D477B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -756,19 +756,19 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -780,10 +780,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1536,7 +1536,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1544,6 +1543,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2305,7 +2305,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2313,6 +2312,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2584,6 +2584,9 @@
                 <c:pt idx="13">
                   <c:v>28.74</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>28.91</c:v>
+                </c:pt>
                 <c:pt idx="15">
                   <c:v>28.98</c:v>
                 </c:pt>
@@ -2768,6 +2771,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>29.06</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>59.36</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>59.98</c:v>
@@ -3068,7 +3074,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3076,6 +3081,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3837,7 +3843,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3845,6 +3850,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4570,7 +4576,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4578,6 +4583,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7520,10 +7526,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -7788,249 +7790,249 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:CP107"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="14.453125" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" customWidth="1"/>
-    <col min="28" max="28" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5" customWidth="1"/>
+    <col min="3" max="3" width="13.1640625" customWidth="1"/>
+    <col min="28" max="28" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:94" ht="15" thickBot="1"/>
-    <row r="2" spans="2:94" ht="15" thickBot="1">
-      <c r="B2" s="44" t="s">
+    <row r="1" spans="2:94" ht="16" thickBot="1"/>
+    <row r="2" spans="2:94" ht="16" thickBot="1">
+      <c r="B2" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="46"/>
-      <c r="AA2" s="44" t="s">
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="53"/>
+      <c r="AA2" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="AB2" s="45"/>
-      <c r="AC2" s="45"/>
-      <c r="AD2" s="45"/>
-      <c r="AE2" s="45"/>
-      <c r="AF2" s="45"/>
-      <c r="AG2" s="45"/>
-      <c r="AH2" s="45"/>
-      <c r="AI2" s="45"/>
-      <c r="AJ2" s="45"/>
-      <c r="AK2" s="45"/>
-      <c r="AL2" s="46"/>
-      <c r="AO2" s="44" t="s">
+      <c r="AB2" s="52"/>
+      <c r="AC2" s="52"/>
+      <c r="AD2" s="52"/>
+      <c r="AE2" s="52"/>
+      <c r="AF2" s="52"/>
+      <c r="AG2" s="52"/>
+      <c r="AH2" s="52"/>
+      <c r="AI2" s="52"/>
+      <c r="AJ2" s="52"/>
+      <c r="AK2" s="52"/>
+      <c r="AL2" s="53"/>
+      <c r="AO2" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="AP2" s="45"/>
-      <c r="AQ2" s="45"/>
-      <c r="AR2" s="45"/>
-      <c r="AS2" s="45"/>
-      <c r="AT2" s="45"/>
-      <c r="AU2" s="45"/>
-      <c r="AV2" s="45"/>
-      <c r="AW2" s="45"/>
-      <c r="AX2" s="45"/>
-      <c r="AY2" s="45"/>
-      <c r="AZ2" s="46"/>
-      <c r="BC2" s="44" t="s">
+      <c r="AP2" s="52"/>
+      <c r="AQ2" s="52"/>
+      <c r="AR2" s="52"/>
+      <c r="AS2" s="52"/>
+      <c r="AT2" s="52"/>
+      <c r="AU2" s="52"/>
+      <c r="AV2" s="52"/>
+      <c r="AW2" s="52"/>
+      <c r="AX2" s="52"/>
+      <c r="AY2" s="52"/>
+      <c r="AZ2" s="53"/>
+      <c r="BC2" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="BD2" s="45"/>
-      <c r="BE2" s="45"/>
-      <c r="BF2" s="45"/>
-      <c r="BG2" s="45"/>
-      <c r="BH2" s="45"/>
-      <c r="BI2" s="45"/>
-      <c r="BJ2" s="45"/>
-      <c r="BK2" s="45"/>
-      <c r="BL2" s="45"/>
-      <c r="BM2" s="45"/>
-      <c r="BN2" s="46"/>
-      <c r="BQ2" s="44" t="s">
+      <c r="BD2" s="52"/>
+      <c r="BE2" s="52"/>
+      <c r="BF2" s="52"/>
+      <c r="BG2" s="52"/>
+      <c r="BH2" s="52"/>
+      <c r="BI2" s="52"/>
+      <c r="BJ2" s="52"/>
+      <c r="BK2" s="52"/>
+      <c r="BL2" s="52"/>
+      <c r="BM2" s="52"/>
+      <c r="BN2" s="53"/>
+      <c r="BQ2" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="BR2" s="45"/>
-      <c r="BS2" s="45"/>
-      <c r="BT2" s="45"/>
-      <c r="BU2" s="45"/>
-      <c r="BV2" s="45"/>
-      <c r="BW2" s="45"/>
-      <c r="BX2" s="45"/>
-      <c r="BY2" s="45"/>
-      <c r="BZ2" s="45"/>
-      <c r="CA2" s="45"/>
-      <c r="CB2" s="46"/>
-      <c r="CE2" s="44" t="s">
+      <c r="BR2" s="52"/>
+      <c r="BS2" s="52"/>
+      <c r="BT2" s="52"/>
+      <c r="BU2" s="52"/>
+      <c r="BV2" s="52"/>
+      <c r="BW2" s="52"/>
+      <c r="BX2" s="52"/>
+      <c r="BY2" s="52"/>
+      <c r="BZ2" s="52"/>
+      <c r="CA2" s="52"/>
+      <c r="CB2" s="53"/>
+      <c r="CE2" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="CF2" s="45"/>
-      <c r="CG2" s="45"/>
-      <c r="CH2" s="45"/>
-      <c r="CI2" s="45"/>
-      <c r="CJ2" s="45"/>
-      <c r="CK2" s="45"/>
-      <c r="CL2" s="45"/>
-      <c r="CM2" s="45"/>
-      <c r="CN2" s="45"/>
-      <c r="CO2" s="45"/>
-      <c r="CP2" s="46"/>
+      <c r="CF2" s="52"/>
+      <c r="CG2" s="52"/>
+      <c r="CH2" s="52"/>
+      <c r="CI2" s="52"/>
+      <c r="CJ2" s="52"/>
+      <c r="CK2" s="52"/>
+      <c r="CL2" s="52"/>
+      <c r="CM2" s="52"/>
+      <c r="CN2" s="52"/>
+      <c r="CO2" s="52"/>
+      <c r="CP2" s="53"/>
     </row>
-    <row r="3" spans="2:94" ht="15" thickBot="1">
+    <row r="3" spans="2:94" ht="16" thickBot="1">
       <c r="B3" s="1"/>
       <c r="C3" s="5"/>
-      <c r="D3" s="47" t="s">
+      <c r="D3" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="48"/>
-      <c r="F3" s="47" t="s">
+      <c r="E3" s="45"/>
+      <c r="F3" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="48"/>
-      <c r="H3" s="47" t="s">
+      <c r="G3" s="45"/>
+      <c r="H3" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="48"/>
-      <c r="J3" s="47" t="s">
+      <c r="I3" s="45"/>
+      <c r="J3" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="48"/>
-      <c r="L3" s="47" t="s">
+      <c r="K3" s="45"/>
+      <c r="L3" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="48"/>
+      <c r="M3" s="45"/>
       <c r="AA3" s="1"/>
       <c r="AB3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AC3" s="47" t="s">
+      <c r="AC3" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="AD3" s="48"/>
-      <c r="AE3" s="47" t="s">
+      <c r="AD3" s="45"/>
+      <c r="AE3" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="AF3" s="48"/>
-      <c r="AG3" s="47" t="s">
+      <c r="AF3" s="45"/>
+      <c r="AG3" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="AH3" s="48"/>
-      <c r="AI3" s="47" t="s">
+      <c r="AH3" s="45"/>
+      <c r="AI3" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="AJ3" s="48"/>
-      <c r="AK3" s="47" t="s">
+      <c r="AJ3" s="45"/>
+      <c r="AK3" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="48"/>
+      <c r="AL3" s="45"/>
       <c r="AO3" s="1"/>
       <c r="AP3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AQ3" s="47" t="s">
+      <c r="AQ3" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="AR3" s="48"/>
-      <c r="AS3" s="47" t="s">
+      <c r="AR3" s="45"/>
+      <c r="AS3" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="AT3" s="48"/>
-      <c r="AU3" s="47" t="s">
+      <c r="AT3" s="45"/>
+      <c r="AU3" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="AV3" s="48"/>
-      <c r="AW3" s="47" t="s">
+      <c r="AV3" s="45"/>
+      <c r="AW3" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="AX3" s="48"/>
-      <c r="AY3" s="47" t="s">
+      <c r="AX3" s="45"/>
+      <c r="AY3" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="AZ3" s="48"/>
+      <c r="AZ3" s="45"/>
       <c r="BC3" s="1"/>
       <c r="BD3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="BE3" s="47" t="s">
+      <c r="BE3" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="BF3" s="48"/>
-      <c r="BG3" s="47" t="s">
+      <c r="BF3" s="45"/>
+      <c r="BG3" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="BH3" s="48"/>
-      <c r="BI3" s="47" t="s">
+      <c r="BH3" s="45"/>
+      <c r="BI3" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="BJ3" s="48"/>
-      <c r="BK3" s="47" t="s">
+      <c r="BJ3" s="45"/>
+      <c r="BK3" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="BL3" s="48"/>
-      <c r="BM3" s="47" t="s">
+      <c r="BL3" s="45"/>
+      <c r="BM3" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="BN3" s="48"/>
+      <c r="BN3" s="45"/>
       <c r="BQ3" s="1"/>
       <c r="BR3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="BS3" s="47" t="s">
+      <c r="BS3" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="BT3" s="48"/>
-      <c r="BU3" s="47" t="s">
+      <c r="BT3" s="45"/>
+      <c r="BU3" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="BV3" s="48"/>
-      <c r="BW3" s="47" t="s">
+      <c r="BV3" s="45"/>
+      <c r="BW3" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="BX3" s="48"/>
-      <c r="BY3" s="47" t="s">
+      <c r="BX3" s="45"/>
+      <c r="BY3" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="BZ3" s="48"/>
-      <c r="CA3" s="47" t="s">
+      <c r="BZ3" s="45"/>
+      <c r="CA3" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="CB3" s="48"/>
+      <c r="CB3" s="45"/>
       <c r="CE3" s="1"/>
       <c r="CF3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="CG3" s="47" t="s">
+      <c r="CG3" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="CH3" s="48"/>
-      <c r="CI3" s="47" t="s">
+      <c r="CH3" s="45"/>
+      <c r="CI3" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="CJ3" s="48"/>
-      <c r="CK3" s="47" t="s">
+      <c r="CJ3" s="45"/>
+      <c r="CK3" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="CL3" s="48"/>
-      <c r="CM3" s="47" t="s">
+      <c r="CL3" s="45"/>
+      <c r="CM3" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="CN3" s="48"/>
-      <c r="CO3" s="47" t="s">
+      <c r="CN3" s="45"/>
+      <c r="CO3" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="CP3" s="48"/>
+      <c r="CP3" s="45"/>
     </row>
-    <row r="4" spans="2:94" ht="15" thickBot="1">
+    <row r="4" spans="2:94" ht="16" thickBot="1">
       <c r="B4" s="6" t="s">
         <v>0</v>
       </c>
@@ -8248,7 +8250,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:94" ht="15" thickTop="1">
+    <row r="5" spans="2:94" ht="16" thickTop="1">
       <c r="B5" s="54" t="s">
         <v>9</v>
       </c>
@@ -8472,7 +8474,7 @@
       <c r="CO6" s="15"/>
       <c r="CP6" s="16"/>
     </row>
-    <row r="7" spans="2:94" ht="15" thickBot="1">
+    <row r="7" spans="2:94" ht="16" thickBot="1">
       <c r="B7" s="55"/>
       <c r="C7" s="11" t="s">
         <v>12</v>
@@ -8578,7 +8580,7 @@
       <c r="CO7" s="15"/>
       <c r="CP7" s="16"/>
     </row>
-    <row r="8" spans="2:94" ht="15.5" thickTop="1" thickBot="1">
+    <row r="8" spans="2:94" ht="17" thickTop="1" thickBot="1">
       <c r="B8" s="49" t="s">
         <v>13</v>
       </c>
@@ -8722,7 +8724,7 @@
         <v>19.09</v>
       </c>
     </row>
-    <row r="10" spans="2:94" ht="15" thickBot="1">
+    <row r="10" spans="2:94" ht="16" thickBot="1">
       <c r="B10" s="50"/>
       <c r="C10" s="9" t="s">
         <v>12</v>
@@ -8758,7 +8760,7 @@
         <v>18.829999999999998</v>
       </c>
     </row>
-    <row r="11" spans="2:94" ht="15" thickBot="1">
+    <row r="11" spans="2:94" ht="16" thickBot="1">
       <c r="B11" s="51"/>
       <c r="C11" s="10" t="s">
         <v>14</v>
@@ -8793,200 +8795,200 @@
       <c r="M11" s="22">
         <v>17.579999999999998</v>
       </c>
-      <c r="AA11" s="44" t="s">
+      <c r="AA11" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="AB11" s="52"/>
-      <c r="AC11" s="52"/>
-      <c r="AD11" s="52"/>
-      <c r="AE11" s="52"/>
-      <c r="AF11" s="52"/>
-      <c r="AG11" s="52"/>
-      <c r="AH11" s="52"/>
-      <c r="AI11" s="52"/>
-      <c r="AJ11" s="52"/>
-      <c r="AK11" s="52"/>
-      <c r="AL11" s="53"/>
-      <c r="AO11" s="44" t="s">
+      <c r="AB11" s="47"/>
+      <c r="AC11" s="47"/>
+      <c r="AD11" s="47"/>
+      <c r="AE11" s="47"/>
+      <c r="AF11" s="47"/>
+      <c r="AG11" s="47"/>
+      <c r="AH11" s="47"/>
+      <c r="AI11" s="47"/>
+      <c r="AJ11" s="47"/>
+      <c r="AK11" s="47"/>
+      <c r="AL11" s="48"/>
+      <c r="AO11" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="AP11" s="52"/>
-      <c r="AQ11" s="52"/>
-      <c r="AR11" s="52"/>
-      <c r="AS11" s="52"/>
-      <c r="AT11" s="52"/>
-      <c r="AU11" s="52"/>
-      <c r="AV11" s="52"/>
-      <c r="AW11" s="52"/>
-      <c r="AX11" s="52"/>
-      <c r="AY11" s="52"/>
-      <c r="AZ11" s="53"/>
-      <c r="BC11" s="44" t="s">
+      <c r="AP11" s="47"/>
+      <c r="AQ11" s="47"/>
+      <c r="AR11" s="47"/>
+      <c r="AS11" s="47"/>
+      <c r="AT11" s="47"/>
+      <c r="AU11" s="47"/>
+      <c r="AV11" s="47"/>
+      <c r="AW11" s="47"/>
+      <c r="AX11" s="47"/>
+      <c r="AY11" s="47"/>
+      <c r="AZ11" s="48"/>
+      <c r="BC11" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="BD11" s="52"/>
-      <c r="BE11" s="52"/>
-      <c r="BF11" s="52"/>
-      <c r="BG11" s="52"/>
-      <c r="BH11" s="52"/>
-      <c r="BI11" s="52"/>
-      <c r="BJ11" s="52"/>
-      <c r="BK11" s="52"/>
-      <c r="BL11" s="52"/>
-      <c r="BM11" s="52"/>
-      <c r="BN11" s="53"/>
-      <c r="BQ11" s="44" t="s">
+      <c r="BD11" s="47"/>
+      <c r="BE11" s="47"/>
+      <c r="BF11" s="47"/>
+      <c r="BG11" s="47"/>
+      <c r="BH11" s="47"/>
+      <c r="BI11" s="47"/>
+      <c r="BJ11" s="47"/>
+      <c r="BK11" s="47"/>
+      <c r="BL11" s="47"/>
+      <c r="BM11" s="47"/>
+      <c r="BN11" s="48"/>
+      <c r="BQ11" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="BR11" s="52"/>
-      <c r="BS11" s="52"/>
-      <c r="BT11" s="52"/>
-      <c r="BU11" s="52"/>
-      <c r="BV11" s="52"/>
-      <c r="BW11" s="52"/>
-      <c r="BX11" s="52"/>
-      <c r="BY11" s="52"/>
-      <c r="BZ11" s="52"/>
-      <c r="CA11" s="52"/>
-      <c r="CB11" s="53"/>
-      <c r="CE11" s="44" t="s">
+      <c r="BR11" s="47"/>
+      <c r="BS11" s="47"/>
+      <c r="BT11" s="47"/>
+      <c r="BU11" s="47"/>
+      <c r="BV11" s="47"/>
+      <c r="BW11" s="47"/>
+      <c r="BX11" s="47"/>
+      <c r="BY11" s="47"/>
+      <c r="BZ11" s="47"/>
+      <c r="CA11" s="47"/>
+      <c r="CB11" s="48"/>
+      <c r="CE11" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="CF11" s="52"/>
-      <c r="CG11" s="52"/>
-      <c r="CH11" s="52"/>
-      <c r="CI11" s="52"/>
-      <c r="CJ11" s="52"/>
-      <c r="CK11" s="52"/>
-      <c r="CL11" s="52"/>
-      <c r="CM11" s="52"/>
-      <c r="CN11" s="52"/>
-      <c r="CO11" s="52"/>
-      <c r="CP11" s="53"/>
+      <c r="CF11" s="47"/>
+      <c r="CG11" s="47"/>
+      <c r="CH11" s="47"/>
+      <c r="CI11" s="47"/>
+      <c r="CJ11" s="47"/>
+      <c r="CK11" s="47"/>
+      <c r="CL11" s="47"/>
+      <c r="CM11" s="47"/>
+      <c r="CN11" s="47"/>
+      <c r="CO11" s="47"/>
+      <c r="CP11" s="48"/>
     </row>
-    <row r="12" spans="2:94" ht="15" thickBot="1">
+    <row r="12" spans="2:94" ht="16" thickBot="1">
       <c r="AA12" s="24"/>
       <c r="AB12" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AC12" s="47" t="s">
+      <c r="AC12" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="AD12" s="48"/>
-      <c r="AE12" s="47" t="s">
+      <c r="AD12" s="45"/>
+      <c r="AE12" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="AF12" s="48"/>
-      <c r="AG12" s="47" t="s">
+      <c r="AF12" s="45"/>
+      <c r="AG12" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="AH12" s="48"/>
-      <c r="AI12" s="47" t="s">
+      <c r="AH12" s="45"/>
+      <c r="AI12" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="AJ12" s="48"/>
-      <c r="AK12" s="47" t="s">
+      <c r="AJ12" s="45"/>
+      <c r="AK12" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="AL12" s="48"/>
+      <c r="AL12" s="45"/>
       <c r="AO12" s="24"/>
       <c r="AP12" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AQ12" s="47" t="s">
+      <c r="AQ12" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="AR12" s="48"/>
-      <c r="AS12" s="47" t="s">
+      <c r="AR12" s="45"/>
+      <c r="AS12" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="AT12" s="48"/>
-      <c r="AU12" s="47" t="s">
+      <c r="AT12" s="45"/>
+      <c r="AU12" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="AV12" s="48"/>
-      <c r="AW12" s="47" t="s">
+      <c r="AV12" s="45"/>
+      <c r="AW12" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="AX12" s="48"/>
-      <c r="AY12" s="47" t="s">
+      <c r="AX12" s="45"/>
+      <c r="AY12" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="AZ12" s="48"/>
+      <c r="AZ12" s="45"/>
       <c r="BC12" s="24"/>
       <c r="BD12" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="BE12" s="47" t="s">
+      <c r="BE12" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="BF12" s="48"/>
-      <c r="BG12" s="47" t="s">
+      <c r="BF12" s="45"/>
+      <c r="BG12" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="BH12" s="48"/>
-      <c r="BI12" s="47" t="s">
+      <c r="BH12" s="45"/>
+      <c r="BI12" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="BJ12" s="48"/>
-      <c r="BK12" s="47" t="s">
+      <c r="BJ12" s="45"/>
+      <c r="BK12" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="BL12" s="48"/>
-      <c r="BM12" s="47" t="s">
+      <c r="BL12" s="45"/>
+      <c r="BM12" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="BN12" s="48"/>
+      <c r="BN12" s="45"/>
       <c r="BQ12" s="24"/>
       <c r="BR12" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="BS12" s="47" t="s">
+      <c r="BS12" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="BT12" s="48"/>
-      <c r="BU12" s="47" t="s">
+      <c r="BT12" s="45"/>
+      <c r="BU12" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="BV12" s="48"/>
-      <c r="BW12" s="47" t="s">
+      <c r="BV12" s="45"/>
+      <c r="BW12" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="BX12" s="48"/>
-      <c r="BY12" s="47" t="s">
+      <c r="BX12" s="45"/>
+      <c r="BY12" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="BZ12" s="48"/>
-      <c r="CA12" s="47" t="s">
+      <c r="BZ12" s="45"/>
+      <c r="CA12" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="CB12" s="48"/>
+      <c r="CB12" s="45"/>
       <c r="CE12" s="24"/>
       <c r="CF12" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="CG12" s="47" t="s">
+      <c r="CG12" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="CH12" s="48"/>
-      <c r="CI12" s="47" t="s">
+      <c r="CH12" s="45"/>
+      <c r="CI12" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="CJ12" s="48"/>
-      <c r="CK12" s="47" t="s">
+      <c r="CJ12" s="45"/>
+      <c r="CK12" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="CL12" s="48"/>
-      <c r="CM12" s="47" t="s">
+      <c r="CL12" s="45"/>
+      <c r="CM12" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="CN12" s="48"/>
-      <c r="CO12" s="47" t="s">
+      <c r="CN12" s="45"/>
+      <c r="CO12" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="CP12" s="48"/>
+      <c r="CP12" s="45"/>
     </row>
-    <row r="13" spans="2:94" ht="15" thickBot="1">
+    <row r="13" spans="2:94" ht="16" thickBot="1">
       <c r="AA13" s="25" t="s">
         <v>16</v>
       </c>
@@ -9168,21 +9170,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:94" ht="15" thickBot="1">
-      <c r="B14" s="44" t="s">
+    <row r="14" spans="2:94" ht="16" thickBot="1">
+      <c r="B14" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="52"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="52"/>
-      <c r="K14" s="52"/>
-      <c r="L14" s="52"/>
-      <c r="M14" s="53"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="47"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="48"/>
       <c r="AA14" s="29" t="s">
         <v>24</v>
       </c>
@@ -9254,29 +9256,29 @@
       <c r="CO14" s="30"/>
       <c r="CP14" s="30"/>
     </row>
-    <row r="15" spans="2:94" ht="15" thickBot="1">
+    <row r="15" spans="2:94" ht="16" thickBot="1">
       <c r="B15" s="24"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="47" t="s">
+      <c r="D15" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="E15" s="48"/>
-      <c r="F15" s="47" t="s">
+      <c r="E15" s="45"/>
+      <c r="F15" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="48"/>
-      <c r="H15" s="47" t="s">
+      <c r="G15" s="45"/>
+      <c r="H15" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="48"/>
-      <c r="J15" s="47" t="s">
+      <c r="I15" s="45"/>
+      <c r="J15" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="48"/>
-      <c r="L15" s="47" t="s">
+      <c r="K15" s="45"/>
+      <c r="L15" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="M15" s="48"/>
+      <c r="M15" s="45"/>
       <c r="AA15" s="29" t="s">
         <v>39</v>
       </c>
@@ -10955,8 +10957,12 @@
       <c r="G31" s="30">
         <v>100</v>
       </c>
-      <c r="H31" s="30"/>
-      <c r="I31" s="30"/>
+      <c r="H31" s="30">
+        <v>28.91</v>
+      </c>
+      <c r="I31" s="30">
+        <v>59.36</v>
+      </c>
       <c r="J31" s="30">
         <v>54.55</v>
       </c>
@@ -11358,7 +11364,7 @@
       <c r="CO34" s="30"/>
       <c r="CP34" s="30"/>
     </row>
-    <row r="35" spans="2:94" ht="15" thickBot="1">
+    <row r="35" spans="2:94" ht="16" thickBot="1">
       <c r="B35" s="29" t="s">
         <v>36</v>
       </c>
@@ -11495,7 +11501,7 @@
         <v>13.42</v>
       </c>
     </row>
-    <row r="37" spans="2:94" ht="15" thickBot="1">
+    <row r="37" spans="2:94" ht="16" thickBot="1">
       <c r="B37" s="29" t="s">
         <v>38</v>
       </c>
@@ -11531,7 +11537,7 @@
         <v>13.38</v>
       </c>
     </row>
-    <row r="38" spans="2:94" ht="15" thickBot="1">
+    <row r="38" spans="2:94" ht="16" thickBot="1">
       <c r="C38" s="23" t="s">
         <v>17</v>
       </c>
@@ -11547,200 +11553,200 @@
       <c r="K38" s="41"/>
       <c r="L38" s="40"/>
       <c r="M38" s="41"/>
-      <c r="AA38" s="44" t="s">
+      <c r="AA38" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="AB38" s="45"/>
-      <c r="AC38" s="45"/>
-      <c r="AD38" s="45"/>
-      <c r="AE38" s="45"/>
-      <c r="AF38" s="45"/>
-      <c r="AG38" s="45"/>
-      <c r="AH38" s="45"/>
-      <c r="AI38" s="45"/>
-      <c r="AJ38" s="45"/>
-      <c r="AK38" s="45"/>
-      <c r="AL38" s="46"/>
-      <c r="AO38" s="44" t="s">
+      <c r="AB38" s="52"/>
+      <c r="AC38" s="52"/>
+      <c r="AD38" s="52"/>
+      <c r="AE38" s="52"/>
+      <c r="AF38" s="52"/>
+      <c r="AG38" s="52"/>
+      <c r="AH38" s="52"/>
+      <c r="AI38" s="52"/>
+      <c r="AJ38" s="52"/>
+      <c r="AK38" s="52"/>
+      <c r="AL38" s="53"/>
+      <c r="AO38" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="AP38" s="45"/>
-      <c r="AQ38" s="45"/>
-      <c r="AR38" s="45"/>
-      <c r="AS38" s="45"/>
-      <c r="AT38" s="45"/>
-      <c r="AU38" s="45"/>
-      <c r="AV38" s="45"/>
-      <c r="AW38" s="45"/>
-      <c r="AX38" s="45"/>
-      <c r="AY38" s="45"/>
-      <c r="AZ38" s="46"/>
-      <c r="BC38" s="44" t="s">
+      <c r="AP38" s="52"/>
+      <c r="AQ38" s="52"/>
+      <c r="AR38" s="52"/>
+      <c r="AS38" s="52"/>
+      <c r="AT38" s="52"/>
+      <c r="AU38" s="52"/>
+      <c r="AV38" s="52"/>
+      <c r="AW38" s="52"/>
+      <c r="AX38" s="52"/>
+      <c r="AY38" s="52"/>
+      <c r="AZ38" s="53"/>
+      <c r="BC38" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="BD38" s="45"/>
-      <c r="BE38" s="45"/>
-      <c r="BF38" s="45"/>
-      <c r="BG38" s="45"/>
-      <c r="BH38" s="45"/>
-      <c r="BI38" s="45"/>
-      <c r="BJ38" s="45"/>
-      <c r="BK38" s="45"/>
-      <c r="BL38" s="45"/>
-      <c r="BM38" s="45"/>
-      <c r="BN38" s="46"/>
-      <c r="BQ38" s="44" t="s">
+      <c r="BD38" s="52"/>
+      <c r="BE38" s="52"/>
+      <c r="BF38" s="52"/>
+      <c r="BG38" s="52"/>
+      <c r="BH38" s="52"/>
+      <c r="BI38" s="52"/>
+      <c r="BJ38" s="52"/>
+      <c r="BK38" s="52"/>
+      <c r="BL38" s="52"/>
+      <c r="BM38" s="52"/>
+      <c r="BN38" s="53"/>
+      <c r="BQ38" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="BR38" s="45"/>
-      <c r="BS38" s="45"/>
-      <c r="BT38" s="45"/>
-      <c r="BU38" s="45"/>
-      <c r="BV38" s="45"/>
-      <c r="BW38" s="45"/>
-      <c r="BX38" s="45"/>
-      <c r="BY38" s="45"/>
-      <c r="BZ38" s="45"/>
-      <c r="CA38" s="45"/>
-      <c r="CB38" s="46"/>
-      <c r="CE38" s="44" t="s">
+      <c r="BR38" s="52"/>
+      <c r="BS38" s="52"/>
+      <c r="BT38" s="52"/>
+      <c r="BU38" s="52"/>
+      <c r="BV38" s="52"/>
+      <c r="BW38" s="52"/>
+      <c r="BX38" s="52"/>
+      <c r="BY38" s="52"/>
+      <c r="BZ38" s="52"/>
+      <c r="CA38" s="52"/>
+      <c r="CB38" s="53"/>
+      <c r="CE38" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="CF38" s="45"/>
-      <c r="CG38" s="45"/>
-      <c r="CH38" s="45"/>
-      <c r="CI38" s="45"/>
-      <c r="CJ38" s="45"/>
-      <c r="CK38" s="45"/>
-      <c r="CL38" s="45"/>
-      <c r="CM38" s="45"/>
-      <c r="CN38" s="45"/>
-      <c r="CO38" s="45"/>
-      <c r="CP38" s="46"/>
+      <c r="CF38" s="52"/>
+      <c r="CG38" s="52"/>
+      <c r="CH38" s="52"/>
+      <c r="CI38" s="52"/>
+      <c r="CJ38" s="52"/>
+      <c r="CK38" s="52"/>
+      <c r="CL38" s="52"/>
+      <c r="CM38" s="52"/>
+      <c r="CN38" s="52"/>
+      <c r="CO38" s="52"/>
+      <c r="CP38" s="53"/>
     </row>
-    <row r="39" spans="2:94" ht="15" thickBot="1">
+    <row r="39" spans="2:94" ht="16" thickBot="1">
       <c r="AA39" s="1"/>
       <c r="AB39" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="AC39" s="47" t="s">
+      <c r="AC39" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="AD39" s="48"/>
-      <c r="AE39" s="47" t="s">
+      <c r="AD39" s="45"/>
+      <c r="AE39" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="AF39" s="48"/>
-      <c r="AG39" s="47" t="s">
+      <c r="AF39" s="45"/>
+      <c r="AG39" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="AH39" s="48"/>
-      <c r="AI39" s="47" t="s">
+      <c r="AH39" s="45"/>
+      <c r="AI39" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="AJ39" s="48"/>
-      <c r="AK39" s="47" t="s">
+      <c r="AJ39" s="45"/>
+      <c r="AK39" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="AL39" s="48"/>
+      <c r="AL39" s="45"/>
       <c r="AO39" s="1"/>
       <c r="AP39" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="AQ39" s="47" t="s">
+      <c r="AQ39" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="AR39" s="48"/>
-      <c r="AS39" s="47" t="s">
+      <c r="AR39" s="45"/>
+      <c r="AS39" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="AT39" s="48"/>
-      <c r="AU39" s="47" t="s">
+      <c r="AT39" s="45"/>
+      <c r="AU39" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="AV39" s="48"/>
-      <c r="AW39" s="47" t="s">
+      <c r="AV39" s="45"/>
+      <c r="AW39" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="AX39" s="48"/>
-      <c r="AY39" s="47" t="s">
+      <c r="AX39" s="45"/>
+      <c r="AY39" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="AZ39" s="48"/>
+      <c r="AZ39" s="45"/>
       <c r="BC39" s="1"/>
       <c r="BD39" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="BE39" s="47" t="s">
+      <c r="BE39" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="BF39" s="48"/>
-      <c r="BG39" s="47" t="s">
+      <c r="BF39" s="45"/>
+      <c r="BG39" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="BH39" s="48"/>
-      <c r="BI39" s="47" t="s">
+      <c r="BH39" s="45"/>
+      <c r="BI39" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="BJ39" s="48"/>
-      <c r="BK39" s="47" t="s">
+      <c r="BJ39" s="45"/>
+      <c r="BK39" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="BL39" s="48"/>
-      <c r="BM39" s="47" t="s">
+      <c r="BL39" s="45"/>
+      <c r="BM39" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="BN39" s="48"/>
+      <c r="BN39" s="45"/>
       <c r="BQ39" s="1"/>
       <c r="BR39" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="BS39" s="47" t="s">
+      <c r="BS39" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="BT39" s="48"/>
-      <c r="BU39" s="47" t="s">
+      <c r="BT39" s="45"/>
+      <c r="BU39" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="BV39" s="48"/>
-      <c r="BW39" s="47" t="s">
+      <c r="BV39" s="45"/>
+      <c r="BW39" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="BX39" s="48"/>
-      <c r="BY39" s="47" t="s">
+      <c r="BX39" s="45"/>
+      <c r="BY39" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="BZ39" s="48"/>
-      <c r="CA39" s="47" t="s">
+      <c r="BZ39" s="45"/>
+      <c r="CA39" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="CB39" s="48"/>
+      <c r="CB39" s="45"/>
       <c r="CE39" s="1"/>
       <c r="CF39" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="CG39" s="47" t="s">
+      <c r="CG39" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="CH39" s="48"/>
-      <c r="CI39" s="47" t="s">
+      <c r="CH39" s="45"/>
+      <c r="CI39" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="CJ39" s="48"/>
-      <c r="CK39" s="47" t="s">
+      <c r="CJ39" s="45"/>
+      <c r="CK39" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="CL39" s="48"/>
-      <c r="CM39" s="47" t="s">
+      <c r="CL39" s="45"/>
+      <c r="CM39" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="CN39" s="48"/>
-      <c r="CO39" s="47" t="s">
+      <c r="CN39" s="45"/>
+      <c r="CO39" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="CP39" s="48"/>
+      <c r="CP39" s="45"/>
     </row>
-    <row r="40" spans="2:94" ht="15" thickBot="1">
+    <row r="40" spans="2:94" ht="16" thickBot="1">
       <c r="AA40" s="6" t="s">
         <v>0</v>
       </c>
@@ -11922,7 +11928,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="2:94" ht="15" thickTop="1">
+    <row r="41" spans="2:94" ht="16" thickTop="1">
       <c r="AA41" s="49" t="s">
         <v>13</v>
       </c>
@@ -12148,7 +12154,7 @@
       <c r="CO43" s="15"/>
       <c r="CP43" s="16"/>
     </row>
-    <row r="44" spans="2:94" ht="15" thickBot="1">
+    <row r="44" spans="2:94" ht="16" thickBot="1">
       <c r="AA44" s="51"/>
       <c r="AB44" s="10" t="s">
         <v>14</v>
@@ -12220,200 +12226,200 @@
       <c r="CO44" s="21"/>
       <c r="CP44" s="22"/>
     </row>
-    <row r="46" spans="2:94" ht="15" thickBot="1"/>
-    <row r="47" spans="2:94" ht="15" thickBot="1">
-      <c r="AA47" s="44" t="s">
+    <row r="46" spans="2:94" ht="16" thickBot="1"/>
+    <row r="47" spans="2:94" ht="16" thickBot="1">
+      <c r="AA47" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="AB47" s="52"/>
-      <c r="AC47" s="52"/>
-      <c r="AD47" s="52"/>
-      <c r="AE47" s="52"/>
-      <c r="AF47" s="52"/>
-      <c r="AG47" s="52"/>
-      <c r="AH47" s="52"/>
-      <c r="AI47" s="52"/>
-      <c r="AJ47" s="52"/>
-      <c r="AK47" s="52"/>
-      <c r="AL47" s="53"/>
-      <c r="AO47" s="44" t="s">
+      <c r="AB47" s="47"/>
+      <c r="AC47" s="47"/>
+      <c r="AD47" s="47"/>
+      <c r="AE47" s="47"/>
+      <c r="AF47" s="47"/>
+      <c r="AG47" s="47"/>
+      <c r="AH47" s="47"/>
+      <c r="AI47" s="47"/>
+      <c r="AJ47" s="47"/>
+      <c r="AK47" s="47"/>
+      <c r="AL47" s="48"/>
+      <c r="AO47" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="AP47" s="52"/>
-      <c r="AQ47" s="52"/>
-      <c r="AR47" s="52"/>
-      <c r="AS47" s="52"/>
-      <c r="AT47" s="52"/>
-      <c r="AU47" s="52"/>
-      <c r="AV47" s="52"/>
-      <c r="AW47" s="52"/>
-      <c r="AX47" s="52"/>
-      <c r="AY47" s="52"/>
-      <c r="AZ47" s="53"/>
-      <c r="BC47" s="44" t="s">
+      <c r="AP47" s="47"/>
+      <c r="AQ47" s="47"/>
+      <c r="AR47" s="47"/>
+      <c r="AS47" s="47"/>
+      <c r="AT47" s="47"/>
+      <c r="AU47" s="47"/>
+      <c r="AV47" s="47"/>
+      <c r="AW47" s="47"/>
+      <c r="AX47" s="47"/>
+      <c r="AY47" s="47"/>
+      <c r="AZ47" s="48"/>
+      <c r="BC47" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="BD47" s="52"/>
-      <c r="BE47" s="52"/>
-      <c r="BF47" s="52"/>
-      <c r="BG47" s="52"/>
-      <c r="BH47" s="52"/>
-      <c r="BI47" s="52"/>
-      <c r="BJ47" s="52"/>
-      <c r="BK47" s="52"/>
-      <c r="BL47" s="52"/>
-      <c r="BM47" s="52"/>
-      <c r="BN47" s="53"/>
-      <c r="BQ47" s="44" t="s">
+      <c r="BD47" s="47"/>
+      <c r="BE47" s="47"/>
+      <c r="BF47" s="47"/>
+      <c r="BG47" s="47"/>
+      <c r="BH47" s="47"/>
+      <c r="BI47" s="47"/>
+      <c r="BJ47" s="47"/>
+      <c r="BK47" s="47"/>
+      <c r="BL47" s="47"/>
+      <c r="BM47" s="47"/>
+      <c r="BN47" s="48"/>
+      <c r="BQ47" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="BR47" s="52"/>
-      <c r="BS47" s="52"/>
-      <c r="BT47" s="52"/>
-      <c r="BU47" s="52"/>
-      <c r="BV47" s="52"/>
-      <c r="BW47" s="52"/>
-      <c r="BX47" s="52"/>
-      <c r="BY47" s="52"/>
-      <c r="BZ47" s="52"/>
-      <c r="CA47" s="52"/>
-      <c r="CB47" s="53"/>
-      <c r="CE47" s="44" t="s">
+      <c r="BR47" s="47"/>
+      <c r="BS47" s="47"/>
+      <c r="BT47" s="47"/>
+      <c r="BU47" s="47"/>
+      <c r="BV47" s="47"/>
+      <c r="BW47" s="47"/>
+      <c r="BX47" s="47"/>
+      <c r="BY47" s="47"/>
+      <c r="BZ47" s="47"/>
+      <c r="CA47" s="47"/>
+      <c r="CB47" s="48"/>
+      <c r="CE47" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="CF47" s="52"/>
-      <c r="CG47" s="52"/>
-      <c r="CH47" s="52"/>
-      <c r="CI47" s="52"/>
-      <c r="CJ47" s="52"/>
-      <c r="CK47" s="52"/>
-      <c r="CL47" s="52"/>
-      <c r="CM47" s="52"/>
-      <c r="CN47" s="52"/>
-      <c r="CO47" s="52"/>
-      <c r="CP47" s="53"/>
+      <c r="CF47" s="47"/>
+      <c r="CG47" s="47"/>
+      <c r="CH47" s="47"/>
+      <c r="CI47" s="47"/>
+      <c r="CJ47" s="47"/>
+      <c r="CK47" s="47"/>
+      <c r="CL47" s="47"/>
+      <c r="CM47" s="47"/>
+      <c r="CN47" s="47"/>
+      <c r="CO47" s="47"/>
+      <c r="CP47" s="48"/>
     </row>
-    <row r="48" spans="2:94" ht="15" thickBot="1">
+    <row r="48" spans="2:94" ht="16" thickBot="1">
       <c r="AA48" s="24"/>
       <c r="AB48" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="AC48" s="47" t="s">
+      <c r="AC48" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="AD48" s="48"/>
-      <c r="AE48" s="47" t="s">
+      <c r="AD48" s="45"/>
+      <c r="AE48" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="AF48" s="48"/>
-      <c r="AG48" s="47" t="s">
+      <c r="AF48" s="45"/>
+      <c r="AG48" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="AH48" s="48"/>
-      <c r="AI48" s="47" t="s">
+      <c r="AH48" s="45"/>
+      <c r="AI48" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="AJ48" s="48"/>
-      <c r="AK48" s="47" t="s">
+      <c r="AJ48" s="45"/>
+      <c r="AK48" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="AL48" s="48"/>
+      <c r="AL48" s="45"/>
       <c r="AO48" s="24"/>
       <c r="AP48" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="AQ48" s="47" t="s">
+      <c r="AQ48" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="AR48" s="48"/>
-      <c r="AS48" s="47" t="s">
+      <c r="AR48" s="45"/>
+      <c r="AS48" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="AT48" s="48"/>
-      <c r="AU48" s="47" t="s">
+      <c r="AT48" s="45"/>
+      <c r="AU48" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="AV48" s="48"/>
-      <c r="AW48" s="47" t="s">
+      <c r="AV48" s="45"/>
+      <c r="AW48" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="AX48" s="48"/>
-      <c r="AY48" s="47" t="s">
+      <c r="AX48" s="45"/>
+      <c r="AY48" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="AZ48" s="48"/>
+      <c r="AZ48" s="45"/>
       <c r="BC48" s="24"/>
       <c r="BD48" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="BE48" s="47" t="s">
+      <c r="BE48" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="BF48" s="48"/>
-      <c r="BG48" s="47" t="s">
+      <c r="BF48" s="45"/>
+      <c r="BG48" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="BH48" s="48"/>
-      <c r="BI48" s="47" t="s">
+      <c r="BH48" s="45"/>
+      <c r="BI48" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="BJ48" s="48"/>
-      <c r="BK48" s="47" t="s">
+      <c r="BJ48" s="45"/>
+      <c r="BK48" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="BL48" s="48"/>
-      <c r="BM48" s="47" t="s">
+      <c r="BL48" s="45"/>
+      <c r="BM48" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="BN48" s="48"/>
+      <c r="BN48" s="45"/>
       <c r="BQ48" s="24"/>
       <c r="BR48" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="BS48" s="47" t="s">
+      <c r="BS48" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="BT48" s="48"/>
-      <c r="BU48" s="47" t="s">
+      <c r="BT48" s="45"/>
+      <c r="BU48" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="BV48" s="48"/>
-      <c r="BW48" s="47" t="s">
+      <c r="BV48" s="45"/>
+      <c r="BW48" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="BX48" s="48"/>
-      <c r="BY48" s="47" t="s">
+      <c r="BX48" s="45"/>
+      <c r="BY48" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="BZ48" s="48"/>
-      <c r="CA48" s="47" t="s">
+      <c r="BZ48" s="45"/>
+      <c r="CA48" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="CB48" s="48"/>
+      <c r="CB48" s="45"/>
       <c r="CE48" s="24"/>
       <c r="CF48" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="CG48" s="47" t="s">
+      <c r="CG48" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="CH48" s="48"/>
-      <c r="CI48" s="47" t="s">
+      <c r="CH48" s="45"/>
+      <c r="CI48" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="CJ48" s="48"/>
-      <c r="CK48" s="47" t="s">
+      <c r="CJ48" s="45"/>
+      <c r="CK48" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="CL48" s="48"/>
-      <c r="CM48" s="47" t="s">
+      <c r="CL48" s="45"/>
+      <c r="CM48" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="CN48" s="48"/>
-      <c r="CO48" s="47" t="s">
+      <c r="CN48" s="45"/>
+      <c r="CO48" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="CP48" s="48"/>
+      <c r="CP48" s="45"/>
     </row>
     <row r="49" spans="27:94">
       <c r="AA49" s="25" t="s">
@@ -14104,7 +14110,7 @@
       <c r="CO70" s="30"/>
       <c r="CP70" s="30"/>
     </row>
-    <row r="71" spans="27:94" ht="15" thickBot="1">
+    <row r="71" spans="27:94" ht="16" thickBot="1">
       <c r="AB71" s="23" t="s">
         <v>17</v>
       </c>
@@ -14171,202 +14177,202 @@
       <c r="CO71" s="40"/>
       <c r="CP71" s="41"/>
     </row>
-    <row r="73" spans="27:94" ht="15" thickBot="1"/>
-    <row r="74" spans="27:94" ht="15" thickBot="1">
-      <c r="AA74" s="44" t="s">
+    <row r="73" spans="27:94" ht="16" thickBot="1"/>
+    <row r="74" spans="27:94" ht="16" thickBot="1">
+      <c r="AA74" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="AB74" s="45"/>
-      <c r="AC74" s="45"/>
-      <c r="AD74" s="45"/>
-      <c r="AE74" s="45"/>
-      <c r="AF74" s="45"/>
-      <c r="AG74" s="45"/>
-      <c r="AH74" s="45"/>
-      <c r="AI74" s="45"/>
-      <c r="AJ74" s="45"/>
-      <c r="AK74" s="45"/>
-      <c r="AL74" s="46"/>
-      <c r="AO74" s="44" t="s">
+      <c r="AB74" s="52"/>
+      <c r="AC74" s="52"/>
+      <c r="AD74" s="52"/>
+      <c r="AE74" s="52"/>
+      <c r="AF74" s="52"/>
+      <c r="AG74" s="52"/>
+      <c r="AH74" s="52"/>
+      <c r="AI74" s="52"/>
+      <c r="AJ74" s="52"/>
+      <c r="AK74" s="52"/>
+      <c r="AL74" s="53"/>
+      <c r="AO74" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="AP74" s="45"/>
-      <c r="AQ74" s="45"/>
-      <c r="AR74" s="45"/>
-      <c r="AS74" s="45"/>
-      <c r="AT74" s="45"/>
-      <c r="AU74" s="45"/>
-      <c r="AV74" s="45"/>
-      <c r="AW74" s="45"/>
-      <c r="AX74" s="45"/>
-      <c r="AY74" s="45"/>
-      <c r="AZ74" s="46"/>
-      <c r="BC74" s="44" t="s">
+      <c r="AP74" s="52"/>
+      <c r="AQ74" s="52"/>
+      <c r="AR74" s="52"/>
+      <c r="AS74" s="52"/>
+      <c r="AT74" s="52"/>
+      <c r="AU74" s="52"/>
+      <c r="AV74" s="52"/>
+      <c r="AW74" s="52"/>
+      <c r="AX74" s="52"/>
+      <c r="AY74" s="52"/>
+      <c r="AZ74" s="53"/>
+      <c r="BC74" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="BD74" s="45"/>
-      <c r="BE74" s="45"/>
-      <c r="BF74" s="45"/>
-      <c r="BG74" s="45"/>
-      <c r="BH74" s="45"/>
-      <c r="BI74" s="45"/>
-      <c r="BJ74" s="45"/>
-      <c r="BK74" s="45"/>
-      <c r="BL74" s="45"/>
-      <c r="BM74" s="45"/>
-      <c r="BN74" s="46"/>
-      <c r="BQ74" s="44" t="s">
+      <c r="BD74" s="52"/>
+      <c r="BE74" s="52"/>
+      <c r="BF74" s="52"/>
+      <c r="BG74" s="52"/>
+      <c r="BH74" s="52"/>
+      <c r="BI74" s="52"/>
+      <c r="BJ74" s="52"/>
+      <c r="BK74" s="52"/>
+      <c r="BL74" s="52"/>
+      <c r="BM74" s="52"/>
+      <c r="BN74" s="53"/>
+      <c r="BQ74" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="BR74" s="45"/>
-      <c r="BS74" s="45"/>
-      <c r="BT74" s="45"/>
-      <c r="BU74" s="45"/>
-      <c r="BV74" s="45"/>
-      <c r="BW74" s="45"/>
-      <c r="BX74" s="45"/>
-      <c r="BY74" s="45"/>
-      <c r="BZ74" s="45"/>
-      <c r="CA74" s="45"/>
-      <c r="CB74" s="46"/>
-      <c r="CE74" s="44" t="s">
+      <c r="BR74" s="52"/>
+      <c r="BS74" s="52"/>
+      <c r="BT74" s="52"/>
+      <c r="BU74" s="52"/>
+      <c r="BV74" s="52"/>
+      <c r="BW74" s="52"/>
+      <c r="BX74" s="52"/>
+      <c r="BY74" s="52"/>
+      <c r="BZ74" s="52"/>
+      <c r="CA74" s="52"/>
+      <c r="CB74" s="53"/>
+      <c r="CE74" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="CF74" s="45"/>
-      <c r="CG74" s="45"/>
-      <c r="CH74" s="45"/>
-      <c r="CI74" s="45"/>
-      <c r="CJ74" s="45"/>
-      <c r="CK74" s="45"/>
-      <c r="CL74" s="45"/>
-      <c r="CM74" s="45"/>
-      <c r="CN74" s="45"/>
-      <c r="CO74" s="45"/>
-      <c r="CP74" s="46"/>
+      <c r="CF74" s="52"/>
+      <c r="CG74" s="52"/>
+      <c r="CH74" s="52"/>
+      <c r="CI74" s="52"/>
+      <c r="CJ74" s="52"/>
+      <c r="CK74" s="52"/>
+      <c r="CL74" s="52"/>
+      <c r="CM74" s="52"/>
+      <c r="CN74" s="52"/>
+      <c r="CO74" s="52"/>
+      <c r="CP74" s="53"/>
     </row>
-    <row r="75" spans="27:94" ht="15" thickBot="1">
+    <row r="75" spans="27:94" ht="16" thickBot="1">
       <c r="AA75" s="1"/>
       <c r="AB75" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="AC75" s="47" t="s">
+      <c r="AC75" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="AD75" s="48"/>
-      <c r="AE75" s="47" t="s">
+      <c r="AD75" s="45"/>
+      <c r="AE75" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="AF75" s="48"/>
-      <c r="AG75" s="47" t="s">
+      <c r="AF75" s="45"/>
+      <c r="AG75" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="AH75" s="48"/>
-      <c r="AI75" s="47" t="s">
+      <c r="AH75" s="45"/>
+      <c r="AI75" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="AJ75" s="48"/>
-      <c r="AK75" s="47" t="s">
+      <c r="AJ75" s="45"/>
+      <c r="AK75" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="AL75" s="48"/>
+      <c r="AL75" s="45"/>
       <c r="AO75" s="1"/>
       <c r="AP75" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="AQ75" s="47" t="s">
+      <c r="AQ75" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="AR75" s="48"/>
-      <c r="AS75" s="47" t="s">
+      <c r="AR75" s="45"/>
+      <c r="AS75" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="AT75" s="48"/>
-      <c r="AU75" s="47" t="s">
+      <c r="AT75" s="45"/>
+      <c r="AU75" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="AV75" s="48"/>
-      <c r="AW75" s="47" t="s">
+      <c r="AV75" s="45"/>
+      <c r="AW75" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="AX75" s="48"/>
-      <c r="AY75" s="47" t="s">
+      <c r="AX75" s="45"/>
+      <c r="AY75" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="AZ75" s="48"/>
+      <c r="AZ75" s="45"/>
       <c r="BC75" s="1"/>
       <c r="BD75" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="BE75" s="47" t="s">
+      <c r="BE75" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="BF75" s="48"/>
-      <c r="BG75" s="47" t="s">
+      <c r="BF75" s="45"/>
+      <c r="BG75" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="BH75" s="48"/>
-      <c r="BI75" s="47" t="s">
+      <c r="BH75" s="45"/>
+      <c r="BI75" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="BJ75" s="48"/>
-      <c r="BK75" s="47" t="s">
+      <c r="BJ75" s="45"/>
+      <c r="BK75" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="BL75" s="48"/>
-      <c r="BM75" s="47" t="s">
+      <c r="BL75" s="45"/>
+      <c r="BM75" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="BN75" s="48"/>
+      <c r="BN75" s="45"/>
       <c r="BQ75" s="1"/>
       <c r="BR75" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="BS75" s="47" t="s">
+      <c r="BS75" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="BT75" s="48"/>
-      <c r="BU75" s="47" t="s">
+      <c r="BT75" s="45"/>
+      <c r="BU75" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="BV75" s="48"/>
-      <c r="BW75" s="47" t="s">
+      <c r="BV75" s="45"/>
+      <c r="BW75" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="BX75" s="48"/>
-      <c r="BY75" s="47" t="s">
+      <c r="BX75" s="45"/>
+      <c r="BY75" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="BZ75" s="48"/>
-      <c r="CA75" s="47" t="s">
+      <c r="BZ75" s="45"/>
+      <c r="CA75" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="CB75" s="48"/>
+      <c r="CB75" s="45"/>
       <c r="CE75" s="1"/>
       <c r="CF75" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="CG75" s="47" t="s">
+      <c r="CG75" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="CH75" s="48"/>
-      <c r="CI75" s="47" t="s">
+      <c r="CH75" s="45"/>
+      <c r="CI75" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="CJ75" s="48"/>
-      <c r="CK75" s="47" t="s">
+      <c r="CJ75" s="45"/>
+      <c r="CK75" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="CL75" s="48"/>
-      <c r="CM75" s="47" t="s">
+      <c r="CL75" s="45"/>
+      <c r="CM75" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="CN75" s="48"/>
-      <c r="CO75" s="47" t="s">
+      <c r="CN75" s="45"/>
+      <c r="CO75" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="CP75" s="48"/>
+      <c r="CP75" s="45"/>
     </row>
-    <row r="76" spans="27:94" ht="15" thickBot="1">
+    <row r="76" spans="27:94" ht="16" thickBot="1">
       <c r="AA76" s="6" t="s">
         <v>0</v>
       </c>
@@ -14548,7 +14554,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="27:94" ht="15" thickTop="1">
+    <row r="77" spans="27:94" ht="16" thickTop="1">
       <c r="AA77" s="49" t="s">
         <v>13</v>
       </c>
@@ -14774,7 +14780,7 @@
       <c r="CO79" s="15"/>
       <c r="CP79" s="16"/>
     </row>
-    <row r="80" spans="27:94" ht="15" thickBot="1">
+    <row r="80" spans="27:94" ht="16" thickBot="1">
       <c r="AA80" s="51"/>
       <c r="AB80" s="10" t="s">
         <v>14</v>
@@ -14846,200 +14852,200 @@
       <c r="CO80" s="21"/>
       <c r="CP80" s="22"/>
     </row>
-    <row r="82" spans="27:94" ht="15" thickBot="1"/>
-    <row r="83" spans="27:94" ht="15" thickBot="1">
-      <c r="AA83" s="44" t="s">
+    <row r="82" spans="27:94" ht="16" thickBot="1"/>
+    <row r="83" spans="27:94" ht="16" thickBot="1">
+      <c r="AA83" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="AB83" s="52"/>
-      <c r="AC83" s="52"/>
-      <c r="AD83" s="52"/>
-      <c r="AE83" s="52"/>
-      <c r="AF83" s="52"/>
-      <c r="AG83" s="52"/>
-      <c r="AH83" s="52"/>
-      <c r="AI83" s="52"/>
-      <c r="AJ83" s="52"/>
-      <c r="AK83" s="52"/>
-      <c r="AL83" s="53"/>
-      <c r="AO83" s="44" t="s">
+      <c r="AB83" s="47"/>
+      <c r="AC83" s="47"/>
+      <c r="AD83" s="47"/>
+      <c r="AE83" s="47"/>
+      <c r="AF83" s="47"/>
+      <c r="AG83" s="47"/>
+      <c r="AH83" s="47"/>
+      <c r="AI83" s="47"/>
+      <c r="AJ83" s="47"/>
+      <c r="AK83" s="47"/>
+      <c r="AL83" s="48"/>
+      <c r="AO83" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="AP83" s="52"/>
-      <c r="AQ83" s="52"/>
-      <c r="AR83" s="52"/>
-      <c r="AS83" s="52"/>
-      <c r="AT83" s="52"/>
-      <c r="AU83" s="52"/>
-      <c r="AV83" s="52"/>
-      <c r="AW83" s="52"/>
-      <c r="AX83" s="52"/>
-      <c r="AY83" s="52"/>
-      <c r="AZ83" s="53"/>
-      <c r="BC83" s="44" t="s">
+      <c r="AP83" s="47"/>
+      <c r="AQ83" s="47"/>
+      <c r="AR83" s="47"/>
+      <c r="AS83" s="47"/>
+      <c r="AT83" s="47"/>
+      <c r="AU83" s="47"/>
+      <c r="AV83" s="47"/>
+      <c r="AW83" s="47"/>
+      <c r="AX83" s="47"/>
+      <c r="AY83" s="47"/>
+      <c r="AZ83" s="48"/>
+      <c r="BC83" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="BD83" s="52"/>
-      <c r="BE83" s="52"/>
-      <c r="BF83" s="52"/>
-      <c r="BG83" s="52"/>
-      <c r="BH83" s="52"/>
-      <c r="BI83" s="52"/>
-      <c r="BJ83" s="52"/>
-      <c r="BK83" s="52"/>
-      <c r="BL83" s="52"/>
-      <c r="BM83" s="52"/>
-      <c r="BN83" s="53"/>
-      <c r="BQ83" s="44" t="s">
+      <c r="BD83" s="47"/>
+      <c r="BE83" s="47"/>
+      <c r="BF83" s="47"/>
+      <c r="BG83" s="47"/>
+      <c r="BH83" s="47"/>
+      <c r="BI83" s="47"/>
+      <c r="BJ83" s="47"/>
+      <c r="BK83" s="47"/>
+      <c r="BL83" s="47"/>
+      <c r="BM83" s="47"/>
+      <c r="BN83" s="48"/>
+      <c r="BQ83" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="BR83" s="52"/>
-      <c r="BS83" s="52"/>
-      <c r="BT83" s="52"/>
-      <c r="BU83" s="52"/>
-      <c r="BV83" s="52"/>
-      <c r="BW83" s="52"/>
-      <c r="BX83" s="52"/>
-      <c r="BY83" s="52"/>
-      <c r="BZ83" s="52"/>
-      <c r="CA83" s="52"/>
-      <c r="CB83" s="53"/>
-      <c r="CE83" s="44" t="s">
+      <c r="BR83" s="47"/>
+      <c r="BS83" s="47"/>
+      <c r="BT83" s="47"/>
+      <c r="BU83" s="47"/>
+      <c r="BV83" s="47"/>
+      <c r="BW83" s="47"/>
+      <c r="BX83" s="47"/>
+      <c r="BY83" s="47"/>
+      <c r="BZ83" s="47"/>
+      <c r="CA83" s="47"/>
+      <c r="CB83" s="48"/>
+      <c r="CE83" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="CF83" s="52"/>
-      <c r="CG83" s="52"/>
-      <c r="CH83" s="52"/>
-      <c r="CI83" s="52"/>
-      <c r="CJ83" s="52"/>
-      <c r="CK83" s="52"/>
-      <c r="CL83" s="52"/>
-      <c r="CM83" s="52"/>
-      <c r="CN83" s="52"/>
-      <c r="CO83" s="52"/>
-      <c r="CP83" s="53"/>
+      <c r="CF83" s="47"/>
+      <c r="CG83" s="47"/>
+      <c r="CH83" s="47"/>
+      <c r="CI83" s="47"/>
+      <c r="CJ83" s="47"/>
+      <c r="CK83" s="47"/>
+      <c r="CL83" s="47"/>
+      <c r="CM83" s="47"/>
+      <c r="CN83" s="47"/>
+      <c r="CO83" s="47"/>
+      <c r="CP83" s="48"/>
     </row>
-    <row r="84" spans="27:94" ht="15" thickBot="1">
+    <row r="84" spans="27:94" ht="16" thickBot="1">
       <c r="AA84" s="24"/>
       <c r="AB84" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="AC84" s="47" t="s">
+      <c r="AC84" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="AD84" s="48"/>
-      <c r="AE84" s="47" t="s">
+      <c r="AD84" s="45"/>
+      <c r="AE84" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="AF84" s="48"/>
-      <c r="AG84" s="47" t="s">
+      <c r="AF84" s="45"/>
+      <c r="AG84" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="AH84" s="48"/>
-      <c r="AI84" s="47" t="s">
+      <c r="AH84" s="45"/>
+      <c r="AI84" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="AJ84" s="48"/>
-      <c r="AK84" s="47" t="s">
+      <c r="AJ84" s="45"/>
+      <c r="AK84" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="AL84" s="48"/>
+      <c r="AL84" s="45"/>
       <c r="AO84" s="24"/>
       <c r="AP84" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="AQ84" s="47" t="s">
+      <c r="AQ84" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="AR84" s="48"/>
-      <c r="AS84" s="47" t="s">
+      <c r="AR84" s="45"/>
+      <c r="AS84" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="AT84" s="48"/>
-      <c r="AU84" s="47" t="s">
+      <c r="AT84" s="45"/>
+      <c r="AU84" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="AV84" s="48"/>
-      <c r="AW84" s="47" t="s">
+      <c r="AV84" s="45"/>
+      <c r="AW84" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="AX84" s="48"/>
-      <c r="AY84" s="47" t="s">
+      <c r="AX84" s="45"/>
+      <c r="AY84" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="AZ84" s="48"/>
+      <c r="AZ84" s="45"/>
       <c r="BC84" s="24"/>
       <c r="BD84" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="BE84" s="47" t="s">
+      <c r="BE84" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="BF84" s="48"/>
-      <c r="BG84" s="47" t="s">
+      <c r="BF84" s="45"/>
+      <c r="BG84" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="BH84" s="48"/>
-      <c r="BI84" s="47" t="s">
+      <c r="BH84" s="45"/>
+      <c r="BI84" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="BJ84" s="48"/>
-      <c r="BK84" s="47" t="s">
+      <c r="BJ84" s="45"/>
+      <c r="BK84" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="BL84" s="48"/>
-      <c r="BM84" s="47" t="s">
+      <c r="BL84" s="45"/>
+      <c r="BM84" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="BN84" s="48"/>
+      <c r="BN84" s="45"/>
       <c r="BQ84" s="24"/>
       <c r="BR84" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="BS84" s="47" t="s">
+      <c r="BS84" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="BT84" s="48"/>
-      <c r="BU84" s="47" t="s">
+      <c r="BT84" s="45"/>
+      <c r="BU84" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="BV84" s="48"/>
-      <c r="BW84" s="47" t="s">
+      <c r="BV84" s="45"/>
+      <c r="BW84" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="BX84" s="48"/>
-      <c r="BY84" s="47" t="s">
+      <c r="BX84" s="45"/>
+      <c r="BY84" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="BZ84" s="48"/>
-      <c r="CA84" s="47" t="s">
+      <c r="BZ84" s="45"/>
+      <c r="CA84" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="CB84" s="48"/>
+      <c r="CB84" s="45"/>
       <c r="CE84" s="24"/>
       <c r="CF84" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="CG84" s="47" t="s">
+      <c r="CG84" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="CH84" s="48"/>
-      <c r="CI84" s="47" t="s">
+      <c r="CH84" s="45"/>
+      <c r="CI84" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="CJ84" s="48"/>
-      <c r="CK84" s="47" t="s">
+      <c r="CJ84" s="45"/>
+      <c r="CK84" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="CL84" s="48"/>
-      <c r="CM84" s="47" t="s">
+      <c r="CL84" s="45"/>
+      <c r="CM84" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="CN84" s="48"/>
-      <c r="CO84" s="47" t="s">
+      <c r="CN84" s="45"/>
+      <c r="CO84" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="CP84" s="48"/>
+      <c r="CP84" s="45"/>
     </row>
     <row r="85" spans="27:94">
       <c r="AA85" s="25" t="s">
@@ -16730,7 +16736,7 @@
       <c r="CO106" s="30"/>
       <c r="CP106" s="30"/>
     </row>
-    <row r="107" spans="27:94" ht="15" thickBot="1">
+    <row r="107" spans="27:94" ht="16" thickBot="1">
       <c r="AB107" s="23" t="s">
         <v>17</v>
       </c>
@@ -16799,21 +16805,256 @@
     </row>
   </sheetData>
   <mergeCells count="289">
-    <mergeCell ref="CO107:CP107"/>
-    <mergeCell ref="BS107:BT107"/>
-    <mergeCell ref="BU107:BV107"/>
-    <mergeCell ref="BW107:BX107"/>
-    <mergeCell ref="BY107:BZ107"/>
-    <mergeCell ref="CA107:CB107"/>
-    <mergeCell ref="AQ107:AR107"/>
-    <mergeCell ref="AS107:AT107"/>
-    <mergeCell ref="AU107:AV107"/>
-    <mergeCell ref="AW107:AX107"/>
-    <mergeCell ref="AY107:AZ107"/>
-    <mergeCell ref="CG107:CH107"/>
-    <mergeCell ref="CI107:CJ107"/>
-    <mergeCell ref="CK107:CL107"/>
-    <mergeCell ref="CM107:CN107"/>
+    <mergeCell ref="BE35:BF35"/>
+    <mergeCell ref="BG35:BH35"/>
+    <mergeCell ref="BI35:BJ35"/>
+    <mergeCell ref="BK35:BL35"/>
+    <mergeCell ref="BM35:BN35"/>
+    <mergeCell ref="BQ2:CB2"/>
+    <mergeCell ref="BS3:BT3"/>
+    <mergeCell ref="BU3:BV3"/>
+    <mergeCell ref="BW3:BX3"/>
+    <mergeCell ref="BY3:BZ3"/>
+    <mergeCell ref="CA3:CB3"/>
+    <mergeCell ref="BQ5:BQ8"/>
+    <mergeCell ref="BQ11:CB11"/>
+    <mergeCell ref="BS12:BT12"/>
+    <mergeCell ref="BU12:BV12"/>
+    <mergeCell ref="BW12:BX12"/>
+    <mergeCell ref="BY12:BZ12"/>
+    <mergeCell ref="CA12:CB12"/>
+    <mergeCell ref="BS35:BT35"/>
+    <mergeCell ref="BU35:BV35"/>
+    <mergeCell ref="BW35:BX35"/>
+    <mergeCell ref="BY35:BZ35"/>
+    <mergeCell ref="CA35:CB35"/>
+    <mergeCell ref="BC2:BN2"/>
+    <mergeCell ref="BE3:BF3"/>
+    <mergeCell ref="BG3:BH3"/>
+    <mergeCell ref="BI3:BJ3"/>
+    <mergeCell ref="BK3:BL3"/>
+    <mergeCell ref="BM3:BN3"/>
+    <mergeCell ref="BC5:BC8"/>
+    <mergeCell ref="BC11:BN11"/>
+    <mergeCell ref="BE12:BF12"/>
+    <mergeCell ref="BG12:BH12"/>
+    <mergeCell ref="BI12:BJ12"/>
+    <mergeCell ref="BK12:BL12"/>
+    <mergeCell ref="BM12:BN12"/>
+    <mergeCell ref="AC35:AD35"/>
+    <mergeCell ref="AE35:AF35"/>
+    <mergeCell ref="AG35:AH35"/>
+    <mergeCell ref="AI35:AJ35"/>
+    <mergeCell ref="AK35:AL35"/>
+    <mergeCell ref="AO2:AZ2"/>
+    <mergeCell ref="AQ3:AR3"/>
+    <mergeCell ref="AS3:AT3"/>
+    <mergeCell ref="AU3:AV3"/>
+    <mergeCell ref="AW3:AX3"/>
+    <mergeCell ref="AY3:AZ3"/>
+    <mergeCell ref="AO5:AO8"/>
+    <mergeCell ref="AO11:AZ11"/>
+    <mergeCell ref="AQ12:AR12"/>
+    <mergeCell ref="AS12:AT12"/>
+    <mergeCell ref="AU12:AV12"/>
+    <mergeCell ref="AW12:AX12"/>
+    <mergeCell ref="AY12:AZ12"/>
+    <mergeCell ref="AQ35:AR35"/>
+    <mergeCell ref="AS35:AT35"/>
+    <mergeCell ref="AU35:AV35"/>
+    <mergeCell ref="AW35:AX35"/>
+    <mergeCell ref="AY35:AZ35"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="B14:M14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="CE2:CP2"/>
+    <mergeCell ref="CG3:CH3"/>
+    <mergeCell ref="CI3:CJ3"/>
+    <mergeCell ref="CK3:CL3"/>
+    <mergeCell ref="CM3:CN3"/>
+    <mergeCell ref="CO3:CP3"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="AA2:AL2"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="AG3:AH3"/>
+    <mergeCell ref="AI3:AJ3"/>
+    <mergeCell ref="AK3:AL3"/>
+    <mergeCell ref="AA5:AA8"/>
+    <mergeCell ref="AA11:AL11"/>
+    <mergeCell ref="AC12:AD12"/>
+    <mergeCell ref="AE12:AF12"/>
+    <mergeCell ref="AG12:AH12"/>
+    <mergeCell ref="AI12:AJ12"/>
+    <mergeCell ref="AK12:AL12"/>
+    <mergeCell ref="CE38:CP38"/>
+    <mergeCell ref="CG35:CH35"/>
+    <mergeCell ref="CI35:CJ35"/>
+    <mergeCell ref="CK35:CL35"/>
+    <mergeCell ref="CM35:CN35"/>
+    <mergeCell ref="CO35:CP35"/>
+    <mergeCell ref="CE5:CE8"/>
+    <mergeCell ref="CE11:CP11"/>
+    <mergeCell ref="CG12:CH12"/>
+    <mergeCell ref="CI12:CJ12"/>
+    <mergeCell ref="CK12:CL12"/>
+    <mergeCell ref="CM12:CN12"/>
+    <mergeCell ref="CO12:CP12"/>
+    <mergeCell ref="AC39:AD39"/>
+    <mergeCell ref="AE39:AF39"/>
+    <mergeCell ref="AG39:AH39"/>
+    <mergeCell ref="AI39:AJ39"/>
+    <mergeCell ref="AK39:AL39"/>
+    <mergeCell ref="AA38:AL38"/>
+    <mergeCell ref="AO38:AZ38"/>
+    <mergeCell ref="BC38:BN38"/>
+    <mergeCell ref="BQ38:CB38"/>
+    <mergeCell ref="BE39:BF39"/>
+    <mergeCell ref="BG39:BH39"/>
+    <mergeCell ref="BI39:BJ39"/>
+    <mergeCell ref="BK39:BL39"/>
+    <mergeCell ref="BM39:BN39"/>
+    <mergeCell ref="AQ39:AR39"/>
+    <mergeCell ref="AS39:AT39"/>
+    <mergeCell ref="AU39:AV39"/>
+    <mergeCell ref="AW39:AX39"/>
+    <mergeCell ref="AY39:AZ39"/>
+    <mergeCell ref="CG39:CH39"/>
+    <mergeCell ref="CI39:CJ39"/>
+    <mergeCell ref="CK39:CL39"/>
+    <mergeCell ref="CM39:CN39"/>
+    <mergeCell ref="CO39:CP39"/>
+    <mergeCell ref="BS39:BT39"/>
+    <mergeCell ref="BU39:BV39"/>
+    <mergeCell ref="BW39:BX39"/>
+    <mergeCell ref="BY39:BZ39"/>
+    <mergeCell ref="CA39:CB39"/>
+    <mergeCell ref="AA47:AL47"/>
+    <mergeCell ref="AO47:AZ47"/>
+    <mergeCell ref="BC47:BN47"/>
+    <mergeCell ref="BQ47:CB47"/>
+    <mergeCell ref="CE47:CP47"/>
+    <mergeCell ref="AA41:AA44"/>
+    <mergeCell ref="AO41:AO44"/>
+    <mergeCell ref="BC41:BC44"/>
+    <mergeCell ref="BQ41:BQ44"/>
+    <mergeCell ref="CE41:CE44"/>
+    <mergeCell ref="CO48:CP48"/>
+    <mergeCell ref="BS48:BT48"/>
+    <mergeCell ref="BU48:BV48"/>
+    <mergeCell ref="BW48:BX48"/>
+    <mergeCell ref="BY48:BZ48"/>
+    <mergeCell ref="CA48:CB48"/>
+    <mergeCell ref="BE48:BF48"/>
+    <mergeCell ref="BG48:BH48"/>
+    <mergeCell ref="BI48:BJ48"/>
+    <mergeCell ref="BK48:BL48"/>
+    <mergeCell ref="BM48:BN48"/>
+    <mergeCell ref="AC71:AD71"/>
+    <mergeCell ref="AE71:AF71"/>
+    <mergeCell ref="AG71:AH71"/>
+    <mergeCell ref="AI71:AJ71"/>
+    <mergeCell ref="AK71:AL71"/>
+    <mergeCell ref="CG48:CH48"/>
+    <mergeCell ref="CI48:CJ48"/>
+    <mergeCell ref="CK48:CL48"/>
+    <mergeCell ref="CM48:CN48"/>
+    <mergeCell ref="AQ48:AR48"/>
+    <mergeCell ref="AS48:AT48"/>
+    <mergeCell ref="AU48:AV48"/>
+    <mergeCell ref="AW48:AX48"/>
+    <mergeCell ref="AY48:AZ48"/>
+    <mergeCell ref="AC48:AD48"/>
+    <mergeCell ref="AE48:AF48"/>
+    <mergeCell ref="AG48:AH48"/>
+    <mergeCell ref="AI48:AJ48"/>
+    <mergeCell ref="AK48:AL48"/>
+    <mergeCell ref="BE71:BF71"/>
+    <mergeCell ref="BG71:BH71"/>
+    <mergeCell ref="BI71:BJ71"/>
+    <mergeCell ref="BK71:BL71"/>
+    <mergeCell ref="BM71:BN71"/>
+    <mergeCell ref="AQ71:AR71"/>
+    <mergeCell ref="AS71:AT71"/>
+    <mergeCell ref="AU71:AV71"/>
+    <mergeCell ref="AW71:AX71"/>
+    <mergeCell ref="AY71:AZ71"/>
+    <mergeCell ref="CE74:CP74"/>
+    <mergeCell ref="CG71:CH71"/>
+    <mergeCell ref="CI71:CJ71"/>
+    <mergeCell ref="CK71:CL71"/>
+    <mergeCell ref="CM71:CN71"/>
+    <mergeCell ref="CO71:CP71"/>
+    <mergeCell ref="BS71:BT71"/>
+    <mergeCell ref="BU71:BV71"/>
+    <mergeCell ref="BW71:BX71"/>
+    <mergeCell ref="BY71:BZ71"/>
+    <mergeCell ref="CA71:CB71"/>
+    <mergeCell ref="AC75:AD75"/>
+    <mergeCell ref="AE75:AF75"/>
+    <mergeCell ref="AG75:AH75"/>
+    <mergeCell ref="AI75:AJ75"/>
+    <mergeCell ref="AK75:AL75"/>
+    <mergeCell ref="AA74:AL74"/>
+    <mergeCell ref="AO74:AZ74"/>
+    <mergeCell ref="BC74:BN74"/>
+    <mergeCell ref="BQ74:CB74"/>
+    <mergeCell ref="BE75:BF75"/>
+    <mergeCell ref="BG75:BH75"/>
+    <mergeCell ref="BI75:BJ75"/>
+    <mergeCell ref="BK75:BL75"/>
+    <mergeCell ref="BM75:BN75"/>
+    <mergeCell ref="AQ75:AR75"/>
+    <mergeCell ref="AS75:AT75"/>
+    <mergeCell ref="AU75:AV75"/>
+    <mergeCell ref="AW75:AX75"/>
+    <mergeCell ref="AY75:AZ75"/>
+    <mergeCell ref="CG75:CH75"/>
+    <mergeCell ref="CI75:CJ75"/>
+    <mergeCell ref="CK75:CL75"/>
+    <mergeCell ref="CM75:CN75"/>
+    <mergeCell ref="CO75:CP75"/>
+    <mergeCell ref="BS75:BT75"/>
+    <mergeCell ref="BU75:BV75"/>
+    <mergeCell ref="BW75:BX75"/>
+    <mergeCell ref="BY75:BZ75"/>
+    <mergeCell ref="CA75:CB75"/>
+    <mergeCell ref="AA83:AL83"/>
+    <mergeCell ref="AO83:AZ83"/>
+    <mergeCell ref="BC83:BN83"/>
+    <mergeCell ref="BQ83:CB83"/>
+    <mergeCell ref="CE83:CP83"/>
+    <mergeCell ref="AA77:AA80"/>
+    <mergeCell ref="AO77:AO80"/>
+    <mergeCell ref="BC77:BC80"/>
+    <mergeCell ref="BQ77:BQ80"/>
+    <mergeCell ref="CE77:CE80"/>
+    <mergeCell ref="CO84:CP84"/>
+    <mergeCell ref="BS84:BT84"/>
+    <mergeCell ref="BU84:BV84"/>
+    <mergeCell ref="BW84:BX84"/>
+    <mergeCell ref="BY84:BZ84"/>
+    <mergeCell ref="CA84:CB84"/>
+    <mergeCell ref="BE84:BF84"/>
+    <mergeCell ref="BG84:BH84"/>
+    <mergeCell ref="BI84:BJ84"/>
+    <mergeCell ref="BK84:BL84"/>
+    <mergeCell ref="BM84:BN84"/>
     <mergeCell ref="AC107:AD107"/>
     <mergeCell ref="AE107:AF107"/>
     <mergeCell ref="AG107:AH107"/>
@@ -16838,256 +17079,21 @@
     <mergeCell ref="BI107:BJ107"/>
     <mergeCell ref="BK107:BL107"/>
     <mergeCell ref="BM107:BN107"/>
-    <mergeCell ref="CO84:CP84"/>
-    <mergeCell ref="BS84:BT84"/>
-    <mergeCell ref="BU84:BV84"/>
-    <mergeCell ref="BW84:BX84"/>
-    <mergeCell ref="BY84:BZ84"/>
-    <mergeCell ref="CA84:CB84"/>
-    <mergeCell ref="BE84:BF84"/>
-    <mergeCell ref="BG84:BH84"/>
-    <mergeCell ref="BI84:BJ84"/>
-    <mergeCell ref="BK84:BL84"/>
-    <mergeCell ref="BM84:BN84"/>
-    <mergeCell ref="AA83:AL83"/>
-    <mergeCell ref="AO83:AZ83"/>
-    <mergeCell ref="BC83:BN83"/>
-    <mergeCell ref="BQ83:CB83"/>
-    <mergeCell ref="CE83:CP83"/>
-    <mergeCell ref="AA77:AA80"/>
-    <mergeCell ref="AO77:AO80"/>
-    <mergeCell ref="BC77:BC80"/>
-    <mergeCell ref="BQ77:BQ80"/>
-    <mergeCell ref="CE77:CE80"/>
-    <mergeCell ref="CG75:CH75"/>
-    <mergeCell ref="CI75:CJ75"/>
-    <mergeCell ref="CK75:CL75"/>
-    <mergeCell ref="CM75:CN75"/>
-    <mergeCell ref="CO75:CP75"/>
-    <mergeCell ref="BS75:BT75"/>
-    <mergeCell ref="BU75:BV75"/>
-    <mergeCell ref="BW75:BX75"/>
-    <mergeCell ref="BY75:BZ75"/>
-    <mergeCell ref="CA75:CB75"/>
-    <mergeCell ref="AC75:AD75"/>
-    <mergeCell ref="AE75:AF75"/>
-    <mergeCell ref="AG75:AH75"/>
-    <mergeCell ref="AI75:AJ75"/>
-    <mergeCell ref="AK75:AL75"/>
-    <mergeCell ref="AA74:AL74"/>
-    <mergeCell ref="AO74:AZ74"/>
-    <mergeCell ref="BC74:BN74"/>
-    <mergeCell ref="BQ74:CB74"/>
-    <mergeCell ref="BE75:BF75"/>
-    <mergeCell ref="BG75:BH75"/>
-    <mergeCell ref="BI75:BJ75"/>
-    <mergeCell ref="BK75:BL75"/>
-    <mergeCell ref="BM75:BN75"/>
-    <mergeCell ref="AQ75:AR75"/>
-    <mergeCell ref="AS75:AT75"/>
-    <mergeCell ref="AU75:AV75"/>
-    <mergeCell ref="AW75:AX75"/>
-    <mergeCell ref="AY75:AZ75"/>
-    <mergeCell ref="AQ71:AR71"/>
-    <mergeCell ref="AS71:AT71"/>
-    <mergeCell ref="AU71:AV71"/>
-    <mergeCell ref="AW71:AX71"/>
-    <mergeCell ref="AY71:AZ71"/>
-    <mergeCell ref="CE74:CP74"/>
-    <mergeCell ref="CG71:CH71"/>
-    <mergeCell ref="CI71:CJ71"/>
-    <mergeCell ref="CK71:CL71"/>
-    <mergeCell ref="CM71:CN71"/>
-    <mergeCell ref="CO71:CP71"/>
-    <mergeCell ref="BS71:BT71"/>
-    <mergeCell ref="BU71:BV71"/>
-    <mergeCell ref="BW71:BX71"/>
-    <mergeCell ref="BY71:BZ71"/>
-    <mergeCell ref="CA71:CB71"/>
-    <mergeCell ref="AC71:AD71"/>
-    <mergeCell ref="AE71:AF71"/>
-    <mergeCell ref="AG71:AH71"/>
-    <mergeCell ref="AI71:AJ71"/>
-    <mergeCell ref="AK71:AL71"/>
-    <mergeCell ref="CG48:CH48"/>
-    <mergeCell ref="CI48:CJ48"/>
-    <mergeCell ref="CK48:CL48"/>
-    <mergeCell ref="CM48:CN48"/>
-    <mergeCell ref="AQ48:AR48"/>
-    <mergeCell ref="AS48:AT48"/>
-    <mergeCell ref="AU48:AV48"/>
-    <mergeCell ref="AW48:AX48"/>
-    <mergeCell ref="AY48:AZ48"/>
-    <mergeCell ref="AC48:AD48"/>
-    <mergeCell ref="AE48:AF48"/>
-    <mergeCell ref="AG48:AH48"/>
-    <mergeCell ref="AI48:AJ48"/>
-    <mergeCell ref="AK48:AL48"/>
-    <mergeCell ref="BE71:BF71"/>
-    <mergeCell ref="BG71:BH71"/>
-    <mergeCell ref="BI71:BJ71"/>
-    <mergeCell ref="BK71:BL71"/>
-    <mergeCell ref="BM71:BN71"/>
-    <mergeCell ref="CO48:CP48"/>
-    <mergeCell ref="BS48:BT48"/>
-    <mergeCell ref="BU48:BV48"/>
-    <mergeCell ref="BW48:BX48"/>
-    <mergeCell ref="BY48:BZ48"/>
-    <mergeCell ref="CA48:CB48"/>
-    <mergeCell ref="BE48:BF48"/>
-    <mergeCell ref="BG48:BH48"/>
-    <mergeCell ref="BI48:BJ48"/>
-    <mergeCell ref="BK48:BL48"/>
-    <mergeCell ref="BM48:BN48"/>
-    <mergeCell ref="AA47:AL47"/>
-    <mergeCell ref="AO47:AZ47"/>
-    <mergeCell ref="BC47:BN47"/>
-    <mergeCell ref="BQ47:CB47"/>
-    <mergeCell ref="CE47:CP47"/>
-    <mergeCell ref="AA41:AA44"/>
-    <mergeCell ref="AO41:AO44"/>
-    <mergeCell ref="BC41:BC44"/>
-    <mergeCell ref="BQ41:BQ44"/>
-    <mergeCell ref="CE41:CE44"/>
-    <mergeCell ref="CG39:CH39"/>
-    <mergeCell ref="CI39:CJ39"/>
-    <mergeCell ref="CK39:CL39"/>
-    <mergeCell ref="CM39:CN39"/>
-    <mergeCell ref="CO39:CP39"/>
-    <mergeCell ref="BS39:BT39"/>
-    <mergeCell ref="BU39:BV39"/>
-    <mergeCell ref="BW39:BX39"/>
-    <mergeCell ref="BY39:BZ39"/>
-    <mergeCell ref="CA39:CB39"/>
-    <mergeCell ref="AC39:AD39"/>
-    <mergeCell ref="AE39:AF39"/>
-    <mergeCell ref="AG39:AH39"/>
-    <mergeCell ref="AI39:AJ39"/>
-    <mergeCell ref="AK39:AL39"/>
-    <mergeCell ref="AA38:AL38"/>
-    <mergeCell ref="AO38:AZ38"/>
-    <mergeCell ref="BC38:BN38"/>
-    <mergeCell ref="BQ38:CB38"/>
-    <mergeCell ref="BE39:BF39"/>
-    <mergeCell ref="BG39:BH39"/>
-    <mergeCell ref="BI39:BJ39"/>
-    <mergeCell ref="BK39:BL39"/>
-    <mergeCell ref="BM39:BN39"/>
-    <mergeCell ref="AQ39:AR39"/>
-    <mergeCell ref="AS39:AT39"/>
-    <mergeCell ref="AU39:AV39"/>
-    <mergeCell ref="AW39:AX39"/>
-    <mergeCell ref="AY39:AZ39"/>
-    <mergeCell ref="CE38:CP38"/>
-    <mergeCell ref="CG35:CH35"/>
-    <mergeCell ref="CI35:CJ35"/>
-    <mergeCell ref="CK35:CL35"/>
-    <mergeCell ref="CM35:CN35"/>
-    <mergeCell ref="CO35:CP35"/>
-    <mergeCell ref="CE5:CE8"/>
-    <mergeCell ref="CE11:CP11"/>
-    <mergeCell ref="CG12:CH12"/>
-    <mergeCell ref="CI12:CJ12"/>
-    <mergeCell ref="CK12:CL12"/>
-    <mergeCell ref="CM12:CN12"/>
-    <mergeCell ref="CO12:CP12"/>
-    <mergeCell ref="CE2:CP2"/>
-    <mergeCell ref="CG3:CH3"/>
-    <mergeCell ref="CI3:CJ3"/>
-    <mergeCell ref="CK3:CL3"/>
-    <mergeCell ref="CM3:CN3"/>
-    <mergeCell ref="CO3:CP3"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="AA2:AL2"/>
-    <mergeCell ref="AC3:AD3"/>
-    <mergeCell ref="AE3:AF3"/>
-    <mergeCell ref="AG3:AH3"/>
-    <mergeCell ref="AI3:AJ3"/>
-    <mergeCell ref="AK3:AL3"/>
-    <mergeCell ref="AA5:AA8"/>
-    <mergeCell ref="AA11:AL11"/>
-    <mergeCell ref="AC12:AD12"/>
-    <mergeCell ref="AE12:AF12"/>
-    <mergeCell ref="AG12:AH12"/>
-    <mergeCell ref="AI12:AJ12"/>
-    <mergeCell ref="AK12:AL12"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="B14:M14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="AC35:AD35"/>
-    <mergeCell ref="AE35:AF35"/>
-    <mergeCell ref="AG35:AH35"/>
-    <mergeCell ref="AI35:AJ35"/>
-    <mergeCell ref="AK35:AL35"/>
-    <mergeCell ref="AO2:AZ2"/>
-    <mergeCell ref="AQ3:AR3"/>
-    <mergeCell ref="AS3:AT3"/>
-    <mergeCell ref="AU3:AV3"/>
-    <mergeCell ref="AW3:AX3"/>
-    <mergeCell ref="AY3:AZ3"/>
-    <mergeCell ref="AO5:AO8"/>
-    <mergeCell ref="AO11:AZ11"/>
-    <mergeCell ref="AQ12:AR12"/>
-    <mergeCell ref="AS12:AT12"/>
-    <mergeCell ref="AU12:AV12"/>
-    <mergeCell ref="AW12:AX12"/>
-    <mergeCell ref="AY12:AZ12"/>
-    <mergeCell ref="AQ35:AR35"/>
-    <mergeCell ref="AS35:AT35"/>
-    <mergeCell ref="AU35:AV35"/>
-    <mergeCell ref="AW35:AX35"/>
-    <mergeCell ref="AY35:AZ35"/>
-    <mergeCell ref="BE3:BF3"/>
-    <mergeCell ref="BG3:BH3"/>
-    <mergeCell ref="BI3:BJ3"/>
-    <mergeCell ref="BK3:BL3"/>
-    <mergeCell ref="BM3:BN3"/>
-    <mergeCell ref="BC5:BC8"/>
-    <mergeCell ref="BC11:BN11"/>
-    <mergeCell ref="BE12:BF12"/>
-    <mergeCell ref="BG12:BH12"/>
-    <mergeCell ref="BI12:BJ12"/>
-    <mergeCell ref="BK12:BL12"/>
-    <mergeCell ref="BM12:BN12"/>
-    <mergeCell ref="BE35:BF35"/>
-    <mergeCell ref="BG35:BH35"/>
-    <mergeCell ref="BI35:BJ35"/>
-    <mergeCell ref="BK35:BL35"/>
-    <mergeCell ref="BM35:BN35"/>
-    <mergeCell ref="BQ2:CB2"/>
-    <mergeCell ref="BS3:BT3"/>
-    <mergeCell ref="BU3:BV3"/>
-    <mergeCell ref="BW3:BX3"/>
-    <mergeCell ref="BY3:BZ3"/>
-    <mergeCell ref="CA3:CB3"/>
-    <mergeCell ref="BQ5:BQ8"/>
-    <mergeCell ref="BQ11:CB11"/>
-    <mergeCell ref="BS12:BT12"/>
-    <mergeCell ref="BU12:BV12"/>
-    <mergeCell ref="BW12:BX12"/>
-    <mergeCell ref="BY12:BZ12"/>
-    <mergeCell ref="CA12:CB12"/>
-    <mergeCell ref="BS35:BT35"/>
-    <mergeCell ref="BU35:BV35"/>
-    <mergeCell ref="BW35:BX35"/>
-    <mergeCell ref="BY35:BZ35"/>
-    <mergeCell ref="CA35:CB35"/>
-    <mergeCell ref="BC2:BN2"/>
+    <mergeCell ref="CO107:CP107"/>
+    <mergeCell ref="BS107:BT107"/>
+    <mergeCell ref="BU107:BV107"/>
+    <mergeCell ref="BW107:BX107"/>
+    <mergeCell ref="BY107:BZ107"/>
+    <mergeCell ref="CA107:CB107"/>
+    <mergeCell ref="AQ107:AR107"/>
+    <mergeCell ref="AS107:AT107"/>
+    <mergeCell ref="AU107:AV107"/>
+    <mergeCell ref="AW107:AX107"/>
+    <mergeCell ref="AY107:AZ107"/>
+    <mergeCell ref="CG107:CH107"/>
+    <mergeCell ref="CI107:CJ107"/>
+    <mergeCell ref="CK107:CL107"/>
+    <mergeCell ref="CM107:CN107"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Results_metrics.xlsx
+++ b/Results_metrics.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Enrica\Desktop\Nuovo_ML_Project\MaskArchitectureAnomaly_CourseProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cgarg\Desktop\MaskArchitectureAnomaly_CourseProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A776971-DE7D-47EC-B3F9-2C72D87D9871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C365DA-9EA7-410A-9830-3CC3FACBA621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11232" yWindow="0" windowWidth="11808" windowHeight="12072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="71">
   <si>
     <t>Model</t>
   </si>
@@ -178,6 +178,66 @@
   </si>
   <si>
     <t>t = 0,2</t>
+  </si>
+  <si>
+    <t>67,42</t>
+  </si>
+  <si>
+    <t>34,08</t>
+  </si>
+  <si>
+    <t>76,57</t>
+  </si>
+  <si>
+    <t>18,14</t>
+  </si>
+  <si>
+    <t>67,65</t>
+  </si>
+  <si>
+    <t>79,41</t>
+  </si>
+  <si>
+    <t>11,36</t>
+  </si>
+  <si>
+    <t>77,11</t>
+  </si>
+  <si>
+    <t>78,91</t>
+  </si>
+  <si>
+    <t>80,72</t>
+  </si>
+  <si>
+    <t>83,29</t>
+  </si>
+  <si>
+    <t>83,39</t>
+  </si>
+  <si>
+    <t>82,99</t>
+  </si>
+  <si>
+    <t>3,27</t>
+  </si>
+  <si>
+    <t>14,06</t>
+  </si>
+  <si>
+    <t>10,01</t>
+  </si>
+  <si>
+    <t>7,03</t>
+  </si>
+  <si>
+    <t>3,71</t>
+  </si>
+  <si>
+    <t>3,23</t>
+  </si>
+  <si>
+    <t>3,15</t>
   </si>
 </sst>
 </file>
@@ -727,10 +787,16 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -756,12 +822,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7677,198 +7737,198 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:CB38"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7890625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="14.44140625" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="2" max="2" width="14.41796875" customWidth="1"/>
+    <col min="3" max="3" width="13.1015625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="45" t="s">
+    <row r="1" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="2" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B2" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="51"/>
-      <c r="AA2" s="45" t="s">
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="53"/>
+      <c r="AA2" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="AB2" s="50"/>
-      <c r="AC2" s="50"/>
-      <c r="AD2" s="50"/>
-      <c r="AE2" s="50"/>
-      <c r="AF2" s="50"/>
-      <c r="AG2" s="50"/>
-      <c r="AH2" s="50"/>
-      <c r="AI2" s="50"/>
-      <c r="AJ2" s="50"/>
-      <c r="AK2" s="50"/>
-      <c r="AL2" s="51"/>
-      <c r="AO2" s="45" t="s">
+      <c r="AB2" s="52"/>
+      <c r="AC2" s="52"/>
+      <c r="AD2" s="52"/>
+      <c r="AE2" s="52"/>
+      <c r="AF2" s="52"/>
+      <c r="AG2" s="52"/>
+      <c r="AH2" s="52"/>
+      <c r="AI2" s="52"/>
+      <c r="AJ2" s="52"/>
+      <c r="AK2" s="52"/>
+      <c r="AL2" s="53"/>
+      <c r="AO2" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="AP2" s="50"/>
-      <c r="AQ2" s="50"/>
-      <c r="AR2" s="50"/>
-      <c r="AS2" s="50"/>
-      <c r="AT2" s="50"/>
-      <c r="AU2" s="50"/>
-      <c r="AV2" s="50"/>
-      <c r="AW2" s="50"/>
-      <c r="AX2" s="50"/>
-      <c r="AY2" s="50"/>
-      <c r="AZ2" s="51"/>
-      <c r="BC2" s="45" t="s">
+      <c r="AP2" s="52"/>
+      <c r="AQ2" s="52"/>
+      <c r="AR2" s="52"/>
+      <c r="AS2" s="52"/>
+      <c r="AT2" s="52"/>
+      <c r="AU2" s="52"/>
+      <c r="AV2" s="52"/>
+      <c r="AW2" s="52"/>
+      <c r="AX2" s="52"/>
+      <c r="AY2" s="52"/>
+      <c r="AZ2" s="53"/>
+      <c r="BC2" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="BD2" s="50"/>
-      <c r="BE2" s="50"/>
-      <c r="BF2" s="50"/>
-      <c r="BG2" s="50"/>
-      <c r="BH2" s="50"/>
-      <c r="BI2" s="50"/>
-      <c r="BJ2" s="50"/>
-      <c r="BK2" s="50"/>
-      <c r="BL2" s="50"/>
-      <c r="BM2" s="50"/>
-      <c r="BN2" s="51"/>
-      <c r="BQ2" s="45" t="s">
+      <c r="BD2" s="52"/>
+      <c r="BE2" s="52"/>
+      <c r="BF2" s="52"/>
+      <c r="BG2" s="52"/>
+      <c r="BH2" s="52"/>
+      <c r="BI2" s="52"/>
+      <c r="BJ2" s="52"/>
+      <c r="BK2" s="52"/>
+      <c r="BL2" s="52"/>
+      <c r="BM2" s="52"/>
+      <c r="BN2" s="53"/>
+      <c r="BQ2" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="BR2" s="50"/>
-      <c r="BS2" s="50"/>
-      <c r="BT2" s="50"/>
-      <c r="BU2" s="50"/>
-      <c r="BV2" s="50"/>
-      <c r="BW2" s="50"/>
-      <c r="BX2" s="50"/>
-      <c r="BY2" s="50"/>
-      <c r="BZ2" s="50"/>
-      <c r="CA2" s="50"/>
-      <c r="CB2" s="51"/>
+      <c r="BR2" s="52"/>
+      <c r="BS2" s="52"/>
+      <c r="BT2" s="52"/>
+      <c r="BU2" s="52"/>
+      <c r="BV2" s="52"/>
+      <c r="BW2" s="52"/>
+      <c r="BX2" s="52"/>
+      <c r="BY2" s="52"/>
+      <c r="BZ2" s="52"/>
+      <c r="CA2" s="52"/>
+      <c r="CB2" s="53"/>
     </row>
-    <row r="3" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B3" s="1"/>
       <c r="C3" s="5"/>
-      <c r="D3" s="48" t="s">
+      <c r="D3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="49"/>
-      <c r="F3" s="48" t="s">
+      <c r="E3" s="51"/>
+      <c r="F3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="49"/>
-      <c r="H3" s="48" t="s">
+      <c r="G3" s="51"/>
+      <c r="H3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="49"/>
-      <c r="J3" s="48" t="s">
+      <c r="I3" s="51"/>
+      <c r="J3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="49"/>
-      <c r="L3" s="48" t="s">
+      <c r="K3" s="51"/>
+      <c r="L3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="49"/>
+      <c r="M3" s="51"/>
       <c r="AA3" s="1"/>
       <c r="AB3" s="5"/>
-      <c r="AC3" s="48" t="s">
+      <c r="AC3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="AD3" s="49"/>
-      <c r="AE3" s="48" t="s">
+      <c r="AD3" s="51"/>
+      <c r="AE3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="AF3" s="49"/>
-      <c r="AG3" s="48" t="s">
+      <c r="AF3" s="51"/>
+      <c r="AG3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="AH3" s="49"/>
-      <c r="AI3" s="48" t="s">
+      <c r="AH3" s="51"/>
+      <c r="AI3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AJ3" s="49"/>
-      <c r="AK3" s="48" t="s">
+      <c r="AJ3" s="51"/>
+      <c r="AK3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="49"/>
+      <c r="AL3" s="51"/>
       <c r="AO3" s="1"/>
       <c r="AP3" s="5"/>
-      <c r="AQ3" s="48" t="s">
+      <c r="AQ3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="AR3" s="49"/>
-      <c r="AS3" s="48" t="s">
+      <c r="AR3" s="51"/>
+      <c r="AS3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="AT3" s="49"/>
-      <c r="AU3" s="48" t="s">
+      <c r="AT3" s="51"/>
+      <c r="AU3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="AV3" s="49"/>
-      <c r="AW3" s="48" t="s">
+      <c r="AV3" s="51"/>
+      <c r="AW3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AX3" s="49"/>
-      <c r="AY3" s="48" t="s">
+      <c r="AX3" s="51"/>
+      <c r="AY3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="AZ3" s="49"/>
+      <c r="AZ3" s="51"/>
       <c r="BC3" s="1"/>
       <c r="BD3" s="5"/>
-      <c r="BE3" s="48" t="s">
+      <c r="BE3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="BF3" s="49"/>
-      <c r="BG3" s="48" t="s">
+      <c r="BF3" s="51"/>
+      <c r="BG3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="BH3" s="49"/>
-      <c r="BI3" s="48" t="s">
+      <c r="BH3" s="51"/>
+      <c r="BI3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="BJ3" s="49"/>
-      <c r="BK3" s="48" t="s">
+      <c r="BJ3" s="51"/>
+      <c r="BK3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="BL3" s="49"/>
-      <c r="BM3" s="48" t="s">
+      <c r="BL3" s="51"/>
+      <c r="BM3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="BN3" s="49"/>
+      <c r="BN3" s="51"/>
       <c r="BQ3" s="1"/>
       <c r="BR3" s="5"/>
-      <c r="BS3" s="48" t="s">
+      <c r="BS3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="BT3" s="49"/>
-      <c r="BU3" s="48" t="s">
+      <c r="BT3" s="51"/>
+      <c r="BU3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="BV3" s="49"/>
-      <c r="BW3" s="48" t="s">
+      <c r="BV3" s="51"/>
+      <c r="BW3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="BX3" s="49"/>
-      <c r="BY3" s="48" t="s">
+      <c r="BX3" s="51"/>
+      <c r="BY3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="BZ3" s="49"/>
-      <c r="CA3" s="48" t="s">
+      <c r="BZ3" s="51"/>
+      <c r="CA3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="CB3" s="49"/>
+      <c r="CB3" s="51"/>
     </row>
-    <row r="4" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B4" s="6" t="s">
         <v>0</v>
       </c>
@@ -8050,8 +8110,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:80" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="52" t="s">
+    <row r="5" spans="2:80" ht="14.7" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="42" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -8087,14 +8147,12 @@
       <c r="M5" s="14">
         <v>82.58</v>
       </c>
-      <c r="AA5" s="42" t="s">
+      <c r="AA5" s="45" t="s">
         <v>13</v>
       </c>
       <c r="AB5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="AC5" s="19"/>
-      <c r="AD5" s="20"/>
       <c r="AE5" s="19">
         <v>66.739999999999995</v>
       </c>
@@ -8111,14 +8169,18 @@
       <c r="AL5" s="20">
         <v>19.14</v>
       </c>
-      <c r="AO5" s="42" t="s">
+      <c r="AO5" s="45" t="s">
         <v>13</v>
       </c>
       <c r="AP5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="AQ5" s="19"/>
-      <c r="AR5" s="20"/>
+      <c r="AQ5" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="AR5" s="20" t="s">
+        <v>52</v>
+      </c>
       <c r="AS5" s="19">
         <v>77.11</v>
       </c>
@@ -8135,7 +8197,7 @@
       <c r="AZ5" s="20">
         <v>19.829999999999998</v>
       </c>
-      <c r="BC5" s="42" t="s">
+      <c r="BC5" s="45" t="s">
         <v>13</v>
       </c>
       <c r="BD5" s="12" t="s">
@@ -8159,7 +8221,7 @@
       <c r="BN5" s="20">
         <v>20.05</v>
       </c>
-      <c r="BQ5" s="42" t="s">
+      <c r="BQ5" s="45" t="s">
         <v>13</v>
       </c>
       <c r="BR5" s="12" t="s">
@@ -8184,7 +8246,7 @@
         <v>20.92</v>
       </c>
     </row>
-    <row r="6" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="43"/>
       <c r="C6" s="9" t="s">
         <v>11</v>
@@ -8223,8 +8285,6 @@
       <c r="AB6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="AC6" s="15"/>
-      <c r="AD6" s="16"/>
       <c r="AE6" s="15">
         <v>66.75</v>
       </c>
@@ -8245,8 +8305,12 @@
       <c r="AP6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="AQ6" s="15"/>
-      <c r="AR6" s="16"/>
+      <c r="AQ6" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR6" s="16" t="s">
+        <v>54</v>
+      </c>
       <c r="AS6" s="15">
         <v>77.12</v>
       </c>
@@ -8308,8 +8372,8 @@
         <v>20.92</v>
       </c>
     </row>
-    <row r="7" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="53"/>
+    <row r="7" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="44"/>
       <c r="C7" s="11" t="s">
         <v>12</v>
       </c>
@@ -8347,8 +8411,6 @@
       <c r="AB7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="AC7" s="15"/>
-      <c r="AD7" s="16"/>
       <c r="AE7" s="15">
         <v>67.03</v>
       </c>
@@ -8369,8 +8431,12 @@
       <c r="AP7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="AQ7" s="15"/>
-      <c r="AR7" s="16"/>
+      <c r="AQ7" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AR7" s="16" t="s">
+        <v>52</v>
+      </c>
       <c r="AS7" s="15">
         <v>77.11</v>
       </c>
@@ -8432,8 +8498,8 @@
         <v>20.49</v>
       </c>
     </row>
-    <row r="8" spans="2:80" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="42" t="s">
+    <row r="8" spans="2:80" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B8" s="45" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="12" t="s">
@@ -8469,12 +8535,10 @@
       <c r="M8" s="20">
         <v>19.09</v>
       </c>
-      <c r="AA8" s="44"/>
+      <c r="AA8" s="46"/>
       <c r="AB8" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="AC8" s="21"/>
-      <c r="AD8" s="22"/>
       <c r="AE8" s="21">
         <v>64.2</v>
       </c>
@@ -8491,12 +8555,16 @@
       <c r="AL8" s="22">
         <v>21.78</v>
       </c>
-      <c r="AO8" s="44"/>
+      <c r="AO8" s="46"/>
       <c r="AP8" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="AQ8" s="21"/>
-      <c r="AR8" s="22"/>
+      <c r="AQ8" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="AR8" s="22" t="s">
+        <v>57</v>
+      </c>
       <c r="AS8" s="21">
         <v>75.72</v>
       </c>
@@ -8513,7 +8581,7 @@
       <c r="AZ8" s="22">
         <v>19.12</v>
       </c>
-      <c r="BC8" s="44"/>
+      <c r="BC8" s="46"/>
       <c r="BD8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8535,7 +8603,7 @@
       <c r="BN8" s="22">
         <v>19.13</v>
       </c>
-      <c r="BQ8" s="44"/>
+      <c r="BQ8" s="46"/>
       <c r="BR8" s="10" t="s">
         <v>14</v>
       </c>
@@ -8558,7 +8626,7 @@
         <v>19.53</v>
       </c>
     </row>
-    <row r="9" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="43"/>
       <c r="C9" s="9" t="s">
         <v>11</v>
@@ -8594,7 +8662,7 @@
         <v>19.09</v>
       </c>
     </row>
-    <row r="10" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B10" s="43"/>
       <c r="C10" s="9" t="s">
         <v>12</v>
@@ -8630,8 +8698,8 @@
         <v>18.829999999999998</v>
       </c>
     </row>
-    <row r="11" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="44"/>
+    <row r="11" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B11" s="46"/>
       <c r="C11" s="10" t="s">
         <v>14</v>
       </c>
@@ -8665,154 +8733,154 @@
       <c r="M11" s="22">
         <v>17.579999999999998</v>
       </c>
-      <c r="AA11" s="45" t="s">
+      <c r="AA11" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="AB11" s="46"/>
-      <c r="AC11" s="46"/>
-      <c r="AD11" s="46"/>
-      <c r="AE11" s="46"/>
-      <c r="AF11" s="46"/>
-      <c r="AG11" s="46"/>
-      <c r="AH11" s="46"/>
-      <c r="AI11" s="46"/>
-      <c r="AJ11" s="46"/>
-      <c r="AK11" s="46"/>
-      <c r="AL11" s="47"/>
-      <c r="AO11" s="45" t="s">
+      <c r="AB11" s="48"/>
+      <c r="AC11" s="48"/>
+      <c r="AD11" s="48"/>
+      <c r="AE11" s="48"/>
+      <c r="AF11" s="48"/>
+      <c r="AG11" s="48"/>
+      <c r="AH11" s="48"/>
+      <c r="AI11" s="48"/>
+      <c r="AJ11" s="48"/>
+      <c r="AK11" s="48"/>
+      <c r="AL11" s="49"/>
+      <c r="AO11" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="AP11" s="46"/>
-      <c r="AQ11" s="46"/>
-      <c r="AR11" s="46"/>
-      <c r="AS11" s="46"/>
-      <c r="AT11" s="46"/>
-      <c r="AU11" s="46"/>
-      <c r="AV11" s="46"/>
-      <c r="AW11" s="46"/>
-      <c r="AX11" s="46"/>
-      <c r="AY11" s="46"/>
-      <c r="AZ11" s="47"/>
-      <c r="BC11" s="45" t="s">
+      <c r="AP11" s="48"/>
+      <c r="AQ11" s="48"/>
+      <c r="AR11" s="48"/>
+      <c r="AS11" s="48"/>
+      <c r="AT11" s="48"/>
+      <c r="AU11" s="48"/>
+      <c r="AV11" s="48"/>
+      <c r="AW11" s="48"/>
+      <c r="AX11" s="48"/>
+      <c r="AY11" s="48"/>
+      <c r="AZ11" s="49"/>
+      <c r="BC11" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="BD11" s="46"/>
-      <c r="BE11" s="46"/>
-      <c r="BF11" s="46"/>
-      <c r="BG11" s="46"/>
-      <c r="BH11" s="46"/>
-      <c r="BI11" s="46"/>
-      <c r="BJ11" s="46"/>
-      <c r="BK11" s="46"/>
-      <c r="BL11" s="46"/>
-      <c r="BM11" s="46"/>
-      <c r="BN11" s="47"/>
-      <c r="BQ11" s="45" t="s">
+      <c r="BD11" s="48"/>
+      <c r="BE11" s="48"/>
+      <c r="BF11" s="48"/>
+      <c r="BG11" s="48"/>
+      <c r="BH11" s="48"/>
+      <c r="BI11" s="48"/>
+      <c r="BJ11" s="48"/>
+      <c r="BK11" s="48"/>
+      <c r="BL11" s="48"/>
+      <c r="BM11" s="48"/>
+      <c r="BN11" s="49"/>
+      <c r="BQ11" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="BR11" s="46"/>
-      <c r="BS11" s="46"/>
-      <c r="BT11" s="46"/>
-      <c r="BU11" s="46"/>
-      <c r="BV11" s="46"/>
-      <c r="BW11" s="46"/>
-      <c r="BX11" s="46"/>
-      <c r="BY11" s="46"/>
-      <c r="BZ11" s="46"/>
-      <c r="CA11" s="46"/>
-      <c r="CB11" s="47"/>
+      <c r="BR11" s="48"/>
+      <c r="BS11" s="48"/>
+      <c r="BT11" s="48"/>
+      <c r="BU11" s="48"/>
+      <c r="BV11" s="48"/>
+      <c r="BW11" s="48"/>
+      <c r="BX11" s="48"/>
+      <c r="BY11" s="48"/>
+      <c r="BZ11" s="48"/>
+      <c r="CA11" s="48"/>
+      <c r="CB11" s="49"/>
     </row>
-    <row r="12" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="AA12" s="24"/>
       <c r="AB12" s="4"/>
-      <c r="AC12" s="48" t="s">
+      <c r="AC12" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="AD12" s="49"/>
-      <c r="AE12" s="48" t="s">
+      <c r="AD12" s="51"/>
+      <c r="AE12" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="AF12" s="49"/>
-      <c r="AG12" s="48" t="s">
+      <c r="AF12" s="51"/>
+      <c r="AG12" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="AH12" s="49"/>
-      <c r="AI12" s="48" t="s">
+      <c r="AH12" s="51"/>
+      <c r="AI12" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AJ12" s="49"/>
-      <c r="AK12" s="48" t="s">
+      <c r="AJ12" s="51"/>
+      <c r="AK12" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="AL12" s="49"/>
+      <c r="AL12" s="51"/>
       <c r="AO12" s="24"/>
       <c r="AP12" s="4"/>
-      <c r="AQ12" s="48" t="s">
+      <c r="AQ12" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="AR12" s="49"/>
-      <c r="AS12" s="48" t="s">
+      <c r="AR12" s="51"/>
+      <c r="AS12" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="AT12" s="49"/>
-      <c r="AU12" s="48" t="s">
+      <c r="AT12" s="51"/>
+      <c r="AU12" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="AV12" s="49"/>
-      <c r="AW12" s="48" t="s">
+      <c r="AV12" s="51"/>
+      <c r="AW12" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AX12" s="49"/>
-      <c r="AY12" s="48" t="s">
+      <c r="AX12" s="51"/>
+      <c r="AY12" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="AZ12" s="49"/>
+      <c r="AZ12" s="51"/>
       <c r="BC12" s="24"/>
       <c r="BD12" s="4"/>
-      <c r="BE12" s="48" t="s">
+      <c r="BE12" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="BF12" s="49"/>
-      <c r="BG12" s="48" t="s">
+      <c r="BF12" s="51"/>
+      <c r="BG12" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="BH12" s="49"/>
-      <c r="BI12" s="48" t="s">
+      <c r="BH12" s="51"/>
+      <c r="BI12" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="BJ12" s="49"/>
-      <c r="BK12" s="48" t="s">
+      <c r="BJ12" s="51"/>
+      <c r="BK12" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="BL12" s="49"/>
-      <c r="BM12" s="48" t="s">
+      <c r="BL12" s="51"/>
+      <c r="BM12" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="BN12" s="49"/>
+      <c r="BN12" s="51"/>
       <c r="BQ12" s="24"/>
       <c r="BR12" s="4"/>
-      <c r="BS12" s="48" t="s">
+      <c r="BS12" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="BT12" s="49"/>
-      <c r="BU12" s="48" t="s">
+      <c r="BT12" s="51"/>
+      <c r="BU12" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="BV12" s="49"/>
-      <c r="BW12" s="48" t="s">
+      <c r="BV12" s="51"/>
+      <c r="BW12" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="BX12" s="49"/>
-      <c r="BY12" s="48" t="s">
+      <c r="BX12" s="51"/>
+      <c r="BY12" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="BZ12" s="49"/>
-      <c r="CA12" s="48" t="s">
+      <c r="BZ12" s="51"/>
+      <c r="CA12" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="CB12" s="49"/>
+      <c r="CB12" s="51"/>
     </row>
-    <row r="13" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="AA13" s="25" t="s">
         <v>16</v>
       </c>
@@ -8958,27 +9026,25 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="45" t="s">
+    <row r="14" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B14" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="47"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="48"/>
+      <c r="M14" s="49"/>
       <c r="AA14" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="AB14" s="36">
-        <v>0.77429999999999999</v>
-      </c>
+      <c r="AB14" s="36"/>
       <c r="AC14" s="30"/>
       <c r="AD14" s="30"/>
       <c r="AE14" s="30"/>
@@ -9034,29 +9100,29 @@
       <c r="CA14" s="30"/>
       <c r="CB14" s="30"/>
     </row>
-    <row r="15" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B15" s="24"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="48" t="s">
+      <c r="D15" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="E15" s="49"/>
-      <c r="F15" s="48" t="s">
+      <c r="E15" s="51"/>
+      <c r="F15" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="49"/>
-      <c r="H15" s="48" t="s">
+      <c r="G15" s="51"/>
+      <c r="H15" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="49"/>
-      <c r="J15" s="48" t="s">
+      <c r="I15" s="51"/>
+      <c r="J15" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="49"/>
-      <c r="L15" s="48" t="s">
+      <c r="K15" s="51"/>
+      <c r="L15" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="M15" s="49"/>
+      <c r="M15" s="51"/>
       <c r="AA15" s="29" t="s">
         <v>39</v>
       </c>
@@ -9114,7 +9180,7 @@
       <c r="CA15" s="30"/>
       <c r="CB15" s="30"/>
     </row>
-    <row r="16" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="25" t="s">
         <v>16</v>
       </c>
@@ -9208,7 +9274,7 @@
       <c r="CA16" s="34"/>
       <c r="CB16" s="34"/>
     </row>
-    <row r="17" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="29" t="s">
         <v>24</v>
       </c>
@@ -9302,7 +9368,7 @@
       <c r="CA17" s="34"/>
       <c r="CB17" s="34"/>
     </row>
-    <row r="18" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="29" t="s">
         <v>50</v>
       </c>
@@ -9394,7 +9460,7 @@
       <c r="CA18" s="30"/>
       <c r="CB18" s="30"/>
     </row>
-    <row r="19" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="29" t="s">
         <v>20</v>
       </c>
@@ -9486,7 +9552,7 @@
       <c r="CA19" s="30"/>
       <c r="CB19" s="30"/>
     </row>
-    <row r="20" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="29" t="s">
         <v>29</v>
       </c>
@@ -9578,7 +9644,7 @@
       <c r="CA20" s="34"/>
       <c r="CB20" s="34"/>
     </row>
-    <row r="21" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="29" t="s">
         <v>25</v>
       </c>
@@ -9617,8 +9683,6 @@
         <v>26</v>
       </c>
       <c r="AB21" s="30"/>
-      <c r="AC21" s="30"/>
-      <c r="AD21" s="30"/>
       <c r="AE21" s="30"/>
       <c r="AF21" s="30"/>
       <c r="AG21" s="30"/>
@@ -9631,8 +9695,12 @@
         <v>26</v>
       </c>
       <c r="AP21" s="30"/>
-      <c r="AQ21" s="30"/>
-      <c r="AR21" s="30"/>
+      <c r="AQ21" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="AR21" t="s">
+        <v>65</v>
+      </c>
       <c r="AS21" s="30"/>
       <c r="AT21" s="30"/>
       <c r="AU21" s="30"/>
@@ -9670,7 +9738,7 @@
       <c r="CA21" s="30"/>
       <c r="CB21" s="30"/>
     </row>
-    <row r="22" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="29" t="s">
         <v>21</v>
       </c>
@@ -9709,8 +9777,6 @@
         <v>22</v>
       </c>
       <c r="AB22" s="30"/>
-      <c r="AC22" s="30"/>
-      <c r="AD22" s="30"/>
       <c r="AF22" s="30"/>
       <c r="AG22" s="30"/>
       <c r="AH22" s="30"/>
@@ -9722,8 +9788,12 @@
         <v>22</v>
       </c>
       <c r="AP22" s="30"/>
-      <c r="AQ22" s="30"/>
-      <c r="AR22" s="30"/>
+      <c r="AQ22" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="AR22" s="30" t="s">
+        <v>66</v>
+      </c>
       <c r="AT22" s="30"/>
       <c r="AU22" s="30"/>
       <c r="AV22" s="30"/>
@@ -9758,7 +9828,7 @@
       <c r="CA22" s="30"/>
       <c r="CB22" s="30"/>
     </row>
-    <row r="23" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="29" t="s">
         <v>30</v>
       </c>
@@ -9797,8 +9867,6 @@
         <v>23</v>
       </c>
       <c r="AB23" s="30"/>
-      <c r="AC23" s="30"/>
-      <c r="AD23" s="30"/>
       <c r="AE23" s="30"/>
       <c r="AF23" s="30"/>
       <c r="AG23" s="30"/>
@@ -9811,8 +9879,12 @@
         <v>23</v>
       </c>
       <c r="AP23" s="30"/>
-      <c r="AQ23" s="30"/>
-      <c r="AR23" s="30"/>
+      <c r="AQ23" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="AR23" s="30" t="s">
+        <v>67</v>
+      </c>
       <c r="AS23" s="30"/>
       <c r="AT23" s="30"/>
       <c r="AU23" s="30"/>
@@ -9850,7 +9922,7 @@
       <c r="CA23" s="30"/>
       <c r="CB23" s="30"/>
     </row>
-    <row r="24" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" s="29" t="s">
         <v>26</v>
       </c>
@@ -9885,8 +9957,6 @@
         <v>31</v>
       </c>
       <c r="AB24" s="30"/>
-      <c r="AC24" s="30"/>
-      <c r="AD24" s="30"/>
       <c r="AE24" s="30">
         <v>48.29</v>
       </c>
@@ -9907,8 +9977,12 @@
         <v>31</v>
       </c>
       <c r="AP24" s="30"/>
-      <c r="AQ24" s="30"/>
-      <c r="AR24" s="30"/>
+      <c r="AQ24" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR24" s="30" t="s">
+        <v>68</v>
+      </c>
       <c r="AS24" s="30">
         <v>45.78</v>
       </c>
@@ -9970,7 +10044,7 @@
         <v>25.74</v>
       </c>
     </row>
-    <row r="25" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="29" t="s">
         <v>22</v>
       </c>
@@ -10006,8 +10080,6 @@
         <v>40</v>
       </c>
       <c r="AB25" s="30"/>
-      <c r="AC25" s="30"/>
-      <c r="AD25" s="30"/>
       <c r="AE25" s="30">
         <v>44.44</v>
       </c>
@@ -10028,8 +10100,12 @@
         <v>40</v>
       </c>
       <c r="AP25" s="30"/>
-      <c r="AQ25" s="30"/>
-      <c r="AR25" s="30"/>
+      <c r="AQ25" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="AR25" s="30" t="s">
+        <v>69</v>
+      </c>
       <c r="AS25" s="30">
         <v>41.72</v>
       </c>
@@ -10091,7 +10167,7 @@
         <v>22.59</v>
       </c>
     </row>
-    <row r="26" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="29" t="s">
         <v>23</v>
       </c>
@@ -10126,8 +10202,6 @@
         <v>27</v>
       </c>
       <c r="AB26" s="30"/>
-      <c r="AC26" s="30"/>
-      <c r="AD26" s="30"/>
       <c r="AE26" s="30"/>
       <c r="AF26" s="30"/>
       <c r="AG26" s="30"/>
@@ -10140,8 +10214,12 @@
         <v>27</v>
       </c>
       <c r="AP26" s="30"/>
-      <c r="AQ26" s="30"/>
-      <c r="AR26" s="30"/>
+      <c r="AQ26" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="AR26" s="30" t="s">
+        <v>70</v>
+      </c>
       <c r="AS26" s="30"/>
       <c r="AT26" s="30"/>
       <c r="AU26" s="30"/>
@@ -10179,7 +10257,7 @@
       <c r="CA26" s="30"/>
       <c r="CB26" s="30"/>
     </row>
-    <row r="27" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" s="29" t="s">
         <v>31</v>
       </c>
@@ -10214,8 +10292,6 @@
         <v>32</v>
       </c>
       <c r="AB27" s="30"/>
-      <c r="AC27" s="30"/>
-      <c r="AD27" s="30"/>
       <c r="AE27" s="30">
         <v>34.159999999999997</v>
       </c>
@@ -10236,8 +10312,12 @@
         <v>32</v>
       </c>
       <c r="AP27" s="30"/>
-      <c r="AQ27" s="30"/>
-      <c r="AR27" s="30"/>
+      <c r="AQ27" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="AR27" s="30" t="s">
+        <v>64</v>
+      </c>
       <c r="AS27" s="30">
         <v>33.619999999999997</v>
       </c>
@@ -10299,7 +10379,7 @@
         <v>64.8</v>
       </c>
     </row>
-    <row r="28" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="29" t="s">
         <v>40</v>
       </c>
@@ -10387,7 +10467,7 @@
       <c r="CA28" s="30"/>
       <c r="CB28" s="30"/>
     </row>
-    <row r="29" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="29" t="s">
         <v>27</v>
       </c>
@@ -10507,7 +10587,7 @@
         <v>93.76</v>
       </c>
     </row>
-    <row r="30" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" s="29" t="s">
         <v>32</v>
       </c>
@@ -10627,7 +10707,7 @@
         <v>93.93</v>
       </c>
     </row>
-    <row r="31" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" s="29" t="s">
         <v>28</v>
       </c>
@@ -10747,7 +10827,7 @@
         <v>94.03</v>
       </c>
     </row>
-    <row r="32" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" s="29" t="s">
         <v>33</v>
       </c>
@@ -10867,7 +10947,7 @@
         <v>94.09</v>
       </c>
     </row>
-    <row r="33" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" s="29" t="s">
         <v>34</v>
       </c>
@@ -10987,7 +11067,7 @@
         <v>94.13</v>
       </c>
     </row>
-    <row r="34" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" s="29" t="s">
         <v>35</v>
       </c>
@@ -11107,7 +11187,7 @@
         <v>94.16</v>
       </c>
     </row>
-    <row r="35" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B35" s="29" t="s">
         <v>36</v>
       </c>
@@ -11191,7 +11271,7 @@
       <c r="CA35" s="38"/>
       <c r="CB35" s="39"/>
     </row>
-    <row r="36" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" s="29" t="s">
         <v>37</v>
       </c>
@@ -11223,7 +11303,7 @@
         <v>13.42</v>
       </c>
     </row>
-    <row r="37" spans="2:80" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" s="29" t="s">
         <v>38</v>
       </c>
@@ -11255,7 +11335,7 @@
         <v>13.38</v>
       </c>
     </row>
-    <row r="38" spans="2:80" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="C38" s="23" t="s">
         <v>17</v>
       </c>
@@ -11274,11 +11354,84 @@
     </row>
   </sheetData>
   <mergeCells count="91">
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="BS35:BT35"/>
+    <mergeCell ref="BU35:BV35"/>
+    <mergeCell ref="BW35:BX35"/>
+    <mergeCell ref="BY35:BZ35"/>
+    <mergeCell ref="CA35:CB35"/>
+    <mergeCell ref="BQ5:BQ8"/>
+    <mergeCell ref="BQ11:CB11"/>
+    <mergeCell ref="BS12:BT12"/>
+    <mergeCell ref="BU12:BV12"/>
+    <mergeCell ref="BW12:BX12"/>
+    <mergeCell ref="BY12:BZ12"/>
+    <mergeCell ref="CA12:CB12"/>
+    <mergeCell ref="BQ2:CB2"/>
+    <mergeCell ref="BS3:BT3"/>
+    <mergeCell ref="BU3:BV3"/>
+    <mergeCell ref="BW3:BX3"/>
+    <mergeCell ref="BY3:BZ3"/>
+    <mergeCell ref="CA3:CB3"/>
+    <mergeCell ref="BE35:BF35"/>
+    <mergeCell ref="BG35:BH35"/>
+    <mergeCell ref="BI35:BJ35"/>
+    <mergeCell ref="BK35:BL35"/>
+    <mergeCell ref="BM35:BN35"/>
+    <mergeCell ref="BC5:BC8"/>
+    <mergeCell ref="BC11:BN11"/>
+    <mergeCell ref="BE12:BF12"/>
+    <mergeCell ref="BG12:BH12"/>
+    <mergeCell ref="BI12:BJ12"/>
+    <mergeCell ref="BK12:BL12"/>
+    <mergeCell ref="BM12:BN12"/>
+    <mergeCell ref="BC2:BN2"/>
+    <mergeCell ref="BE3:BF3"/>
+    <mergeCell ref="BG3:BH3"/>
+    <mergeCell ref="BI3:BJ3"/>
+    <mergeCell ref="BK3:BL3"/>
+    <mergeCell ref="BM3:BN3"/>
+    <mergeCell ref="AQ35:AR35"/>
+    <mergeCell ref="AS35:AT35"/>
+    <mergeCell ref="AU35:AV35"/>
+    <mergeCell ref="AW35:AX35"/>
+    <mergeCell ref="AY35:AZ35"/>
+    <mergeCell ref="AO5:AO8"/>
+    <mergeCell ref="AO11:AZ11"/>
+    <mergeCell ref="AQ12:AR12"/>
+    <mergeCell ref="AS12:AT12"/>
+    <mergeCell ref="AU12:AV12"/>
+    <mergeCell ref="AW12:AX12"/>
+    <mergeCell ref="AY12:AZ12"/>
+    <mergeCell ref="AO2:AZ2"/>
+    <mergeCell ref="AQ3:AR3"/>
+    <mergeCell ref="AS3:AT3"/>
+    <mergeCell ref="AU3:AV3"/>
+    <mergeCell ref="AW3:AX3"/>
+    <mergeCell ref="AY3:AZ3"/>
+    <mergeCell ref="AC35:AD35"/>
+    <mergeCell ref="AE35:AF35"/>
+    <mergeCell ref="AG35:AH35"/>
+    <mergeCell ref="AI35:AJ35"/>
+    <mergeCell ref="AK35:AL35"/>
+    <mergeCell ref="AA5:AA8"/>
+    <mergeCell ref="AA11:AL11"/>
+    <mergeCell ref="AC12:AD12"/>
+    <mergeCell ref="AE12:AF12"/>
+    <mergeCell ref="AG12:AH12"/>
+    <mergeCell ref="AI12:AJ12"/>
+    <mergeCell ref="AK12:AL12"/>
+    <mergeCell ref="AA2:AL2"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="AG3:AH3"/>
+    <mergeCell ref="AI3:AJ3"/>
+    <mergeCell ref="AK3:AL3"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="B14:M14"/>
@@ -11287,84 +11440,11 @@
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="J15:K15"/>
     <mergeCell ref="L15:M15"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="AA2:AL2"/>
-    <mergeCell ref="AC3:AD3"/>
-    <mergeCell ref="AE3:AF3"/>
-    <mergeCell ref="AG3:AH3"/>
-    <mergeCell ref="AI3:AJ3"/>
-    <mergeCell ref="AK3:AL3"/>
-    <mergeCell ref="AA5:AA8"/>
-    <mergeCell ref="AA11:AL11"/>
-    <mergeCell ref="AC12:AD12"/>
-    <mergeCell ref="AE12:AF12"/>
-    <mergeCell ref="AG12:AH12"/>
-    <mergeCell ref="AI12:AJ12"/>
-    <mergeCell ref="AK12:AL12"/>
-    <mergeCell ref="AC35:AD35"/>
-    <mergeCell ref="AE35:AF35"/>
-    <mergeCell ref="AG35:AH35"/>
-    <mergeCell ref="AI35:AJ35"/>
-    <mergeCell ref="AK35:AL35"/>
-    <mergeCell ref="AO2:AZ2"/>
-    <mergeCell ref="AQ3:AR3"/>
-    <mergeCell ref="AS3:AT3"/>
-    <mergeCell ref="AU3:AV3"/>
-    <mergeCell ref="AW3:AX3"/>
-    <mergeCell ref="AY3:AZ3"/>
-    <mergeCell ref="AO5:AO8"/>
-    <mergeCell ref="AO11:AZ11"/>
-    <mergeCell ref="AQ12:AR12"/>
-    <mergeCell ref="AS12:AT12"/>
-    <mergeCell ref="AU12:AV12"/>
-    <mergeCell ref="AW12:AX12"/>
-    <mergeCell ref="AY12:AZ12"/>
-    <mergeCell ref="AQ35:AR35"/>
-    <mergeCell ref="AS35:AT35"/>
-    <mergeCell ref="AU35:AV35"/>
-    <mergeCell ref="AW35:AX35"/>
-    <mergeCell ref="AY35:AZ35"/>
-    <mergeCell ref="BC2:BN2"/>
-    <mergeCell ref="BE3:BF3"/>
-    <mergeCell ref="BG3:BH3"/>
-    <mergeCell ref="BI3:BJ3"/>
-    <mergeCell ref="BK3:BL3"/>
-    <mergeCell ref="BM3:BN3"/>
-    <mergeCell ref="BC5:BC8"/>
-    <mergeCell ref="BC11:BN11"/>
-    <mergeCell ref="BE12:BF12"/>
-    <mergeCell ref="BG12:BH12"/>
-    <mergeCell ref="BI12:BJ12"/>
-    <mergeCell ref="BK12:BL12"/>
-    <mergeCell ref="BM12:BN12"/>
-    <mergeCell ref="BE35:BF35"/>
-    <mergeCell ref="BG35:BH35"/>
-    <mergeCell ref="BI35:BJ35"/>
-    <mergeCell ref="BK35:BL35"/>
-    <mergeCell ref="BM35:BN35"/>
-    <mergeCell ref="BQ2:CB2"/>
-    <mergeCell ref="BS3:BT3"/>
-    <mergeCell ref="BU3:BV3"/>
-    <mergeCell ref="BW3:BX3"/>
-    <mergeCell ref="BY3:BZ3"/>
-    <mergeCell ref="CA3:CB3"/>
-    <mergeCell ref="BQ5:BQ8"/>
-    <mergeCell ref="BQ11:CB11"/>
-    <mergeCell ref="BS12:BT12"/>
-    <mergeCell ref="BU12:BV12"/>
-    <mergeCell ref="BW12:BX12"/>
-    <mergeCell ref="BY12:BZ12"/>
-    <mergeCell ref="CA12:CB12"/>
-    <mergeCell ref="BS35:BT35"/>
-    <mergeCell ref="BU35:BV35"/>
-    <mergeCell ref="BW35:BX35"/>
-    <mergeCell ref="BY35:BZ35"/>
-    <mergeCell ref="CA35:CB35"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="L38:M38"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
